--- a/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
   </numFmts>
-  <fonts count="80">
+  <fonts count="82">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -488,6 +488,16 @@
       <color rgb="00163A70"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="51">
     <fill>
@@ -742,7 +752,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="286">
+  <borders count="309">
     <border>
       <left/>
       <right/>
@@ -3838,11 +3848,237 @@
         <color rgb="000078D4"/>
       </bottom>
     </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="424">
+  <cellXfs count="505">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4865,6 +5101,189 @@
     <xf numFmtId="0" fontId="17" fillId="7" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="288" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="293" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="294" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="295" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="296" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="297" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="288" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="301" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="300" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="304" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="306" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="307" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="308" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="302" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="303" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="301" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="300" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="304" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="306" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="307" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="308" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="302" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="303" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -4938,72 +5357,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>219075</colOff>
-      <row>0</row>
-      <rowOff>257175</rowOff>
-    </from>
-    <ext cx="1552575" cy="438150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>219075</colOff>
-      <row>0</row>
-      <rowOff>257175</rowOff>
-    </from>
-    <ext cx="1552575" cy="438150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5236,837 +5589,2284 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:AN47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.64" customWidth="1" min="1" max="1"/>
-    <col width="10.64" customWidth="1" min="2" max="2"/>
-    <col width="14.18" customWidth="1" min="3" max="3"/>
-    <col width="14.18" customWidth="1" min="4" max="4"/>
-    <col width="14.18" customWidth="1" min="5" max="5"/>
-    <col width="10.64" customWidth="1" min="6" max="6"/>
-    <col width="10.64" customWidth="1" min="7" max="7"/>
-    <col width="14.18" customWidth="1" min="8" max="8"/>
-    <col width="14.18" customWidth="1" min="9" max="9"/>
-    <col width="16.55" customWidth="1" min="10" max="10"/>
-    <col hidden="1" outlineLevel="1" width="13" customWidth="1" min="11" max="16384"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col hidden="1" outlineLevel="1" width="2.33" customWidth="1" min="11" max="16384"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="413" t="n"/>
-      <c r="B1" s="310" t="n"/>
-      <c r="C1" s="414" t="inlineStr">
+      <c r="A1" s="424" t="n"/>
+      <c r="B1" s="496" t="n"/>
+      <c r="C1" s="426" t="inlineStr">
         <is>
           <t>RMA TRACKING LOG</t>
         </is>
       </c>
-      <c r="D1" s="268" t="n"/>
-      <c r="E1" s="268" t="n"/>
-      <c r="F1" s="268" t="n"/>
-      <c r="G1" s="268" t="n"/>
-      <c r="H1" s="310" t="n"/>
-      <c r="I1" s="343" t="inlineStr">
+      <c r="D1" s="497" t="n"/>
+      <c r="E1" s="497" t="n"/>
+      <c r="F1" s="497" t="n"/>
+      <c r="G1" s="497" t="n"/>
+      <c r="H1" s="496" t="n"/>
+      <c r="I1" s="428" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="J1" s="344" t="inlineStr">
+      <c r="J1" s="429" t="inlineStr">
         <is>
           <t>FRM-213</t>
         </is>
       </c>
+      <c r="K1" s="430" t="n"/>
+      <c r="L1" s="430" t="n"/>
+      <c r="M1" s="430" t="n"/>
+      <c r="N1" s="430" t="n"/>
+      <c r="O1" s="430" t="n"/>
+      <c r="P1" s="430" t="n"/>
+      <c r="Q1" s="430" t="n"/>
+      <c r="R1" s="430" t="n"/>
+      <c r="S1" s="430" t="n"/>
+      <c r="T1" s="430" t="n"/>
+      <c r="U1" s="430" t="n"/>
+      <c r="V1" s="430" t="n"/>
+      <c r="W1" s="430" t="n"/>
+      <c r="X1" s="430" t="n"/>
+      <c r="Y1" s="430" t="n"/>
+      <c r="Z1" s="430" t="n"/>
+      <c r="AA1" s="430" t="n"/>
+      <c r="AB1" s="430" t="n"/>
+      <c r="AC1" s="430" t="n"/>
+      <c r="AD1" s="430" t="n"/>
+      <c r="AE1" s="430" t="n"/>
+      <c r="AF1" s="430" t="n"/>
+      <c r="AG1" s="430" t="n"/>
+      <c r="AH1" s="430" t="n"/>
+      <c r="AI1" s="430" t="n"/>
+      <c r="AJ1" s="430" t="n"/>
+      <c r="AK1" s="430" t="n"/>
+      <c r="AL1" s="430" t="n"/>
+      <c r="AM1" s="430" t="n"/>
+      <c r="AN1" s="430" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="B2" s="312" t="n"/>
-      <c r="C2" s="275" t="n"/>
-      <c r="H2" s="312" t="n"/>
-      <c r="I2" s="350" t="inlineStr">
+      <c r="A2" s="498" t="n"/>
+      <c r="B2" s="499" t="n"/>
+      <c r="C2" s="498" t="n"/>
+      <c r="H2" s="499" t="n"/>
+      <c r="I2" s="428" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="J2" s="351" t="inlineStr">
+      <c r="J2" s="429" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
+      <c r="K2" s="430" t="n"/>
+      <c r="L2" s="430" t="n"/>
+      <c r="M2" s="430" t="n"/>
+      <c r="N2" s="430" t="n"/>
+      <c r="O2" s="430" t="n"/>
+      <c r="P2" s="430" t="n"/>
+      <c r="Q2" s="430" t="n"/>
+      <c r="R2" s="430" t="n"/>
+      <c r="S2" s="430" t="n"/>
+      <c r="T2" s="430" t="n"/>
+      <c r="U2" s="430" t="n"/>
+      <c r="V2" s="430" t="n"/>
+      <c r="W2" s="430" t="n"/>
+      <c r="X2" s="430" t="n"/>
+      <c r="Y2" s="430" t="n"/>
+      <c r="Z2" s="430" t="n"/>
+      <c r="AA2" s="430" t="n"/>
+      <c r="AB2" s="430" t="n"/>
+      <c r="AC2" s="430" t="n"/>
+      <c r="AD2" s="430" t="n"/>
+      <c r="AE2" s="430" t="n"/>
+      <c r="AF2" s="430" t="n"/>
+      <c r="AG2" s="430" t="n"/>
+      <c r="AH2" s="430" t="n"/>
+      <c r="AI2" s="430" t="n"/>
+      <c r="AJ2" s="430" t="n"/>
+      <c r="AK2" s="430" t="n"/>
+      <c r="AL2" s="430" t="n"/>
+      <c r="AM2" s="430" t="n"/>
+      <c r="AN2" s="430" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="B3" s="312" t="n"/>
-      <c r="C3" s="282" t="n"/>
-      <c r="D3" s="283" t="n"/>
-      <c r="E3" s="283" t="n"/>
-      <c r="F3" s="283" t="n"/>
-      <c r="G3" s="283" t="n"/>
-      <c r="H3" s="287" t="n"/>
-      <c r="I3" s="350" t="inlineStr">
+      <c r="A3" s="498" t="n"/>
+      <c r="B3" s="499" t="n"/>
+      <c r="C3" s="500" t="n"/>
+      <c r="D3" s="501" t="n"/>
+      <c r="E3" s="501" t="n"/>
+      <c r="F3" s="501" t="n"/>
+      <c r="G3" s="501" t="n"/>
+      <c r="H3" s="502" t="n"/>
+      <c r="I3" s="428" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="J3" s="351" t="inlineStr">
+      <c r="J3" s="429" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
+      <c r="K3" s="430" t="n"/>
+      <c r="L3" s="430" t="n"/>
+      <c r="M3" s="430" t="n"/>
+      <c r="N3" s="430" t="n"/>
+      <c r="O3" s="430" t="n"/>
+      <c r="P3" s="430" t="n"/>
+      <c r="Q3" s="430" t="n"/>
+      <c r="R3" s="430" t="n"/>
+      <c r="S3" s="430" t="n"/>
+      <c r="T3" s="430" t="n"/>
+      <c r="U3" s="430" t="n"/>
+      <c r="V3" s="430" t="n"/>
+      <c r="W3" s="430" t="n"/>
+      <c r="X3" s="430" t="n"/>
+      <c r="Y3" s="430" t="n"/>
+      <c r="Z3" s="430" t="n"/>
+      <c r="AA3" s="430" t="n"/>
+      <c r="AB3" s="430" t="n"/>
+      <c r="AC3" s="430" t="n"/>
+      <c r="AD3" s="430" t="n"/>
+      <c r="AE3" s="430" t="n"/>
+      <c r="AF3" s="430" t="n"/>
+      <c r="AG3" s="430" t="n"/>
+      <c r="AH3" s="430" t="n"/>
+      <c r="AI3" s="430" t="n"/>
+      <c r="AJ3" s="430" t="n"/>
+      <c r="AK3" s="430" t="n"/>
+      <c r="AL3" s="430" t="n"/>
+      <c r="AM3" s="430" t="n"/>
+      <c r="AN3" s="430" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="B4" s="312" t="n"/>
-      <c r="C4" s="415" t="inlineStr">
+      <c r="A4" s="498" t="n"/>
+      <c r="B4" s="499" t="n"/>
+      <c r="C4" s="436" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="289" t="n"/>
-      <c r="E4" s="289" t="n"/>
-      <c r="F4" s="289" t="n"/>
-      <c r="G4" s="289" t="n"/>
-      <c r="H4" s="290" t="n"/>
-      <c r="I4" s="350" t="inlineStr">
+      <c r="D4" s="503" t="n"/>
+      <c r="E4" s="503" t="n"/>
+      <c r="F4" s="503" t="n"/>
+      <c r="G4" s="503" t="n"/>
+      <c r="H4" s="504" t="n"/>
+      <c r="I4" s="428" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="J4" s="351" t="inlineStr">
+      <c r="J4" s="429" t="inlineStr">
         <is>
           <t>QA / Customer Service</t>
         </is>
       </c>
+      <c r="K4" s="430" t="n"/>
+      <c r="L4" s="430" t="n"/>
+      <c r="M4" s="430" t="n"/>
+      <c r="N4" s="430" t="n"/>
+      <c r="O4" s="430" t="n"/>
+      <c r="P4" s="430" t="n"/>
+      <c r="Q4" s="430" t="n"/>
+      <c r="R4" s="430" t="n"/>
+      <c r="S4" s="430" t="n"/>
+      <c r="T4" s="430" t="n"/>
+      <c r="U4" s="430" t="n"/>
+      <c r="V4" s="430" t="n"/>
+      <c r="W4" s="430" t="n"/>
+      <c r="X4" s="430" t="n"/>
+      <c r="Y4" s="430" t="n"/>
+      <c r="Z4" s="430" t="n"/>
+      <c r="AA4" s="430" t="n"/>
+      <c r="AB4" s="430" t="n"/>
+      <c r="AC4" s="430" t="n"/>
+      <c r="AD4" s="430" t="n"/>
+      <c r="AE4" s="430" t="n"/>
+      <c r="AF4" s="430" t="n"/>
+      <c r="AG4" s="430" t="n"/>
+      <c r="AH4" s="430" t="n"/>
+      <c r="AI4" s="430" t="n"/>
+      <c r="AJ4" s="430" t="n"/>
+      <c r="AK4" s="430" t="n"/>
+      <c r="AL4" s="430" t="n"/>
+      <c r="AM4" s="430" t="n"/>
+      <c r="AN4" s="430" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="282" t="n"/>
-      <c r="B5" s="287" t="n"/>
-      <c r="C5" s="416" t="inlineStr">
+      <c r="A5" s="500" t="n"/>
+      <c r="B5" s="502" t="n"/>
+      <c r="C5" s="439" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="289" t="n"/>
-      <c r="E5" s="289" t="n"/>
-      <c r="F5" s="289" t="n"/>
-      <c r="G5" s="289" t="n"/>
-      <c r="H5" s="290" t="n"/>
-      <c r="I5" s="363" t="inlineStr">
+      <c r="D5" s="503" t="n"/>
+      <c r="E5" s="503" t="n"/>
+      <c r="F5" s="503" t="n"/>
+      <c r="G5" s="503" t="n"/>
+      <c r="H5" s="504" t="n"/>
+      <c r="I5" s="440" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="J5" s="364" t="inlineStr">
+      <c r="J5" s="441" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
       </c>
+      <c r="K5" s="430" t="n"/>
+      <c r="L5" s="430" t="n"/>
+      <c r="M5" s="430" t="n"/>
+      <c r="N5" s="430" t="n"/>
+      <c r="O5" s="430" t="n"/>
+      <c r="P5" s="430" t="n"/>
+      <c r="Q5" s="430" t="n"/>
+      <c r="R5" s="430" t="n"/>
+      <c r="S5" s="430" t="n"/>
+      <c r="T5" s="430" t="n"/>
+      <c r="U5" s="430" t="n"/>
+      <c r="V5" s="430" t="n"/>
+      <c r="W5" s="430" t="n"/>
+      <c r="X5" s="430" t="n"/>
+      <c r="Y5" s="430" t="n"/>
+      <c r="Z5" s="430" t="n"/>
+      <c r="AA5" s="430" t="n"/>
+      <c r="AB5" s="430" t="n"/>
+      <c r="AC5" s="430" t="n"/>
+      <c r="AD5" s="430" t="n"/>
+      <c r="AE5" s="430" t="n"/>
+      <c r="AF5" s="430" t="n"/>
+      <c r="AG5" s="430" t="n"/>
+      <c r="AH5" s="430" t="n"/>
+      <c r="AI5" s="430" t="n"/>
+      <c r="AJ5" s="430" t="n"/>
+      <c r="AK5" s="430" t="n"/>
+      <c r="AL5" s="430" t="n"/>
+      <c r="AM5" s="430" t="n"/>
+      <c r="AN5" s="430" t="n"/>
     </row>
     <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="413" t="n"/>
-      <c r="B6" s="289" t="n"/>
-      <c r="C6" s="289" t="n"/>
-      <c r="D6" s="289" t="n"/>
-      <c r="E6" s="289" t="n"/>
-      <c r="F6" s="289" t="n"/>
-      <c r="G6" s="289" t="n"/>
-      <c r="H6" s="289" t="n"/>
-      <c r="I6" s="289" t="n"/>
-      <c r="J6" s="290" t="n"/>
+      <c r="A6" s="442" t="n"/>
+      <c r="B6" s="495" t="n"/>
+      <c r="C6" s="495" t="n"/>
+      <c r="D6" s="495" t="n"/>
+      <c r="E6" s="495" t="n"/>
+      <c r="F6" s="495" t="n"/>
+      <c r="G6" s="495" t="n"/>
+      <c r="H6" s="495" t="n"/>
+      <c r="I6" s="495" t="n"/>
+      <c r="J6" s="495" t="n"/>
+      <c r="K6" s="443" t="n"/>
+      <c r="L6" s="443" t="n"/>
+      <c r="M6" s="443" t="n"/>
+      <c r="N6" s="443" t="n"/>
+      <c r="O6" s="443" t="n"/>
+      <c r="P6" s="443" t="n"/>
+      <c r="Q6" s="443" t="n"/>
+      <c r="R6" s="443" t="n"/>
+      <c r="S6" s="443" t="n"/>
+      <c r="T6" s="443" t="n"/>
+      <c r="U6" s="443" t="n"/>
+      <c r="V6" s="443" t="n"/>
+      <c r="W6" s="443" t="n"/>
+      <c r="X6" s="443" t="n"/>
+      <c r="Y6" s="443" t="n"/>
+      <c r="Z6" s="443" t="n"/>
+      <c r="AA6" s="443" t="n"/>
+      <c r="AB6" s="443" t="n"/>
+      <c r="AC6" s="443" t="n"/>
+      <c r="AD6" s="443" t="n"/>
+      <c r="AE6" s="443" t="n"/>
+      <c r="AF6" s="443" t="n"/>
+      <c r="AG6" s="443" t="n"/>
+      <c r="AH6" s="443" t="n"/>
+      <c r="AI6" s="443" t="n"/>
+      <c r="AJ6" s="443" t="n"/>
+      <c r="AK6" s="443" t="n"/>
+      <c r="AL6" s="443" t="n"/>
+      <c r="AM6" s="443" t="n"/>
+      <c r="AN6" s="443" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="417" t="inlineStr">
+      <c r="A7" s="444" t="inlineStr">
         <is>
           <t>1.  RMA HEADER</t>
         </is>
       </c>
-      <c r="B7" s="289" t="n"/>
-      <c r="C7" s="289" t="n"/>
-      <c r="D7" s="289" t="n"/>
-      <c r="E7" s="289" t="n"/>
-      <c r="F7" s="289" t="n"/>
-      <c r="G7" s="289" t="n"/>
-      <c r="H7" s="289" t="n"/>
-      <c r="I7" s="289" t="n"/>
-      <c r="J7" s="290" t="n"/>
+      <c r="B7" s="503" t="n"/>
+      <c r="C7" s="503" t="n"/>
+      <c r="D7" s="503" t="n"/>
+      <c r="E7" s="503" t="n"/>
+      <c r="F7" s="503" t="n"/>
+      <c r="G7" s="503" t="n"/>
+      <c r="H7" s="503" t="n"/>
+      <c r="I7" s="503" t="n"/>
+      <c r="J7" s="504" t="n"/>
+      <c r="K7" s="430" t="n"/>
+      <c r="L7" s="430" t="n"/>
+      <c r="M7" s="430" t="n"/>
+      <c r="N7" s="430" t="n"/>
+      <c r="O7" s="430" t="n"/>
+      <c r="P7" s="430" t="n"/>
+      <c r="Q7" s="430" t="n"/>
+      <c r="R7" s="430" t="n"/>
+      <c r="S7" s="430" t="n"/>
+      <c r="T7" s="430" t="n"/>
+      <c r="U7" s="430" t="n"/>
+      <c r="V7" s="430" t="n"/>
+      <c r="W7" s="430" t="n"/>
+      <c r="X7" s="430" t="n"/>
+      <c r="Y7" s="430" t="n"/>
+      <c r="Z7" s="430" t="n"/>
+      <c r="AA7" s="430" t="n"/>
+      <c r="AB7" s="430" t="n"/>
+      <c r="AC7" s="430" t="n"/>
+      <c r="AD7" s="430" t="n"/>
+      <c r="AE7" s="430" t="n"/>
+      <c r="AF7" s="430" t="n"/>
+      <c r="AG7" s="430" t="n"/>
+      <c r="AH7" s="430" t="n"/>
+      <c r="AI7" s="430" t="n"/>
+      <c r="AJ7" s="430" t="n"/>
+      <c r="AK7" s="430" t="n"/>
+      <c r="AL7" s="430" t="n"/>
+      <c r="AM7" s="430" t="n"/>
+      <c r="AN7" s="430" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="418" t="inlineStr">
+      <c r="A8" s="440" t="inlineStr">
         <is>
           <t>Open Period</t>
         </is>
       </c>
-      <c r="B8" s="290" t="n"/>
-      <c r="C8" s="419" t="inlineStr"/>
-      <c r="D8" s="289" t="n"/>
-      <c r="E8" s="290" t="n"/>
-      <c r="F8" s="418" t="inlineStr">
+      <c r="B8" s="486" t="n"/>
+      <c r="C8" s="441" t="inlineStr"/>
+      <c r="D8" s="487" t="n"/>
+      <c r="E8" s="486" t="n"/>
+      <c r="F8" s="440" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="G8" s="290" t="n"/>
-      <c r="H8" s="419" t="inlineStr"/>
-      <c r="I8" s="289" t="n"/>
-      <c r="J8" s="290" t="n"/>
+      <c r="G8" s="486" t="n"/>
+      <c r="H8" s="441" t="inlineStr"/>
+      <c r="I8" s="487" t="n"/>
+      <c r="J8" s="486" t="n"/>
+      <c r="K8" s="447" t="n"/>
+      <c r="L8" s="447" t="n"/>
+      <c r="M8" s="447" t="n"/>
+      <c r="N8" s="447" t="n"/>
+      <c r="O8" s="447" t="n"/>
+      <c r="P8" s="447" t="n"/>
+      <c r="Q8" s="447" t="n"/>
+      <c r="R8" s="447" t="n"/>
+      <c r="S8" s="447" t="n"/>
+      <c r="T8" s="447" t="n"/>
+      <c r="U8" s="447" t="n"/>
+      <c r="V8" s="447" t="n"/>
+      <c r="W8" s="447" t="n"/>
+      <c r="X8" s="447" t="n"/>
+      <c r="Y8" s="447" t="n"/>
+      <c r="Z8" s="447" t="n"/>
+      <c r="AA8" s="447" t="n"/>
+      <c r="AB8" s="447" t="n"/>
+      <c r="AC8" s="447" t="n"/>
+      <c r="AD8" s="447" t="n"/>
+      <c r="AE8" s="447" t="n"/>
+      <c r="AF8" s="447" t="n"/>
+      <c r="AG8" s="447" t="n"/>
+      <c r="AH8" s="447" t="n"/>
+      <c r="AI8" s="447" t="n"/>
+      <c r="AJ8" s="447" t="n"/>
+      <c r="AK8" s="447" t="n"/>
+      <c r="AL8" s="447" t="n"/>
+      <c r="AM8" s="447" t="n"/>
+      <c r="AN8" s="447" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="418" t="inlineStr">
+      <c r="A9" s="440" t="inlineStr">
         <is>
           <t>RMA Owner</t>
         </is>
       </c>
-      <c r="B9" s="290" t="n"/>
-      <c r="C9" s="419" t="inlineStr"/>
-      <c r="D9" s="289" t="n"/>
-      <c r="E9" s="290" t="n"/>
-      <c r="F9" s="418" t="inlineStr">
+      <c r="B9" s="486" t="n"/>
+      <c r="C9" s="441" t="inlineStr"/>
+      <c r="D9" s="487" t="n"/>
+      <c r="E9" s="486" t="n"/>
+      <c r="F9" s="440" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="G9" s="290" t="n"/>
-      <c r="H9" s="419" t="inlineStr"/>
-      <c r="I9" s="289" t="n"/>
-      <c r="J9" s="290" t="n"/>
+      <c r="G9" s="486" t="n"/>
+      <c r="H9" s="441" t="inlineStr"/>
+      <c r="I9" s="487" t="n"/>
+      <c r="J9" s="486" t="n"/>
+      <c r="K9" s="447" t="n"/>
+      <c r="L9" s="447" t="n"/>
+      <c r="M9" s="447" t="n"/>
+      <c r="N9" s="447" t="n"/>
+      <c r="O9" s="447" t="n"/>
+      <c r="P9" s="447" t="n"/>
+      <c r="Q9" s="447" t="n"/>
+      <c r="R9" s="447" t="n"/>
+      <c r="S9" s="447" t="n"/>
+      <c r="T9" s="447" t="n"/>
+      <c r="U9" s="447" t="n"/>
+      <c r="V9" s="447" t="n"/>
+      <c r="W9" s="447" t="n"/>
+      <c r="X9" s="447" t="n"/>
+      <c r="Y9" s="447" t="n"/>
+      <c r="Z9" s="447" t="n"/>
+      <c r="AA9" s="447" t="n"/>
+      <c r="AB9" s="447" t="n"/>
+      <c r="AC9" s="447" t="n"/>
+      <c r="AD9" s="447" t="n"/>
+      <c r="AE9" s="447" t="n"/>
+      <c r="AF9" s="447" t="n"/>
+      <c r="AG9" s="447" t="n"/>
+      <c r="AH9" s="447" t="n"/>
+      <c r="AI9" s="447" t="n"/>
+      <c r="AJ9" s="447" t="n"/>
+      <c r="AK9" s="447" t="n"/>
+      <c r="AL9" s="447" t="n"/>
+      <c r="AM9" s="447" t="n"/>
+      <c r="AN9" s="447" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="418" t="inlineStr">
+      <c r="A10" s="440" t="inlineStr">
         <is>
           <t>Evidence Folder</t>
         </is>
       </c>
-      <c r="B10" s="290" t="n"/>
-      <c r="C10" s="419" t="inlineStr"/>
-      <c r="D10" s="289" t="n"/>
-      <c r="E10" s="290" t="n"/>
-      <c r="F10" s="418" t="inlineStr">
+      <c r="B10" s="486" t="n"/>
+      <c r="C10" s="441" t="inlineStr"/>
+      <c r="D10" s="487" t="n"/>
+      <c r="E10" s="486" t="n"/>
+      <c r="F10" s="440" t="inlineStr">
         <is>
           <t>Returned Qty / Condition</t>
         </is>
       </c>
-      <c r="G10" s="290" t="n"/>
-      <c r="H10" s="419" t="inlineStr"/>
-      <c r="I10" s="289" t="n"/>
-      <c r="J10" s="290" t="n"/>
+      <c r="G10" s="486" t="n"/>
+      <c r="H10" s="441" t="inlineStr"/>
+      <c r="I10" s="487" t="n"/>
+      <c r="J10" s="486" t="n"/>
+      <c r="K10" s="447" t="n"/>
+      <c r="L10" s="447" t="n"/>
+      <c r="M10" s="447" t="n"/>
+      <c r="N10" s="447" t="n"/>
+      <c r="O10" s="447" t="n"/>
+      <c r="P10" s="447" t="n"/>
+      <c r="Q10" s="447" t="n"/>
+      <c r="R10" s="447" t="n"/>
+      <c r="S10" s="447" t="n"/>
+      <c r="T10" s="447" t="n"/>
+      <c r="U10" s="447" t="n"/>
+      <c r="V10" s="447" t="n"/>
+      <c r="W10" s="447" t="n"/>
+      <c r="X10" s="447" t="n"/>
+      <c r="Y10" s="447" t="n"/>
+      <c r="Z10" s="447" t="n"/>
+      <c r="AA10" s="447" t="n"/>
+      <c r="AB10" s="447" t="n"/>
+      <c r="AC10" s="447" t="n"/>
+      <c r="AD10" s="447" t="n"/>
+      <c r="AE10" s="447" t="n"/>
+      <c r="AF10" s="447" t="n"/>
+      <c r="AG10" s="447" t="n"/>
+      <c r="AH10" s="447" t="n"/>
+      <c r="AI10" s="447" t="n"/>
+      <c r="AJ10" s="447" t="n"/>
+      <c r="AK10" s="447" t="n"/>
+      <c r="AL10" s="447" t="n"/>
+      <c r="AM10" s="447" t="n"/>
+      <c r="AN10" s="447" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="418" t="inlineStr">
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="440" t="inlineStr">
         <is>
           <t>Receipt Ref. / Date</t>
         </is>
       </c>
-      <c r="B11" s="290" t="n"/>
-      <c r="C11" s="419" t="inlineStr"/>
-      <c r="D11" s="289" t="n"/>
-      <c r="E11" s="290" t="n"/>
-      <c r="F11" s="418" t="inlineStr">
+      <c r="B11" s="485" t="n"/>
+      <c r="C11" s="441" t="inlineStr"/>
+      <c r="D11" s="484" t="n"/>
+      <c r="E11" s="485" t="n"/>
+      <c r="F11" s="440" t="inlineStr">
         <is>
           <t>Evaluation Owner</t>
         </is>
       </c>
-      <c r="G11" s="290" t="n"/>
-      <c r="H11" s="419" t="inlineStr"/>
-      <c r="I11" s="289" t="n"/>
-      <c r="J11" s="290" t="n"/>
+      <c r="G11" s="485" t="n"/>
+      <c r="H11" s="441" t="inlineStr"/>
+      <c r="I11" s="484" t="n"/>
+      <c r="J11" s="485" t="n"/>
+      <c r="K11" s="430" t="n"/>
+      <c r="L11" s="430" t="n"/>
+      <c r="M11" s="430" t="n"/>
+      <c r="N11" s="430" t="n"/>
+      <c r="O11" s="430" t="n"/>
+      <c r="P11" s="430" t="n"/>
+      <c r="Q11" s="430" t="n"/>
+      <c r="R11" s="430" t="n"/>
+      <c r="S11" s="430" t="n"/>
+      <c r="T11" s="430" t="n"/>
+      <c r="U11" s="430" t="n"/>
+      <c r="V11" s="430" t="n"/>
+      <c r="W11" s="430" t="n"/>
+      <c r="X11" s="430" t="n"/>
+      <c r="Y11" s="430" t="n"/>
+      <c r="Z11" s="430" t="n"/>
+      <c r="AA11" s="430" t="n"/>
+      <c r="AB11" s="430" t="n"/>
+      <c r="AC11" s="430" t="n"/>
+      <c r="AD11" s="430" t="n"/>
+      <c r="AE11" s="430" t="n"/>
+      <c r="AF11" s="430" t="n"/>
+      <c r="AG11" s="430" t="n"/>
+      <c r="AH11" s="430" t="n"/>
+      <c r="AI11" s="430" t="n"/>
+      <c r="AJ11" s="430" t="n"/>
+      <c r="AK11" s="430" t="n"/>
+      <c r="AL11" s="430" t="n"/>
+      <c r="AM11" s="430" t="n"/>
+      <c r="AN11" s="430" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="418" t="inlineStr">
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="440" t="inlineStr">
         <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="B12" s="290" t="n"/>
-      <c r="C12" s="419" t="inlineStr"/>
-      <c r="D12" s="289" t="n"/>
-      <c r="E12" s="290" t="n"/>
-      <c r="F12" s="418" t="inlineStr">
+      <c r="B12" s="485" t="n"/>
+      <c r="C12" s="441" t="inlineStr"/>
+      <c r="D12" s="484" t="n"/>
+      <c r="E12" s="485" t="n"/>
+      <c r="F12" s="440" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="G12" s="290" t="n"/>
-      <c r="H12" s="419" t="inlineStr"/>
-      <c r="I12" s="289" t="n"/>
-      <c r="J12" s="290" t="n"/>
+      <c r="G12" s="485" t="n"/>
+      <c r="H12" s="441" t="inlineStr"/>
+      <c r="I12" s="484" t="n"/>
+      <c r="J12" s="485" t="n"/>
+      <c r="K12" s="430" t="n"/>
+      <c r="L12" s="430" t="n"/>
+      <c r="M12" s="430" t="n"/>
+      <c r="N12" s="430" t="n"/>
+      <c r="O12" s="430" t="n"/>
+      <c r="P12" s="430" t="n"/>
+      <c r="Q12" s="430" t="n"/>
+      <c r="R12" s="430" t="n"/>
+      <c r="S12" s="430" t="n"/>
+      <c r="T12" s="430" t="n"/>
+      <c r="U12" s="430" t="n"/>
+      <c r="V12" s="430" t="n"/>
+      <c r="W12" s="430" t="n"/>
+      <c r="X12" s="430" t="n"/>
+      <c r="Y12" s="430" t="n"/>
+      <c r="Z12" s="430" t="n"/>
+      <c r="AA12" s="430" t="n"/>
+      <c r="AB12" s="430" t="n"/>
+      <c r="AC12" s="430" t="n"/>
+      <c r="AD12" s="430" t="n"/>
+      <c r="AE12" s="430" t="n"/>
+      <c r="AF12" s="430" t="n"/>
+      <c r="AG12" s="430" t="n"/>
+      <c r="AH12" s="430" t="n"/>
+      <c r="AI12" s="430" t="n"/>
+      <c r="AJ12" s="430" t="n"/>
+      <c r="AK12" s="430" t="n"/>
+      <c r="AL12" s="430" t="n"/>
+      <c r="AM12" s="430" t="n"/>
+      <c r="AN12" s="430" t="n"/>
     </row>
     <row r="13" ht="4" customHeight="1">
-      <c r="A13" s="413" t="n"/>
-      <c r="B13" s="289" t="n"/>
-      <c r="C13" s="289" t="n"/>
-      <c r="D13" s="289" t="n"/>
-      <c r="E13" s="289" t="n"/>
-      <c r="F13" s="289" t="n"/>
-      <c r="G13" s="289" t="n"/>
-      <c r="H13" s="289" t="n"/>
-      <c r="I13" s="289" t="n"/>
-      <c r="J13" s="290" t="n"/>
+      <c r="A13" s="442" t="n"/>
+      <c r="B13" s="495" t="n"/>
+      <c r="C13" s="495" t="n"/>
+      <c r="D13" s="495" t="n"/>
+      <c r="E13" s="495" t="n"/>
+      <c r="F13" s="495" t="n"/>
+      <c r="G13" s="495" t="n"/>
+      <c r="H13" s="495" t="n"/>
+      <c r="I13" s="495" t="n"/>
+      <c r="J13" s="495" t="n"/>
+      <c r="K13" s="443" t="n"/>
+      <c r="L13" s="443" t="n"/>
+      <c r="M13" s="443" t="n"/>
+      <c r="N13" s="443" t="n"/>
+      <c r="O13" s="443" t="n"/>
+      <c r="P13" s="443" t="n"/>
+      <c r="Q13" s="443" t="n"/>
+      <c r="R13" s="443" t="n"/>
+      <c r="S13" s="443" t="n"/>
+      <c r="T13" s="443" t="n"/>
+      <c r="U13" s="443" t="n"/>
+      <c r="V13" s="443" t="n"/>
+      <c r="W13" s="443" t="n"/>
+      <c r="X13" s="443" t="n"/>
+      <c r="Y13" s="443" t="n"/>
+      <c r="Z13" s="443" t="n"/>
+      <c r="AA13" s="443" t="n"/>
+      <c r="AB13" s="443" t="n"/>
+      <c r="AC13" s="443" t="n"/>
+      <c r="AD13" s="443" t="n"/>
+      <c r="AE13" s="443" t="n"/>
+      <c r="AF13" s="443" t="n"/>
+      <c r="AG13" s="443" t="n"/>
+      <c r="AH13" s="443" t="n"/>
+      <c r="AI13" s="443" t="n"/>
+      <c r="AJ13" s="443" t="n"/>
+      <c r="AK13" s="443" t="n"/>
+      <c r="AL13" s="443" t="n"/>
+      <c r="AM13" s="443" t="n"/>
+      <c r="AN13" s="443" t="n"/>
     </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="417" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="444" t="inlineStr">
         <is>
           <t>2.  RECEIPT AND EVALUATION SECTION</t>
         </is>
       </c>
-      <c r="B14" s="289" t="n"/>
-      <c r="C14" s="289" t="n"/>
-      <c r="D14" s="289" t="n"/>
-      <c r="E14" s="289" t="n"/>
-      <c r="F14" s="289" t="n"/>
-      <c r="G14" s="289" t="n"/>
-      <c r="H14" s="289" t="n"/>
-      <c r="I14" s="289" t="n"/>
-      <c r="J14" s="290" t="n"/>
+      <c r="B14" s="487" t="n"/>
+      <c r="C14" s="487" t="n"/>
+      <c r="D14" s="487" t="n"/>
+      <c r="E14" s="487" t="n"/>
+      <c r="F14" s="487" t="n"/>
+      <c r="G14" s="487" t="n"/>
+      <c r="H14" s="487" t="n"/>
+      <c r="I14" s="487" t="n"/>
+      <c r="J14" s="486" t="n"/>
+      <c r="K14" s="447" t="n"/>
+      <c r="L14" s="447" t="n"/>
+      <c r="M14" s="447" t="n"/>
+      <c r="N14" s="447" t="n"/>
+      <c r="O14" s="447" t="n"/>
+      <c r="P14" s="447" t="n"/>
+      <c r="Q14" s="447" t="n"/>
+      <c r="R14" s="447" t="n"/>
+      <c r="S14" s="447" t="n"/>
+      <c r="T14" s="447" t="n"/>
+      <c r="U14" s="447" t="n"/>
+      <c r="V14" s="447" t="n"/>
+      <c r="W14" s="447" t="n"/>
+      <c r="X14" s="447" t="n"/>
+      <c r="Y14" s="447" t="n"/>
+      <c r="Z14" s="447" t="n"/>
+      <c r="AA14" s="447" t="n"/>
+      <c r="AB14" s="447" t="n"/>
+      <c r="AC14" s="447" t="n"/>
+      <c r="AD14" s="447" t="n"/>
+      <c r="AE14" s="447" t="n"/>
+      <c r="AF14" s="447" t="n"/>
+      <c r="AG14" s="447" t="n"/>
+      <c r="AH14" s="447" t="n"/>
+      <c r="AI14" s="447" t="n"/>
+      <c r="AJ14" s="447" t="n"/>
+      <c r="AK14" s="447" t="n"/>
+      <c r="AL14" s="447" t="n"/>
+      <c r="AM14" s="447" t="n"/>
+      <c r="AN14" s="447" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="418" t="inlineStr">
+      <c r="A15" s="440" t="inlineStr">
         <is>
           <t>Current Scope</t>
         </is>
       </c>
-      <c r="B15" s="290" t="n"/>
-      <c r="C15" s="419" t="inlineStr"/>
-      <c r="D15" s="289" t="n"/>
-      <c r="E15" s="290" t="n"/>
-      <c r="F15" s="418" t="inlineStr">
+      <c r="B15" s="486" t="n"/>
+      <c r="C15" s="441" t="inlineStr"/>
+      <c r="D15" s="487" t="n"/>
+      <c r="E15" s="486" t="n"/>
+      <c r="F15" s="440" t="inlineStr">
         <is>
           <t>Disposition Summary</t>
         </is>
       </c>
-      <c r="G15" s="290" t="n"/>
-      <c r="H15" s="419" t="inlineStr"/>
-      <c r="I15" s="289" t="n"/>
-      <c r="J15" s="290" t="n"/>
+      <c r="G15" s="486" t="n"/>
+      <c r="H15" s="441" t="inlineStr"/>
+      <c r="I15" s="487" t="n"/>
+      <c r="J15" s="486" t="n"/>
+      <c r="K15" s="447" t="n"/>
+      <c r="L15" s="447" t="n"/>
+      <c r="M15" s="447" t="n"/>
+      <c r="N15" s="447" t="n"/>
+      <c r="O15" s="447" t="n"/>
+      <c r="P15" s="447" t="n"/>
+      <c r="Q15" s="447" t="n"/>
+      <c r="R15" s="447" t="n"/>
+      <c r="S15" s="447" t="n"/>
+      <c r="T15" s="447" t="n"/>
+      <c r="U15" s="447" t="n"/>
+      <c r="V15" s="447" t="n"/>
+      <c r="W15" s="447" t="n"/>
+      <c r="X15" s="447" t="n"/>
+      <c r="Y15" s="447" t="n"/>
+      <c r="Z15" s="447" t="n"/>
+      <c r="AA15" s="447" t="n"/>
+      <c r="AB15" s="447" t="n"/>
+      <c r="AC15" s="447" t="n"/>
+      <c r="AD15" s="447" t="n"/>
+      <c r="AE15" s="447" t="n"/>
+      <c r="AF15" s="447" t="n"/>
+      <c r="AG15" s="447" t="n"/>
+      <c r="AH15" s="447" t="n"/>
+      <c r="AI15" s="447" t="n"/>
+      <c r="AJ15" s="447" t="n"/>
+      <c r="AK15" s="447" t="n"/>
+      <c r="AL15" s="447" t="n"/>
+      <c r="AM15" s="447" t="n"/>
+      <c r="AN15" s="447" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="418" t="inlineStr">
+      <c r="A16" s="440" t="inlineStr">
         <is>
           <t>Primary Return / Defect Note</t>
         </is>
       </c>
-      <c r="B16" s="290" t="n"/>
-      <c r="C16" s="419" t="inlineStr"/>
-      <c r="D16" s="289" t="n"/>
-      <c r="E16" s="290" t="n"/>
-      <c r="F16" s="418" t="inlineStr">
+      <c r="B16" s="486" t="n"/>
+      <c r="C16" s="441" t="inlineStr"/>
+      <c r="D16" s="487" t="n"/>
+      <c r="E16" s="486" t="n"/>
+      <c r="F16" s="440" t="inlineStr">
         <is>
           <t>Next Review</t>
         </is>
       </c>
-      <c r="G16" s="290" t="n"/>
-      <c r="H16" s="419" t="inlineStr"/>
-      <c r="I16" s="289" t="n"/>
-      <c r="J16" s="290" t="n"/>
+      <c r="G16" s="486" t="n"/>
+      <c r="H16" s="441" t="inlineStr"/>
+      <c r="I16" s="487" t="n"/>
+      <c r="J16" s="486" t="n"/>
+      <c r="K16" s="447" t="n"/>
+      <c r="L16" s="447" t="n"/>
+      <c r="M16" s="447" t="n"/>
+      <c r="N16" s="447" t="n"/>
+      <c r="O16" s="447" t="n"/>
+      <c r="P16" s="447" t="n"/>
+      <c r="Q16" s="447" t="n"/>
+      <c r="R16" s="447" t="n"/>
+      <c r="S16" s="447" t="n"/>
+      <c r="T16" s="447" t="n"/>
+      <c r="U16" s="447" t="n"/>
+      <c r="V16" s="447" t="n"/>
+      <c r="W16" s="447" t="n"/>
+      <c r="X16" s="447" t="n"/>
+      <c r="Y16" s="447" t="n"/>
+      <c r="Z16" s="447" t="n"/>
+      <c r="AA16" s="447" t="n"/>
+      <c r="AB16" s="447" t="n"/>
+      <c r="AC16" s="447" t="n"/>
+      <c r="AD16" s="447" t="n"/>
+      <c r="AE16" s="447" t="n"/>
+      <c r="AF16" s="447" t="n"/>
+      <c r="AG16" s="447" t="n"/>
+      <c r="AH16" s="447" t="n"/>
+      <c r="AI16" s="447" t="n"/>
+      <c r="AJ16" s="447" t="n"/>
+      <c r="AK16" s="447" t="n"/>
+      <c r="AL16" s="447" t="n"/>
+      <c r="AM16" s="447" t="n"/>
+      <c r="AN16" s="447" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="418" t="inlineStr">
+      <c r="A17" s="440" t="inlineStr">
         <is>
           <t>Action Owner</t>
         </is>
       </c>
-      <c r="B17" s="290" t="n"/>
-      <c r="C17" s="419" t="inlineStr"/>
-      <c r="D17" s="289" t="n"/>
-      <c r="E17" s="290" t="n"/>
-      <c r="F17" s="418" t="inlineStr">
+      <c r="B17" s="486" t="n"/>
+      <c r="C17" s="441" t="inlineStr"/>
+      <c r="D17" s="487" t="n"/>
+      <c r="E17" s="486" t="n"/>
+      <c r="F17" s="440" t="inlineStr">
         <is>
           <t>Next Review Date</t>
         </is>
       </c>
-      <c r="G17" s="290" t="n"/>
-      <c r="H17" s="419" t="inlineStr"/>
-      <c r="I17" s="289" t="n"/>
-      <c r="J17" s="290" t="n"/>
+      <c r="G17" s="486" t="n"/>
+      <c r="H17" s="441" t="inlineStr"/>
+      <c r="I17" s="487" t="n"/>
+      <c r="J17" s="486" t="n"/>
+      <c r="K17" s="447" t="n"/>
+      <c r="L17" s="447" t="n"/>
+      <c r="M17" s="447" t="n"/>
+      <c r="N17" s="447" t="n"/>
+      <c r="O17" s="447" t="n"/>
+      <c r="P17" s="447" t="n"/>
+      <c r="Q17" s="447" t="n"/>
+      <c r="R17" s="447" t="n"/>
+      <c r="S17" s="447" t="n"/>
+      <c r="T17" s="447" t="n"/>
+      <c r="U17" s="447" t="n"/>
+      <c r="V17" s="447" t="n"/>
+      <c r="W17" s="447" t="n"/>
+      <c r="X17" s="447" t="n"/>
+      <c r="Y17" s="447" t="n"/>
+      <c r="Z17" s="447" t="n"/>
+      <c r="AA17" s="447" t="n"/>
+      <c r="AB17" s="447" t="n"/>
+      <c r="AC17" s="447" t="n"/>
+      <c r="AD17" s="447" t="n"/>
+      <c r="AE17" s="447" t="n"/>
+      <c r="AF17" s="447" t="n"/>
+      <c r="AG17" s="447" t="n"/>
+      <c r="AH17" s="447" t="n"/>
+      <c r="AI17" s="447" t="n"/>
+      <c r="AJ17" s="447" t="n"/>
+      <c r="AK17" s="447" t="n"/>
+      <c r="AL17" s="447" t="n"/>
+      <c r="AM17" s="447" t="n"/>
+      <c r="AN17" s="447" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="418" t="inlineStr">
+      <c r="A18" s="440" t="inlineStr">
         <is>
           <t>Escalation if Not Disposed</t>
         </is>
       </c>
-      <c r="B18" s="290" t="n"/>
-      <c r="C18" s="419" t="inlineStr"/>
-      <c r="D18" s="289" t="n"/>
-      <c r="E18" s="290" t="n"/>
-      <c r="F18" s="418" t="inlineStr">
+      <c r="B18" s="486" t="n"/>
+      <c r="C18" s="441" t="inlineStr"/>
+      <c r="D18" s="487" t="n"/>
+      <c r="E18" s="486" t="n"/>
+      <c r="F18" s="440" t="inlineStr">
         <is>
           <t>Overall Status</t>
         </is>
       </c>
-      <c r="G18" s="290" t="n"/>
-      <c r="H18" s="419" t="inlineStr"/>
-      <c r="I18" s="289" t="n"/>
-      <c r="J18" s="290" t="n"/>
+      <c r="G18" s="486" t="n"/>
+      <c r="H18" s="441" t="inlineStr"/>
+      <c r="I18" s="487" t="n"/>
+      <c r="J18" s="486" t="n"/>
+      <c r="K18" s="447" t="n"/>
+      <c r="L18" s="447" t="n"/>
+      <c r="M18" s="447" t="n"/>
+      <c r="N18" s="447" t="n"/>
+      <c r="O18" s="447" t="n"/>
+      <c r="P18" s="447" t="n"/>
+      <c r="Q18" s="447" t="n"/>
+      <c r="R18" s="447" t="n"/>
+      <c r="S18" s="447" t="n"/>
+      <c r="T18" s="447" t="n"/>
+      <c r="U18" s="447" t="n"/>
+      <c r="V18" s="447" t="n"/>
+      <c r="W18" s="447" t="n"/>
+      <c r="X18" s="447" t="n"/>
+      <c r="Y18" s="447" t="n"/>
+      <c r="Z18" s="447" t="n"/>
+      <c r="AA18" s="447" t="n"/>
+      <c r="AB18" s="447" t="n"/>
+      <c r="AC18" s="447" t="n"/>
+      <c r="AD18" s="447" t="n"/>
+      <c r="AE18" s="447" t="n"/>
+      <c r="AF18" s="447" t="n"/>
+      <c r="AG18" s="447" t="n"/>
+      <c r="AH18" s="447" t="n"/>
+      <c r="AI18" s="447" t="n"/>
+      <c r="AJ18" s="447" t="n"/>
+      <c r="AK18" s="447" t="n"/>
+      <c r="AL18" s="447" t="n"/>
+      <c r="AM18" s="447" t="n"/>
+      <c r="AN18" s="447" t="n"/>
     </row>
     <row r="19" ht="4" customHeight="1">
-      <c r="A19" s="413" t="n"/>
-      <c r="B19" s="289" t="n"/>
-      <c r="C19" s="289" t="n"/>
-      <c r="D19" s="289" t="n"/>
-      <c r="E19" s="289" t="n"/>
-      <c r="F19" s="289" t="n"/>
-      <c r="G19" s="289" t="n"/>
-      <c r="H19" s="289" t="n"/>
-      <c r="I19" s="289" t="n"/>
-      <c r="J19" s="290" t="n"/>
+      <c r="A19" s="442" t="n"/>
+      <c r="B19" s="495" t="n"/>
+      <c r="C19" s="495" t="n"/>
+      <c r="D19" s="495" t="n"/>
+      <c r="E19" s="495" t="n"/>
+      <c r="F19" s="495" t="n"/>
+      <c r="G19" s="495" t="n"/>
+      <c r="H19" s="495" t="n"/>
+      <c r="I19" s="495" t="n"/>
+      <c r="J19" s="495" t="n"/>
+      <c r="K19" s="443" t="n"/>
+      <c r="L19" s="443" t="n"/>
+      <c r="M19" s="443" t="n"/>
+      <c r="N19" s="443" t="n"/>
+      <c r="O19" s="443" t="n"/>
+      <c r="P19" s="443" t="n"/>
+      <c r="Q19" s="443" t="n"/>
+      <c r="R19" s="443" t="n"/>
+      <c r="S19" s="443" t="n"/>
+      <c r="T19" s="443" t="n"/>
+      <c r="U19" s="443" t="n"/>
+      <c r="V19" s="443" t="n"/>
+      <c r="W19" s="443" t="n"/>
+      <c r="X19" s="443" t="n"/>
+      <c r="Y19" s="443" t="n"/>
+      <c r="Z19" s="443" t="n"/>
+      <c r="AA19" s="443" t="n"/>
+      <c r="AB19" s="443" t="n"/>
+      <c r="AC19" s="443" t="n"/>
+      <c r="AD19" s="443" t="n"/>
+      <c r="AE19" s="443" t="n"/>
+      <c r="AF19" s="443" t="n"/>
+      <c r="AG19" s="443" t="n"/>
+      <c r="AH19" s="443" t="n"/>
+      <c r="AI19" s="443" t="n"/>
+      <c r="AJ19" s="443" t="n"/>
+      <c r="AK19" s="443" t="n"/>
+      <c r="AL19" s="443" t="n"/>
+      <c r="AM19" s="443" t="n"/>
+      <c r="AN19" s="443" t="n"/>
     </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="417" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="444" t="inlineStr">
         <is>
           <t>3.  DISPOSITION SECTION</t>
         </is>
       </c>
-      <c r="B20" s="289" t="n"/>
-      <c r="C20" s="289" t="n"/>
-      <c r="D20" s="289" t="n"/>
-      <c r="E20" s="289" t="n"/>
-      <c r="F20" s="289" t="n"/>
-      <c r="G20" s="289" t="n"/>
-      <c r="H20" s="289" t="n"/>
-      <c r="I20" s="289" t="n"/>
-      <c r="J20" s="290" t="n"/>
+      <c r="B20" s="487" t="n"/>
+      <c r="C20" s="487" t="n"/>
+      <c r="D20" s="487" t="n"/>
+      <c r="E20" s="487" t="n"/>
+      <c r="F20" s="487" t="n"/>
+      <c r="G20" s="487" t="n"/>
+      <c r="H20" s="487" t="n"/>
+      <c r="I20" s="487" t="n"/>
+      <c r="J20" s="486" t="n"/>
+      <c r="K20" s="447" t="n"/>
+      <c r="L20" s="447" t="n"/>
+      <c r="M20" s="447" t="n"/>
+      <c r="N20" s="447" t="n"/>
+      <c r="O20" s="447" t="n"/>
+      <c r="P20" s="447" t="n"/>
+      <c r="Q20" s="447" t="n"/>
+      <c r="R20" s="447" t="n"/>
+      <c r="S20" s="447" t="n"/>
+      <c r="T20" s="447" t="n"/>
+      <c r="U20" s="447" t="n"/>
+      <c r="V20" s="447" t="n"/>
+      <c r="W20" s="447" t="n"/>
+      <c r="X20" s="447" t="n"/>
+      <c r="Y20" s="447" t="n"/>
+      <c r="Z20" s="447" t="n"/>
+      <c r="AA20" s="447" t="n"/>
+      <c r="AB20" s="447" t="n"/>
+      <c r="AC20" s="447" t="n"/>
+      <c r="AD20" s="447" t="n"/>
+      <c r="AE20" s="447" t="n"/>
+      <c r="AF20" s="447" t="n"/>
+      <c r="AG20" s="447" t="n"/>
+      <c r="AH20" s="447" t="n"/>
+      <c r="AI20" s="447" t="n"/>
+      <c r="AJ20" s="447" t="n"/>
+      <c r="AK20" s="447" t="n"/>
+      <c r="AL20" s="447" t="n"/>
+      <c r="AM20" s="447" t="n"/>
+      <c r="AN20" s="447" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="376" t="inlineStr">
+      <c r="A21" s="448" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B21" s="377" t="inlineStr">
+      <c r="B21" s="448" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="C21" s="377" t="inlineStr">
+      <c r="C21" s="448" t="inlineStr">
         <is>
           <t>RMA ID</t>
         </is>
       </c>
-      <c r="D21" s="377" t="inlineStr">
+      <c r="D21" s="448" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="E21" s="377" t="inlineStr">
+      <c r="E21" s="448" t="inlineStr">
         <is>
           <t>Part / Revision</t>
         </is>
       </c>
-      <c r="F21" s="377" t="inlineStr">
+      <c r="F21" s="448" t="inlineStr">
         <is>
           <t>Qty / Condition</t>
         </is>
       </c>
-      <c r="G21" s="377" t="inlineStr">
+      <c r="G21" s="448" t="inlineStr">
         <is>
           <t>Disposition</t>
         </is>
       </c>
-      <c r="H21" s="377" t="inlineStr">
+      <c r="H21" s="448" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="I21" s="377" t="inlineStr">
+      <c r="I21" s="448" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J21" s="378" t="inlineStr">
+      <c r="J21" s="449" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
+      <c r="K21" s="447" t="n"/>
+      <c r="L21" s="447" t="n"/>
+      <c r="M21" s="447" t="n"/>
+      <c r="N21" s="447" t="n"/>
+      <c r="O21" s="447" t="n"/>
+      <c r="P21" s="447" t="n"/>
+      <c r="Q21" s="447" t="n"/>
+      <c r="R21" s="447" t="n"/>
+      <c r="S21" s="447" t="n"/>
+      <c r="T21" s="447" t="n"/>
+      <c r="U21" s="447" t="n"/>
+      <c r="V21" s="447" t="n"/>
+      <c r="W21" s="447" t="n"/>
+      <c r="X21" s="447" t="n"/>
+      <c r="Y21" s="447" t="n"/>
+      <c r="Z21" s="447" t="n"/>
+      <c r="AA21" s="447" t="n"/>
+      <c r="AB21" s="447" t="n"/>
+      <c r="AC21" s="447" t="n"/>
+      <c r="AD21" s="447" t="n"/>
+      <c r="AE21" s="447" t="n"/>
+      <c r="AF21" s="447" t="n"/>
+      <c r="AG21" s="447" t="n"/>
+      <c r="AH21" s="447" t="n"/>
+      <c r="AI21" s="447" t="n"/>
+      <c r="AJ21" s="447" t="n"/>
+      <c r="AK21" s="447" t="n"/>
+      <c r="AL21" s="447" t="n"/>
+      <c r="AM21" s="447" t="n"/>
+      <c r="AN21" s="447" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="379">
+      <c r="A22" s="450">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B22" s="380" t="n"/>
-      <c r="C22" s="381" t="n"/>
-      <c r="D22" s="381" t="n"/>
-      <c r="E22" s="381" t="n"/>
-      <c r="F22" s="381" t="n"/>
-      <c r="G22" s="381" t="n"/>
-      <c r="H22" s="381" t="n"/>
-      <c r="I22" s="381" t="n"/>
-      <c r="J22" s="351" t="n"/>
+      <c r="B22" s="451" t="n"/>
+      <c r="C22" s="452" t="n"/>
+      <c r="D22" s="452" t="n"/>
+      <c r="E22" s="452" t="n"/>
+      <c r="F22" s="452" t="n"/>
+      <c r="G22" s="452" t="n"/>
+      <c r="H22" s="452" t="n"/>
+      <c r="I22" s="452" t="n"/>
+      <c r="J22" s="429" t="n"/>
+      <c r="K22" s="447" t="n"/>
+      <c r="L22" s="447" t="n"/>
+      <c r="M22" s="447" t="n"/>
+      <c r="N22" s="447" t="n"/>
+      <c r="O22" s="447" t="n"/>
+      <c r="P22" s="447" t="n"/>
+      <c r="Q22" s="447" t="n"/>
+      <c r="R22" s="447" t="n"/>
+      <c r="S22" s="447" t="n"/>
+      <c r="T22" s="447" t="n"/>
+      <c r="U22" s="447" t="n"/>
+      <c r="V22" s="447" t="n"/>
+      <c r="W22" s="447" t="n"/>
+      <c r="X22" s="447" t="n"/>
+      <c r="Y22" s="447" t="n"/>
+      <c r="Z22" s="447" t="n"/>
+      <c r="AA22" s="447" t="n"/>
+      <c r="AB22" s="447" t="n"/>
+      <c r="AC22" s="447" t="n"/>
+      <c r="AD22" s="447" t="n"/>
+      <c r="AE22" s="447" t="n"/>
+      <c r="AF22" s="447" t="n"/>
+      <c r="AG22" s="447" t="n"/>
+      <c r="AH22" s="447" t="n"/>
+      <c r="AI22" s="447" t="n"/>
+      <c r="AJ22" s="447" t="n"/>
+      <c r="AK22" s="447" t="n"/>
+      <c r="AL22" s="447" t="n"/>
+      <c r="AM22" s="447" t="n"/>
+      <c r="AN22" s="447" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="379">
+      <c r="A23" s="450">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B23" s="382" t="n"/>
-      <c r="C23" s="383" t="n"/>
-      <c r="D23" s="383" t="n"/>
-      <c r="E23" s="383" t="n"/>
-      <c r="F23" s="383" t="n"/>
-      <c r="G23" s="383" t="n"/>
-      <c r="H23" s="383" t="n"/>
-      <c r="I23" s="383" t="n"/>
-      <c r="J23" s="384" t="n"/>
+      <c r="B23" s="453" t="n"/>
+      <c r="C23" s="454" t="n"/>
+      <c r="D23" s="454" t="n"/>
+      <c r="E23" s="454" t="n"/>
+      <c r="F23" s="454" t="n"/>
+      <c r="G23" s="454" t="n"/>
+      <c r="H23" s="454" t="n"/>
+      <c r="I23" s="454" t="n"/>
+      <c r="J23" s="455" t="n"/>
+      <c r="K23" s="447" t="n"/>
+      <c r="L23" s="447" t="n"/>
+      <c r="M23" s="447" t="n"/>
+      <c r="N23" s="447" t="n"/>
+      <c r="O23" s="447" t="n"/>
+      <c r="P23" s="447" t="n"/>
+      <c r="Q23" s="447" t="n"/>
+      <c r="R23" s="447" t="n"/>
+      <c r="S23" s="447" t="n"/>
+      <c r="T23" s="447" t="n"/>
+      <c r="U23" s="447" t="n"/>
+      <c r="V23" s="447" t="n"/>
+      <c r="W23" s="447" t="n"/>
+      <c r="X23" s="447" t="n"/>
+      <c r="Y23" s="447" t="n"/>
+      <c r="Z23" s="447" t="n"/>
+      <c r="AA23" s="447" t="n"/>
+      <c r="AB23" s="447" t="n"/>
+      <c r="AC23" s="447" t="n"/>
+      <c r="AD23" s="447" t="n"/>
+      <c r="AE23" s="447" t="n"/>
+      <c r="AF23" s="447" t="n"/>
+      <c r="AG23" s="447" t="n"/>
+      <c r="AH23" s="447" t="n"/>
+      <c r="AI23" s="447" t="n"/>
+      <c r="AJ23" s="447" t="n"/>
+      <c r="AK23" s="447" t="n"/>
+      <c r="AL23" s="447" t="n"/>
+      <c r="AM23" s="447" t="n"/>
+      <c r="AN23" s="447" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="379">
+      <c r="A24" s="450">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B24" s="380" t="n"/>
-      <c r="C24" s="381" t="n"/>
-      <c r="D24" s="381" t="n"/>
-      <c r="E24" s="381" t="n"/>
-      <c r="F24" s="381" t="n"/>
-      <c r="G24" s="381" t="n"/>
-      <c r="H24" s="381" t="n"/>
-      <c r="I24" s="381" t="n"/>
-      <c r="J24" s="351" t="n"/>
+      <c r="B24" s="451" t="n"/>
+      <c r="C24" s="452" t="n"/>
+      <c r="D24" s="452" t="n"/>
+      <c r="E24" s="452" t="n"/>
+      <c r="F24" s="452" t="n"/>
+      <c r="G24" s="452" t="n"/>
+      <c r="H24" s="452" t="n"/>
+      <c r="I24" s="452" t="n"/>
+      <c r="J24" s="429" t="n"/>
+      <c r="K24" s="447" t="n"/>
+      <c r="L24" s="447" t="n"/>
+      <c r="M24" s="447" t="n"/>
+      <c r="N24" s="447" t="n"/>
+      <c r="O24" s="447" t="n"/>
+      <c r="P24" s="447" t="n"/>
+      <c r="Q24" s="447" t="n"/>
+      <c r="R24" s="447" t="n"/>
+      <c r="S24" s="447" t="n"/>
+      <c r="T24" s="447" t="n"/>
+      <c r="U24" s="447" t="n"/>
+      <c r="V24" s="447" t="n"/>
+      <c r="W24" s="447" t="n"/>
+      <c r="X24" s="447" t="n"/>
+      <c r="Y24" s="447" t="n"/>
+      <c r="Z24" s="447" t="n"/>
+      <c r="AA24" s="447" t="n"/>
+      <c r="AB24" s="447" t="n"/>
+      <c r="AC24" s="447" t="n"/>
+      <c r="AD24" s="447" t="n"/>
+      <c r="AE24" s="447" t="n"/>
+      <c r="AF24" s="447" t="n"/>
+      <c r="AG24" s="447" t="n"/>
+      <c r="AH24" s="447" t="n"/>
+      <c r="AI24" s="447" t="n"/>
+      <c r="AJ24" s="447" t="n"/>
+      <c r="AK24" s="447" t="n"/>
+      <c r="AL24" s="447" t="n"/>
+      <c r="AM24" s="447" t="n"/>
+      <c r="AN24" s="447" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="379">
+      <c r="A25" s="450">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B25" s="382" t="n"/>
-      <c r="C25" s="383" t="n"/>
-      <c r="D25" s="383" t="n"/>
-      <c r="E25" s="383" t="n"/>
-      <c r="F25" s="383" t="n"/>
-      <c r="G25" s="383" t="n"/>
-      <c r="H25" s="383" t="n"/>
-      <c r="I25" s="383" t="n"/>
-      <c r="J25" s="384" t="n"/>
+      <c r="B25" s="453" t="n"/>
+      <c r="C25" s="454" t="n"/>
+      <c r="D25" s="454" t="n"/>
+      <c r="E25" s="454" t="n"/>
+      <c r="F25" s="454" t="n"/>
+      <c r="G25" s="454" t="n"/>
+      <c r="H25" s="454" t="n"/>
+      <c r="I25" s="454" t="n"/>
+      <c r="J25" s="455" t="n"/>
+      <c r="K25" s="447" t="n"/>
+      <c r="L25" s="447" t="n"/>
+      <c r="M25" s="447" t="n"/>
+      <c r="N25" s="447" t="n"/>
+      <c r="O25" s="447" t="n"/>
+      <c r="P25" s="447" t="n"/>
+      <c r="Q25" s="447" t="n"/>
+      <c r="R25" s="447" t="n"/>
+      <c r="S25" s="447" t="n"/>
+      <c r="T25" s="447" t="n"/>
+      <c r="U25" s="447" t="n"/>
+      <c r="V25" s="447" t="n"/>
+      <c r="W25" s="447" t="n"/>
+      <c r="X25" s="447" t="n"/>
+      <c r="Y25" s="447" t="n"/>
+      <c r="Z25" s="447" t="n"/>
+      <c r="AA25" s="447" t="n"/>
+      <c r="AB25" s="447" t="n"/>
+      <c r="AC25" s="447" t="n"/>
+      <c r="AD25" s="447" t="n"/>
+      <c r="AE25" s="447" t="n"/>
+      <c r="AF25" s="447" t="n"/>
+      <c r="AG25" s="447" t="n"/>
+      <c r="AH25" s="447" t="n"/>
+      <c r="AI25" s="447" t="n"/>
+      <c r="AJ25" s="447" t="n"/>
+      <c r="AK25" s="447" t="n"/>
+      <c r="AL25" s="447" t="n"/>
+      <c r="AM25" s="447" t="n"/>
+      <c r="AN25" s="447" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="379">
+      <c r="A26" s="450">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B26" s="380" t="n"/>
-      <c r="C26" s="381" t="n"/>
-      <c r="D26" s="381" t="n"/>
-      <c r="E26" s="381" t="n"/>
-      <c r="F26" s="381" t="n"/>
-      <c r="G26" s="381" t="n"/>
-      <c r="H26" s="381" t="n"/>
-      <c r="I26" s="381" t="n"/>
-      <c r="J26" s="351" t="n"/>
+      <c r="B26" s="451" t="n"/>
+      <c r="C26" s="452" t="n"/>
+      <c r="D26" s="452" t="n"/>
+      <c r="E26" s="452" t="n"/>
+      <c r="F26" s="452" t="n"/>
+      <c r="G26" s="452" t="n"/>
+      <c r="H26" s="452" t="n"/>
+      <c r="I26" s="452" t="n"/>
+      <c r="J26" s="429" t="n"/>
+      <c r="K26" s="447" t="n"/>
+      <c r="L26" s="447" t="n"/>
+      <c r="M26" s="447" t="n"/>
+      <c r="N26" s="447" t="n"/>
+      <c r="O26" s="447" t="n"/>
+      <c r="P26" s="447" t="n"/>
+      <c r="Q26" s="447" t="n"/>
+      <c r="R26" s="447" t="n"/>
+      <c r="S26" s="447" t="n"/>
+      <c r="T26" s="447" t="n"/>
+      <c r="U26" s="447" t="n"/>
+      <c r="V26" s="447" t="n"/>
+      <c r="W26" s="447" t="n"/>
+      <c r="X26" s="447" t="n"/>
+      <c r="Y26" s="447" t="n"/>
+      <c r="Z26" s="447" t="n"/>
+      <c r="AA26" s="447" t="n"/>
+      <c r="AB26" s="447" t="n"/>
+      <c r="AC26" s="447" t="n"/>
+      <c r="AD26" s="447" t="n"/>
+      <c r="AE26" s="447" t="n"/>
+      <c r="AF26" s="447" t="n"/>
+      <c r="AG26" s="447" t="n"/>
+      <c r="AH26" s="447" t="n"/>
+      <c r="AI26" s="447" t="n"/>
+      <c r="AJ26" s="447" t="n"/>
+      <c r="AK26" s="447" t="n"/>
+      <c r="AL26" s="447" t="n"/>
+      <c r="AM26" s="447" t="n"/>
+      <c r="AN26" s="447" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="379">
+      <c r="A27" s="450">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B27" s="382" t="n"/>
-      <c r="C27" s="383" t="n"/>
-      <c r="D27" s="383" t="n"/>
-      <c r="E27" s="383" t="n"/>
-      <c r="F27" s="383" t="n"/>
-      <c r="G27" s="383" t="n"/>
-      <c r="H27" s="383" t="n"/>
-      <c r="I27" s="383" t="n"/>
-      <c r="J27" s="384" t="n"/>
+      <c r="B27" s="453" t="n"/>
+      <c r="C27" s="454" t="n"/>
+      <c r="D27" s="454" t="n"/>
+      <c r="E27" s="454" t="n"/>
+      <c r="F27" s="454" t="n"/>
+      <c r="G27" s="454" t="n"/>
+      <c r="H27" s="454" t="n"/>
+      <c r="I27" s="454" t="n"/>
+      <c r="J27" s="455" t="n"/>
+      <c r="K27" s="447" t="n"/>
+      <c r="L27" s="447" t="n"/>
+      <c r="M27" s="447" t="n"/>
+      <c r="N27" s="447" t="n"/>
+      <c r="O27" s="447" t="n"/>
+      <c r="P27" s="447" t="n"/>
+      <c r="Q27" s="447" t="n"/>
+      <c r="R27" s="447" t="n"/>
+      <c r="S27" s="447" t="n"/>
+      <c r="T27" s="447" t="n"/>
+      <c r="U27" s="447" t="n"/>
+      <c r="V27" s="447" t="n"/>
+      <c r="W27" s="447" t="n"/>
+      <c r="X27" s="447" t="n"/>
+      <c r="Y27" s="447" t="n"/>
+      <c r="Z27" s="447" t="n"/>
+      <c r="AA27" s="447" t="n"/>
+      <c r="AB27" s="447" t="n"/>
+      <c r="AC27" s="447" t="n"/>
+      <c r="AD27" s="447" t="n"/>
+      <c r="AE27" s="447" t="n"/>
+      <c r="AF27" s="447" t="n"/>
+      <c r="AG27" s="447" t="n"/>
+      <c r="AH27" s="447" t="n"/>
+      <c r="AI27" s="447" t="n"/>
+      <c r="AJ27" s="447" t="n"/>
+      <c r="AK27" s="447" t="n"/>
+      <c r="AL27" s="447" t="n"/>
+      <c r="AM27" s="447" t="n"/>
+      <c r="AN27" s="447" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="379">
+      <c r="A28" s="450">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B28" s="380" t="n"/>
-      <c r="C28" s="381" t="n"/>
-      <c r="D28" s="381" t="n"/>
-      <c r="E28" s="381" t="n"/>
-      <c r="F28" s="381" t="n"/>
-      <c r="G28" s="381" t="n"/>
-      <c r="H28" s="381" t="n"/>
-      <c r="I28" s="381" t="n"/>
-      <c r="J28" s="351" t="n"/>
+      <c r="B28" s="451" t="n"/>
+      <c r="C28" s="452" t="n"/>
+      <c r="D28" s="452" t="n"/>
+      <c r="E28" s="452" t="n"/>
+      <c r="F28" s="452" t="n"/>
+      <c r="G28" s="452" t="n"/>
+      <c r="H28" s="452" t="n"/>
+      <c r="I28" s="452" t="n"/>
+      <c r="J28" s="429" t="n"/>
+      <c r="K28" s="447" t="n"/>
+      <c r="L28" s="447" t="n"/>
+      <c r="M28" s="447" t="n"/>
+      <c r="N28" s="447" t="n"/>
+      <c r="O28" s="447" t="n"/>
+      <c r="P28" s="447" t="n"/>
+      <c r="Q28" s="447" t="n"/>
+      <c r="R28" s="447" t="n"/>
+      <c r="S28" s="447" t="n"/>
+      <c r="T28" s="447" t="n"/>
+      <c r="U28" s="447" t="n"/>
+      <c r="V28" s="447" t="n"/>
+      <c r="W28" s="447" t="n"/>
+      <c r="X28" s="447" t="n"/>
+      <c r="Y28" s="447" t="n"/>
+      <c r="Z28" s="447" t="n"/>
+      <c r="AA28" s="447" t="n"/>
+      <c r="AB28" s="447" t="n"/>
+      <c r="AC28" s="447" t="n"/>
+      <c r="AD28" s="447" t="n"/>
+      <c r="AE28" s="447" t="n"/>
+      <c r="AF28" s="447" t="n"/>
+      <c r="AG28" s="447" t="n"/>
+      <c r="AH28" s="447" t="n"/>
+      <c r="AI28" s="447" t="n"/>
+      <c r="AJ28" s="447" t="n"/>
+      <c r="AK28" s="447" t="n"/>
+      <c r="AL28" s="447" t="n"/>
+      <c r="AM28" s="447" t="n"/>
+      <c r="AN28" s="447" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="379">
+      <c r="A29" s="450">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B29" s="382" t="n"/>
-      <c r="C29" s="383" t="n"/>
-      <c r="D29" s="383" t="n"/>
-      <c r="E29" s="383" t="n"/>
-      <c r="F29" s="383" t="n"/>
-      <c r="G29" s="383" t="n"/>
-      <c r="H29" s="383" t="n"/>
-      <c r="I29" s="383" t="n"/>
-      <c r="J29" s="384" t="n"/>
+      <c r="B29" s="453" t="n"/>
+      <c r="C29" s="454" t="n"/>
+      <c r="D29" s="454" t="n"/>
+      <c r="E29" s="454" t="n"/>
+      <c r="F29" s="454" t="n"/>
+      <c r="G29" s="454" t="n"/>
+      <c r="H29" s="454" t="n"/>
+      <c r="I29" s="454" t="n"/>
+      <c r="J29" s="455" t="n"/>
+      <c r="K29" s="447" t="n"/>
+      <c r="L29" s="447" t="n"/>
+      <c r="M29" s="447" t="n"/>
+      <c r="N29" s="447" t="n"/>
+      <c r="O29" s="447" t="n"/>
+      <c r="P29" s="447" t="n"/>
+      <c r="Q29" s="447" t="n"/>
+      <c r="R29" s="447" t="n"/>
+      <c r="S29" s="447" t="n"/>
+      <c r="T29" s="447" t="n"/>
+      <c r="U29" s="447" t="n"/>
+      <c r="V29" s="447" t="n"/>
+      <c r="W29" s="447" t="n"/>
+      <c r="X29" s="447" t="n"/>
+      <c r="Y29" s="447" t="n"/>
+      <c r="Z29" s="447" t="n"/>
+      <c r="AA29" s="447" t="n"/>
+      <c r="AB29" s="447" t="n"/>
+      <c r="AC29" s="447" t="n"/>
+      <c r="AD29" s="447" t="n"/>
+      <c r="AE29" s="447" t="n"/>
+      <c r="AF29" s="447" t="n"/>
+      <c r="AG29" s="447" t="n"/>
+      <c r="AH29" s="447" t="n"/>
+      <c r="AI29" s="447" t="n"/>
+      <c r="AJ29" s="447" t="n"/>
+      <c r="AK29" s="447" t="n"/>
+      <c r="AL29" s="447" t="n"/>
+      <c r="AM29" s="447" t="n"/>
+      <c r="AN29" s="447" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="379">
+      <c r="A30" s="450">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B30" s="380" t="n"/>
-      <c r="C30" s="381" t="n"/>
-      <c r="D30" s="381" t="n"/>
-      <c r="E30" s="381" t="n"/>
-      <c r="F30" s="381" t="n"/>
-      <c r="G30" s="381" t="n"/>
-      <c r="H30" s="381" t="n"/>
-      <c r="I30" s="381" t="n"/>
-      <c r="J30" s="351" t="n"/>
+      <c r="B30" s="451" t="n"/>
+      <c r="C30" s="452" t="n"/>
+      <c r="D30" s="452" t="n"/>
+      <c r="E30" s="452" t="n"/>
+      <c r="F30" s="452" t="n"/>
+      <c r="G30" s="452" t="n"/>
+      <c r="H30" s="452" t="n"/>
+      <c r="I30" s="452" t="n"/>
+      <c r="J30" s="429" t="n"/>
+      <c r="K30" s="447" t="n"/>
+      <c r="L30" s="447" t="n"/>
+      <c r="M30" s="447" t="n"/>
+      <c r="N30" s="447" t="n"/>
+      <c r="O30" s="447" t="n"/>
+      <c r="P30" s="447" t="n"/>
+      <c r="Q30" s="447" t="n"/>
+      <c r="R30" s="447" t="n"/>
+      <c r="S30" s="447" t="n"/>
+      <c r="T30" s="447" t="n"/>
+      <c r="U30" s="447" t="n"/>
+      <c r="V30" s="447" t="n"/>
+      <c r="W30" s="447" t="n"/>
+      <c r="X30" s="447" t="n"/>
+      <c r="Y30" s="447" t="n"/>
+      <c r="Z30" s="447" t="n"/>
+      <c r="AA30" s="447" t="n"/>
+      <c r="AB30" s="447" t="n"/>
+      <c r="AC30" s="447" t="n"/>
+      <c r="AD30" s="447" t="n"/>
+      <c r="AE30" s="447" t="n"/>
+      <c r="AF30" s="447" t="n"/>
+      <c r="AG30" s="447" t="n"/>
+      <c r="AH30" s="447" t="n"/>
+      <c r="AI30" s="447" t="n"/>
+      <c r="AJ30" s="447" t="n"/>
+      <c r="AK30" s="447" t="n"/>
+      <c r="AL30" s="447" t="n"/>
+      <c r="AM30" s="447" t="n"/>
+      <c r="AN30" s="447" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="379">
+      <c r="A31" s="450">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B31" s="382" t="n"/>
-      <c r="C31" s="383" t="n"/>
-      <c r="D31" s="383" t="n"/>
-      <c r="E31" s="383" t="n"/>
-      <c r="F31" s="383" t="n"/>
-      <c r="G31" s="383" t="n"/>
-      <c r="H31" s="383" t="n"/>
-      <c r="I31" s="383" t="n"/>
-      <c r="J31" s="384" t="n"/>
+      <c r="B31" s="453" t="n"/>
+      <c r="C31" s="454" t="n"/>
+      <c r="D31" s="454" t="n"/>
+      <c r="E31" s="454" t="n"/>
+      <c r="F31" s="454" t="n"/>
+      <c r="G31" s="454" t="n"/>
+      <c r="H31" s="454" t="n"/>
+      <c r="I31" s="454" t="n"/>
+      <c r="J31" s="455" t="n"/>
+      <c r="K31" s="447" t="n"/>
+      <c r="L31" s="447" t="n"/>
+      <c r="M31" s="447" t="n"/>
+      <c r="N31" s="447" t="n"/>
+      <c r="O31" s="447" t="n"/>
+      <c r="P31" s="447" t="n"/>
+      <c r="Q31" s="447" t="n"/>
+      <c r="R31" s="447" t="n"/>
+      <c r="S31" s="447" t="n"/>
+      <c r="T31" s="447" t="n"/>
+      <c r="U31" s="447" t="n"/>
+      <c r="V31" s="447" t="n"/>
+      <c r="W31" s="447" t="n"/>
+      <c r="X31" s="447" t="n"/>
+      <c r="Y31" s="447" t="n"/>
+      <c r="Z31" s="447" t="n"/>
+      <c r="AA31" s="447" t="n"/>
+      <c r="AB31" s="447" t="n"/>
+      <c r="AC31" s="447" t="n"/>
+      <c r="AD31" s="447" t="n"/>
+      <c r="AE31" s="447" t="n"/>
+      <c r="AF31" s="447" t="n"/>
+      <c r="AG31" s="447" t="n"/>
+      <c r="AH31" s="447" t="n"/>
+      <c r="AI31" s="447" t="n"/>
+      <c r="AJ31" s="447" t="n"/>
+      <c r="AK31" s="447" t="n"/>
+      <c r="AL31" s="447" t="n"/>
+      <c r="AM31" s="447" t="n"/>
+      <c r="AN31" s="447" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="379">
+      <c r="A32" s="450">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B32" s="380" t="n"/>
-      <c r="C32" s="381" t="n"/>
-      <c r="D32" s="381" t="n"/>
-      <c r="E32" s="381" t="n"/>
-      <c r="F32" s="381" t="n"/>
-      <c r="G32" s="381" t="n"/>
-      <c r="H32" s="381" t="n"/>
-      <c r="I32" s="381" t="n"/>
-      <c r="J32" s="351" t="n"/>
+      <c r="B32" s="451" t="n"/>
+      <c r="C32" s="452" t="n"/>
+      <c r="D32" s="452" t="n"/>
+      <c r="E32" s="452" t="n"/>
+      <c r="F32" s="452" t="n"/>
+      <c r="G32" s="452" t="n"/>
+      <c r="H32" s="452" t="n"/>
+      <c r="I32" s="452" t="n"/>
+      <c r="J32" s="429" t="n"/>
+      <c r="K32" s="447" t="n"/>
+      <c r="L32" s="447" t="n"/>
+      <c r="M32" s="447" t="n"/>
+      <c r="N32" s="447" t="n"/>
+      <c r="O32" s="447" t="n"/>
+      <c r="P32" s="447" t="n"/>
+      <c r="Q32" s="447" t="n"/>
+      <c r="R32" s="447" t="n"/>
+      <c r="S32" s="447" t="n"/>
+      <c r="T32" s="447" t="n"/>
+      <c r="U32" s="447" t="n"/>
+      <c r="V32" s="447" t="n"/>
+      <c r="W32" s="447" t="n"/>
+      <c r="X32" s="447" t="n"/>
+      <c r="Y32" s="447" t="n"/>
+      <c r="Z32" s="447" t="n"/>
+      <c r="AA32" s="447" t="n"/>
+      <c r="AB32" s="447" t="n"/>
+      <c r="AC32" s="447" t="n"/>
+      <c r="AD32" s="447" t="n"/>
+      <c r="AE32" s="447" t="n"/>
+      <c r="AF32" s="447" t="n"/>
+      <c r="AG32" s="447" t="n"/>
+      <c r="AH32" s="447" t="n"/>
+      <c r="AI32" s="447" t="n"/>
+      <c r="AJ32" s="447" t="n"/>
+      <c r="AK32" s="447" t="n"/>
+      <c r="AL32" s="447" t="n"/>
+      <c r="AM32" s="447" t="n"/>
+      <c r="AN32" s="447" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="379">
+      <c r="A33" s="450">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B33" s="382" t="n"/>
-      <c r="C33" s="383" t="n"/>
-      <c r="D33" s="383" t="n"/>
-      <c r="E33" s="383" t="n"/>
-      <c r="F33" s="383" t="n"/>
-      <c r="G33" s="383" t="n"/>
-      <c r="H33" s="383" t="n"/>
-      <c r="I33" s="383" t="n"/>
-      <c r="J33" s="384" t="n"/>
+      <c r="B33" s="453" t="n"/>
+      <c r="C33" s="454" t="n"/>
+      <c r="D33" s="454" t="n"/>
+      <c r="E33" s="454" t="n"/>
+      <c r="F33" s="454" t="n"/>
+      <c r="G33" s="454" t="n"/>
+      <c r="H33" s="454" t="n"/>
+      <c r="I33" s="454" t="n"/>
+      <c r="J33" s="455" t="n"/>
+      <c r="K33" s="447" t="n"/>
+      <c r="L33" s="447" t="n"/>
+      <c r="M33" s="447" t="n"/>
+      <c r="N33" s="447" t="n"/>
+      <c r="O33" s="447" t="n"/>
+      <c r="P33" s="447" t="n"/>
+      <c r="Q33" s="447" t="n"/>
+      <c r="R33" s="447" t="n"/>
+      <c r="S33" s="447" t="n"/>
+      <c r="T33" s="447" t="n"/>
+      <c r="U33" s="447" t="n"/>
+      <c r="V33" s="447" t="n"/>
+      <c r="W33" s="447" t="n"/>
+      <c r="X33" s="447" t="n"/>
+      <c r="Y33" s="447" t="n"/>
+      <c r="Z33" s="447" t="n"/>
+      <c r="AA33" s="447" t="n"/>
+      <c r="AB33" s="447" t="n"/>
+      <c r="AC33" s="447" t="n"/>
+      <c r="AD33" s="447" t="n"/>
+      <c r="AE33" s="447" t="n"/>
+      <c r="AF33" s="447" t="n"/>
+      <c r="AG33" s="447" t="n"/>
+      <c r="AH33" s="447" t="n"/>
+      <c r="AI33" s="447" t="n"/>
+      <c r="AJ33" s="447" t="n"/>
+      <c r="AK33" s="447" t="n"/>
+      <c r="AL33" s="447" t="n"/>
+      <c r="AM33" s="447" t="n"/>
+      <c r="AN33" s="447" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="379">
+      <c r="A34" s="450">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B34" s="380" t="n"/>
-      <c r="C34" s="381" t="n"/>
-      <c r="D34" s="381" t="n"/>
-      <c r="E34" s="381" t="n"/>
-      <c r="F34" s="381" t="n"/>
-      <c r="G34" s="381" t="n"/>
-      <c r="H34" s="381" t="n"/>
-      <c r="I34" s="381" t="n"/>
-      <c r="J34" s="351" t="n"/>
+      <c r="B34" s="451" t="n"/>
+      <c r="C34" s="452" t="n"/>
+      <c r="D34" s="452" t="n"/>
+      <c r="E34" s="452" t="n"/>
+      <c r="F34" s="452" t="n"/>
+      <c r="G34" s="452" t="n"/>
+      <c r="H34" s="452" t="n"/>
+      <c r="I34" s="452" t="n"/>
+      <c r="J34" s="429" t="n"/>
+      <c r="K34" s="447" t="n"/>
+      <c r="L34" s="447" t="n"/>
+      <c r="M34" s="447" t="n"/>
+      <c r="N34" s="447" t="n"/>
+      <c r="O34" s="447" t="n"/>
+      <c r="P34" s="447" t="n"/>
+      <c r="Q34" s="447" t="n"/>
+      <c r="R34" s="447" t="n"/>
+      <c r="S34" s="447" t="n"/>
+      <c r="T34" s="447" t="n"/>
+      <c r="U34" s="447" t="n"/>
+      <c r="V34" s="447" t="n"/>
+      <c r="W34" s="447" t="n"/>
+      <c r="X34" s="447" t="n"/>
+      <c r="Y34" s="447" t="n"/>
+      <c r="Z34" s="447" t="n"/>
+      <c r="AA34" s="447" t="n"/>
+      <c r="AB34" s="447" t="n"/>
+      <c r="AC34" s="447" t="n"/>
+      <c r="AD34" s="447" t="n"/>
+      <c r="AE34" s="447" t="n"/>
+      <c r="AF34" s="447" t="n"/>
+      <c r="AG34" s="447" t="n"/>
+      <c r="AH34" s="447" t="n"/>
+      <c r="AI34" s="447" t="n"/>
+      <c r="AJ34" s="447" t="n"/>
+      <c r="AK34" s="447" t="n"/>
+      <c r="AL34" s="447" t="n"/>
+      <c r="AM34" s="447" t="n"/>
+      <c r="AN34" s="447" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="379">
+      <c r="A35" s="450">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B35" s="382" t="n"/>
-      <c r="C35" s="383" t="n"/>
-      <c r="D35" s="383" t="n"/>
-      <c r="E35" s="383" t="n"/>
-      <c r="F35" s="383" t="n"/>
-      <c r="G35" s="383" t="n"/>
-      <c r="H35" s="383" t="n"/>
-      <c r="I35" s="383" t="n"/>
-      <c r="J35" s="384" t="n"/>
+      <c r="B35" s="453" t="n"/>
+      <c r="C35" s="454" t="n"/>
+      <c r="D35" s="454" t="n"/>
+      <c r="E35" s="454" t="n"/>
+      <c r="F35" s="454" t="n"/>
+      <c r="G35" s="454" t="n"/>
+      <c r="H35" s="454" t="n"/>
+      <c r="I35" s="454" t="n"/>
+      <c r="J35" s="455" t="n"/>
+      <c r="K35" s="447" t="n"/>
+      <c r="L35" s="447" t="n"/>
+      <c r="M35" s="447" t="n"/>
+      <c r="N35" s="447" t="n"/>
+      <c r="O35" s="447" t="n"/>
+      <c r="P35" s="447" t="n"/>
+      <c r="Q35" s="447" t="n"/>
+      <c r="R35" s="447" t="n"/>
+      <c r="S35" s="447" t="n"/>
+      <c r="T35" s="447" t="n"/>
+      <c r="U35" s="447" t="n"/>
+      <c r="V35" s="447" t="n"/>
+      <c r="W35" s="447" t="n"/>
+      <c r="X35" s="447" t="n"/>
+      <c r="Y35" s="447" t="n"/>
+      <c r="Z35" s="447" t="n"/>
+      <c r="AA35" s="447" t="n"/>
+      <c r="AB35" s="447" t="n"/>
+      <c r="AC35" s="447" t="n"/>
+      <c r="AD35" s="447" t="n"/>
+      <c r="AE35" s="447" t="n"/>
+      <c r="AF35" s="447" t="n"/>
+      <c r="AG35" s="447" t="n"/>
+      <c r="AH35" s="447" t="n"/>
+      <c r="AI35" s="447" t="n"/>
+      <c r="AJ35" s="447" t="n"/>
+      <c r="AK35" s="447" t="n"/>
+      <c r="AL35" s="447" t="n"/>
+      <c r="AM35" s="447" t="n"/>
+      <c r="AN35" s="447" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="379">
+      <c r="A36" s="450">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B36" s="380" t="n"/>
-      <c r="C36" s="381" t="n"/>
-      <c r="D36" s="381" t="n"/>
-      <c r="E36" s="381" t="n"/>
-      <c r="F36" s="381" t="n"/>
-      <c r="G36" s="381" t="n"/>
-      <c r="H36" s="381" t="n"/>
-      <c r="I36" s="381" t="n"/>
-      <c r="J36" s="351" t="n"/>
+      <c r="B36" s="451" t="n"/>
+      <c r="C36" s="452" t="n"/>
+      <c r="D36" s="452" t="n"/>
+      <c r="E36" s="452" t="n"/>
+      <c r="F36" s="452" t="n"/>
+      <c r="G36" s="452" t="n"/>
+      <c r="H36" s="452" t="n"/>
+      <c r="I36" s="452" t="n"/>
+      <c r="J36" s="429" t="n"/>
+      <c r="K36" s="447" t="n"/>
+      <c r="L36" s="447" t="n"/>
+      <c r="M36" s="447" t="n"/>
+      <c r="N36" s="447" t="n"/>
+      <c r="O36" s="447" t="n"/>
+      <c r="P36" s="447" t="n"/>
+      <c r="Q36" s="447" t="n"/>
+      <c r="R36" s="447" t="n"/>
+      <c r="S36" s="447" t="n"/>
+      <c r="T36" s="447" t="n"/>
+      <c r="U36" s="447" t="n"/>
+      <c r="V36" s="447" t="n"/>
+      <c r="W36" s="447" t="n"/>
+      <c r="X36" s="447" t="n"/>
+      <c r="Y36" s="447" t="n"/>
+      <c r="Z36" s="447" t="n"/>
+      <c r="AA36" s="447" t="n"/>
+      <c r="AB36" s="447" t="n"/>
+      <c r="AC36" s="447" t="n"/>
+      <c r="AD36" s="447" t="n"/>
+      <c r="AE36" s="447" t="n"/>
+      <c r="AF36" s="447" t="n"/>
+      <c r="AG36" s="447" t="n"/>
+      <c r="AH36" s="447" t="n"/>
+      <c r="AI36" s="447" t="n"/>
+      <c r="AJ36" s="447" t="n"/>
+      <c r="AK36" s="447" t="n"/>
+      <c r="AL36" s="447" t="n"/>
+      <c r="AM36" s="447" t="n"/>
+      <c r="AN36" s="447" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="379">
+      <c r="A37" s="450">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B37" s="382" t="n"/>
-      <c r="C37" s="383" t="n"/>
-      <c r="D37" s="383" t="n"/>
-      <c r="E37" s="383" t="n"/>
-      <c r="F37" s="383" t="n"/>
-      <c r="G37" s="383" t="n"/>
-      <c r="H37" s="383" t="n"/>
-      <c r="I37" s="383" t="n"/>
-      <c r="J37" s="384" t="n"/>
+      <c r="B37" s="453" t="n"/>
+      <c r="C37" s="454" t="n"/>
+      <c r="D37" s="454" t="n"/>
+      <c r="E37" s="454" t="n"/>
+      <c r="F37" s="454" t="n"/>
+      <c r="G37" s="454" t="n"/>
+      <c r="H37" s="454" t="n"/>
+      <c r="I37" s="454" t="n"/>
+      <c r="J37" s="455" t="n"/>
+      <c r="K37" s="447" t="n"/>
+      <c r="L37" s="447" t="n"/>
+      <c r="M37" s="447" t="n"/>
+      <c r="N37" s="447" t="n"/>
+      <c r="O37" s="447" t="n"/>
+      <c r="P37" s="447" t="n"/>
+      <c r="Q37" s="447" t="n"/>
+      <c r="R37" s="447" t="n"/>
+      <c r="S37" s="447" t="n"/>
+      <c r="T37" s="447" t="n"/>
+      <c r="U37" s="447" t="n"/>
+      <c r="V37" s="447" t="n"/>
+      <c r="W37" s="447" t="n"/>
+      <c r="X37" s="447" t="n"/>
+      <c r="Y37" s="447" t="n"/>
+      <c r="Z37" s="447" t="n"/>
+      <c r="AA37" s="447" t="n"/>
+      <c r="AB37" s="447" t="n"/>
+      <c r="AC37" s="447" t="n"/>
+      <c r="AD37" s="447" t="n"/>
+      <c r="AE37" s="447" t="n"/>
+      <c r="AF37" s="447" t="n"/>
+      <c r="AG37" s="447" t="n"/>
+      <c r="AH37" s="447" t="n"/>
+      <c r="AI37" s="447" t="n"/>
+      <c r="AJ37" s="447" t="n"/>
+      <c r="AK37" s="447" t="n"/>
+      <c r="AL37" s="447" t="n"/>
+      <c r="AM37" s="447" t="n"/>
+      <c r="AN37" s="447" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="379">
+      <c r="A38" s="450">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B38" s="380" t="n"/>
-      <c r="C38" s="381" t="n"/>
-      <c r="D38" s="381" t="n"/>
-      <c r="E38" s="381" t="n"/>
-      <c r="F38" s="381" t="n"/>
-      <c r="G38" s="381" t="n"/>
-      <c r="H38" s="381" t="n"/>
-      <c r="I38" s="381" t="n"/>
-      <c r="J38" s="351" t="n"/>
+      <c r="B38" s="451" t="n"/>
+      <c r="C38" s="452" t="n"/>
+      <c r="D38" s="452" t="n"/>
+      <c r="E38" s="452" t="n"/>
+      <c r="F38" s="452" t="n"/>
+      <c r="G38" s="452" t="n"/>
+      <c r="H38" s="452" t="n"/>
+      <c r="I38" s="452" t="n"/>
+      <c r="J38" s="429" t="n"/>
+      <c r="K38" s="447" t="n"/>
+      <c r="L38" s="447" t="n"/>
+      <c r="M38" s="447" t="n"/>
+      <c r="N38" s="447" t="n"/>
+      <c r="O38" s="447" t="n"/>
+      <c r="P38" s="447" t="n"/>
+      <c r="Q38" s="447" t="n"/>
+      <c r="R38" s="447" t="n"/>
+      <c r="S38" s="447" t="n"/>
+      <c r="T38" s="447" t="n"/>
+      <c r="U38" s="447" t="n"/>
+      <c r="V38" s="447" t="n"/>
+      <c r="W38" s="447" t="n"/>
+      <c r="X38" s="447" t="n"/>
+      <c r="Y38" s="447" t="n"/>
+      <c r="Z38" s="447" t="n"/>
+      <c r="AA38" s="447" t="n"/>
+      <c r="AB38" s="447" t="n"/>
+      <c r="AC38" s="447" t="n"/>
+      <c r="AD38" s="447" t="n"/>
+      <c r="AE38" s="447" t="n"/>
+      <c r="AF38" s="447" t="n"/>
+      <c r="AG38" s="447" t="n"/>
+      <c r="AH38" s="447" t="n"/>
+      <c r="AI38" s="447" t="n"/>
+      <c r="AJ38" s="447" t="n"/>
+      <c r="AK38" s="447" t="n"/>
+      <c r="AL38" s="447" t="n"/>
+      <c r="AM38" s="447" t="n"/>
+      <c r="AN38" s="447" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="385">
+      <c r="A39" s="456">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B39" s="386" t="n"/>
-      <c r="C39" s="387" t="n"/>
-      <c r="D39" s="387" t="n"/>
-      <c r="E39" s="387" t="n"/>
-      <c r="F39" s="387" t="n"/>
-      <c r="G39" s="387" t="n"/>
-      <c r="H39" s="387" t="n"/>
-      <c r="I39" s="387" t="n"/>
-      <c r="J39" s="388" t="n"/>
+      <c r="B39" s="457" t="n"/>
+      <c r="C39" s="458" t="n"/>
+      <c r="D39" s="458" t="n"/>
+      <c r="E39" s="458" t="n"/>
+      <c r="F39" s="458" t="n"/>
+      <c r="G39" s="458" t="n"/>
+      <c r="H39" s="458" t="n"/>
+      <c r="I39" s="458" t="n"/>
+      <c r="J39" s="459" t="n"/>
+      <c r="K39" s="447" t="n"/>
+      <c r="L39" s="447" t="n"/>
+      <c r="M39" s="447" t="n"/>
+      <c r="N39" s="447" t="n"/>
+      <c r="O39" s="447" t="n"/>
+      <c r="P39" s="447" t="n"/>
+      <c r="Q39" s="447" t="n"/>
+      <c r="R39" s="447" t="n"/>
+      <c r="S39" s="447" t="n"/>
+      <c r="T39" s="447" t="n"/>
+      <c r="U39" s="447" t="n"/>
+      <c r="V39" s="447" t="n"/>
+      <c r="W39" s="447" t="n"/>
+      <c r="X39" s="447" t="n"/>
+      <c r="Y39" s="447" t="n"/>
+      <c r="Z39" s="447" t="n"/>
+      <c r="AA39" s="447" t="n"/>
+      <c r="AB39" s="447" t="n"/>
+      <c r="AC39" s="447" t="n"/>
+      <c r="AD39" s="447" t="n"/>
+      <c r="AE39" s="447" t="n"/>
+      <c r="AF39" s="447" t="n"/>
+      <c r="AG39" s="447" t="n"/>
+      <c r="AH39" s="447" t="n"/>
+      <c r="AI39" s="447" t="n"/>
+      <c r="AJ39" s="447" t="n"/>
+      <c r="AK39" s="447" t="n"/>
+      <c r="AL39" s="447" t="n"/>
+      <c r="AM39" s="447" t="n"/>
+      <c r="AN39" s="447" t="n"/>
     </row>
     <row r="40" ht="4" customHeight="1">
-      <c r="A40" s="413" t="n"/>
-      <c r="B40" s="289" t="n"/>
-      <c r="C40" s="289" t="n"/>
-      <c r="D40" s="289" t="n"/>
-      <c r="E40" s="289" t="n"/>
-      <c r="F40" s="289" t="n"/>
-      <c r="G40" s="289" t="n"/>
-      <c r="H40" s="289" t="n"/>
-      <c r="I40" s="289" t="n"/>
-      <c r="J40" s="290" t="n"/>
+      <c r="A40" s="442" t="n"/>
+      <c r="B40" s="495" t="n"/>
+      <c r="C40" s="495" t="n"/>
+      <c r="D40" s="495" t="n"/>
+      <c r="E40" s="495" t="n"/>
+      <c r="F40" s="495" t="n"/>
+      <c r="G40" s="495" t="n"/>
+      <c r="H40" s="495" t="n"/>
+      <c r="I40" s="495" t="n"/>
+      <c r="J40" s="495" t="n"/>
+      <c r="K40" s="443" t="n"/>
+      <c r="L40" s="443" t="n"/>
+      <c r="M40" s="443" t="n"/>
+      <c r="N40" s="443" t="n"/>
+      <c r="O40" s="443" t="n"/>
+      <c r="P40" s="443" t="n"/>
+      <c r="Q40" s="443" t="n"/>
+      <c r="R40" s="443" t="n"/>
+      <c r="S40" s="443" t="n"/>
+      <c r="T40" s="443" t="n"/>
+      <c r="U40" s="443" t="n"/>
+      <c r="V40" s="443" t="n"/>
+      <c r="W40" s="443" t="n"/>
+      <c r="X40" s="443" t="n"/>
+      <c r="Y40" s="443" t="n"/>
+      <c r="Z40" s="443" t="n"/>
+      <c r="AA40" s="443" t="n"/>
+      <c r="AB40" s="443" t="n"/>
+      <c r="AC40" s="443" t="n"/>
+      <c r="AD40" s="443" t="n"/>
+      <c r="AE40" s="443" t="n"/>
+      <c r="AF40" s="443" t="n"/>
+      <c r="AG40" s="443" t="n"/>
+      <c r="AH40" s="443" t="n"/>
+      <c r="AI40" s="443" t="n"/>
+      <c r="AJ40" s="443" t="n"/>
+      <c r="AK40" s="443" t="n"/>
+      <c r="AL40" s="443" t="n"/>
+      <c r="AM40" s="443" t="n"/>
+      <c r="AN40" s="443" t="n"/>
     </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="417" t="inlineStr">
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="444" t="inlineStr">
         <is>
           <t>4.  CLOSURE AND EVIDENCE SECTION</t>
         </is>
       </c>
-      <c r="B41" s="289" t="n"/>
-      <c r="C41" s="289" t="n"/>
-      <c r="D41" s="289" t="n"/>
-      <c r="E41" s="289" t="n"/>
-      <c r="F41" s="289" t="n"/>
-      <c r="G41" s="289" t="n"/>
-      <c r="H41" s="289" t="n"/>
-      <c r="I41" s="289" t="n"/>
-      <c r="J41" s="290" t="n"/>
+      <c r="B41" s="487" t="n"/>
+      <c r="C41" s="487" t="n"/>
+      <c r="D41" s="487" t="n"/>
+      <c r="E41" s="487" t="n"/>
+      <c r="F41" s="487" t="n"/>
+      <c r="G41" s="487" t="n"/>
+      <c r="H41" s="487" t="n"/>
+      <c r="I41" s="487" t="n"/>
+      <c r="J41" s="486" t="n"/>
+      <c r="K41" s="447" t="n"/>
+      <c r="L41" s="447" t="n"/>
+      <c r="M41" s="447" t="n"/>
+      <c r="N41" s="447" t="n"/>
+      <c r="O41" s="447" t="n"/>
+      <c r="P41" s="447" t="n"/>
+      <c r="Q41" s="447" t="n"/>
+      <c r="R41" s="447" t="n"/>
+      <c r="S41" s="447" t="n"/>
+      <c r="T41" s="447" t="n"/>
+      <c r="U41" s="447" t="n"/>
+      <c r="V41" s="447" t="n"/>
+      <c r="W41" s="447" t="n"/>
+      <c r="X41" s="447" t="n"/>
+      <c r="Y41" s="447" t="n"/>
+      <c r="Z41" s="447" t="n"/>
+      <c r="AA41" s="447" t="n"/>
+      <c r="AB41" s="447" t="n"/>
+      <c r="AC41" s="447" t="n"/>
+      <c r="AD41" s="447" t="n"/>
+      <c r="AE41" s="447" t="n"/>
+      <c r="AF41" s="447" t="n"/>
+      <c r="AG41" s="447" t="n"/>
+      <c r="AH41" s="447" t="n"/>
+      <c r="AI41" s="447" t="n"/>
+      <c r="AJ41" s="447" t="n"/>
+      <c r="AK41" s="447" t="n"/>
+      <c r="AL41" s="447" t="n"/>
+      <c r="AM41" s="447" t="n"/>
+      <c r="AN41" s="447" t="n"/>
     </row>
-    <row r="42">
-      <c r="A42" s="420" t="inlineStr">
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="460" t="inlineStr">
         <is>
           <t>Periodic review</t>
         </is>
       </c>
-      <c r="B42" s="289" t="n"/>
-      <c r="C42" s="290" t="n"/>
-      <c r="D42" s="420" t="inlineStr">
+      <c r="B42" s="487" t="n"/>
+      <c r="C42" s="486" t="n"/>
+      <c r="D42" s="460" t="inlineStr">
         <is>
           <t>Open items / escalation</t>
         </is>
       </c>
-      <c r="E42" s="289" t="n"/>
-      <c r="F42" s="290" t="n"/>
-      <c r="G42" s="420" t="inlineStr">
+      <c r="E42" s="487" t="n"/>
+      <c r="F42" s="486" t="n"/>
+      <c r="G42" s="460" t="inlineStr">
         <is>
           <t>Approval / archive</t>
         </is>
       </c>
-      <c r="H42" s="289" t="n"/>
-      <c r="I42" s="289" t="n"/>
-      <c r="J42" s="290" t="n"/>
+      <c r="H42" s="487" t="n"/>
+      <c r="I42" s="487" t="n"/>
+      <c r="J42" s="486" t="n"/>
+      <c r="K42" s="447" t="n"/>
+      <c r="L42" s="447" t="n"/>
+      <c r="M42" s="447" t="n"/>
+      <c r="N42" s="447" t="n"/>
+      <c r="O42" s="447" t="n"/>
+      <c r="P42" s="447" t="n"/>
+      <c r="Q42" s="447" t="n"/>
+      <c r="R42" s="447" t="n"/>
+      <c r="S42" s="447" t="n"/>
+      <c r="T42" s="447" t="n"/>
+      <c r="U42" s="447" t="n"/>
+      <c r="V42" s="447" t="n"/>
+      <c r="W42" s="447" t="n"/>
+      <c r="X42" s="447" t="n"/>
+      <c r="Y42" s="447" t="n"/>
+      <c r="Z42" s="447" t="n"/>
+      <c r="AA42" s="447" t="n"/>
+      <c r="AB42" s="447" t="n"/>
+      <c r="AC42" s="447" t="n"/>
+      <c r="AD42" s="447" t="n"/>
+      <c r="AE42" s="447" t="n"/>
+      <c r="AF42" s="447" t="n"/>
+      <c r="AG42" s="447" t="n"/>
+      <c r="AH42" s="447" t="n"/>
+      <c r="AI42" s="447" t="n"/>
+      <c r="AJ42" s="447" t="n"/>
+      <c r="AK42" s="447" t="n"/>
+      <c r="AL42" s="447" t="n"/>
+      <c r="AM42" s="447" t="n"/>
+      <c r="AN42" s="447" t="n"/>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="421" t="inlineStr">
+      <c r="A43" s="461" t="inlineStr">
         <is>
           <t>Return-material tracking memory only; formal quality investigation remains in linked quality records.
 Review owner: _____________________________________________</t>
         </is>
       </c>
-      <c r="B43" s="268" t="n"/>
-      <c r="C43" s="310" t="n"/>
-      <c r="D43" s="421" t="inlineStr">
+      <c r="B43" s="488" t="n"/>
+      <c r="C43" s="489" t="n"/>
+      <c r="D43" s="461" t="inlineStr">
         <is>
           <t>Final evidence ref: ________________________________________
 Outstanding items / actions: ________________________________</t>
         </is>
       </c>
-      <c r="E43" s="268" t="n"/>
-      <c r="F43" s="310" t="n"/>
-      <c r="G43" s="422" t="inlineStr">
+      <c r="E43" s="488" t="n"/>
+      <c r="F43" s="489" t="n"/>
+      <c r="G43" s="464" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="H43" s="268" t="n"/>
-      <c r="I43" s="268" t="n"/>
-      <c r="J43" s="310" t="n"/>
+      <c r="H43" s="488" t="n"/>
+      <c r="I43" s="488" t="n"/>
+      <c r="J43" s="489" t="n"/>
+      <c r="K43" s="447" t="n"/>
+      <c r="L43" s="447" t="n"/>
+      <c r="M43" s="447" t="n"/>
+      <c r="N43" s="447" t="n"/>
+      <c r="O43" s="447" t="n"/>
+      <c r="P43" s="447" t="n"/>
+      <c r="Q43" s="447" t="n"/>
+      <c r="R43" s="447" t="n"/>
+      <c r="S43" s="447" t="n"/>
+      <c r="T43" s="447" t="n"/>
+      <c r="U43" s="447" t="n"/>
+      <c r="V43" s="447" t="n"/>
+      <c r="W43" s="447" t="n"/>
+      <c r="X43" s="447" t="n"/>
+      <c r="Y43" s="447" t="n"/>
+      <c r="Z43" s="447" t="n"/>
+      <c r="AA43" s="447" t="n"/>
+      <c r="AB43" s="447" t="n"/>
+      <c r="AC43" s="447" t="n"/>
+      <c r="AD43" s="447" t="n"/>
+      <c r="AE43" s="447" t="n"/>
+      <c r="AF43" s="447" t="n"/>
+      <c r="AG43" s="447" t="n"/>
+      <c r="AH43" s="447" t="n"/>
+      <c r="AI43" s="447" t="n"/>
+      <c r="AJ43" s="447" t="n"/>
+      <c r="AK43" s="447" t="n"/>
+      <c r="AL43" s="447" t="n"/>
+      <c r="AM43" s="447" t="n"/>
+      <c r="AN43" s="447" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="275" t="n"/>
-      <c r="C44" s="312" t="n"/>
-      <c r="D44" s="275" t="n"/>
-      <c r="F44" s="312" t="n"/>
-      <c r="G44" s="275" t="n"/>
-      <c r="J44" s="312" t="n"/>
+      <c r="A44" s="490" t="n"/>
+      <c r="B44" s="447" t="n"/>
+      <c r="C44" s="491" t="n"/>
+      <c r="D44" s="490" t="n"/>
+      <c r="E44" s="447" t="n"/>
+      <c r="F44" s="491" t="n"/>
+      <c r="G44" s="490" t="n"/>
+      <c r="H44" s="447" t="n"/>
+      <c r="I44" s="447" t="n"/>
+      <c r="J44" s="491" t="n"/>
+      <c r="K44" s="447" t="n"/>
+      <c r="L44" s="447" t="n"/>
+      <c r="M44" s="447" t="n"/>
+      <c r="N44" s="447" t="n"/>
+      <c r="O44" s="447" t="n"/>
+      <c r="P44" s="447" t="n"/>
+      <c r="Q44" s="447" t="n"/>
+      <c r="R44" s="447" t="n"/>
+      <c r="S44" s="447" t="n"/>
+      <c r="T44" s="447" t="n"/>
+      <c r="U44" s="447" t="n"/>
+      <c r="V44" s="447" t="n"/>
+      <c r="W44" s="447" t="n"/>
+      <c r="X44" s="447" t="n"/>
+      <c r="Y44" s="447" t="n"/>
+      <c r="Z44" s="447" t="n"/>
+      <c r="AA44" s="447" t="n"/>
+      <c r="AB44" s="447" t="n"/>
+      <c r="AC44" s="447" t="n"/>
+      <c r="AD44" s="447" t="n"/>
+      <c r="AE44" s="447" t="n"/>
+      <c r="AF44" s="447" t="n"/>
+      <c r="AG44" s="447" t="n"/>
+      <c r="AH44" s="447" t="n"/>
+      <c r="AI44" s="447" t="n"/>
+      <c r="AJ44" s="447" t="n"/>
+      <c r="AK44" s="447" t="n"/>
+      <c r="AL44" s="447" t="n"/>
+      <c r="AM44" s="447" t="n"/>
+      <c r="AN44" s="447" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="275" t="n"/>
-      <c r="C45" s="312" t="n"/>
-      <c r="D45" s="275" t="n"/>
-      <c r="F45" s="312" t="n"/>
-      <c r="G45" s="275" t="n"/>
-      <c r="J45" s="312" t="n"/>
+      <c r="A45" s="490" t="n"/>
+      <c r="B45" s="447" t="n"/>
+      <c r="C45" s="491" t="n"/>
+      <c r="D45" s="490" t="n"/>
+      <c r="E45" s="447" t="n"/>
+      <c r="F45" s="491" t="n"/>
+      <c r="G45" s="490" t="n"/>
+      <c r="H45" s="447" t="n"/>
+      <c r="I45" s="447" t="n"/>
+      <c r="J45" s="491" t="n"/>
+      <c r="K45" s="447" t="n"/>
+      <c r="L45" s="447" t="n"/>
+      <c r="M45" s="447" t="n"/>
+      <c r="N45" s="447" t="n"/>
+      <c r="O45" s="447" t="n"/>
+      <c r="P45" s="447" t="n"/>
+      <c r="Q45" s="447" t="n"/>
+      <c r="R45" s="447" t="n"/>
+      <c r="S45" s="447" t="n"/>
+      <c r="T45" s="447" t="n"/>
+      <c r="U45" s="447" t="n"/>
+      <c r="V45" s="447" t="n"/>
+      <c r="W45" s="447" t="n"/>
+      <c r="X45" s="447" t="n"/>
+      <c r="Y45" s="447" t="n"/>
+      <c r="Z45" s="447" t="n"/>
+      <c r="AA45" s="447" t="n"/>
+      <c r="AB45" s="447" t="n"/>
+      <c r="AC45" s="447" t="n"/>
+      <c r="AD45" s="447" t="n"/>
+      <c r="AE45" s="447" t="n"/>
+      <c r="AF45" s="447" t="n"/>
+      <c r="AG45" s="447" t="n"/>
+      <c r="AH45" s="447" t="n"/>
+      <c r="AI45" s="447" t="n"/>
+      <c r="AJ45" s="447" t="n"/>
+      <c r="AK45" s="447" t="n"/>
+      <c r="AL45" s="447" t="n"/>
+      <c r="AM45" s="447" t="n"/>
+      <c r="AN45" s="447" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="282" t="n"/>
-      <c r="B46" s="283" t="n"/>
-      <c r="C46" s="287" t="n"/>
-      <c r="D46" s="282" t="n"/>
-      <c r="E46" s="283" t="n"/>
-      <c r="F46" s="287" t="n"/>
-      <c r="G46" s="282" t="n"/>
-      <c r="H46" s="283" t="n"/>
-      <c r="I46" s="283" t="n"/>
-      <c r="J46" s="287" t="n"/>
+      <c r="A46" s="492" t="n"/>
+      <c r="B46" s="493" t="n"/>
+      <c r="C46" s="494" t="n"/>
+      <c r="D46" s="492" t="n"/>
+      <c r="E46" s="493" t="n"/>
+      <c r="F46" s="494" t="n"/>
+      <c r="G46" s="492" t="n"/>
+      <c r="H46" s="493" t="n"/>
+      <c r="I46" s="493" t="n"/>
+      <c r="J46" s="494" t="n"/>
+      <c r="K46" s="447" t="n"/>
+      <c r="L46" s="447" t="n"/>
+      <c r="M46" s="447" t="n"/>
+      <c r="N46" s="447" t="n"/>
+      <c r="O46" s="447" t="n"/>
+      <c r="P46" s="447" t="n"/>
+      <c r="Q46" s="447" t="n"/>
+      <c r="R46" s="447" t="n"/>
+      <c r="S46" s="447" t="n"/>
+      <c r="T46" s="447" t="n"/>
+      <c r="U46" s="447" t="n"/>
+      <c r="V46" s="447" t="n"/>
+      <c r="W46" s="447" t="n"/>
+      <c r="X46" s="447" t="n"/>
+      <c r="Y46" s="447" t="n"/>
+      <c r="Z46" s="447" t="n"/>
+      <c r="AA46" s="447" t="n"/>
+      <c r="AB46" s="447" t="n"/>
+      <c r="AC46" s="447" t="n"/>
+      <c r="AD46" s="447" t="n"/>
+      <c r="AE46" s="447" t="n"/>
+      <c r="AF46" s="447" t="n"/>
+      <c r="AG46" s="447" t="n"/>
+      <c r="AH46" s="447" t="n"/>
+      <c r="AI46" s="447" t="n"/>
+      <c r="AJ46" s="447" t="n"/>
+      <c r="AK46" s="447" t="n"/>
+      <c r="AL46" s="447" t="n"/>
+      <c r="AM46" s="447" t="n"/>
+      <c r="AN46" s="447" t="n"/>
     </row>
-    <row r="47">
-      <c r="A47" s="423" t="inlineStr">
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="470" t="inlineStr">
         <is>
           <t>NOTICE  —  Enter data only in designated white input cells. One form per event or job unless this workbook is designated as rolling. Do not add, delete or resize columns/rows. File naming: FRM-213_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="289" t="n"/>
-      <c r="C47" s="289" t="n"/>
-      <c r="D47" s="289" t="n"/>
-      <c r="E47" s="289" t="n"/>
-      <c r="F47" s="289" t="n"/>
-      <c r="G47" s="289" t="n"/>
-      <c r="H47" s="289" t="n"/>
-      <c r="I47" s="289" t="n"/>
-      <c r="J47" s="290" t="n"/>
+      <c r="B47" s="487" t="n"/>
+      <c r="C47" s="487" t="n"/>
+      <c r="D47" s="487" t="n"/>
+      <c r="E47" s="487" t="n"/>
+      <c r="F47" s="487" t="n"/>
+      <c r="G47" s="487" t="n"/>
+      <c r="H47" s="487" t="n"/>
+      <c r="I47" s="487" t="n"/>
+      <c r="J47" s="486" t="n"/>
+      <c r="K47" s="447" t="n"/>
+      <c r="L47" s="447" t="n"/>
+      <c r="M47" s="447" t="n"/>
+      <c r="N47" s="447" t="n"/>
+      <c r="O47" s="447" t="n"/>
+      <c r="P47" s="447" t="n"/>
+      <c r="Q47" s="447" t="n"/>
+      <c r="R47" s="447" t="n"/>
+      <c r="S47" s="447" t="n"/>
+      <c r="T47" s="447" t="n"/>
+      <c r="U47" s="447" t="n"/>
+      <c r="V47" s="447" t="n"/>
+      <c r="W47" s="447" t="n"/>
+      <c r="X47" s="447" t="n"/>
+      <c r="Y47" s="447" t="n"/>
+      <c r="Z47" s="447" t="n"/>
+      <c r="AA47" s="447" t="n"/>
+      <c r="AB47" s="447" t="n"/>
+      <c r="AC47" s="447" t="n"/>
+      <c r="AD47" s="447" t="n"/>
+      <c r="AE47" s="447" t="n"/>
+      <c r="AF47" s="447" t="n"/>
+      <c r="AG47" s="447" t="n"/>
+      <c r="AH47" s="447" t="n"/>
+      <c r="AI47" s="447" t="n"/>
+      <c r="AJ47" s="447" t="n"/>
+      <c r="AK47" s="447" t="n"/>
+      <c r="AL47" s="447" t="n"/>
+      <c r="AM47" s="447" t="n"/>
+      <c r="AN47" s="447" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="1"/>
     <row r="49" hidden="1" outlineLevel="1"/>
@@ -6334,9 +8134,8 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6347,118 +8146,416 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col hidden="1" width="20" customWidth="1" min="4" max="16384"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col hidden="1" width="2.33" customWidth="1" min="4" max="16384"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="430" t="inlineStr">
         <is>
           <t>VAL_DECISION_GATE_CORE</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="430" t="inlineStr">
         <is>
           <t>VAL_ESCALATION_LEVEL</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="430" t="inlineStr">
         <is>
           <t>VAL_STATUS_CORE</t>
         </is>
       </c>
+      <c r="D1" s="430" t="n"/>
+      <c r="E1" s="430" t="n"/>
+      <c r="F1" s="430" t="n"/>
+      <c r="G1" s="430" t="n"/>
+      <c r="H1" s="430" t="n"/>
+      <c r="I1" s="430" t="n"/>
+      <c r="J1" s="430" t="n"/>
+      <c r="K1" s="430" t="n"/>
+      <c r="L1" s="430" t="n"/>
+      <c r="M1" s="430" t="n"/>
+      <c r="N1" s="430" t="n"/>
+      <c r="O1" s="430" t="n"/>
+      <c r="P1" s="430" t="n"/>
+      <c r="Q1" s="430" t="n"/>
+      <c r="R1" s="430" t="n"/>
+      <c r="S1" s="430" t="n"/>
+      <c r="T1" s="430" t="n"/>
+      <c r="U1" s="430" t="n"/>
+      <c r="V1" s="430" t="n"/>
+      <c r="W1" s="430" t="n"/>
+      <c r="X1" s="430" t="n"/>
+      <c r="Y1" s="430" t="n"/>
+      <c r="Z1" s="430" t="n"/>
+      <c r="AA1" s="430" t="n"/>
+      <c r="AB1" s="430" t="n"/>
+      <c r="AC1" s="430" t="n"/>
+      <c r="AD1" s="430" t="n"/>
+      <c r="AE1" s="430" t="n"/>
+      <c r="AF1" s="430" t="n"/>
+      <c r="AG1" s="430" t="n"/>
+      <c r="AH1" s="430" t="n"/>
+      <c r="AI1" s="430" t="n"/>
+      <c r="AJ1" s="430" t="n"/>
+      <c r="AK1" s="430" t="n"/>
+      <c r="AL1" s="430" t="n"/>
+      <c r="AM1" s="430" t="n"/>
+      <c r="AN1" s="430" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="430" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="430" t="inlineStr">
         <is>
           <t>TIER 1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="430" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
+      <c r="D2" s="430" t="n"/>
+      <c r="E2" s="430" t="n"/>
+      <c r="F2" s="430" t="n"/>
+      <c r="G2" s="430" t="n"/>
+      <c r="H2" s="430" t="n"/>
+      <c r="I2" s="430" t="n"/>
+      <c r="J2" s="430" t="n"/>
+      <c r="K2" s="430" t="n"/>
+      <c r="L2" s="430" t="n"/>
+      <c r="M2" s="430" t="n"/>
+      <c r="N2" s="430" t="n"/>
+      <c r="O2" s="430" t="n"/>
+      <c r="P2" s="430" t="n"/>
+      <c r="Q2" s="430" t="n"/>
+      <c r="R2" s="430" t="n"/>
+      <c r="S2" s="430" t="n"/>
+      <c r="T2" s="430" t="n"/>
+      <c r="U2" s="430" t="n"/>
+      <c r="V2" s="430" t="n"/>
+      <c r="W2" s="430" t="n"/>
+      <c r="X2" s="430" t="n"/>
+      <c r="Y2" s="430" t="n"/>
+      <c r="Z2" s="430" t="n"/>
+      <c r="AA2" s="430" t="n"/>
+      <c r="AB2" s="430" t="n"/>
+      <c r="AC2" s="430" t="n"/>
+      <c r="AD2" s="430" t="n"/>
+      <c r="AE2" s="430" t="n"/>
+      <c r="AF2" s="430" t="n"/>
+      <c r="AG2" s="430" t="n"/>
+      <c r="AH2" s="430" t="n"/>
+      <c r="AI2" s="430" t="n"/>
+      <c r="AJ2" s="430" t="n"/>
+      <c r="AK2" s="430" t="n"/>
+      <c r="AL2" s="430" t="n"/>
+      <c r="AM2" s="430" t="n"/>
+      <c r="AN2" s="430" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="430" t="inlineStr">
         <is>
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="430" t="inlineStr">
         <is>
           <t>TIER 2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="430" t="inlineStr">
         <is>
           <t>IN PROGRESS</t>
         </is>
       </c>
+      <c r="D3" s="430" t="n"/>
+      <c r="E3" s="430" t="n"/>
+      <c r="F3" s="430" t="n"/>
+      <c r="G3" s="430" t="n"/>
+      <c r="H3" s="430" t="n"/>
+      <c r="I3" s="430" t="n"/>
+      <c r="J3" s="430" t="n"/>
+      <c r="K3" s="430" t="n"/>
+      <c r="L3" s="430" t="n"/>
+      <c r="M3" s="430" t="n"/>
+      <c r="N3" s="430" t="n"/>
+      <c r="O3" s="430" t="n"/>
+      <c r="P3" s="430" t="n"/>
+      <c r="Q3" s="430" t="n"/>
+      <c r="R3" s="430" t="n"/>
+      <c r="S3" s="430" t="n"/>
+      <c r="T3" s="430" t="n"/>
+      <c r="U3" s="430" t="n"/>
+      <c r="V3" s="430" t="n"/>
+      <c r="W3" s="430" t="n"/>
+      <c r="X3" s="430" t="n"/>
+      <c r="Y3" s="430" t="n"/>
+      <c r="Z3" s="430" t="n"/>
+      <c r="AA3" s="430" t="n"/>
+      <c r="AB3" s="430" t="n"/>
+      <c r="AC3" s="430" t="n"/>
+      <c r="AD3" s="430" t="n"/>
+      <c r="AE3" s="430" t="n"/>
+      <c r="AF3" s="430" t="n"/>
+      <c r="AG3" s="430" t="n"/>
+      <c r="AH3" s="430" t="n"/>
+      <c r="AI3" s="430" t="n"/>
+      <c r="AJ3" s="430" t="n"/>
+      <c r="AK3" s="430" t="n"/>
+      <c r="AL3" s="430" t="n"/>
+      <c r="AM3" s="430" t="n"/>
+      <c r="AN3" s="430" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="430" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="430" t="inlineStr">
         <is>
           <t>TIER 3</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="430" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
+      <c r="D4" s="430" t="n"/>
+      <c r="E4" s="430" t="n"/>
+      <c r="F4" s="430" t="n"/>
+      <c r="G4" s="430" t="n"/>
+      <c r="H4" s="430" t="n"/>
+      <c r="I4" s="430" t="n"/>
+      <c r="J4" s="430" t="n"/>
+      <c r="K4" s="430" t="n"/>
+      <c r="L4" s="430" t="n"/>
+      <c r="M4" s="430" t="n"/>
+      <c r="N4" s="430" t="n"/>
+      <c r="O4" s="430" t="n"/>
+      <c r="P4" s="430" t="n"/>
+      <c r="Q4" s="430" t="n"/>
+      <c r="R4" s="430" t="n"/>
+      <c r="S4" s="430" t="n"/>
+      <c r="T4" s="430" t="n"/>
+      <c r="U4" s="430" t="n"/>
+      <c r="V4" s="430" t="n"/>
+      <c r="W4" s="430" t="n"/>
+      <c r="X4" s="430" t="n"/>
+      <c r="Y4" s="430" t="n"/>
+      <c r="Z4" s="430" t="n"/>
+      <c r="AA4" s="430" t="n"/>
+      <c r="AB4" s="430" t="n"/>
+      <c r="AC4" s="430" t="n"/>
+      <c r="AD4" s="430" t="n"/>
+      <c r="AE4" s="430" t="n"/>
+      <c r="AF4" s="430" t="n"/>
+      <c r="AG4" s="430" t="n"/>
+      <c r="AH4" s="430" t="n"/>
+      <c r="AI4" s="430" t="n"/>
+      <c r="AJ4" s="430" t="n"/>
+      <c r="AK4" s="430" t="n"/>
+      <c r="AL4" s="430" t="n"/>
+      <c r="AM4" s="430" t="n"/>
+      <c r="AN4" s="430" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="430" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="430" t="inlineStr">
         <is>
           <t>WAR ROOM</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="430" t="inlineStr">
         <is>
           <t>MONITORING</t>
         </is>
       </c>
+      <c r="D5" s="430" t="n"/>
+      <c r="E5" s="430" t="n"/>
+      <c r="F5" s="430" t="n"/>
+      <c r="G5" s="430" t="n"/>
+      <c r="H5" s="430" t="n"/>
+      <c r="I5" s="430" t="n"/>
+      <c r="J5" s="430" t="n"/>
+      <c r="K5" s="430" t="n"/>
+      <c r="L5" s="430" t="n"/>
+      <c r="M5" s="430" t="n"/>
+      <c r="N5" s="430" t="n"/>
+      <c r="O5" s="430" t="n"/>
+      <c r="P5" s="430" t="n"/>
+      <c r="Q5" s="430" t="n"/>
+      <c r="R5" s="430" t="n"/>
+      <c r="S5" s="430" t="n"/>
+      <c r="T5" s="430" t="n"/>
+      <c r="U5" s="430" t="n"/>
+      <c r="V5" s="430" t="n"/>
+      <c r="W5" s="430" t="n"/>
+      <c r="X5" s="430" t="n"/>
+      <c r="Y5" s="430" t="n"/>
+      <c r="Z5" s="430" t="n"/>
+      <c r="AA5" s="430" t="n"/>
+      <c r="AB5" s="430" t="n"/>
+      <c r="AC5" s="430" t="n"/>
+      <c r="AD5" s="430" t="n"/>
+      <c r="AE5" s="430" t="n"/>
+      <c r="AF5" s="430" t="n"/>
+      <c r="AG5" s="430" t="n"/>
+      <c r="AH5" s="430" t="n"/>
+      <c r="AI5" s="430" t="n"/>
+      <c r="AJ5" s="430" t="n"/>
+      <c r="AK5" s="430" t="n"/>
+      <c r="AL5" s="430" t="n"/>
+      <c r="AM5" s="430" t="n"/>
+      <c r="AN5" s="430" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="430" t="n"/>
+      <c r="B6" s="430" t="inlineStr">
         <is>
           <t>CUSTOMER</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="430" t="inlineStr">
         <is>
           <t>SUPERSEDED</t>
         </is>
       </c>
+      <c r="D6" s="430" t="n"/>
+      <c r="E6" s="430" t="n"/>
+      <c r="F6" s="430" t="n"/>
+      <c r="G6" s="430" t="n"/>
+      <c r="H6" s="430" t="n"/>
+      <c r="I6" s="430" t="n"/>
+      <c r="J6" s="430" t="n"/>
+      <c r="K6" s="430" t="n"/>
+      <c r="L6" s="430" t="n"/>
+      <c r="M6" s="430" t="n"/>
+      <c r="N6" s="430" t="n"/>
+      <c r="O6" s="430" t="n"/>
+      <c r="P6" s="430" t="n"/>
+      <c r="Q6" s="430" t="n"/>
+      <c r="R6" s="430" t="n"/>
+      <c r="S6" s="430" t="n"/>
+      <c r="T6" s="430" t="n"/>
+      <c r="U6" s="430" t="n"/>
+      <c r="V6" s="430" t="n"/>
+      <c r="W6" s="430" t="n"/>
+      <c r="X6" s="430" t="n"/>
+      <c r="Y6" s="430" t="n"/>
+      <c r="Z6" s="430" t="n"/>
+      <c r="AA6" s="430" t="n"/>
+      <c r="AB6" s="430" t="n"/>
+      <c r="AC6" s="430" t="n"/>
+      <c r="AD6" s="430" t="n"/>
+      <c r="AE6" s="430" t="n"/>
+      <c r="AF6" s="430" t="n"/>
+      <c r="AG6" s="430" t="n"/>
+      <c r="AH6" s="430" t="n"/>
+      <c r="AI6" s="430" t="n"/>
+      <c r="AJ6" s="430" t="n"/>
+      <c r="AK6" s="430" t="n"/>
+      <c r="AL6" s="430" t="n"/>
+      <c r="AM6" s="430" t="n"/>
+      <c r="AN6" s="430" t="n"/>
     </row>
     <row r="7">
-      <c r="C7" t="inlineStr">
+      <c r="A7" s="430" t="n"/>
+      <c r="B7" s="430" t="n"/>
+      <c r="C7" s="430" t="inlineStr">
         <is>
           <t>VOID</t>
         </is>
       </c>
+      <c r="D7" s="430" t="n"/>
+      <c r="E7" s="430" t="n"/>
+      <c r="F7" s="430" t="n"/>
+      <c r="G7" s="430" t="n"/>
+      <c r="H7" s="430" t="n"/>
+      <c r="I7" s="430" t="n"/>
+      <c r="J7" s="430" t="n"/>
+      <c r="K7" s="430" t="n"/>
+      <c r="L7" s="430" t="n"/>
+      <c r="M7" s="430" t="n"/>
+      <c r="N7" s="430" t="n"/>
+      <c r="O7" s="430" t="n"/>
+      <c r="P7" s="430" t="n"/>
+      <c r="Q7" s="430" t="n"/>
+      <c r="R7" s="430" t="n"/>
+      <c r="S7" s="430" t="n"/>
+      <c r="T7" s="430" t="n"/>
+      <c r="U7" s="430" t="n"/>
+      <c r="V7" s="430" t="n"/>
+      <c r="W7" s="430" t="n"/>
+      <c r="X7" s="430" t="n"/>
+      <c r="Y7" s="430" t="n"/>
+      <c r="Z7" s="430" t="n"/>
+      <c r="AA7" s="430" t="n"/>
+      <c r="AB7" s="430" t="n"/>
+      <c r="AC7" s="430" t="n"/>
+      <c r="AD7" s="430" t="n"/>
+      <c r="AE7" s="430" t="n"/>
+      <c r="AF7" s="430" t="n"/>
+      <c r="AG7" s="430" t="n"/>
+      <c r="AH7" s="430" t="n"/>
+      <c r="AI7" s="430" t="n"/>
+      <c r="AJ7" s="430" t="n"/>
+      <c r="AK7" s="430" t="n"/>
+      <c r="AL7" s="430" t="n"/>
+      <c r="AM7" s="430" t="n"/>
+      <c r="AN7" s="430" t="n"/>
     </row>
     <row r="8" hidden="1"/>
     <row r="9" hidden="1"/>
@@ -6654,7 +8751,8 @@
     <row r="199" hidden="1"/>
     <row r="200" hidden="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -6664,142 +8762,478 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col hidden="1" width="13" customWidth="1" min="5" max="16384"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col hidden="1" width="2.33" customWidth="1" min="5" max="16384"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="430" t="inlineStr">
         <is>
           <t>REF_CUSTOMER_MASTER</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="430" t="inlineStr">
         <is>
           <t>REF_EVIDENCE_LINK</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="430" t="inlineStr">
         <is>
           <t>REF_OWNER_PERSON_MASTER</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="430" t="inlineStr">
         <is>
           <t>REF_PART_REV_MASTER</t>
         </is>
       </c>
+      <c r="E1" s="430" t="n"/>
+      <c r="F1" s="430" t="n"/>
+      <c r="G1" s="430" t="n"/>
+      <c r="H1" s="430" t="n"/>
+      <c r="I1" s="430" t="n"/>
+      <c r="J1" s="430" t="n"/>
+      <c r="K1" s="430" t="n"/>
+      <c r="L1" s="430" t="n"/>
+      <c r="M1" s="430" t="n"/>
+      <c r="N1" s="430" t="n"/>
+      <c r="O1" s="430" t="n"/>
+      <c r="P1" s="430" t="n"/>
+      <c r="Q1" s="430" t="n"/>
+      <c r="R1" s="430" t="n"/>
+      <c r="S1" s="430" t="n"/>
+      <c r="T1" s="430" t="n"/>
+      <c r="U1" s="430" t="n"/>
+      <c r="V1" s="430" t="n"/>
+      <c r="W1" s="430" t="n"/>
+      <c r="X1" s="430" t="n"/>
+      <c r="Y1" s="430" t="n"/>
+      <c r="Z1" s="430" t="n"/>
+      <c r="AA1" s="430" t="n"/>
+      <c r="AB1" s="430" t="n"/>
+      <c r="AC1" s="430" t="n"/>
+      <c r="AD1" s="430" t="n"/>
+      <c r="AE1" s="430" t="n"/>
+      <c r="AF1" s="430" t="n"/>
+      <c r="AG1" s="430" t="n"/>
+      <c r="AH1" s="430" t="n"/>
+      <c r="AI1" s="430" t="n"/>
+      <c r="AJ1" s="430" t="n"/>
+      <c r="AK1" s="430" t="n"/>
+      <c r="AL1" s="430" t="n"/>
+      <c r="AM1" s="430" t="n"/>
+      <c r="AN1" s="430" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="430" t="inlineStr">
         <is>
           <t>CUST-001 Alpha Semi</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="430" t="inlineStr">
         <is>
           <t>M365://dossier/JOB-240001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="430" t="inlineStr">
         <is>
           <t>Planning Lead</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="430" t="inlineStr">
         <is>
           <t>PN-1001 / Rev.A</t>
         </is>
       </c>
+      <c r="E2" s="430" t="n"/>
+      <c r="F2" s="430" t="n"/>
+      <c r="G2" s="430" t="n"/>
+      <c r="H2" s="430" t="n"/>
+      <c r="I2" s="430" t="n"/>
+      <c r="J2" s="430" t="n"/>
+      <c r="K2" s="430" t="n"/>
+      <c r="L2" s="430" t="n"/>
+      <c r="M2" s="430" t="n"/>
+      <c r="N2" s="430" t="n"/>
+      <c r="O2" s="430" t="n"/>
+      <c r="P2" s="430" t="n"/>
+      <c r="Q2" s="430" t="n"/>
+      <c r="R2" s="430" t="n"/>
+      <c r="S2" s="430" t="n"/>
+      <c r="T2" s="430" t="n"/>
+      <c r="U2" s="430" t="n"/>
+      <c r="V2" s="430" t="n"/>
+      <c r="W2" s="430" t="n"/>
+      <c r="X2" s="430" t="n"/>
+      <c r="Y2" s="430" t="n"/>
+      <c r="Z2" s="430" t="n"/>
+      <c r="AA2" s="430" t="n"/>
+      <c r="AB2" s="430" t="n"/>
+      <c r="AC2" s="430" t="n"/>
+      <c r="AD2" s="430" t="n"/>
+      <c r="AE2" s="430" t="n"/>
+      <c r="AF2" s="430" t="n"/>
+      <c r="AG2" s="430" t="n"/>
+      <c r="AH2" s="430" t="n"/>
+      <c r="AI2" s="430" t="n"/>
+      <c r="AJ2" s="430" t="n"/>
+      <c r="AK2" s="430" t="n"/>
+      <c r="AL2" s="430" t="n"/>
+      <c r="AM2" s="430" t="n"/>
+      <c r="AN2" s="430" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="430" t="inlineStr">
         <is>
           <t>CUST-002 NovaFab</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="430" t="inlineStr">
         <is>
           <t>SP://evidence/FRM-202/001</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="430" t="inlineStr">
         <is>
           <t>Production Supervisor</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="430" t="inlineStr">
         <is>
           <t>PN-1002 / Rev.B</t>
         </is>
       </c>
+      <c r="E3" s="430" t="n"/>
+      <c r="F3" s="430" t="n"/>
+      <c r="G3" s="430" t="n"/>
+      <c r="H3" s="430" t="n"/>
+      <c r="I3" s="430" t="n"/>
+      <c r="J3" s="430" t="n"/>
+      <c r="K3" s="430" t="n"/>
+      <c r="L3" s="430" t="n"/>
+      <c r="M3" s="430" t="n"/>
+      <c r="N3" s="430" t="n"/>
+      <c r="O3" s="430" t="n"/>
+      <c r="P3" s="430" t="n"/>
+      <c r="Q3" s="430" t="n"/>
+      <c r="R3" s="430" t="n"/>
+      <c r="S3" s="430" t="n"/>
+      <c r="T3" s="430" t="n"/>
+      <c r="U3" s="430" t="n"/>
+      <c r="V3" s="430" t="n"/>
+      <c r="W3" s="430" t="n"/>
+      <c r="X3" s="430" t="n"/>
+      <c r="Y3" s="430" t="n"/>
+      <c r="Z3" s="430" t="n"/>
+      <c r="AA3" s="430" t="n"/>
+      <c r="AB3" s="430" t="n"/>
+      <c r="AC3" s="430" t="n"/>
+      <c r="AD3" s="430" t="n"/>
+      <c r="AE3" s="430" t="n"/>
+      <c r="AF3" s="430" t="n"/>
+      <c r="AG3" s="430" t="n"/>
+      <c r="AH3" s="430" t="n"/>
+      <c r="AI3" s="430" t="n"/>
+      <c r="AJ3" s="430" t="n"/>
+      <c r="AK3" s="430" t="n"/>
+      <c r="AL3" s="430" t="n"/>
+      <c r="AM3" s="430" t="n"/>
+      <c r="AN3" s="430" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="430" t="inlineStr">
         <is>
           <t>CUST-003 Orion Tech</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="430" t="inlineStr">
         <is>
           <t>SP://evidence/FRM-306/002</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="430" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="430" t="inlineStr">
         <is>
           <t>PN-1003 / Rev.C</t>
         </is>
       </c>
+      <c r="E4" s="430" t="n"/>
+      <c r="F4" s="430" t="n"/>
+      <c r="G4" s="430" t="n"/>
+      <c r="H4" s="430" t="n"/>
+      <c r="I4" s="430" t="n"/>
+      <c r="J4" s="430" t="n"/>
+      <c r="K4" s="430" t="n"/>
+      <c r="L4" s="430" t="n"/>
+      <c r="M4" s="430" t="n"/>
+      <c r="N4" s="430" t="n"/>
+      <c r="O4" s="430" t="n"/>
+      <c r="P4" s="430" t="n"/>
+      <c r="Q4" s="430" t="n"/>
+      <c r="R4" s="430" t="n"/>
+      <c r="S4" s="430" t="n"/>
+      <c r="T4" s="430" t="n"/>
+      <c r="U4" s="430" t="n"/>
+      <c r="V4" s="430" t="n"/>
+      <c r="W4" s="430" t="n"/>
+      <c r="X4" s="430" t="n"/>
+      <c r="Y4" s="430" t="n"/>
+      <c r="Z4" s="430" t="n"/>
+      <c r="AA4" s="430" t="n"/>
+      <c r="AB4" s="430" t="n"/>
+      <c r="AC4" s="430" t="n"/>
+      <c r="AD4" s="430" t="n"/>
+      <c r="AE4" s="430" t="n"/>
+      <c r="AF4" s="430" t="n"/>
+      <c r="AG4" s="430" t="n"/>
+      <c r="AH4" s="430" t="n"/>
+      <c r="AI4" s="430" t="n"/>
+      <c r="AJ4" s="430" t="n"/>
+      <c r="AK4" s="430" t="n"/>
+      <c r="AL4" s="430" t="n"/>
+      <c r="AM4" s="430" t="n"/>
+      <c r="AN4" s="430" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="430" t="inlineStr">
         <is>
           <t>CUST-004 Quantum Devices</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="430" t="inlineStr">
         <is>
           <t>Epicor://Job/JOB-240001</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="430" t="inlineStr">
         <is>
           <t>Engineering Lead</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="430" t="inlineStr">
         <is>
           <t>PN-1004 / Rev.D</t>
         </is>
       </c>
+      <c r="E5" s="430" t="n"/>
+      <c r="F5" s="430" t="n"/>
+      <c r="G5" s="430" t="n"/>
+      <c r="H5" s="430" t="n"/>
+      <c r="I5" s="430" t="n"/>
+      <c r="J5" s="430" t="n"/>
+      <c r="K5" s="430" t="n"/>
+      <c r="L5" s="430" t="n"/>
+      <c r="M5" s="430" t="n"/>
+      <c r="N5" s="430" t="n"/>
+      <c r="O5" s="430" t="n"/>
+      <c r="P5" s="430" t="n"/>
+      <c r="Q5" s="430" t="n"/>
+      <c r="R5" s="430" t="n"/>
+      <c r="S5" s="430" t="n"/>
+      <c r="T5" s="430" t="n"/>
+      <c r="U5" s="430" t="n"/>
+      <c r="V5" s="430" t="n"/>
+      <c r="W5" s="430" t="n"/>
+      <c r="X5" s="430" t="n"/>
+      <c r="Y5" s="430" t="n"/>
+      <c r="Z5" s="430" t="n"/>
+      <c r="AA5" s="430" t="n"/>
+      <c r="AB5" s="430" t="n"/>
+      <c r="AC5" s="430" t="n"/>
+      <c r="AD5" s="430" t="n"/>
+      <c r="AE5" s="430" t="n"/>
+      <c r="AF5" s="430" t="n"/>
+      <c r="AG5" s="430" t="n"/>
+      <c r="AH5" s="430" t="n"/>
+      <c r="AI5" s="430" t="n"/>
+      <c r="AJ5" s="430" t="n"/>
+      <c r="AK5" s="430" t="n"/>
+      <c r="AL5" s="430" t="n"/>
+      <c r="AM5" s="430" t="n"/>
+      <c r="AN5" s="430" t="n"/>
     </row>
     <row r="6">
-      <c r="C6" t="inlineStr">
+      <c r="A6" s="430" t="n"/>
+      <c r="B6" s="430" t="n"/>
+      <c r="C6" s="430" t="inlineStr">
         <is>
           <t>Setup Technician</t>
         </is>
       </c>
+      <c r="D6" s="430" t="n"/>
+      <c r="E6" s="430" t="n"/>
+      <c r="F6" s="430" t="n"/>
+      <c r="G6" s="430" t="n"/>
+      <c r="H6" s="430" t="n"/>
+      <c r="I6" s="430" t="n"/>
+      <c r="J6" s="430" t="n"/>
+      <c r="K6" s="430" t="n"/>
+      <c r="L6" s="430" t="n"/>
+      <c r="M6" s="430" t="n"/>
+      <c r="N6" s="430" t="n"/>
+      <c r="O6" s="430" t="n"/>
+      <c r="P6" s="430" t="n"/>
+      <c r="Q6" s="430" t="n"/>
+      <c r="R6" s="430" t="n"/>
+      <c r="S6" s="430" t="n"/>
+      <c r="T6" s="430" t="n"/>
+      <c r="U6" s="430" t="n"/>
+      <c r="V6" s="430" t="n"/>
+      <c r="W6" s="430" t="n"/>
+      <c r="X6" s="430" t="n"/>
+      <c r="Y6" s="430" t="n"/>
+      <c r="Z6" s="430" t="n"/>
+      <c r="AA6" s="430" t="n"/>
+      <c r="AB6" s="430" t="n"/>
+      <c r="AC6" s="430" t="n"/>
+      <c r="AD6" s="430" t="n"/>
+      <c r="AE6" s="430" t="n"/>
+      <c r="AF6" s="430" t="n"/>
+      <c r="AG6" s="430" t="n"/>
+      <c r="AH6" s="430" t="n"/>
+      <c r="AI6" s="430" t="n"/>
+      <c r="AJ6" s="430" t="n"/>
+      <c r="AK6" s="430" t="n"/>
+      <c r="AL6" s="430" t="n"/>
+      <c r="AM6" s="430" t="n"/>
+      <c r="AN6" s="430" t="n"/>
     </row>
     <row r="7">
-      <c r="C7" t="inlineStr">
+      <c r="A7" s="430" t="n"/>
+      <c r="B7" s="430" t="n"/>
+      <c r="C7" s="430" t="inlineStr">
         <is>
           <t>Maintenance Lead</t>
         </is>
       </c>
+      <c r="D7" s="430" t="n"/>
+      <c r="E7" s="430" t="n"/>
+      <c r="F7" s="430" t="n"/>
+      <c r="G7" s="430" t="n"/>
+      <c r="H7" s="430" t="n"/>
+      <c r="I7" s="430" t="n"/>
+      <c r="J7" s="430" t="n"/>
+      <c r="K7" s="430" t="n"/>
+      <c r="L7" s="430" t="n"/>
+      <c r="M7" s="430" t="n"/>
+      <c r="N7" s="430" t="n"/>
+      <c r="O7" s="430" t="n"/>
+      <c r="P7" s="430" t="n"/>
+      <c r="Q7" s="430" t="n"/>
+      <c r="R7" s="430" t="n"/>
+      <c r="S7" s="430" t="n"/>
+      <c r="T7" s="430" t="n"/>
+      <c r="U7" s="430" t="n"/>
+      <c r="V7" s="430" t="n"/>
+      <c r="W7" s="430" t="n"/>
+      <c r="X7" s="430" t="n"/>
+      <c r="Y7" s="430" t="n"/>
+      <c r="Z7" s="430" t="n"/>
+      <c r="AA7" s="430" t="n"/>
+      <c r="AB7" s="430" t="n"/>
+      <c r="AC7" s="430" t="n"/>
+      <c r="AD7" s="430" t="n"/>
+      <c r="AE7" s="430" t="n"/>
+      <c r="AF7" s="430" t="n"/>
+      <c r="AG7" s="430" t="n"/>
+      <c r="AH7" s="430" t="n"/>
+      <c r="AI7" s="430" t="n"/>
+      <c r="AJ7" s="430" t="n"/>
+      <c r="AK7" s="430" t="n"/>
+      <c r="AL7" s="430" t="n"/>
+      <c r="AM7" s="430" t="n"/>
+      <c r="AN7" s="430" t="n"/>
     </row>
-    <row r="8">
-      <c r="C8" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="447" t="n"/>
+      <c r="B8" s="447" t="n"/>
+      <c r="C8" s="447" t="inlineStr">
         <is>
           <t>Commercial Owner</t>
         </is>
       </c>
+      <c r="D8" s="447" t="n"/>
+      <c r="E8" s="447" t="n"/>
+      <c r="F8" s="447" t="n"/>
+      <c r="G8" s="447" t="n"/>
+      <c r="H8" s="447" t="n"/>
+      <c r="I8" s="447" t="n"/>
+      <c r="J8" s="447" t="n"/>
+      <c r="K8" s="447" t="n"/>
+      <c r="L8" s="447" t="n"/>
+      <c r="M8" s="447" t="n"/>
+      <c r="N8" s="447" t="n"/>
+      <c r="O8" s="447" t="n"/>
+      <c r="P8" s="447" t="n"/>
+      <c r="Q8" s="447" t="n"/>
+      <c r="R8" s="447" t="n"/>
+      <c r="S8" s="447" t="n"/>
+      <c r="T8" s="447" t="n"/>
+      <c r="U8" s="447" t="n"/>
+      <c r="V8" s="447" t="n"/>
+      <c r="W8" s="447" t="n"/>
+      <c r="X8" s="447" t="n"/>
+      <c r="Y8" s="447" t="n"/>
+      <c r="Z8" s="447" t="n"/>
+      <c r="AA8" s="447" t="n"/>
+      <c r="AB8" s="447" t="n"/>
+      <c r="AC8" s="447" t="n"/>
+      <c r="AD8" s="447" t="n"/>
+      <c r="AE8" s="447" t="n"/>
+      <c r="AF8" s="447" t="n"/>
+      <c r="AG8" s="447" t="n"/>
+      <c r="AH8" s="447" t="n"/>
+      <c r="AI8" s="447" t="n"/>
+      <c r="AJ8" s="447" t="n"/>
+      <c r="AK8" s="447" t="n"/>
+      <c r="AL8" s="447" t="n"/>
+      <c r="AM8" s="447" t="n"/>
+      <c r="AN8" s="447" t="n"/>
     </row>
     <row r="9" hidden="1"/>
     <row r="10" hidden="1"/>
@@ -6994,7 +9428,8 @@
     <row r="199" hidden="1"/>
     <row r="200" hidden="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -7004,472 +9439,1344 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:AN26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9.81" customWidth="1" min="1" max="1"/>
-    <col width="13.49" customWidth="1" min="2" max="2"/>
-    <col width="22.08" customWidth="1" min="3" max="3"/>
-    <col width="12.26" customWidth="1" min="4" max="4"/>
-    <col width="15.94" customWidth="1" min="5" max="5"/>
-    <col width="14.72" customWidth="1" min="6" max="6"/>
-    <col width="19.62" customWidth="1" min="7" max="7"/>
-    <col width="22.08" customWidth="1" min="8" max="8"/>
-    <col hidden="1" outlineLevel="1" width="13" customWidth="1" min="9" max="16384"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col hidden="1" outlineLevel="1" width="2.33" customWidth="1" min="9" max="16384"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="413" t="n"/>
-      <c r="B1" s="310" t="n"/>
-      <c r="C1" s="414" t="inlineStr">
+      <c r="A1" s="424" t="n"/>
+      <c r="B1" s="496" t="n"/>
+      <c r="C1" s="426" t="inlineStr">
         <is>
           <t>PERIODIC REVIEW RECORD</t>
         </is>
       </c>
-      <c r="D1" s="268" t="n"/>
-      <c r="E1" s="268" t="n"/>
-      <c r="F1" s="310" t="n"/>
-      <c r="G1" s="343" t="inlineStr">
+      <c r="D1" s="497" t="n"/>
+      <c r="E1" s="497" t="n"/>
+      <c r="F1" s="496" t="n"/>
+      <c r="G1" s="428" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="H1" s="344" t="inlineStr">
+      <c r="H1" s="429" t="inlineStr">
         <is>
           <t>FRM-213</t>
         </is>
       </c>
+      <c r="I1" s="430" t="n"/>
+      <c r="J1" s="430" t="n"/>
+      <c r="K1" s="430" t="n"/>
+      <c r="L1" s="430" t="n"/>
+      <c r="M1" s="430" t="n"/>
+      <c r="N1" s="430" t="n"/>
+      <c r="O1" s="430" t="n"/>
+      <c r="P1" s="430" t="n"/>
+      <c r="Q1" s="430" t="n"/>
+      <c r="R1" s="430" t="n"/>
+      <c r="S1" s="430" t="n"/>
+      <c r="T1" s="430" t="n"/>
+      <c r="U1" s="430" t="n"/>
+      <c r="V1" s="430" t="n"/>
+      <c r="W1" s="430" t="n"/>
+      <c r="X1" s="430" t="n"/>
+      <c r="Y1" s="430" t="n"/>
+      <c r="Z1" s="430" t="n"/>
+      <c r="AA1" s="430" t="n"/>
+      <c r="AB1" s="430" t="n"/>
+      <c r="AC1" s="430" t="n"/>
+      <c r="AD1" s="430" t="n"/>
+      <c r="AE1" s="430" t="n"/>
+      <c r="AF1" s="430" t="n"/>
+      <c r="AG1" s="430" t="n"/>
+      <c r="AH1" s="430" t="n"/>
+      <c r="AI1" s="430" t="n"/>
+      <c r="AJ1" s="430" t="n"/>
+      <c r="AK1" s="430" t="n"/>
+      <c r="AL1" s="430" t="n"/>
+      <c r="AM1" s="430" t="n"/>
+      <c r="AN1" s="430" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="B2" s="312" t="n"/>
-      <c r="C2" s="275" t="n"/>
-      <c r="F2" s="312" t="n"/>
-      <c r="G2" s="350" t="inlineStr">
+      <c r="A2" s="498" t="n"/>
+      <c r="B2" s="499" t="n"/>
+      <c r="C2" s="498" t="n"/>
+      <c r="F2" s="499" t="n"/>
+      <c r="G2" s="428" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="H2" s="351" t="inlineStr">
+      <c r="H2" s="429" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
+      <c r="I2" s="430" t="n"/>
+      <c r="J2" s="430" t="n"/>
+      <c r="K2" s="430" t="n"/>
+      <c r="L2" s="430" t="n"/>
+      <c r="M2" s="430" t="n"/>
+      <c r="N2" s="430" t="n"/>
+      <c r="O2" s="430" t="n"/>
+      <c r="P2" s="430" t="n"/>
+      <c r="Q2" s="430" t="n"/>
+      <c r="R2" s="430" t="n"/>
+      <c r="S2" s="430" t="n"/>
+      <c r="T2" s="430" t="n"/>
+      <c r="U2" s="430" t="n"/>
+      <c r="V2" s="430" t="n"/>
+      <c r="W2" s="430" t="n"/>
+      <c r="X2" s="430" t="n"/>
+      <c r="Y2" s="430" t="n"/>
+      <c r="Z2" s="430" t="n"/>
+      <c r="AA2" s="430" t="n"/>
+      <c r="AB2" s="430" t="n"/>
+      <c r="AC2" s="430" t="n"/>
+      <c r="AD2" s="430" t="n"/>
+      <c r="AE2" s="430" t="n"/>
+      <c r="AF2" s="430" t="n"/>
+      <c r="AG2" s="430" t="n"/>
+      <c r="AH2" s="430" t="n"/>
+      <c r="AI2" s="430" t="n"/>
+      <c r="AJ2" s="430" t="n"/>
+      <c r="AK2" s="430" t="n"/>
+      <c r="AL2" s="430" t="n"/>
+      <c r="AM2" s="430" t="n"/>
+      <c r="AN2" s="430" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="B3" s="312" t="n"/>
-      <c r="C3" s="282" t="n"/>
-      <c r="D3" s="283" t="n"/>
-      <c r="E3" s="283" t="n"/>
-      <c r="F3" s="287" t="n"/>
-      <c r="G3" s="350" t="inlineStr">
+      <c r="A3" s="498" t="n"/>
+      <c r="B3" s="499" t="n"/>
+      <c r="C3" s="500" t="n"/>
+      <c r="D3" s="501" t="n"/>
+      <c r="E3" s="501" t="n"/>
+      <c r="F3" s="502" t="n"/>
+      <c r="G3" s="428" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="H3" s="351" t="inlineStr">
+      <c r="H3" s="429" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
+      <c r="I3" s="430" t="n"/>
+      <c r="J3" s="430" t="n"/>
+      <c r="K3" s="430" t="n"/>
+      <c r="L3" s="430" t="n"/>
+      <c r="M3" s="430" t="n"/>
+      <c r="N3" s="430" t="n"/>
+      <c r="O3" s="430" t="n"/>
+      <c r="P3" s="430" t="n"/>
+      <c r="Q3" s="430" t="n"/>
+      <c r="R3" s="430" t="n"/>
+      <c r="S3" s="430" t="n"/>
+      <c r="T3" s="430" t="n"/>
+      <c r="U3" s="430" t="n"/>
+      <c r="V3" s="430" t="n"/>
+      <c r="W3" s="430" t="n"/>
+      <c r="X3" s="430" t="n"/>
+      <c r="Y3" s="430" t="n"/>
+      <c r="Z3" s="430" t="n"/>
+      <c r="AA3" s="430" t="n"/>
+      <c r="AB3" s="430" t="n"/>
+      <c r="AC3" s="430" t="n"/>
+      <c r="AD3" s="430" t="n"/>
+      <c r="AE3" s="430" t="n"/>
+      <c r="AF3" s="430" t="n"/>
+      <c r="AG3" s="430" t="n"/>
+      <c r="AH3" s="430" t="n"/>
+      <c r="AI3" s="430" t="n"/>
+      <c r="AJ3" s="430" t="n"/>
+      <c r="AK3" s="430" t="n"/>
+      <c r="AL3" s="430" t="n"/>
+      <c r="AM3" s="430" t="n"/>
+      <c r="AN3" s="430" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="B4" s="312" t="n"/>
-      <c r="C4" s="415" t="inlineStr">
+      <c r="A4" s="498" t="n"/>
+      <c r="B4" s="499" t="n"/>
+      <c r="C4" s="436" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="289" t="n"/>
-      <c r="E4" s="289" t="n"/>
-      <c r="F4" s="290" t="n"/>
-      <c r="G4" s="350" t="inlineStr">
+      <c r="D4" s="503" t="n"/>
+      <c r="E4" s="503" t="n"/>
+      <c r="F4" s="504" t="n"/>
+      <c r="G4" s="428" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H4" s="351" t="inlineStr">
+      <c r="H4" s="429" t="inlineStr">
         <is>
           <t>QA / Customer Service</t>
         </is>
       </c>
+      <c r="I4" s="430" t="n"/>
+      <c r="J4" s="430" t="n"/>
+      <c r="K4" s="430" t="n"/>
+      <c r="L4" s="430" t="n"/>
+      <c r="M4" s="430" t="n"/>
+      <c r="N4" s="430" t="n"/>
+      <c r="O4" s="430" t="n"/>
+      <c r="P4" s="430" t="n"/>
+      <c r="Q4" s="430" t="n"/>
+      <c r="R4" s="430" t="n"/>
+      <c r="S4" s="430" t="n"/>
+      <c r="T4" s="430" t="n"/>
+      <c r="U4" s="430" t="n"/>
+      <c r="V4" s="430" t="n"/>
+      <c r="W4" s="430" t="n"/>
+      <c r="X4" s="430" t="n"/>
+      <c r="Y4" s="430" t="n"/>
+      <c r="Z4" s="430" t="n"/>
+      <c r="AA4" s="430" t="n"/>
+      <c r="AB4" s="430" t="n"/>
+      <c r="AC4" s="430" t="n"/>
+      <c r="AD4" s="430" t="n"/>
+      <c r="AE4" s="430" t="n"/>
+      <c r="AF4" s="430" t="n"/>
+      <c r="AG4" s="430" t="n"/>
+      <c r="AH4" s="430" t="n"/>
+      <c r="AI4" s="430" t="n"/>
+      <c r="AJ4" s="430" t="n"/>
+      <c r="AK4" s="430" t="n"/>
+      <c r="AL4" s="430" t="n"/>
+      <c r="AM4" s="430" t="n"/>
+      <c r="AN4" s="430" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="282" t="n"/>
-      <c r="B5" s="287" t="n"/>
-      <c r="C5" s="416" t="inlineStr">
+      <c r="A5" s="500" t="n"/>
+      <c r="B5" s="502" t="n"/>
+      <c r="C5" s="439" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="289" t="n"/>
-      <c r="E5" s="289" t="n"/>
-      <c r="F5" s="290" t="n"/>
-      <c r="G5" s="363" t="inlineStr">
+      <c r="D5" s="503" t="n"/>
+      <c r="E5" s="503" t="n"/>
+      <c r="F5" s="504" t="n"/>
+      <c r="G5" s="440" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="H5" s="364" t="inlineStr">
+      <c r="H5" s="441" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
       </c>
+      <c r="I5" s="430" t="n"/>
+      <c r="J5" s="430" t="n"/>
+      <c r="K5" s="430" t="n"/>
+      <c r="L5" s="430" t="n"/>
+      <c r="M5" s="430" t="n"/>
+      <c r="N5" s="430" t="n"/>
+      <c r="O5" s="430" t="n"/>
+      <c r="P5" s="430" t="n"/>
+      <c r="Q5" s="430" t="n"/>
+      <c r="R5" s="430" t="n"/>
+      <c r="S5" s="430" t="n"/>
+      <c r="T5" s="430" t="n"/>
+      <c r="U5" s="430" t="n"/>
+      <c r="V5" s="430" t="n"/>
+      <c r="W5" s="430" t="n"/>
+      <c r="X5" s="430" t="n"/>
+      <c r="Y5" s="430" t="n"/>
+      <c r="Z5" s="430" t="n"/>
+      <c r="AA5" s="430" t="n"/>
+      <c r="AB5" s="430" t="n"/>
+      <c r="AC5" s="430" t="n"/>
+      <c r="AD5" s="430" t="n"/>
+      <c r="AE5" s="430" t="n"/>
+      <c r="AF5" s="430" t="n"/>
+      <c r="AG5" s="430" t="n"/>
+      <c r="AH5" s="430" t="n"/>
+      <c r="AI5" s="430" t="n"/>
+      <c r="AJ5" s="430" t="n"/>
+      <c r="AK5" s="430" t="n"/>
+      <c r="AL5" s="430" t="n"/>
+      <c r="AM5" s="430" t="n"/>
+      <c r="AN5" s="430" t="n"/>
     </row>
     <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="413" t="n"/>
-      <c r="B6" s="289" t="n"/>
-      <c r="C6" s="289" t="n"/>
-      <c r="D6" s="289" t="n"/>
-      <c r="E6" s="289" t="n"/>
-      <c r="F6" s="289" t="n"/>
-      <c r="G6" s="289" t="n"/>
-      <c r="H6" s="290" t="n"/>
+      <c r="A6" s="442" t="n"/>
+      <c r="B6" s="495" t="n"/>
+      <c r="C6" s="495" t="n"/>
+      <c r="D6" s="495" t="n"/>
+      <c r="E6" s="495" t="n"/>
+      <c r="F6" s="495" t="n"/>
+      <c r="G6" s="495" t="n"/>
+      <c r="H6" s="495" t="n"/>
+      <c r="I6" s="443" t="n"/>
+      <c r="J6" s="443" t="n"/>
+      <c r="K6" s="443" t="n"/>
+      <c r="L6" s="443" t="n"/>
+      <c r="M6" s="443" t="n"/>
+      <c r="N6" s="443" t="n"/>
+      <c r="O6" s="443" t="n"/>
+      <c r="P6" s="443" t="n"/>
+      <c r="Q6" s="443" t="n"/>
+      <c r="R6" s="443" t="n"/>
+      <c r="S6" s="443" t="n"/>
+      <c r="T6" s="443" t="n"/>
+      <c r="U6" s="443" t="n"/>
+      <c r="V6" s="443" t="n"/>
+      <c r="W6" s="443" t="n"/>
+      <c r="X6" s="443" t="n"/>
+      <c r="Y6" s="443" t="n"/>
+      <c r="Z6" s="443" t="n"/>
+      <c r="AA6" s="443" t="n"/>
+      <c r="AB6" s="443" t="n"/>
+      <c r="AC6" s="443" t="n"/>
+      <c r="AD6" s="443" t="n"/>
+      <c r="AE6" s="443" t="n"/>
+      <c r="AF6" s="443" t="n"/>
+      <c r="AG6" s="443" t="n"/>
+      <c r="AH6" s="443" t="n"/>
+      <c r="AI6" s="443" t="n"/>
+      <c r="AJ6" s="443" t="n"/>
+      <c r="AK6" s="443" t="n"/>
+      <c r="AL6" s="443" t="n"/>
+      <c r="AM6" s="443" t="n"/>
+      <c r="AN6" s="443" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="417" t="inlineStr">
+      <c r="A7" s="444" t="inlineStr">
         <is>
           <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
         </is>
       </c>
-      <c r="B7" s="289" t="n"/>
-      <c r="C7" s="289" t="n"/>
-      <c r="D7" s="289" t="n"/>
-      <c r="E7" s="289" t="n"/>
-      <c r="F7" s="289" t="n"/>
-      <c r="G7" s="289" t="n"/>
-      <c r="H7" s="290" t="n"/>
+      <c r="B7" s="503" t="n"/>
+      <c r="C7" s="503" t="n"/>
+      <c r="D7" s="503" t="n"/>
+      <c r="E7" s="503" t="n"/>
+      <c r="F7" s="503" t="n"/>
+      <c r="G7" s="503" t="n"/>
+      <c r="H7" s="504" t="n"/>
+      <c r="I7" s="430" t="n"/>
+      <c r="J7" s="430" t="n"/>
+      <c r="K7" s="430" t="n"/>
+      <c r="L7" s="430" t="n"/>
+      <c r="M7" s="430" t="n"/>
+      <c r="N7" s="430" t="n"/>
+      <c r="O7" s="430" t="n"/>
+      <c r="P7" s="430" t="n"/>
+      <c r="Q7" s="430" t="n"/>
+      <c r="R7" s="430" t="n"/>
+      <c r="S7" s="430" t="n"/>
+      <c r="T7" s="430" t="n"/>
+      <c r="U7" s="430" t="n"/>
+      <c r="V7" s="430" t="n"/>
+      <c r="W7" s="430" t="n"/>
+      <c r="X7" s="430" t="n"/>
+      <c r="Y7" s="430" t="n"/>
+      <c r="Z7" s="430" t="n"/>
+      <c r="AA7" s="430" t="n"/>
+      <c r="AB7" s="430" t="n"/>
+      <c r="AC7" s="430" t="n"/>
+      <c r="AD7" s="430" t="n"/>
+      <c r="AE7" s="430" t="n"/>
+      <c r="AF7" s="430" t="n"/>
+      <c r="AG7" s="430" t="n"/>
+      <c r="AH7" s="430" t="n"/>
+      <c r="AI7" s="430" t="n"/>
+      <c r="AJ7" s="430" t="n"/>
+      <c r="AK7" s="430" t="n"/>
+      <c r="AL7" s="430" t="n"/>
+      <c r="AM7" s="430" t="n"/>
+      <c r="AN7" s="430" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="418" t="inlineStr">
+      <c r="A8" s="440" t="inlineStr">
         <is>
           <t>Parent Form</t>
         </is>
       </c>
-      <c r="B8" s="290" t="n"/>
-      <c r="C8" s="419" t="inlineStr">
+      <c r="B8" s="486" t="n"/>
+      <c r="C8" s="441" t="inlineStr">
         <is>
           <t>FRM-213 · RMA TRACKING LOG</t>
         </is>
       </c>
-      <c r="D8" s="290" t="n"/>
-      <c r="E8" s="418" t="inlineStr">
+      <c r="D8" s="486" t="n"/>
+      <c r="E8" s="440" t="inlineStr">
         <is>
           <t>Support Tab</t>
         </is>
       </c>
-      <c r="F8" s="290" t="n"/>
-      <c r="G8" s="419" t="inlineStr">
+      <c r="F8" s="486" t="n"/>
+      <c r="G8" s="441" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="H8" s="290" t="n"/>
+      <c r="H8" s="486" t="n"/>
+      <c r="I8" s="447" t="n"/>
+      <c r="J8" s="447" t="n"/>
+      <c r="K8" s="447" t="n"/>
+      <c r="L8" s="447" t="n"/>
+      <c r="M8" s="447" t="n"/>
+      <c r="N8" s="447" t="n"/>
+      <c r="O8" s="447" t="n"/>
+      <c r="P8" s="447" t="n"/>
+      <c r="Q8" s="447" t="n"/>
+      <c r="R8" s="447" t="n"/>
+      <c r="S8" s="447" t="n"/>
+      <c r="T8" s="447" t="n"/>
+      <c r="U8" s="447" t="n"/>
+      <c r="V8" s="447" t="n"/>
+      <c r="W8" s="447" t="n"/>
+      <c r="X8" s="447" t="n"/>
+      <c r="Y8" s="447" t="n"/>
+      <c r="Z8" s="447" t="n"/>
+      <c r="AA8" s="447" t="n"/>
+      <c r="AB8" s="447" t="n"/>
+      <c r="AC8" s="447" t="n"/>
+      <c r="AD8" s="447" t="n"/>
+      <c r="AE8" s="447" t="n"/>
+      <c r="AF8" s="447" t="n"/>
+      <c r="AG8" s="447" t="n"/>
+      <c r="AH8" s="447" t="n"/>
+      <c r="AI8" s="447" t="n"/>
+      <c r="AJ8" s="447" t="n"/>
+      <c r="AK8" s="447" t="n"/>
+      <c r="AL8" s="447" t="n"/>
+      <c r="AM8" s="447" t="n"/>
+      <c r="AN8" s="447" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="418" t="inlineStr">
+      <c r="A9" s="440" t="inlineStr">
         <is>
           <t>Tab Purpose</t>
         </is>
       </c>
-      <c r="B9" s="290" t="n"/>
-      <c r="C9" s="419" t="inlineStr">
+      <c r="B9" s="486" t="n"/>
+      <c r="C9" s="441" t="inlineStr">
         <is>
           <t>Periodic review and closeout support sheet for the rolling workbook.</t>
         </is>
       </c>
-      <c r="D9" s="290" t="n"/>
-      <c r="E9" s="418" t="inlineStr">
+      <c r="D9" s="486" t="n"/>
+      <c r="E9" s="440" t="inlineStr">
         <is>
           <t>Working Owner</t>
         </is>
       </c>
-      <c r="F9" s="290" t="n"/>
-      <c r="G9" s="419" t="inlineStr">
+      <c r="F9" s="486" t="n"/>
+      <c r="G9" s="441" t="inlineStr">
         <is>
           <t>QA / Customer Service</t>
         </is>
       </c>
-      <c r="H9" s="290" t="n"/>
+      <c r="H9" s="486" t="n"/>
+      <c r="I9" s="447" t="n"/>
+      <c r="J9" s="447" t="n"/>
+      <c r="K9" s="447" t="n"/>
+      <c r="L9" s="447" t="n"/>
+      <c r="M9" s="447" t="n"/>
+      <c r="N9" s="447" t="n"/>
+      <c r="O9" s="447" t="n"/>
+      <c r="P9" s="447" t="n"/>
+      <c r="Q9" s="447" t="n"/>
+      <c r="R9" s="447" t="n"/>
+      <c r="S9" s="447" t="n"/>
+      <c r="T9" s="447" t="n"/>
+      <c r="U9" s="447" t="n"/>
+      <c r="V9" s="447" t="n"/>
+      <c r="W9" s="447" t="n"/>
+      <c r="X9" s="447" t="n"/>
+      <c r="Y9" s="447" t="n"/>
+      <c r="Z9" s="447" t="n"/>
+      <c r="AA9" s="447" t="n"/>
+      <c r="AB9" s="447" t="n"/>
+      <c r="AC9" s="447" t="n"/>
+      <c r="AD9" s="447" t="n"/>
+      <c r="AE9" s="447" t="n"/>
+      <c r="AF9" s="447" t="n"/>
+      <c r="AG9" s="447" t="n"/>
+      <c r="AH9" s="447" t="n"/>
+      <c r="AI9" s="447" t="n"/>
+      <c r="AJ9" s="447" t="n"/>
+      <c r="AK9" s="447" t="n"/>
+      <c r="AL9" s="447" t="n"/>
+      <c r="AM9" s="447" t="n"/>
+      <c r="AN9" s="447" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="418" t="inlineStr">
+      <c r="A10" s="440" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B10" s="290" t="n"/>
-      <c r="C10" s="419" t="inlineStr">
+      <c r="B10" s="486" t="n"/>
+      <c r="C10" s="441" t="inlineStr">
         <is>
           <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
         </is>
       </c>
-      <c r="D10" s="290" t="n"/>
-      <c r="E10" s="418" t="inlineStr">
+      <c r="D10" s="486" t="n"/>
+      <c r="E10" s="440" t="inlineStr">
         <is>
           <t>Reviewed By</t>
         </is>
       </c>
-      <c r="F10" s="290" t="n"/>
-      <c r="G10" s="419" t="inlineStr">
+      <c r="F10" s="486" t="n"/>
+      <c r="G10" s="441" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
       </c>
-      <c r="H10" s="290" t="n"/>
+      <c r="H10" s="486" t="n"/>
+      <c r="I10" s="447" t="n"/>
+      <c r="J10" s="447" t="n"/>
+      <c r="K10" s="447" t="n"/>
+      <c r="L10" s="447" t="n"/>
+      <c r="M10" s="447" t="n"/>
+      <c r="N10" s="447" t="n"/>
+      <c r="O10" s="447" t="n"/>
+      <c r="P10" s="447" t="n"/>
+      <c r="Q10" s="447" t="n"/>
+      <c r="R10" s="447" t="n"/>
+      <c r="S10" s="447" t="n"/>
+      <c r="T10" s="447" t="n"/>
+      <c r="U10" s="447" t="n"/>
+      <c r="V10" s="447" t="n"/>
+      <c r="W10" s="447" t="n"/>
+      <c r="X10" s="447" t="n"/>
+      <c r="Y10" s="447" t="n"/>
+      <c r="Z10" s="447" t="n"/>
+      <c r="AA10" s="447" t="n"/>
+      <c r="AB10" s="447" t="n"/>
+      <c r="AC10" s="447" t="n"/>
+      <c r="AD10" s="447" t="n"/>
+      <c r="AE10" s="447" t="n"/>
+      <c r="AF10" s="447" t="n"/>
+      <c r="AG10" s="447" t="n"/>
+      <c r="AH10" s="447" t="n"/>
+      <c r="AI10" s="447" t="n"/>
+      <c r="AJ10" s="447" t="n"/>
+      <c r="AK10" s="447" t="n"/>
+      <c r="AL10" s="447" t="n"/>
+      <c r="AM10" s="447" t="n"/>
+      <c r="AN10" s="447" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="418" t="inlineStr">
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="440" t="inlineStr">
         <is>
           <t>Update Trigger</t>
         </is>
       </c>
-      <c r="B11" s="290" t="n"/>
-      <c r="C11" s="419" t="inlineStr">
+      <c r="B11" s="485" t="n"/>
+      <c r="C11" s="441" t="inlineStr">
         <is>
           <t>Update when the linked review, evidence or follow-up status changes.</t>
         </is>
       </c>
-      <c r="D11" s="290" t="n"/>
-      <c r="E11" s="418" t="inlineStr">
+      <c r="D11" s="485" t="n"/>
+      <c r="E11" s="440" t="inlineStr">
         <is>
           <t>Data Structure</t>
         </is>
       </c>
-      <c r="F11" s="290" t="n"/>
-      <c r="G11" s="419" t="inlineStr">
+      <c r="F11" s="485" t="n"/>
+      <c r="G11" s="441" t="inlineStr">
         <is>
           <t>Structured Excel Table with filters and print-title rows.</t>
         </is>
       </c>
-      <c r="H11" s="290" t="n"/>
+      <c r="H11" s="485" t="n"/>
+      <c r="I11" s="430" t="n"/>
+      <c r="J11" s="430" t="n"/>
+      <c r="K11" s="430" t="n"/>
+      <c r="L11" s="430" t="n"/>
+      <c r="M11" s="430" t="n"/>
+      <c r="N11" s="430" t="n"/>
+      <c r="O11" s="430" t="n"/>
+      <c r="P11" s="430" t="n"/>
+      <c r="Q11" s="430" t="n"/>
+      <c r="R11" s="430" t="n"/>
+      <c r="S11" s="430" t="n"/>
+      <c r="T11" s="430" t="n"/>
+      <c r="U11" s="430" t="n"/>
+      <c r="V11" s="430" t="n"/>
+      <c r="W11" s="430" t="n"/>
+      <c r="X11" s="430" t="n"/>
+      <c r="Y11" s="430" t="n"/>
+      <c r="Z11" s="430" t="n"/>
+      <c r="AA11" s="430" t="n"/>
+      <c r="AB11" s="430" t="n"/>
+      <c r="AC11" s="430" t="n"/>
+      <c r="AD11" s="430" t="n"/>
+      <c r="AE11" s="430" t="n"/>
+      <c r="AF11" s="430" t="n"/>
+      <c r="AG11" s="430" t="n"/>
+      <c r="AH11" s="430" t="n"/>
+      <c r="AI11" s="430" t="n"/>
+      <c r="AJ11" s="430" t="n"/>
+      <c r="AK11" s="430" t="n"/>
+      <c r="AL11" s="430" t="n"/>
+      <c r="AM11" s="430" t="n"/>
+      <c r="AN11" s="430" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="418" t="inlineStr">
+      <c r="A12" s="440" t="inlineStr">
         <is>
           <t>Retention Rule</t>
         </is>
       </c>
-      <c r="B12" s="290" t="n"/>
-      <c r="C12" s="419" t="inlineStr">
+      <c r="B12" s="486" t="n"/>
+      <c r="C12" s="441" t="inlineStr">
         <is>
           <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
         </is>
       </c>
-      <c r="D12" s="290" t="n"/>
-      <c r="E12" s="418" t="inlineStr">
+      <c r="D12" s="486" t="n"/>
+      <c r="E12" s="440" t="inlineStr">
         <is>
           <t>Controlled Status</t>
         </is>
       </c>
-      <c r="F12" s="290" t="n"/>
-      <c r="G12" s="419" t="inlineStr">
+      <c r="F12" s="486" t="n"/>
+      <c r="G12" s="441" t="inlineStr">
         <is>
           <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
         </is>
       </c>
-      <c r="H12" s="290" t="n"/>
+      <c r="H12" s="486" t="n"/>
+      <c r="I12" s="447" t="n"/>
+      <c r="J12" s="447" t="n"/>
+      <c r="K12" s="447" t="n"/>
+      <c r="L12" s="447" t="n"/>
+      <c r="M12" s="447" t="n"/>
+      <c r="N12" s="447" t="n"/>
+      <c r="O12" s="447" t="n"/>
+      <c r="P12" s="447" t="n"/>
+      <c r="Q12" s="447" t="n"/>
+      <c r="R12" s="447" t="n"/>
+      <c r="S12" s="447" t="n"/>
+      <c r="T12" s="447" t="n"/>
+      <c r="U12" s="447" t="n"/>
+      <c r="V12" s="447" t="n"/>
+      <c r="W12" s="447" t="n"/>
+      <c r="X12" s="447" t="n"/>
+      <c r="Y12" s="447" t="n"/>
+      <c r="Z12" s="447" t="n"/>
+      <c r="AA12" s="447" t="n"/>
+      <c r="AB12" s="447" t="n"/>
+      <c r="AC12" s="447" t="n"/>
+      <c r="AD12" s="447" t="n"/>
+      <c r="AE12" s="447" t="n"/>
+      <c r="AF12" s="447" t="n"/>
+      <c r="AG12" s="447" t="n"/>
+      <c r="AH12" s="447" t="n"/>
+      <c r="AI12" s="447" t="n"/>
+      <c r="AJ12" s="447" t="n"/>
+      <c r="AK12" s="447" t="n"/>
+      <c r="AL12" s="447" t="n"/>
+      <c r="AM12" s="447" t="n"/>
+      <c r="AN12" s="447" t="n"/>
     </row>
     <row r="13" ht="4" customHeight="1">
-      <c r="A13" s="413" t="n"/>
-      <c r="B13" s="289" t="n"/>
-      <c r="C13" s="289" t="n"/>
-      <c r="D13" s="289" t="n"/>
-      <c r="E13" s="289" t="n"/>
-      <c r="F13" s="289" t="n"/>
-      <c r="G13" s="289" t="n"/>
-      <c r="H13" s="290" t="n"/>
+      <c r="A13" s="442" t="n"/>
+      <c r="B13" s="495" t="n"/>
+      <c r="C13" s="495" t="n"/>
+      <c r="D13" s="495" t="n"/>
+      <c r="E13" s="495" t="n"/>
+      <c r="F13" s="495" t="n"/>
+      <c r="G13" s="495" t="n"/>
+      <c r="H13" s="495" t="n"/>
+      <c r="I13" s="443" t="n"/>
+      <c r="J13" s="443" t="n"/>
+      <c r="K13" s="443" t="n"/>
+      <c r="L13" s="443" t="n"/>
+      <c r="M13" s="443" t="n"/>
+      <c r="N13" s="443" t="n"/>
+      <c r="O13" s="443" t="n"/>
+      <c r="P13" s="443" t="n"/>
+      <c r="Q13" s="443" t="n"/>
+      <c r="R13" s="443" t="n"/>
+      <c r="S13" s="443" t="n"/>
+      <c r="T13" s="443" t="n"/>
+      <c r="U13" s="443" t="n"/>
+      <c r="V13" s="443" t="n"/>
+      <c r="W13" s="443" t="n"/>
+      <c r="X13" s="443" t="n"/>
+      <c r="Y13" s="443" t="n"/>
+      <c r="Z13" s="443" t="n"/>
+      <c r="AA13" s="443" t="n"/>
+      <c r="AB13" s="443" t="n"/>
+      <c r="AC13" s="443" t="n"/>
+      <c r="AD13" s="443" t="n"/>
+      <c r="AE13" s="443" t="n"/>
+      <c r="AF13" s="443" t="n"/>
+      <c r="AG13" s="443" t="n"/>
+      <c r="AH13" s="443" t="n"/>
+      <c r="AI13" s="443" t="n"/>
+      <c r="AJ13" s="443" t="n"/>
+      <c r="AK13" s="443" t="n"/>
+      <c r="AL13" s="443" t="n"/>
+      <c r="AM13" s="443" t="n"/>
+      <c r="AN13" s="443" t="n"/>
     </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="417" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="444" t="inlineStr">
         <is>
           <t>2.  WORKING TABLE / DETAIL LINES</t>
         </is>
       </c>
-      <c r="B14" s="289" t="n"/>
-      <c r="C14" s="289" t="n"/>
-      <c r="D14" s="289" t="n"/>
-      <c r="E14" s="289" t="n"/>
-      <c r="F14" s="289" t="n"/>
-      <c r="G14" s="289" t="n"/>
-      <c r="H14" s="290" t="n"/>
+      <c r="B14" s="487" t="n"/>
+      <c r="C14" s="487" t="n"/>
+      <c r="D14" s="487" t="n"/>
+      <c r="E14" s="487" t="n"/>
+      <c r="F14" s="487" t="n"/>
+      <c r="G14" s="487" t="n"/>
+      <c r="H14" s="486" t="n"/>
+      <c r="I14" s="447" t="n"/>
+      <c r="J14" s="447" t="n"/>
+      <c r="K14" s="447" t="n"/>
+      <c r="L14" s="447" t="n"/>
+      <c r="M14" s="447" t="n"/>
+      <c r="N14" s="447" t="n"/>
+      <c r="O14" s="447" t="n"/>
+      <c r="P14" s="447" t="n"/>
+      <c r="Q14" s="447" t="n"/>
+      <c r="R14" s="447" t="n"/>
+      <c r="S14" s="447" t="n"/>
+      <c r="T14" s="447" t="n"/>
+      <c r="U14" s="447" t="n"/>
+      <c r="V14" s="447" t="n"/>
+      <c r="W14" s="447" t="n"/>
+      <c r="X14" s="447" t="n"/>
+      <c r="Y14" s="447" t="n"/>
+      <c r="Z14" s="447" t="n"/>
+      <c r="AA14" s="447" t="n"/>
+      <c r="AB14" s="447" t="n"/>
+      <c r="AC14" s="447" t="n"/>
+      <c r="AD14" s="447" t="n"/>
+      <c r="AE14" s="447" t="n"/>
+      <c r="AF14" s="447" t="n"/>
+      <c r="AG14" s="447" t="n"/>
+      <c r="AH14" s="447" t="n"/>
+      <c r="AI14" s="447" t="n"/>
+      <c r="AJ14" s="447" t="n"/>
+      <c r="AK14" s="447" t="n"/>
+      <c r="AL14" s="447" t="n"/>
+      <c r="AM14" s="447" t="n"/>
+      <c r="AN14" s="447" t="n"/>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="423" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="470" t="inlineStr">
         <is>
           <t>Periodic review and closeout support sheet for the rolling workbook.</t>
         </is>
       </c>
-      <c r="B15" s="289" t="n"/>
-      <c r="C15" s="289" t="n"/>
-      <c r="D15" s="289" t="n"/>
-      <c r="E15" s="289" t="n"/>
-      <c r="F15" s="289" t="n"/>
-      <c r="G15" s="289" t="n"/>
-      <c r="H15" s="290" t="n"/>
+      <c r="B15" s="487" t="n"/>
+      <c r="C15" s="487" t="n"/>
+      <c r="D15" s="487" t="n"/>
+      <c r="E15" s="487" t="n"/>
+      <c r="F15" s="487" t="n"/>
+      <c r="G15" s="487" t="n"/>
+      <c r="H15" s="486" t="n"/>
+      <c r="I15" s="447" t="n"/>
+      <c r="J15" s="447" t="n"/>
+      <c r="K15" s="447" t="n"/>
+      <c r="L15" s="447" t="n"/>
+      <c r="M15" s="447" t="n"/>
+      <c r="N15" s="447" t="n"/>
+      <c r="O15" s="447" t="n"/>
+      <c r="P15" s="447" t="n"/>
+      <c r="Q15" s="447" t="n"/>
+      <c r="R15" s="447" t="n"/>
+      <c r="S15" s="447" t="n"/>
+      <c r="T15" s="447" t="n"/>
+      <c r="U15" s="447" t="n"/>
+      <c r="V15" s="447" t="n"/>
+      <c r="W15" s="447" t="n"/>
+      <c r="X15" s="447" t="n"/>
+      <c r="Y15" s="447" t="n"/>
+      <c r="Z15" s="447" t="n"/>
+      <c r="AA15" s="447" t="n"/>
+      <c r="AB15" s="447" t="n"/>
+      <c r="AC15" s="447" t="n"/>
+      <c r="AD15" s="447" t="n"/>
+      <c r="AE15" s="447" t="n"/>
+      <c r="AF15" s="447" t="n"/>
+      <c r="AG15" s="447" t="n"/>
+      <c r="AH15" s="447" t="n"/>
+      <c r="AI15" s="447" t="n"/>
+      <c r="AJ15" s="447" t="n"/>
+      <c r="AK15" s="447" t="n"/>
+      <c r="AL15" s="447" t="n"/>
+      <c r="AM15" s="447" t="n"/>
+      <c r="AN15" s="447" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="376" t="inlineStr">
+      <c r="A16" s="448" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B16" s="377" t="inlineStr">
+      <c r="B16" s="448" t="inlineStr">
         <is>
           <t>Review Item</t>
         </is>
       </c>
-      <c r="C16" s="377" t="inlineStr">
+      <c r="C16" s="448" t="inlineStr">
         <is>
           <t>Expectation / Rule</t>
         </is>
       </c>
-      <c r="D16" s="377" t="inlineStr">
+      <c r="D16" s="448" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="E16" s="377" t="inlineStr">
+      <c r="E16" s="448" t="inlineStr">
         <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="F16" s="377" t="inlineStr">
+      <c r="F16" s="448" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G16" s="377" t="inlineStr">
+      <c r="G16" s="448" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="H16" s="378" t="inlineStr">
+      <c r="H16" s="449" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
+      <c r="I16" s="447" t="n"/>
+      <c r="J16" s="447" t="n"/>
+      <c r="K16" s="447" t="n"/>
+      <c r="L16" s="447" t="n"/>
+      <c r="M16" s="447" t="n"/>
+      <c r="N16" s="447" t="n"/>
+      <c r="O16" s="447" t="n"/>
+      <c r="P16" s="447" t="n"/>
+      <c r="Q16" s="447" t="n"/>
+      <c r="R16" s="447" t="n"/>
+      <c r="S16" s="447" t="n"/>
+      <c r="T16" s="447" t="n"/>
+      <c r="U16" s="447" t="n"/>
+      <c r="V16" s="447" t="n"/>
+      <c r="W16" s="447" t="n"/>
+      <c r="X16" s="447" t="n"/>
+      <c r="Y16" s="447" t="n"/>
+      <c r="Z16" s="447" t="n"/>
+      <c r="AA16" s="447" t="n"/>
+      <c r="AB16" s="447" t="n"/>
+      <c r="AC16" s="447" t="n"/>
+      <c r="AD16" s="447" t="n"/>
+      <c r="AE16" s="447" t="n"/>
+      <c r="AF16" s="447" t="n"/>
+      <c r="AG16" s="447" t="n"/>
+      <c r="AH16" s="447" t="n"/>
+      <c r="AI16" s="447" t="n"/>
+      <c r="AJ16" s="447" t="n"/>
+      <c r="AK16" s="447" t="n"/>
+      <c r="AL16" s="447" t="n"/>
+      <c r="AM16" s="447" t="n"/>
+      <c r="AN16" s="447" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="379">
+      <c r="A17" s="450">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B17" s="381" t="n"/>
-      <c r="C17" s="381" t="n"/>
-      <c r="D17" s="381" t="n"/>
-      <c r="E17" s="410" t="n"/>
-      <c r="F17" s="381" t="n"/>
-      <c r="G17" s="381" t="n"/>
-      <c r="H17" s="351" t="n"/>
+      <c r="B17" s="452" t="n"/>
+      <c r="C17" s="452" t="n"/>
+      <c r="D17" s="452" t="n"/>
+      <c r="E17" s="471" t="n"/>
+      <c r="F17" s="452" t="n"/>
+      <c r="G17" s="452" t="n"/>
+      <c r="H17" s="429" t="n"/>
+      <c r="I17" s="447" t="n"/>
+      <c r="J17" s="447" t="n"/>
+      <c r="K17" s="447" t="n"/>
+      <c r="L17" s="447" t="n"/>
+      <c r="M17" s="447" t="n"/>
+      <c r="N17" s="447" t="n"/>
+      <c r="O17" s="447" t="n"/>
+      <c r="P17" s="447" t="n"/>
+      <c r="Q17" s="447" t="n"/>
+      <c r="R17" s="447" t="n"/>
+      <c r="S17" s="447" t="n"/>
+      <c r="T17" s="447" t="n"/>
+      <c r="U17" s="447" t="n"/>
+      <c r="V17" s="447" t="n"/>
+      <c r="W17" s="447" t="n"/>
+      <c r="X17" s="447" t="n"/>
+      <c r="Y17" s="447" t="n"/>
+      <c r="Z17" s="447" t="n"/>
+      <c r="AA17" s="447" t="n"/>
+      <c r="AB17" s="447" t="n"/>
+      <c r="AC17" s="447" t="n"/>
+      <c r="AD17" s="447" t="n"/>
+      <c r="AE17" s="447" t="n"/>
+      <c r="AF17" s="447" t="n"/>
+      <c r="AG17" s="447" t="n"/>
+      <c r="AH17" s="447" t="n"/>
+      <c r="AI17" s="447" t="n"/>
+      <c r="AJ17" s="447" t="n"/>
+      <c r="AK17" s="447" t="n"/>
+      <c r="AL17" s="447" t="n"/>
+      <c r="AM17" s="447" t="n"/>
+      <c r="AN17" s="447" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="379">
+      <c r="A18" s="450">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B18" s="383" t="n"/>
-      <c r="C18" s="383" t="n"/>
-      <c r="D18" s="383" t="n"/>
-      <c r="E18" s="411" t="n"/>
-      <c r="F18" s="383" t="n"/>
-      <c r="G18" s="383" t="n"/>
-      <c r="H18" s="384" t="n"/>
+      <c r="B18" s="454" t="n"/>
+      <c r="C18" s="454" t="n"/>
+      <c r="D18" s="454" t="n"/>
+      <c r="E18" s="472" t="n"/>
+      <c r="F18" s="454" t="n"/>
+      <c r="G18" s="454" t="n"/>
+      <c r="H18" s="455" t="n"/>
+      <c r="I18" s="447" t="n"/>
+      <c r="J18" s="447" t="n"/>
+      <c r="K18" s="447" t="n"/>
+      <c r="L18" s="447" t="n"/>
+      <c r="M18" s="447" t="n"/>
+      <c r="N18" s="447" t="n"/>
+      <c r="O18" s="447" t="n"/>
+      <c r="P18" s="447" t="n"/>
+      <c r="Q18" s="447" t="n"/>
+      <c r="R18" s="447" t="n"/>
+      <c r="S18" s="447" t="n"/>
+      <c r="T18" s="447" t="n"/>
+      <c r="U18" s="447" t="n"/>
+      <c r="V18" s="447" t="n"/>
+      <c r="W18" s="447" t="n"/>
+      <c r="X18" s="447" t="n"/>
+      <c r="Y18" s="447" t="n"/>
+      <c r="Z18" s="447" t="n"/>
+      <c r="AA18" s="447" t="n"/>
+      <c r="AB18" s="447" t="n"/>
+      <c r="AC18" s="447" t="n"/>
+      <c r="AD18" s="447" t="n"/>
+      <c r="AE18" s="447" t="n"/>
+      <c r="AF18" s="447" t="n"/>
+      <c r="AG18" s="447" t="n"/>
+      <c r="AH18" s="447" t="n"/>
+      <c r="AI18" s="447" t="n"/>
+      <c r="AJ18" s="447" t="n"/>
+      <c r="AK18" s="447" t="n"/>
+      <c r="AL18" s="447" t="n"/>
+      <c r="AM18" s="447" t="n"/>
+      <c r="AN18" s="447" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="379">
+      <c r="A19" s="450">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B19" s="381" t="n"/>
-      <c r="C19" s="381" t="n"/>
-      <c r="D19" s="381" t="n"/>
-      <c r="E19" s="410" t="n"/>
-      <c r="F19" s="381" t="n"/>
-      <c r="G19" s="381" t="n"/>
-      <c r="H19" s="351" t="n"/>
+      <c r="B19" s="452" t="n"/>
+      <c r="C19" s="452" t="n"/>
+      <c r="D19" s="452" t="n"/>
+      <c r="E19" s="471" t="n"/>
+      <c r="F19" s="452" t="n"/>
+      <c r="G19" s="452" t="n"/>
+      <c r="H19" s="429" t="n"/>
+      <c r="I19" s="447" t="n"/>
+      <c r="J19" s="447" t="n"/>
+      <c r="K19" s="447" t="n"/>
+      <c r="L19" s="447" t="n"/>
+      <c r="M19" s="447" t="n"/>
+      <c r="N19" s="447" t="n"/>
+      <c r="O19" s="447" t="n"/>
+      <c r="P19" s="447" t="n"/>
+      <c r="Q19" s="447" t="n"/>
+      <c r="R19" s="447" t="n"/>
+      <c r="S19" s="447" t="n"/>
+      <c r="T19" s="447" t="n"/>
+      <c r="U19" s="447" t="n"/>
+      <c r="V19" s="447" t="n"/>
+      <c r="W19" s="447" t="n"/>
+      <c r="X19" s="447" t="n"/>
+      <c r="Y19" s="447" t="n"/>
+      <c r="Z19" s="447" t="n"/>
+      <c r="AA19" s="447" t="n"/>
+      <c r="AB19" s="447" t="n"/>
+      <c r="AC19" s="447" t="n"/>
+      <c r="AD19" s="447" t="n"/>
+      <c r="AE19" s="447" t="n"/>
+      <c r="AF19" s="447" t="n"/>
+      <c r="AG19" s="447" t="n"/>
+      <c r="AH19" s="447" t="n"/>
+      <c r="AI19" s="447" t="n"/>
+      <c r="AJ19" s="447" t="n"/>
+      <c r="AK19" s="447" t="n"/>
+      <c r="AL19" s="447" t="n"/>
+      <c r="AM19" s="447" t="n"/>
+      <c r="AN19" s="447" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="379">
+      <c r="A20" s="450">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B20" s="383" t="n"/>
-      <c r="C20" s="383" t="n"/>
-      <c r="D20" s="383" t="n"/>
-      <c r="E20" s="411" t="n"/>
-      <c r="F20" s="383" t="n"/>
-      <c r="G20" s="383" t="n"/>
-      <c r="H20" s="384" t="n"/>
+      <c r="B20" s="454" t="n"/>
+      <c r="C20" s="454" t="n"/>
+      <c r="D20" s="454" t="n"/>
+      <c r="E20" s="472" t="n"/>
+      <c r="F20" s="454" t="n"/>
+      <c r="G20" s="454" t="n"/>
+      <c r="H20" s="455" t="n"/>
+      <c r="I20" s="447" t="n"/>
+      <c r="J20" s="447" t="n"/>
+      <c r="K20" s="447" t="n"/>
+      <c r="L20" s="447" t="n"/>
+      <c r="M20" s="447" t="n"/>
+      <c r="N20" s="447" t="n"/>
+      <c r="O20" s="447" t="n"/>
+      <c r="P20" s="447" t="n"/>
+      <c r="Q20" s="447" t="n"/>
+      <c r="R20" s="447" t="n"/>
+      <c r="S20" s="447" t="n"/>
+      <c r="T20" s="447" t="n"/>
+      <c r="U20" s="447" t="n"/>
+      <c r="V20" s="447" t="n"/>
+      <c r="W20" s="447" t="n"/>
+      <c r="X20" s="447" t="n"/>
+      <c r="Y20" s="447" t="n"/>
+      <c r="Z20" s="447" t="n"/>
+      <c r="AA20" s="447" t="n"/>
+      <c r="AB20" s="447" t="n"/>
+      <c r="AC20" s="447" t="n"/>
+      <c r="AD20" s="447" t="n"/>
+      <c r="AE20" s="447" t="n"/>
+      <c r="AF20" s="447" t="n"/>
+      <c r="AG20" s="447" t="n"/>
+      <c r="AH20" s="447" t="n"/>
+      <c r="AI20" s="447" t="n"/>
+      <c r="AJ20" s="447" t="n"/>
+      <c r="AK20" s="447" t="n"/>
+      <c r="AL20" s="447" t="n"/>
+      <c r="AM20" s="447" t="n"/>
+      <c r="AN20" s="447" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="379">
+      <c r="A21" s="450">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B21" s="381" t="n"/>
-      <c r="C21" s="381" t="n"/>
-      <c r="D21" s="381" t="n"/>
-      <c r="E21" s="410" t="n"/>
-      <c r="F21" s="381" t="n"/>
-      <c r="G21" s="381" t="n"/>
-      <c r="H21" s="351" t="n"/>
+      <c r="B21" s="452" t="n"/>
+      <c r="C21" s="452" t="n"/>
+      <c r="D21" s="452" t="n"/>
+      <c r="E21" s="471" t="n"/>
+      <c r="F21" s="452" t="n"/>
+      <c r="G21" s="452" t="n"/>
+      <c r="H21" s="429" t="n"/>
+      <c r="I21" s="447" t="n"/>
+      <c r="J21" s="447" t="n"/>
+      <c r="K21" s="447" t="n"/>
+      <c r="L21" s="447" t="n"/>
+      <c r="M21" s="447" t="n"/>
+      <c r="N21" s="447" t="n"/>
+      <c r="O21" s="447" t="n"/>
+      <c r="P21" s="447" t="n"/>
+      <c r="Q21" s="447" t="n"/>
+      <c r="R21" s="447" t="n"/>
+      <c r="S21" s="447" t="n"/>
+      <c r="T21" s="447" t="n"/>
+      <c r="U21" s="447" t="n"/>
+      <c r="V21" s="447" t="n"/>
+      <c r="W21" s="447" t="n"/>
+      <c r="X21" s="447" t="n"/>
+      <c r="Y21" s="447" t="n"/>
+      <c r="Z21" s="447" t="n"/>
+      <c r="AA21" s="447" t="n"/>
+      <c r="AB21" s="447" t="n"/>
+      <c r="AC21" s="447" t="n"/>
+      <c r="AD21" s="447" t="n"/>
+      <c r="AE21" s="447" t="n"/>
+      <c r="AF21" s="447" t="n"/>
+      <c r="AG21" s="447" t="n"/>
+      <c r="AH21" s="447" t="n"/>
+      <c r="AI21" s="447" t="n"/>
+      <c r="AJ21" s="447" t="n"/>
+      <c r="AK21" s="447" t="n"/>
+      <c r="AL21" s="447" t="n"/>
+      <c r="AM21" s="447" t="n"/>
+      <c r="AN21" s="447" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="379">
+      <c r="A22" s="450">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B22" s="383" t="n"/>
-      <c r="C22" s="383" t="n"/>
-      <c r="D22" s="383" t="n"/>
-      <c r="E22" s="411" t="n"/>
-      <c r="F22" s="383" t="n"/>
-      <c r="G22" s="383" t="n"/>
-      <c r="H22" s="384" t="n"/>
+      <c r="B22" s="454" t="n"/>
+      <c r="C22" s="454" t="n"/>
+      <c r="D22" s="454" t="n"/>
+      <c r="E22" s="472" t="n"/>
+      <c r="F22" s="454" t="n"/>
+      <c r="G22" s="454" t="n"/>
+      <c r="H22" s="455" t="n"/>
+      <c r="I22" s="447" t="n"/>
+      <c r="J22" s="447" t="n"/>
+      <c r="K22" s="447" t="n"/>
+      <c r="L22" s="447" t="n"/>
+      <c r="M22" s="447" t="n"/>
+      <c r="N22" s="447" t="n"/>
+      <c r="O22" s="447" t="n"/>
+      <c r="P22" s="447" t="n"/>
+      <c r="Q22" s="447" t="n"/>
+      <c r="R22" s="447" t="n"/>
+      <c r="S22" s="447" t="n"/>
+      <c r="T22" s="447" t="n"/>
+      <c r="U22" s="447" t="n"/>
+      <c r="V22" s="447" t="n"/>
+      <c r="W22" s="447" t="n"/>
+      <c r="X22" s="447" t="n"/>
+      <c r="Y22" s="447" t="n"/>
+      <c r="Z22" s="447" t="n"/>
+      <c r="AA22" s="447" t="n"/>
+      <c r="AB22" s="447" t="n"/>
+      <c r="AC22" s="447" t="n"/>
+      <c r="AD22" s="447" t="n"/>
+      <c r="AE22" s="447" t="n"/>
+      <c r="AF22" s="447" t="n"/>
+      <c r="AG22" s="447" t="n"/>
+      <c r="AH22" s="447" t="n"/>
+      <c r="AI22" s="447" t="n"/>
+      <c r="AJ22" s="447" t="n"/>
+      <c r="AK22" s="447" t="n"/>
+      <c r="AL22" s="447" t="n"/>
+      <c r="AM22" s="447" t="n"/>
+      <c r="AN22" s="447" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="379">
+      <c r="A23" s="450">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B23" s="381" t="n"/>
-      <c r="C23" s="381" t="n"/>
-      <c r="D23" s="381" t="n"/>
-      <c r="E23" s="410" t="n"/>
-      <c r="F23" s="381" t="n"/>
-      <c r="G23" s="381" t="n"/>
-      <c r="H23" s="351" t="n"/>
+      <c r="B23" s="452" t="n"/>
+      <c r="C23" s="452" t="n"/>
+      <c r="D23" s="452" t="n"/>
+      <c r="E23" s="471" t="n"/>
+      <c r="F23" s="452" t="n"/>
+      <c r="G23" s="452" t="n"/>
+      <c r="H23" s="429" t="n"/>
+      <c r="I23" s="447" t="n"/>
+      <c r="J23" s="447" t="n"/>
+      <c r="K23" s="447" t="n"/>
+      <c r="L23" s="447" t="n"/>
+      <c r="M23" s="447" t="n"/>
+      <c r="N23" s="447" t="n"/>
+      <c r="O23" s="447" t="n"/>
+      <c r="P23" s="447" t="n"/>
+      <c r="Q23" s="447" t="n"/>
+      <c r="R23" s="447" t="n"/>
+      <c r="S23" s="447" t="n"/>
+      <c r="T23" s="447" t="n"/>
+      <c r="U23" s="447" t="n"/>
+      <c r="V23" s="447" t="n"/>
+      <c r="W23" s="447" t="n"/>
+      <c r="X23" s="447" t="n"/>
+      <c r="Y23" s="447" t="n"/>
+      <c r="Z23" s="447" t="n"/>
+      <c r="AA23" s="447" t="n"/>
+      <c r="AB23" s="447" t="n"/>
+      <c r="AC23" s="447" t="n"/>
+      <c r="AD23" s="447" t="n"/>
+      <c r="AE23" s="447" t="n"/>
+      <c r="AF23" s="447" t="n"/>
+      <c r="AG23" s="447" t="n"/>
+      <c r="AH23" s="447" t="n"/>
+      <c r="AI23" s="447" t="n"/>
+      <c r="AJ23" s="447" t="n"/>
+      <c r="AK23" s="447" t="n"/>
+      <c r="AL23" s="447" t="n"/>
+      <c r="AM23" s="447" t="n"/>
+      <c r="AN23" s="447" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="385">
+      <c r="A24" s="456">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B24" s="387" t="n"/>
-      <c r="C24" s="387" t="n"/>
-      <c r="D24" s="387" t="n"/>
-      <c r="E24" s="412" t="n"/>
-      <c r="F24" s="387" t="n"/>
-      <c r="G24" s="387" t="n"/>
-      <c r="H24" s="388" t="n"/>
+      <c r="B24" s="458" t="n"/>
+      <c r="C24" s="458" t="n"/>
+      <c r="D24" s="458" t="n"/>
+      <c r="E24" s="473" t="n"/>
+      <c r="F24" s="458" t="n"/>
+      <c r="G24" s="458" t="n"/>
+      <c r="H24" s="459" t="n"/>
+      <c r="I24" s="447" t="n"/>
+      <c r="J24" s="447" t="n"/>
+      <c r="K24" s="447" t="n"/>
+      <c r="L24" s="447" t="n"/>
+      <c r="M24" s="447" t="n"/>
+      <c r="N24" s="447" t="n"/>
+      <c r="O24" s="447" t="n"/>
+      <c r="P24" s="447" t="n"/>
+      <c r="Q24" s="447" t="n"/>
+      <c r="R24" s="447" t="n"/>
+      <c r="S24" s="447" t="n"/>
+      <c r="T24" s="447" t="n"/>
+      <c r="U24" s="447" t="n"/>
+      <c r="V24" s="447" t="n"/>
+      <c r="W24" s="447" t="n"/>
+      <c r="X24" s="447" t="n"/>
+      <c r="Y24" s="447" t="n"/>
+      <c r="Z24" s="447" t="n"/>
+      <c r="AA24" s="447" t="n"/>
+      <c r="AB24" s="447" t="n"/>
+      <c r="AC24" s="447" t="n"/>
+      <c r="AD24" s="447" t="n"/>
+      <c r="AE24" s="447" t="n"/>
+      <c r="AF24" s="447" t="n"/>
+      <c r="AG24" s="447" t="n"/>
+      <c r="AH24" s="447" t="n"/>
+      <c r="AI24" s="447" t="n"/>
+      <c r="AJ24" s="447" t="n"/>
+      <c r="AK24" s="447" t="n"/>
+      <c r="AL24" s="447" t="n"/>
+      <c r="AM24" s="447" t="n"/>
+      <c r="AN24" s="447" t="n"/>
     </row>
-    <row r="25"/>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="423" t="inlineStr">
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="447" t="n"/>
+      <c r="B25" s="447" t="n"/>
+      <c r="C25" s="447" t="n"/>
+      <c r="D25" s="447" t="n"/>
+      <c r="E25" s="447" t="n"/>
+      <c r="F25" s="447" t="n"/>
+      <c r="G25" s="447" t="n"/>
+      <c r="H25" s="447" t="n"/>
+      <c r="I25" s="447" t="n"/>
+      <c r="J25" s="447" t="n"/>
+      <c r="K25" s="447" t="n"/>
+      <c r="L25" s="447" t="n"/>
+      <c r="M25" s="447" t="n"/>
+      <c r="N25" s="447" t="n"/>
+      <c r="O25" s="447" t="n"/>
+      <c r="P25" s="447" t="n"/>
+      <c r="Q25" s="447" t="n"/>
+      <c r="R25" s="447" t="n"/>
+      <c r="S25" s="447" t="n"/>
+      <c r="T25" s="447" t="n"/>
+      <c r="U25" s="447" t="n"/>
+      <c r="V25" s="447" t="n"/>
+      <c r="W25" s="447" t="n"/>
+      <c r="X25" s="447" t="n"/>
+      <c r="Y25" s="447" t="n"/>
+      <c r="Z25" s="447" t="n"/>
+      <c r="AA25" s="447" t="n"/>
+      <c r="AB25" s="447" t="n"/>
+      <c r="AC25" s="447" t="n"/>
+      <c r="AD25" s="447" t="n"/>
+      <c r="AE25" s="447" t="n"/>
+      <c r="AF25" s="447" t="n"/>
+      <c r="AG25" s="447" t="n"/>
+      <c r="AH25" s="447" t="n"/>
+      <c r="AI25" s="447" t="n"/>
+      <c r="AJ25" s="447" t="n"/>
+      <c r="AK25" s="447" t="n"/>
+      <c r="AL25" s="447" t="n"/>
+      <c r="AM25" s="447" t="n"/>
+      <c r="AN25" s="447" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="470" t="inlineStr">
         <is>
           <t>NOTICE  —  Periodic review and closeout support sheet for the rolling workbook.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B26" s="289" t="n"/>
-      <c r="C26" s="289" t="n"/>
-      <c r="D26" s="289" t="n"/>
-      <c r="E26" s="289" t="n"/>
-      <c r="F26" s="289" t="n"/>
-      <c r="G26" s="289" t="n"/>
-      <c r="H26" s="290" t="n"/>
+      <c r="B26" s="484" t="n"/>
+      <c r="C26" s="484" t="n"/>
+      <c r="D26" s="484" t="n"/>
+      <c r="E26" s="484" t="n"/>
+      <c r="F26" s="484" t="n"/>
+      <c r="G26" s="484" t="n"/>
+      <c r="H26" s="485" t="n"/>
+      <c r="I26" s="430" t="n"/>
+      <c r="J26" s="430" t="n"/>
+      <c r="K26" s="430" t="n"/>
+      <c r="L26" s="430" t="n"/>
+      <c r="M26" s="430" t="n"/>
+      <c r="N26" s="430" t="n"/>
+      <c r="O26" s="430" t="n"/>
+      <c r="P26" s="430" t="n"/>
+      <c r="Q26" s="430" t="n"/>
+      <c r="R26" s="430" t="n"/>
+      <c r="S26" s="430" t="n"/>
+      <c r="T26" s="430" t="n"/>
+      <c r="U26" s="430" t="n"/>
+      <c r="V26" s="430" t="n"/>
+      <c r="W26" s="430" t="n"/>
+      <c r="X26" s="430" t="n"/>
+      <c r="Y26" s="430" t="n"/>
+      <c r="Z26" s="430" t="n"/>
+      <c r="AA26" s="430" t="n"/>
+      <c r="AB26" s="430" t="n"/>
+      <c r="AC26" s="430" t="n"/>
+      <c r="AD26" s="430" t="n"/>
+      <c r="AE26" s="430" t="n"/>
+      <c r="AF26" s="430" t="n"/>
+      <c r="AG26" s="430" t="n"/>
+      <c r="AH26" s="430" t="n"/>
+      <c r="AI26" s="430" t="n"/>
+      <c r="AJ26" s="430" t="n"/>
+      <c r="AK26" s="430" t="n"/>
+      <c r="AL26" s="430" t="n"/>
+      <c r="AM26" s="430" t="n"/>
+      <c r="AN26" s="430" t="n"/>
     </row>
     <row r="27" hidden="1" outlineLevel="1"/>
     <row r="28" hidden="1" outlineLevel="1"/>
@@ -7700,9 +11007,8 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7713,31 +11019,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col hidden="1" width="13" customWidth="1" min="8" max="16384"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col hidden="1" width="2.33" customWidth="1" min="8" max="16384"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="320" t="inlineStr">
+      <c r="A1" s="474" t="inlineStr">
         <is>
           <t>REF_LINKS</t>
         </is>
       </c>
-      <c r="B1" s="324" t="n"/>
-      <c r="C1" s="324" t="n"/>
-      <c r="D1" s="324" t="n"/>
-      <c r="E1" s="324" t="n"/>
-      <c r="F1" s="324" t="n"/>
-      <c r="G1" s="325" t="n"/>
+      <c r="B1" s="503" t="n"/>
+      <c r="C1" s="503" t="n"/>
+      <c r="D1" s="503" t="n"/>
+      <c r="E1" s="503" t="n"/>
+      <c r="F1" s="503" t="n"/>
+      <c r="G1" s="504" t="n"/>
+      <c r="H1" s="430" t="n"/>
+      <c r="I1" s="430" t="n"/>
+      <c r="J1" s="430" t="n"/>
+      <c r="K1" s="430" t="n"/>
+      <c r="L1" s="430" t="n"/>
+      <c r="M1" s="430" t="n"/>
+      <c r="N1" s="430" t="n"/>
+      <c r="O1" s="430" t="n"/>
+      <c r="P1" s="430" t="n"/>
+      <c r="Q1" s="430" t="n"/>
+      <c r="R1" s="430" t="n"/>
+      <c r="S1" s="430" t="n"/>
+      <c r="T1" s="430" t="n"/>
+      <c r="U1" s="430" t="n"/>
+      <c r="V1" s="430" t="n"/>
+      <c r="W1" s="430" t="n"/>
+      <c r="X1" s="430" t="n"/>
+      <c r="Y1" s="430" t="n"/>
+      <c r="Z1" s="430" t="n"/>
+      <c r="AA1" s="430" t="n"/>
+      <c r="AB1" s="430" t="n"/>
+      <c r="AC1" s="430" t="n"/>
+      <c r="AD1" s="430" t="n"/>
+      <c r="AE1" s="430" t="n"/>
+      <c r="AF1" s="430" t="n"/>
+      <c r="AG1" s="430" t="n"/>
+      <c r="AH1" s="430" t="n"/>
+      <c r="AI1" s="430" t="n"/>
+      <c r="AJ1" s="430" t="n"/>
+      <c r="AK1" s="430" t="n"/>
+      <c r="AL1" s="430" t="n"/>
+      <c r="AM1" s="430" t="n"/>
+      <c r="AN1" s="430" t="n"/>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="321" t="inlineStr">
@@ -7745,115 +11116,445 @@
           <t>Reference Epicor / M365 / controlled documents only.</t>
         </is>
       </c>
+      <c r="H2" s="430" t="n"/>
+      <c r="I2" s="430" t="n"/>
+      <c r="J2" s="430" t="n"/>
+      <c r="K2" s="430" t="n"/>
+      <c r="L2" s="430" t="n"/>
+      <c r="M2" s="430" t="n"/>
+      <c r="N2" s="430" t="n"/>
+      <c r="O2" s="430" t="n"/>
+      <c r="P2" s="430" t="n"/>
+      <c r="Q2" s="430" t="n"/>
+      <c r="R2" s="430" t="n"/>
+      <c r="S2" s="430" t="n"/>
+      <c r="T2" s="430" t="n"/>
+      <c r="U2" s="430" t="n"/>
+      <c r="V2" s="430" t="n"/>
+      <c r="W2" s="430" t="n"/>
+      <c r="X2" s="430" t="n"/>
+      <c r="Y2" s="430" t="n"/>
+      <c r="Z2" s="430" t="n"/>
+      <c r="AA2" s="430" t="n"/>
+      <c r="AB2" s="430" t="n"/>
+      <c r="AC2" s="430" t="n"/>
+      <c r="AD2" s="430" t="n"/>
+      <c r="AE2" s="430" t="n"/>
+      <c r="AF2" s="430" t="n"/>
+      <c r="AG2" s="430" t="n"/>
+      <c r="AH2" s="430" t="n"/>
+      <c r="AI2" s="430" t="n"/>
+      <c r="AJ2" s="430" t="n"/>
+      <c r="AK2" s="430" t="n"/>
+      <c r="AL2" s="430" t="n"/>
+      <c r="AM2" s="430" t="n"/>
+      <c r="AN2" s="430" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="322" t="inlineStr">
+      <c r="A3" s="475" t="inlineStr">
         <is>
           <t>Ref Type</t>
         </is>
       </c>
-      <c r="B3" s="322" t="inlineStr">
+      <c r="B3" s="475" t="inlineStr">
         <is>
           <t>Document / Record</t>
         </is>
       </c>
-      <c r="C3" s="322" t="inlineStr">
+      <c r="C3" s="475" t="inlineStr">
         <is>
           <t>System of Record</t>
         </is>
       </c>
-      <c r="D3" s="322" t="inlineStr">
+      <c r="D3" s="475" t="inlineStr">
         <is>
           <t>Unique Ref</t>
         </is>
       </c>
-      <c r="E3" s="322" t="inlineStr">
+      <c r="E3" s="475" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F3" s="322" t="inlineStr">
+      <c r="F3" s="475" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G3" s="322" t="inlineStr">
+      <c r="G3" s="475" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
+      <c r="H3" s="430" t="n"/>
+      <c r="I3" s="430" t="n"/>
+      <c r="J3" s="430" t="n"/>
+      <c r="K3" s="430" t="n"/>
+      <c r="L3" s="430" t="n"/>
+      <c r="M3" s="430" t="n"/>
+      <c r="N3" s="430" t="n"/>
+      <c r="O3" s="430" t="n"/>
+      <c r="P3" s="430" t="n"/>
+      <c r="Q3" s="430" t="n"/>
+      <c r="R3" s="430" t="n"/>
+      <c r="S3" s="430" t="n"/>
+      <c r="T3" s="430" t="n"/>
+      <c r="U3" s="430" t="n"/>
+      <c r="V3" s="430" t="n"/>
+      <c r="W3" s="430" t="n"/>
+      <c r="X3" s="430" t="n"/>
+      <c r="Y3" s="430" t="n"/>
+      <c r="Z3" s="430" t="n"/>
+      <c r="AA3" s="430" t="n"/>
+      <c r="AB3" s="430" t="n"/>
+      <c r="AC3" s="430" t="n"/>
+      <c r="AD3" s="430" t="n"/>
+      <c r="AE3" s="430" t="n"/>
+      <c r="AF3" s="430" t="n"/>
+      <c r="AG3" s="430" t="n"/>
+      <c r="AH3" s="430" t="n"/>
+      <c r="AI3" s="430" t="n"/>
+      <c r="AJ3" s="430" t="n"/>
+      <c r="AK3" s="430" t="n"/>
+      <c r="AL3" s="430" t="n"/>
+      <c r="AM3" s="430" t="n"/>
+      <c r="AN3" s="430" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="302" t="n"/>
-      <c r="B4" s="302" t="n"/>
-      <c r="C4" s="302" t="n"/>
-      <c r="D4" s="302" t="n"/>
-      <c r="E4" s="302" t="n"/>
-      <c r="F4" s="302" t="n"/>
-      <c r="G4" s="302" t="n"/>
+      <c r="A4" s="476" t="n"/>
+      <c r="B4" s="476" t="n"/>
+      <c r="C4" s="476" t="n"/>
+      <c r="D4" s="476" t="n"/>
+      <c r="E4" s="476" t="n"/>
+      <c r="F4" s="476" t="n"/>
+      <c r="G4" s="476" t="n"/>
+      <c r="H4" s="430" t="n"/>
+      <c r="I4" s="430" t="n"/>
+      <c r="J4" s="430" t="n"/>
+      <c r="K4" s="430" t="n"/>
+      <c r="L4" s="430" t="n"/>
+      <c r="M4" s="430" t="n"/>
+      <c r="N4" s="430" t="n"/>
+      <c r="O4" s="430" t="n"/>
+      <c r="P4" s="430" t="n"/>
+      <c r="Q4" s="430" t="n"/>
+      <c r="R4" s="430" t="n"/>
+      <c r="S4" s="430" t="n"/>
+      <c r="T4" s="430" t="n"/>
+      <c r="U4" s="430" t="n"/>
+      <c r="V4" s="430" t="n"/>
+      <c r="W4" s="430" t="n"/>
+      <c r="X4" s="430" t="n"/>
+      <c r="Y4" s="430" t="n"/>
+      <c r="Z4" s="430" t="n"/>
+      <c r="AA4" s="430" t="n"/>
+      <c r="AB4" s="430" t="n"/>
+      <c r="AC4" s="430" t="n"/>
+      <c r="AD4" s="430" t="n"/>
+      <c r="AE4" s="430" t="n"/>
+      <c r="AF4" s="430" t="n"/>
+      <c r="AG4" s="430" t="n"/>
+      <c r="AH4" s="430" t="n"/>
+      <c r="AI4" s="430" t="n"/>
+      <c r="AJ4" s="430" t="n"/>
+      <c r="AK4" s="430" t="n"/>
+      <c r="AL4" s="430" t="n"/>
+      <c r="AM4" s="430" t="n"/>
+      <c r="AN4" s="430" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="302" t="n"/>
-      <c r="B5" s="302" t="n"/>
-      <c r="C5" s="302" t="n"/>
-      <c r="D5" s="302" t="n"/>
-      <c r="E5" s="302" t="n"/>
-      <c r="F5" s="302" t="n"/>
-      <c r="G5" s="302" t="n"/>
+      <c r="A5" s="476" t="n"/>
+      <c r="B5" s="476" t="n"/>
+      <c r="C5" s="476" t="n"/>
+      <c r="D5" s="476" t="n"/>
+      <c r="E5" s="476" t="n"/>
+      <c r="F5" s="476" t="n"/>
+      <c r="G5" s="476" t="n"/>
+      <c r="H5" s="430" t="n"/>
+      <c r="I5" s="430" t="n"/>
+      <c r="J5" s="430" t="n"/>
+      <c r="K5" s="430" t="n"/>
+      <c r="L5" s="430" t="n"/>
+      <c r="M5" s="430" t="n"/>
+      <c r="N5" s="430" t="n"/>
+      <c r="O5" s="430" t="n"/>
+      <c r="P5" s="430" t="n"/>
+      <c r="Q5" s="430" t="n"/>
+      <c r="R5" s="430" t="n"/>
+      <c r="S5" s="430" t="n"/>
+      <c r="T5" s="430" t="n"/>
+      <c r="U5" s="430" t="n"/>
+      <c r="V5" s="430" t="n"/>
+      <c r="W5" s="430" t="n"/>
+      <c r="X5" s="430" t="n"/>
+      <c r="Y5" s="430" t="n"/>
+      <c r="Z5" s="430" t="n"/>
+      <c r="AA5" s="430" t="n"/>
+      <c r="AB5" s="430" t="n"/>
+      <c r="AC5" s="430" t="n"/>
+      <c r="AD5" s="430" t="n"/>
+      <c r="AE5" s="430" t="n"/>
+      <c r="AF5" s="430" t="n"/>
+      <c r="AG5" s="430" t="n"/>
+      <c r="AH5" s="430" t="n"/>
+      <c r="AI5" s="430" t="n"/>
+      <c r="AJ5" s="430" t="n"/>
+      <c r="AK5" s="430" t="n"/>
+      <c r="AL5" s="430" t="n"/>
+      <c r="AM5" s="430" t="n"/>
+      <c r="AN5" s="430" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="302" t="n"/>
-      <c r="B6" s="302" t="n"/>
-      <c r="C6" s="302" t="n"/>
-      <c r="D6" s="302" t="n"/>
-      <c r="E6" s="302" t="n"/>
-      <c r="F6" s="302" t="n"/>
-      <c r="G6" s="302" t="n"/>
+      <c r="A6" s="476" t="n"/>
+      <c r="B6" s="476" t="n"/>
+      <c r="C6" s="476" t="n"/>
+      <c r="D6" s="476" t="n"/>
+      <c r="E6" s="476" t="n"/>
+      <c r="F6" s="476" t="n"/>
+      <c r="G6" s="476" t="n"/>
+      <c r="H6" s="430" t="n"/>
+      <c r="I6" s="430" t="n"/>
+      <c r="J6" s="430" t="n"/>
+      <c r="K6" s="430" t="n"/>
+      <c r="L6" s="430" t="n"/>
+      <c r="M6" s="430" t="n"/>
+      <c r="N6" s="430" t="n"/>
+      <c r="O6" s="430" t="n"/>
+      <c r="P6" s="430" t="n"/>
+      <c r="Q6" s="430" t="n"/>
+      <c r="R6" s="430" t="n"/>
+      <c r="S6" s="430" t="n"/>
+      <c r="T6" s="430" t="n"/>
+      <c r="U6" s="430" t="n"/>
+      <c r="V6" s="430" t="n"/>
+      <c r="W6" s="430" t="n"/>
+      <c r="X6" s="430" t="n"/>
+      <c r="Y6" s="430" t="n"/>
+      <c r="Z6" s="430" t="n"/>
+      <c r="AA6" s="430" t="n"/>
+      <c r="AB6" s="430" t="n"/>
+      <c r="AC6" s="430" t="n"/>
+      <c r="AD6" s="430" t="n"/>
+      <c r="AE6" s="430" t="n"/>
+      <c r="AF6" s="430" t="n"/>
+      <c r="AG6" s="430" t="n"/>
+      <c r="AH6" s="430" t="n"/>
+      <c r="AI6" s="430" t="n"/>
+      <c r="AJ6" s="430" t="n"/>
+      <c r="AK6" s="430" t="n"/>
+      <c r="AL6" s="430" t="n"/>
+      <c r="AM6" s="430" t="n"/>
+      <c r="AN6" s="430" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="302" t="n"/>
-      <c r="B7" s="302" t="n"/>
-      <c r="C7" s="302" t="n"/>
-      <c r="D7" s="302" t="n"/>
-      <c r="E7" s="302" t="n"/>
-      <c r="F7" s="302" t="n"/>
-      <c r="G7" s="302" t="n"/>
+      <c r="A7" s="476" t="n"/>
+      <c r="B7" s="476" t="n"/>
+      <c r="C7" s="476" t="n"/>
+      <c r="D7" s="476" t="n"/>
+      <c r="E7" s="476" t="n"/>
+      <c r="F7" s="476" t="n"/>
+      <c r="G7" s="476" t="n"/>
+      <c r="H7" s="430" t="n"/>
+      <c r="I7" s="430" t="n"/>
+      <c r="J7" s="430" t="n"/>
+      <c r="K7" s="430" t="n"/>
+      <c r="L7" s="430" t="n"/>
+      <c r="M7" s="430" t="n"/>
+      <c r="N7" s="430" t="n"/>
+      <c r="O7" s="430" t="n"/>
+      <c r="P7" s="430" t="n"/>
+      <c r="Q7" s="430" t="n"/>
+      <c r="R7" s="430" t="n"/>
+      <c r="S7" s="430" t="n"/>
+      <c r="T7" s="430" t="n"/>
+      <c r="U7" s="430" t="n"/>
+      <c r="V7" s="430" t="n"/>
+      <c r="W7" s="430" t="n"/>
+      <c r="X7" s="430" t="n"/>
+      <c r="Y7" s="430" t="n"/>
+      <c r="Z7" s="430" t="n"/>
+      <c r="AA7" s="430" t="n"/>
+      <c r="AB7" s="430" t="n"/>
+      <c r="AC7" s="430" t="n"/>
+      <c r="AD7" s="430" t="n"/>
+      <c r="AE7" s="430" t="n"/>
+      <c r="AF7" s="430" t="n"/>
+      <c r="AG7" s="430" t="n"/>
+      <c r="AH7" s="430" t="n"/>
+      <c r="AI7" s="430" t="n"/>
+      <c r="AJ7" s="430" t="n"/>
+      <c r="AK7" s="430" t="n"/>
+      <c r="AL7" s="430" t="n"/>
+      <c r="AM7" s="430" t="n"/>
+      <c r="AN7" s="430" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="302" t="n"/>
-      <c r="B8" s="302" t="n"/>
-      <c r="C8" s="302" t="n"/>
-      <c r="D8" s="302" t="n"/>
-      <c r="E8" s="302" t="n"/>
-      <c r="F8" s="302" t="n"/>
-      <c r="G8" s="302" t="n"/>
+      <c r="A8" s="476" t="n"/>
+      <c r="B8" s="476" t="n"/>
+      <c r="C8" s="476" t="n"/>
+      <c r="D8" s="476" t="n"/>
+      <c r="E8" s="476" t="n"/>
+      <c r="F8" s="476" t="n"/>
+      <c r="G8" s="476" t="n"/>
+      <c r="H8" s="447" t="n"/>
+      <c r="I8" s="447" t="n"/>
+      <c r="J8" s="447" t="n"/>
+      <c r="K8" s="447" t="n"/>
+      <c r="L8" s="447" t="n"/>
+      <c r="M8" s="447" t="n"/>
+      <c r="N8" s="447" t="n"/>
+      <c r="O8" s="447" t="n"/>
+      <c r="P8" s="447" t="n"/>
+      <c r="Q8" s="447" t="n"/>
+      <c r="R8" s="447" t="n"/>
+      <c r="S8" s="447" t="n"/>
+      <c r="T8" s="447" t="n"/>
+      <c r="U8" s="447" t="n"/>
+      <c r="V8" s="447" t="n"/>
+      <c r="W8" s="447" t="n"/>
+      <c r="X8" s="447" t="n"/>
+      <c r="Y8" s="447" t="n"/>
+      <c r="Z8" s="447" t="n"/>
+      <c r="AA8" s="447" t="n"/>
+      <c r="AB8" s="447" t="n"/>
+      <c r="AC8" s="447" t="n"/>
+      <c r="AD8" s="447" t="n"/>
+      <c r="AE8" s="447" t="n"/>
+      <c r="AF8" s="447" t="n"/>
+      <c r="AG8" s="447" t="n"/>
+      <c r="AH8" s="447" t="n"/>
+      <c r="AI8" s="447" t="n"/>
+      <c r="AJ8" s="447" t="n"/>
+      <c r="AK8" s="447" t="n"/>
+      <c r="AL8" s="447" t="n"/>
+      <c r="AM8" s="447" t="n"/>
+      <c r="AN8" s="447" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="302" t="n"/>
-      <c r="B9" s="302" t="n"/>
-      <c r="C9" s="302" t="n"/>
-      <c r="D9" s="302" t="n"/>
-      <c r="E9" s="302" t="n"/>
-      <c r="F9" s="302" t="n"/>
-      <c r="G9" s="302" t="n"/>
+      <c r="A9" s="476" t="n"/>
+      <c r="B9" s="476" t="n"/>
+      <c r="C9" s="476" t="n"/>
+      <c r="D9" s="476" t="n"/>
+      <c r="E9" s="476" t="n"/>
+      <c r="F9" s="476" t="n"/>
+      <c r="G9" s="476" t="n"/>
+      <c r="H9" s="447" t="n"/>
+      <c r="I9" s="447" t="n"/>
+      <c r="J9" s="447" t="n"/>
+      <c r="K9" s="447" t="n"/>
+      <c r="L9" s="447" t="n"/>
+      <c r="M9" s="447" t="n"/>
+      <c r="N9" s="447" t="n"/>
+      <c r="O9" s="447" t="n"/>
+      <c r="P9" s="447" t="n"/>
+      <c r="Q9" s="447" t="n"/>
+      <c r="R9" s="447" t="n"/>
+      <c r="S9" s="447" t="n"/>
+      <c r="T9" s="447" t="n"/>
+      <c r="U9" s="447" t="n"/>
+      <c r="V9" s="447" t="n"/>
+      <c r="W9" s="447" t="n"/>
+      <c r="X9" s="447" t="n"/>
+      <c r="Y9" s="447" t="n"/>
+      <c r="Z9" s="447" t="n"/>
+      <c r="AA9" s="447" t="n"/>
+      <c r="AB9" s="447" t="n"/>
+      <c r="AC9" s="447" t="n"/>
+      <c r="AD9" s="447" t="n"/>
+      <c r="AE9" s="447" t="n"/>
+      <c r="AF9" s="447" t="n"/>
+      <c r="AG9" s="447" t="n"/>
+      <c r="AH9" s="447" t="n"/>
+      <c r="AI9" s="447" t="n"/>
+      <c r="AJ9" s="447" t="n"/>
+      <c r="AK9" s="447" t="n"/>
+      <c r="AL9" s="447" t="n"/>
+      <c r="AM9" s="447" t="n"/>
+      <c r="AN9" s="447" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="302" t="n"/>
-      <c r="B10" s="302" t="n"/>
-      <c r="C10" s="302" t="n"/>
-      <c r="D10" s="302" t="n"/>
-      <c r="E10" s="302" t="n"/>
-      <c r="F10" s="302" t="n"/>
-      <c r="G10" s="302" t="n"/>
+      <c r="A10" s="476" t="n"/>
+      <c r="B10" s="476" t="n"/>
+      <c r="C10" s="476" t="n"/>
+      <c r="D10" s="476" t="n"/>
+      <c r="E10" s="476" t="n"/>
+      <c r="F10" s="476" t="n"/>
+      <c r="G10" s="476" t="n"/>
+      <c r="H10" s="447" t="n"/>
+      <c r="I10" s="447" t="n"/>
+      <c r="J10" s="447" t="n"/>
+      <c r="K10" s="447" t="n"/>
+      <c r="L10" s="447" t="n"/>
+      <c r="M10" s="447" t="n"/>
+      <c r="N10" s="447" t="n"/>
+      <c r="O10" s="447" t="n"/>
+      <c r="P10" s="447" t="n"/>
+      <c r="Q10" s="447" t="n"/>
+      <c r="R10" s="447" t="n"/>
+      <c r="S10" s="447" t="n"/>
+      <c r="T10" s="447" t="n"/>
+      <c r="U10" s="447" t="n"/>
+      <c r="V10" s="447" t="n"/>
+      <c r="W10" s="447" t="n"/>
+      <c r="X10" s="447" t="n"/>
+      <c r="Y10" s="447" t="n"/>
+      <c r="Z10" s="447" t="n"/>
+      <c r="AA10" s="447" t="n"/>
+      <c r="AB10" s="447" t="n"/>
+      <c r="AC10" s="447" t="n"/>
+      <c r="AD10" s="447" t="n"/>
+      <c r="AE10" s="447" t="n"/>
+      <c r="AF10" s="447" t="n"/>
+      <c r="AG10" s="447" t="n"/>
+      <c r="AH10" s="447" t="n"/>
+      <c r="AI10" s="447" t="n"/>
+      <c r="AJ10" s="447" t="n"/>
+      <c r="AK10" s="447" t="n"/>
+      <c r="AL10" s="447" t="n"/>
+      <c r="AM10" s="447" t="n"/>
+      <c r="AN10" s="447" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="302" t="n"/>
-      <c r="B11" s="302" t="n"/>
-      <c r="C11" s="302" t="n"/>
-      <c r="D11" s="302" t="n"/>
-      <c r="E11" s="302" t="n"/>
-      <c r="F11" s="302" t="n"/>
-      <c r="G11" s="302" t="n"/>
+      <c r="A11" s="476" t="n"/>
+      <c r="B11" s="476" t="n"/>
+      <c r="C11" s="476" t="n"/>
+      <c r="D11" s="476" t="n"/>
+      <c r="E11" s="476" t="n"/>
+      <c r="F11" s="476" t="n"/>
+      <c r="G11" s="476" t="n"/>
+      <c r="H11" s="447" t="n"/>
+      <c r="I11" s="447" t="n"/>
+      <c r="J11" s="447" t="n"/>
+      <c r="K11" s="447" t="n"/>
+      <c r="L11" s="447" t="n"/>
+      <c r="M11" s="447" t="n"/>
+      <c r="N11" s="447" t="n"/>
+      <c r="O11" s="447" t="n"/>
+      <c r="P11" s="447" t="n"/>
+      <c r="Q11" s="447" t="n"/>
+      <c r="R11" s="447" t="n"/>
+      <c r="S11" s="447" t="n"/>
+      <c r="T11" s="447" t="n"/>
+      <c r="U11" s="447" t="n"/>
+      <c r="V11" s="447" t="n"/>
+      <c r="W11" s="447" t="n"/>
+      <c r="X11" s="447" t="n"/>
+      <c r="Y11" s="447" t="n"/>
+      <c r="Z11" s="447" t="n"/>
+      <c r="AA11" s="447" t="n"/>
+      <c r="AB11" s="447" t="n"/>
+      <c r="AC11" s="447" t="n"/>
+      <c r="AD11" s="447" t="n"/>
+      <c r="AE11" s="447" t="n"/>
+      <c r="AF11" s="447" t="n"/>
+      <c r="AG11" s="447" t="n"/>
+      <c r="AH11" s="447" t="n"/>
+      <c r="AI11" s="447" t="n"/>
+      <c r="AJ11" s="447" t="n"/>
+      <c r="AK11" s="447" t="n"/>
+      <c r="AL11" s="447" t="n"/>
+      <c r="AM11" s="447" t="n"/>
+      <c r="AN11" s="447" t="n"/>
     </row>
     <row r="12" hidden="1"/>
     <row r="13" hidden="1"/>

--- a/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
   </numFmts>
-  <fonts count="82">
+  <fonts count="86">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -498,8 +498,30 @@
       <color theme="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001565C0"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007A8FA6"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="51">
+  <fills count="56">
     <fill>
       <patternFill/>
     </fill>
@@ -751,8 +773,33 @@
         <fgColor rgb="00F3F7FB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002C9CD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F0F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001565C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F7FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000C2D48"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="309">
+  <borders count="335">
     <border>
       <left/>
       <right/>
@@ -4073,12 +4120,286 @@
         <color rgb="00C5D9E8"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="505">
+  <cellXfs count="623">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5284,6 +5605,318 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="308" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="302" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="303" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="310" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="311" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="52" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="52" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="52" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="314" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="315" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="52" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="52" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="52" borderId="288" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="317" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="318" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="320" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="52" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="52" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="52" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="51" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="51" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="53" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="53" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="53" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="54" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="330" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="54" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="54" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="54" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="334" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="83" fillId="54" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="322" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="54" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="324" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="325" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="55" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="55" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="55" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="54" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="54" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="54" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="54" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="54" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="333" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="321" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="329" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="332" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="311" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="315" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="320" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -5357,6 +5990,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5635,602 +6358,606 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="424" t="n"/>
-      <c r="B1" s="496" t="n"/>
-      <c r="C1" s="426" t="inlineStr">
+      <c r="A1" s="505" t="n"/>
+      <c r="B1" s="506" t="n"/>
+      <c r="C1" s="507" t="inlineStr">
         <is>
           <t>RMA TRACKING LOG</t>
         </is>
       </c>
-      <c r="D1" s="497" t="n"/>
-      <c r="E1" s="497" t="n"/>
-      <c r="F1" s="497" t="n"/>
-      <c r="G1" s="497" t="n"/>
-      <c r="H1" s="496" t="n"/>
-      <c r="I1" s="428" t="inlineStr">
+      <c r="D1" s="506" t="n"/>
+      <c r="E1" s="506" t="n"/>
+      <c r="F1" s="506" t="n"/>
+      <c r="G1" s="506" t="n"/>
+      <c r="H1" s="508" t="n"/>
+      <c r="I1" s="509" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="J1" s="429" t="inlineStr">
+      <c r="J1" s="510" t="inlineStr">
         <is>
           <t>FRM-213</t>
         </is>
       </c>
-      <c r="K1" s="430" t="n"/>
-      <c r="L1" s="430" t="n"/>
-      <c r="M1" s="430" t="n"/>
-      <c r="N1" s="430" t="n"/>
-      <c r="O1" s="430" t="n"/>
-      <c r="P1" s="430" t="n"/>
-      <c r="Q1" s="430" t="n"/>
-      <c r="R1" s="430" t="n"/>
-      <c r="S1" s="430" t="n"/>
-      <c r="T1" s="430" t="n"/>
-      <c r="U1" s="430" t="n"/>
-      <c r="V1" s="430" t="n"/>
-      <c r="W1" s="430" t="n"/>
-      <c r="X1" s="430" t="n"/>
-      <c r="Y1" s="430" t="n"/>
-      <c r="Z1" s="430" t="n"/>
-      <c r="AA1" s="430" t="n"/>
-      <c r="AB1" s="430" t="n"/>
-      <c r="AC1" s="430" t="n"/>
-      <c r="AD1" s="430" t="n"/>
-      <c r="AE1" s="430" t="n"/>
-      <c r="AF1" s="430" t="n"/>
-      <c r="AG1" s="430" t="n"/>
-      <c r="AH1" s="430" t="n"/>
-      <c r="AI1" s="430" t="n"/>
-      <c r="AJ1" s="430" t="n"/>
-      <c r="AK1" s="430" t="n"/>
-      <c r="AL1" s="430" t="n"/>
-      <c r="AM1" s="430" t="n"/>
-      <c r="AN1" s="430" t="n"/>
+      <c r="K1" s="510" t="n"/>
+      <c r="L1" s="510" t="n"/>
+      <c r="M1" s="510" t="n"/>
+      <c r="N1" s="510" t="n"/>
+      <c r="O1" s="510" t="n"/>
+      <c r="P1" s="510" t="n"/>
+      <c r="Q1" s="510" t="n"/>
+      <c r="R1" s="510" t="n"/>
+      <c r="S1" s="510" t="n"/>
+      <c r="T1" s="510" t="n"/>
+      <c r="U1" s="510" t="n"/>
+      <c r="V1" s="510" t="n"/>
+      <c r="W1" s="510" t="n"/>
+      <c r="X1" s="510" t="n"/>
+      <c r="Y1" s="510" t="n"/>
+      <c r="Z1" s="510" t="n"/>
+      <c r="AA1" s="510" t="n"/>
+      <c r="AB1" s="510" t="n"/>
+      <c r="AC1" s="510" t="n"/>
+      <c r="AD1" s="511" t="n"/>
+      <c r="AE1" s="512" t="n"/>
+      <c r="AF1" s="513" t="n"/>
+      <c r="AG1" s="513" t="n"/>
+      <c r="AH1" s="514" t="n"/>
+      <c r="AI1" s="515" t="n"/>
+      <c r="AJ1" s="516" t="n"/>
+      <c r="AK1" s="516" t="n"/>
+      <c r="AL1" s="516" t="n"/>
+      <c r="AM1" s="516" t="n"/>
+      <c r="AN1" s="517" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="498" t="n"/>
-      <c r="B2" s="499" t="n"/>
-      <c r="C2" s="498" t="n"/>
-      <c r="H2" s="499" t="n"/>
-      <c r="I2" s="428" t="inlineStr">
+      <c r="A2" s="518" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="519" t="n"/>
+      <c r="I2" s="520" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="J2" s="429" t="inlineStr">
+      <c r="J2" s="521" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="K2" s="430" t="n"/>
-      <c r="L2" s="430" t="n"/>
-      <c r="M2" s="430" t="n"/>
-      <c r="N2" s="430" t="n"/>
-      <c r="O2" s="430" t="n"/>
-      <c r="P2" s="430" t="n"/>
-      <c r="Q2" s="430" t="n"/>
-      <c r="R2" s="430" t="n"/>
-      <c r="S2" s="430" t="n"/>
-      <c r="T2" s="430" t="n"/>
-      <c r="U2" s="430" t="n"/>
-      <c r="V2" s="430" t="n"/>
-      <c r="W2" s="430" t="n"/>
-      <c r="X2" s="430" t="n"/>
-      <c r="Y2" s="430" t="n"/>
-      <c r="Z2" s="430" t="n"/>
-      <c r="AA2" s="430" t="n"/>
-      <c r="AB2" s="430" t="n"/>
-      <c r="AC2" s="430" t="n"/>
-      <c r="AD2" s="430" t="n"/>
-      <c r="AE2" s="430" t="n"/>
-      <c r="AF2" s="430" t="n"/>
-      <c r="AG2" s="430" t="n"/>
-      <c r="AH2" s="430" t="n"/>
-      <c r="AI2" s="430" t="n"/>
-      <c r="AJ2" s="430" t="n"/>
-      <c r="AK2" s="430" t="n"/>
-      <c r="AL2" s="430" t="n"/>
-      <c r="AM2" s="430" t="n"/>
-      <c r="AN2" s="430" t="n"/>
+      <c r="K2" s="521" t="n"/>
+      <c r="L2" s="521" t="n"/>
+      <c r="M2" s="521" t="n"/>
+      <c r="N2" s="521" t="n"/>
+      <c r="O2" s="521" t="n"/>
+      <c r="P2" s="521" t="n"/>
+      <c r="Q2" s="521" t="n"/>
+      <c r="R2" s="521" t="n"/>
+      <c r="S2" s="521" t="n"/>
+      <c r="T2" s="521" t="n"/>
+      <c r="U2" s="521" t="n"/>
+      <c r="V2" s="521" t="n"/>
+      <c r="W2" s="521" t="n"/>
+      <c r="X2" s="521" t="n"/>
+      <c r="Y2" s="521" t="n"/>
+      <c r="Z2" s="521" t="n"/>
+      <c r="AA2" s="521" t="n"/>
+      <c r="AB2" s="521" t="n"/>
+      <c r="AC2" s="521" t="n"/>
+      <c r="AD2" s="522" t="n"/>
+      <c r="AE2" s="523" t="n"/>
+      <c r="AF2" s="524" t="n"/>
+      <c r="AG2" s="524" t="n"/>
+      <c r="AH2" s="525" t="n"/>
+      <c r="AI2" s="526" t="n"/>
+      <c r="AJ2" s="527" t="n"/>
+      <c r="AK2" s="527" t="n"/>
+      <c r="AL2" s="527" t="n"/>
+      <c r="AM2" s="527" t="n"/>
+      <c r="AN2" s="528" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="498" t="n"/>
-      <c r="B3" s="499" t="n"/>
-      <c r="C3" s="500" t="n"/>
-      <c r="D3" s="501" t="n"/>
-      <c r="E3" s="501" t="n"/>
-      <c r="F3" s="501" t="n"/>
-      <c r="G3" s="501" t="n"/>
-      <c r="H3" s="502" t="n"/>
-      <c r="I3" s="428" t="inlineStr">
+      <c r="A3" s="518" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="519" t="n"/>
+      <c r="I3" s="520" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="J3" s="429" t="inlineStr">
+      <c r="J3" s="521" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="K3" s="430" t="n"/>
-      <c r="L3" s="430" t="n"/>
-      <c r="M3" s="430" t="n"/>
-      <c r="N3" s="430" t="n"/>
-      <c r="O3" s="430" t="n"/>
-      <c r="P3" s="430" t="n"/>
-      <c r="Q3" s="430" t="n"/>
-      <c r="R3" s="430" t="n"/>
-      <c r="S3" s="430" t="n"/>
-      <c r="T3" s="430" t="n"/>
-      <c r="U3" s="430" t="n"/>
-      <c r="V3" s="430" t="n"/>
-      <c r="W3" s="430" t="n"/>
-      <c r="X3" s="430" t="n"/>
-      <c r="Y3" s="430" t="n"/>
-      <c r="Z3" s="430" t="n"/>
-      <c r="AA3" s="430" t="n"/>
-      <c r="AB3" s="430" t="n"/>
-      <c r="AC3" s="430" t="n"/>
-      <c r="AD3" s="430" t="n"/>
-      <c r="AE3" s="430" t="n"/>
-      <c r="AF3" s="430" t="n"/>
-      <c r="AG3" s="430" t="n"/>
-      <c r="AH3" s="430" t="n"/>
-      <c r="AI3" s="430" t="n"/>
-      <c r="AJ3" s="430" t="n"/>
-      <c r="AK3" s="430" t="n"/>
-      <c r="AL3" s="430" t="n"/>
-      <c r="AM3" s="430" t="n"/>
-      <c r="AN3" s="430" t="n"/>
+      <c r="K3" s="521" t="n"/>
+      <c r="L3" s="521" t="n"/>
+      <c r="M3" s="521" t="n"/>
+      <c r="N3" s="521" t="n"/>
+      <c r="O3" s="521" t="n"/>
+      <c r="P3" s="521" t="n"/>
+      <c r="Q3" s="521" t="n"/>
+      <c r="R3" s="521" t="n"/>
+      <c r="S3" s="521" t="n"/>
+      <c r="T3" s="521" t="n"/>
+      <c r="U3" s="521" t="n"/>
+      <c r="V3" s="521" t="n"/>
+      <c r="W3" s="521" t="n"/>
+      <c r="X3" s="521" t="n"/>
+      <c r="Y3" s="521" t="n"/>
+      <c r="Z3" s="521" t="n"/>
+      <c r="AA3" s="521" t="n"/>
+      <c r="AB3" s="521" t="n"/>
+      <c r="AC3" s="521" t="n"/>
+      <c r="AD3" s="522" t="n"/>
+      <c r="AE3" s="523" t="n"/>
+      <c r="AF3" s="524" t="n"/>
+      <c r="AG3" s="524" t="n"/>
+      <c r="AH3" s="525" t="n"/>
+      <c r="AI3" s="526" t="n"/>
+      <c r="AJ3" s="527" t="n"/>
+      <c r="AK3" s="527" t="n"/>
+      <c r="AL3" s="527" t="n"/>
+      <c r="AM3" s="527" t="n"/>
+      <c r="AN3" s="528" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="498" t="n"/>
-      <c r="B4" s="499" t="n"/>
-      <c r="C4" s="436" t="inlineStr">
+      <c r="A4" s="518" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="529" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="503" t="n"/>
-      <c r="E4" s="503" t="n"/>
-      <c r="F4" s="503" t="n"/>
-      <c r="G4" s="503" t="n"/>
-      <c r="H4" s="504" t="n"/>
-      <c r="I4" s="428" t="inlineStr">
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="519" t="n"/>
+      <c r="I4" s="530" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="J4" s="429" t="inlineStr">
+      <c r="J4" s="531" t="inlineStr">
         <is>
           <t>QA / Customer Service</t>
         </is>
       </c>
-      <c r="K4" s="430" t="n"/>
-      <c r="L4" s="430" t="n"/>
-      <c r="M4" s="430" t="n"/>
-      <c r="N4" s="430" t="n"/>
-      <c r="O4" s="430" t="n"/>
-      <c r="P4" s="430" t="n"/>
-      <c r="Q4" s="430" t="n"/>
-      <c r="R4" s="430" t="n"/>
-      <c r="S4" s="430" t="n"/>
-      <c r="T4" s="430" t="n"/>
-      <c r="U4" s="430" t="n"/>
-      <c r="V4" s="430" t="n"/>
-      <c r="W4" s="430" t="n"/>
-      <c r="X4" s="430" t="n"/>
-      <c r="Y4" s="430" t="n"/>
-      <c r="Z4" s="430" t="n"/>
-      <c r="AA4" s="430" t="n"/>
-      <c r="AB4" s="430" t="n"/>
-      <c r="AC4" s="430" t="n"/>
-      <c r="AD4" s="430" t="n"/>
-      <c r="AE4" s="430" t="n"/>
-      <c r="AF4" s="430" t="n"/>
-      <c r="AG4" s="430" t="n"/>
-      <c r="AH4" s="430" t="n"/>
-      <c r="AI4" s="430" t="n"/>
-      <c r="AJ4" s="430" t="n"/>
-      <c r="AK4" s="430" t="n"/>
-      <c r="AL4" s="430" t="n"/>
-      <c r="AM4" s="430" t="n"/>
-      <c r="AN4" s="430" t="n"/>
+      <c r="K4" s="531" t="n"/>
+      <c r="L4" s="531" t="n"/>
+      <c r="M4" s="531" t="n"/>
+      <c r="N4" s="531" t="n"/>
+      <c r="O4" s="531" t="n"/>
+      <c r="P4" s="531" t="n"/>
+      <c r="Q4" s="531" t="n"/>
+      <c r="R4" s="531" t="n"/>
+      <c r="S4" s="531" t="n"/>
+      <c r="T4" s="531" t="n"/>
+      <c r="U4" s="531" t="n"/>
+      <c r="V4" s="531" t="n"/>
+      <c r="W4" s="531" t="n"/>
+      <c r="X4" s="531" t="n"/>
+      <c r="Y4" s="531" t="n"/>
+      <c r="Z4" s="531" t="n"/>
+      <c r="AA4" s="531" t="n"/>
+      <c r="AB4" s="531" t="n"/>
+      <c r="AC4" s="531" t="n"/>
+      <c r="AD4" s="532" t="n"/>
+      <c r="AE4" s="523" t="n"/>
+      <c r="AF4" s="524" t="n"/>
+      <c r="AG4" s="524" t="n"/>
+      <c r="AH4" s="525" t="n"/>
+      <c r="AI4" s="526" t="n"/>
+      <c r="AJ4" s="527" t="n"/>
+      <c r="AK4" s="527" t="n"/>
+      <c r="AL4" s="527" t="n"/>
+      <c r="AM4" s="527" t="n"/>
+      <c r="AN4" s="528" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="500" t="n"/>
-      <c r="B5" s="502" t="n"/>
-      <c r="C5" s="439" t="inlineStr">
+      <c r="A5" s="533" t="n"/>
+      <c r="B5" s="534" t="n"/>
+      <c r="C5" s="535" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="503" t="n"/>
-      <c r="E5" s="503" t="n"/>
-      <c r="F5" s="503" t="n"/>
-      <c r="G5" s="503" t="n"/>
-      <c r="H5" s="504" t="n"/>
-      <c r="I5" s="440" t="inlineStr">
+      <c r="D5" s="534" t="n"/>
+      <c r="E5" s="534" t="n"/>
+      <c r="F5" s="534" t="n"/>
+      <c r="G5" s="534" t="n"/>
+      <c r="H5" s="536" t="n"/>
+      <c r="I5" s="537" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="J5" s="441" t="inlineStr">
+      <c r="J5" s="538" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
       </c>
-      <c r="K5" s="430" t="n"/>
-      <c r="L5" s="430" t="n"/>
-      <c r="M5" s="430" t="n"/>
-      <c r="N5" s="430" t="n"/>
-      <c r="O5" s="430" t="n"/>
-      <c r="P5" s="430" t="n"/>
-      <c r="Q5" s="430" t="n"/>
-      <c r="R5" s="430" t="n"/>
-      <c r="S5" s="430" t="n"/>
-      <c r="T5" s="430" t="n"/>
-      <c r="U5" s="430" t="n"/>
-      <c r="V5" s="430" t="n"/>
-      <c r="W5" s="430" t="n"/>
-      <c r="X5" s="430" t="n"/>
-      <c r="Y5" s="430" t="n"/>
-      <c r="Z5" s="430" t="n"/>
-      <c r="AA5" s="430" t="n"/>
-      <c r="AB5" s="430" t="n"/>
-      <c r="AC5" s="430" t="n"/>
-      <c r="AD5" s="430" t="n"/>
-      <c r="AE5" s="430" t="n"/>
-      <c r="AF5" s="430" t="n"/>
-      <c r="AG5" s="430" t="n"/>
-      <c r="AH5" s="430" t="n"/>
-      <c r="AI5" s="430" t="n"/>
-      <c r="AJ5" s="430" t="n"/>
-      <c r="AK5" s="430" t="n"/>
-      <c r="AL5" s="430" t="n"/>
-      <c r="AM5" s="430" t="n"/>
-      <c r="AN5" s="430" t="n"/>
+      <c r="K5" s="538" t="n"/>
+      <c r="L5" s="538" t="n"/>
+      <c r="M5" s="538" t="n"/>
+      <c r="N5" s="538" t="n"/>
+      <c r="O5" s="538" t="n"/>
+      <c r="P5" s="538" t="n"/>
+      <c r="Q5" s="538" t="n"/>
+      <c r="R5" s="538" t="n"/>
+      <c r="S5" s="538" t="n"/>
+      <c r="T5" s="538" t="n"/>
+      <c r="U5" s="538" t="n"/>
+      <c r="V5" s="538" t="n"/>
+      <c r="W5" s="538" t="n"/>
+      <c r="X5" s="538" t="n"/>
+      <c r="Y5" s="538" t="n"/>
+      <c r="Z5" s="538" t="n"/>
+      <c r="AA5" s="538" t="n"/>
+      <c r="AB5" s="538" t="n"/>
+      <c r="AC5" s="538" t="n"/>
+      <c r="AD5" s="539" t="n"/>
+      <c r="AE5" s="540" t="n"/>
+      <c r="AF5" s="541" t="n"/>
+      <c r="AG5" s="541" t="n"/>
+      <c r="AH5" s="542" t="n"/>
+      <c r="AI5" s="543" t="n"/>
+      <c r="AJ5" s="544" t="n"/>
+      <c r="AK5" s="544" t="n"/>
+      <c r="AL5" s="544" t="n"/>
+      <c r="AM5" s="544" t="n"/>
+      <c r="AN5" s="545" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="442" t="n"/>
-      <c r="B6" s="495" t="n"/>
-      <c r="C6" s="495" t="n"/>
-      <c r="D6" s="495" t="n"/>
-      <c r="E6" s="495" t="n"/>
-      <c r="F6" s="495" t="n"/>
-      <c r="G6" s="495" t="n"/>
-      <c r="H6" s="495" t="n"/>
-      <c r="I6" s="495" t="n"/>
-      <c r="J6" s="495" t="n"/>
-      <c r="K6" s="443" t="n"/>
-      <c r="L6" s="443" t="n"/>
-      <c r="M6" s="443" t="n"/>
-      <c r="N6" s="443" t="n"/>
-      <c r="O6" s="443" t="n"/>
-      <c r="P6" s="443" t="n"/>
-      <c r="Q6" s="443" t="n"/>
-      <c r="R6" s="443" t="n"/>
-      <c r="S6" s="443" t="n"/>
-      <c r="T6" s="443" t="n"/>
-      <c r="U6" s="443" t="n"/>
-      <c r="V6" s="443" t="n"/>
-      <c r="W6" s="443" t="n"/>
-      <c r="X6" s="443" t="n"/>
-      <c r="Y6" s="443" t="n"/>
-      <c r="Z6" s="443" t="n"/>
-      <c r="AA6" s="443" t="n"/>
-      <c r="AB6" s="443" t="n"/>
-      <c r="AC6" s="443" t="n"/>
-      <c r="AD6" s="443" t="n"/>
-      <c r="AE6" s="443" t="n"/>
-      <c r="AF6" s="443" t="n"/>
-      <c r="AG6" s="443" t="n"/>
-      <c r="AH6" s="443" t="n"/>
-      <c r="AI6" s="443" t="n"/>
-      <c r="AJ6" s="443" t="n"/>
-      <c r="AK6" s="443" t="n"/>
-      <c r="AL6" s="443" t="n"/>
-      <c r="AM6" s="443" t="n"/>
-      <c r="AN6" s="443" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="546" t="n"/>
+      <c r="B6" s="547" t="n"/>
+      <c r="C6" s="547" t="n"/>
+      <c r="D6" s="547" t="n"/>
+      <c r="E6" s="547" t="n"/>
+      <c r="F6" s="547" t="n"/>
+      <c r="G6" s="547" t="n"/>
+      <c r="H6" s="547" t="n"/>
+      <c r="I6" s="547" t="n"/>
+      <c r="J6" s="547" t="n"/>
+      <c r="K6" s="547" t="n"/>
+      <c r="L6" s="547" t="n"/>
+      <c r="M6" s="547" t="n"/>
+      <c r="N6" s="547" t="n"/>
+      <c r="O6" s="547" t="n"/>
+      <c r="P6" s="547" t="n"/>
+      <c r="Q6" s="547" t="n"/>
+      <c r="R6" s="547" t="n"/>
+      <c r="S6" s="547" t="n"/>
+      <c r="T6" s="547" t="n"/>
+      <c r="U6" s="547" t="n"/>
+      <c r="V6" s="547" t="n"/>
+      <c r="W6" s="547" t="n"/>
+      <c r="X6" s="547" t="n"/>
+      <c r="Y6" s="547" t="n"/>
+      <c r="Z6" s="547" t="n"/>
+      <c r="AA6" s="547" t="n"/>
+      <c r="AB6" s="547" t="n"/>
+      <c r="AC6" s="547" t="n"/>
+      <c r="AD6" s="547" t="n"/>
+      <c r="AE6" s="547" t="n"/>
+      <c r="AF6" s="547" t="n"/>
+      <c r="AG6" s="547" t="n"/>
+      <c r="AH6" s="547" t="n"/>
+      <c r="AI6" s="547" t="n"/>
+      <c r="AJ6" s="547" t="n"/>
+      <c r="AK6" s="547" t="n"/>
+      <c r="AL6" s="547" t="n"/>
+      <c r="AM6" s="547" t="n"/>
+      <c r="AN6" s="547" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="444" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="548" t="inlineStr">
         <is>
           <t>1.  RMA HEADER</t>
         </is>
       </c>
-      <c r="B7" s="503" t="n"/>
-      <c r="C7" s="503" t="n"/>
-      <c r="D7" s="503" t="n"/>
-      <c r="E7" s="503" t="n"/>
-      <c r="F7" s="503" t="n"/>
-      <c r="G7" s="503" t="n"/>
-      <c r="H7" s="503" t="n"/>
-      <c r="I7" s="503" t="n"/>
-      <c r="J7" s="504" t="n"/>
-      <c r="K7" s="430" t="n"/>
-      <c r="L7" s="430" t="n"/>
-      <c r="M7" s="430" t="n"/>
-      <c r="N7" s="430" t="n"/>
-      <c r="O7" s="430" t="n"/>
-      <c r="P7" s="430" t="n"/>
-      <c r="Q7" s="430" t="n"/>
-      <c r="R7" s="430" t="n"/>
-      <c r="S7" s="430" t="n"/>
-      <c r="T7" s="430" t="n"/>
-      <c r="U7" s="430" t="n"/>
-      <c r="V7" s="430" t="n"/>
-      <c r="W7" s="430" t="n"/>
-      <c r="X7" s="430" t="n"/>
-      <c r="Y7" s="430" t="n"/>
-      <c r="Z7" s="430" t="n"/>
-      <c r="AA7" s="430" t="n"/>
-      <c r="AB7" s="430" t="n"/>
-      <c r="AC7" s="430" t="n"/>
-      <c r="AD7" s="430" t="n"/>
-      <c r="AE7" s="430" t="n"/>
-      <c r="AF7" s="430" t="n"/>
-      <c r="AG7" s="430" t="n"/>
-      <c r="AH7" s="430" t="n"/>
-      <c r="AI7" s="430" t="n"/>
-      <c r="AJ7" s="430" t="n"/>
-      <c r="AK7" s="430" t="n"/>
-      <c r="AL7" s="430" t="n"/>
-      <c r="AM7" s="430" t="n"/>
-      <c r="AN7" s="430" t="n"/>
+      <c r="B7" s="549" t="n"/>
+      <c r="C7" s="549" t="n"/>
+      <c r="D7" s="549" t="n"/>
+      <c r="E7" s="549" t="n"/>
+      <c r="F7" s="549" t="n"/>
+      <c r="G7" s="549" t="n"/>
+      <c r="H7" s="549" t="n"/>
+      <c r="I7" s="549" t="n"/>
+      <c r="J7" s="549" t="n"/>
+      <c r="K7" s="549" t="n"/>
+      <c r="L7" s="549" t="n"/>
+      <c r="M7" s="549" t="n"/>
+      <c r="N7" s="549" t="n"/>
+      <c r="O7" s="549" t="n"/>
+      <c r="P7" s="549" t="n"/>
+      <c r="Q7" s="549" t="n"/>
+      <c r="R7" s="549" t="n"/>
+      <c r="S7" s="549" t="n"/>
+      <c r="T7" s="549" t="n"/>
+      <c r="U7" s="549" t="n"/>
+      <c r="V7" s="549" t="n"/>
+      <c r="W7" s="549" t="n"/>
+      <c r="X7" s="549" t="n"/>
+      <c r="Y7" s="549" t="n"/>
+      <c r="Z7" s="549" t="n"/>
+      <c r="AA7" s="549" t="n"/>
+      <c r="AB7" s="549" t="n"/>
+      <c r="AC7" s="549" t="n"/>
+      <c r="AD7" s="549" t="n"/>
+      <c r="AE7" s="549" t="n"/>
+      <c r="AF7" s="549" t="n"/>
+      <c r="AG7" s="549" t="n"/>
+      <c r="AH7" s="549" t="n"/>
+      <c r="AI7" s="549" t="n"/>
+      <c r="AJ7" s="549" t="n"/>
+      <c r="AK7" s="549" t="n"/>
+      <c r="AL7" s="549" t="n"/>
+      <c r="AM7" s="549" t="n"/>
+      <c r="AN7" s="550" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="440" t="inlineStr">
+      <c r="A8" s="551" t="inlineStr">
         <is>
           <t>Open Period</t>
         </is>
       </c>
-      <c r="B8" s="486" t="n"/>
-      <c r="C8" s="441" t="inlineStr"/>
-      <c r="D8" s="487" t="n"/>
-      <c r="E8" s="486" t="n"/>
-      <c r="F8" s="440" t="inlineStr">
+      <c r="B8" s="552" t="n"/>
+      <c r="C8" s="553" t="inlineStr"/>
+      <c r="D8" s="552" t="n"/>
+      <c r="E8" s="552" t="n"/>
+      <c r="F8" s="554" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="G8" s="486" t="n"/>
-      <c r="H8" s="441" t="inlineStr"/>
-      <c r="I8" s="487" t="n"/>
-      <c r="J8" s="486" t="n"/>
-      <c r="K8" s="447" t="n"/>
-      <c r="L8" s="447" t="n"/>
-      <c r="M8" s="447" t="n"/>
-      <c r="N8" s="447" t="n"/>
-      <c r="O8" s="447" t="n"/>
-      <c r="P8" s="447" t="n"/>
-      <c r="Q8" s="447" t="n"/>
-      <c r="R8" s="447" t="n"/>
-      <c r="S8" s="447" t="n"/>
-      <c r="T8" s="447" t="n"/>
-      <c r="U8" s="447" t="n"/>
-      <c r="V8" s="447" t="n"/>
-      <c r="W8" s="447" t="n"/>
-      <c r="X8" s="447" t="n"/>
-      <c r="Y8" s="447" t="n"/>
-      <c r="Z8" s="447" t="n"/>
-      <c r="AA8" s="447" t="n"/>
-      <c r="AB8" s="447" t="n"/>
-      <c r="AC8" s="447" t="n"/>
-      <c r="AD8" s="447" t="n"/>
-      <c r="AE8" s="447" t="n"/>
-      <c r="AF8" s="447" t="n"/>
-      <c r="AG8" s="447" t="n"/>
-      <c r="AH8" s="447" t="n"/>
-      <c r="AI8" s="447" t="n"/>
-      <c r="AJ8" s="447" t="n"/>
-      <c r="AK8" s="447" t="n"/>
-      <c r="AL8" s="447" t="n"/>
-      <c r="AM8" s="447" t="n"/>
-      <c r="AN8" s="447" t="n"/>
+      <c r="G8" s="552" t="n"/>
+      <c r="H8" s="553" t="inlineStr"/>
+      <c r="I8" s="552" t="n"/>
+      <c r="J8" s="552" t="n"/>
+      <c r="K8" s="555" t="n"/>
+      <c r="L8" s="556" t="n"/>
+      <c r="M8" s="556" t="n"/>
+      <c r="N8" s="556" t="n"/>
+      <c r="O8" s="556" t="n"/>
+      <c r="P8" s="556" t="n"/>
+      <c r="Q8" s="556" t="n"/>
+      <c r="R8" s="556" t="n"/>
+      <c r="S8" s="556" t="n"/>
+      <c r="T8" s="556" t="n"/>
+      <c r="U8" s="556" t="n"/>
+      <c r="V8" s="556" t="n"/>
+      <c r="W8" s="556" t="n"/>
+      <c r="X8" s="556" t="n"/>
+      <c r="Y8" s="556" t="n"/>
+      <c r="Z8" s="556" t="n"/>
+      <c r="AA8" s="556" t="n"/>
+      <c r="AB8" s="556" t="n"/>
+      <c r="AC8" s="556" t="n"/>
+      <c r="AD8" s="556" t="n"/>
+      <c r="AE8" s="556" t="n"/>
+      <c r="AF8" s="556" t="n"/>
+      <c r="AG8" s="556" t="n"/>
+      <c r="AH8" s="556" t="n"/>
+      <c r="AI8" s="556" t="n"/>
+      <c r="AJ8" s="556" t="n"/>
+      <c r="AK8" s="556" t="n"/>
+      <c r="AL8" s="556" t="n"/>
+      <c r="AM8" s="556" t="n"/>
+      <c r="AN8" s="557" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="440" t="inlineStr">
+      <c r="A9" s="558" t="inlineStr">
         <is>
           <t>RMA Owner</t>
         </is>
       </c>
-      <c r="B9" s="486" t="n"/>
-      <c r="C9" s="441" t="inlineStr"/>
-      <c r="D9" s="487" t="n"/>
-      <c r="E9" s="486" t="n"/>
-      <c r="F9" s="440" t="inlineStr">
+      <c r="B9" s="437" t="n"/>
+      <c r="C9" s="559" t="inlineStr"/>
+      <c r="D9" s="437" t="n"/>
+      <c r="E9" s="437" t="n"/>
+      <c r="F9" s="560" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="G9" s="486" t="n"/>
-      <c r="H9" s="441" t="inlineStr"/>
-      <c r="I9" s="487" t="n"/>
-      <c r="J9" s="486" t="n"/>
-      <c r="K9" s="447" t="n"/>
-      <c r="L9" s="447" t="n"/>
-      <c r="M9" s="447" t="n"/>
-      <c r="N9" s="447" t="n"/>
-      <c r="O9" s="447" t="n"/>
-      <c r="P9" s="447" t="n"/>
-      <c r="Q9" s="447" t="n"/>
-      <c r="R9" s="447" t="n"/>
-      <c r="S9" s="447" t="n"/>
-      <c r="T9" s="447" t="n"/>
-      <c r="U9" s="447" t="n"/>
-      <c r="V9" s="447" t="n"/>
-      <c r="W9" s="447" t="n"/>
-      <c r="X9" s="447" t="n"/>
-      <c r="Y9" s="447" t="n"/>
-      <c r="Z9" s="447" t="n"/>
-      <c r="AA9" s="447" t="n"/>
-      <c r="AB9" s="447" t="n"/>
-      <c r="AC9" s="447" t="n"/>
-      <c r="AD9" s="447" t="n"/>
-      <c r="AE9" s="447" t="n"/>
-      <c r="AF9" s="447" t="n"/>
-      <c r="AG9" s="447" t="n"/>
-      <c r="AH9" s="447" t="n"/>
-      <c r="AI9" s="447" t="n"/>
-      <c r="AJ9" s="447" t="n"/>
-      <c r="AK9" s="447" t="n"/>
-      <c r="AL9" s="447" t="n"/>
-      <c r="AM9" s="447" t="n"/>
-      <c r="AN9" s="447" t="n"/>
+      <c r="G9" s="437" t="n"/>
+      <c r="H9" s="559" t="inlineStr"/>
+      <c r="I9" s="437" t="n"/>
+      <c r="J9" s="437" t="n"/>
+      <c r="K9" s="561" t="n"/>
+      <c r="L9" s="446" t="n"/>
+      <c r="M9" s="446" t="n"/>
+      <c r="N9" s="446" t="n"/>
+      <c r="O9" s="446" t="n"/>
+      <c r="P9" s="446" t="n"/>
+      <c r="Q9" s="446" t="n"/>
+      <c r="R9" s="446" t="n"/>
+      <c r="S9" s="446" t="n"/>
+      <c r="T9" s="446" t="n"/>
+      <c r="U9" s="446" t="n"/>
+      <c r="V9" s="446" t="n"/>
+      <c r="W9" s="446" t="n"/>
+      <c r="X9" s="446" t="n"/>
+      <c r="Y9" s="446" t="n"/>
+      <c r="Z9" s="446" t="n"/>
+      <c r="AA9" s="446" t="n"/>
+      <c r="AB9" s="446" t="n"/>
+      <c r="AC9" s="446" t="n"/>
+      <c r="AD9" s="446" t="n"/>
+      <c r="AE9" s="446" t="n"/>
+      <c r="AF9" s="446" t="n"/>
+      <c r="AG9" s="446" t="n"/>
+      <c r="AH9" s="446" t="n"/>
+      <c r="AI9" s="446" t="n"/>
+      <c r="AJ9" s="446" t="n"/>
+      <c r="AK9" s="446" t="n"/>
+      <c r="AL9" s="446" t="n"/>
+      <c r="AM9" s="446" t="n"/>
+      <c r="AN9" s="562" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="440" t="inlineStr">
+      <c r="A10" s="558" t="inlineStr">
         <is>
           <t>Evidence Folder</t>
         </is>
       </c>
-      <c r="B10" s="486" t="n"/>
-      <c r="C10" s="441" t="inlineStr"/>
-      <c r="D10" s="487" t="n"/>
-      <c r="E10" s="486" t="n"/>
-      <c r="F10" s="440" t="inlineStr">
+      <c r="B10" s="437" t="n"/>
+      <c r="C10" s="559" t="inlineStr"/>
+      <c r="D10" s="437" t="n"/>
+      <c r="E10" s="437" t="n"/>
+      <c r="F10" s="560" t="inlineStr">
         <is>
           <t>Returned Qty / Condition</t>
         </is>
       </c>
-      <c r="G10" s="486" t="n"/>
-      <c r="H10" s="441" t="inlineStr"/>
-      <c r="I10" s="487" t="n"/>
-      <c r="J10" s="486" t="n"/>
-      <c r="K10" s="447" t="n"/>
-      <c r="L10" s="447" t="n"/>
-      <c r="M10" s="447" t="n"/>
-      <c r="N10" s="447" t="n"/>
-      <c r="O10" s="447" t="n"/>
-      <c r="P10" s="447" t="n"/>
-      <c r="Q10" s="447" t="n"/>
-      <c r="R10" s="447" t="n"/>
-      <c r="S10" s="447" t="n"/>
-      <c r="T10" s="447" t="n"/>
-      <c r="U10" s="447" t="n"/>
-      <c r="V10" s="447" t="n"/>
-      <c r="W10" s="447" t="n"/>
-      <c r="X10" s="447" t="n"/>
-      <c r="Y10" s="447" t="n"/>
-      <c r="Z10" s="447" t="n"/>
-      <c r="AA10" s="447" t="n"/>
-      <c r="AB10" s="447" t="n"/>
-      <c r="AC10" s="447" t="n"/>
-      <c r="AD10" s="447" t="n"/>
-      <c r="AE10" s="447" t="n"/>
-      <c r="AF10" s="447" t="n"/>
-      <c r="AG10" s="447" t="n"/>
-      <c r="AH10" s="447" t="n"/>
-      <c r="AI10" s="447" t="n"/>
-      <c r="AJ10" s="447" t="n"/>
-      <c r="AK10" s="447" t="n"/>
-      <c r="AL10" s="447" t="n"/>
-      <c r="AM10" s="447" t="n"/>
-      <c r="AN10" s="447" t="n"/>
+      <c r="G10" s="437" t="n"/>
+      <c r="H10" s="559" t="inlineStr"/>
+      <c r="I10" s="437" t="n"/>
+      <c r="J10" s="437" t="n"/>
+      <c r="K10" s="561" t="n"/>
+      <c r="L10" s="446" t="n"/>
+      <c r="M10" s="446" t="n"/>
+      <c r="N10" s="446" t="n"/>
+      <c r="O10" s="446" t="n"/>
+      <c r="P10" s="446" t="n"/>
+      <c r="Q10" s="446" t="n"/>
+      <c r="R10" s="446" t="n"/>
+      <c r="S10" s="446" t="n"/>
+      <c r="T10" s="446" t="n"/>
+      <c r="U10" s="446" t="n"/>
+      <c r="V10" s="446" t="n"/>
+      <c r="W10" s="446" t="n"/>
+      <c r="X10" s="446" t="n"/>
+      <c r="Y10" s="446" t="n"/>
+      <c r="Z10" s="446" t="n"/>
+      <c r="AA10" s="446" t="n"/>
+      <c r="AB10" s="446" t="n"/>
+      <c r="AC10" s="446" t="n"/>
+      <c r="AD10" s="446" t="n"/>
+      <c r="AE10" s="446" t="n"/>
+      <c r="AF10" s="446" t="n"/>
+      <c r="AG10" s="446" t="n"/>
+      <c r="AH10" s="446" t="n"/>
+      <c r="AI10" s="446" t="n"/>
+      <c r="AJ10" s="446" t="n"/>
+      <c r="AK10" s="446" t="n"/>
+      <c r="AL10" s="446" t="n"/>
+      <c r="AM10" s="446" t="n"/>
+      <c r="AN10" s="562" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="440" t="inlineStr">
+      <c r="A11" s="558" t="inlineStr">
         <is>
           <t>Receipt Ref. / Date</t>
         </is>
       </c>
-      <c r="B11" s="485" t="n"/>
-      <c r="C11" s="441" t="inlineStr"/>
-      <c r="D11" s="484" t="n"/>
-      <c r="E11" s="485" t="n"/>
-      <c r="F11" s="440" t="inlineStr">
+      <c r="B11" s="437" t="n"/>
+      <c r="C11" s="559" t="inlineStr"/>
+      <c r="D11" s="437" t="n"/>
+      <c r="E11" s="437" t="n"/>
+      <c r="F11" s="560" t="inlineStr">
         <is>
           <t>Evaluation Owner</t>
         </is>
       </c>
-      <c r="G11" s="485" t="n"/>
-      <c r="H11" s="441" t="inlineStr"/>
-      <c r="I11" s="484" t="n"/>
-      <c r="J11" s="485" t="n"/>
-      <c r="K11" s="430" t="n"/>
-      <c r="L11" s="430" t="n"/>
-      <c r="M11" s="430" t="n"/>
-      <c r="N11" s="430" t="n"/>
-      <c r="O11" s="430" t="n"/>
-      <c r="P11" s="430" t="n"/>
-      <c r="Q11" s="430" t="n"/>
-      <c r="R11" s="430" t="n"/>
-      <c r="S11" s="430" t="n"/>
-      <c r="T11" s="430" t="n"/>
-      <c r="U11" s="430" t="n"/>
-      <c r="V11" s="430" t="n"/>
-      <c r="W11" s="430" t="n"/>
-      <c r="X11" s="430" t="n"/>
-      <c r="Y11" s="430" t="n"/>
-      <c r="Z11" s="430" t="n"/>
-      <c r="AA11" s="430" t="n"/>
-      <c r="AB11" s="430" t="n"/>
-      <c r="AC11" s="430" t="n"/>
-      <c r="AD11" s="430" t="n"/>
-      <c r="AE11" s="430" t="n"/>
-      <c r="AF11" s="430" t="n"/>
-      <c r="AG11" s="430" t="n"/>
-      <c r="AH11" s="430" t="n"/>
-      <c r="AI11" s="430" t="n"/>
-      <c r="AJ11" s="430" t="n"/>
-      <c r="AK11" s="430" t="n"/>
-      <c r="AL11" s="430" t="n"/>
-      <c r="AM11" s="430" t="n"/>
-      <c r="AN11" s="430" t="n"/>
+      <c r="G11" s="437" t="n"/>
+      <c r="H11" s="559" t="inlineStr"/>
+      <c r="I11" s="437" t="n"/>
+      <c r="J11" s="437" t="n"/>
+      <c r="K11" s="563" t="n"/>
+      <c r="L11" s="437" t="n"/>
+      <c r="M11" s="437" t="n"/>
+      <c r="N11" s="437" t="n"/>
+      <c r="O11" s="437" t="n"/>
+      <c r="P11" s="437" t="n"/>
+      <c r="Q11" s="437" t="n"/>
+      <c r="R11" s="437" t="n"/>
+      <c r="S11" s="437" t="n"/>
+      <c r="T11" s="437" t="n"/>
+      <c r="U11" s="437" t="n"/>
+      <c r="V11" s="437" t="n"/>
+      <c r="W11" s="437" t="n"/>
+      <c r="X11" s="437" t="n"/>
+      <c r="Y11" s="437" t="n"/>
+      <c r="Z11" s="437" t="n"/>
+      <c r="AA11" s="437" t="n"/>
+      <c r="AB11" s="437" t="n"/>
+      <c r="AC11" s="437" t="n"/>
+      <c r="AD11" s="437" t="n"/>
+      <c r="AE11" s="437" t="n"/>
+      <c r="AF11" s="437" t="n"/>
+      <c r="AG11" s="437" t="n"/>
+      <c r="AH11" s="437" t="n"/>
+      <c r="AI11" s="437" t="n"/>
+      <c r="AJ11" s="437" t="n"/>
+      <c r="AK11" s="437" t="n"/>
+      <c r="AL11" s="437" t="n"/>
+      <c r="AM11" s="437" t="n"/>
+      <c r="AN11" s="564" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="440" t="inlineStr">
+      <c r="A12" s="565" t="inlineStr">
         <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="B12" s="485" t="n"/>
-      <c r="C12" s="441" t="inlineStr"/>
-      <c r="D12" s="484" t="n"/>
-      <c r="E12" s="485" t="n"/>
-      <c r="F12" s="440" t="inlineStr">
+      <c r="B12" s="566" t="n"/>
+      <c r="C12" s="567" t="inlineStr"/>
+      <c r="D12" s="566" t="n"/>
+      <c r="E12" s="566" t="n"/>
+      <c r="F12" s="568" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="G12" s="485" t="n"/>
-      <c r="H12" s="441" t="inlineStr"/>
-      <c r="I12" s="484" t="n"/>
-      <c r="J12" s="485" t="n"/>
-      <c r="K12" s="430" t="n"/>
-      <c r="L12" s="430" t="n"/>
-      <c r="M12" s="430" t="n"/>
-      <c r="N12" s="430" t="n"/>
-      <c r="O12" s="430" t="n"/>
-      <c r="P12" s="430" t="n"/>
-      <c r="Q12" s="430" t="n"/>
-      <c r="R12" s="430" t="n"/>
-      <c r="S12" s="430" t="n"/>
-      <c r="T12" s="430" t="n"/>
-      <c r="U12" s="430" t="n"/>
-      <c r="V12" s="430" t="n"/>
-      <c r="W12" s="430" t="n"/>
-      <c r="X12" s="430" t="n"/>
-      <c r="Y12" s="430" t="n"/>
-      <c r="Z12" s="430" t="n"/>
-      <c r="AA12" s="430" t="n"/>
-      <c r="AB12" s="430" t="n"/>
-      <c r="AC12" s="430" t="n"/>
-      <c r="AD12" s="430" t="n"/>
-      <c r="AE12" s="430" t="n"/>
-      <c r="AF12" s="430" t="n"/>
-      <c r="AG12" s="430" t="n"/>
-      <c r="AH12" s="430" t="n"/>
-      <c r="AI12" s="430" t="n"/>
-      <c r="AJ12" s="430" t="n"/>
-      <c r="AK12" s="430" t="n"/>
-      <c r="AL12" s="430" t="n"/>
-      <c r="AM12" s="430" t="n"/>
-      <c r="AN12" s="430" t="n"/>
+      <c r="G12" s="566" t="n"/>
+      <c r="H12" s="567" t="inlineStr"/>
+      <c r="I12" s="566" t="n"/>
+      <c r="J12" s="566" t="n"/>
+      <c r="K12" s="569" t="n"/>
+      <c r="L12" s="566" t="n"/>
+      <c r="M12" s="566" t="n"/>
+      <c r="N12" s="566" t="n"/>
+      <c r="O12" s="566" t="n"/>
+      <c r="P12" s="566" t="n"/>
+      <c r="Q12" s="566" t="n"/>
+      <c r="R12" s="566" t="n"/>
+      <c r="S12" s="566" t="n"/>
+      <c r="T12" s="566" t="n"/>
+      <c r="U12" s="566" t="n"/>
+      <c r="V12" s="566" t="n"/>
+      <c r="W12" s="566" t="n"/>
+      <c r="X12" s="566" t="n"/>
+      <c r="Y12" s="566" t="n"/>
+      <c r="Z12" s="566" t="n"/>
+      <c r="AA12" s="566" t="n"/>
+      <c r="AB12" s="566" t="n"/>
+      <c r="AC12" s="566" t="n"/>
+      <c r="AD12" s="566" t="n"/>
+      <c r="AE12" s="566" t="n"/>
+      <c r="AF12" s="566" t="n"/>
+      <c r="AG12" s="566" t="n"/>
+      <c r="AH12" s="566" t="n"/>
+      <c r="AI12" s="566" t="n"/>
+      <c r="AJ12" s="566" t="n"/>
+      <c r="AK12" s="566" t="n"/>
+      <c r="AL12" s="566" t="n"/>
+      <c r="AM12" s="566" t="n"/>
+      <c r="AN12" s="570" t="n"/>
     </row>
-    <row r="13" ht="4" customHeight="1">
+    <row r="13" ht="3" customHeight="1">
       <c r="A13" s="442" t="n"/>
       <c r="B13" s="495" t="n"/>
       <c r="C13" s="495" t="n"/>
@@ -6272,253 +6999,253 @@
       <c r="AM13" s="443" t="n"/>
       <c r="AN13" s="443" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="444" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="548" t="inlineStr">
         <is>
           <t>2.  RECEIPT AND EVALUATION SECTION</t>
         </is>
       </c>
-      <c r="B14" s="487" t="n"/>
-      <c r="C14" s="487" t="n"/>
-      <c r="D14" s="487" t="n"/>
-      <c r="E14" s="487" t="n"/>
-      <c r="F14" s="487" t="n"/>
-      <c r="G14" s="487" t="n"/>
-      <c r="H14" s="487" t="n"/>
-      <c r="I14" s="487" t="n"/>
-      <c r="J14" s="486" t="n"/>
-      <c r="K14" s="447" t="n"/>
-      <c r="L14" s="447" t="n"/>
-      <c r="M14" s="447" t="n"/>
-      <c r="N14" s="447" t="n"/>
-      <c r="O14" s="447" t="n"/>
-      <c r="P14" s="447" t="n"/>
-      <c r="Q14" s="447" t="n"/>
-      <c r="R14" s="447" t="n"/>
-      <c r="S14" s="447" t="n"/>
-      <c r="T14" s="447" t="n"/>
-      <c r="U14" s="447" t="n"/>
-      <c r="V14" s="447" t="n"/>
-      <c r="W14" s="447" t="n"/>
-      <c r="X14" s="447" t="n"/>
-      <c r="Y14" s="447" t="n"/>
-      <c r="Z14" s="447" t="n"/>
-      <c r="AA14" s="447" t="n"/>
-      <c r="AB14" s="447" t="n"/>
-      <c r="AC14" s="447" t="n"/>
-      <c r="AD14" s="447" t="n"/>
-      <c r="AE14" s="447" t="n"/>
-      <c r="AF14" s="447" t="n"/>
-      <c r="AG14" s="447" t="n"/>
-      <c r="AH14" s="447" t="n"/>
-      <c r="AI14" s="447" t="n"/>
-      <c r="AJ14" s="447" t="n"/>
-      <c r="AK14" s="447" t="n"/>
-      <c r="AL14" s="447" t="n"/>
-      <c r="AM14" s="447" t="n"/>
-      <c r="AN14" s="447" t="n"/>
+      <c r="B14" s="549" t="n"/>
+      <c r="C14" s="549" t="n"/>
+      <c r="D14" s="549" t="n"/>
+      <c r="E14" s="549" t="n"/>
+      <c r="F14" s="549" t="n"/>
+      <c r="G14" s="549" t="n"/>
+      <c r="H14" s="549" t="n"/>
+      <c r="I14" s="549" t="n"/>
+      <c r="J14" s="549" t="n"/>
+      <c r="K14" s="549" t="n"/>
+      <c r="L14" s="549" t="n"/>
+      <c r="M14" s="549" t="n"/>
+      <c r="N14" s="549" t="n"/>
+      <c r="O14" s="549" t="n"/>
+      <c r="P14" s="549" t="n"/>
+      <c r="Q14" s="549" t="n"/>
+      <c r="R14" s="549" t="n"/>
+      <c r="S14" s="549" t="n"/>
+      <c r="T14" s="549" t="n"/>
+      <c r="U14" s="549" t="n"/>
+      <c r="V14" s="549" t="n"/>
+      <c r="W14" s="549" t="n"/>
+      <c r="X14" s="549" t="n"/>
+      <c r="Y14" s="549" t="n"/>
+      <c r="Z14" s="549" t="n"/>
+      <c r="AA14" s="549" t="n"/>
+      <c r="AB14" s="549" t="n"/>
+      <c r="AC14" s="549" t="n"/>
+      <c r="AD14" s="549" t="n"/>
+      <c r="AE14" s="549" t="n"/>
+      <c r="AF14" s="549" t="n"/>
+      <c r="AG14" s="549" t="n"/>
+      <c r="AH14" s="549" t="n"/>
+      <c r="AI14" s="549" t="n"/>
+      <c r="AJ14" s="549" t="n"/>
+      <c r="AK14" s="549" t="n"/>
+      <c r="AL14" s="549" t="n"/>
+      <c r="AM14" s="549" t="n"/>
+      <c r="AN14" s="550" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="440" t="inlineStr">
+      <c r="A15" s="551" t="inlineStr">
         <is>
           <t>Current Scope</t>
         </is>
       </c>
-      <c r="B15" s="486" t="n"/>
-      <c r="C15" s="441" t="inlineStr"/>
-      <c r="D15" s="487" t="n"/>
-      <c r="E15" s="486" t="n"/>
-      <c r="F15" s="440" t="inlineStr">
+      <c r="B15" s="552" t="n"/>
+      <c r="C15" s="553" t="inlineStr"/>
+      <c r="D15" s="552" t="n"/>
+      <c r="E15" s="552" t="n"/>
+      <c r="F15" s="554" t="inlineStr">
         <is>
           <t>Disposition Summary</t>
         </is>
       </c>
-      <c r="G15" s="486" t="n"/>
-      <c r="H15" s="441" t="inlineStr"/>
-      <c r="I15" s="487" t="n"/>
-      <c r="J15" s="486" t="n"/>
-      <c r="K15" s="447" t="n"/>
-      <c r="L15" s="447" t="n"/>
-      <c r="M15" s="447" t="n"/>
-      <c r="N15" s="447" t="n"/>
-      <c r="O15" s="447" t="n"/>
-      <c r="P15" s="447" t="n"/>
-      <c r="Q15" s="447" t="n"/>
-      <c r="R15" s="447" t="n"/>
-      <c r="S15" s="447" t="n"/>
-      <c r="T15" s="447" t="n"/>
-      <c r="U15" s="447" t="n"/>
-      <c r="V15" s="447" t="n"/>
-      <c r="W15" s="447" t="n"/>
-      <c r="X15" s="447" t="n"/>
-      <c r="Y15" s="447" t="n"/>
-      <c r="Z15" s="447" t="n"/>
-      <c r="AA15" s="447" t="n"/>
-      <c r="AB15" s="447" t="n"/>
-      <c r="AC15" s="447" t="n"/>
-      <c r="AD15" s="447" t="n"/>
-      <c r="AE15" s="447" t="n"/>
-      <c r="AF15" s="447" t="n"/>
-      <c r="AG15" s="447" t="n"/>
-      <c r="AH15" s="447" t="n"/>
-      <c r="AI15" s="447" t="n"/>
-      <c r="AJ15" s="447" t="n"/>
-      <c r="AK15" s="447" t="n"/>
-      <c r="AL15" s="447" t="n"/>
-      <c r="AM15" s="447" t="n"/>
-      <c r="AN15" s="447" t="n"/>
+      <c r="G15" s="552" t="n"/>
+      <c r="H15" s="553" t="inlineStr"/>
+      <c r="I15" s="552" t="n"/>
+      <c r="J15" s="552" t="n"/>
+      <c r="K15" s="555" t="n"/>
+      <c r="L15" s="556" t="n"/>
+      <c r="M15" s="556" t="n"/>
+      <c r="N15" s="556" t="n"/>
+      <c r="O15" s="556" t="n"/>
+      <c r="P15" s="556" t="n"/>
+      <c r="Q15" s="556" t="n"/>
+      <c r="R15" s="556" t="n"/>
+      <c r="S15" s="556" t="n"/>
+      <c r="T15" s="556" t="n"/>
+      <c r="U15" s="556" t="n"/>
+      <c r="V15" s="556" t="n"/>
+      <c r="W15" s="556" t="n"/>
+      <c r="X15" s="556" t="n"/>
+      <c r="Y15" s="556" t="n"/>
+      <c r="Z15" s="556" t="n"/>
+      <c r="AA15" s="556" t="n"/>
+      <c r="AB15" s="556" t="n"/>
+      <c r="AC15" s="556" t="n"/>
+      <c r="AD15" s="556" t="n"/>
+      <c r="AE15" s="556" t="n"/>
+      <c r="AF15" s="556" t="n"/>
+      <c r="AG15" s="556" t="n"/>
+      <c r="AH15" s="556" t="n"/>
+      <c r="AI15" s="556" t="n"/>
+      <c r="AJ15" s="556" t="n"/>
+      <c r="AK15" s="556" t="n"/>
+      <c r="AL15" s="556" t="n"/>
+      <c r="AM15" s="556" t="n"/>
+      <c r="AN15" s="557" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="440" t="inlineStr">
+      <c r="A16" s="558" t="inlineStr">
         <is>
           <t>Primary Return / Defect Note</t>
         </is>
       </c>
-      <c r="B16" s="486" t="n"/>
-      <c r="C16" s="441" t="inlineStr"/>
-      <c r="D16" s="487" t="n"/>
-      <c r="E16" s="486" t="n"/>
-      <c r="F16" s="440" t="inlineStr">
+      <c r="B16" s="437" t="n"/>
+      <c r="C16" s="559" t="inlineStr"/>
+      <c r="D16" s="437" t="n"/>
+      <c r="E16" s="437" t="n"/>
+      <c r="F16" s="560" t="inlineStr">
         <is>
           <t>Next Review</t>
         </is>
       </c>
-      <c r="G16" s="486" t="n"/>
-      <c r="H16" s="441" t="inlineStr"/>
-      <c r="I16" s="487" t="n"/>
-      <c r="J16" s="486" t="n"/>
-      <c r="K16" s="447" t="n"/>
-      <c r="L16" s="447" t="n"/>
-      <c r="M16" s="447" t="n"/>
-      <c r="N16" s="447" t="n"/>
-      <c r="O16" s="447" t="n"/>
-      <c r="P16" s="447" t="n"/>
-      <c r="Q16" s="447" t="n"/>
-      <c r="R16" s="447" t="n"/>
-      <c r="S16" s="447" t="n"/>
-      <c r="T16" s="447" t="n"/>
-      <c r="U16" s="447" t="n"/>
-      <c r="V16" s="447" t="n"/>
-      <c r="W16" s="447" t="n"/>
-      <c r="X16" s="447" t="n"/>
-      <c r="Y16" s="447" t="n"/>
-      <c r="Z16" s="447" t="n"/>
-      <c r="AA16" s="447" t="n"/>
-      <c r="AB16" s="447" t="n"/>
-      <c r="AC16" s="447" t="n"/>
-      <c r="AD16" s="447" t="n"/>
-      <c r="AE16" s="447" t="n"/>
-      <c r="AF16" s="447" t="n"/>
-      <c r="AG16" s="447" t="n"/>
-      <c r="AH16" s="447" t="n"/>
-      <c r="AI16" s="447" t="n"/>
-      <c r="AJ16" s="447" t="n"/>
-      <c r="AK16" s="447" t="n"/>
-      <c r="AL16" s="447" t="n"/>
-      <c r="AM16" s="447" t="n"/>
-      <c r="AN16" s="447" t="n"/>
+      <c r="G16" s="437" t="n"/>
+      <c r="H16" s="559" t="inlineStr"/>
+      <c r="I16" s="437" t="n"/>
+      <c r="J16" s="437" t="n"/>
+      <c r="K16" s="561" t="n"/>
+      <c r="L16" s="446" t="n"/>
+      <c r="M16" s="446" t="n"/>
+      <c r="N16" s="446" t="n"/>
+      <c r="O16" s="446" t="n"/>
+      <c r="P16" s="446" t="n"/>
+      <c r="Q16" s="446" t="n"/>
+      <c r="R16" s="446" t="n"/>
+      <c r="S16" s="446" t="n"/>
+      <c r="T16" s="446" t="n"/>
+      <c r="U16" s="446" t="n"/>
+      <c r="V16" s="446" t="n"/>
+      <c r="W16" s="446" t="n"/>
+      <c r="X16" s="446" t="n"/>
+      <c r="Y16" s="446" t="n"/>
+      <c r="Z16" s="446" t="n"/>
+      <c r="AA16" s="446" t="n"/>
+      <c r="AB16" s="446" t="n"/>
+      <c r="AC16" s="446" t="n"/>
+      <c r="AD16" s="446" t="n"/>
+      <c r="AE16" s="446" t="n"/>
+      <c r="AF16" s="446" t="n"/>
+      <c r="AG16" s="446" t="n"/>
+      <c r="AH16" s="446" t="n"/>
+      <c r="AI16" s="446" t="n"/>
+      <c r="AJ16" s="446" t="n"/>
+      <c r="AK16" s="446" t="n"/>
+      <c r="AL16" s="446" t="n"/>
+      <c r="AM16" s="446" t="n"/>
+      <c r="AN16" s="562" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="440" t="inlineStr">
+      <c r="A17" s="558" t="inlineStr">
         <is>
           <t>Action Owner</t>
         </is>
       </c>
-      <c r="B17" s="486" t="n"/>
-      <c r="C17" s="441" t="inlineStr"/>
-      <c r="D17" s="487" t="n"/>
-      <c r="E17" s="486" t="n"/>
-      <c r="F17" s="440" t="inlineStr">
+      <c r="B17" s="437" t="n"/>
+      <c r="C17" s="559" t="inlineStr"/>
+      <c r="D17" s="437" t="n"/>
+      <c r="E17" s="437" t="n"/>
+      <c r="F17" s="560" t="inlineStr">
         <is>
           <t>Next Review Date</t>
         </is>
       </c>
-      <c r="G17" s="486" t="n"/>
-      <c r="H17" s="441" t="inlineStr"/>
-      <c r="I17" s="487" t="n"/>
-      <c r="J17" s="486" t="n"/>
-      <c r="K17" s="447" t="n"/>
-      <c r="L17" s="447" t="n"/>
-      <c r="M17" s="447" t="n"/>
-      <c r="N17" s="447" t="n"/>
-      <c r="O17" s="447" t="n"/>
-      <c r="P17" s="447" t="n"/>
-      <c r="Q17" s="447" t="n"/>
-      <c r="R17" s="447" t="n"/>
-      <c r="S17" s="447" t="n"/>
-      <c r="T17" s="447" t="n"/>
-      <c r="U17" s="447" t="n"/>
-      <c r="V17" s="447" t="n"/>
-      <c r="W17" s="447" t="n"/>
-      <c r="X17" s="447" t="n"/>
-      <c r="Y17" s="447" t="n"/>
-      <c r="Z17" s="447" t="n"/>
-      <c r="AA17" s="447" t="n"/>
-      <c r="AB17" s="447" t="n"/>
-      <c r="AC17" s="447" t="n"/>
-      <c r="AD17" s="447" t="n"/>
-      <c r="AE17" s="447" t="n"/>
-      <c r="AF17" s="447" t="n"/>
-      <c r="AG17" s="447" t="n"/>
-      <c r="AH17" s="447" t="n"/>
-      <c r="AI17" s="447" t="n"/>
-      <c r="AJ17" s="447" t="n"/>
-      <c r="AK17" s="447" t="n"/>
-      <c r="AL17" s="447" t="n"/>
-      <c r="AM17" s="447" t="n"/>
-      <c r="AN17" s="447" t="n"/>
+      <c r="G17" s="437" t="n"/>
+      <c r="H17" s="559" t="inlineStr"/>
+      <c r="I17" s="437" t="n"/>
+      <c r="J17" s="437" t="n"/>
+      <c r="K17" s="561" t="n"/>
+      <c r="L17" s="446" t="n"/>
+      <c r="M17" s="446" t="n"/>
+      <c r="N17" s="446" t="n"/>
+      <c r="O17" s="446" t="n"/>
+      <c r="P17" s="446" t="n"/>
+      <c r="Q17" s="446" t="n"/>
+      <c r="R17" s="446" t="n"/>
+      <c r="S17" s="446" t="n"/>
+      <c r="T17" s="446" t="n"/>
+      <c r="U17" s="446" t="n"/>
+      <c r="V17" s="446" t="n"/>
+      <c r="W17" s="446" t="n"/>
+      <c r="X17" s="446" t="n"/>
+      <c r="Y17" s="446" t="n"/>
+      <c r="Z17" s="446" t="n"/>
+      <c r="AA17" s="446" t="n"/>
+      <c r="AB17" s="446" t="n"/>
+      <c r="AC17" s="446" t="n"/>
+      <c r="AD17" s="446" t="n"/>
+      <c r="AE17" s="446" t="n"/>
+      <c r="AF17" s="446" t="n"/>
+      <c r="AG17" s="446" t="n"/>
+      <c r="AH17" s="446" t="n"/>
+      <c r="AI17" s="446" t="n"/>
+      <c r="AJ17" s="446" t="n"/>
+      <c r="AK17" s="446" t="n"/>
+      <c r="AL17" s="446" t="n"/>
+      <c r="AM17" s="446" t="n"/>
+      <c r="AN17" s="562" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="440" t="inlineStr">
+      <c r="A18" s="565" t="inlineStr">
         <is>
           <t>Escalation if Not Disposed</t>
         </is>
       </c>
-      <c r="B18" s="486" t="n"/>
-      <c r="C18" s="441" t="inlineStr"/>
-      <c r="D18" s="487" t="n"/>
-      <c r="E18" s="486" t="n"/>
-      <c r="F18" s="440" t="inlineStr">
+      <c r="B18" s="566" t="n"/>
+      <c r="C18" s="567" t="inlineStr"/>
+      <c r="D18" s="566" t="n"/>
+      <c r="E18" s="566" t="n"/>
+      <c r="F18" s="568" t="inlineStr">
         <is>
           <t>Overall Status</t>
         </is>
       </c>
-      <c r="G18" s="486" t="n"/>
-      <c r="H18" s="441" t="inlineStr"/>
-      <c r="I18" s="487" t="n"/>
-      <c r="J18" s="486" t="n"/>
-      <c r="K18" s="447" t="n"/>
-      <c r="L18" s="447" t="n"/>
-      <c r="M18" s="447" t="n"/>
-      <c r="N18" s="447" t="n"/>
-      <c r="O18" s="447" t="n"/>
-      <c r="P18" s="447" t="n"/>
-      <c r="Q18" s="447" t="n"/>
-      <c r="R18" s="447" t="n"/>
-      <c r="S18" s="447" t="n"/>
-      <c r="T18" s="447" t="n"/>
-      <c r="U18" s="447" t="n"/>
-      <c r="V18" s="447" t="n"/>
-      <c r="W18" s="447" t="n"/>
-      <c r="X18" s="447" t="n"/>
-      <c r="Y18" s="447" t="n"/>
-      <c r="Z18" s="447" t="n"/>
-      <c r="AA18" s="447" t="n"/>
-      <c r="AB18" s="447" t="n"/>
-      <c r="AC18" s="447" t="n"/>
-      <c r="AD18" s="447" t="n"/>
-      <c r="AE18" s="447" t="n"/>
-      <c r="AF18" s="447" t="n"/>
-      <c r="AG18" s="447" t="n"/>
-      <c r="AH18" s="447" t="n"/>
-      <c r="AI18" s="447" t="n"/>
-      <c r="AJ18" s="447" t="n"/>
-      <c r="AK18" s="447" t="n"/>
-      <c r="AL18" s="447" t="n"/>
-      <c r="AM18" s="447" t="n"/>
-      <c r="AN18" s="447" t="n"/>
+      <c r="G18" s="566" t="n"/>
+      <c r="H18" s="567" t="inlineStr"/>
+      <c r="I18" s="566" t="n"/>
+      <c r="J18" s="566" t="n"/>
+      <c r="K18" s="571" t="n"/>
+      <c r="L18" s="572" t="n"/>
+      <c r="M18" s="572" t="n"/>
+      <c r="N18" s="572" t="n"/>
+      <c r="O18" s="572" t="n"/>
+      <c r="P18" s="572" t="n"/>
+      <c r="Q18" s="572" t="n"/>
+      <c r="R18" s="572" t="n"/>
+      <c r="S18" s="572" t="n"/>
+      <c r="T18" s="572" t="n"/>
+      <c r="U18" s="572" t="n"/>
+      <c r="V18" s="572" t="n"/>
+      <c r="W18" s="572" t="n"/>
+      <c r="X18" s="572" t="n"/>
+      <c r="Y18" s="572" t="n"/>
+      <c r="Z18" s="572" t="n"/>
+      <c r="AA18" s="572" t="n"/>
+      <c r="AB18" s="572" t="n"/>
+      <c r="AC18" s="572" t="n"/>
+      <c r="AD18" s="572" t="n"/>
+      <c r="AE18" s="572" t="n"/>
+      <c r="AF18" s="572" t="n"/>
+      <c r="AG18" s="572" t="n"/>
+      <c r="AH18" s="572" t="n"/>
+      <c r="AI18" s="572" t="n"/>
+      <c r="AJ18" s="572" t="n"/>
+      <c r="AK18" s="572" t="n"/>
+      <c r="AL18" s="572" t="n"/>
+      <c r="AM18" s="572" t="n"/>
+      <c r="AN18" s="573" t="n"/>
     </row>
-    <row r="19" ht="4" customHeight="1">
+    <row r="19" ht="3" customHeight="1">
       <c r="A19" s="442" t="n"/>
       <c r="B19" s="495" t="n"/>
       <c r="C19" s="495" t="n"/>
@@ -6560,945 +7287,945 @@
       <c r="AM19" s="443" t="n"/>
       <c r="AN19" s="443" t="n"/>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="444" t="inlineStr">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="548" t="inlineStr">
         <is>
           <t>3.  DISPOSITION SECTION</t>
         </is>
       </c>
-      <c r="B20" s="487" t="n"/>
-      <c r="C20" s="487" t="n"/>
-      <c r="D20" s="487" t="n"/>
-      <c r="E20" s="487" t="n"/>
-      <c r="F20" s="487" t="n"/>
-      <c r="G20" s="487" t="n"/>
-      <c r="H20" s="487" t="n"/>
-      <c r="I20" s="487" t="n"/>
-      <c r="J20" s="486" t="n"/>
-      <c r="K20" s="447" t="n"/>
-      <c r="L20" s="447" t="n"/>
-      <c r="M20" s="447" t="n"/>
-      <c r="N20" s="447" t="n"/>
-      <c r="O20" s="447" t="n"/>
-      <c r="P20" s="447" t="n"/>
-      <c r="Q20" s="447" t="n"/>
-      <c r="R20" s="447" t="n"/>
-      <c r="S20" s="447" t="n"/>
-      <c r="T20" s="447" t="n"/>
-      <c r="U20" s="447" t="n"/>
-      <c r="V20" s="447" t="n"/>
-      <c r="W20" s="447" t="n"/>
-      <c r="X20" s="447" t="n"/>
-      <c r="Y20" s="447" t="n"/>
-      <c r="Z20" s="447" t="n"/>
-      <c r="AA20" s="447" t="n"/>
-      <c r="AB20" s="447" t="n"/>
-      <c r="AC20" s="447" t="n"/>
-      <c r="AD20" s="447" t="n"/>
-      <c r="AE20" s="447" t="n"/>
-      <c r="AF20" s="447" t="n"/>
-      <c r="AG20" s="447" t="n"/>
-      <c r="AH20" s="447" t="n"/>
-      <c r="AI20" s="447" t="n"/>
-      <c r="AJ20" s="447" t="n"/>
-      <c r="AK20" s="447" t="n"/>
-      <c r="AL20" s="447" t="n"/>
-      <c r="AM20" s="447" t="n"/>
-      <c r="AN20" s="447" t="n"/>
+      <c r="B20" s="549" t="n"/>
+      <c r="C20" s="549" t="n"/>
+      <c r="D20" s="549" t="n"/>
+      <c r="E20" s="549" t="n"/>
+      <c r="F20" s="549" t="n"/>
+      <c r="G20" s="549" t="n"/>
+      <c r="H20" s="549" t="n"/>
+      <c r="I20" s="549" t="n"/>
+      <c r="J20" s="549" t="n"/>
+      <c r="K20" s="549" t="n"/>
+      <c r="L20" s="549" t="n"/>
+      <c r="M20" s="549" t="n"/>
+      <c r="N20" s="549" t="n"/>
+      <c r="O20" s="549" t="n"/>
+      <c r="P20" s="549" t="n"/>
+      <c r="Q20" s="549" t="n"/>
+      <c r="R20" s="549" t="n"/>
+      <c r="S20" s="549" t="n"/>
+      <c r="T20" s="549" t="n"/>
+      <c r="U20" s="549" t="n"/>
+      <c r="V20" s="549" t="n"/>
+      <c r="W20" s="549" t="n"/>
+      <c r="X20" s="549" t="n"/>
+      <c r="Y20" s="549" t="n"/>
+      <c r="Z20" s="549" t="n"/>
+      <c r="AA20" s="549" t="n"/>
+      <c r="AB20" s="549" t="n"/>
+      <c r="AC20" s="549" t="n"/>
+      <c r="AD20" s="549" t="n"/>
+      <c r="AE20" s="549" t="n"/>
+      <c r="AF20" s="549" t="n"/>
+      <c r="AG20" s="549" t="n"/>
+      <c r="AH20" s="549" t="n"/>
+      <c r="AI20" s="549" t="n"/>
+      <c r="AJ20" s="549" t="n"/>
+      <c r="AK20" s="549" t="n"/>
+      <c r="AL20" s="549" t="n"/>
+      <c r="AM20" s="549" t="n"/>
+      <c r="AN20" s="550" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="448" t="inlineStr">
+      <c r="A21" s="574" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B21" s="448" t="inlineStr">
+      <c r="B21" s="575" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="C21" s="448" t="inlineStr">
+      <c r="C21" s="575" t="inlineStr">
         <is>
           <t>RMA ID</t>
         </is>
       </c>
-      <c r="D21" s="448" t="inlineStr">
+      <c r="D21" s="575" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="E21" s="448" t="inlineStr">
+      <c r="E21" s="575" t="inlineStr">
         <is>
           <t>Part / Revision</t>
         </is>
       </c>
-      <c r="F21" s="448" t="inlineStr">
+      <c r="F21" s="575" t="inlineStr">
         <is>
           <t>Qty / Condition</t>
         </is>
       </c>
-      <c r="G21" s="448" t="inlineStr">
+      <c r="G21" s="575" t="inlineStr">
         <is>
           <t>Disposition</t>
         </is>
       </c>
-      <c r="H21" s="448" t="inlineStr">
+      <c r="H21" s="575" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="I21" s="448" t="inlineStr">
+      <c r="I21" s="575" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J21" s="449" t="inlineStr">
+      <c r="J21" s="575" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="K21" s="447" t="n"/>
-      <c r="L21" s="447" t="n"/>
-      <c r="M21" s="447" t="n"/>
-      <c r="N21" s="447" t="n"/>
-      <c r="O21" s="447" t="n"/>
-      <c r="P21" s="447" t="n"/>
-      <c r="Q21" s="447" t="n"/>
-      <c r="R21" s="447" t="n"/>
-      <c r="S21" s="447" t="n"/>
-      <c r="T21" s="447" t="n"/>
-      <c r="U21" s="447" t="n"/>
-      <c r="V21" s="447" t="n"/>
-      <c r="W21" s="447" t="n"/>
-      <c r="X21" s="447" t="n"/>
-      <c r="Y21" s="447" t="n"/>
-      <c r="Z21" s="447" t="n"/>
-      <c r="AA21" s="447" t="n"/>
-      <c r="AB21" s="447" t="n"/>
-      <c r="AC21" s="447" t="n"/>
-      <c r="AD21" s="447" t="n"/>
-      <c r="AE21" s="447" t="n"/>
-      <c r="AF21" s="447" t="n"/>
-      <c r="AG21" s="447" t="n"/>
-      <c r="AH21" s="447" t="n"/>
-      <c r="AI21" s="447" t="n"/>
-      <c r="AJ21" s="447" t="n"/>
-      <c r="AK21" s="447" t="n"/>
-      <c r="AL21" s="447" t="n"/>
-      <c r="AM21" s="447" t="n"/>
-      <c r="AN21" s="447" t="n"/>
+      <c r="K21" s="575" t="n"/>
+      <c r="L21" s="575" t="n"/>
+      <c r="M21" s="575" t="n"/>
+      <c r="N21" s="575" t="n"/>
+      <c r="O21" s="575" t="n"/>
+      <c r="P21" s="575" t="n"/>
+      <c r="Q21" s="575" t="n"/>
+      <c r="R21" s="575" t="n"/>
+      <c r="S21" s="575" t="n"/>
+      <c r="T21" s="575" t="n"/>
+      <c r="U21" s="575" t="n"/>
+      <c r="V21" s="575" t="n"/>
+      <c r="W21" s="575" t="n"/>
+      <c r="X21" s="575" t="n"/>
+      <c r="Y21" s="575" t="n"/>
+      <c r="Z21" s="575" t="n"/>
+      <c r="AA21" s="575" t="n"/>
+      <c r="AB21" s="575" t="n"/>
+      <c r="AC21" s="575" t="n"/>
+      <c r="AD21" s="575" t="n"/>
+      <c r="AE21" s="575" t="n"/>
+      <c r="AF21" s="575" t="n"/>
+      <c r="AG21" s="575" t="n"/>
+      <c r="AH21" s="575" t="n"/>
+      <c r="AI21" s="575" t="n"/>
+      <c r="AJ21" s="575" t="n"/>
+      <c r="AK21" s="575" t="n"/>
+      <c r="AL21" s="575" t="n"/>
+      <c r="AM21" s="575" t="n"/>
+      <c r="AN21" s="576" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="450">
+      <c r="A22" s="577">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B22" s="451" t="n"/>
-      <c r="C22" s="452" t="n"/>
-      <c r="D22" s="452" t="n"/>
-      <c r="E22" s="452" t="n"/>
-      <c r="F22" s="452" t="n"/>
-      <c r="G22" s="452" t="n"/>
-      <c r="H22" s="452" t="n"/>
-      <c r="I22" s="452" t="n"/>
-      <c r="J22" s="429" t="n"/>
-      <c r="K22" s="447" t="n"/>
-      <c r="L22" s="447" t="n"/>
-      <c r="M22" s="447" t="n"/>
-      <c r="N22" s="447" t="n"/>
-      <c r="O22" s="447" t="n"/>
-      <c r="P22" s="447" t="n"/>
-      <c r="Q22" s="447" t="n"/>
-      <c r="R22" s="447" t="n"/>
-      <c r="S22" s="447" t="n"/>
-      <c r="T22" s="447" t="n"/>
-      <c r="U22" s="447" t="n"/>
-      <c r="V22" s="447" t="n"/>
-      <c r="W22" s="447" t="n"/>
-      <c r="X22" s="447" t="n"/>
-      <c r="Y22" s="447" t="n"/>
-      <c r="Z22" s="447" t="n"/>
-      <c r="AA22" s="447" t="n"/>
-      <c r="AB22" s="447" t="n"/>
-      <c r="AC22" s="447" t="n"/>
-      <c r="AD22" s="447" t="n"/>
-      <c r="AE22" s="447" t="n"/>
-      <c r="AF22" s="447" t="n"/>
-      <c r="AG22" s="447" t="n"/>
-      <c r="AH22" s="447" t="n"/>
-      <c r="AI22" s="447" t="n"/>
-      <c r="AJ22" s="447" t="n"/>
-      <c r="AK22" s="447" t="n"/>
-      <c r="AL22" s="447" t="n"/>
-      <c r="AM22" s="447" t="n"/>
-      <c r="AN22" s="447" t="n"/>
+      <c r="B22" s="578" t="n"/>
+      <c r="C22" s="579" t="n"/>
+      <c r="D22" s="579" t="n"/>
+      <c r="E22" s="579" t="n"/>
+      <c r="F22" s="579" t="n"/>
+      <c r="G22" s="579" t="n"/>
+      <c r="H22" s="579" t="n"/>
+      <c r="I22" s="579" t="n"/>
+      <c r="J22" s="579" t="n"/>
+      <c r="K22" s="556" t="n"/>
+      <c r="L22" s="556" t="n"/>
+      <c r="M22" s="556" t="n"/>
+      <c r="N22" s="556" t="n"/>
+      <c r="O22" s="556" t="n"/>
+      <c r="P22" s="556" t="n"/>
+      <c r="Q22" s="556" t="n"/>
+      <c r="R22" s="556" t="n"/>
+      <c r="S22" s="556" t="n"/>
+      <c r="T22" s="556" t="n"/>
+      <c r="U22" s="556" t="n"/>
+      <c r="V22" s="556" t="n"/>
+      <c r="W22" s="556" t="n"/>
+      <c r="X22" s="556" t="n"/>
+      <c r="Y22" s="556" t="n"/>
+      <c r="Z22" s="556" t="n"/>
+      <c r="AA22" s="556" t="n"/>
+      <c r="AB22" s="556" t="n"/>
+      <c r="AC22" s="556" t="n"/>
+      <c r="AD22" s="556" t="n"/>
+      <c r="AE22" s="556" t="n"/>
+      <c r="AF22" s="556" t="n"/>
+      <c r="AG22" s="556" t="n"/>
+      <c r="AH22" s="556" t="n"/>
+      <c r="AI22" s="556" t="n"/>
+      <c r="AJ22" s="556" t="n"/>
+      <c r="AK22" s="556" t="n"/>
+      <c r="AL22" s="556" t="n"/>
+      <c r="AM22" s="556" t="n"/>
+      <c r="AN22" s="557" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="450">
+      <c r="A23" s="580">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B23" s="453" t="n"/>
-      <c r="C23" s="454" t="n"/>
-      <c r="D23" s="454" t="n"/>
-      <c r="E23" s="454" t="n"/>
-      <c r="F23" s="454" t="n"/>
-      <c r="G23" s="454" t="n"/>
-      <c r="H23" s="454" t="n"/>
-      <c r="I23" s="454" t="n"/>
-      <c r="J23" s="455" t="n"/>
-      <c r="K23" s="447" t="n"/>
-      <c r="L23" s="447" t="n"/>
-      <c r="M23" s="447" t="n"/>
-      <c r="N23" s="447" t="n"/>
-      <c r="O23" s="447" t="n"/>
-      <c r="P23" s="447" t="n"/>
-      <c r="Q23" s="447" t="n"/>
-      <c r="R23" s="447" t="n"/>
-      <c r="S23" s="447" t="n"/>
-      <c r="T23" s="447" t="n"/>
-      <c r="U23" s="447" t="n"/>
-      <c r="V23" s="447" t="n"/>
-      <c r="W23" s="447" t="n"/>
-      <c r="X23" s="447" t="n"/>
-      <c r="Y23" s="447" t="n"/>
-      <c r="Z23" s="447" t="n"/>
-      <c r="AA23" s="447" t="n"/>
-      <c r="AB23" s="447" t="n"/>
-      <c r="AC23" s="447" t="n"/>
-      <c r="AD23" s="447" t="n"/>
-      <c r="AE23" s="447" t="n"/>
-      <c r="AF23" s="447" t="n"/>
-      <c r="AG23" s="447" t="n"/>
-      <c r="AH23" s="447" t="n"/>
-      <c r="AI23" s="447" t="n"/>
-      <c r="AJ23" s="447" t="n"/>
-      <c r="AK23" s="447" t="n"/>
-      <c r="AL23" s="447" t="n"/>
-      <c r="AM23" s="447" t="n"/>
-      <c r="AN23" s="447" t="n"/>
+      <c r="B23" s="457" t="n"/>
+      <c r="C23" s="581" t="n"/>
+      <c r="D23" s="581" t="n"/>
+      <c r="E23" s="581" t="n"/>
+      <c r="F23" s="581" t="n"/>
+      <c r="G23" s="581" t="n"/>
+      <c r="H23" s="581" t="n"/>
+      <c r="I23" s="581" t="n"/>
+      <c r="J23" s="581" t="n"/>
+      <c r="K23" s="446" t="n"/>
+      <c r="L23" s="446" t="n"/>
+      <c r="M23" s="446" t="n"/>
+      <c r="N23" s="446" t="n"/>
+      <c r="O23" s="446" t="n"/>
+      <c r="P23" s="446" t="n"/>
+      <c r="Q23" s="446" t="n"/>
+      <c r="R23" s="446" t="n"/>
+      <c r="S23" s="446" t="n"/>
+      <c r="T23" s="446" t="n"/>
+      <c r="U23" s="446" t="n"/>
+      <c r="V23" s="446" t="n"/>
+      <c r="W23" s="446" t="n"/>
+      <c r="X23" s="446" t="n"/>
+      <c r="Y23" s="446" t="n"/>
+      <c r="Z23" s="446" t="n"/>
+      <c r="AA23" s="446" t="n"/>
+      <c r="AB23" s="446" t="n"/>
+      <c r="AC23" s="446" t="n"/>
+      <c r="AD23" s="446" t="n"/>
+      <c r="AE23" s="446" t="n"/>
+      <c r="AF23" s="446" t="n"/>
+      <c r="AG23" s="446" t="n"/>
+      <c r="AH23" s="446" t="n"/>
+      <c r="AI23" s="446" t="n"/>
+      <c r="AJ23" s="446" t="n"/>
+      <c r="AK23" s="446" t="n"/>
+      <c r="AL23" s="446" t="n"/>
+      <c r="AM23" s="446" t="n"/>
+      <c r="AN23" s="562" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="450">
+      <c r="A24" s="580">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B24" s="451" t="n"/>
-      <c r="C24" s="452" t="n"/>
-      <c r="D24" s="452" t="n"/>
-      <c r="E24" s="452" t="n"/>
-      <c r="F24" s="452" t="n"/>
-      <c r="G24" s="452" t="n"/>
-      <c r="H24" s="452" t="n"/>
-      <c r="I24" s="452" t="n"/>
-      <c r="J24" s="429" t="n"/>
-      <c r="K24" s="447" t="n"/>
-      <c r="L24" s="447" t="n"/>
-      <c r="M24" s="447" t="n"/>
-      <c r="N24" s="447" t="n"/>
-      <c r="O24" s="447" t="n"/>
-      <c r="P24" s="447" t="n"/>
-      <c r="Q24" s="447" t="n"/>
-      <c r="R24" s="447" t="n"/>
-      <c r="S24" s="447" t="n"/>
-      <c r="T24" s="447" t="n"/>
-      <c r="U24" s="447" t="n"/>
-      <c r="V24" s="447" t="n"/>
-      <c r="W24" s="447" t="n"/>
-      <c r="X24" s="447" t="n"/>
-      <c r="Y24" s="447" t="n"/>
-      <c r="Z24" s="447" t="n"/>
-      <c r="AA24" s="447" t="n"/>
-      <c r="AB24" s="447" t="n"/>
-      <c r="AC24" s="447" t="n"/>
-      <c r="AD24" s="447" t="n"/>
-      <c r="AE24" s="447" t="n"/>
-      <c r="AF24" s="447" t="n"/>
-      <c r="AG24" s="447" t="n"/>
-      <c r="AH24" s="447" t="n"/>
-      <c r="AI24" s="447" t="n"/>
-      <c r="AJ24" s="447" t="n"/>
-      <c r="AK24" s="447" t="n"/>
-      <c r="AL24" s="447" t="n"/>
-      <c r="AM24" s="447" t="n"/>
-      <c r="AN24" s="447" t="n"/>
+      <c r="B24" s="582" t="n"/>
+      <c r="C24" s="583" t="n"/>
+      <c r="D24" s="583" t="n"/>
+      <c r="E24" s="583" t="n"/>
+      <c r="F24" s="583" t="n"/>
+      <c r="G24" s="583" t="n"/>
+      <c r="H24" s="583" t="n"/>
+      <c r="I24" s="583" t="n"/>
+      <c r="J24" s="583" t="n"/>
+      <c r="K24" s="446" t="n"/>
+      <c r="L24" s="446" t="n"/>
+      <c r="M24" s="446" t="n"/>
+      <c r="N24" s="446" t="n"/>
+      <c r="O24" s="446" t="n"/>
+      <c r="P24" s="446" t="n"/>
+      <c r="Q24" s="446" t="n"/>
+      <c r="R24" s="446" t="n"/>
+      <c r="S24" s="446" t="n"/>
+      <c r="T24" s="446" t="n"/>
+      <c r="U24" s="446" t="n"/>
+      <c r="V24" s="446" t="n"/>
+      <c r="W24" s="446" t="n"/>
+      <c r="X24" s="446" t="n"/>
+      <c r="Y24" s="446" t="n"/>
+      <c r="Z24" s="446" t="n"/>
+      <c r="AA24" s="446" t="n"/>
+      <c r="AB24" s="446" t="n"/>
+      <c r="AC24" s="446" t="n"/>
+      <c r="AD24" s="446" t="n"/>
+      <c r="AE24" s="446" t="n"/>
+      <c r="AF24" s="446" t="n"/>
+      <c r="AG24" s="446" t="n"/>
+      <c r="AH24" s="446" t="n"/>
+      <c r="AI24" s="446" t="n"/>
+      <c r="AJ24" s="446" t="n"/>
+      <c r="AK24" s="446" t="n"/>
+      <c r="AL24" s="446" t="n"/>
+      <c r="AM24" s="446" t="n"/>
+      <c r="AN24" s="562" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="450">
+      <c r="A25" s="580">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B25" s="453" t="n"/>
-      <c r="C25" s="454" t="n"/>
-      <c r="D25" s="454" t="n"/>
-      <c r="E25" s="454" t="n"/>
-      <c r="F25" s="454" t="n"/>
-      <c r="G25" s="454" t="n"/>
-      <c r="H25" s="454" t="n"/>
-      <c r="I25" s="454" t="n"/>
-      <c r="J25" s="455" t="n"/>
-      <c r="K25" s="447" t="n"/>
-      <c r="L25" s="447" t="n"/>
-      <c r="M25" s="447" t="n"/>
-      <c r="N25" s="447" t="n"/>
-      <c r="O25" s="447" t="n"/>
-      <c r="P25" s="447" t="n"/>
-      <c r="Q25" s="447" t="n"/>
-      <c r="R25" s="447" t="n"/>
-      <c r="S25" s="447" t="n"/>
-      <c r="T25" s="447" t="n"/>
-      <c r="U25" s="447" t="n"/>
-      <c r="V25" s="447" t="n"/>
-      <c r="W25" s="447" t="n"/>
-      <c r="X25" s="447" t="n"/>
-      <c r="Y25" s="447" t="n"/>
-      <c r="Z25" s="447" t="n"/>
-      <c r="AA25" s="447" t="n"/>
-      <c r="AB25" s="447" t="n"/>
-      <c r="AC25" s="447" t="n"/>
-      <c r="AD25" s="447" t="n"/>
-      <c r="AE25" s="447" t="n"/>
-      <c r="AF25" s="447" t="n"/>
-      <c r="AG25" s="447" t="n"/>
-      <c r="AH25" s="447" t="n"/>
-      <c r="AI25" s="447" t="n"/>
-      <c r="AJ25" s="447" t="n"/>
-      <c r="AK25" s="447" t="n"/>
-      <c r="AL25" s="447" t="n"/>
-      <c r="AM25" s="447" t="n"/>
-      <c r="AN25" s="447" t="n"/>
+      <c r="B25" s="457" t="n"/>
+      <c r="C25" s="581" t="n"/>
+      <c r="D25" s="581" t="n"/>
+      <c r="E25" s="581" t="n"/>
+      <c r="F25" s="581" t="n"/>
+      <c r="G25" s="581" t="n"/>
+      <c r="H25" s="581" t="n"/>
+      <c r="I25" s="581" t="n"/>
+      <c r="J25" s="581" t="n"/>
+      <c r="K25" s="446" t="n"/>
+      <c r="L25" s="446" t="n"/>
+      <c r="M25" s="446" t="n"/>
+      <c r="N25" s="446" t="n"/>
+      <c r="O25" s="446" t="n"/>
+      <c r="P25" s="446" t="n"/>
+      <c r="Q25" s="446" t="n"/>
+      <c r="R25" s="446" t="n"/>
+      <c r="S25" s="446" t="n"/>
+      <c r="T25" s="446" t="n"/>
+      <c r="U25" s="446" t="n"/>
+      <c r="V25" s="446" t="n"/>
+      <c r="W25" s="446" t="n"/>
+      <c r="X25" s="446" t="n"/>
+      <c r="Y25" s="446" t="n"/>
+      <c r="Z25" s="446" t="n"/>
+      <c r="AA25" s="446" t="n"/>
+      <c r="AB25" s="446" t="n"/>
+      <c r="AC25" s="446" t="n"/>
+      <c r="AD25" s="446" t="n"/>
+      <c r="AE25" s="446" t="n"/>
+      <c r="AF25" s="446" t="n"/>
+      <c r="AG25" s="446" t="n"/>
+      <c r="AH25" s="446" t="n"/>
+      <c r="AI25" s="446" t="n"/>
+      <c r="AJ25" s="446" t="n"/>
+      <c r="AK25" s="446" t="n"/>
+      <c r="AL25" s="446" t="n"/>
+      <c r="AM25" s="446" t="n"/>
+      <c r="AN25" s="562" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="450">
+      <c r="A26" s="580">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B26" s="451" t="n"/>
-      <c r="C26" s="452" t="n"/>
-      <c r="D26" s="452" t="n"/>
-      <c r="E26" s="452" t="n"/>
-      <c r="F26" s="452" t="n"/>
-      <c r="G26" s="452" t="n"/>
-      <c r="H26" s="452" t="n"/>
-      <c r="I26" s="452" t="n"/>
-      <c r="J26" s="429" t="n"/>
-      <c r="K26" s="447" t="n"/>
-      <c r="L26" s="447" t="n"/>
-      <c r="M26" s="447" t="n"/>
-      <c r="N26" s="447" t="n"/>
-      <c r="O26" s="447" t="n"/>
-      <c r="P26" s="447" t="n"/>
-      <c r="Q26" s="447" t="n"/>
-      <c r="R26" s="447" t="n"/>
-      <c r="S26" s="447" t="n"/>
-      <c r="T26" s="447" t="n"/>
-      <c r="U26" s="447" t="n"/>
-      <c r="V26" s="447" t="n"/>
-      <c r="W26" s="447" t="n"/>
-      <c r="X26" s="447" t="n"/>
-      <c r="Y26" s="447" t="n"/>
-      <c r="Z26" s="447" t="n"/>
-      <c r="AA26" s="447" t="n"/>
-      <c r="AB26" s="447" t="n"/>
-      <c r="AC26" s="447" t="n"/>
-      <c r="AD26" s="447" t="n"/>
-      <c r="AE26" s="447" t="n"/>
-      <c r="AF26" s="447" t="n"/>
-      <c r="AG26" s="447" t="n"/>
-      <c r="AH26" s="447" t="n"/>
-      <c r="AI26" s="447" t="n"/>
-      <c r="AJ26" s="447" t="n"/>
-      <c r="AK26" s="447" t="n"/>
-      <c r="AL26" s="447" t="n"/>
-      <c r="AM26" s="447" t="n"/>
-      <c r="AN26" s="447" t="n"/>
+      <c r="B26" s="582" t="n"/>
+      <c r="C26" s="583" t="n"/>
+      <c r="D26" s="583" t="n"/>
+      <c r="E26" s="583" t="n"/>
+      <c r="F26" s="583" t="n"/>
+      <c r="G26" s="583" t="n"/>
+      <c r="H26" s="583" t="n"/>
+      <c r="I26" s="583" t="n"/>
+      <c r="J26" s="583" t="n"/>
+      <c r="K26" s="446" t="n"/>
+      <c r="L26" s="446" t="n"/>
+      <c r="M26" s="446" t="n"/>
+      <c r="N26" s="446" t="n"/>
+      <c r="O26" s="446" t="n"/>
+      <c r="P26" s="446" t="n"/>
+      <c r="Q26" s="446" t="n"/>
+      <c r="R26" s="446" t="n"/>
+      <c r="S26" s="446" t="n"/>
+      <c r="T26" s="446" t="n"/>
+      <c r="U26" s="446" t="n"/>
+      <c r="V26" s="446" t="n"/>
+      <c r="W26" s="446" t="n"/>
+      <c r="X26" s="446" t="n"/>
+      <c r="Y26" s="446" t="n"/>
+      <c r="Z26" s="446" t="n"/>
+      <c r="AA26" s="446" t="n"/>
+      <c r="AB26" s="446" t="n"/>
+      <c r="AC26" s="446" t="n"/>
+      <c r="AD26" s="446" t="n"/>
+      <c r="AE26" s="446" t="n"/>
+      <c r="AF26" s="446" t="n"/>
+      <c r="AG26" s="446" t="n"/>
+      <c r="AH26" s="446" t="n"/>
+      <c r="AI26" s="446" t="n"/>
+      <c r="AJ26" s="446" t="n"/>
+      <c r="AK26" s="446" t="n"/>
+      <c r="AL26" s="446" t="n"/>
+      <c r="AM26" s="446" t="n"/>
+      <c r="AN26" s="562" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="450">
+      <c r="A27" s="580">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B27" s="453" t="n"/>
-      <c r="C27" s="454" t="n"/>
-      <c r="D27" s="454" t="n"/>
-      <c r="E27" s="454" t="n"/>
-      <c r="F27" s="454" t="n"/>
-      <c r="G27" s="454" t="n"/>
-      <c r="H27" s="454" t="n"/>
-      <c r="I27" s="454" t="n"/>
-      <c r="J27" s="455" t="n"/>
-      <c r="K27" s="447" t="n"/>
-      <c r="L27" s="447" t="n"/>
-      <c r="M27" s="447" t="n"/>
-      <c r="N27" s="447" t="n"/>
-      <c r="O27" s="447" t="n"/>
-      <c r="P27" s="447" t="n"/>
-      <c r="Q27" s="447" t="n"/>
-      <c r="R27" s="447" t="n"/>
-      <c r="S27" s="447" t="n"/>
-      <c r="T27" s="447" t="n"/>
-      <c r="U27" s="447" t="n"/>
-      <c r="V27" s="447" t="n"/>
-      <c r="W27" s="447" t="n"/>
-      <c r="X27" s="447" t="n"/>
-      <c r="Y27" s="447" t="n"/>
-      <c r="Z27" s="447" t="n"/>
-      <c r="AA27" s="447" t="n"/>
-      <c r="AB27" s="447" t="n"/>
-      <c r="AC27" s="447" t="n"/>
-      <c r="AD27" s="447" t="n"/>
-      <c r="AE27" s="447" t="n"/>
-      <c r="AF27" s="447" t="n"/>
-      <c r="AG27" s="447" t="n"/>
-      <c r="AH27" s="447" t="n"/>
-      <c r="AI27" s="447" t="n"/>
-      <c r="AJ27" s="447" t="n"/>
-      <c r="AK27" s="447" t="n"/>
-      <c r="AL27" s="447" t="n"/>
-      <c r="AM27" s="447" t="n"/>
-      <c r="AN27" s="447" t="n"/>
+      <c r="B27" s="457" t="n"/>
+      <c r="C27" s="581" t="n"/>
+      <c r="D27" s="581" t="n"/>
+      <c r="E27" s="581" t="n"/>
+      <c r="F27" s="581" t="n"/>
+      <c r="G27" s="581" t="n"/>
+      <c r="H27" s="581" t="n"/>
+      <c r="I27" s="581" t="n"/>
+      <c r="J27" s="581" t="n"/>
+      <c r="K27" s="446" t="n"/>
+      <c r="L27" s="446" t="n"/>
+      <c r="M27" s="446" t="n"/>
+      <c r="N27" s="446" t="n"/>
+      <c r="O27" s="446" t="n"/>
+      <c r="P27" s="446" t="n"/>
+      <c r="Q27" s="446" t="n"/>
+      <c r="R27" s="446" t="n"/>
+      <c r="S27" s="446" t="n"/>
+      <c r="T27" s="446" t="n"/>
+      <c r="U27" s="446" t="n"/>
+      <c r="V27" s="446" t="n"/>
+      <c r="W27" s="446" t="n"/>
+      <c r="X27" s="446" t="n"/>
+      <c r="Y27" s="446" t="n"/>
+      <c r="Z27" s="446" t="n"/>
+      <c r="AA27" s="446" t="n"/>
+      <c r="AB27" s="446" t="n"/>
+      <c r="AC27" s="446" t="n"/>
+      <c r="AD27" s="446" t="n"/>
+      <c r="AE27" s="446" t="n"/>
+      <c r="AF27" s="446" t="n"/>
+      <c r="AG27" s="446" t="n"/>
+      <c r="AH27" s="446" t="n"/>
+      <c r="AI27" s="446" t="n"/>
+      <c r="AJ27" s="446" t="n"/>
+      <c r="AK27" s="446" t="n"/>
+      <c r="AL27" s="446" t="n"/>
+      <c r="AM27" s="446" t="n"/>
+      <c r="AN27" s="562" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="450">
+      <c r="A28" s="580">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B28" s="451" t="n"/>
-      <c r="C28" s="452" t="n"/>
-      <c r="D28" s="452" t="n"/>
-      <c r="E28" s="452" t="n"/>
-      <c r="F28" s="452" t="n"/>
-      <c r="G28" s="452" t="n"/>
-      <c r="H28" s="452" t="n"/>
-      <c r="I28" s="452" t="n"/>
-      <c r="J28" s="429" t="n"/>
-      <c r="K28" s="447" t="n"/>
-      <c r="L28" s="447" t="n"/>
-      <c r="M28" s="447" t="n"/>
-      <c r="N28" s="447" t="n"/>
-      <c r="O28" s="447" t="n"/>
-      <c r="P28" s="447" t="n"/>
-      <c r="Q28" s="447" t="n"/>
-      <c r="R28" s="447" t="n"/>
-      <c r="S28" s="447" t="n"/>
-      <c r="T28" s="447" t="n"/>
-      <c r="U28" s="447" t="n"/>
-      <c r="V28" s="447" t="n"/>
-      <c r="W28" s="447" t="n"/>
-      <c r="X28" s="447" t="n"/>
-      <c r="Y28" s="447" t="n"/>
-      <c r="Z28" s="447" t="n"/>
-      <c r="AA28" s="447" t="n"/>
-      <c r="AB28" s="447" t="n"/>
-      <c r="AC28" s="447" t="n"/>
-      <c r="AD28" s="447" t="n"/>
-      <c r="AE28" s="447" t="n"/>
-      <c r="AF28" s="447" t="n"/>
-      <c r="AG28" s="447" t="n"/>
-      <c r="AH28" s="447" t="n"/>
-      <c r="AI28" s="447" t="n"/>
-      <c r="AJ28" s="447" t="n"/>
-      <c r="AK28" s="447" t="n"/>
-      <c r="AL28" s="447" t="n"/>
-      <c r="AM28" s="447" t="n"/>
-      <c r="AN28" s="447" t="n"/>
+      <c r="B28" s="582" t="n"/>
+      <c r="C28" s="583" t="n"/>
+      <c r="D28" s="583" t="n"/>
+      <c r="E28" s="583" t="n"/>
+      <c r="F28" s="583" t="n"/>
+      <c r="G28" s="583" t="n"/>
+      <c r="H28" s="583" t="n"/>
+      <c r="I28" s="583" t="n"/>
+      <c r="J28" s="583" t="n"/>
+      <c r="K28" s="446" t="n"/>
+      <c r="L28" s="446" t="n"/>
+      <c r="M28" s="446" t="n"/>
+      <c r="N28" s="446" t="n"/>
+      <c r="O28" s="446" t="n"/>
+      <c r="P28" s="446" t="n"/>
+      <c r="Q28" s="446" t="n"/>
+      <c r="R28" s="446" t="n"/>
+      <c r="S28" s="446" t="n"/>
+      <c r="T28" s="446" t="n"/>
+      <c r="U28" s="446" t="n"/>
+      <c r="V28" s="446" t="n"/>
+      <c r="W28" s="446" t="n"/>
+      <c r="X28" s="446" t="n"/>
+      <c r="Y28" s="446" t="n"/>
+      <c r="Z28" s="446" t="n"/>
+      <c r="AA28" s="446" t="n"/>
+      <c r="AB28" s="446" t="n"/>
+      <c r="AC28" s="446" t="n"/>
+      <c r="AD28" s="446" t="n"/>
+      <c r="AE28" s="446" t="n"/>
+      <c r="AF28" s="446" t="n"/>
+      <c r="AG28" s="446" t="n"/>
+      <c r="AH28" s="446" t="n"/>
+      <c r="AI28" s="446" t="n"/>
+      <c r="AJ28" s="446" t="n"/>
+      <c r="AK28" s="446" t="n"/>
+      <c r="AL28" s="446" t="n"/>
+      <c r="AM28" s="446" t="n"/>
+      <c r="AN28" s="562" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="450">
+      <c r="A29" s="580">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B29" s="453" t="n"/>
-      <c r="C29" s="454" t="n"/>
-      <c r="D29" s="454" t="n"/>
-      <c r="E29" s="454" t="n"/>
-      <c r="F29" s="454" t="n"/>
-      <c r="G29" s="454" t="n"/>
-      <c r="H29" s="454" t="n"/>
-      <c r="I29" s="454" t="n"/>
-      <c r="J29" s="455" t="n"/>
-      <c r="K29" s="447" t="n"/>
-      <c r="L29" s="447" t="n"/>
-      <c r="M29" s="447" t="n"/>
-      <c r="N29" s="447" t="n"/>
-      <c r="O29" s="447" t="n"/>
-      <c r="P29" s="447" t="n"/>
-      <c r="Q29" s="447" t="n"/>
-      <c r="R29" s="447" t="n"/>
-      <c r="S29" s="447" t="n"/>
-      <c r="T29" s="447" t="n"/>
-      <c r="U29" s="447" t="n"/>
-      <c r="V29" s="447" t="n"/>
-      <c r="W29" s="447" t="n"/>
-      <c r="X29" s="447" t="n"/>
-      <c r="Y29" s="447" t="n"/>
-      <c r="Z29" s="447" t="n"/>
-      <c r="AA29" s="447" t="n"/>
-      <c r="AB29" s="447" t="n"/>
-      <c r="AC29" s="447" t="n"/>
-      <c r="AD29" s="447" t="n"/>
-      <c r="AE29" s="447" t="n"/>
-      <c r="AF29" s="447" t="n"/>
-      <c r="AG29" s="447" t="n"/>
-      <c r="AH29" s="447" t="n"/>
-      <c r="AI29" s="447" t="n"/>
-      <c r="AJ29" s="447" t="n"/>
-      <c r="AK29" s="447" t="n"/>
-      <c r="AL29" s="447" t="n"/>
-      <c r="AM29" s="447" t="n"/>
-      <c r="AN29" s="447" t="n"/>
+      <c r="B29" s="457" t="n"/>
+      <c r="C29" s="581" t="n"/>
+      <c r="D29" s="581" t="n"/>
+      <c r="E29" s="581" t="n"/>
+      <c r="F29" s="581" t="n"/>
+      <c r="G29" s="581" t="n"/>
+      <c r="H29" s="581" t="n"/>
+      <c r="I29" s="581" t="n"/>
+      <c r="J29" s="581" t="n"/>
+      <c r="K29" s="446" t="n"/>
+      <c r="L29" s="446" t="n"/>
+      <c r="M29" s="446" t="n"/>
+      <c r="N29" s="446" t="n"/>
+      <c r="O29" s="446" t="n"/>
+      <c r="P29" s="446" t="n"/>
+      <c r="Q29" s="446" t="n"/>
+      <c r="R29" s="446" t="n"/>
+      <c r="S29" s="446" t="n"/>
+      <c r="T29" s="446" t="n"/>
+      <c r="U29" s="446" t="n"/>
+      <c r="V29" s="446" t="n"/>
+      <c r="W29" s="446" t="n"/>
+      <c r="X29" s="446" t="n"/>
+      <c r="Y29" s="446" t="n"/>
+      <c r="Z29" s="446" t="n"/>
+      <c r="AA29" s="446" t="n"/>
+      <c r="AB29" s="446" t="n"/>
+      <c r="AC29" s="446" t="n"/>
+      <c r="AD29" s="446" t="n"/>
+      <c r="AE29" s="446" t="n"/>
+      <c r="AF29" s="446" t="n"/>
+      <c r="AG29" s="446" t="n"/>
+      <c r="AH29" s="446" t="n"/>
+      <c r="AI29" s="446" t="n"/>
+      <c r="AJ29" s="446" t="n"/>
+      <c r="AK29" s="446" t="n"/>
+      <c r="AL29" s="446" t="n"/>
+      <c r="AM29" s="446" t="n"/>
+      <c r="AN29" s="562" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="450">
+      <c r="A30" s="580">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B30" s="451" t="n"/>
-      <c r="C30" s="452" t="n"/>
-      <c r="D30" s="452" t="n"/>
-      <c r="E30" s="452" t="n"/>
-      <c r="F30" s="452" t="n"/>
-      <c r="G30" s="452" t="n"/>
-      <c r="H30" s="452" t="n"/>
-      <c r="I30" s="452" t="n"/>
-      <c r="J30" s="429" t="n"/>
-      <c r="K30" s="447" t="n"/>
-      <c r="L30" s="447" t="n"/>
-      <c r="M30" s="447" t="n"/>
-      <c r="N30" s="447" t="n"/>
-      <c r="O30" s="447" t="n"/>
-      <c r="P30" s="447" t="n"/>
-      <c r="Q30" s="447" t="n"/>
-      <c r="R30" s="447" t="n"/>
-      <c r="S30" s="447" t="n"/>
-      <c r="T30" s="447" t="n"/>
-      <c r="U30" s="447" t="n"/>
-      <c r="V30" s="447" t="n"/>
-      <c r="W30" s="447" t="n"/>
-      <c r="X30" s="447" t="n"/>
-      <c r="Y30" s="447" t="n"/>
-      <c r="Z30" s="447" t="n"/>
-      <c r="AA30" s="447" t="n"/>
-      <c r="AB30" s="447" t="n"/>
-      <c r="AC30" s="447" t="n"/>
-      <c r="AD30" s="447" t="n"/>
-      <c r="AE30" s="447" t="n"/>
-      <c r="AF30" s="447" t="n"/>
-      <c r="AG30" s="447" t="n"/>
-      <c r="AH30" s="447" t="n"/>
-      <c r="AI30" s="447" t="n"/>
-      <c r="AJ30" s="447" t="n"/>
-      <c r="AK30" s="447" t="n"/>
-      <c r="AL30" s="447" t="n"/>
-      <c r="AM30" s="447" t="n"/>
-      <c r="AN30" s="447" t="n"/>
+      <c r="B30" s="582" t="n"/>
+      <c r="C30" s="583" t="n"/>
+      <c r="D30" s="583" t="n"/>
+      <c r="E30" s="583" t="n"/>
+      <c r="F30" s="583" t="n"/>
+      <c r="G30" s="583" t="n"/>
+      <c r="H30" s="583" t="n"/>
+      <c r="I30" s="583" t="n"/>
+      <c r="J30" s="583" t="n"/>
+      <c r="K30" s="446" t="n"/>
+      <c r="L30" s="446" t="n"/>
+      <c r="M30" s="446" t="n"/>
+      <c r="N30" s="446" t="n"/>
+      <c r="O30" s="446" t="n"/>
+      <c r="P30" s="446" t="n"/>
+      <c r="Q30" s="446" t="n"/>
+      <c r="R30" s="446" t="n"/>
+      <c r="S30" s="446" t="n"/>
+      <c r="T30" s="446" t="n"/>
+      <c r="U30" s="446" t="n"/>
+      <c r="V30" s="446" t="n"/>
+      <c r="W30" s="446" t="n"/>
+      <c r="X30" s="446" t="n"/>
+      <c r="Y30" s="446" t="n"/>
+      <c r="Z30" s="446" t="n"/>
+      <c r="AA30" s="446" t="n"/>
+      <c r="AB30" s="446" t="n"/>
+      <c r="AC30" s="446" t="n"/>
+      <c r="AD30" s="446" t="n"/>
+      <c r="AE30" s="446" t="n"/>
+      <c r="AF30" s="446" t="n"/>
+      <c r="AG30" s="446" t="n"/>
+      <c r="AH30" s="446" t="n"/>
+      <c r="AI30" s="446" t="n"/>
+      <c r="AJ30" s="446" t="n"/>
+      <c r="AK30" s="446" t="n"/>
+      <c r="AL30" s="446" t="n"/>
+      <c r="AM30" s="446" t="n"/>
+      <c r="AN30" s="562" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="450">
+      <c r="A31" s="580">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B31" s="453" t="n"/>
-      <c r="C31" s="454" t="n"/>
-      <c r="D31" s="454" t="n"/>
-      <c r="E31" s="454" t="n"/>
-      <c r="F31" s="454" t="n"/>
-      <c r="G31" s="454" t="n"/>
-      <c r="H31" s="454" t="n"/>
-      <c r="I31" s="454" t="n"/>
-      <c r="J31" s="455" t="n"/>
-      <c r="K31" s="447" t="n"/>
-      <c r="L31" s="447" t="n"/>
-      <c r="M31" s="447" t="n"/>
-      <c r="N31" s="447" t="n"/>
-      <c r="O31" s="447" t="n"/>
-      <c r="P31" s="447" t="n"/>
-      <c r="Q31" s="447" t="n"/>
-      <c r="R31" s="447" t="n"/>
-      <c r="S31" s="447" t="n"/>
-      <c r="T31" s="447" t="n"/>
-      <c r="U31" s="447" t="n"/>
-      <c r="V31" s="447" t="n"/>
-      <c r="W31" s="447" t="n"/>
-      <c r="X31" s="447" t="n"/>
-      <c r="Y31" s="447" t="n"/>
-      <c r="Z31" s="447" t="n"/>
-      <c r="AA31" s="447" t="n"/>
-      <c r="AB31" s="447" t="n"/>
-      <c r="AC31" s="447" t="n"/>
-      <c r="AD31" s="447" t="n"/>
-      <c r="AE31" s="447" t="n"/>
-      <c r="AF31" s="447" t="n"/>
-      <c r="AG31" s="447" t="n"/>
-      <c r="AH31" s="447" t="n"/>
-      <c r="AI31" s="447" t="n"/>
-      <c r="AJ31" s="447" t="n"/>
-      <c r="AK31" s="447" t="n"/>
-      <c r="AL31" s="447" t="n"/>
-      <c r="AM31" s="447" t="n"/>
-      <c r="AN31" s="447" t="n"/>
+      <c r="B31" s="457" t="n"/>
+      <c r="C31" s="581" t="n"/>
+      <c r="D31" s="581" t="n"/>
+      <c r="E31" s="581" t="n"/>
+      <c r="F31" s="581" t="n"/>
+      <c r="G31" s="581" t="n"/>
+      <c r="H31" s="581" t="n"/>
+      <c r="I31" s="581" t="n"/>
+      <c r="J31" s="581" t="n"/>
+      <c r="K31" s="446" t="n"/>
+      <c r="L31" s="446" t="n"/>
+      <c r="M31" s="446" t="n"/>
+      <c r="N31" s="446" t="n"/>
+      <c r="O31" s="446" t="n"/>
+      <c r="P31" s="446" t="n"/>
+      <c r="Q31" s="446" t="n"/>
+      <c r="R31" s="446" t="n"/>
+      <c r="S31" s="446" t="n"/>
+      <c r="T31" s="446" t="n"/>
+      <c r="U31" s="446" t="n"/>
+      <c r="V31" s="446" t="n"/>
+      <c r="W31" s="446" t="n"/>
+      <c r="X31" s="446" t="n"/>
+      <c r="Y31" s="446" t="n"/>
+      <c r="Z31" s="446" t="n"/>
+      <c r="AA31" s="446" t="n"/>
+      <c r="AB31" s="446" t="n"/>
+      <c r="AC31" s="446" t="n"/>
+      <c r="AD31" s="446" t="n"/>
+      <c r="AE31" s="446" t="n"/>
+      <c r="AF31" s="446" t="n"/>
+      <c r="AG31" s="446" t="n"/>
+      <c r="AH31" s="446" t="n"/>
+      <c r="AI31" s="446" t="n"/>
+      <c r="AJ31" s="446" t="n"/>
+      <c r="AK31" s="446" t="n"/>
+      <c r="AL31" s="446" t="n"/>
+      <c r="AM31" s="446" t="n"/>
+      <c r="AN31" s="562" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="450">
+      <c r="A32" s="580">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B32" s="451" t="n"/>
-      <c r="C32" s="452" t="n"/>
-      <c r="D32" s="452" t="n"/>
-      <c r="E32" s="452" t="n"/>
-      <c r="F32" s="452" t="n"/>
-      <c r="G32" s="452" t="n"/>
-      <c r="H32" s="452" t="n"/>
-      <c r="I32" s="452" t="n"/>
-      <c r="J32" s="429" t="n"/>
-      <c r="K32" s="447" t="n"/>
-      <c r="L32" s="447" t="n"/>
-      <c r="M32" s="447" t="n"/>
-      <c r="N32" s="447" t="n"/>
-      <c r="O32" s="447" t="n"/>
-      <c r="P32" s="447" t="n"/>
-      <c r="Q32" s="447" t="n"/>
-      <c r="R32" s="447" t="n"/>
-      <c r="S32" s="447" t="n"/>
-      <c r="T32" s="447" t="n"/>
-      <c r="U32" s="447" t="n"/>
-      <c r="V32" s="447" t="n"/>
-      <c r="W32" s="447" t="n"/>
-      <c r="X32" s="447" t="n"/>
-      <c r="Y32" s="447" t="n"/>
-      <c r="Z32" s="447" t="n"/>
-      <c r="AA32" s="447" t="n"/>
-      <c r="AB32" s="447" t="n"/>
-      <c r="AC32" s="447" t="n"/>
-      <c r="AD32" s="447" t="n"/>
-      <c r="AE32" s="447" t="n"/>
-      <c r="AF32" s="447" t="n"/>
-      <c r="AG32" s="447" t="n"/>
-      <c r="AH32" s="447" t="n"/>
-      <c r="AI32" s="447" t="n"/>
-      <c r="AJ32" s="447" t="n"/>
-      <c r="AK32" s="447" t="n"/>
-      <c r="AL32" s="447" t="n"/>
-      <c r="AM32" s="447" t="n"/>
-      <c r="AN32" s="447" t="n"/>
+      <c r="B32" s="582" t="n"/>
+      <c r="C32" s="583" t="n"/>
+      <c r="D32" s="583" t="n"/>
+      <c r="E32" s="583" t="n"/>
+      <c r="F32" s="583" t="n"/>
+      <c r="G32" s="583" t="n"/>
+      <c r="H32" s="583" t="n"/>
+      <c r="I32" s="583" t="n"/>
+      <c r="J32" s="583" t="n"/>
+      <c r="K32" s="446" t="n"/>
+      <c r="L32" s="446" t="n"/>
+      <c r="M32" s="446" t="n"/>
+      <c r="N32" s="446" t="n"/>
+      <c r="O32" s="446" t="n"/>
+      <c r="P32" s="446" t="n"/>
+      <c r="Q32" s="446" t="n"/>
+      <c r="R32" s="446" t="n"/>
+      <c r="S32" s="446" t="n"/>
+      <c r="T32" s="446" t="n"/>
+      <c r="U32" s="446" t="n"/>
+      <c r="V32" s="446" t="n"/>
+      <c r="W32" s="446" t="n"/>
+      <c r="X32" s="446" t="n"/>
+      <c r="Y32" s="446" t="n"/>
+      <c r="Z32" s="446" t="n"/>
+      <c r="AA32" s="446" t="n"/>
+      <c r="AB32" s="446" t="n"/>
+      <c r="AC32" s="446" t="n"/>
+      <c r="AD32" s="446" t="n"/>
+      <c r="AE32" s="446" t="n"/>
+      <c r="AF32" s="446" t="n"/>
+      <c r="AG32" s="446" t="n"/>
+      <c r="AH32" s="446" t="n"/>
+      <c r="AI32" s="446" t="n"/>
+      <c r="AJ32" s="446" t="n"/>
+      <c r="AK32" s="446" t="n"/>
+      <c r="AL32" s="446" t="n"/>
+      <c r="AM32" s="446" t="n"/>
+      <c r="AN32" s="562" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="450">
+      <c r="A33" s="580">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B33" s="453" t="n"/>
-      <c r="C33" s="454" t="n"/>
-      <c r="D33" s="454" t="n"/>
-      <c r="E33" s="454" t="n"/>
-      <c r="F33" s="454" t="n"/>
-      <c r="G33" s="454" t="n"/>
-      <c r="H33" s="454" t="n"/>
-      <c r="I33" s="454" t="n"/>
-      <c r="J33" s="455" t="n"/>
-      <c r="K33" s="447" t="n"/>
-      <c r="L33" s="447" t="n"/>
-      <c r="M33" s="447" t="n"/>
-      <c r="N33" s="447" t="n"/>
-      <c r="O33" s="447" t="n"/>
-      <c r="P33" s="447" t="n"/>
-      <c r="Q33" s="447" t="n"/>
-      <c r="R33" s="447" t="n"/>
-      <c r="S33" s="447" t="n"/>
-      <c r="T33" s="447" t="n"/>
-      <c r="U33" s="447" t="n"/>
-      <c r="V33" s="447" t="n"/>
-      <c r="W33" s="447" t="n"/>
-      <c r="X33" s="447" t="n"/>
-      <c r="Y33" s="447" t="n"/>
-      <c r="Z33" s="447" t="n"/>
-      <c r="AA33" s="447" t="n"/>
-      <c r="AB33" s="447" t="n"/>
-      <c r="AC33" s="447" t="n"/>
-      <c r="AD33" s="447" t="n"/>
-      <c r="AE33" s="447" t="n"/>
-      <c r="AF33" s="447" t="n"/>
-      <c r="AG33" s="447" t="n"/>
-      <c r="AH33" s="447" t="n"/>
-      <c r="AI33" s="447" t="n"/>
-      <c r="AJ33" s="447" t="n"/>
-      <c r="AK33" s="447" t="n"/>
-      <c r="AL33" s="447" t="n"/>
-      <c r="AM33" s="447" t="n"/>
-      <c r="AN33" s="447" t="n"/>
+      <c r="B33" s="457" t="n"/>
+      <c r="C33" s="581" t="n"/>
+      <c r="D33" s="581" t="n"/>
+      <c r="E33" s="581" t="n"/>
+      <c r="F33" s="581" t="n"/>
+      <c r="G33" s="581" t="n"/>
+      <c r="H33" s="581" t="n"/>
+      <c r="I33" s="581" t="n"/>
+      <c r="J33" s="581" t="n"/>
+      <c r="K33" s="446" t="n"/>
+      <c r="L33" s="446" t="n"/>
+      <c r="M33" s="446" t="n"/>
+      <c r="N33" s="446" t="n"/>
+      <c r="O33" s="446" t="n"/>
+      <c r="P33" s="446" t="n"/>
+      <c r="Q33" s="446" t="n"/>
+      <c r="R33" s="446" t="n"/>
+      <c r="S33" s="446" t="n"/>
+      <c r="T33" s="446" t="n"/>
+      <c r="U33" s="446" t="n"/>
+      <c r="V33" s="446" t="n"/>
+      <c r="W33" s="446" t="n"/>
+      <c r="X33" s="446" t="n"/>
+      <c r="Y33" s="446" t="n"/>
+      <c r="Z33" s="446" t="n"/>
+      <c r="AA33" s="446" t="n"/>
+      <c r="AB33" s="446" t="n"/>
+      <c r="AC33" s="446" t="n"/>
+      <c r="AD33" s="446" t="n"/>
+      <c r="AE33" s="446" t="n"/>
+      <c r="AF33" s="446" t="n"/>
+      <c r="AG33" s="446" t="n"/>
+      <c r="AH33" s="446" t="n"/>
+      <c r="AI33" s="446" t="n"/>
+      <c r="AJ33" s="446" t="n"/>
+      <c r="AK33" s="446" t="n"/>
+      <c r="AL33" s="446" t="n"/>
+      <c r="AM33" s="446" t="n"/>
+      <c r="AN33" s="562" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="450">
+      <c r="A34" s="580">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B34" s="451" t="n"/>
-      <c r="C34" s="452" t="n"/>
-      <c r="D34" s="452" t="n"/>
-      <c r="E34" s="452" t="n"/>
-      <c r="F34" s="452" t="n"/>
-      <c r="G34" s="452" t="n"/>
-      <c r="H34" s="452" t="n"/>
-      <c r="I34" s="452" t="n"/>
-      <c r="J34" s="429" t="n"/>
-      <c r="K34" s="447" t="n"/>
-      <c r="L34" s="447" t="n"/>
-      <c r="M34" s="447" t="n"/>
-      <c r="N34" s="447" t="n"/>
-      <c r="O34" s="447" t="n"/>
-      <c r="P34" s="447" t="n"/>
-      <c r="Q34" s="447" t="n"/>
-      <c r="R34" s="447" t="n"/>
-      <c r="S34" s="447" t="n"/>
-      <c r="T34" s="447" t="n"/>
-      <c r="U34" s="447" t="n"/>
-      <c r="V34" s="447" t="n"/>
-      <c r="W34" s="447" t="n"/>
-      <c r="X34" s="447" t="n"/>
-      <c r="Y34" s="447" t="n"/>
-      <c r="Z34" s="447" t="n"/>
-      <c r="AA34" s="447" t="n"/>
-      <c r="AB34" s="447" t="n"/>
-      <c r="AC34" s="447" t="n"/>
-      <c r="AD34" s="447" t="n"/>
-      <c r="AE34" s="447" t="n"/>
-      <c r="AF34" s="447" t="n"/>
-      <c r="AG34" s="447" t="n"/>
-      <c r="AH34" s="447" t="n"/>
-      <c r="AI34" s="447" t="n"/>
-      <c r="AJ34" s="447" t="n"/>
-      <c r="AK34" s="447" t="n"/>
-      <c r="AL34" s="447" t="n"/>
-      <c r="AM34" s="447" t="n"/>
-      <c r="AN34" s="447" t="n"/>
+      <c r="B34" s="582" t="n"/>
+      <c r="C34" s="583" t="n"/>
+      <c r="D34" s="583" t="n"/>
+      <c r="E34" s="583" t="n"/>
+      <c r="F34" s="583" t="n"/>
+      <c r="G34" s="583" t="n"/>
+      <c r="H34" s="583" t="n"/>
+      <c r="I34" s="583" t="n"/>
+      <c r="J34" s="583" t="n"/>
+      <c r="K34" s="446" t="n"/>
+      <c r="L34" s="446" t="n"/>
+      <c r="M34" s="446" t="n"/>
+      <c r="N34" s="446" t="n"/>
+      <c r="O34" s="446" t="n"/>
+      <c r="P34" s="446" t="n"/>
+      <c r="Q34" s="446" t="n"/>
+      <c r="R34" s="446" t="n"/>
+      <c r="S34" s="446" t="n"/>
+      <c r="T34" s="446" t="n"/>
+      <c r="U34" s="446" t="n"/>
+      <c r="V34" s="446" t="n"/>
+      <c r="W34" s="446" t="n"/>
+      <c r="X34" s="446" t="n"/>
+      <c r="Y34" s="446" t="n"/>
+      <c r="Z34" s="446" t="n"/>
+      <c r="AA34" s="446" t="n"/>
+      <c r="AB34" s="446" t="n"/>
+      <c r="AC34" s="446" t="n"/>
+      <c r="AD34" s="446" t="n"/>
+      <c r="AE34" s="446" t="n"/>
+      <c r="AF34" s="446" t="n"/>
+      <c r="AG34" s="446" t="n"/>
+      <c r="AH34" s="446" t="n"/>
+      <c r="AI34" s="446" t="n"/>
+      <c r="AJ34" s="446" t="n"/>
+      <c r="AK34" s="446" t="n"/>
+      <c r="AL34" s="446" t="n"/>
+      <c r="AM34" s="446" t="n"/>
+      <c r="AN34" s="562" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="450">
+      <c r="A35" s="580">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B35" s="453" t="n"/>
-      <c r="C35" s="454" t="n"/>
-      <c r="D35" s="454" t="n"/>
-      <c r="E35" s="454" t="n"/>
-      <c r="F35" s="454" t="n"/>
-      <c r="G35" s="454" t="n"/>
-      <c r="H35" s="454" t="n"/>
-      <c r="I35" s="454" t="n"/>
-      <c r="J35" s="455" t="n"/>
-      <c r="K35" s="447" t="n"/>
-      <c r="L35" s="447" t="n"/>
-      <c r="M35" s="447" t="n"/>
-      <c r="N35" s="447" t="n"/>
-      <c r="O35" s="447" t="n"/>
-      <c r="P35" s="447" t="n"/>
-      <c r="Q35" s="447" t="n"/>
-      <c r="R35" s="447" t="n"/>
-      <c r="S35" s="447" t="n"/>
-      <c r="T35" s="447" t="n"/>
-      <c r="U35" s="447" t="n"/>
-      <c r="V35" s="447" t="n"/>
-      <c r="W35" s="447" t="n"/>
-      <c r="X35" s="447" t="n"/>
-      <c r="Y35" s="447" t="n"/>
-      <c r="Z35" s="447" t="n"/>
-      <c r="AA35" s="447" t="n"/>
-      <c r="AB35" s="447" t="n"/>
-      <c r="AC35" s="447" t="n"/>
-      <c r="AD35" s="447" t="n"/>
-      <c r="AE35" s="447" t="n"/>
-      <c r="AF35" s="447" t="n"/>
-      <c r="AG35" s="447" t="n"/>
-      <c r="AH35" s="447" t="n"/>
-      <c r="AI35" s="447" t="n"/>
-      <c r="AJ35" s="447" t="n"/>
-      <c r="AK35" s="447" t="n"/>
-      <c r="AL35" s="447" t="n"/>
-      <c r="AM35" s="447" t="n"/>
-      <c r="AN35" s="447" t="n"/>
+      <c r="B35" s="457" t="n"/>
+      <c r="C35" s="581" t="n"/>
+      <c r="D35" s="581" t="n"/>
+      <c r="E35" s="581" t="n"/>
+      <c r="F35" s="581" t="n"/>
+      <c r="G35" s="581" t="n"/>
+      <c r="H35" s="581" t="n"/>
+      <c r="I35" s="581" t="n"/>
+      <c r="J35" s="581" t="n"/>
+      <c r="K35" s="446" t="n"/>
+      <c r="L35" s="446" t="n"/>
+      <c r="M35" s="446" t="n"/>
+      <c r="N35" s="446" t="n"/>
+      <c r="O35" s="446" t="n"/>
+      <c r="P35" s="446" t="n"/>
+      <c r="Q35" s="446" t="n"/>
+      <c r="R35" s="446" t="n"/>
+      <c r="S35" s="446" t="n"/>
+      <c r="T35" s="446" t="n"/>
+      <c r="U35" s="446" t="n"/>
+      <c r="V35" s="446" t="n"/>
+      <c r="W35" s="446" t="n"/>
+      <c r="X35" s="446" t="n"/>
+      <c r="Y35" s="446" t="n"/>
+      <c r="Z35" s="446" t="n"/>
+      <c r="AA35" s="446" t="n"/>
+      <c r="AB35" s="446" t="n"/>
+      <c r="AC35" s="446" t="n"/>
+      <c r="AD35" s="446" t="n"/>
+      <c r="AE35" s="446" t="n"/>
+      <c r="AF35" s="446" t="n"/>
+      <c r="AG35" s="446" t="n"/>
+      <c r="AH35" s="446" t="n"/>
+      <c r="AI35" s="446" t="n"/>
+      <c r="AJ35" s="446" t="n"/>
+      <c r="AK35" s="446" t="n"/>
+      <c r="AL35" s="446" t="n"/>
+      <c r="AM35" s="446" t="n"/>
+      <c r="AN35" s="562" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="450">
+      <c r="A36" s="580">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B36" s="451" t="n"/>
-      <c r="C36" s="452" t="n"/>
-      <c r="D36" s="452" t="n"/>
-      <c r="E36" s="452" t="n"/>
-      <c r="F36" s="452" t="n"/>
-      <c r="G36" s="452" t="n"/>
-      <c r="H36" s="452" t="n"/>
-      <c r="I36" s="452" t="n"/>
-      <c r="J36" s="429" t="n"/>
-      <c r="K36" s="447" t="n"/>
-      <c r="L36" s="447" t="n"/>
-      <c r="M36" s="447" t="n"/>
-      <c r="N36" s="447" t="n"/>
-      <c r="O36" s="447" t="n"/>
-      <c r="P36" s="447" t="n"/>
-      <c r="Q36" s="447" t="n"/>
-      <c r="R36" s="447" t="n"/>
-      <c r="S36" s="447" t="n"/>
-      <c r="T36" s="447" t="n"/>
-      <c r="U36" s="447" t="n"/>
-      <c r="V36" s="447" t="n"/>
-      <c r="W36" s="447" t="n"/>
-      <c r="X36" s="447" t="n"/>
-      <c r="Y36" s="447" t="n"/>
-      <c r="Z36" s="447" t="n"/>
-      <c r="AA36" s="447" t="n"/>
-      <c r="AB36" s="447" t="n"/>
-      <c r="AC36" s="447" t="n"/>
-      <c r="AD36" s="447" t="n"/>
-      <c r="AE36" s="447" t="n"/>
-      <c r="AF36" s="447" t="n"/>
-      <c r="AG36" s="447" t="n"/>
-      <c r="AH36" s="447" t="n"/>
-      <c r="AI36" s="447" t="n"/>
-      <c r="AJ36" s="447" t="n"/>
-      <c r="AK36" s="447" t="n"/>
-      <c r="AL36" s="447" t="n"/>
-      <c r="AM36" s="447" t="n"/>
-      <c r="AN36" s="447" t="n"/>
+      <c r="B36" s="582" t="n"/>
+      <c r="C36" s="583" t="n"/>
+      <c r="D36" s="583" t="n"/>
+      <c r="E36" s="583" t="n"/>
+      <c r="F36" s="583" t="n"/>
+      <c r="G36" s="583" t="n"/>
+      <c r="H36" s="583" t="n"/>
+      <c r="I36" s="583" t="n"/>
+      <c r="J36" s="583" t="n"/>
+      <c r="K36" s="446" t="n"/>
+      <c r="L36" s="446" t="n"/>
+      <c r="M36" s="446" t="n"/>
+      <c r="N36" s="446" t="n"/>
+      <c r="O36" s="446" t="n"/>
+      <c r="P36" s="446" t="n"/>
+      <c r="Q36" s="446" t="n"/>
+      <c r="R36" s="446" t="n"/>
+      <c r="S36" s="446" t="n"/>
+      <c r="T36" s="446" t="n"/>
+      <c r="U36" s="446" t="n"/>
+      <c r="V36" s="446" t="n"/>
+      <c r="W36" s="446" t="n"/>
+      <c r="X36" s="446" t="n"/>
+      <c r="Y36" s="446" t="n"/>
+      <c r="Z36" s="446" t="n"/>
+      <c r="AA36" s="446" t="n"/>
+      <c r="AB36" s="446" t="n"/>
+      <c r="AC36" s="446" t="n"/>
+      <c r="AD36" s="446" t="n"/>
+      <c r="AE36" s="446" t="n"/>
+      <c r="AF36" s="446" t="n"/>
+      <c r="AG36" s="446" t="n"/>
+      <c r="AH36" s="446" t="n"/>
+      <c r="AI36" s="446" t="n"/>
+      <c r="AJ36" s="446" t="n"/>
+      <c r="AK36" s="446" t="n"/>
+      <c r="AL36" s="446" t="n"/>
+      <c r="AM36" s="446" t="n"/>
+      <c r="AN36" s="562" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="450">
+      <c r="A37" s="580">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B37" s="453" t="n"/>
-      <c r="C37" s="454" t="n"/>
-      <c r="D37" s="454" t="n"/>
-      <c r="E37" s="454" t="n"/>
-      <c r="F37" s="454" t="n"/>
-      <c r="G37" s="454" t="n"/>
-      <c r="H37" s="454" t="n"/>
-      <c r="I37" s="454" t="n"/>
-      <c r="J37" s="455" t="n"/>
-      <c r="K37" s="447" t="n"/>
-      <c r="L37" s="447" t="n"/>
-      <c r="M37" s="447" t="n"/>
-      <c r="N37" s="447" t="n"/>
-      <c r="O37" s="447" t="n"/>
-      <c r="P37" s="447" t="n"/>
-      <c r="Q37" s="447" t="n"/>
-      <c r="R37" s="447" t="n"/>
-      <c r="S37" s="447" t="n"/>
-      <c r="T37" s="447" t="n"/>
-      <c r="U37" s="447" t="n"/>
-      <c r="V37" s="447" t="n"/>
-      <c r="W37" s="447" t="n"/>
-      <c r="X37" s="447" t="n"/>
-      <c r="Y37" s="447" t="n"/>
-      <c r="Z37" s="447" t="n"/>
-      <c r="AA37" s="447" t="n"/>
-      <c r="AB37" s="447" t="n"/>
-      <c r="AC37" s="447" t="n"/>
-      <c r="AD37" s="447" t="n"/>
-      <c r="AE37" s="447" t="n"/>
-      <c r="AF37" s="447" t="n"/>
-      <c r="AG37" s="447" t="n"/>
-      <c r="AH37" s="447" t="n"/>
-      <c r="AI37" s="447" t="n"/>
-      <c r="AJ37" s="447" t="n"/>
-      <c r="AK37" s="447" t="n"/>
-      <c r="AL37" s="447" t="n"/>
-      <c r="AM37" s="447" t="n"/>
-      <c r="AN37" s="447" t="n"/>
+      <c r="B37" s="457" t="n"/>
+      <c r="C37" s="581" t="n"/>
+      <c r="D37" s="581" t="n"/>
+      <c r="E37" s="581" t="n"/>
+      <c r="F37" s="581" t="n"/>
+      <c r="G37" s="581" t="n"/>
+      <c r="H37" s="581" t="n"/>
+      <c r="I37" s="581" t="n"/>
+      <c r="J37" s="581" t="n"/>
+      <c r="K37" s="446" t="n"/>
+      <c r="L37" s="446" t="n"/>
+      <c r="M37" s="446" t="n"/>
+      <c r="N37" s="446" t="n"/>
+      <c r="O37" s="446" t="n"/>
+      <c r="P37" s="446" t="n"/>
+      <c r="Q37" s="446" t="n"/>
+      <c r="R37" s="446" t="n"/>
+      <c r="S37" s="446" t="n"/>
+      <c r="T37" s="446" t="n"/>
+      <c r="U37" s="446" t="n"/>
+      <c r="V37" s="446" t="n"/>
+      <c r="W37" s="446" t="n"/>
+      <c r="X37" s="446" t="n"/>
+      <c r="Y37" s="446" t="n"/>
+      <c r="Z37" s="446" t="n"/>
+      <c r="AA37" s="446" t="n"/>
+      <c r="AB37" s="446" t="n"/>
+      <c r="AC37" s="446" t="n"/>
+      <c r="AD37" s="446" t="n"/>
+      <c r="AE37" s="446" t="n"/>
+      <c r="AF37" s="446" t="n"/>
+      <c r="AG37" s="446" t="n"/>
+      <c r="AH37" s="446" t="n"/>
+      <c r="AI37" s="446" t="n"/>
+      <c r="AJ37" s="446" t="n"/>
+      <c r="AK37" s="446" t="n"/>
+      <c r="AL37" s="446" t="n"/>
+      <c r="AM37" s="446" t="n"/>
+      <c r="AN37" s="562" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="450">
+      <c r="A38" s="580">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B38" s="451" t="n"/>
-      <c r="C38" s="452" t="n"/>
-      <c r="D38" s="452" t="n"/>
-      <c r="E38" s="452" t="n"/>
-      <c r="F38" s="452" t="n"/>
-      <c r="G38" s="452" t="n"/>
-      <c r="H38" s="452" t="n"/>
-      <c r="I38" s="452" t="n"/>
-      <c r="J38" s="429" t="n"/>
-      <c r="K38" s="447" t="n"/>
-      <c r="L38" s="447" t="n"/>
-      <c r="M38" s="447" t="n"/>
-      <c r="N38" s="447" t="n"/>
-      <c r="O38" s="447" t="n"/>
-      <c r="P38" s="447" t="n"/>
-      <c r="Q38" s="447" t="n"/>
-      <c r="R38" s="447" t="n"/>
-      <c r="S38" s="447" t="n"/>
-      <c r="T38" s="447" t="n"/>
-      <c r="U38" s="447" t="n"/>
-      <c r="V38" s="447" t="n"/>
-      <c r="W38" s="447" t="n"/>
-      <c r="X38" s="447" t="n"/>
-      <c r="Y38" s="447" t="n"/>
-      <c r="Z38" s="447" t="n"/>
-      <c r="AA38" s="447" t="n"/>
-      <c r="AB38" s="447" t="n"/>
-      <c r="AC38" s="447" t="n"/>
-      <c r="AD38" s="447" t="n"/>
-      <c r="AE38" s="447" t="n"/>
-      <c r="AF38" s="447" t="n"/>
-      <c r="AG38" s="447" t="n"/>
-      <c r="AH38" s="447" t="n"/>
-      <c r="AI38" s="447" t="n"/>
-      <c r="AJ38" s="447" t="n"/>
-      <c r="AK38" s="447" t="n"/>
-      <c r="AL38" s="447" t="n"/>
-      <c r="AM38" s="447" t="n"/>
-      <c r="AN38" s="447" t="n"/>
+      <c r="B38" s="582" t="n"/>
+      <c r="C38" s="583" t="n"/>
+      <c r="D38" s="583" t="n"/>
+      <c r="E38" s="583" t="n"/>
+      <c r="F38" s="583" t="n"/>
+      <c r="G38" s="583" t="n"/>
+      <c r="H38" s="583" t="n"/>
+      <c r="I38" s="583" t="n"/>
+      <c r="J38" s="583" t="n"/>
+      <c r="K38" s="446" t="n"/>
+      <c r="L38" s="446" t="n"/>
+      <c r="M38" s="446" t="n"/>
+      <c r="N38" s="446" t="n"/>
+      <c r="O38" s="446" t="n"/>
+      <c r="P38" s="446" t="n"/>
+      <c r="Q38" s="446" t="n"/>
+      <c r="R38" s="446" t="n"/>
+      <c r="S38" s="446" t="n"/>
+      <c r="T38" s="446" t="n"/>
+      <c r="U38" s="446" t="n"/>
+      <c r="V38" s="446" t="n"/>
+      <c r="W38" s="446" t="n"/>
+      <c r="X38" s="446" t="n"/>
+      <c r="Y38" s="446" t="n"/>
+      <c r="Z38" s="446" t="n"/>
+      <c r="AA38" s="446" t="n"/>
+      <c r="AB38" s="446" t="n"/>
+      <c r="AC38" s="446" t="n"/>
+      <c r="AD38" s="446" t="n"/>
+      <c r="AE38" s="446" t="n"/>
+      <c r="AF38" s="446" t="n"/>
+      <c r="AG38" s="446" t="n"/>
+      <c r="AH38" s="446" t="n"/>
+      <c r="AI38" s="446" t="n"/>
+      <c r="AJ38" s="446" t="n"/>
+      <c r="AK38" s="446" t="n"/>
+      <c r="AL38" s="446" t="n"/>
+      <c r="AM38" s="446" t="n"/>
+      <c r="AN38" s="562" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="456">
+      <c r="A39" s="584">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B39" s="457" t="n"/>
-      <c r="C39" s="458" t="n"/>
-      <c r="D39" s="458" t="n"/>
-      <c r="E39" s="458" t="n"/>
-      <c r="F39" s="458" t="n"/>
-      <c r="G39" s="458" t="n"/>
-      <c r="H39" s="458" t="n"/>
-      <c r="I39" s="458" t="n"/>
-      <c r="J39" s="459" t="n"/>
-      <c r="K39" s="447" t="n"/>
-      <c r="L39" s="447" t="n"/>
-      <c r="M39" s="447" t="n"/>
-      <c r="N39" s="447" t="n"/>
-      <c r="O39" s="447" t="n"/>
-      <c r="P39" s="447" t="n"/>
-      <c r="Q39" s="447" t="n"/>
-      <c r="R39" s="447" t="n"/>
-      <c r="S39" s="447" t="n"/>
-      <c r="T39" s="447" t="n"/>
-      <c r="U39" s="447" t="n"/>
-      <c r="V39" s="447" t="n"/>
-      <c r="W39" s="447" t="n"/>
-      <c r="X39" s="447" t="n"/>
-      <c r="Y39" s="447" t="n"/>
-      <c r="Z39" s="447" t="n"/>
-      <c r="AA39" s="447" t="n"/>
-      <c r="AB39" s="447" t="n"/>
-      <c r="AC39" s="447" t="n"/>
-      <c r="AD39" s="447" t="n"/>
-      <c r="AE39" s="447" t="n"/>
-      <c r="AF39" s="447" t="n"/>
-      <c r="AG39" s="447" t="n"/>
-      <c r="AH39" s="447" t="n"/>
-      <c r="AI39" s="447" t="n"/>
-      <c r="AJ39" s="447" t="n"/>
-      <c r="AK39" s="447" t="n"/>
-      <c r="AL39" s="447" t="n"/>
-      <c r="AM39" s="447" t="n"/>
-      <c r="AN39" s="447" t="n"/>
+      <c r="B39" s="585" t="n"/>
+      <c r="C39" s="586" t="n"/>
+      <c r="D39" s="586" t="n"/>
+      <c r="E39" s="586" t="n"/>
+      <c r="F39" s="586" t="n"/>
+      <c r="G39" s="586" t="n"/>
+      <c r="H39" s="586" t="n"/>
+      <c r="I39" s="586" t="n"/>
+      <c r="J39" s="586" t="n"/>
+      <c r="K39" s="572" t="n"/>
+      <c r="L39" s="572" t="n"/>
+      <c r="M39" s="572" t="n"/>
+      <c r="N39" s="572" t="n"/>
+      <c r="O39" s="572" t="n"/>
+      <c r="P39" s="572" t="n"/>
+      <c r="Q39" s="572" t="n"/>
+      <c r="R39" s="572" t="n"/>
+      <c r="S39" s="572" t="n"/>
+      <c r="T39" s="572" t="n"/>
+      <c r="U39" s="572" t="n"/>
+      <c r="V39" s="572" t="n"/>
+      <c r="W39" s="572" t="n"/>
+      <c r="X39" s="572" t="n"/>
+      <c r="Y39" s="572" t="n"/>
+      <c r="Z39" s="572" t="n"/>
+      <c r="AA39" s="572" t="n"/>
+      <c r="AB39" s="572" t="n"/>
+      <c r="AC39" s="572" t="n"/>
+      <c r="AD39" s="572" t="n"/>
+      <c r="AE39" s="572" t="n"/>
+      <c r="AF39" s="572" t="n"/>
+      <c r="AG39" s="572" t="n"/>
+      <c r="AH39" s="572" t="n"/>
+      <c r="AI39" s="572" t="n"/>
+      <c r="AJ39" s="572" t="n"/>
+      <c r="AK39" s="572" t="n"/>
+      <c r="AL39" s="572" t="n"/>
+      <c r="AM39" s="572" t="n"/>
+      <c r="AN39" s="573" t="n"/>
     </row>
-    <row r="40" ht="4" customHeight="1">
+    <row r="40" ht="3" customHeight="1">
       <c r="A40" s="442" t="n"/>
       <c r="B40" s="495" t="n"/>
       <c r="C40" s="495" t="n"/>
@@ -7540,333 +8267,333 @@
       <c r="AM40" s="443" t="n"/>
       <c r="AN40" s="443" t="n"/>
     </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="444" t="inlineStr">
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="548" t="inlineStr">
         <is>
           <t>4.  CLOSURE AND EVIDENCE SECTION</t>
         </is>
       </c>
-      <c r="B41" s="487" t="n"/>
-      <c r="C41" s="487" t="n"/>
-      <c r="D41" s="487" t="n"/>
-      <c r="E41" s="487" t="n"/>
-      <c r="F41" s="487" t="n"/>
-      <c r="G41" s="487" t="n"/>
-      <c r="H41" s="487" t="n"/>
-      <c r="I41" s="487" t="n"/>
-      <c r="J41" s="486" t="n"/>
-      <c r="K41" s="447" t="n"/>
-      <c r="L41" s="447" t="n"/>
-      <c r="M41" s="447" t="n"/>
-      <c r="N41" s="447" t="n"/>
-      <c r="O41" s="447" t="n"/>
-      <c r="P41" s="447" t="n"/>
-      <c r="Q41" s="447" t="n"/>
-      <c r="R41" s="447" t="n"/>
-      <c r="S41" s="447" t="n"/>
-      <c r="T41" s="447" t="n"/>
-      <c r="U41" s="447" t="n"/>
-      <c r="V41" s="447" t="n"/>
-      <c r="W41" s="447" t="n"/>
-      <c r="X41" s="447" t="n"/>
-      <c r="Y41" s="447" t="n"/>
-      <c r="Z41" s="447" t="n"/>
-      <c r="AA41" s="447" t="n"/>
-      <c r="AB41" s="447" t="n"/>
-      <c r="AC41" s="447" t="n"/>
-      <c r="AD41" s="447" t="n"/>
-      <c r="AE41" s="447" t="n"/>
-      <c r="AF41" s="447" t="n"/>
-      <c r="AG41" s="447" t="n"/>
-      <c r="AH41" s="447" t="n"/>
-      <c r="AI41" s="447" t="n"/>
-      <c r="AJ41" s="447" t="n"/>
-      <c r="AK41" s="447" t="n"/>
-      <c r="AL41" s="447" t="n"/>
-      <c r="AM41" s="447" t="n"/>
-      <c r="AN41" s="447" t="n"/>
+      <c r="B41" s="549" t="n"/>
+      <c r="C41" s="549" t="n"/>
+      <c r="D41" s="549" t="n"/>
+      <c r="E41" s="549" t="n"/>
+      <c r="F41" s="549" t="n"/>
+      <c r="G41" s="549" t="n"/>
+      <c r="H41" s="549" t="n"/>
+      <c r="I41" s="549" t="n"/>
+      <c r="J41" s="549" t="n"/>
+      <c r="K41" s="549" t="n"/>
+      <c r="L41" s="549" t="n"/>
+      <c r="M41" s="549" t="n"/>
+      <c r="N41" s="549" t="n"/>
+      <c r="O41" s="549" t="n"/>
+      <c r="P41" s="549" t="n"/>
+      <c r="Q41" s="549" t="n"/>
+      <c r="R41" s="549" t="n"/>
+      <c r="S41" s="549" t="n"/>
+      <c r="T41" s="549" t="n"/>
+      <c r="U41" s="549" t="n"/>
+      <c r="V41" s="549" t="n"/>
+      <c r="W41" s="549" t="n"/>
+      <c r="X41" s="549" t="n"/>
+      <c r="Y41" s="549" t="n"/>
+      <c r="Z41" s="549" t="n"/>
+      <c r="AA41" s="549" t="n"/>
+      <c r="AB41" s="549" t="n"/>
+      <c r="AC41" s="549" t="n"/>
+      <c r="AD41" s="549" t="n"/>
+      <c r="AE41" s="549" t="n"/>
+      <c r="AF41" s="549" t="n"/>
+      <c r="AG41" s="549" t="n"/>
+      <c r="AH41" s="549" t="n"/>
+      <c r="AI41" s="549" t="n"/>
+      <c r="AJ41" s="549" t="n"/>
+      <c r="AK41" s="549" t="n"/>
+      <c r="AL41" s="549" t="n"/>
+      <c r="AM41" s="549" t="n"/>
+      <c r="AN41" s="550" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="460" t="inlineStr">
+      <c r="A42" s="587" t="inlineStr">
         <is>
           <t>Periodic review</t>
         </is>
       </c>
-      <c r="B42" s="487" t="n"/>
-      <c r="C42" s="486" t="n"/>
-      <c r="D42" s="460" t="inlineStr">
+      <c r="B42" s="552" t="n"/>
+      <c r="C42" s="552" t="n"/>
+      <c r="D42" s="588" t="inlineStr">
         <is>
           <t>Open items / escalation</t>
         </is>
       </c>
-      <c r="E42" s="487" t="n"/>
-      <c r="F42" s="486" t="n"/>
-      <c r="G42" s="460" t="inlineStr">
+      <c r="E42" s="552" t="n"/>
+      <c r="F42" s="552" t="n"/>
+      <c r="G42" s="588" t="inlineStr">
         <is>
           <t>Approval / archive</t>
         </is>
       </c>
-      <c r="H42" s="487" t="n"/>
-      <c r="I42" s="487" t="n"/>
-      <c r="J42" s="486" t="n"/>
-      <c r="K42" s="447" t="n"/>
-      <c r="L42" s="447" t="n"/>
-      <c r="M42" s="447" t="n"/>
-      <c r="N42" s="447" t="n"/>
-      <c r="O42" s="447" t="n"/>
-      <c r="P42" s="447" t="n"/>
-      <c r="Q42" s="447" t="n"/>
-      <c r="R42" s="447" t="n"/>
-      <c r="S42" s="447" t="n"/>
-      <c r="T42" s="447" t="n"/>
-      <c r="U42" s="447" t="n"/>
-      <c r="V42" s="447" t="n"/>
-      <c r="W42" s="447" t="n"/>
-      <c r="X42" s="447" t="n"/>
-      <c r="Y42" s="447" t="n"/>
-      <c r="Z42" s="447" t="n"/>
-      <c r="AA42" s="447" t="n"/>
-      <c r="AB42" s="447" t="n"/>
-      <c r="AC42" s="447" t="n"/>
-      <c r="AD42" s="447" t="n"/>
-      <c r="AE42" s="447" t="n"/>
-      <c r="AF42" s="447" t="n"/>
-      <c r="AG42" s="447" t="n"/>
-      <c r="AH42" s="447" t="n"/>
-      <c r="AI42" s="447" t="n"/>
-      <c r="AJ42" s="447" t="n"/>
-      <c r="AK42" s="447" t="n"/>
-      <c r="AL42" s="447" t="n"/>
-      <c r="AM42" s="447" t="n"/>
-      <c r="AN42" s="447" t="n"/>
+      <c r="H42" s="552" t="n"/>
+      <c r="I42" s="552" t="n"/>
+      <c r="J42" s="552" t="n"/>
+      <c r="K42" s="555" t="n"/>
+      <c r="L42" s="556" t="n"/>
+      <c r="M42" s="556" t="n"/>
+      <c r="N42" s="556" t="n"/>
+      <c r="O42" s="556" t="n"/>
+      <c r="P42" s="556" t="n"/>
+      <c r="Q42" s="556" t="n"/>
+      <c r="R42" s="556" t="n"/>
+      <c r="S42" s="556" t="n"/>
+      <c r="T42" s="556" t="n"/>
+      <c r="U42" s="556" t="n"/>
+      <c r="V42" s="556" t="n"/>
+      <c r="W42" s="556" t="n"/>
+      <c r="X42" s="556" t="n"/>
+      <c r="Y42" s="556" t="n"/>
+      <c r="Z42" s="556" t="n"/>
+      <c r="AA42" s="556" t="n"/>
+      <c r="AB42" s="556" t="n"/>
+      <c r="AC42" s="556" t="n"/>
+      <c r="AD42" s="556" t="n"/>
+      <c r="AE42" s="556" t="n"/>
+      <c r="AF42" s="556" t="n"/>
+      <c r="AG42" s="556" t="n"/>
+      <c r="AH42" s="556" t="n"/>
+      <c r="AI42" s="556" t="n"/>
+      <c r="AJ42" s="556" t="n"/>
+      <c r="AK42" s="556" t="n"/>
+      <c r="AL42" s="556" t="n"/>
+      <c r="AM42" s="556" t="n"/>
+      <c r="AN42" s="557" t="n"/>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="461" t="inlineStr">
+      <c r="A43" s="589" t="inlineStr">
         <is>
           <t>Return-material tracking memory only; formal quality investigation remains in linked quality records.
 Review owner: _____________________________________________</t>
         </is>
       </c>
-      <c r="B43" s="488" t="n"/>
-      <c r="C43" s="489" t="n"/>
-      <c r="D43" s="461" t="inlineStr">
+      <c r="B43" s="437" t="n"/>
+      <c r="C43" s="437" t="n"/>
+      <c r="D43" s="590" t="inlineStr">
         <is>
           <t>Final evidence ref: ________________________________________
 Outstanding items / actions: ________________________________</t>
         </is>
       </c>
-      <c r="E43" s="488" t="n"/>
-      <c r="F43" s="489" t="n"/>
-      <c r="G43" s="464" t="inlineStr">
+      <c r="E43" s="437" t="n"/>
+      <c r="F43" s="437" t="n"/>
+      <c r="G43" s="591" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="H43" s="488" t="n"/>
-      <c r="I43" s="488" t="n"/>
-      <c r="J43" s="489" t="n"/>
-      <c r="K43" s="447" t="n"/>
-      <c r="L43" s="447" t="n"/>
-      <c r="M43" s="447" t="n"/>
-      <c r="N43" s="447" t="n"/>
-      <c r="O43" s="447" t="n"/>
-      <c r="P43" s="447" t="n"/>
-      <c r="Q43" s="447" t="n"/>
-      <c r="R43" s="447" t="n"/>
-      <c r="S43" s="447" t="n"/>
-      <c r="T43" s="447" t="n"/>
-      <c r="U43" s="447" t="n"/>
-      <c r="V43" s="447" t="n"/>
-      <c r="W43" s="447" t="n"/>
-      <c r="X43" s="447" t="n"/>
-      <c r="Y43" s="447" t="n"/>
-      <c r="Z43" s="447" t="n"/>
-      <c r="AA43" s="447" t="n"/>
-      <c r="AB43" s="447" t="n"/>
-      <c r="AC43" s="447" t="n"/>
-      <c r="AD43" s="447" t="n"/>
-      <c r="AE43" s="447" t="n"/>
-      <c r="AF43" s="447" t="n"/>
-      <c r="AG43" s="447" t="n"/>
-      <c r="AH43" s="447" t="n"/>
-      <c r="AI43" s="447" t="n"/>
-      <c r="AJ43" s="447" t="n"/>
-      <c r="AK43" s="447" t="n"/>
-      <c r="AL43" s="447" t="n"/>
-      <c r="AM43" s="447" t="n"/>
-      <c r="AN43" s="447" t="n"/>
+      <c r="H43" s="437" t="n"/>
+      <c r="I43" s="437" t="n"/>
+      <c r="J43" s="437" t="n"/>
+      <c r="K43" s="561" t="n"/>
+      <c r="L43" s="446" t="n"/>
+      <c r="M43" s="446" t="n"/>
+      <c r="N43" s="446" t="n"/>
+      <c r="O43" s="446" t="n"/>
+      <c r="P43" s="446" t="n"/>
+      <c r="Q43" s="446" t="n"/>
+      <c r="R43" s="446" t="n"/>
+      <c r="S43" s="446" t="n"/>
+      <c r="T43" s="446" t="n"/>
+      <c r="U43" s="446" t="n"/>
+      <c r="V43" s="446" t="n"/>
+      <c r="W43" s="446" t="n"/>
+      <c r="X43" s="446" t="n"/>
+      <c r="Y43" s="446" t="n"/>
+      <c r="Z43" s="446" t="n"/>
+      <c r="AA43" s="446" t="n"/>
+      <c r="AB43" s="446" t="n"/>
+      <c r="AC43" s="446" t="n"/>
+      <c r="AD43" s="446" t="n"/>
+      <c r="AE43" s="446" t="n"/>
+      <c r="AF43" s="446" t="n"/>
+      <c r="AG43" s="446" t="n"/>
+      <c r="AH43" s="446" t="n"/>
+      <c r="AI43" s="446" t="n"/>
+      <c r="AJ43" s="446" t="n"/>
+      <c r="AK43" s="446" t="n"/>
+      <c r="AL43" s="446" t="n"/>
+      <c r="AM43" s="446" t="n"/>
+      <c r="AN43" s="562" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="490" t="n"/>
-      <c r="B44" s="447" t="n"/>
-      <c r="C44" s="491" t="n"/>
-      <c r="D44" s="490" t="n"/>
-      <c r="E44" s="447" t="n"/>
-      <c r="F44" s="491" t="n"/>
-      <c r="G44" s="490" t="n"/>
-      <c r="H44" s="447" t="n"/>
-      <c r="I44" s="447" t="n"/>
-      <c r="J44" s="491" t="n"/>
-      <c r="K44" s="447" t="n"/>
-      <c r="L44" s="447" t="n"/>
-      <c r="M44" s="447" t="n"/>
-      <c r="N44" s="447" t="n"/>
-      <c r="O44" s="447" t="n"/>
-      <c r="P44" s="447" t="n"/>
-      <c r="Q44" s="447" t="n"/>
-      <c r="R44" s="447" t="n"/>
-      <c r="S44" s="447" t="n"/>
-      <c r="T44" s="447" t="n"/>
-      <c r="U44" s="447" t="n"/>
-      <c r="V44" s="447" t="n"/>
-      <c r="W44" s="447" t="n"/>
-      <c r="X44" s="447" t="n"/>
-      <c r="Y44" s="447" t="n"/>
-      <c r="Z44" s="447" t="n"/>
-      <c r="AA44" s="447" t="n"/>
-      <c r="AB44" s="447" t="n"/>
-      <c r="AC44" s="447" t="n"/>
-      <c r="AD44" s="447" t="n"/>
-      <c r="AE44" s="447" t="n"/>
-      <c r="AF44" s="447" t="n"/>
-      <c r="AG44" s="447" t="n"/>
-      <c r="AH44" s="447" t="n"/>
-      <c r="AI44" s="447" t="n"/>
-      <c r="AJ44" s="447" t="n"/>
-      <c r="AK44" s="447" t="n"/>
-      <c r="AL44" s="447" t="n"/>
-      <c r="AM44" s="447" t="n"/>
-      <c r="AN44" s="447" t="n"/>
+      <c r="A44" s="592" t="n"/>
+      <c r="B44" s="437" t="n"/>
+      <c r="C44" s="437" t="n"/>
+      <c r="D44" s="563" t="n"/>
+      <c r="E44" s="437" t="n"/>
+      <c r="F44" s="437" t="n"/>
+      <c r="G44" s="563" t="n"/>
+      <c r="H44" s="437" t="n"/>
+      <c r="I44" s="437" t="n"/>
+      <c r="J44" s="437" t="n"/>
+      <c r="K44" s="561" t="n"/>
+      <c r="L44" s="446" t="n"/>
+      <c r="M44" s="446" t="n"/>
+      <c r="N44" s="446" t="n"/>
+      <c r="O44" s="446" t="n"/>
+      <c r="P44" s="446" t="n"/>
+      <c r="Q44" s="446" t="n"/>
+      <c r="R44" s="446" t="n"/>
+      <c r="S44" s="446" t="n"/>
+      <c r="T44" s="446" t="n"/>
+      <c r="U44" s="446" t="n"/>
+      <c r="V44" s="446" t="n"/>
+      <c r="W44" s="446" t="n"/>
+      <c r="X44" s="446" t="n"/>
+      <c r="Y44" s="446" t="n"/>
+      <c r="Z44" s="446" t="n"/>
+      <c r="AA44" s="446" t="n"/>
+      <c r="AB44" s="446" t="n"/>
+      <c r="AC44" s="446" t="n"/>
+      <c r="AD44" s="446" t="n"/>
+      <c r="AE44" s="446" t="n"/>
+      <c r="AF44" s="446" t="n"/>
+      <c r="AG44" s="446" t="n"/>
+      <c r="AH44" s="446" t="n"/>
+      <c r="AI44" s="446" t="n"/>
+      <c r="AJ44" s="446" t="n"/>
+      <c r="AK44" s="446" t="n"/>
+      <c r="AL44" s="446" t="n"/>
+      <c r="AM44" s="446" t="n"/>
+      <c r="AN44" s="562" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="490" t="n"/>
-      <c r="B45" s="447" t="n"/>
-      <c r="C45" s="491" t="n"/>
-      <c r="D45" s="490" t="n"/>
-      <c r="E45" s="447" t="n"/>
-      <c r="F45" s="491" t="n"/>
-      <c r="G45" s="490" t="n"/>
-      <c r="H45" s="447" t="n"/>
-      <c r="I45" s="447" t="n"/>
-      <c r="J45" s="491" t="n"/>
-      <c r="K45" s="447" t="n"/>
-      <c r="L45" s="447" t="n"/>
-      <c r="M45" s="447" t="n"/>
-      <c r="N45" s="447" t="n"/>
-      <c r="O45" s="447" t="n"/>
-      <c r="P45" s="447" t="n"/>
-      <c r="Q45" s="447" t="n"/>
-      <c r="R45" s="447" t="n"/>
-      <c r="S45" s="447" t="n"/>
-      <c r="T45" s="447" t="n"/>
-      <c r="U45" s="447" t="n"/>
-      <c r="V45" s="447" t="n"/>
-      <c r="W45" s="447" t="n"/>
-      <c r="X45" s="447" t="n"/>
-      <c r="Y45" s="447" t="n"/>
-      <c r="Z45" s="447" t="n"/>
-      <c r="AA45" s="447" t="n"/>
-      <c r="AB45" s="447" t="n"/>
-      <c r="AC45" s="447" t="n"/>
-      <c r="AD45" s="447" t="n"/>
-      <c r="AE45" s="447" t="n"/>
-      <c r="AF45" s="447" t="n"/>
-      <c r="AG45" s="447" t="n"/>
-      <c r="AH45" s="447" t="n"/>
-      <c r="AI45" s="447" t="n"/>
-      <c r="AJ45" s="447" t="n"/>
-      <c r="AK45" s="447" t="n"/>
-      <c r="AL45" s="447" t="n"/>
-      <c r="AM45" s="447" t="n"/>
-      <c r="AN45" s="447" t="n"/>
+      <c r="A45" s="592" t="n"/>
+      <c r="B45" s="437" t="n"/>
+      <c r="C45" s="437" t="n"/>
+      <c r="D45" s="563" t="n"/>
+      <c r="E45" s="437" t="n"/>
+      <c r="F45" s="437" t="n"/>
+      <c r="G45" s="563" t="n"/>
+      <c r="H45" s="437" t="n"/>
+      <c r="I45" s="437" t="n"/>
+      <c r="J45" s="437" t="n"/>
+      <c r="K45" s="561" t="n"/>
+      <c r="L45" s="446" t="n"/>
+      <c r="M45" s="446" t="n"/>
+      <c r="N45" s="446" t="n"/>
+      <c r="O45" s="446" t="n"/>
+      <c r="P45" s="446" t="n"/>
+      <c r="Q45" s="446" t="n"/>
+      <c r="R45" s="446" t="n"/>
+      <c r="S45" s="446" t="n"/>
+      <c r="T45" s="446" t="n"/>
+      <c r="U45" s="446" t="n"/>
+      <c r="V45" s="446" t="n"/>
+      <c r="W45" s="446" t="n"/>
+      <c r="X45" s="446" t="n"/>
+      <c r="Y45" s="446" t="n"/>
+      <c r="Z45" s="446" t="n"/>
+      <c r="AA45" s="446" t="n"/>
+      <c r="AB45" s="446" t="n"/>
+      <c r="AC45" s="446" t="n"/>
+      <c r="AD45" s="446" t="n"/>
+      <c r="AE45" s="446" t="n"/>
+      <c r="AF45" s="446" t="n"/>
+      <c r="AG45" s="446" t="n"/>
+      <c r="AH45" s="446" t="n"/>
+      <c r="AI45" s="446" t="n"/>
+      <c r="AJ45" s="446" t="n"/>
+      <c r="AK45" s="446" t="n"/>
+      <c r="AL45" s="446" t="n"/>
+      <c r="AM45" s="446" t="n"/>
+      <c r="AN45" s="562" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="492" t="n"/>
-      <c r="B46" s="493" t="n"/>
-      <c r="C46" s="494" t="n"/>
-      <c r="D46" s="492" t="n"/>
-      <c r="E46" s="493" t="n"/>
-      <c r="F46" s="494" t="n"/>
-      <c r="G46" s="492" t="n"/>
-      <c r="H46" s="493" t="n"/>
-      <c r="I46" s="493" t="n"/>
-      <c r="J46" s="494" t="n"/>
-      <c r="K46" s="447" t="n"/>
-      <c r="L46" s="447" t="n"/>
-      <c r="M46" s="447" t="n"/>
-      <c r="N46" s="447" t="n"/>
-      <c r="O46" s="447" t="n"/>
-      <c r="P46" s="447" t="n"/>
-      <c r="Q46" s="447" t="n"/>
-      <c r="R46" s="447" t="n"/>
-      <c r="S46" s="447" t="n"/>
-      <c r="T46" s="447" t="n"/>
-      <c r="U46" s="447" t="n"/>
-      <c r="V46" s="447" t="n"/>
-      <c r="W46" s="447" t="n"/>
-      <c r="X46" s="447" t="n"/>
-      <c r="Y46" s="447" t="n"/>
-      <c r="Z46" s="447" t="n"/>
-      <c r="AA46" s="447" t="n"/>
-      <c r="AB46" s="447" t="n"/>
-      <c r="AC46" s="447" t="n"/>
-      <c r="AD46" s="447" t="n"/>
-      <c r="AE46" s="447" t="n"/>
-      <c r="AF46" s="447" t="n"/>
-      <c r="AG46" s="447" t="n"/>
-      <c r="AH46" s="447" t="n"/>
-      <c r="AI46" s="447" t="n"/>
-      <c r="AJ46" s="447" t="n"/>
-      <c r="AK46" s="447" t="n"/>
-      <c r="AL46" s="447" t="n"/>
-      <c r="AM46" s="447" t="n"/>
-      <c r="AN46" s="447" t="n"/>
+      <c r="A46" s="593" t="n"/>
+      <c r="B46" s="566" t="n"/>
+      <c r="C46" s="566" t="n"/>
+      <c r="D46" s="569" t="n"/>
+      <c r="E46" s="566" t="n"/>
+      <c r="F46" s="566" t="n"/>
+      <c r="G46" s="569" t="n"/>
+      <c r="H46" s="566" t="n"/>
+      <c r="I46" s="566" t="n"/>
+      <c r="J46" s="566" t="n"/>
+      <c r="K46" s="571" t="n"/>
+      <c r="L46" s="572" t="n"/>
+      <c r="M46" s="572" t="n"/>
+      <c r="N46" s="572" t="n"/>
+      <c r="O46" s="572" t="n"/>
+      <c r="P46" s="572" t="n"/>
+      <c r="Q46" s="572" t="n"/>
+      <c r="R46" s="572" t="n"/>
+      <c r="S46" s="572" t="n"/>
+      <c r="T46" s="572" t="n"/>
+      <c r="U46" s="572" t="n"/>
+      <c r="V46" s="572" t="n"/>
+      <c r="W46" s="572" t="n"/>
+      <c r="X46" s="572" t="n"/>
+      <c r="Y46" s="572" t="n"/>
+      <c r="Z46" s="572" t="n"/>
+      <c r="AA46" s="572" t="n"/>
+      <c r="AB46" s="572" t="n"/>
+      <c r="AC46" s="572" t="n"/>
+      <c r="AD46" s="572" t="n"/>
+      <c r="AE46" s="572" t="n"/>
+      <c r="AF46" s="572" t="n"/>
+      <c r="AG46" s="572" t="n"/>
+      <c r="AH46" s="572" t="n"/>
+      <c r="AI46" s="572" t="n"/>
+      <c r="AJ46" s="572" t="n"/>
+      <c r="AK46" s="572" t="n"/>
+      <c r="AL46" s="572" t="n"/>
+      <c r="AM46" s="572" t="n"/>
+      <c r="AN46" s="573" t="n"/>
     </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="470" t="inlineStr">
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="548" t="inlineStr">
         <is>
           <t>NOTICE  —  Enter data only in designated white input cells. One form per event or job unless this workbook is designated as rolling. Do not add, delete or resize columns/rows. File naming: FRM-213_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="487" t="n"/>
-      <c r="C47" s="487" t="n"/>
-      <c r="D47" s="487" t="n"/>
-      <c r="E47" s="487" t="n"/>
-      <c r="F47" s="487" t="n"/>
-      <c r="G47" s="487" t="n"/>
-      <c r="H47" s="487" t="n"/>
-      <c r="I47" s="487" t="n"/>
-      <c r="J47" s="486" t="n"/>
-      <c r="K47" s="447" t="n"/>
-      <c r="L47" s="447" t="n"/>
-      <c r="M47" s="447" t="n"/>
-      <c r="N47" s="447" t="n"/>
-      <c r="O47" s="447" t="n"/>
-      <c r="P47" s="447" t="n"/>
-      <c r="Q47" s="447" t="n"/>
-      <c r="R47" s="447" t="n"/>
-      <c r="S47" s="447" t="n"/>
-      <c r="T47" s="447" t="n"/>
-      <c r="U47" s="447" t="n"/>
-      <c r="V47" s="447" t="n"/>
-      <c r="W47" s="447" t="n"/>
-      <c r="X47" s="447" t="n"/>
-      <c r="Y47" s="447" t="n"/>
-      <c r="Z47" s="447" t="n"/>
-      <c r="AA47" s="447" t="n"/>
-      <c r="AB47" s="447" t="n"/>
-      <c r="AC47" s="447" t="n"/>
-      <c r="AD47" s="447" t="n"/>
-      <c r="AE47" s="447" t="n"/>
-      <c r="AF47" s="447" t="n"/>
-      <c r="AG47" s="447" t="n"/>
-      <c r="AH47" s="447" t="n"/>
-      <c r="AI47" s="447" t="n"/>
-      <c r="AJ47" s="447" t="n"/>
-      <c r="AK47" s="447" t="n"/>
-      <c r="AL47" s="447" t="n"/>
-      <c r="AM47" s="447" t="n"/>
-      <c r="AN47" s="447" t="n"/>
+      <c r="B47" s="549" t="n"/>
+      <c r="C47" s="549" t="n"/>
+      <c r="D47" s="549" t="n"/>
+      <c r="E47" s="549" t="n"/>
+      <c r="F47" s="549" t="n"/>
+      <c r="G47" s="549" t="n"/>
+      <c r="H47" s="549" t="n"/>
+      <c r="I47" s="549" t="n"/>
+      <c r="J47" s="549" t="n"/>
+      <c r="K47" s="549" t="n"/>
+      <c r="L47" s="549" t="n"/>
+      <c r="M47" s="549" t="n"/>
+      <c r="N47" s="549" t="n"/>
+      <c r="O47" s="549" t="n"/>
+      <c r="P47" s="549" t="n"/>
+      <c r="Q47" s="549" t="n"/>
+      <c r="R47" s="549" t="n"/>
+      <c r="S47" s="549" t="n"/>
+      <c r="T47" s="549" t="n"/>
+      <c r="U47" s="549" t="n"/>
+      <c r="V47" s="549" t="n"/>
+      <c r="W47" s="549" t="n"/>
+      <c r="X47" s="549" t="n"/>
+      <c r="Y47" s="549" t="n"/>
+      <c r="Z47" s="549" t="n"/>
+      <c r="AA47" s="549" t="n"/>
+      <c r="AB47" s="549" t="n"/>
+      <c r="AC47" s="549" t="n"/>
+      <c r="AD47" s="549" t="n"/>
+      <c r="AE47" s="549" t="n"/>
+      <c r="AF47" s="549" t="n"/>
+      <c r="AG47" s="549" t="n"/>
+      <c r="AH47" s="549" t="n"/>
+      <c r="AI47" s="549" t="n"/>
+      <c r="AJ47" s="549" t="n"/>
+      <c r="AK47" s="549" t="n"/>
+      <c r="AL47" s="549" t="n"/>
+      <c r="AM47" s="549" t="n"/>
+      <c r="AN47" s="550" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="1"/>
     <row r="49" hidden="1" outlineLevel="1"/>
@@ -8022,7 +8749,7 @@
     <row r="199" hidden="1" outlineLevel="1"/>
     <row r="200" hidden="1" outlineLevel="1"/>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="51">
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A47:J47"/>
     <mergeCell ref="F11:G11"/>
@@ -8040,15 +8767,12 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="C12:E12"/>
-    <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A19:J19"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="F15:G15"/>
-    <mergeCell ref="A40:J40"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="A1:B5"/>
@@ -8062,7 +8786,6 @@
     <mergeCell ref="D42:F42"/>
     <mergeCell ref="G42:J42"/>
     <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A6:J6"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="A7:J7"/>
@@ -8134,8 +8857,9 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8808,432 +9532,432 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="430" t="inlineStr">
+      <c r="A1" s="594" t="inlineStr">
         <is>
           <t>REF_CUSTOMER_MASTER</t>
         </is>
       </c>
-      <c r="B1" s="430" t="inlineStr">
+      <c r="B1" s="552" t="inlineStr">
         <is>
           <t>REF_EVIDENCE_LINK</t>
         </is>
       </c>
-      <c r="C1" s="430" t="inlineStr">
+      <c r="C1" s="552" t="inlineStr">
         <is>
           <t>REF_OWNER_PERSON_MASTER</t>
         </is>
       </c>
-      <c r="D1" s="430" t="inlineStr">
+      <c r="D1" s="552" t="inlineStr">
         <is>
           <t>REF_PART_REV_MASTER</t>
         </is>
       </c>
-      <c r="E1" s="430" t="n"/>
-      <c r="F1" s="430" t="n"/>
-      <c r="G1" s="430" t="n"/>
-      <c r="H1" s="430" t="n"/>
-      <c r="I1" s="430" t="n"/>
-      <c r="J1" s="430" t="n"/>
-      <c r="K1" s="430" t="n"/>
-      <c r="L1" s="430" t="n"/>
-      <c r="M1" s="430" t="n"/>
-      <c r="N1" s="430" t="n"/>
-      <c r="O1" s="430" t="n"/>
-      <c r="P1" s="430" t="n"/>
-      <c r="Q1" s="430" t="n"/>
-      <c r="R1" s="430" t="n"/>
-      <c r="S1" s="430" t="n"/>
-      <c r="T1" s="430" t="n"/>
-      <c r="U1" s="430" t="n"/>
-      <c r="V1" s="430" t="n"/>
-      <c r="W1" s="430" t="n"/>
-      <c r="X1" s="430" t="n"/>
-      <c r="Y1" s="430" t="n"/>
-      <c r="Z1" s="430" t="n"/>
-      <c r="AA1" s="430" t="n"/>
-      <c r="AB1" s="430" t="n"/>
-      <c r="AC1" s="430" t="n"/>
-      <c r="AD1" s="430" t="n"/>
-      <c r="AE1" s="430" t="n"/>
-      <c r="AF1" s="430" t="n"/>
-      <c r="AG1" s="430" t="n"/>
-      <c r="AH1" s="430" t="n"/>
-      <c r="AI1" s="430" t="n"/>
-      <c r="AJ1" s="430" t="n"/>
-      <c r="AK1" s="430" t="n"/>
-      <c r="AL1" s="430" t="n"/>
-      <c r="AM1" s="430" t="n"/>
-      <c r="AN1" s="430" t="n"/>
+      <c r="E1" s="552" t="n"/>
+      <c r="F1" s="552" t="n"/>
+      <c r="G1" s="552" t="n"/>
+      <c r="H1" s="552" t="n"/>
+      <c r="I1" s="552" t="n"/>
+      <c r="J1" s="552" t="n"/>
+      <c r="K1" s="552" t="n"/>
+      <c r="L1" s="552" t="n"/>
+      <c r="M1" s="552" t="n"/>
+      <c r="N1" s="552" t="n"/>
+      <c r="O1" s="552" t="n"/>
+      <c r="P1" s="552" t="n"/>
+      <c r="Q1" s="552" t="n"/>
+      <c r="R1" s="552" t="n"/>
+      <c r="S1" s="552" t="n"/>
+      <c r="T1" s="552" t="n"/>
+      <c r="U1" s="552" t="n"/>
+      <c r="V1" s="552" t="n"/>
+      <c r="W1" s="552" t="n"/>
+      <c r="X1" s="552" t="n"/>
+      <c r="Y1" s="552" t="n"/>
+      <c r="Z1" s="552" t="n"/>
+      <c r="AA1" s="552" t="n"/>
+      <c r="AB1" s="552" t="n"/>
+      <c r="AC1" s="552" t="n"/>
+      <c r="AD1" s="552" t="n"/>
+      <c r="AE1" s="552" t="n"/>
+      <c r="AF1" s="552" t="n"/>
+      <c r="AG1" s="552" t="n"/>
+      <c r="AH1" s="552" t="n"/>
+      <c r="AI1" s="552" t="n"/>
+      <c r="AJ1" s="552" t="n"/>
+      <c r="AK1" s="552" t="n"/>
+      <c r="AL1" s="552" t="n"/>
+      <c r="AM1" s="552" t="n"/>
+      <c r="AN1" s="595" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="430" t="inlineStr">
+      <c r="A2" s="592" t="inlineStr">
         <is>
           <t>CUST-001 Alpha Semi</t>
         </is>
       </c>
-      <c r="B2" s="430" t="inlineStr">
+      <c r="B2" s="437" t="inlineStr">
         <is>
           <t>M365://dossier/JOB-240001</t>
         </is>
       </c>
-      <c r="C2" s="430" t="inlineStr">
+      <c r="C2" s="437" t="inlineStr">
         <is>
           <t>Planning Lead</t>
         </is>
       </c>
-      <c r="D2" s="430" t="inlineStr">
+      <c r="D2" s="437" t="inlineStr">
         <is>
           <t>PN-1001 / Rev.A</t>
         </is>
       </c>
-      <c r="E2" s="430" t="n"/>
-      <c r="F2" s="430" t="n"/>
-      <c r="G2" s="430" t="n"/>
-      <c r="H2" s="430" t="n"/>
-      <c r="I2" s="430" t="n"/>
-      <c r="J2" s="430" t="n"/>
-      <c r="K2" s="430" t="n"/>
-      <c r="L2" s="430" t="n"/>
-      <c r="M2" s="430" t="n"/>
-      <c r="N2" s="430" t="n"/>
-      <c r="O2" s="430" t="n"/>
-      <c r="P2" s="430" t="n"/>
-      <c r="Q2" s="430" t="n"/>
-      <c r="R2" s="430" t="n"/>
-      <c r="S2" s="430" t="n"/>
-      <c r="T2" s="430" t="n"/>
-      <c r="U2" s="430" t="n"/>
-      <c r="V2" s="430" t="n"/>
-      <c r="W2" s="430" t="n"/>
-      <c r="X2" s="430" t="n"/>
-      <c r="Y2" s="430" t="n"/>
-      <c r="Z2" s="430" t="n"/>
-      <c r="AA2" s="430" t="n"/>
-      <c r="AB2" s="430" t="n"/>
-      <c r="AC2" s="430" t="n"/>
-      <c r="AD2" s="430" t="n"/>
-      <c r="AE2" s="430" t="n"/>
-      <c r="AF2" s="430" t="n"/>
-      <c r="AG2" s="430" t="n"/>
-      <c r="AH2" s="430" t="n"/>
-      <c r="AI2" s="430" t="n"/>
-      <c r="AJ2" s="430" t="n"/>
-      <c r="AK2" s="430" t="n"/>
-      <c r="AL2" s="430" t="n"/>
-      <c r="AM2" s="430" t="n"/>
-      <c r="AN2" s="430" t="n"/>
+      <c r="E2" s="437" t="n"/>
+      <c r="F2" s="437" t="n"/>
+      <c r="G2" s="437" t="n"/>
+      <c r="H2" s="437" t="n"/>
+      <c r="I2" s="437" t="n"/>
+      <c r="J2" s="437" t="n"/>
+      <c r="K2" s="437" t="n"/>
+      <c r="L2" s="437" t="n"/>
+      <c r="M2" s="437" t="n"/>
+      <c r="N2" s="437" t="n"/>
+      <c r="O2" s="437" t="n"/>
+      <c r="P2" s="437" t="n"/>
+      <c r="Q2" s="437" t="n"/>
+      <c r="R2" s="437" t="n"/>
+      <c r="S2" s="437" t="n"/>
+      <c r="T2" s="437" t="n"/>
+      <c r="U2" s="437" t="n"/>
+      <c r="V2" s="437" t="n"/>
+      <c r="W2" s="437" t="n"/>
+      <c r="X2" s="437" t="n"/>
+      <c r="Y2" s="437" t="n"/>
+      <c r="Z2" s="437" t="n"/>
+      <c r="AA2" s="437" t="n"/>
+      <c r="AB2" s="437" t="n"/>
+      <c r="AC2" s="437" t="n"/>
+      <c r="AD2" s="437" t="n"/>
+      <c r="AE2" s="437" t="n"/>
+      <c r="AF2" s="437" t="n"/>
+      <c r="AG2" s="437" t="n"/>
+      <c r="AH2" s="437" t="n"/>
+      <c r="AI2" s="437" t="n"/>
+      <c r="AJ2" s="437" t="n"/>
+      <c r="AK2" s="437" t="n"/>
+      <c r="AL2" s="437" t="n"/>
+      <c r="AM2" s="437" t="n"/>
+      <c r="AN2" s="564" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="430" t="inlineStr">
+      <c r="A3" s="592" t="inlineStr">
         <is>
           <t>CUST-002 NovaFab</t>
         </is>
       </c>
-      <c r="B3" s="430" t="inlineStr">
+      <c r="B3" s="437" t="inlineStr">
         <is>
           <t>SP://evidence/FRM-202/001</t>
         </is>
       </c>
-      <c r="C3" s="430" t="inlineStr">
+      <c r="C3" s="437" t="inlineStr">
         <is>
           <t>Production Supervisor</t>
         </is>
       </c>
-      <c r="D3" s="430" t="inlineStr">
+      <c r="D3" s="437" t="inlineStr">
         <is>
           <t>PN-1002 / Rev.B</t>
         </is>
       </c>
-      <c r="E3" s="430" t="n"/>
-      <c r="F3" s="430" t="n"/>
-      <c r="G3" s="430" t="n"/>
-      <c r="H3" s="430" t="n"/>
-      <c r="I3" s="430" t="n"/>
-      <c r="J3" s="430" t="n"/>
-      <c r="K3" s="430" t="n"/>
-      <c r="L3" s="430" t="n"/>
-      <c r="M3" s="430" t="n"/>
-      <c r="N3" s="430" t="n"/>
-      <c r="O3" s="430" t="n"/>
-      <c r="P3" s="430" t="n"/>
-      <c r="Q3" s="430" t="n"/>
-      <c r="R3" s="430" t="n"/>
-      <c r="S3" s="430" t="n"/>
-      <c r="T3" s="430" t="n"/>
-      <c r="U3" s="430" t="n"/>
-      <c r="V3" s="430" t="n"/>
-      <c r="W3" s="430" t="n"/>
-      <c r="X3" s="430" t="n"/>
-      <c r="Y3" s="430" t="n"/>
-      <c r="Z3" s="430" t="n"/>
-      <c r="AA3" s="430" t="n"/>
-      <c r="AB3" s="430" t="n"/>
-      <c r="AC3" s="430" t="n"/>
-      <c r="AD3" s="430" t="n"/>
-      <c r="AE3" s="430" t="n"/>
-      <c r="AF3" s="430" t="n"/>
-      <c r="AG3" s="430" t="n"/>
-      <c r="AH3" s="430" t="n"/>
-      <c r="AI3" s="430" t="n"/>
-      <c r="AJ3" s="430" t="n"/>
-      <c r="AK3" s="430" t="n"/>
-      <c r="AL3" s="430" t="n"/>
-      <c r="AM3" s="430" t="n"/>
-      <c r="AN3" s="430" t="n"/>
+      <c r="E3" s="437" t="n"/>
+      <c r="F3" s="437" t="n"/>
+      <c r="G3" s="437" t="n"/>
+      <c r="H3" s="437" t="n"/>
+      <c r="I3" s="437" t="n"/>
+      <c r="J3" s="437" t="n"/>
+      <c r="K3" s="437" t="n"/>
+      <c r="L3" s="437" t="n"/>
+      <c r="M3" s="437" t="n"/>
+      <c r="N3" s="437" t="n"/>
+      <c r="O3" s="437" t="n"/>
+      <c r="P3" s="437" t="n"/>
+      <c r="Q3" s="437" t="n"/>
+      <c r="R3" s="437" t="n"/>
+      <c r="S3" s="437" t="n"/>
+      <c r="T3" s="437" t="n"/>
+      <c r="U3" s="437" t="n"/>
+      <c r="V3" s="437" t="n"/>
+      <c r="W3" s="437" t="n"/>
+      <c r="X3" s="437" t="n"/>
+      <c r="Y3" s="437" t="n"/>
+      <c r="Z3" s="437" t="n"/>
+      <c r="AA3" s="437" t="n"/>
+      <c r="AB3" s="437" t="n"/>
+      <c r="AC3" s="437" t="n"/>
+      <c r="AD3" s="437" t="n"/>
+      <c r="AE3" s="437" t="n"/>
+      <c r="AF3" s="437" t="n"/>
+      <c r="AG3" s="437" t="n"/>
+      <c r="AH3" s="437" t="n"/>
+      <c r="AI3" s="437" t="n"/>
+      <c r="AJ3" s="437" t="n"/>
+      <c r="AK3" s="437" t="n"/>
+      <c r="AL3" s="437" t="n"/>
+      <c r="AM3" s="437" t="n"/>
+      <c r="AN3" s="564" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="430" t="inlineStr">
+      <c r="A4" s="592" t="inlineStr">
         <is>
           <t>CUST-003 Orion Tech</t>
         </is>
       </c>
-      <c r="B4" s="430" t="inlineStr">
+      <c r="B4" s="437" t="inlineStr">
         <is>
           <t>SP://evidence/FRM-306/002</t>
         </is>
       </c>
-      <c r="C4" s="430" t="inlineStr">
+      <c r="C4" s="437" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="D4" s="430" t="inlineStr">
+      <c r="D4" s="437" t="inlineStr">
         <is>
           <t>PN-1003 / Rev.C</t>
         </is>
       </c>
-      <c r="E4" s="430" t="n"/>
-      <c r="F4" s="430" t="n"/>
-      <c r="G4" s="430" t="n"/>
-      <c r="H4" s="430" t="n"/>
-      <c r="I4" s="430" t="n"/>
-      <c r="J4" s="430" t="n"/>
-      <c r="K4" s="430" t="n"/>
-      <c r="L4" s="430" t="n"/>
-      <c r="M4" s="430" t="n"/>
-      <c r="N4" s="430" t="n"/>
-      <c r="O4" s="430" t="n"/>
-      <c r="P4" s="430" t="n"/>
-      <c r="Q4" s="430" t="n"/>
-      <c r="R4" s="430" t="n"/>
-      <c r="S4" s="430" t="n"/>
-      <c r="T4" s="430" t="n"/>
-      <c r="U4" s="430" t="n"/>
-      <c r="V4" s="430" t="n"/>
-      <c r="W4" s="430" t="n"/>
-      <c r="X4" s="430" t="n"/>
-      <c r="Y4" s="430" t="n"/>
-      <c r="Z4" s="430" t="n"/>
-      <c r="AA4" s="430" t="n"/>
-      <c r="AB4" s="430" t="n"/>
-      <c r="AC4" s="430" t="n"/>
-      <c r="AD4" s="430" t="n"/>
-      <c r="AE4" s="430" t="n"/>
-      <c r="AF4" s="430" t="n"/>
-      <c r="AG4" s="430" t="n"/>
-      <c r="AH4" s="430" t="n"/>
-      <c r="AI4" s="430" t="n"/>
-      <c r="AJ4" s="430" t="n"/>
-      <c r="AK4" s="430" t="n"/>
-      <c r="AL4" s="430" t="n"/>
-      <c r="AM4" s="430" t="n"/>
-      <c r="AN4" s="430" t="n"/>
+      <c r="E4" s="437" t="n"/>
+      <c r="F4" s="437" t="n"/>
+      <c r="G4" s="437" t="n"/>
+      <c r="H4" s="437" t="n"/>
+      <c r="I4" s="437" t="n"/>
+      <c r="J4" s="437" t="n"/>
+      <c r="K4" s="437" t="n"/>
+      <c r="L4" s="437" t="n"/>
+      <c r="M4" s="437" t="n"/>
+      <c r="N4" s="437" t="n"/>
+      <c r="O4" s="437" t="n"/>
+      <c r="P4" s="437" t="n"/>
+      <c r="Q4" s="437" t="n"/>
+      <c r="R4" s="437" t="n"/>
+      <c r="S4" s="437" t="n"/>
+      <c r="T4" s="437" t="n"/>
+      <c r="U4" s="437" t="n"/>
+      <c r="V4" s="437" t="n"/>
+      <c r="W4" s="437" t="n"/>
+      <c r="X4" s="437" t="n"/>
+      <c r="Y4" s="437" t="n"/>
+      <c r="Z4" s="437" t="n"/>
+      <c r="AA4" s="437" t="n"/>
+      <c r="AB4" s="437" t="n"/>
+      <c r="AC4" s="437" t="n"/>
+      <c r="AD4" s="437" t="n"/>
+      <c r="AE4" s="437" t="n"/>
+      <c r="AF4" s="437" t="n"/>
+      <c r="AG4" s="437" t="n"/>
+      <c r="AH4" s="437" t="n"/>
+      <c r="AI4" s="437" t="n"/>
+      <c r="AJ4" s="437" t="n"/>
+      <c r="AK4" s="437" t="n"/>
+      <c r="AL4" s="437" t="n"/>
+      <c r="AM4" s="437" t="n"/>
+      <c r="AN4" s="564" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="430" t="inlineStr">
+      <c r="A5" s="592" t="inlineStr">
         <is>
           <t>CUST-004 Quantum Devices</t>
         </is>
       </c>
-      <c r="B5" s="430" t="inlineStr">
+      <c r="B5" s="437" t="inlineStr">
         <is>
           <t>Epicor://Job/JOB-240001</t>
         </is>
       </c>
-      <c r="C5" s="430" t="inlineStr">
+      <c r="C5" s="437" t="inlineStr">
         <is>
           <t>Engineering Lead</t>
         </is>
       </c>
-      <c r="D5" s="430" t="inlineStr">
+      <c r="D5" s="437" t="inlineStr">
         <is>
           <t>PN-1004 / Rev.D</t>
         </is>
       </c>
-      <c r="E5" s="430" t="n"/>
-      <c r="F5" s="430" t="n"/>
-      <c r="G5" s="430" t="n"/>
-      <c r="H5" s="430" t="n"/>
-      <c r="I5" s="430" t="n"/>
-      <c r="J5" s="430" t="n"/>
-      <c r="K5" s="430" t="n"/>
-      <c r="L5" s="430" t="n"/>
-      <c r="M5" s="430" t="n"/>
-      <c r="N5" s="430" t="n"/>
-      <c r="O5" s="430" t="n"/>
-      <c r="P5" s="430" t="n"/>
-      <c r="Q5" s="430" t="n"/>
-      <c r="R5" s="430" t="n"/>
-      <c r="S5" s="430" t="n"/>
-      <c r="T5" s="430" t="n"/>
-      <c r="U5" s="430" t="n"/>
-      <c r="V5" s="430" t="n"/>
-      <c r="W5" s="430" t="n"/>
-      <c r="X5" s="430" t="n"/>
-      <c r="Y5" s="430" t="n"/>
-      <c r="Z5" s="430" t="n"/>
-      <c r="AA5" s="430" t="n"/>
-      <c r="AB5" s="430" t="n"/>
-      <c r="AC5" s="430" t="n"/>
-      <c r="AD5" s="430" t="n"/>
-      <c r="AE5" s="430" t="n"/>
-      <c r="AF5" s="430" t="n"/>
-      <c r="AG5" s="430" t="n"/>
-      <c r="AH5" s="430" t="n"/>
-      <c r="AI5" s="430" t="n"/>
-      <c r="AJ5" s="430" t="n"/>
-      <c r="AK5" s="430" t="n"/>
-      <c r="AL5" s="430" t="n"/>
-      <c r="AM5" s="430" t="n"/>
-      <c r="AN5" s="430" t="n"/>
+      <c r="E5" s="437" t="n"/>
+      <c r="F5" s="437" t="n"/>
+      <c r="G5" s="437" t="n"/>
+      <c r="H5" s="437" t="n"/>
+      <c r="I5" s="437" t="n"/>
+      <c r="J5" s="437" t="n"/>
+      <c r="K5" s="437" t="n"/>
+      <c r="L5" s="437" t="n"/>
+      <c r="M5" s="437" t="n"/>
+      <c r="N5" s="437" t="n"/>
+      <c r="O5" s="437" t="n"/>
+      <c r="P5" s="437" t="n"/>
+      <c r="Q5" s="437" t="n"/>
+      <c r="R5" s="437" t="n"/>
+      <c r="S5" s="437" t="n"/>
+      <c r="T5" s="437" t="n"/>
+      <c r="U5" s="437" t="n"/>
+      <c r="V5" s="437" t="n"/>
+      <c r="W5" s="437" t="n"/>
+      <c r="X5" s="437" t="n"/>
+      <c r="Y5" s="437" t="n"/>
+      <c r="Z5" s="437" t="n"/>
+      <c r="AA5" s="437" t="n"/>
+      <c r="AB5" s="437" t="n"/>
+      <c r="AC5" s="437" t="n"/>
+      <c r="AD5" s="437" t="n"/>
+      <c r="AE5" s="437" t="n"/>
+      <c r="AF5" s="437" t="n"/>
+      <c r="AG5" s="437" t="n"/>
+      <c r="AH5" s="437" t="n"/>
+      <c r="AI5" s="437" t="n"/>
+      <c r="AJ5" s="437" t="n"/>
+      <c r="AK5" s="437" t="n"/>
+      <c r="AL5" s="437" t="n"/>
+      <c r="AM5" s="437" t="n"/>
+      <c r="AN5" s="564" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="430" t="n"/>
-      <c r="B6" s="430" t="n"/>
-      <c r="C6" s="430" t="inlineStr">
+      <c r="A6" s="592" t="n"/>
+      <c r="B6" s="437" t="n"/>
+      <c r="C6" s="437" t="inlineStr">
         <is>
           <t>Setup Technician</t>
         </is>
       </c>
-      <c r="D6" s="430" t="n"/>
-      <c r="E6" s="430" t="n"/>
-      <c r="F6" s="430" t="n"/>
-      <c r="G6" s="430" t="n"/>
-      <c r="H6" s="430" t="n"/>
-      <c r="I6" s="430" t="n"/>
-      <c r="J6" s="430" t="n"/>
-      <c r="K6" s="430" t="n"/>
-      <c r="L6" s="430" t="n"/>
-      <c r="M6" s="430" t="n"/>
-      <c r="N6" s="430" t="n"/>
-      <c r="O6" s="430" t="n"/>
-      <c r="P6" s="430" t="n"/>
-      <c r="Q6" s="430" t="n"/>
-      <c r="R6" s="430" t="n"/>
-      <c r="S6" s="430" t="n"/>
-      <c r="T6" s="430" t="n"/>
-      <c r="U6" s="430" t="n"/>
-      <c r="V6" s="430" t="n"/>
-      <c r="W6" s="430" t="n"/>
-      <c r="X6" s="430" t="n"/>
-      <c r="Y6" s="430" t="n"/>
-      <c r="Z6" s="430" t="n"/>
-      <c r="AA6" s="430" t="n"/>
-      <c r="AB6" s="430" t="n"/>
-      <c r="AC6" s="430" t="n"/>
-      <c r="AD6" s="430" t="n"/>
-      <c r="AE6" s="430" t="n"/>
-      <c r="AF6" s="430" t="n"/>
-      <c r="AG6" s="430" t="n"/>
-      <c r="AH6" s="430" t="n"/>
-      <c r="AI6" s="430" t="n"/>
-      <c r="AJ6" s="430" t="n"/>
-      <c r="AK6" s="430" t="n"/>
-      <c r="AL6" s="430" t="n"/>
-      <c r="AM6" s="430" t="n"/>
-      <c r="AN6" s="430" t="n"/>
+      <c r="D6" s="437" t="n"/>
+      <c r="E6" s="437" t="n"/>
+      <c r="F6" s="437" t="n"/>
+      <c r="G6" s="437" t="n"/>
+      <c r="H6" s="437" t="n"/>
+      <c r="I6" s="437" t="n"/>
+      <c r="J6" s="437" t="n"/>
+      <c r="K6" s="437" t="n"/>
+      <c r="L6" s="437" t="n"/>
+      <c r="M6" s="437" t="n"/>
+      <c r="N6" s="437" t="n"/>
+      <c r="O6" s="437" t="n"/>
+      <c r="P6" s="437" t="n"/>
+      <c r="Q6" s="437" t="n"/>
+      <c r="R6" s="437" t="n"/>
+      <c r="S6" s="437" t="n"/>
+      <c r="T6" s="437" t="n"/>
+      <c r="U6" s="437" t="n"/>
+      <c r="V6" s="437" t="n"/>
+      <c r="W6" s="437" t="n"/>
+      <c r="X6" s="437" t="n"/>
+      <c r="Y6" s="437" t="n"/>
+      <c r="Z6" s="437" t="n"/>
+      <c r="AA6" s="437" t="n"/>
+      <c r="AB6" s="437" t="n"/>
+      <c r="AC6" s="437" t="n"/>
+      <c r="AD6" s="437" t="n"/>
+      <c r="AE6" s="437" t="n"/>
+      <c r="AF6" s="437" t="n"/>
+      <c r="AG6" s="437" t="n"/>
+      <c r="AH6" s="437" t="n"/>
+      <c r="AI6" s="437" t="n"/>
+      <c r="AJ6" s="437" t="n"/>
+      <c r="AK6" s="437" t="n"/>
+      <c r="AL6" s="437" t="n"/>
+      <c r="AM6" s="437" t="n"/>
+      <c r="AN6" s="564" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="430" t="n"/>
-      <c r="B7" s="430" t="n"/>
-      <c r="C7" s="430" t="inlineStr">
+      <c r="A7" s="592" t="n"/>
+      <c r="B7" s="437" t="n"/>
+      <c r="C7" s="437" t="inlineStr">
         <is>
           <t>Maintenance Lead</t>
         </is>
       </c>
-      <c r="D7" s="430" t="n"/>
-      <c r="E7" s="430" t="n"/>
-      <c r="F7" s="430" t="n"/>
-      <c r="G7" s="430" t="n"/>
-      <c r="H7" s="430" t="n"/>
-      <c r="I7" s="430" t="n"/>
-      <c r="J7" s="430" t="n"/>
-      <c r="K7" s="430" t="n"/>
-      <c r="L7" s="430" t="n"/>
-      <c r="M7" s="430" t="n"/>
-      <c r="N7" s="430" t="n"/>
-      <c r="O7" s="430" t="n"/>
-      <c r="P7" s="430" t="n"/>
-      <c r="Q7" s="430" t="n"/>
-      <c r="R7" s="430" t="n"/>
-      <c r="S7" s="430" t="n"/>
-      <c r="T7" s="430" t="n"/>
-      <c r="U7" s="430" t="n"/>
-      <c r="V7" s="430" t="n"/>
-      <c r="W7" s="430" t="n"/>
-      <c r="X7" s="430" t="n"/>
-      <c r="Y7" s="430" t="n"/>
-      <c r="Z7" s="430" t="n"/>
-      <c r="AA7" s="430" t="n"/>
-      <c r="AB7" s="430" t="n"/>
-      <c r="AC7" s="430" t="n"/>
-      <c r="AD7" s="430" t="n"/>
-      <c r="AE7" s="430" t="n"/>
-      <c r="AF7" s="430" t="n"/>
-      <c r="AG7" s="430" t="n"/>
-      <c r="AH7" s="430" t="n"/>
-      <c r="AI7" s="430" t="n"/>
-      <c r="AJ7" s="430" t="n"/>
-      <c r="AK7" s="430" t="n"/>
-      <c r="AL7" s="430" t="n"/>
-      <c r="AM7" s="430" t="n"/>
-      <c r="AN7" s="430" t="n"/>
+      <c r="D7" s="437" t="n"/>
+      <c r="E7" s="437" t="n"/>
+      <c r="F7" s="437" t="n"/>
+      <c r="G7" s="437" t="n"/>
+      <c r="H7" s="437" t="n"/>
+      <c r="I7" s="437" t="n"/>
+      <c r="J7" s="437" t="n"/>
+      <c r="K7" s="437" t="n"/>
+      <c r="L7" s="437" t="n"/>
+      <c r="M7" s="437" t="n"/>
+      <c r="N7" s="437" t="n"/>
+      <c r="O7" s="437" t="n"/>
+      <c r="P7" s="437" t="n"/>
+      <c r="Q7" s="437" t="n"/>
+      <c r="R7" s="437" t="n"/>
+      <c r="S7" s="437" t="n"/>
+      <c r="T7" s="437" t="n"/>
+      <c r="U7" s="437" t="n"/>
+      <c r="V7" s="437" t="n"/>
+      <c r="W7" s="437" t="n"/>
+      <c r="X7" s="437" t="n"/>
+      <c r="Y7" s="437" t="n"/>
+      <c r="Z7" s="437" t="n"/>
+      <c r="AA7" s="437" t="n"/>
+      <c r="AB7" s="437" t="n"/>
+      <c r="AC7" s="437" t="n"/>
+      <c r="AD7" s="437" t="n"/>
+      <c r="AE7" s="437" t="n"/>
+      <c r="AF7" s="437" t="n"/>
+      <c r="AG7" s="437" t="n"/>
+      <c r="AH7" s="437" t="n"/>
+      <c r="AI7" s="437" t="n"/>
+      <c r="AJ7" s="437" t="n"/>
+      <c r="AK7" s="437" t="n"/>
+      <c r="AL7" s="437" t="n"/>
+      <c r="AM7" s="437" t="n"/>
+      <c r="AN7" s="564" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="447" t="n"/>
-      <c r="B8" s="447" t="n"/>
-      <c r="C8" s="447" t="inlineStr">
+      <c r="A8" s="596" t="n"/>
+      <c r="B8" s="572" t="n"/>
+      <c r="C8" s="572" t="inlineStr">
         <is>
           <t>Commercial Owner</t>
         </is>
       </c>
-      <c r="D8" s="447" t="n"/>
-      <c r="E8" s="447" t="n"/>
-      <c r="F8" s="447" t="n"/>
-      <c r="G8" s="447" t="n"/>
-      <c r="H8" s="447" t="n"/>
-      <c r="I8" s="447" t="n"/>
-      <c r="J8" s="447" t="n"/>
-      <c r="K8" s="447" t="n"/>
-      <c r="L8" s="447" t="n"/>
-      <c r="M8" s="447" t="n"/>
-      <c r="N8" s="447" t="n"/>
-      <c r="O8" s="447" t="n"/>
-      <c r="P8" s="447" t="n"/>
-      <c r="Q8" s="447" t="n"/>
-      <c r="R8" s="447" t="n"/>
-      <c r="S8" s="447" t="n"/>
-      <c r="T8" s="447" t="n"/>
-      <c r="U8" s="447" t="n"/>
-      <c r="V8" s="447" t="n"/>
-      <c r="W8" s="447" t="n"/>
-      <c r="X8" s="447" t="n"/>
-      <c r="Y8" s="447" t="n"/>
-      <c r="Z8" s="447" t="n"/>
-      <c r="AA8" s="447" t="n"/>
-      <c r="AB8" s="447" t="n"/>
-      <c r="AC8" s="447" t="n"/>
-      <c r="AD8" s="447" t="n"/>
-      <c r="AE8" s="447" t="n"/>
-      <c r="AF8" s="447" t="n"/>
-      <c r="AG8" s="447" t="n"/>
-      <c r="AH8" s="447" t="n"/>
-      <c r="AI8" s="447" t="n"/>
-      <c r="AJ8" s="447" t="n"/>
-      <c r="AK8" s="447" t="n"/>
-      <c r="AL8" s="447" t="n"/>
-      <c r="AM8" s="447" t="n"/>
-      <c r="AN8" s="447" t="n"/>
+      <c r="D8" s="572" t="n"/>
+      <c r="E8" s="572" t="n"/>
+      <c r="F8" s="572" t="n"/>
+      <c r="G8" s="572" t="n"/>
+      <c r="H8" s="572" t="n"/>
+      <c r="I8" s="572" t="n"/>
+      <c r="J8" s="572" t="n"/>
+      <c r="K8" s="572" t="n"/>
+      <c r="L8" s="572" t="n"/>
+      <c r="M8" s="572" t="n"/>
+      <c r="N8" s="572" t="n"/>
+      <c r="O8" s="572" t="n"/>
+      <c r="P8" s="572" t="n"/>
+      <c r="Q8" s="572" t="n"/>
+      <c r="R8" s="572" t="n"/>
+      <c r="S8" s="572" t="n"/>
+      <c r="T8" s="572" t="n"/>
+      <c r="U8" s="572" t="n"/>
+      <c r="V8" s="572" t="n"/>
+      <c r="W8" s="572" t="n"/>
+      <c r="X8" s="572" t="n"/>
+      <c r="Y8" s="572" t="n"/>
+      <c r="Z8" s="572" t="n"/>
+      <c r="AA8" s="572" t="n"/>
+      <c r="AB8" s="572" t="n"/>
+      <c r="AC8" s="572" t="n"/>
+      <c r="AD8" s="572" t="n"/>
+      <c r="AE8" s="572" t="n"/>
+      <c r="AF8" s="572" t="n"/>
+      <c r="AG8" s="572" t="n"/>
+      <c r="AH8" s="572" t="n"/>
+      <c r="AI8" s="572" t="n"/>
+      <c r="AJ8" s="572" t="n"/>
+      <c r="AK8" s="572" t="n"/>
+      <c r="AL8" s="572" t="n"/>
+      <c r="AM8" s="572" t="n"/>
+      <c r="AN8" s="573" t="n"/>
     </row>
     <row r="9" hidden="1"/>
     <row r="10" hidden="1"/>
@@ -9485,644 +10209,646 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="424" t="n"/>
-      <c r="B1" s="496" t="n"/>
-      <c r="C1" s="426" t="inlineStr">
+      <c r="A1" s="505" t="n"/>
+      <c r="B1" s="506" t="n"/>
+      <c r="C1" s="507" t="inlineStr">
         <is>
           <t>PERIODIC REVIEW RECORD</t>
         </is>
       </c>
-      <c r="D1" s="497" t="n"/>
-      <c r="E1" s="497" t="n"/>
-      <c r="F1" s="496" t="n"/>
-      <c r="G1" s="428" t="inlineStr">
+      <c r="D1" s="506" t="n"/>
+      <c r="E1" s="506" t="n"/>
+      <c r="F1" s="506" t="n"/>
+      <c r="G1" s="597" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="H1" s="429" t="inlineStr">
+      <c r="H1" s="598" t="inlineStr">
         <is>
           <t>FRM-213</t>
         </is>
       </c>
-      <c r="I1" s="430" t="n"/>
-      <c r="J1" s="430" t="n"/>
-      <c r="K1" s="430" t="n"/>
-      <c r="L1" s="430" t="n"/>
-      <c r="M1" s="430" t="n"/>
-      <c r="N1" s="430" t="n"/>
-      <c r="O1" s="430" t="n"/>
-      <c r="P1" s="430" t="n"/>
-      <c r="Q1" s="430" t="n"/>
-      <c r="R1" s="430" t="n"/>
-      <c r="S1" s="430" t="n"/>
-      <c r="T1" s="430" t="n"/>
-      <c r="U1" s="430" t="n"/>
-      <c r="V1" s="430" t="n"/>
-      <c r="W1" s="430" t="n"/>
-      <c r="X1" s="430" t="n"/>
-      <c r="Y1" s="430" t="n"/>
-      <c r="Z1" s="430" t="n"/>
-      <c r="AA1" s="430" t="n"/>
-      <c r="AB1" s="430" t="n"/>
-      <c r="AC1" s="430" t="n"/>
-      <c r="AD1" s="430" t="n"/>
-      <c r="AE1" s="430" t="n"/>
-      <c r="AF1" s="430" t="n"/>
-      <c r="AG1" s="430" t="n"/>
-      <c r="AH1" s="430" t="n"/>
-      <c r="AI1" s="430" t="n"/>
-      <c r="AJ1" s="430" t="n"/>
-      <c r="AK1" s="430" t="n"/>
-      <c r="AL1" s="430" t="n"/>
-      <c r="AM1" s="430" t="n"/>
-      <c r="AN1" s="430" t="n"/>
+      <c r="I1" s="509" t="n"/>
+      <c r="J1" s="510" t="n"/>
+      <c r="K1" s="510" t="n"/>
+      <c r="L1" s="510" t="n"/>
+      <c r="M1" s="510" t="n"/>
+      <c r="N1" s="510" t="n"/>
+      <c r="O1" s="510" t="n"/>
+      <c r="P1" s="510" t="n"/>
+      <c r="Q1" s="510" t="n"/>
+      <c r="R1" s="510" t="n"/>
+      <c r="S1" s="510" t="n"/>
+      <c r="T1" s="510" t="n"/>
+      <c r="U1" s="510" t="n"/>
+      <c r="V1" s="510" t="n"/>
+      <c r="W1" s="510" t="n"/>
+      <c r="X1" s="510" t="n"/>
+      <c r="Y1" s="510" t="n"/>
+      <c r="Z1" s="510" t="n"/>
+      <c r="AA1" s="510" t="n"/>
+      <c r="AB1" s="510" t="n"/>
+      <c r="AC1" s="510" t="n"/>
+      <c r="AD1" s="511" t="n"/>
+      <c r="AE1" s="512" t="n"/>
+      <c r="AF1" s="513" t="n"/>
+      <c r="AG1" s="513" t="n"/>
+      <c r="AH1" s="514" t="n"/>
+      <c r="AI1" s="515" t="n"/>
+      <c r="AJ1" s="516" t="n"/>
+      <c r="AK1" s="516" t="n"/>
+      <c r="AL1" s="516" t="n"/>
+      <c r="AM1" s="516" t="n"/>
+      <c r="AN1" s="517" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="498" t="n"/>
-      <c r="B2" s="499" t="n"/>
-      <c r="C2" s="498" t="n"/>
-      <c r="F2" s="499" t="n"/>
-      <c r="G2" s="428" t="inlineStr">
+      <c r="A2" s="518" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="599" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="H2" s="429" t="inlineStr">
+      <c r="H2" s="600" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="I2" s="430" t="n"/>
-      <c r="J2" s="430" t="n"/>
-      <c r="K2" s="430" t="n"/>
-      <c r="L2" s="430" t="n"/>
-      <c r="M2" s="430" t="n"/>
-      <c r="N2" s="430" t="n"/>
-      <c r="O2" s="430" t="n"/>
-      <c r="P2" s="430" t="n"/>
-      <c r="Q2" s="430" t="n"/>
-      <c r="R2" s="430" t="n"/>
-      <c r="S2" s="430" t="n"/>
-      <c r="T2" s="430" t="n"/>
-      <c r="U2" s="430" t="n"/>
-      <c r="V2" s="430" t="n"/>
-      <c r="W2" s="430" t="n"/>
-      <c r="X2" s="430" t="n"/>
-      <c r="Y2" s="430" t="n"/>
-      <c r="Z2" s="430" t="n"/>
-      <c r="AA2" s="430" t="n"/>
-      <c r="AB2" s="430" t="n"/>
-      <c r="AC2" s="430" t="n"/>
-      <c r="AD2" s="430" t="n"/>
-      <c r="AE2" s="430" t="n"/>
-      <c r="AF2" s="430" t="n"/>
-      <c r="AG2" s="430" t="n"/>
-      <c r="AH2" s="430" t="n"/>
-      <c r="AI2" s="430" t="n"/>
-      <c r="AJ2" s="430" t="n"/>
-      <c r="AK2" s="430" t="n"/>
-      <c r="AL2" s="430" t="n"/>
-      <c r="AM2" s="430" t="n"/>
-      <c r="AN2" s="430" t="n"/>
+      <c r="I2" s="520" t="n"/>
+      <c r="J2" s="521" t="n"/>
+      <c r="K2" s="521" t="n"/>
+      <c r="L2" s="521" t="n"/>
+      <c r="M2" s="521" t="n"/>
+      <c r="N2" s="521" t="n"/>
+      <c r="O2" s="521" t="n"/>
+      <c r="P2" s="521" t="n"/>
+      <c r="Q2" s="521" t="n"/>
+      <c r="R2" s="521" t="n"/>
+      <c r="S2" s="521" t="n"/>
+      <c r="T2" s="521" t="n"/>
+      <c r="U2" s="521" t="n"/>
+      <c r="V2" s="521" t="n"/>
+      <c r="W2" s="521" t="n"/>
+      <c r="X2" s="521" t="n"/>
+      <c r="Y2" s="521" t="n"/>
+      <c r="Z2" s="521" t="n"/>
+      <c r="AA2" s="521" t="n"/>
+      <c r="AB2" s="521" t="n"/>
+      <c r="AC2" s="521" t="n"/>
+      <c r="AD2" s="522" t="n"/>
+      <c r="AE2" s="523" t="n"/>
+      <c r="AF2" s="524" t="n"/>
+      <c r="AG2" s="524" t="n"/>
+      <c r="AH2" s="525" t="n"/>
+      <c r="AI2" s="526" t="n"/>
+      <c r="AJ2" s="527" t="n"/>
+      <c r="AK2" s="527" t="n"/>
+      <c r="AL2" s="527" t="n"/>
+      <c r="AM2" s="527" t="n"/>
+      <c r="AN2" s="528" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="498" t="n"/>
-      <c r="B3" s="499" t="n"/>
-      <c r="C3" s="500" t="n"/>
-      <c r="D3" s="501" t="n"/>
-      <c r="E3" s="501" t="n"/>
-      <c r="F3" s="502" t="n"/>
-      <c r="G3" s="428" t="inlineStr">
+      <c r="A3" s="518" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="599" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="H3" s="429" t="inlineStr">
+      <c r="H3" s="600" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I3" s="430" t="n"/>
-      <c r="J3" s="430" t="n"/>
-      <c r="K3" s="430" t="n"/>
-      <c r="L3" s="430" t="n"/>
-      <c r="M3" s="430" t="n"/>
-      <c r="N3" s="430" t="n"/>
-      <c r="O3" s="430" t="n"/>
-      <c r="P3" s="430" t="n"/>
-      <c r="Q3" s="430" t="n"/>
-      <c r="R3" s="430" t="n"/>
-      <c r="S3" s="430" t="n"/>
-      <c r="T3" s="430" t="n"/>
-      <c r="U3" s="430" t="n"/>
-      <c r="V3" s="430" t="n"/>
-      <c r="W3" s="430" t="n"/>
-      <c r="X3" s="430" t="n"/>
-      <c r="Y3" s="430" t="n"/>
-      <c r="Z3" s="430" t="n"/>
-      <c r="AA3" s="430" t="n"/>
-      <c r="AB3" s="430" t="n"/>
-      <c r="AC3" s="430" t="n"/>
-      <c r="AD3" s="430" t="n"/>
-      <c r="AE3" s="430" t="n"/>
-      <c r="AF3" s="430" t="n"/>
-      <c r="AG3" s="430" t="n"/>
-      <c r="AH3" s="430" t="n"/>
-      <c r="AI3" s="430" t="n"/>
-      <c r="AJ3" s="430" t="n"/>
-      <c r="AK3" s="430" t="n"/>
-      <c r="AL3" s="430" t="n"/>
-      <c r="AM3" s="430" t="n"/>
-      <c r="AN3" s="430" t="n"/>
+      <c r="I3" s="520" t="n"/>
+      <c r="J3" s="521" t="n"/>
+      <c r="K3" s="521" t="n"/>
+      <c r="L3" s="521" t="n"/>
+      <c r="M3" s="521" t="n"/>
+      <c r="N3" s="521" t="n"/>
+      <c r="O3" s="521" t="n"/>
+      <c r="P3" s="521" t="n"/>
+      <c r="Q3" s="521" t="n"/>
+      <c r="R3" s="521" t="n"/>
+      <c r="S3" s="521" t="n"/>
+      <c r="T3" s="521" t="n"/>
+      <c r="U3" s="521" t="n"/>
+      <c r="V3" s="521" t="n"/>
+      <c r="W3" s="521" t="n"/>
+      <c r="X3" s="521" t="n"/>
+      <c r="Y3" s="521" t="n"/>
+      <c r="Z3" s="521" t="n"/>
+      <c r="AA3" s="521" t="n"/>
+      <c r="AB3" s="521" t="n"/>
+      <c r="AC3" s="521" t="n"/>
+      <c r="AD3" s="522" t="n"/>
+      <c r="AE3" s="523" t="n"/>
+      <c r="AF3" s="524" t="n"/>
+      <c r="AG3" s="524" t="n"/>
+      <c r="AH3" s="525" t="n"/>
+      <c r="AI3" s="526" t="n"/>
+      <c r="AJ3" s="527" t="n"/>
+      <c r="AK3" s="527" t="n"/>
+      <c r="AL3" s="527" t="n"/>
+      <c r="AM3" s="527" t="n"/>
+      <c r="AN3" s="528" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="498" t="n"/>
-      <c r="B4" s="499" t="n"/>
-      <c r="C4" s="436" t="inlineStr">
+      <c r="A4" s="518" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="529" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="503" t="n"/>
-      <c r="E4" s="503" t="n"/>
-      <c r="F4" s="504" t="n"/>
-      <c r="G4" s="428" t="inlineStr">
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="599" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H4" s="429" t="inlineStr">
+      <c r="H4" s="600" t="inlineStr">
         <is>
           <t>QA / Customer Service</t>
         </is>
       </c>
-      <c r="I4" s="430" t="n"/>
-      <c r="J4" s="430" t="n"/>
-      <c r="K4" s="430" t="n"/>
-      <c r="L4" s="430" t="n"/>
-      <c r="M4" s="430" t="n"/>
-      <c r="N4" s="430" t="n"/>
-      <c r="O4" s="430" t="n"/>
-      <c r="P4" s="430" t="n"/>
-      <c r="Q4" s="430" t="n"/>
-      <c r="R4" s="430" t="n"/>
-      <c r="S4" s="430" t="n"/>
-      <c r="T4" s="430" t="n"/>
-      <c r="U4" s="430" t="n"/>
-      <c r="V4" s="430" t="n"/>
-      <c r="W4" s="430" t="n"/>
-      <c r="X4" s="430" t="n"/>
-      <c r="Y4" s="430" t="n"/>
-      <c r="Z4" s="430" t="n"/>
-      <c r="AA4" s="430" t="n"/>
-      <c r="AB4" s="430" t="n"/>
-      <c r="AC4" s="430" t="n"/>
-      <c r="AD4" s="430" t="n"/>
-      <c r="AE4" s="430" t="n"/>
-      <c r="AF4" s="430" t="n"/>
-      <c r="AG4" s="430" t="n"/>
-      <c r="AH4" s="430" t="n"/>
-      <c r="AI4" s="430" t="n"/>
-      <c r="AJ4" s="430" t="n"/>
-      <c r="AK4" s="430" t="n"/>
-      <c r="AL4" s="430" t="n"/>
-      <c r="AM4" s="430" t="n"/>
-      <c r="AN4" s="430" t="n"/>
+      <c r="I4" s="530" t="n"/>
+      <c r="J4" s="531" t="n"/>
+      <c r="K4" s="531" t="n"/>
+      <c r="L4" s="531" t="n"/>
+      <c r="M4" s="531" t="n"/>
+      <c r="N4" s="531" t="n"/>
+      <c r="O4" s="531" t="n"/>
+      <c r="P4" s="531" t="n"/>
+      <c r="Q4" s="531" t="n"/>
+      <c r="R4" s="531" t="n"/>
+      <c r="S4" s="531" t="n"/>
+      <c r="T4" s="531" t="n"/>
+      <c r="U4" s="531" t="n"/>
+      <c r="V4" s="531" t="n"/>
+      <c r="W4" s="531" t="n"/>
+      <c r="X4" s="531" t="n"/>
+      <c r="Y4" s="531" t="n"/>
+      <c r="Z4" s="531" t="n"/>
+      <c r="AA4" s="531" t="n"/>
+      <c r="AB4" s="531" t="n"/>
+      <c r="AC4" s="531" t="n"/>
+      <c r="AD4" s="532" t="n"/>
+      <c r="AE4" s="523" t="n"/>
+      <c r="AF4" s="524" t="n"/>
+      <c r="AG4" s="524" t="n"/>
+      <c r="AH4" s="525" t="n"/>
+      <c r="AI4" s="526" t="n"/>
+      <c r="AJ4" s="527" t="n"/>
+      <c r="AK4" s="527" t="n"/>
+      <c r="AL4" s="527" t="n"/>
+      <c r="AM4" s="527" t="n"/>
+      <c r="AN4" s="528" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="500" t="n"/>
-      <c r="B5" s="502" t="n"/>
-      <c r="C5" s="439" t="inlineStr">
+      <c r="A5" s="533" t="n"/>
+      <c r="B5" s="534" t="n"/>
+      <c r="C5" s="535" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="503" t="n"/>
-      <c r="E5" s="503" t="n"/>
-      <c r="F5" s="504" t="n"/>
-      <c r="G5" s="440" t="inlineStr">
+      <c r="D5" s="534" t="n"/>
+      <c r="E5" s="534" t="n"/>
+      <c r="F5" s="534" t="n"/>
+      <c r="G5" s="601" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="H5" s="441" t="inlineStr">
+      <c r="H5" s="602" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
       </c>
-      <c r="I5" s="430" t="n"/>
-      <c r="J5" s="430" t="n"/>
-      <c r="K5" s="430" t="n"/>
-      <c r="L5" s="430" t="n"/>
-      <c r="M5" s="430" t="n"/>
-      <c r="N5" s="430" t="n"/>
-      <c r="O5" s="430" t="n"/>
-      <c r="P5" s="430" t="n"/>
-      <c r="Q5" s="430" t="n"/>
-      <c r="R5" s="430" t="n"/>
-      <c r="S5" s="430" t="n"/>
-      <c r="T5" s="430" t="n"/>
-      <c r="U5" s="430" t="n"/>
-      <c r="V5" s="430" t="n"/>
-      <c r="W5" s="430" t="n"/>
-      <c r="X5" s="430" t="n"/>
-      <c r="Y5" s="430" t="n"/>
-      <c r="Z5" s="430" t="n"/>
-      <c r="AA5" s="430" t="n"/>
-      <c r="AB5" s="430" t="n"/>
-      <c r="AC5" s="430" t="n"/>
-      <c r="AD5" s="430" t="n"/>
-      <c r="AE5" s="430" t="n"/>
-      <c r="AF5" s="430" t="n"/>
-      <c r="AG5" s="430" t="n"/>
-      <c r="AH5" s="430" t="n"/>
-      <c r="AI5" s="430" t="n"/>
-      <c r="AJ5" s="430" t="n"/>
-      <c r="AK5" s="430" t="n"/>
-      <c r="AL5" s="430" t="n"/>
-      <c r="AM5" s="430" t="n"/>
-      <c r="AN5" s="430" t="n"/>
+      <c r="I5" s="537" t="n"/>
+      <c r="J5" s="538" t="n"/>
+      <c r="K5" s="538" t="n"/>
+      <c r="L5" s="538" t="n"/>
+      <c r="M5" s="538" t="n"/>
+      <c r="N5" s="538" t="n"/>
+      <c r="O5" s="538" t="n"/>
+      <c r="P5" s="538" t="n"/>
+      <c r="Q5" s="538" t="n"/>
+      <c r="R5" s="538" t="n"/>
+      <c r="S5" s="538" t="n"/>
+      <c r="T5" s="538" t="n"/>
+      <c r="U5" s="538" t="n"/>
+      <c r="V5" s="538" t="n"/>
+      <c r="W5" s="538" t="n"/>
+      <c r="X5" s="538" t="n"/>
+      <c r="Y5" s="538" t="n"/>
+      <c r="Z5" s="538" t="n"/>
+      <c r="AA5" s="538" t="n"/>
+      <c r="AB5" s="538" t="n"/>
+      <c r="AC5" s="538" t="n"/>
+      <c r="AD5" s="539" t="n"/>
+      <c r="AE5" s="540" t="n"/>
+      <c r="AF5" s="541" t="n"/>
+      <c r="AG5" s="541" t="n"/>
+      <c r="AH5" s="542" t="n"/>
+      <c r="AI5" s="543" t="n"/>
+      <c r="AJ5" s="544" t="n"/>
+      <c r="AK5" s="544" t="n"/>
+      <c r="AL5" s="544" t="n"/>
+      <c r="AM5" s="544" t="n"/>
+      <c r="AN5" s="545" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="442" t="n"/>
-      <c r="B6" s="495" t="n"/>
-      <c r="C6" s="495" t="n"/>
-      <c r="D6" s="495" t="n"/>
-      <c r="E6" s="495" t="n"/>
-      <c r="F6" s="495" t="n"/>
-      <c r="G6" s="495" t="n"/>
-      <c r="H6" s="495" t="n"/>
-      <c r="I6" s="443" t="n"/>
-      <c r="J6" s="443" t="n"/>
-      <c r="K6" s="443" t="n"/>
-      <c r="L6" s="443" t="n"/>
-      <c r="M6" s="443" t="n"/>
-      <c r="N6" s="443" t="n"/>
-      <c r="O6" s="443" t="n"/>
-      <c r="P6" s="443" t="n"/>
-      <c r="Q6" s="443" t="n"/>
-      <c r="R6" s="443" t="n"/>
-      <c r="S6" s="443" t="n"/>
-      <c r="T6" s="443" t="n"/>
-      <c r="U6" s="443" t="n"/>
-      <c r="V6" s="443" t="n"/>
-      <c r="W6" s="443" t="n"/>
-      <c r="X6" s="443" t="n"/>
-      <c r="Y6" s="443" t="n"/>
-      <c r="Z6" s="443" t="n"/>
-      <c r="AA6" s="443" t="n"/>
-      <c r="AB6" s="443" t="n"/>
-      <c r="AC6" s="443" t="n"/>
-      <c r="AD6" s="443" t="n"/>
-      <c r="AE6" s="443" t="n"/>
-      <c r="AF6" s="443" t="n"/>
-      <c r="AG6" s="443" t="n"/>
-      <c r="AH6" s="443" t="n"/>
-      <c r="AI6" s="443" t="n"/>
-      <c r="AJ6" s="443" t="n"/>
-      <c r="AK6" s="443" t="n"/>
-      <c r="AL6" s="443" t="n"/>
-      <c r="AM6" s="443" t="n"/>
-      <c r="AN6" s="443" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="546" t="n"/>
+      <c r="B6" s="547" t="n"/>
+      <c r="C6" s="547" t="n"/>
+      <c r="D6" s="547" t="n"/>
+      <c r="E6" s="547" t="n"/>
+      <c r="F6" s="547" t="n"/>
+      <c r="G6" s="547" t="n"/>
+      <c r="H6" s="547" t="n"/>
+      <c r="I6" s="547" t="n"/>
+      <c r="J6" s="547" t="n"/>
+      <c r="K6" s="547" t="n"/>
+      <c r="L6" s="547" t="n"/>
+      <c r="M6" s="547" t="n"/>
+      <c r="N6" s="547" t="n"/>
+      <c r="O6" s="547" t="n"/>
+      <c r="P6" s="547" t="n"/>
+      <c r="Q6" s="547" t="n"/>
+      <c r="R6" s="547" t="n"/>
+      <c r="S6" s="547" t="n"/>
+      <c r="T6" s="547" t="n"/>
+      <c r="U6" s="547" t="n"/>
+      <c r="V6" s="547" t="n"/>
+      <c r="W6" s="547" t="n"/>
+      <c r="X6" s="547" t="n"/>
+      <c r="Y6" s="547" t="n"/>
+      <c r="Z6" s="547" t="n"/>
+      <c r="AA6" s="547" t="n"/>
+      <c r="AB6" s="547" t="n"/>
+      <c r="AC6" s="547" t="n"/>
+      <c r="AD6" s="547" t="n"/>
+      <c r="AE6" s="547" t="n"/>
+      <c r="AF6" s="547" t="n"/>
+      <c r="AG6" s="547" t="n"/>
+      <c r="AH6" s="547" t="n"/>
+      <c r="AI6" s="547" t="n"/>
+      <c r="AJ6" s="547" t="n"/>
+      <c r="AK6" s="547" t="n"/>
+      <c r="AL6" s="547" t="n"/>
+      <c r="AM6" s="547" t="n"/>
+      <c r="AN6" s="547" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="444" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="548" t="inlineStr">
         <is>
           <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
         </is>
       </c>
-      <c r="B7" s="503" t="n"/>
-      <c r="C7" s="503" t="n"/>
-      <c r="D7" s="503" t="n"/>
-      <c r="E7" s="503" t="n"/>
-      <c r="F7" s="503" t="n"/>
-      <c r="G7" s="503" t="n"/>
-      <c r="H7" s="504" t="n"/>
-      <c r="I7" s="430" t="n"/>
-      <c r="J7" s="430" t="n"/>
-      <c r="K7" s="430" t="n"/>
-      <c r="L7" s="430" t="n"/>
-      <c r="M7" s="430" t="n"/>
-      <c r="N7" s="430" t="n"/>
-      <c r="O7" s="430" t="n"/>
-      <c r="P7" s="430" t="n"/>
-      <c r="Q7" s="430" t="n"/>
-      <c r="R7" s="430" t="n"/>
-      <c r="S7" s="430" t="n"/>
-      <c r="T7" s="430" t="n"/>
-      <c r="U7" s="430" t="n"/>
-      <c r="V7" s="430" t="n"/>
-      <c r="W7" s="430" t="n"/>
-      <c r="X7" s="430" t="n"/>
-      <c r="Y7" s="430" t="n"/>
-      <c r="Z7" s="430" t="n"/>
-      <c r="AA7" s="430" t="n"/>
-      <c r="AB7" s="430" t="n"/>
-      <c r="AC7" s="430" t="n"/>
-      <c r="AD7" s="430" t="n"/>
-      <c r="AE7" s="430" t="n"/>
-      <c r="AF7" s="430" t="n"/>
-      <c r="AG7" s="430" t="n"/>
-      <c r="AH7" s="430" t="n"/>
-      <c r="AI7" s="430" t="n"/>
-      <c r="AJ7" s="430" t="n"/>
-      <c r="AK7" s="430" t="n"/>
-      <c r="AL7" s="430" t="n"/>
-      <c r="AM7" s="430" t="n"/>
-      <c r="AN7" s="430" t="n"/>
+      <c r="B7" s="549" t="n"/>
+      <c r="C7" s="549" t="n"/>
+      <c r="D7" s="549" t="n"/>
+      <c r="E7" s="549" t="n"/>
+      <c r="F7" s="549" t="n"/>
+      <c r="G7" s="549" t="n"/>
+      <c r="H7" s="549" t="n"/>
+      <c r="I7" s="549" t="n"/>
+      <c r="J7" s="549" t="n"/>
+      <c r="K7" s="549" t="n"/>
+      <c r="L7" s="549" t="n"/>
+      <c r="M7" s="549" t="n"/>
+      <c r="N7" s="549" t="n"/>
+      <c r="O7" s="549" t="n"/>
+      <c r="P7" s="549" t="n"/>
+      <c r="Q7" s="549" t="n"/>
+      <c r="R7" s="549" t="n"/>
+      <c r="S7" s="549" t="n"/>
+      <c r="T7" s="549" t="n"/>
+      <c r="U7" s="549" t="n"/>
+      <c r="V7" s="549" t="n"/>
+      <c r="W7" s="549" t="n"/>
+      <c r="X7" s="549" t="n"/>
+      <c r="Y7" s="549" t="n"/>
+      <c r="Z7" s="549" t="n"/>
+      <c r="AA7" s="549" t="n"/>
+      <c r="AB7" s="549" t="n"/>
+      <c r="AC7" s="549" t="n"/>
+      <c r="AD7" s="549" t="n"/>
+      <c r="AE7" s="549" t="n"/>
+      <c r="AF7" s="549" t="n"/>
+      <c r="AG7" s="549" t="n"/>
+      <c r="AH7" s="549" t="n"/>
+      <c r="AI7" s="549" t="n"/>
+      <c r="AJ7" s="549" t="n"/>
+      <c r="AK7" s="549" t="n"/>
+      <c r="AL7" s="549" t="n"/>
+      <c r="AM7" s="549" t="n"/>
+      <c r="AN7" s="550" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="440" t="inlineStr">
+      <c r="A8" s="551" t="inlineStr">
         <is>
           <t>Parent Form</t>
         </is>
       </c>
-      <c r="B8" s="486" t="n"/>
-      <c r="C8" s="441" t="inlineStr">
+      <c r="B8" s="552" t="n"/>
+      <c r="C8" s="553" t="inlineStr">
         <is>
           <t>FRM-213 · RMA TRACKING LOG</t>
         </is>
       </c>
-      <c r="D8" s="486" t="n"/>
-      <c r="E8" s="440" t="inlineStr">
+      <c r="D8" s="552" t="n"/>
+      <c r="E8" s="554" t="inlineStr">
         <is>
           <t>Support Tab</t>
         </is>
       </c>
-      <c r="F8" s="486" t="n"/>
-      <c r="G8" s="441" t="inlineStr">
+      <c r="F8" s="552" t="n"/>
+      <c r="G8" s="553" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="H8" s="486" t="n"/>
-      <c r="I8" s="447" t="n"/>
-      <c r="J8" s="447" t="n"/>
-      <c r="K8" s="447" t="n"/>
-      <c r="L8" s="447" t="n"/>
-      <c r="M8" s="447" t="n"/>
-      <c r="N8" s="447" t="n"/>
-      <c r="O8" s="447" t="n"/>
-      <c r="P8" s="447" t="n"/>
-      <c r="Q8" s="447" t="n"/>
-      <c r="R8" s="447" t="n"/>
-      <c r="S8" s="447" t="n"/>
-      <c r="T8" s="447" t="n"/>
-      <c r="U8" s="447" t="n"/>
-      <c r="V8" s="447" t="n"/>
-      <c r="W8" s="447" t="n"/>
-      <c r="X8" s="447" t="n"/>
-      <c r="Y8" s="447" t="n"/>
-      <c r="Z8" s="447" t="n"/>
-      <c r="AA8" s="447" t="n"/>
-      <c r="AB8" s="447" t="n"/>
-      <c r="AC8" s="447" t="n"/>
-      <c r="AD8" s="447" t="n"/>
-      <c r="AE8" s="447" t="n"/>
-      <c r="AF8" s="447" t="n"/>
-      <c r="AG8" s="447" t="n"/>
-      <c r="AH8" s="447" t="n"/>
-      <c r="AI8" s="447" t="n"/>
-      <c r="AJ8" s="447" t="n"/>
-      <c r="AK8" s="447" t="n"/>
-      <c r="AL8" s="447" t="n"/>
-      <c r="AM8" s="447" t="n"/>
-      <c r="AN8" s="447" t="n"/>
+      <c r="H8" s="552" t="n"/>
+      <c r="I8" s="555" t="n"/>
+      <c r="J8" s="556" t="n"/>
+      <c r="K8" s="556" t="n"/>
+      <c r="L8" s="556" t="n"/>
+      <c r="M8" s="556" t="n"/>
+      <c r="N8" s="556" t="n"/>
+      <c r="O8" s="556" t="n"/>
+      <c r="P8" s="556" t="n"/>
+      <c r="Q8" s="556" t="n"/>
+      <c r="R8" s="556" t="n"/>
+      <c r="S8" s="556" t="n"/>
+      <c r="T8" s="556" t="n"/>
+      <c r="U8" s="556" t="n"/>
+      <c r="V8" s="556" t="n"/>
+      <c r="W8" s="556" t="n"/>
+      <c r="X8" s="556" t="n"/>
+      <c r="Y8" s="556" t="n"/>
+      <c r="Z8" s="556" t="n"/>
+      <c r="AA8" s="556" t="n"/>
+      <c r="AB8" s="556" t="n"/>
+      <c r="AC8" s="556" t="n"/>
+      <c r="AD8" s="556" t="n"/>
+      <c r="AE8" s="556" t="n"/>
+      <c r="AF8" s="556" t="n"/>
+      <c r="AG8" s="556" t="n"/>
+      <c r="AH8" s="556" t="n"/>
+      <c r="AI8" s="556" t="n"/>
+      <c r="AJ8" s="556" t="n"/>
+      <c r="AK8" s="556" t="n"/>
+      <c r="AL8" s="556" t="n"/>
+      <c r="AM8" s="556" t="n"/>
+      <c r="AN8" s="557" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="440" t="inlineStr">
+      <c r="A9" s="558" t="inlineStr">
         <is>
           <t>Tab Purpose</t>
         </is>
       </c>
-      <c r="B9" s="486" t="n"/>
-      <c r="C9" s="441" t="inlineStr">
+      <c r="B9" s="437" t="n"/>
+      <c r="C9" s="559" t="inlineStr">
         <is>
           <t>Periodic review and closeout support sheet for the rolling workbook.</t>
         </is>
       </c>
-      <c r="D9" s="486" t="n"/>
-      <c r="E9" s="440" t="inlineStr">
+      <c r="D9" s="437" t="n"/>
+      <c r="E9" s="560" t="inlineStr">
         <is>
           <t>Working Owner</t>
         </is>
       </c>
-      <c r="F9" s="486" t="n"/>
-      <c r="G9" s="441" t="inlineStr">
+      <c r="F9" s="437" t="n"/>
+      <c r="G9" s="559" t="inlineStr">
         <is>
           <t>QA / Customer Service</t>
         </is>
       </c>
-      <c r="H9" s="486" t="n"/>
-      <c r="I9" s="447" t="n"/>
-      <c r="J9" s="447" t="n"/>
-      <c r="K9" s="447" t="n"/>
-      <c r="L9" s="447" t="n"/>
-      <c r="M9" s="447" t="n"/>
-      <c r="N9" s="447" t="n"/>
-      <c r="O9" s="447" t="n"/>
-      <c r="P9" s="447" t="n"/>
-      <c r="Q9" s="447" t="n"/>
-      <c r="R9" s="447" t="n"/>
-      <c r="S9" s="447" t="n"/>
-      <c r="T9" s="447" t="n"/>
-      <c r="U9" s="447" t="n"/>
-      <c r="V9" s="447" t="n"/>
-      <c r="W9" s="447" t="n"/>
-      <c r="X9" s="447" t="n"/>
-      <c r="Y9" s="447" t="n"/>
-      <c r="Z9" s="447" t="n"/>
-      <c r="AA9" s="447" t="n"/>
-      <c r="AB9" s="447" t="n"/>
-      <c r="AC9" s="447" t="n"/>
-      <c r="AD9" s="447" t="n"/>
-      <c r="AE9" s="447" t="n"/>
-      <c r="AF9" s="447" t="n"/>
-      <c r="AG9" s="447" t="n"/>
-      <c r="AH9" s="447" t="n"/>
-      <c r="AI9" s="447" t="n"/>
-      <c r="AJ9" s="447" t="n"/>
-      <c r="AK9" s="447" t="n"/>
-      <c r="AL9" s="447" t="n"/>
-      <c r="AM9" s="447" t="n"/>
-      <c r="AN9" s="447" t="n"/>
+      <c r="H9" s="437" t="n"/>
+      <c r="I9" s="561" t="n"/>
+      <c r="J9" s="446" t="n"/>
+      <c r="K9" s="446" t="n"/>
+      <c r="L9" s="446" t="n"/>
+      <c r="M9" s="446" t="n"/>
+      <c r="N9" s="446" t="n"/>
+      <c r="O9" s="446" t="n"/>
+      <c r="P9" s="446" t="n"/>
+      <c r="Q9" s="446" t="n"/>
+      <c r="R9" s="446" t="n"/>
+      <c r="S9" s="446" t="n"/>
+      <c r="T9" s="446" t="n"/>
+      <c r="U9" s="446" t="n"/>
+      <c r="V9" s="446" t="n"/>
+      <c r="W9" s="446" t="n"/>
+      <c r="X9" s="446" t="n"/>
+      <c r="Y9" s="446" t="n"/>
+      <c r="Z9" s="446" t="n"/>
+      <c r="AA9" s="446" t="n"/>
+      <c r="AB9" s="446" t="n"/>
+      <c r="AC9" s="446" t="n"/>
+      <c r="AD9" s="446" t="n"/>
+      <c r="AE9" s="446" t="n"/>
+      <c r="AF9" s="446" t="n"/>
+      <c r="AG9" s="446" t="n"/>
+      <c r="AH9" s="446" t="n"/>
+      <c r="AI9" s="446" t="n"/>
+      <c r="AJ9" s="446" t="n"/>
+      <c r="AK9" s="446" t="n"/>
+      <c r="AL9" s="446" t="n"/>
+      <c r="AM9" s="446" t="n"/>
+      <c r="AN9" s="562" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="440" t="inlineStr">
+      <c r="A10" s="558" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B10" s="486" t="n"/>
-      <c r="C10" s="441" t="inlineStr">
+      <c r="B10" s="437" t="n"/>
+      <c r="C10" s="559" t="inlineStr">
         <is>
           <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
         </is>
       </c>
-      <c r="D10" s="486" t="n"/>
-      <c r="E10" s="440" t="inlineStr">
+      <c r="D10" s="437" t="n"/>
+      <c r="E10" s="560" t="inlineStr">
         <is>
           <t>Reviewed By</t>
         </is>
       </c>
-      <c r="F10" s="486" t="n"/>
-      <c r="G10" s="441" t="inlineStr">
+      <c r="F10" s="437" t="n"/>
+      <c r="G10" s="559" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
       </c>
-      <c r="H10" s="486" t="n"/>
-      <c r="I10" s="447" t="n"/>
-      <c r="J10" s="447" t="n"/>
-      <c r="K10" s="447" t="n"/>
-      <c r="L10" s="447" t="n"/>
-      <c r="M10" s="447" t="n"/>
-      <c r="N10" s="447" t="n"/>
-      <c r="O10" s="447" t="n"/>
-      <c r="P10" s="447" t="n"/>
-      <c r="Q10" s="447" t="n"/>
-      <c r="R10" s="447" t="n"/>
-      <c r="S10" s="447" t="n"/>
-      <c r="T10" s="447" t="n"/>
-      <c r="U10" s="447" t="n"/>
-      <c r="V10" s="447" t="n"/>
-      <c r="W10" s="447" t="n"/>
-      <c r="X10" s="447" t="n"/>
-      <c r="Y10" s="447" t="n"/>
-      <c r="Z10" s="447" t="n"/>
-      <c r="AA10" s="447" t="n"/>
-      <c r="AB10" s="447" t="n"/>
-      <c r="AC10" s="447" t="n"/>
-      <c r="AD10" s="447" t="n"/>
-      <c r="AE10" s="447" t="n"/>
-      <c r="AF10" s="447" t="n"/>
-      <c r="AG10" s="447" t="n"/>
-      <c r="AH10" s="447" t="n"/>
-      <c r="AI10" s="447" t="n"/>
-      <c r="AJ10" s="447" t="n"/>
-      <c r="AK10" s="447" t="n"/>
-      <c r="AL10" s="447" t="n"/>
-      <c r="AM10" s="447" t="n"/>
-      <c r="AN10" s="447" t="n"/>
+      <c r="H10" s="437" t="n"/>
+      <c r="I10" s="561" t="n"/>
+      <c r="J10" s="446" t="n"/>
+      <c r="K10" s="446" t="n"/>
+      <c r="L10" s="446" t="n"/>
+      <c r="M10" s="446" t="n"/>
+      <c r="N10" s="446" t="n"/>
+      <c r="O10" s="446" t="n"/>
+      <c r="P10" s="446" t="n"/>
+      <c r="Q10" s="446" t="n"/>
+      <c r="R10" s="446" t="n"/>
+      <c r="S10" s="446" t="n"/>
+      <c r="T10" s="446" t="n"/>
+      <c r="U10" s="446" t="n"/>
+      <c r="V10" s="446" t="n"/>
+      <c r="W10" s="446" t="n"/>
+      <c r="X10" s="446" t="n"/>
+      <c r="Y10" s="446" t="n"/>
+      <c r="Z10" s="446" t="n"/>
+      <c r="AA10" s="446" t="n"/>
+      <c r="AB10" s="446" t="n"/>
+      <c r="AC10" s="446" t="n"/>
+      <c r="AD10" s="446" t="n"/>
+      <c r="AE10" s="446" t="n"/>
+      <c r="AF10" s="446" t="n"/>
+      <c r="AG10" s="446" t="n"/>
+      <c r="AH10" s="446" t="n"/>
+      <c r="AI10" s="446" t="n"/>
+      <c r="AJ10" s="446" t="n"/>
+      <c r="AK10" s="446" t="n"/>
+      <c r="AL10" s="446" t="n"/>
+      <c r="AM10" s="446" t="n"/>
+      <c r="AN10" s="562" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="440" t="inlineStr">
+      <c r="A11" s="558" t="inlineStr">
         <is>
           <t>Update Trigger</t>
         </is>
       </c>
-      <c r="B11" s="485" t="n"/>
-      <c r="C11" s="441" t="inlineStr">
+      <c r="B11" s="437" t="n"/>
+      <c r="C11" s="559" t="inlineStr">
         <is>
           <t>Update when the linked review, evidence or follow-up status changes.</t>
         </is>
       </c>
-      <c r="D11" s="485" t="n"/>
-      <c r="E11" s="440" t="inlineStr">
+      <c r="D11" s="437" t="n"/>
+      <c r="E11" s="560" t="inlineStr">
         <is>
           <t>Data Structure</t>
         </is>
       </c>
-      <c r="F11" s="485" t="n"/>
-      <c r="G11" s="441" t="inlineStr">
+      <c r="F11" s="437" t="n"/>
+      <c r="G11" s="559" t="inlineStr">
         <is>
           <t>Structured Excel Table with filters and print-title rows.</t>
         </is>
       </c>
-      <c r="H11" s="485" t="n"/>
-      <c r="I11" s="430" t="n"/>
-      <c r="J11" s="430" t="n"/>
-      <c r="K11" s="430" t="n"/>
-      <c r="L11" s="430" t="n"/>
-      <c r="M11" s="430" t="n"/>
-      <c r="N11" s="430" t="n"/>
-      <c r="O11" s="430" t="n"/>
-      <c r="P11" s="430" t="n"/>
-      <c r="Q11" s="430" t="n"/>
-      <c r="R11" s="430" t="n"/>
-      <c r="S11" s="430" t="n"/>
-      <c r="T11" s="430" t="n"/>
-      <c r="U11" s="430" t="n"/>
-      <c r="V11" s="430" t="n"/>
-      <c r="W11" s="430" t="n"/>
-      <c r="X11" s="430" t="n"/>
-      <c r="Y11" s="430" t="n"/>
-      <c r="Z11" s="430" t="n"/>
-      <c r="AA11" s="430" t="n"/>
-      <c r="AB11" s="430" t="n"/>
-      <c r="AC11" s="430" t="n"/>
-      <c r="AD11" s="430" t="n"/>
-      <c r="AE11" s="430" t="n"/>
-      <c r="AF11" s="430" t="n"/>
-      <c r="AG11" s="430" t="n"/>
-      <c r="AH11" s="430" t="n"/>
-      <c r="AI11" s="430" t="n"/>
-      <c r="AJ11" s="430" t="n"/>
-      <c r="AK11" s="430" t="n"/>
-      <c r="AL11" s="430" t="n"/>
-      <c r="AM11" s="430" t="n"/>
-      <c r="AN11" s="430" t="n"/>
+      <c r="H11" s="437" t="n"/>
+      <c r="I11" s="563" t="n"/>
+      <c r="J11" s="437" t="n"/>
+      <c r="K11" s="437" t="n"/>
+      <c r="L11" s="437" t="n"/>
+      <c r="M11" s="437" t="n"/>
+      <c r="N11" s="437" t="n"/>
+      <c r="O11" s="437" t="n"/>
+      <c r="P11" s="437" t="n"/>
+      <c r="Q11" s="437" t="n"/>
+      <c r="R11" s="437" t="n"/>
+      <c r="S11" s="437" t="n"/>
+      <c r="T11" s="437" t="n"/>
+      <c r="U11" s="437" t="n"/>
+      <c r="V11" s="437" t="n"/>
+      <c r="W11" s="437" t="n"/>
+      <c r="X11" s="437" t="n"/>
+      <c r="Y11" s="437" t="n"/>
+      <c r="Z11" s="437" t="n"/>
+      <c r="AA11" s="437" t="n"/>
+      <c r="AB11" s="437" t="n"/>
+      <c r="AC11" s="437" t="n"/>
+      <c r="AD11" s="437" t="n"/>
+      <c r="AE11" s="437" t="n"/>
+      <c r="AF11" s="437" t="n"/>
+      <c r="AG11" s="437" t="n"/>
+      <c r="AH11" s="437" t="n"/>
+      <c r="AI11" s="437" t="n"/>
+      <c r="AJ11" s="437" t="n"/>
+      <c r="AK11" s="437" t="n"/>
+      <c r="AL11" s="437" t="n"/>
+      <c r="AM11" s="437" t="n"/>
+      <c r="AN11" s="564" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="440" t="inlineStr">
+      <c r="A12" s="565" t="inlineStr">
         <is>
           <t>Retention Rule</t>
         </is>
       </c>
-      <c r="B12" s="486" t="n"/>
-      <c r="C12" s="441" t="inlineStr">
+      <c r="B12" s="566" t="n"/>
+      <c r="C12" s="567" t="inlineStr">
         <is>
           <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
         </is>
       </c>
-      <c r="D12" s="486" t="n"/>
-      <c r="E12" s="440" t="inlineStr">
+      <c r="D12" s="566" t="n"/>
+      <c r="E12" s="568" t="inlineStr">
         <is>
           <t>Controlled Status</t>
         </is>
       </c>
-      <c r="F12" s="486" t="n"/>
-      <c r="G12" s="441" t="inlineStr">
+      <c r="F12" s="566" t="n"/>
+      <c r="G12" s="567" t="inlineStr">
         <is>
           <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
         </is>
       </c>
-      <c r="H12" s="486" t="n"/>
-      <c r="I12" s="447" t="n"/>
-      <c r="J12" s="447" t="n"/>
-      <c r="K12" s="447" t="n"/>
-      <c r="L12" s="447" t="n"/>
-      <c r="M12" s="447" t="n"/>
-      <c r="N12" s="447" t="n"/>
-      <c r="O12" s="447" t="n"/>
-      <c r="P12" s="447" t="n"/>
-      <c r="Q12" s="447" t="n"/>
-      <c r="R12" s="447" t="n"/>
-      <c r="S12" s="447" t="n"/>
-      <c r="T12" s="447" t="n"/>
-      <c r="U12" s="447" t="n"/>
-      <c r="V12" s="447" t="n"/>
-      <c r="W12" s="447" t="n"/>
-      <c r="X12" s="447" t="n"/>
-      <c r="Y12" s="447" t="n"/>
-      <c r="Z12" s="447" t="n"/>
-      <c r="AA12" s="447" t="n"/>
-      <c r="AB12" s="447" t="n"/>
-      <c r="AC12" s="447" t="n"/>
-      <c r="AD12" s="447" t="n"/>
-      <c r="AE12" s="447" t="n"/>
-      <c r="AF12" s="447" t="n"/>
-      <c r="AG12" s="447" t="n"/>
-      <c r="AH12" s="447" t="n"/>
-      <c r="AI12" s="447" t="n"/>
-      <c r="AJ12" s="447" t="n"/>
-      <c r="AK12" s="447" t="n"/>
-      <c r="AL12" s="447" t="n"/>
-      <c r="AM12" s="447" t="n"/>
-      <c r="AN12" s="447" t="n"/>
+      <c r="H12" s="566" t="n"/>
+      <c r="I12" s="571" t="n"/>
+      <c r="J12" s="572" t="n"/>
+      <c r="K12" s="572" t="n"/>
+      <c r="L12" s="572" t="n"/>
+      <c r="M12" s="572" t="n"/>
+      <c r="N12" s="572" t="n"/>
+      <c r="O12" s="572" t="n"/>
+      <c r="P12" s="572" t="n"/>
+      <c r="Q12" s="572" t="n"/>
+      <c r="R12" s="572" t="n"/>
+      <c r="S12" s="572" t="n"/>
+      <c r="T12" s="572" t="n"/>
+      <c r="U12" s="572" t="n"/>
+      <c r="V12" s="572" t="n"/>
+      <c r="W12" s="572" t="n"/>
+      <c r="X12" s="572" t="n"/>
+      <c r="Y12" s="572" t="n"/>
+      <c r="Z12" s="572" t="n"/>
+      <c r="AA12" s="572" t="n"/>
+      <c r="AB12" s="572" t="n"/>
+      <c r="AC12" s="572" t="n"/>
+      <c r="AD12" s="572" t="n"/>
+      <c r="AE12" s="572" t="n"/>
+      <c r="AF12" s="572" t="n"/>
+      <c r="AG12" s="572" t="n"/>
+      <c r="AH12" s="572" t="n"/>
+      <c r="AI12" s="572" t="n"/>
+      <c r="AJ12" s="572" t="n"/>
+      <c r="AK12" s="572" t="n"/>
+      <c r="AL12" s="572" t="n"/>
+      <c r="AM12" s="572" t="n"/>
+      <c r="AN12" s="573" t="n"/>
     </row>
-    <row r="13" ht="4" customHeight="1">
+    <row r="13" ht="3" customHeight="1">
       <c r="A13" s="442" t="n"/>
       <c r="B13" s="495" t="n"/>
       <c r="C13" s="495" t="n"/>
@@ -10164,619 +10890,619 @@
       <c r="AM13" s="443" t="n"/>
       <c r="AN13" s="443" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="444" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="548" t="inlineStr">
         <is>
           <t>2.  WORKING TABLE / DETAIL LINES</t>
         </is>
       </c>
-      <c r="B14" s="487" t="n"/>
-      <c r="C14" s="487" t="n"/>
-      <c r="D14" s="487" t="n"/>
-      <c r="E14" s="487" t="n"/>
-      <c r="F14" s="487" t="n"/>
-      <c r="G14" s="487" t="n"/>
-      <c r="H14" s="486" t="n"/>
-      <c r="I14" s="447" t="n"/>
-      <c r="J14" s="447" t="n"/>
-      <c r="K14" s="447" t="n"/>
-      <c r="L14" s="447" t="n"/>
-      <c r="M14" s="447" t="n"/>
-      <c r="N14" s="447" t="n"/>
-      <c r="O14" s="447" t="n"/>
-      <c r="P14" s="447" t="n"/>
-      <c r="Q14" s="447" t="n"/>
-      <c r="R14" s="447" t="n"/>
-      <c r="S14" s="447" t="n"/>
-      <c r="T14" s="447" t="n"/>
-      <c r="U14" s="447" t="n"/>
-      <c r="V14" s="447" t="n"/>
-      <c r="W14" s="447" t="n"/>
-      <c r="X14" s="447" t="n"/>
-      <c r="Y14" s="447" t="n"/>
-      <c r="Z14" s="447" t="n"/>
-      <c r="AA14" s="447" t="n"/>
-      <c r="AB14" s="447" t="n"/>
-      <c r="AC14" s="447" t="n"/>
-      <c r="AD14" s="447" t="n"/>
-      <c r="AE14" s="447" t="n"/>
-      <c r="AF14" s="447" t="n"/>
-      <c r="AG14" s="447" t="n"/>
-      <c r="AH14" s="447" t="n"/>
-      <c r="AI14" s="447" t="n"/>
-      <c r="AJ14" s="447" t="n"/>
-      <c r="AK14" s="447" t="n"/>
-      <c r="AL14" s="447" t="n"/>
-      <c r="AM14" s="447" t="n"/>
-      <c r="AN14" s="447" t="n"/>
+      <c r="B14" s="549" t="n"/>
+      <c r="C14" s="549" t="n"/>
+      <c r="D14" s="549" t="n"/>
+      <c r="E14" s="549" t="n"/>
+      <c r="F14" s="549" t="n"/>
+      <c r="G14" s="549" t="n"/>
+      <c r="H14" s="549" t="n"/>
+      <c r="I14" s="549" t="n"/>
+      <c r="J14" s="549" t="n"/>
+      <c r="K14" s="549" t="n"/>
+      <c r="L14" s="549" t="n"/>
+      <c r="M14" s="549" t="n"/>
+      <c r="N14" s="549" t="n"/>
+      <c r="O14" s="549" t="n"/>
+      <c r="P14" s="549" t="n"/>
+      <c r="Q14" s="549" t="n"/>
+      <c r="R14" s="549" t="n"/>
+      <c r="S14" s="549" t="n"/>
+      <c r="T14" s="549" t="n"/>
+      <c r="U14" s="549" t="n"/>
+      <c r="V14" s="549" t="n"/>
+      <c r="W14" s="549" t="n"/>
+      <c r="X14" s="549" t="n"/>
+      <c r="Y14" s="549" t="n"/>
+      <c r="Z14" s="549" t="n"/>
+      <c r="AA14" s="549" t="n"/>
+      <c r="AB14" s="549" t="n"/>
+      <c r="AC14" s="549" t="n"/>
+      <c r="AD14" s="549" t="n"/>
+      <c r="AE14" s="549" t="n"/>
+      <c r="AF14" s="549" t="n"/>
+      <c r="AG14" s="549" t="n"/>
+      <c r="AH14" s="549" t="n"/>
+      <c r="AI14" s="549" t="n"/>
+      <c r="AJ14" s="549" t="n"/>
+      <c r="AK14" s="549" t="n"/>
+      <c r="AL14" s="549" t="n"/>
+      <c r="AM14" s="549" t="n"/>
+      <c r="AN14" s="550" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="470" t="inlineStr">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="548" t="inlineStr">
         <is>
           <t>Periodic review and closeout support sheet for the rolling workbook.</t>
         </is>
       </c>
-      <c r="B15" s="487" t="n"/>
-      <c r="C15" s="487" t="n"/>
-      <c r="D15" s="487" t="n"/>
-      <c r="E15" s="487" t="n"/>
-      <c r="F15" s="487" t="n"/>
-      <c r="G15" s="487" t="n"/>
-      <c r="H15" s="486" t="n"/>
-      <c r="I15" s="447" t="n"/>
-      <c r="J15" s="447" t="n"/>
-      <c r="K15" s="447" t="n"/>
-      <c r="L15" s="447" t="n"/>
-      <c r="M15" s="447" t="n"/>
-      <c r="N15" s="447" t="n"/>
-      <c r="O15" s="447" t="n"/>
-      <c r="P15" s="447" t="n"/>
-      <c r="Q15" s="447" t="n"/>
-      <c r="R15" s="447" t="n"/>
-      <c r="S15" s="447" t="n"/>
-      <c r="T15" s="447" t="n"/>
-      <c r="U15" s="447" t="n"/>
-      <c r="V15" s="447" t="n"/>
-      <c r="W15" s="447" t="n"/>
-      <c r="X15" s="447" t="n"/>
-      <c r="Y15" s="447" t="n"/>
-      <c r="Z15" s="447" t="n"/>
-      <c r="AA15" s="447" t="n"/>
-      <c r="AB15" s="447" t="n"/>
-      <c r="AC15" s="447" t="n"/>
-      <c r="AD15" s="447" t="n"/>
-      <c r="AE15" s="447" t="n"/>
-      <c r="AF15" s="447" t="n"/>
-      <c r="AG15" s="447" t="n"/>
-      <c r="AH15" s="447" t="n"/>
-      <c r="AI15" s="447" t="n"/>
-      <c r="AJ15" s="447" t="n"/>
-      <c r="AK15" s="447" t="n"/>
-      <c r="AL15" s="447" t="n"/>
-      <c r="AM15" s="447" t="n"/>
-      <c r="AN15" s="447" t="n"/>
+      <c r="B15" s="549" t="n"/>
+      <c r="C15" s="549" t="n"/>
+      <c r="D15" s="549" t="n"/>
+      <c r="E15" s="549" t="n"/>
+      <c r="F15" s="549" t="n"/>
+      <c r="G15" s="549" t="n"/>
+      <c r="H15" s="549" t="n"/>
+      <c r="I15" s="549" t="n"/>
+      <c r="J15" s="549" t="n"/>
+      <c r="K15" s="549" t="n"/>
+      <c r="L15" s="549" t="n"/>
+      <c r="M15" s="549" t="n"/>
+      <c r="N15" s="549" t="n"/>
+      <c r="O15" s="549" t="n"/>
+      <c r="P15" s="549" t="n"/>
+      <c r="Q15" s="549" t="n"/>
+      <c r="R15" s="549" t="n"/>
+      <c r="S15" s="549" t="n"/>
+      <c r="T15" s="549" t="n"/>
+      <c r="U15" s="549" t="n"/>
+      <c r="V15" s="549" t="n"/>
+      <c r="W15" s="549" t="n"/>
+      <c r="X15" s="549" t="n"/>
+      <c r="Y15" s="549" t="n"/>
+      <c r="Z15" s="549" t="n"/>
+      <c r="AA15" s="549" t="n"/>
+      <c r="AB15" s="549" t="n"/>
+      <c r="AC15" s="549" t="n"/>
+      <c r="AD15" s="549" t="n"/>
+      <c r="AE15" s="549" t="n"/>
+      <c r="AF15" s="549" t="n"/>
+      <c r="AG15" s="549" t="n"/>
+      <c r="AH15" s="549" t="n"/>
+      <c r="AI15" s="549" t="n"/>
+      <c r="AJ15" s="549" t="n"/>
+      <c r="AK15" s="549" t="n"/>
+      <c r="AL15" s="549" t="n"/>
+      <c r="AM15" s="549" t="n"/>
+      <c r="AN15" s="550" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="448" t="inlineStr">
+      <c r="A16" s="574" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B16" s="448" t="inlineStr">
+      <c r="B16" s="575" t="inlineStr">
         <is>
           <t>Review Item</t>
         </is>
       </c>
-      <c r="C16" s="448" t="inlineStr">
+      <c r="C16" s="575" t="inlineStr">
         <is>
           <t>Expectation / Rule</t>
         </is>
       </c>
-      <c r="D16" s="448" t="inlineStr">
+      <c r="D16" s="575" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="E16" s="448" t="inlineStr">
+      <c r="E16" s="575" t="inlineStr">
         <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="F16" s="448" t="inlineStr">
+      <c r="F16" s="575" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G16" s="448" t="inlineStr">
+      <c r="G16" s="575" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="H16" s="449" t="inlineStr">
+      <c r="H16" s="575" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="I16" s="447" t="n"/>
-      <c r="J16" s="447" t="n"/>
-      <c r="K16" s="447" t="n"/>
-      <c r="L16" s="447" t="n"/>
-      <c r="M16" s="447" t="n"/>
-      <c r="N16" s="447" t="n"/>
-      <c r="O16" s="447" t="n"/>
-      <c r="P16" s="447" t="n"/>
-      <c r="Q16" s="447" t="n"/>
-      <c r="R16" s="447" t="n"/>
-      <c r="S16" s="447" t="n"/>
-      <c r="T16" s="447" t="n"/>
-      <c r="U16" s="447" t="n"/>
-      <c r="V16" s="447" t="n"/>
-      <c r="W16" s="447" t="n"/>
-      <c r="X16" s="447" t="n"/>
-      <c r="Y16" s="447" t="n"/>
-      <c r="Z16" s="447" t="n"/>
-      <c r="AA16" s="447" t="n"/>
-      <c r="AB16" s="447" t="n"/>
-      <c r="AC16" s="447" t="n"/>
-      <c r="AD16" s="447" t="n"/>
-      <c r="AE16" s="447" t="n"/>
-      <c r="AF16" s="447" t="n"/>
-      <c r="AG16" s="447" t="n"/>
-      <c r="AH16" s="447" t="n"/>
-      <c r="AI16" s="447" t="n"/>
-      <c r="AJ16" s="447" t="n"/>
-      <c r="AK16" s="447" t="n"/>
-      <c r="AL16" s="447" t="n"/>
-      <c r="AM16" s="447" t="n"/>
-      <c r="AN16" s="447" t="n"/>
+      <c r="I16" s="575" t="n"/>
+      <c r="J16" s="575" t="n"/>
+      <c r="K16" s="575" t="n"/>
+      <c r="L16" s="575" t="n"/>
+      <c r="M16" s="575" t="n"/>
+      <c r="N16" s="575" t="n"/>
+      <c r="O16" s="575" t="n"/>
+      <c r="P16" s="575" t="n"/>
+      <c r="Q16" s="575" t="n"/>
+      <c r="R16" s="575" t="n"/>
+      <c r="S16" s="575" t="n"/>
+      <c r="T16" s="575" t="n"/>
+      <c r="U16" s="575" t="n"/>
+      <c r="V16" s="575" t="n"/>
+      <c r="W16" s="575" t="n"/>
+      <c r="X16" s="575" t="n"/>
+      <c r="Y16" s="575" t="n"/>
+      <c r="Z16" s="575" t="n"/>
+      <c r="AA16" s="575" t="n"/>
+      <c r="AB16" s="575" t="n"/>
+      <c r="AC16" s="575" t="n"/>
+      <c r="AD16" s="575" t="n"/>
+      <c r="AE16" s="575" t="n"/>
+      <c r="AF16" s="575" t="n"/>
+      <c r="AG16" s="575" t="n"/>
+      <c r="AH16" s="575" t="n"/>
+      <c r="AI16" s="575" t="n"/>
+      <c r="AJ16" s="575" t="n"/>
+      <c r="AK16" s="575" t="n"/>
+      <c r="AL16" s="575" t="n"/>
+      <c r="AM16" s="575" t="n"/>
+      <c r="AN16" s="576" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="450">
+      <c r="A17" s="577">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B17" s="452" t="n"/>
-      <c r="C17" s="452" t="n"/>
-      <c r="D17" s="452" t="n"/>
-      <c r="E17" s="471" t="n"/>
-      <c r="F17" s="452" t="n"/>
-      <c r="G17" s="452" t="n"/>
-      <c r="H17" s="429" t="n"/>
-      <c r="I17" s="447" t="n"/>
-      <c r="J17" s="447" t="n"/>
-      <c r="K17" s="447" t="n"/>
-      <c r="L17" s="447" t="n"/>
-      <c r="M17" s="447" t="n"/>
-      <c r="N17" s="447" t="n"/>
-      <c r="O17" s="447" t="n"/>
-      <c r="P17" s="447" t="n"/>
-      <c r="Q17" s="447" t="n"/>
-      <c r="R17" s="447" t="n"/>
-      <c r="S17" s="447" t="n"/>
-      <c r="T17" s="447" t="n"/>
-      <c r="U17" s="447" t="n"/>
-      <c r="V17" s="447" t="n"/>
-      <c r="W17" s="447" t="n"/>
-      <c r="X17" s="447" t="n"/>
-      <c r="Y17" s="447" t="n"/>
-      <c r="Z17" s="447" t="n"/>
-      <c r="AA17" s="447" t="n"/>
-      <c r="AB17" s="447" t="n"/>
-      <c r="AC17" s="447" t="n"/>
-      <c r="AD17" s="447" t="n"/>
-      <c r="AE17" s="447" t="n"/>
-      <c r="AF17" s="447" t="n"/>
-      <c r="AG17" s="447" t="n"/>
-      <c r="AH17" s="447" t="n"/>
-      <c r="AI17" s="447" t="n"/>
-      <c r="AJ17" s="447" t="n"/>
-      <c r="AK17" s="447" t="n"/>
-      <c r="AL17" s="447" t="n"/>
-      <c r="AM17" s="447" t="n"/>
-      <c r="AN17" s="447" t="n"/>
+      <c r="B17" s="553" t="n"/>
+      <c r="C17" s="579" t="n"/>
+      <c r="D17" s="579" t="n"/>
+      <c r="E17" s="603" t="n"/>
+      <c r="F17" s="579" t="n"/>
+      <c r="G17" s="579" t="n"/>
+      <c r="H17" s="579" t="n"/>
+      <c r="I17" s="556" t="n"/>
+      <c r="J17" s="556" t="n"/>
+      <c r="K17" s="556" t="n"/>
+      <c r="L17" s="556" t="n"/>
+      <c r="M17" s="556" t="n"/>
+      <c r="N17" s="556" t="n"/>
+      <c r="O17" s="556" t="n"/>
+      <c r="P17" s="556" t="n"/>
+      <c r="Q17" s="556" t="n"/>
+      <c r="R17" s="556" t="n"/>
+      <c r="S17" s="556" t="n"/>
+      <c r="T17" s="556" t="n"/>
+      <c r="U17" s="556" t="n"/>
+      <c r="V17" s="556" t="n"/>
+      <c r="W17" s="556" t="n"/>
+      <c r="X17" s="556" t="n"/>
+      <c r="Y17" s="556" t="n"/>
+      <c r="Z17" s="556" t="n"/>
+      <c r="AA17" s="556" t="n"/>
+      <c r="AB17" s="556" t="n"/>
+      <c r="AC17" s="556" t="n"/>
+      <c r="AD17" s="556" t="n"/>
+      <c r="AE17" s="556" t="n"/>
+      <c r="AF17" s="556" t="n"/>
+      <c r="AG17" s="556" t="n"/>
+      <c r="AH17" s="556" t="n"/>
+      <c r="AI17" s="556" t="n"/>
+      <c r="AJ17" s="556" t="n"/>
+      <c r="AK17" s="556" t="n"/>
+      <c r="AL17" s="556" t="n"/>
+      <c r="AM17" s="556" t="n"/>
+      <c r="AN17" s="557" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="450">
+      <c r="A18" s="580">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B18" s="454" t="n"/>
-      <c r="C18" s="454" t="n"/>
-      <c r="D18" s="454" t="n"/>
-      <c r="E18" s="472" t="n"/>
-      <c r="F18" s="454" t="n"/>
-      <c r="G18" s="454" t="n"/>
-      <c r="H18" s="455" t="n"/>
-      <c r="I18" s="447" t="n"/>
-      <c r="J18" s="447" t="n"/>
-      <c r="K18" s="447" t="n"/>
-      <c r="L18" s="447" t="n"/>
-      <c r="M18" s="447" t="n"/>
-      <c r="N18" s="447" t="n"/>
-      <c r="O18" s="447" t="n"/>
-      <c r="P18" s="447" t="n"/>
-      <c r="Q18" s="447" t="n"/>
-      <c r="R18" s="447" t="n"/>
-      <c r="S18" s="447" t="n"/>
-      <c r="T18" s="447" t="n"/>
-      <c r="U18" s="447" t="n"/>
-      <c r="V18" s="447" t="n"/>
-      <c r="W18" s="447" t="n"/>
-      <c r="X18" s="447" t="n"/>
-      <c r="Y18" s="447" t="n"/>
-      <c r="Z18" s="447" t="n"/>
-      <c r="AA18" s="447" t="n"/>
-      <c r="AB18" s="447" t="n"/>
-      <c r="AC18" s="447" t="n"/>
-      <c r="AD18" s="447" t="n"/>
-      <c r="AE18" s="447" t="n"/>
-      <c r="AF18" s="447" t="n"/>
-      <c r="AG18" s="447" t="n"/>
-      <c r="AH18" s="447" t="n"/>
-      <c r="AI18" s="447" t="n"/>
-      <c r="AJ18" s="447" t="n"/>
-      <c r="AK18" s="447" t="n"/>
-      <c r="AL18" s="447" t="n"/>
-      <c r="AM18" s="447" t="n"/>
-      <c r="AN18" s="447" t="n"/>
+      <c r="B18" s="458" t="n"/>
+      <c r="C18" s="581" t="n"/>
+      <c r="D18" s="581" t="n"/>
+      <c r="E18" s="604" t="n"/>
+      <c r="F18" s="581" t="n"/>
+      <c r="G18" s="581" t="n"/>
+      <c r="H18" s="581" t="n"/>
+      <c r="I18" s="446" t="n"/>
+      <c r="J18" s="446" t="n"/>
+      <c r="K18" s="446" t="n"/>
+      <c r="L18" s="446" t="n"/>
+      <c r="M18" s="446" t="n"/>
+      <c r="N18" s="446" t="n"/>
+      <c r="O18" s="446" t="n"/>
+      <c r="P18" s="446" t="n"/>
+      <c r="Q18" s="446" t="n"/>
+      <c r="R18" s="446" t="n"/>
+      <c r="S18" s="446" t="n"/>
+      <c r="T18" s="446" t="n"/>
+      <c r="U18" s="446" t="n"/>
+      <c r="V18" s="446" t="n"/>
+      <c r="W18" s="446" t="n"/>
+      <c r="X18" s="446" t="n"/>
+      <c r="Y18" s="446" t="n"/>
+      <c r="Z18" s="446" t="n"/>
+      <c r="AA18" s="446" t="n"/>
+      <c r="AB18" s="446" t="n"/>
+      <c r="AC18" s="446" t="n"/>
+      <c r="AD18" s="446" t="n"/>
+      <c r="AE18" s="446" t="n"/>
+      <c r="AF18" s="446" t="n"/>
+      <c r="AG18" s="446" t="n"/>
+      <c r="AH18" s="446" t="n"/>
+      <c r="AI18" s="446" t="n"/>
+      <c r="AJ18" s="446" t="n"/>
+      <c r="AK18" s="446" t="n"/>
+      <c r="AL18" s="446" t="n"/>
+      <c r="AM18" s="446" t="n"/>
+      <c r="AN18" s="562" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="450">
+      <c r="A19" s="580">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B19" s="452" t="n"/>
-      <c r="C19" s="452" t="n"/>
-      <c r="D19" s="452" t="n"/>
-      <c r="E19" s="471" t="n"/>
-      <c r="F19" s="452" t="n"/>
-      <c r="G19" s="452" t="n"/>
-      <c r="H19" s="429" t="n"/>
-      <c r="I19" s="447" t="n"/>
-      <c r="J19" s="447" t="n"/>
-      <c r="K19" s="447" t="n"/>
-      <c r="L19" s="447" t="n"/>
-      <c r="M19" s="447" t="n"/>
-      <c r="N19" s="447" t="n"/>
-      <c r="O19" s="447" t="n"/>
-      <c r="P19" s="447" t="n"/>
-      <c r="Q19" s="447" t="n"/>
-      <c r="R19" s="447" t="n"/>
-      <c r="S19" s="447" t="n"/>
-      <c r="T19" s="447" t="n"/>
-      <c r="U19" s="447" t="n"/>
-      <c r="V19" s="447" t="n"/>
-      <c r="W19" s="447" t="n"/>
-      <c r="X19" s="447" t="n"/>
-      <c r="Y19" s="447" t="n"/>
-      <c r="Z19" s="447" t="n"/>
-      <c r="AA19" s="447" t="n"/>
-      <c r="AB19" s="447" t="n"/>
-      <c r="AC19" s="447" t="n"/>
-      <c r="AD19" s="447" t="n"/>
-      <c r="AE19" s="447" t="n"/>
-      <c r="AF19" s="447" t="n"/>
-      <c r="AG19" s="447" t="n"/>
-      <c r="AH19" s="447" t="n"/>
-      <c r="AI19" s="447" t="n"/>
-      <c r="AJ19" s="447" t="n"/>
-      <c r="AK19" s="447" t="n"/>
-      <c r="AL19" s="447" t="n"/>
-      <c r="AM19" s="447" t="n"/>
-      <c r="AN19" s="447" t="n"/>
+      <c r="B19" s="559" t="n"/>
+      <c r="C19" s="583" t="n"/>
+      <c r="D19" s="583" t="n"/>
+      <c r="E19" s="605" t="n"/>
+      <c r="F19" s="583" t="n"/>
+      <c r="G19" s="583" t="n"/>
+      <c r="H19" s="583" t="n"/>
+      <c r="I19" s="446" t="n"/>
+      <c r="J19" s="446" t="n"/>
+      <c r="K19" s="446" t="n"/>
+      <c r="L19" s="446" t="n"/>
+      <c r="M19" s="446" t="n"/>
+      <c r="N19" s="446" t="n"/>
+      <c r="O19" s="446" t="n"/>
+      <c r="P19" s="446" t="n"/>
+      <c r="Q19" s="446" t="n"/>
+      <c r="R19" s="446" t="n"/>
+      <c r="S19" s="446" t="n"/>
+      <c r="T19" s="446" t="n"/>
+      <c r="U19" s="446" t="n"/>
+      <c r="V19" s="446" t="n"/>
+      <c r="W19" s="446" t="n"/>
+      <c r="X19" s="446" t="n"/>
+      <c r="Y19" s="446" t="n"/>
+      <c r="Z19" s="446" t="n"/>
+      <c r="AA19" s="446" t="n"/>
+      <c r="AB19" s="446" t="n"/>
+      <c r="AC19" s="446" t="n"/>
+      <c r="AD19" s="446" t="n"/>
+      <c r="AE19" s="446" t="n"/>
+      <c r="AF19" s="446" t="n"/>
+      <c r="AG19" s="446" t="n"/>
+      <c r="AH19" s="446" t="n"/>
+      <c r="AI19" s="446" t="n"/>
+      <c r="AJ19" s="446" t="n"/>
+      <c r="AK19" s="446" t="n"/>
+      <c r="AL19" s="446" t="n"/>
+      <c r="AM19" s="446" t="n"/>
+      <c r="AN19" s="562" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="450">
+      <c r="A20" s="580">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B20" s="454" t="n"/>
-      <c r="C20" s="454" t="n"/>
-      <c r="D20" s="454" t="n"/>
-      <c r="E20" s="472" t="n"/>
-      <c r="F20" s="454" t="n"/>
-      <c r="G20" s="454" t="n"/>
-      <c r="H20" s="455" t="n"/>
-      <c r="I20" s="447" t="n"/>
-      <c r="J20" s="447" t="n"/>
-      <c r="K20" s="447" t="n"/>
-      <c r="L20" s="447" t="n"/>
-      <c r="M20" s="447" t="n"/>
-      <c r="N20" s="447" t="n"/>
-      <c r="O20" s="447" t="n"/>
-      <c r="P20" s="447" t="n"/>
-      <c r="Q20" s="447" t="n"/>
-      <c r="R20" s="447" t="n"/>
-      <c r="S20" s="447" t="n"/>
-      <c r="T20" s="447" t="n"/>
-      <c r="U20" s="447" t="n"/>
-      <c r="V20" s="447" t="n"/>
-      <c r="W20" s="447" t="n"/>
-      <c r="X20" s="447" t="n"/>
-      <c r="Y20" s="447" t="n"/>
-      <c r="Z20" s="447" t="n"/>
-      <c r="AA20" s="447" t="n"/>
-      <c r="AB20" s="447" t="n"/>
-      <c r="AC20" s="447" t="n"/>
-      <c r="AD20" s="447" t="n"/>
-      <c r="AE20" s="447" t="n"/>
-      <c r="AF20" s="447" t="n"/>
-      <c r="AG20" s="447" t="n"/>
-      <c r="AH20" s="447" t="n"/>
-      <c r="AI20" s="447" t="n"/>
-      <c r="AJ20" s="447" t="n"/>
-      <c r="AK20" s="447" t="n"/>
-      <c r="AL20" s="447" t="n"/>
-      <c r="AM20" s="447" t="n"/>
-      <c r="AN20" s="447" t="n"/>
+      <c r="B20" s="458" t="n"/>
+      <c r="C20" s="581" t="n"/>
+      <c r="D20" s="581" t="n"/>
+      <c r="E20" s="604" t="n"/>
+      <c r="F20" s="581" t="n"/>
+      <c r="G20" s="581" t="n"/>
+      <c r="H20" s="581" t="n"/>
+      <c r="I20" s="446" t="n"/>
+      <c r="J20" s="446" t="n"/>
+      <c r="K20" s="446" t="n"/>
+      <c r="L20" s="446" t="n"/>
+      <c r="M20" s="446" t="n"/>
+      <c r="N20" s="446" t="n"/>
+      <c r="O20" s="446" t="n"/>
+      <c r="P20" s="446" t="n"/>
+      <c r="Q20" s="446" t="n"/>
+      <c r="R20" s="446" t="n"/>
+      <c r="S20" s="446" t="n"/>
+      <c r="T20" s="446" t="n"/>
+      <c r="U20" s="446" t="n"/>
+      <c r="V20" s="446" t="n"/>
+      <c r="W20" s="446" t="n"/>
+      <c r="X20" s="446" t="n"/>
+      <c r="Y20" s="446" t="n"/>
+      <c r="Z20" s="446" t="n"/>
+      <c r="AA20" s="446" t="n"/>
+      <c r="AB20" s="446" t="n"/>
+      <c r="AC20" s="446" t="n"/>
+      <c r="AD20" s="446" t="n"/>
+      <c r="AE20" s="446" t="n"/>
+      <c r="AF20" s="446" t="n"/>
+      <c r="AG20" s="446" t="n"/>
+      <c r="AH20" s="446" t="n"/>
+      <c r="AI20" s="446" t="n"/>
+      <c r="AJ20" s="446" t="n"/>
+      <c r="AK20" s="446" t="n"/>
+      <c r="AL20" s="446" t="n"/>
+      <c r="AM20" s="446" t="n"/>
+      <c r="AN20" s="562" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="450">
+      <c r="A21" s="580">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B21" s="452" t="n"/>
-      <c r="C21" s="452" t="n"/>
-      <c r="D21" s="452" t="n"/>
-      <c r="E21" s="471" t="n"/>
-      <c r="F21" s="452" t="n"/>
-      <c r="G21" s="452" t="n"/>
-      <c r="H21" s="429" t="n"/>
-      <c r="I21" s="447" t="n"/>
-      <c r="J21" s="447" t="n"/>
-      <c r="K21" s="447" t="n"/>
-      <c r="L21" s="447" t="n"/>
-      <c r="M21" s="447" t="n"/>
-      <c r="N21" s="447" t="n"/>
-      <c r="O21" s="447" t="n"/>
-      <c r="P21" s="447" t="n"/>
-      <c r="Q21" s="447" t="n"/>
-      <c r="R21" s="447" t="n"/>
-      <c r="S21" s="447" t="n"/>
-      <c r="T21" s="447" t="n"/>
-      <c r="U21" s="447" t="n"/>
-      <c r="V21" s="447" t="n"/>
-      <c r="W21" s="447" t="n"/>
-      <c r="X21" s="447" t="n"/>
-      <c r="Y21" s="447" t="n"/>
-      <c r="Z21" s="447" t="n"/>
-      <c r="AA21" s="447" t="n"/>
-      <c r="AB21" s="447" t="n"/>
-      <c r="AC21" s="447" t="n"/>
-      <c r="AD21" s="447" t="n"/>
-      <c r="AE21" s="447" t="n"/>
-      <c r="AF21" s="447" t="n"/>
-      <c r="AG21" s="447" t="n"/>
-      <c r="AH21" s="447" t="n"/>
-      <c r="AI21" s="447" t="n"/>
-      <c r="AJ21" s="447" t="n"/>
-      <c r="AK21" s="447" t="n"/>
-      <c r="AL21" s="447" t="n"/>
-      <c r="AM21" s="447" t="n"/>
-      <c r="AN21" s="447" t="n"/>
+      <c r="B21" s="559" t="n"/>
+      <c r="C21" s="583" t="n"/>
+      <c r="D21" s="583" t="n"/>
+      <c r="E21" s="605" t="n"/>
+      <c r="F21" s="583" t="n"/>
+      <c r="G21" s="583" t="n"/>
+      <c r="H21" s="583" t="n"/>
+      <c r="I21" s="446" t="n"/>
+      <c r="J21" s="446" t="n"/>
+      <c r="K21" s="446" t="n"/>
+      <c r="L21" s="446" t="n"/>
+      <c r="M21" s="446" t="n"/>
+      <c r="N21" s="446" t="n"/>
+      <c r="O21" s="446" t="n"/>
+      <c r="P21" s="446" t="n"/>
+      <c r="Q21" s="446" t="n"/>
+      <c r="R21" s="446" t="n"/>
+      <c r="S21" s="446" t="n"/>
+      <c r="T21" s="446" t="n"/>
+      <c r="U21" s="446" t="n"/>
+      <c r="V21" s="446" t="n"/>
+      <c r="W21" s="446" t="n"/>
+      <c r="X21" s="446" t="n"/>
+      <c r="Y21" s="446" t="n"/>
+      <c r="Z21" s="446" t="n"/>
+      <c r="AA21" s="446" t="n"/>
+      <c r="AB21" s="446" t="n"/>
+      <c r="AC21" s="446" t="n"/>
+      <c r="AD21" s="446" t="n"/>
+      <c r="AE21" s="446" t="n"/>
+      <c r="AF21" s="446" t="n"/>
+      <c r="AG21" s="446" t="n"/>
+      <c r="AH21" s="446" t="n"/>
+      <c r="AI21" s="446" t="n"/>
+      <c r="AJ21" s="446" t="n"/>
+      <c r="AK21" s="446" t="n"/>
+      <c r="AL21" s="446" t="n"/>
+      <c r="AM21" s="446" t="n"/>
+      <c r="AN21" s="562" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="450">
+      <c r="A22" s="580">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B22" s="454" t="n"/>
-      <c r="C22" s="454" t="n"/>
-      <c r="D22" s="454" t="n"/>
-      <c r="E22" s="472" t="n"/>
-      <c r="F22" s="454" t="n"/>
-      <c r="G22" s="454" t="n"/>
-      <c r="H22" s="455" t="n"/>
-      <c r="I22" s="447" t="n"/>
-      <c r="J22" s="447" t="n"/>
-      <c r="K22" s="447" t="n"/>
-      <c r="L22" s="447" t="n"/>
-      <c r="M22" s="447" t="n"/>
-      <c r="N22" s="447" t="n"/>
-      <c r="O22" s="447" t="n"/>
-      <c r="P22" s="447" t="n"/>
-      <c r="Q22" s="447" t="n"/>
-      <c r="R22" s="447" t="n"/>
-      <c r="S22" s="447" t="n"/>
-      <c r="T22" s="447" t="n"/>
-      <c r="U22" s="447" t="n"/>
-      <c r="V22" s="447" t="n"/>
-      <c r="W22" s="447" t="n"/>
-      <c r="X22" s="447" t="n"/>
-      <c r="Y22" s="447" t="n"/>
-      <c r="Z22" s="447" t="n"/>
-      <c r="AA22" s="447" t="n"/>
-      <c r="AB22" s="447" t="n"/>
-      <c r="AC22" s="447" t="n"/>
-      <c r="AD22" s="447" t="n"/>
-      <c r="AE22" s="447" t="n"/>
-      <c r="AF22" s="447" t="n"/>
-      <c r="AG22" s="447" t="n"/>
-      <c r="AH22" s="447" t="n"/>
-      <c r="AI22" s="447" t="n"/>
-      <c r="AJ22" s="447" t="n"/>
-      <c r="AK22" s="447" t="n"/>
-      <c r="AL22" s="447" t="n"/>
-      <c r="AM22" s="447" t="n"/>
-      <c r="AN22" s="447" t="n"/>
+      <c r="B22" s="458" t="n"/>
+      <c r="C22" s="581" t="n"/>
+      <c r="D22" s="581" t="n"/>
+      <c r="E22" s="604" t="n"/>
+      <c r="F22" s="581" t="n"/>
+      <c r="G22" s="581" t="n"/>
+      <c r="H22" s="581" t="n"/>
+      <c r="I22" s="446" t="n"/>
+      <c r="J22" s="446" t="n"/>
+      <c r="K22" s="446" t="n"/>
+      <c r="L22" s="446" t="n"/>
+      <c r="M22" s="446" t="n"/>
+      <c r="N22" s="446" t="n"/>
+      <c r="O22" s="446" t="n"/>
+      <c r="P22" s="446" t="n"/>
+      <c r="Q22" s="446" t="n"/>
+      <c r="R22" s="446" t="n"/>
+      <c r="S22" s="446" t="n"/>
+      <c r="T22" s="446" t="n"/>
+      <c r="U22" s="446" t="n"/>
+      <c r="V22" s="446" t="n"/>
+      <c r="W22" s="446" t="n"/>
+      <c r="X22" s="446" t="n"/>
+      <c r="Y22" s="446" t="n"/>
+      <c r="Z22" s="446" t="n"/>
+      <c r="AA22" s="446" t="n"/>
+      <c r="AB22" s="446" t="n"/>
+      <c r="AC22" s="446" t="n"/>
+      <c r="AD22" s="446" t="n"/>
+      <c r="AE22" s="446" t="n"/>
+      <c r="AF22" s="446" t="n"/>
+      <c r="AG22" s="446" t="n"/>
+      <c r="AH22" s="446" t="n"/>
+      <c r="AI22" s="446" t="n"/>
+      <c r="AJ22" s="446" t="n"/>
+      <c r="AK22" s="446" t="n"/>
+      <c r="AL22" s="446" t="n"/>
+      <c r="AM22" s="446" t="n"/>
+      <c r="AN22" s="562" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="450">
+      <c r="A23" s="580">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B23" s="452" t="n"/>
-      <c r="C23" s="452" t="n"/>
-      <c r="D23" s="452" t="n"/>
-      <c r="E23" s="471" t="n"/>
-      <c r="F23" s="452" t="n"/>
-      <c r="G23" s="452" t="n"/>
-      <c r="H23" s="429" t="n"/>
-      <c r="I23" s="447" t="n"/>
-      <c r="J23" s="447" t="n"/>
-      <c r="K23" s="447" t="n"/>
-      <c r="L23" s="447" t="n"/>
-      <c r="M23" s="447" t="n"/>
-      <c r="N23" s="447" t="n"/>
-      <c r="O23" s="447" t="n"/>
-      <c r="P23" s="447" t="n"/>
-      <c r="Q23" s="447" t="n"/>
-      <c r="R23" s="447" t="n"/>
-      <c r="S23" s="447" t="n"/>
-      <c r="T23" s="447" t="n"/>
-      <c r="U23" s="447" t="n"/>
-      <c r="V23" s="447" t="n"/>
-      <c r="W23" s="447" t="n"/>
-      <c r="X23" s="447" t="n"/>
-      <c r="Y23" s="447" t="n"/>
-      <c r="Z23" s="447" t="n"/>
-      <c r="AA23" s="447" t="n"/>
-      <c r="AB23" s="447" t="n"/>
-      <c r="AC23" s="447" t="n"/>
-      <c r="AD23" s="447" t="n"/>
-      <c r="AE23" s="447" t="n"/>
-      <c r="AF23" s="447" t="n"/>
-      <c r="AG23" s="447" t="n"/>
-      <c r="AH23" s="447" t="n"/>
-      <c r="AI23" s="447" t="n"/>
-      <c r="AJ23" s="447" t="n"/>
-      <c r="AK23" s="447" t="n"/>
-      <c r="AL23" s="447" t="n"/>
-      <c r="AM23" s="447" t="n"/>
-      <c r="AN23" s="447" t="n"/>
+      <c r="B23" s="559" t="n"/>
+      <c r="C23" s="583" t="n"/>
+      <c r="D23" s="583" t="n"/>
+      <c r="E23" s="605" t="n"/>
+      <c r="F23" s="583" t="n"/>
+      <c r="G23" s="583" t="n"/>
+      <c r="H23" s="583" t="n"/>
+      <c r="I23" s="446" t="n"/>
+      <c r="J23" s="446" t="n"/>
+      <c r="K23" s="446" t="n"/>
+      <c r="L23" s="446" t="n"/>
+      <c r="M23" s="446" t="n"/>
+      <c r="N23" s="446" t="n"/>
+      <c r="O23" s="446" t="n"/>
+      <c r="P23" s="446" t="n"/>
+      <c r="Q23" s="446" t="n"/>
+      <c r="R23" s="446" t="n"/>
+      <c r="S23" s="446" t="n"/>
+      <c r="T23" s="446" t="n"/>
+      <c r="U23" s="446" t="n"/>
+      <c r="V23" s="446" t="n"/>
+      <c r="W23" s="446" t="n"/>
+      <c r="X23" s="446" t="n"/>
+      <c r="Y23" s="446" t="n"/>
+      <c r="Z23" s="446" t="n"/>
+      <c r="AA23" s="446" t="n"/>
+      <c r="AB23" s="446" t="n"/>
+      <c r="AC23" s="446" t="n"/>
+      <c r="AD23" s="446" t="n"/>
+      <c r="AE23" s="446" t="n"/>
+      <c r="AF23" s="446" t="n"/>
+      <c r="AG23" s="446" t="n"/>
+      <c r="AH23" s="446" t="n"/>
+      <c r="AI23" s="446" t="n"/>
+      <c r="AJ23" s="446" t="n"/>
+      <c r="AK23" s="446" t="n"/>
+      <c r="AL23" s="446" t="n"/>
+      <c r="AM23" s="446" t="n"/>
+      <c r="AN23" s="562" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="456">
+      <c r="A24" s="580">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
       <c r="B24" s="458" t="n"/>
-      <c r="C24" s="458" t="n"/>
-      <c r="D24" s="458" t="n"/>
-      <c r="E24" s="473" t="n"/>
-      <c r="F24" s="458" t="n"/>
-      <c r="G24" s="458" t="n"/>
-      <c r="H24" s="459" t="n"/>
-      <c r="I24" s="447" t="n"/>
-      <c r="J24" s="447" t="n"/>
-      <c r="K24" s="447" t="n"/>
-      <c r="L24" s="447" t="n"/>
-      <c r="M24" s="447" t="n"/>
-      <c r="N24" s="447" t="n"/>
-      <c r="O24" s="447" t="n"/>
-      <c r="P24" s="447" t="n"/>
-      <c r="Q24" s="447" t="n"/>
-      <c r="R24" s="447" t="n"/>
-      <c r="S24" s="447" t="n"/>
-      <c r="T24" s="447" t="n"/>
-      <c r="U24" s="447" t="n"/>
-      <c r="V24" s="447" t="n"/>
-      <c r="W24" s="447" t="n"/>
-      <c r="X24" s="447" t="n"/>
-      <c r="Y24" s="447" t="n"/>
-      <c r="Z24" s="447" t="n"/>
-      <c r="AA24" s="447" t="n"/>
-      <c r="AB24" s="447" t="n"/>
-      <c r="AC24" s="447" t="n"/>
-      <c r="AD24" s="447" t="n"/>
-      <c r="AE24" s="447" t="n"/>
-      <c r="AF24" s="447" t="n"/>
-      <c r="AG24" s="447" t="n"/>
-      <c r="AH24" s="447" t="n"/>
-      <c r="AI24" s="447" t="n"/>
-      <c r="AJ24" s="447" t="n"/>
-      <c r="AK24" s="447" t="n"/>
-      <c r="AL24" s="447" t="n"/>
-      <c r="AM24" s="447" t="n"/>
-      <c r="AN24" s="447" t="n"/>
+      <c r="C24" s="581" t="n"/>
+      <c r="D24" s="581" t="n"/>
+      <c r="E24" s="604" t="n"/>
+      <c r="F24" s="581" t="n"/>
+      <c r="G24" s="581" t="n"/>
+      <c r="H24" s="581" t="n"/>
+      <c r="I24" s="446" t="n"/>
+      <c r="J24" s="446" t="n"/>
+      <c r="K24" s="446" t="n"/>
+      <c r="L24" s="446" t="n"/>
+      <c r="M24" s="446" t="n"/>
+      <c r="N24" s="446" t="n"/>
+      <c r="O24" s="446" t="n"/>
+      <c r="P24" s="446" t="n"/>
+      <c r="Q24" s="446" t="n"/>
+      <c r="R24" s="446" t="n"/>
+      <c r="S24" s="446" t="n"/>
+      <c r="T24" s="446" t="n"/>
+      <c r="U24" s="446" t="n"/>
+      <c r="V24" s="446" t="n"/>
+      <c r="W24" s="446" t="n"/>
+      <c r="X24" s="446" t="n"/>
+      <c r="Y24" s="446" t="n"/>
+      <c r="Z24" s="446" t="n"/>
+      <c r="AA24" s="446" t="n"/>
+      <c r="AB24" s="446" t="n"/>
+      <c r="AC24" s="446" t="n"/>
+      <c r="AD24" s="446" t="n"/>
+      <c r="AE24" s="446" t="n"/>
+      <c r="AF24" s="446" t="n"/>
+      <c r="AG24" s="446" t="n"/>
+      <c r="AH24" s="446" t="n"/>
+      <c r="AI24" s="446" t="n"/>
+      <c r="AJ24" s="446" t="n"/>
+      <c r="AK24" s="446" t="n"/>
+      <c r="AL24" s="446" t="n"/>
+      <c r="AM24" s="446" t="n"/>
+      <c r="AN24" s="562" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="447" t="n"/>
-      <c r="B25" s="447" t="n"/>
-      <c r="C25" s="447" t="n"/>
-      <c r="D25" s="447" t="n"/>
-      <c r="E25" s="447" t="n"/>
-      <c r="F25" s="447" t="n"/>
-      <c r="G25" s="447" t="n"/>
-      <c r="H25" s="447" t="n"/>
-      <c r="I25" s="447" t="n"/>
-      <c r="J25" s="447" t="n"/>
-      <c r="K25" s="447" t="n"/>
-      <c r="L25" s="447" t="n"/>
-      <c r="M25" s="447" t="n"/>
-      <c r="N25" s="447" t="n"/>
-      <c r="O25" s="447" t="n"/>
-      <c r="P25" s="447" t="n"/>
-      <c r="Q25" s="447" t="n"/>
-      <c r="R25" s="447" t="n"/>
-      <c r="S25" s="447" t="n"/>
-      <c r="T25" s="447" t="n"/>
-      <c r="U25" s="447" t="n"/>
-      <c r="V25" s="447" t="n"/>
-      <c r="W25" s="447" t="n"/>
-      <c r="X25" s="447" t="n"/>
-      <c r="Y25" s="447" t="n"/>
-      <c r="Z25" s="447" t="n"/>
-      <c r="AA25" s="447" t="n"/>
-      <c r="AB25" s="447" t="n"/>
-      <c r="AC25" s="447" t="n"/>
-      <c r="AD25" s="447" t="n"/>
-      <c r="AE25" s="447" t="n"/>
-      <c r="AF25" s="447" t="n"/>
-      <c r="AG25" s="447" t="n"/>
-      <c r="AH25" s="447" t="n"/>
-      <c r="AI25" s="447" t="n"/>
-      <c r="AJ25" s="447" t="n"/>
-      <c r="AK25" s="447" t="n"/>
-      <c r="AL25" s="447" t="n"/>
-      <c r="AM25" s="447" t="n"/>
-      <c r="AN25" s="447" t="n"/>
+      <c r="A25" s="596" t="n"/>
+      <c r="B25" s="571" t="n"/>
+      <c r="C25" s="572" t="n"/>
+      <c r="D25" s="572" t="n"/>
+      <c r="E25" s="572" t="n"/>
+      <c r="F25" s="572" t="n"/>
+      <c r="G25" s="572" t="n"/>
+      <c r="H25" s="572" t="n"/>
+      <c r="I25" s="572" t="n"/>
+      <c r="J25" s="572" t="n"/>
+      <c r="K25" s="572" t="n"/>
+      <c r="L25" s="572" t="n"/>
+      <c r="M25" s="572" t="n"/>
+      <c r="N25" s="572" t="n"/>
+      <c r="O25" s="572" t="n"/>
+      <c r="P25" s="572" t="n"/>
+      <c r="Q25" s="572" t="n"/>
+      <c r="R25" s="572" t="n"/>
+      <c r="S25" s="572" t="n"/>
+      <c r="T25" s="572" t="n"/>
+      <c r="U25" s="572" t="n"/>
+      <c r="V25" s="572" t="n"/>
+      <c r="W25" s="572" t="n"/>
+      <c r="X25" s="572" t="n"/>
+      <c r="Y25" s="572" t="n"/>
+      <c r="Z25" s="572" t="n"/>
+      <c r="AA25" s="572" t="n"/>
+      <c r="AB25" s="572" t="n"/>
+      <c r="AC25" s="572" t="n"/>
+      <c r="AD25" s="572" t="n"/>
+      <c r="AE25" s="572" t="n"/>
+      <c r="AF25" s="572" t="n"/>
+      <c r="AG25" s="572" t="n"/>
+      <c r="AH25" s="572" t="n"/>
+      <c r="AI25" s="572" t="n"/>
+      <c r="AJ25" s="572" t="n"/>
+      <c r="AK25" s="572" t="n"/>
+      <c r="AL25" s="572" t="n"/>
+      <c r="AM25" s="572" t="n"/>
+      <c r="AN25" s="573" t="n"/>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="470" t="inlineStr">
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="548" t="inlineStr">
         <is>
           <t>NOTICE  —  Periodic review and closeout support sheet for the rolling workbook.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B26" s="484" t="n"/>
-      <c r="C26" s="484" t="n"/>
-      <c r="D26" s="484" t="n"/>
-      <c r="E26" s="484" t="n"/>
-      <c r="F26" s="484" t="n"/>
-      <c r="G26" s="484" t="n"/>
-      <c r="H26" s="485" t="n"/>
-      <c r="I26" s="430" t="n"/>
-      <c r="J26" s="430" t="n"/>
-      <c r="K26" s="430" t="n"/>
-      <c r="L26" s="430" t="n"/>
-      <c r="M26" s="430" t="n"/>
-      <c r="N26" s="430" t="n"/>
-      <c r="O26" s="430" t="n"/>
-      <c r="P26" s="430" t="n"/>
-      <c r="Q26" s="430" t="n"/>
-      <c r="R26" s="430" t="n"/>
-      <c r="S26" s="430" t="n"/>
-      <c r="T26" s="430" t="n"/>
-      <c r="U26" s="430" t="n"/>
-      <c r="V26" s="430" t="n"/>
-      <c r="W26" s="430" t="n"/>
-      <c r="X26" s="430" t="n"/>
-      <c r="Y26" s="430" t="n"/>
-      <c r="Z26" s="430" t="n"/>
-      <c r="AA26" s="430" t="n"/>
-      <c r="AB26" s="430" t="n"/>
-      <c r="AC26" s="430" t="n"/>
-      <c r="AD26" s="430" t="n"/>
-      <c r="AE26" s="430" t="n"/>
-      <c r="AF26" s="430" t="n"/>
-      <c r="AG26" s="430" t="n"/>
-      <c r="AH26" s="430" t="n"/>
-      <c r="AI26" s="430" t="n"/>
-      <c r="AJ26" s="430" t="n"/>
-      <c r="AK26" s="430" t="n"/>
-      <c r="AL26" s="430" t="n"/>
-      <c r="AM26" s="430" t="n"/>
-      <c r="AN26" s="430" t="n"/>
+      <c r="B26" s="549" t="n"/>
+      <c r="C26" s="549" t="n"/>
+      <c r="D26" s="549" t="n"/>
+      <c r="E26" s="549" t="n"/>
+      <c r="F26" s="549" t="n"/>
+      <c r="G26" s="549" t="n"/>
+      <c r="H26" s="549" t="n"/>
+      <c r="I26" s="549" t="n"/>
+      <c r="J26" s="549" t="n"/>
+      <c r="K26" s="549" t="n"/>
+      <c r="L26" s="549" t="n"/>
+      <c r="M26" s="549" t="n"/>
+      <c r="N26" s="549" t="n"/>
+      <c r="O26" s="549" t="n"/>
+      <c r="P26" s="549" t="n"/>
+      <c r="Q26" s="549" t="n"/>
+      <c r="R26" s="549" t="n"/>
+      <c r="S26" s="549" t="n"/>
+      <c r="T26" s="549" t="n"/>
+      <c r="U26" s="549" t="n"/>
+      <c r="V26" s="549" t="n"/>
+      <c r="W26" s="549" t="n"/>
+      <c r="X26" s="549" t="n"/>
+      <c r="Y26" s="549" t="n"/>
+      <c r="Z26" s="549" t="n"/>
+      <c r="AA26" s="549" t="n"/>
+      <c r="AB26" s="549" t="n"/>
+      <c r="AC26" s="549" t="n"/>
+      <c r="AD26" s="549" t="n"/>
+      <c r="AE26" s="549" t="n"/>
+      <c r="AF26" s="549" t="n"/>
+      <c r="AG26" s="549" t="n"/>
+      <c r="AH26" s="549" t="n"/>
+      <c r="AI26" s="549" t="n"/>
+      <c r="AJ26" s="549" t="n"/>
+      <c r="AK26" s="549" t="n"/>
+      <c r="AL26" s="549" t="n"/>
+      <c r="AM26" s="549" t="n"/>
+      <c r="AN26" s="550" t="n"/>
     </row>
     <row r="27" hidden="1" outlineLevel="1"/>
     <row r="28" hidden="1" outlineLevel="1"/>
@@ -10953,7 +11679,7 @@
     <row r="199" hidden="1" outlineLevel="1"/>
     <row r="200" hidden="1" outlineLevel="1"/>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="28">
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A15:H15"/>
@@ -10961,7 +11687,6 @@
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="E8:F8"/>
-    <mergeCell ref="A6:H6"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="E10:F10"/>
@@ -10981,7 +11706,6 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C1:F3"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:H13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="G9:H9"/>
   </mergeCells>
@@ -11007,8 +11731,9 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -11064,497 +11789,503 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="474" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="606" t="inlineStr">
         <is>
           <t>REF_LINKS</t>
         </is>
       </c>
-      <c r="B1" s="503" t="n"/>
-      <c r="C1" s="503" t="n"/>
-      <c r="D1" s="503" t="n"/>
-      <c r="E1" s="503" t="n"/>
-      <c r="F1" s="503" t="n"/>
-      <c r="G1" s="504" t="n"/>
-      <c r="H1" s="430" t="n"/>
-      <c r="I1" s="430" t="n"/>
-      <c r="J1" s="430" t="n"/>
-      <c r="K1" s="430" t="n"/>
-      <c r="L1" s="430" t="n"/>
-      <c r="M1" s="430" t="n"/>
-      <c r="N1" s="430" t="n"/>
-      <c r="O1" s="430" t="n"/>
-      <c r="P1" s="430" t="n"/>
-      <c r="Q1" s="430" t="n"/>
-      <c r="R1" s="430" t="n"/>
-      <c r="S1" s="430" t="n"/>
-      <c r="T1" s="430" t="n"/>
-      <c r="U1" s="430" t="n"/>
-      <c r="V1" s="430" t="n"/>
-      <c r="W1" s="430" t="n"/>
-      <c r="X1" s="430" t="n"/>
-      <c r="Y1" s="430" t="n"/>
-      <c r="Z1" s="430" t="n"/>
-      <c r="AA1" s="430" t="n"/>
-      <c r="AB1" s="430" t="n"/>
-      <c r="AC1" s="430" t="n"/>
-      <c r="AD1" s="430" t="n"/>
-      <c r="AE1" s="430" t="n"/>
-      <c r="AF1" s="430" t="n"/>
-      <c r="AG1" s="430" t="n"/>
-      <c r="AH1" s="430" t="n"/>
-      <c r="AI1" s="430" t="n"/>
-      <c r="AJ1" s="430" t="n"/>
-      <c r="AK1" s="430" t="n"/>
-      <c r="AL1" s="430" t="n"/>
-      <c r="AM1" s="430" t="n"/>
-      <c r="AN1" s="430" t="n"/>
+      <c r="B1" s="506" t="n"/>
+      <c r="C1" s="506" t="n"/>
+      <c r="D1" s="506" t="n"/>
+      <c r="E1" s="506" t="n"/>
+      <c r="F1" s="506" t="n"/>
+      <c r="G1" s="506" t="n"/>
+      <c r="H1" s="607" t="n"/>
+      <c r="I1" s="509" t="n"/>
+      <c r="J1" s="510" t="n"/>
+      <c r="K1" s="510" t="n"/>
+      <c r="L1" s="510" t="n"/>
+      <c r="M1" s="510" t="n"/>
+      <c r="N1" s="510" t="n"/>
+      <c r="O1" s="510" t="n"/>
+      <c r="P1" s="510" t="n"/>
+      <c r="Q1" s="510" t="n"/>
+      <c r="R1" s="510" t="n"/>
+      <c r="S1" s="510" t="n"/>
+      <c r="T1" s="510" t="n"/>
+      <c r="U1" s="510" t="n"/>
+      <c r="V1" s="510" t="n"/>
+      <c r="W1" s="510" t="n"/>
+      <c r="X1" s="510" t="n"/>
+      <c r="Y1" s="510" t="n"/>
+      <c r="Z1" s="510" t="n"/>
+      <c r="AA1" s="510" t="n"/>
+      <c r="AB1" s="510" t="n"/>
+      <c r="AC1" s="510" t="n"/>
+      <c r="AD1" s="511" t="n"/>
+      <c r="AE1" s="512" t="n"/>
+      <c r="AF1" s="513" t="n"/>
+      <c r="AG1" s="513" t="n"/>
+      <c r="AH1" s="514" t="n"/>
+      <c r="AI1" s="515" t="n"/>
+      <c r="AJ1" s="516" t="n"/>
+      <c r="AK1" s="516" t="n"/>
+      <c r="AL1" s="516" t="n"/>
+      <c r="AM1" s="516" t="n"/>
+      <c r="AN1" s="517" t="n"/>
     </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="321" t="inlineStr">
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="608" t="inlineStr">
         <is>
           <t>Reference Epicor / M365 / controlled documents only.</t>
         </is>
       </c>
-      <c r="H2" s="430" t="n"/>
-      <c r="I2" s="430" t="n"/>
-      <c r="J2" s="430" t="n"/>
-      <c r="K2" s="430" t="n"/>
-      <c r="L2" s="430" t="n"/>
-      <c r="M2" s="430" t="n"/>
-      <c r="N2" s="430" t="n"/>
-      <c r="O2" s="430" t="n"/>
-      <c r="P2" s="430" t="n"/>
-      <c r="Q2" s="430" t="n"/>
-      <c r="R2" s="430" t="n"/>
-      <c r="S2" s="430" t="n"/>
-      <c r="T2" s="430" t="n"/>
-      <c r="U2" s="430" t="n"/>
-      <c r="V2" s="430" t="n"/>
-      <c r="W2" s="430" t="n"/>
-      <c r="X2" s="430" t="n"/>
-      <c r="Y2" s="430" t="n"/>
-      <c r="Z2" s="430" t="n"/>
-      <c r="AA2" s="430" t="n"/>
-      <c r="AB2" s="430" t="n"/>
-      <c r="AC2" s="430" t="n"/>
-      <c r="AD2" s="430" t="n"/>
-      <c r="AE2" s="430" t="n"/>
-      <c r="AF2" s="430" t="n"/>
-      <c r="AG2" s="430" t="n"/>
-      <c r="AH2" s="430" t="n"/>
-      <c r="AI2" s="430" t="n"/>
-      <c r="AJ2" s="430" t="n"/>
-      <c r="AK2" s="430" t="n"/>
-      <c r="AL2" s="430" t="n"/>
-      <c r="AM2" s="430" t="n"/>
-      <c r="AN2" s="430" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="609" t="n"/>
+      <c r="I2" s="520" t="n"/>
+      <c r="J2" s="521" t="n"/>
+      <c r="K2" s="521" t="n"/>
+      <c r="L2" s="521" t="n"/>
+      <c r="M2" s="521" t="n"/>
+      <c r="N2" s="521" t="n"/>
+      <c r="O2" s="521" t="n"/>
+      <c r="P2" s="521" t="n"/>
+      <c r="Q2" s="521" t="n"/>
+      <c r="R2" s="521" t="n"/>
+      <c r="S2" s="521" t="n"/>
+      <c r="T2" s="521" t="n"/>
+      <c r="U2" s="521" t="n"/>
+      <c r="V2" s="521" t="n"/>
+      <c r="W2" s="521" t="n"/>
+      <c r="X2" s="521" t="n"/>
+      <c r="Y2" s="521" t="n"/>
+      <c r="Z2" s="521" t="n"/>
+      <c r="AA2" s="521" t="n"/>
+      <c r="AB2" s="521" t="n"/>
+      <c r="AC2" s="521" t="n"/>
+      <c r="AD2" s="522" t="n"/>
+      <c r="AE2" s="523" t="n"/>
+      <c r="AF2" s="524" t="n"/>
+      <c r="AG2" s="524" t="n"/>
+      <c r="AH2" s="525" t="n"/>
+      <c r="AI2" s="526" t="n"/>
+      <c r="AJ2" s="527" t="n"/>
+      <c r="AK2" s="527" t="n"/>
+      <c r="AL2" s="527" t="n"/>
+      <c r="AM2" s="527" t="n"/>
+      <c r="AN2" s="528" t="n"/>
     </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="475" t="inlineStr">
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="610" t="inlineStr">
         <is>
           <t>Ref Type</t>
         </is>
       </c>
-      <c r="B3" s="475" t="inlineStr">
+      <c r="B3" s="611" t="inlineStr">
         <is>
           <t>Document / Record</t>
         </is>
       </c>
-      <c r="C3" s="475" t="inlineStr">
+      <c r="C3" s="611" t="inlineStr">
         <is>
           <t>System of Record</t>
         </is>
       </c>
-      <c r="D3" s="475" t="inlineStr">
+      <c r="D3" s="611" t="inlineStr">
         <is>
           <t>Unique Ref</t>
         </is>
       </c>
-      <c r="E3" s="475" t="inlineStr">
+      <c r="E3" s="611" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F3" s="475" t="inlineStr">
+      <c r="F3" s="611" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G3" s="475" t="inlineStr">
+      <c r="G3" s="611" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="H3" s="430" t="n"/>
-      <c r="I3" s="430" t="n"/>
-      <c r="J3" s="430" t="n"/>
-      <c r="K3" s="430" t="n"/>
-      <c r="L3" s="430" t="n"/>
-      <c r="M3" s="430" t="n"/>
-      <c r="N3" s="430" t="n"/>
-      <c r="O3" s="430" t="n"/>
-      <c r="P3" s="430" t="n"/>
-      <c r="Q3" s="430" t="n"/>
-      <c r="R3" s="430" t="n"/>
-      <c r="S3" s="430" t="n"/>
-      <c r="T3" s="430" t="n"/>
-      <c r="U3" s="430" t="n"/>
-      <c r="V3" s="430" t="n"/>
-      <c r="W3" s="430" t="n"/>
-      <c r="X3" s="430" t="n"/>
-      <c r="Y3" s="430" t="n"/>
-      <c r="Z3" s="430" t="n"/>
-      <c r="AA3" s="430" t="n"/>
-      <c r="AB3" s="430" t="n"/>
-      <c r="AC3" s="430" t="n"/>
-      <c r="AD3" s="430" t="n"/>
-      <c r="AE3" s="430" t="n"/>
-      <c r="AF3" s="430" t="n"/>
-      <c r="AG3" s="430" t="n"/>
-      <c r="AH3" s="430" t="n"/>
-      <c r="AI3" s="430" t="n"/>
-      <c r="AJ3" s="430" t="n"/>
-      <c r="AK3" s="430" t="n"/>
-      <c r="AL3" s="430" t="n"/>
-      <c r="AM3" s="430" t="n"/>
-      <c r="AN3" s="430" t="n"/>
+      <c r="H3" s="609" t="n"/>
+      <c r="I3" s="520" t="n"/>
+      <c r="J3" s="521" t="n"/>
+      <c r="K3" s="521" t="n"/>
+      <c r="L3" s="521" t="n"/>
+      <c r="M3" s="521" t="n"/>
+      <c r="N3" s="521" t="n"/>
+      <c r="O3" s="521" t="n"/>
+      <c r="P3" s="521" t="n"/>
+      <c r="Q3" s="521" t="n"/>
+      <c r="R3" s="521" t="n"/>
+      <c r="S3" s="521" t="n"/>
+      <c r="T3" s="521" t="n"/>
+      <c r="U3" s="521" t="n"/>
+      <c r="V3" s="521" t="n"/>
+      <c r="W3" s="521" t="n"/>
+      <c r="X3" s="521" t="n"/>
+      <c r="Y3" s="521" t="n"/>
+      <c r="Z3" s="521" t="n"/>
+      <c r="AA3" s="521" t="n"/>
+      <c r="AB3" s="521" t="n"/>
+      <c r="AC3" s="521" t="n"/>
+      <c r="AD3" s="522" t="n"/>
+      <c r="AE3" s="523" t="n"/>
+      <c r="AF3" s="524" t="n"/>
+      <c r="AG3" s="524" t="n"/>
+      <c r="AH3" s="525" t="n"/>
+      <c r="AI3" s="526" t="n"/>
+      <c r="AJ3" s="527" t="n"/>
+      <c r="AK3" s="527" t="n"/>
+      <c r="AL3" s="527" t="n"/>
+      <c r="AM3" s="527" t="n"/>
+      <c r="AN3" s="528" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="476" t="n"/>
-      <c r="B4" s="476" t="n"/>
-      <c r="C4" s="476" t="n"/>
-      <c r="D4" s="476" t="n"/>
-      <c r="E4" s="476" t="n"/>
-      <c r="F4" s="476" t="n"/>
-      <c r="G4" s="476" t="n"/>
-      <c r="H4" s="430" t="n"/>
-      <c r="I4" s="430" t="n"/>
-      <c r="J4" s="430" t="n"/>
-      <c r="K4" s="430" t="n"/>
-      <c r="L4" s="430" t="n"/>
-      <c r="M4" s="430" t="n"/>
-      <c r="N4" s="430" t="n"/>
-      <c r="O4" s="430" t="n"/>
-      <c r="P4" s="430" t="n"/>
-      <c r="Q4" s="430" t="n"/>
-      <c r="R4" s="430" t="n"/>
-      <c r="S4" s="430" t="n"/>
-      <c r="T4" s="430" t="n"/>
-      <c r="U4" s="430" t="n"/>
-      <c r="V4" s="430" t="n"/>
-      <c r="W4" s="430" t="n"/>
-      <c r="X4" s="430" t="n"/>
-      <c r="Y4" s="430" t="n"/>
-      <c r="Z4" s="430" t="n"/>
-      <c r="AA4" s="430" t="n"/>
-      <c r="AB4" s="430" t="n"/>
-      <c r="AC4" s="430" t="n"/>
-      <c r="AD4" s="430" t="n"/>
-      <c r="AE4" s="430" t="n"/>
-      <c r="AF4" s="430" t="n"/>
-      <c r="AG4" s="430" t="n"/>
-      <c r="AH4" s="430" t="n"/>
-      <c r="AI4" s="430" t="n"/>
-      <c r="AJ4" s="430" t="n"/>
-      <c r="AK4" s="430" t="n"/>
-      <c r="AL4" s="430" t="n"/>
-      <c r="AM4" s="430" t="n"/>
-      <c r="AN4" s="430" t="n"/>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="612" t="n"/>
+      <c r="B4" s="613" t="n"/>
+      <c r="C4" s="613" t="n"/>
+      <c r="D4" s="613" t="n"/>
+      <c r="E4" s="613" t="n"/>
+      <c r="F4" s="613" t="n"/>
+      <c r="G4" s="613" t="n"/>
+      <c r="H4" s="609" t="n"/>
+      <c r="I4" s="530" t="n"/>
+      <c r="J4" s="531" t="n"/>
+      <c r="K4" s="531" t="n"/>
+      <c r="L4" s="531" t="n"/>
+      <c r="M4" s="531" t="n"/>
+      <c r="N4" s="531" t="n"/>
+      <c r="O4" s="531" t="n"/>
+      <c r="P4" s="531" t="n"/>
+      <c r="Q4" s="531" t="n"/>
+      <c r="R4" s="531" t="n"/>
+      <c r="S4" s="531" t="n"/>
+      <c r="T4" s="531" t="n"/>
+      <c r="U4" s="531" t="n"/>
+      <c r="V4" s="531" t="n"/>
+      <c r="W4" s="531" t="n"/>
+      <c r="X4" s="531" t="n"/>
+      <c r="Y4" s="531" t="n"/>
+      <c r="Z4" s="531" t="n"/>
+      <c r="AA4" s="531" t="n"/>
+      <c r="AB4" s="531" t="n"/>
+      <c r="AC4" s="531" t="n"/>
+      <c r="AD4" s="532" t="n"/>
+      <c r="AE4" s="523" t="n"/>
+      <c r="AF4" s="524" t="n"/>
+      <c r="AG4" s="524" t="n"/>
+      <c r="AH4" s="525" t="n"/>
+      <c r="AI4" s="526" t="n"/>
+      <c r="AJ4" s="527" t="n"/>
+      <c r="AK4" s="527" t="n"/>
+      <c r="AL4" s="527" t="n"/>
+      <c r="AM4" s="527" t="n"/>
+      <c r="AN4" s="528" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="476" t="n"/>
-      <c r="B5" s="476" t="n"/>
-      <c r="C5" s="476" t="n"/>
-      <c r="D5" s="476" t="n"/>
-      <c r="E5" s="476" t="n"/>
-      <c r="F5" s="476" t="n"/>
-      <c r="G5" s="476" t="n"/>
-      <c r="H5" s="430" t="n"/>
-      <c r="I5" s="430" t="n"/>
-      <c r="J5" s="430" t="n"/>
-      <c r="K5" s="430" t="n"/>
-      <c r="L5" s="430" t="n"/>
-      <c r="M5" s="430" t="n"/>
-      <c r="N5" s="430" t="n"/>
-      <c r="O5" s="430" t="n"/>
-      <c r="P5" s="430" t="n"/>
-      <c r="Q5" s="430" t="n"/>
-      <c r="R5" s="430" t="n"/>
-      <c r="S5" s="430" t="n"/>
-      <c r="T5" s="430" t="n"/>
-      <c r="U5" s="430" t="n"/>
-      <c r="V5" s="430" t="n"/>
-      <c r="W5" s="430" t="n"/>
-      <c r="X5" s="430" t="n"/>
-      <c r="Y5" s="430" t="n"/>
-      <c r="Z5" s="430" t="n"/>
-      <c r="AA5" s="430" t="n"/>
-      <c r="AB5" s="430" t="n"/>
-      <c r="AC5" s="430" t="n"/>
-      <c r="AD5" s="430" t="n"/>
-      <c r="AE5" s="430" t="n"/>
-      <c r="AF5" s="430" t="n"/>
-      <c r="AG5" s="430" t="n"/>
-      <c r="AH5" s="430" t="n"/>
-      <c r="AI5" s="430" t="n"/>
-      <c r="AJ5" s="430" t="n"/>
-      <c r="AK5" s="430" t="n"/>
-      <c r="AL5" s="430" t="n"/>
-      <c r="AM5" s="430" t="n"/>
-      <c r="AN5" s="430" t="n"/>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="614" t="n"/>
+      <c r="B5" s="615" t="n"/>
+      <c r="C5" s="615" t="n"/>
+      <c r="D5" s="615" t="n"/>
+      <c r="E5" s="615" t="n"/>
+      <c r="F5" s="615" t="n"/>
+      <c r="G5" s="615" t="n"/>
+      <c r="H5" s="616" t="n"/>
+      <c r="I5" s="537" t="n"/>
+      <c r="J5" s="538" t="n"/>
+      <c r="K5" s="538" t="n"/>
+      <c r="L5" s="538" t="n"/>
+      <c r="M5" s="538" t="n"/>
+      <c r="N5" s="538" t="n"/>
+      <c r="O5" s="538" t="n"/>
+      <c r="P5" s="538" t="n"/>
+      <c r="Q5" s="538" t="n"/>
+      <c r="R5" s="538" t="n"/>
+      <c r="S5" s="538" t="n"/>
+      <c r="T5" s="538" t="n"/>
+      <c r="U5" s="538" t="n"/>
+      <c r="V5" s="538" t="n"/>
+      <c r="W5" s="538" t="n"/>
+      <c r="X5" s="538" t="n"/>
+      <c r="Y5" s="538" t="n"/>
+      <c r="Z5" s="538" t="n"/>
+      <c r="AA5" s="538" t="n"/>
+      <c r="AB5" s="538" t="n"/>
+      <c r="AC5" s="538" t="n"/>
+      <c r="AD5" s="539" t="n"/>
+      <c r="AE5" s="540" t="n"/>
+      <c r="AF5" s="541" t="n"/>
+      <c r="AG5" s="541" t="n"/>
+      <c r="AH5" s="542" t="n"/>
+      <c r="AI5" s="543" t="n"/>
+      <c r="AJ5" s="544" t="n"/>
+      <c r="AK5" s="544" t="n"/>
+      <c r="AL5" s="544" t="n"/>
+      <c r="AM5" s="544" t="n"/>
+      <c r="AN5" s="545" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="476" t="n"/>
-      <c r="B6" s="476" t="n"/>
-      <c r="C6" s="476" t="n"/>
-      <c r="D6" s="476" t="n"/>
-      <c r="E6" s="476" t="n"/>
-      <c r="F6" s="476" t="n"/>
-      <c r="G6" s="476" t="n"/>
-      <c r="H6" s="430" t="n"/>
-      <c r="I6" s="430" t="n"/>
-      <c r="J6" s="430" t="n"/>
-      <c r="K6" s="430" t="n"/>
-      <c r="L6" s="430" t="n"/>
-      <c r="M6" s="430" t="n"/>
-      <c r="N6" s="430" t="n"/>
-      <c r="O6" s="430" t="n"/>
-      <c r="P6" s="430" t="n"/>
-      <c r="Q6" s="430" t="n"/>
-      <c r="R6" s="430" t="n"/>
-      <c r="S6" s="430" t="n"/>
-      <c r="T6" s="430" t="n"/>
-      <c r="U6" s="430" t="n"/>
-      <c r="V6" s="430" t="n"/>
-      <c r="W6" s="430" t="n"/>
-      <c r="X6" s="430" t="n"/>
-      <c r="Y6" s="430" t="n"/>
-      <c r="Z6" s="430" t="n"/>
-      <c r="AA6" s="430" t="n"/>
-      <c r="AB6" s="430" t="n"/>
-      <c r="AC6" s="430" t="n"/>
-      <c r="AD6" s="430" t="n"/>
-      <c r="AE6" s="430" t="n"/>
-      <c r="AF6" s="430" t="n"/>
-      <c r="AG6" s="430" t="n"/>
-      <c r="AH6" s="430" t="n"/>
-      <c r="AI6" s="430" t="n"/>
-      <c r="AJ6" s="430" t="n"/>
-      <c r="AK6" s="430" t="n"/>
-      <c r="AL6" s="430" t="n"/>
-      <c r="AM6" s="430" t="n"/>
-      <c r="AN6" s="430" t="n"/>
+      <c r="A6" s="617" t="n"/>
+      <c r="B6" s="618" t="n"/>
+      <c r="C6" s="618" t="n"/>
+      <c r="D6" s="618" t="n"/>
+      <c r="E6" s="618" t="n"/>
+      <c r="F6" s="618" t="n"/>
+      <c r="G6" s="618" t="n"/>
+      <c r="H6" s="552" t="n"/>
+      <c r="I6" s="552" t="n"/>
+      <c r="J6" s="552" t="n"/>
+      <c r="K6" s="552" t="n"/>
+      <c r="L6" s="552" t="n"/>
+      <c r="M6" s="552" t="n"/>
+      <c r="N6" s="552" t="n"/>
+      <c r="O6" s="552" t="n"/>
+      <c r="P6" s="552" t="n"/>
+      <c r="Q6" s="552" t="n"/>
+      <c r="R6" s="552" t="n"/>
+      <c r="S6" s="552" t="n"/>
+      <c r="T6" s="552" t="n"/>
+      <c r="U6" s="552" t="n"/>
+      <c r="V6" s="552" t="n"/>
+      <c r="W6" s="552" t="n"/>
+      <c r="X6" s="552" t="n"/>
+      <c r="Y6" s="552" t="n"/>
+      <c r="Z6" s="552" t="n"/>
+      <c r="AA6" s="552" t="n"/>
+      <c r="AB6" s="552" t="n"/>
+      <c r="AC6" s="552" t="n"/>
+      <c r="AD6" s="552" t="n"/>
+      <c r="AE6" s="552" t="n"/>
+      <c r="AF6" s="552" t="n"/>
+      <c r="AG6" s="552" t="n"/>
+      <c r="AH6" s="552" t="n"/>
+      <c r="AI6" s="552" t="n"/>
+      <c r="AJ6" s="552" t="n"/>
+      <c r="AK6" s="552" t="n"/>
+      <c r="AL6" s="552" t="n"/>
+      <c r="AM6" s="552" t="n"/>
+      <c r="AN6" s="595" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="476" t="n"/>
-      <c r="B7" s="476" t="n"/>
-      <c r="C7" s="476" t="n"/>
-      <c r="D7" s="476" t="n"/>
-      <c r="E7" s="476" t="n"/>
-      <c r="F7" s="476" t="n"/>
-      <c r="G7" s="476" t="n"/>
-      <c r="H7" s="430" t="n"/>
-      <c r="I7" s="430" t="n"/>
-      <c r="J7" s="430" t="n"/>
-      <c r="K7" s="430" t="n"/>
-      <c r="L7" s="430" t="n"/>
-      <c r="M7" s="430" t="n"/>
-      <c r="N7" s="430" t="n"/>
-      <c r="O7" s="430" t="n"/>
-      <c r="P7" s="430" t="n"/>
-      <c r="Q7" s="430" t="n"/>
-      <c r="R7" s="430" t="n"/>
-      <c r="S7" s="430" t="n"/>
-      <c r="T7" s="430" t="n"/>
-      <c r="U7" s="430" t="n"/>
-      <c r="V7" s="430" t="n"/>
-      <c r="W7" s="430" t="n"/>
-      <c r="X7" s="430" t="n"/>
-      <c r="Y7" s="430" t="n"/>
-      <c r="Z7" s="430" t="n"/>
-      <c r="AA7" s="430" t="n"/>
-      <c r="AB7" s="430" t="n"/>
-      <c r="AC7" s="430" t="n"/>
-      <c r="AD7" s="430" t="n"/>
-      <c r="AE7" s="430" t="n"/>
-      <c r="AF7" s="430" t="n"/>
-      <c r="AG7" s="430" t="n"/>
-      <c r="AH7" s="430" t="n"/>
-      <c r="AI7" s="430" t="n"/>
-      <c r="AJ7" s="430" t="n"/>
-      <c r="AK7" s="430" t="n"/>
-      <c r="AL7" s="430" t="n"/>
-      <c r="AM7" s="430" t="n"/>
-      <c r="AN7" s="430" t="n"/>
+      <c r="A7" s="619" t="n"/>
+      <c r="B7" s="620" t="n"/>
+      <c r="C7" s="620" t="n"/>
+      <c r="D7" s="620" t="n"/>
+      <c r="E7" s="620" t="n"/>
+      <c r="F7" s="620" t="n"/>
+      <c r="G7" s="620" t="n"/>
+      <c r="H7" s="437" t="n"/>
+      <c r="I7" s="437" t="n"/>
+      <c r="J7" s="437" t="n"/>
+      <c r="K7" s="437" t="n"/>
+      <c r="L7" s="437" t="n"/>
+      <c r="M7" s="437" t="n"/>
+      <c r="N7" s="437" t="n"/>
+      <c r="O7" s="437" t="n"/>
+      <c r="P7" s="437" t="n"/>
+      <c r="Q7" s="437" t="n"/>
+      <c r="R7" s="437" t="n"/>
+      <c r="S7" s="437" t="n"/>
+      <c r="T7" s="437" t="n"/>
+      <c r="U7" s="437" t="n"/>
+      <c r="V7" s="437" t="n"/>
+      <c r="W7" s="437" t="n"/>
+      <c r="X7" s="437" t="n"/>
+      <c r="Y7" s="437" t="n"/>
+      <c r="Z7" s="437" t="n"/>
+      <c r="AA7" s="437" t="n"/>
+      <c r="AB7" s="437" t="n"/>
+      <c r="AC7" s="437" t="n"/>
+      <c r="AD7" s="437" t="n"/>
+      <c r="AE7" s="437" t="n"/>
+      <c r="AF7" s="437" t="n"/>
+      <c r="AG7" s="437" t="n"/>
+      <c r="AH7" s="437" t="n"/>
+      <c r="AI7" s="437" t="n"/>
+      <c r="AJ7" s="437" t="n"/>
+      <c r="AK7" s="437" t="n"/>
+      <c r="AL7" s="437" t="n"/>
+      <c r="AM7" s="437" t="n"/>
+      <c r="AN7" s="564" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="476" t="n"/>
-      <c r="B8" s="476" t="n"/>
-      <c r="C8" s="476" t="n"/>
-      <c r="D8" s="476" t="n"/>
-      <c r="E8" s="476" t="n"/>
-      <c r="F8" s="476" t="n"/>
-      <c r="G8" s="476" t="n"/>
-      <c r="H8" s="447" t="n"/>
-      <c r="I8" s="447" t="n"/>
-      <c r="J8" s="447" t="n"/>
-      <c r="K8" s="447" t="n"/>
-      <c r="L8" s="447" t="n"/>
-      <c r="M8" s="447" t="n"/>
-      <c r="N8" s="447" t="n"/>
-      <c r="O8" s="447" t="n"/>
-      <c r="P8" s="447" t="n"/>
-      <c r="Q8" s="447" t="n"/>
-      <c r="R8" s="447" t="n"/>
-      <c r="S8" s="447" t="n"/>
-      <c r="T8" s="447" t="n"/>
-      <c r="U8" s="447" t="n"/>
-      <c r="V8" s="447" t="n"/>
-      <c r="W8" s="447" t="n"/>
-      <c r="X8" s="447" t="n"/>
-      <c r="Y8" s="447" t="n"/>
-      <c r="Z8" s="447" t="n"/>
-      <c r="AA8" s="447" t="n"/>
-      <c r="AB8" s="447" t="n"/>
-      <c r="AC8" s="447" t="n"/>
-      <c r="AD8" s="447" t="n"/>
-      <c r="AE8" s="447" t="n"/>
-      <c r="AF8" s="447" t="n"/>
-      <c r="AG8" s="447" t="n"/>
-      <c r="AH8" s="447" t="n"/>
-      <c r="AI8" s="447" t="n"/>
-      <c r="AJ8" s="447" t="n"/>
-      <c r="AK8" s="447" t="n"/>
-      <c r="AL8" s="447" t="n"/>
-      <c r="AM8" s="447" t="n"/>
-      <c r="AN8" s="447" t="n"/>
+      <c r="A8" s="619" t="n"/>
+      <c r="B8" s="620" t="n"/>
+      <c r="C8" s="620" t="n"/>
+      <c r="D8" s="620" t="n"/>
+      <c r="E8" s="620" t="n"/>
+      <c r="F8" s="620" t="n"/>
+      <c r="G8" s="620" t="n"/>
+      <c r="H8" s="446" t="n"/>
+      <c r="I8" s="446" t="n"/>
+      <c r="J8" s="446" t="n"/>
+      <c r="K8" s="446" t="n"/>
+      <c r="L8" s="446" t="n"/>
+      <c r="M8" s="446" t="n"/>
+      <c r="N8" s="446" t="n"/>
+      <c r="O8" s="446" t="n"/>
+      <c r="P8" s="446" t="n"/>
+      <c r="Q8" s="446" t="n"/>
+      <c r="R8" s="446" t="n"/>
+      <c r="S8" s="446" t="n"/>
+      <c r="T8" s="446" t="n"/>
+      <c r="U8" s="446" t="n"/>
+      <c r="V8" s="446" t="n"/>
+      <c r="W8" s="446" t="n"/>
+      <c r="X8" s="446" t="n"/>
+      <c r="Y8" s="446" t="n"/>
+      <c r="Z8" s="446" t="n"/>
+      <c r="AA8" s="446" t="n"/>
+      <c r="AB8" s="446" t="n"/>
+      <c r="AC8" s="446" t="n"/>
+      <c r="AD8" s="446" t="n"/>
+      <c r="AE8" s="446" t="n"/>
+      <c r="AF8" s="446" t="n"/>
+      <c r="AG8" s="446" t="n"/>
+      <c r="AH8" s="446" t="n"/>
+      <c r="AI8" s="446" t="n"/>
+      <c r="AJ8" s="446" t="n"/>
+      <c r="AK8" s="446" t="n"/>
+      <c r="AL8" s="446" t="n"/>
+      <c r="AM8" s="446" t="n"/>
+      <c r="AN8" s="562" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="476" t="n"/>
-      <c r="B9" s="476" t="n"/>
-      <c r="C9" s="476" t="n"/>
-      <c r="D9" s="476" t="n"/>
-      <c r="E9" s="476" t="n"/>
-      <c r="F9" s="476" t="n"/>
-      <c r="G9" s="476" t="n"/>
-      <c r="H9" s="447" t="n"/>
-      <c r="I9" s="447" t="n"/>
-      <c r="J9" s="447" t="n"/>
-      <c r="K9" s="447" t="n"/>
-      <c r="L9" s="447" t="n"/>
-      <c r="M9" s="447" t="n"/>
-      <c r="N9" s="447" t="n"/>
-      <c r="O9" s="447" t="n"/>
-      <c r="P9" s="447" t="n"/>
-      <c r="Q9" s="447" t="n"/>
-      <c r="R9" s="447" t="n"/>
-      <c r="S9" s="447" t="n"/>
-      <c r="T9" s="447" t="n"/>
-      <c r="U9" s="447" t="n"/>
-      <c r="V9" s="447" t="n"/>
-      <c r="W9" s="447" t="n"/>
-      <c r="X9" s="447" t="n"/>
-      <c r="Y9" s="447" t="n"/>
-      <c r="Z9" s="447" t="n"/>
-      <c r="AA9" s="447" t="n"/>
-      <c r="AB9" s="447" t="n"/>
-      <c r="AC9" s="447" t="n"/>
-      <c r="AD9" s="447" t="n"/>
-      <c r="AE9" s="447" t="n"/>
-      <c r="AF9" s="447" t="n"/>
-      <c r="AG9" s="447" t="n"/>
-      <c r="AH9" s="447" t="n"/>
-      <c r="AI9" s="447" t="n"/>
-      <c r="AJ9" s="447" t="n"/>
-      <c r="AK9" s="447" t="n"/>
-      <c r="AL9" s="447" t="n"/>
-      <c r="AM9" s="447" t="n"/>
-      <c r="AN9" s="447" t="n"/>
+      <c r="A9" s="619" t="n"/>
+      <c r="B9" s="620" t="n"/>
+      <c r="C9" s="620" t="n"/>
+      <c r="D9" s="620" t="n"/>
+      <c r="E9" s="620" t="n"/>
+      <c r="F9" s="620" t="n"/>
+      <c r="G9" s="620" t="n"/>
+      <c r="H9" s="446" t="n"/>
+      <c r="I9" s="446" t="n"/>
+      <c r="J9" s="446" t="n"/>
+      <c r="K9" s="446" t="n"/>
+      <c r="L9" s="446" t="n"/>
+      <c r="M9" s="446" t="n"/>
+      <c r="N9" s="446" t="n"/>
+      <c r="O9" s="446" t="n"/>
+      <c r="P9" s="446" t="n"/>
+      <c r="Q9" s="446" t="n"/>
+      <c r="R9" s="446" t="n"/>
+      <c r="S9" s="446" t="n"/>
+      <c r="T9" s="446" t="n"/>
+      <c r="U9" s="446" t="n"/>
+      <c r="V9" s="446" t="n"/>
+      <c r="W9" s="446" t="n"/>
+      <c r="X9" s="446" t="n"/>
+      <c r="Y9" s="446" t="n"/>
+      <c r="Z9" s="446" t="n"/>
+      <c r="AA9" s="446" t="n"/>
+      <c r="AB9" s="446" t="n"/>
+      <c r="AC9" s="446" t="n"/>
+      <c r="AD9" s="446" t="n"/>
+      <c r="AE9" s="446" t="n"/>
+      <c r="AF9" s="446" t="n"/>
+      <c r="AG9" s="446" t="n"/>
+      <c r="AH9" s="446" t="n"/>
+      <c r="AI9" s="446" t="n"/>
+      <c r="AJ9" s="446" t="n"/>
+      <c r="AK9" s="446" t="n"/>
+      <c r="AL9" s="446" t="n"/>
+      <c r="AM9" s="446" t="n"/>
+      <c r="AN9" s="562" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="476" t="n"/>
-      <c r="B10" s="476" t="n"/>
-      <c r="C10" s="476" t="n"/>
-      <c r="D10" s="476" t="n"/>
-      <c r="E10" s="476" t="n"/>
-      <c r="F10" s="476" t="n"/>
-      <c r="G10" s="476" t="n"/>
-      <c r="H10" s="447" t="n"/>
-      <c r="I10" s="447" t="n"/>
-      <c r="J10" s="447" t="n"/>
-      <c r="K10" s="447" t="n"/>
-      <c r="L10" s="447" t="n"/>
-      <c r="M10" s="447" t="n"/>
-      <c r="N10" s="447" t="n"/>
-      <c r="O10" s="447" t="n"/>
-      <c r="P10" s="447" t="n"/>
-      <c r="Q10" s="447" t="n"/>
-      <c r="R10" s="447" t="n"/>
-      <c r="S10" s="447" t="n"/>
-      <c r="T10" s="447" t="n"/>
-      <c r="U10" s="447" t="n"/>
-      <c r="V10" s="447" t="n"/>
-      <c r="W10" s="447" t="n"/>
-      <c r="X10" s="447" t="n"/>
-      <c r="Y10" s="447" t="n"/>
-      <c r="Z10" s="447" t="n"/>
-      <c r="AA10" s="447" t="n"/>
-      <c r="AB10" s="447" t="n"/>
-      <c r="AC10" s="447" t="n"/>
-      <c r="AD10" s="447" t="n"/>
-      <c r="AE10" s="447" t="n"/>
-      <c r="AF10" s="447" t="n"/>
-      <c r="AG10" s="447" t="n"/>
-      <c r="AH10" s="447" t="n"/>
-      <c r="AI10" s="447" t="n"/>
-      <c r="AJ10" s="447" t="n"/>
-      <c r="AK10" s="447" t="n"/>
-      <c r="AL10" s="447" t="n"/>
-      <c r="AM10" s="447" t="n"/>
-      <c r="AN10" s="447" t="n"/>
+      <c r="A10" s="619" t="n"/>
+      <c r="B10" s="620" t="n"/>
+      <c r="C10" s="620" t="n"/>
+      <c r="D10" s="620" t="n"/>
+      <c r="E10" s="620" t="n"/>
+      <c r="F10" s="620" t="n"/>
+      <c r="G10" s="620" t="n"/>
+      <c r="H10" s="446" t="n"/>
+      <c r="I10" s="446" t="n"/>
+      <c r="J10" s="446" t="n"/>
+      <c r="K10" s="446" t="n"/>
+      <c r="L10" s="446" t="n"/>
+      <c r="M10" s="446" t="n"/>
+      <c r="N10" s="446" t="n"/>
+      <c r="O10" s="446" t="n"/>
+      <c r="P10" s="446" t="n"/>
+      <c r="Q10" s="446" t="n"/>
+      <c r="R10" s="446" t="n"/>
+      <c r="S10" s="446" t="n"/>
+      <c r="T10" s="446" t="n"/>
+      <c r="U10" s="446" t="n"/>
+      <c r="V10" s="446" t="n"/>
+      <c r="W10" s="446" t="n"/>
+      <c r="X10" s="446" t="n"/>
+      <c r="Y10" s="446" t="n"/>
+      <c r="Z10" s="446" t="n"/>
+      <c r="AA10" s="446" t="n"/>
+      <c r="AB10" s="446" t="n"/>
+      <c r="AC10" s="446" t="n"/>
+      <c r="AD10" s="446" t="n"/>
+      <c r="AE10" s="446" t="n"/>
+      <c r="AF10" s="446" t="n"/>
+      <c r="AG10" s="446" t="n"/>
+      <c r="AH10" s="446" t="n"/>
+      <c r="AI10" s="446" t="n"/>
+      <c r="AJ10" s="446" t="n"/>
+      <c r="AK10" s="446" t="n"/>
+      <c r="AL10" s="446" t="n"/>
+      <c r="AM10" s="446" t="n"/>
+      <c r="AN10" s="562" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="476" t="n"/>
-      <c r="B11" s="476" t="n"/>
-      <c r="C11" s="476" t="n"/>
-      <c r="D11" s="476" t="n"/>
-      <c r="E11" s="476" t="n"/>
-      <c r="F11" s="476" t="n"/>
-      <c r="G11" s="476" t="n"/>
-      <c r="H11" s="447" t="n"/>
-      <c r="I11" s="447" t="n"/>
-      <c r="J11" s="447" t="n"/>
-      <c r="K11" s="447" t="n"/>
-      <c r="L11" s="447" t="n"/>
-      <c r="M11" s="447" t="n"/>
-      <c r="N11" s="447" t="n"/>
-      <c r="O11" s="447" t="n"/>
-      <c r="P11" s="447" t="n"/>
-      <c r="Q11" s="447" t="n"/>
-      <c r="R11" s="447" t="n"/>
-      <c r="S11" s="447" t="n"/>
-      <c r="T11" s="447" t="n"/>
-      <c r="U11" s="447" t="n"/>
-      <c r="V11" s="447" t="n"/>
-      <c r="W11" s="447" t="n"/>
-      <c r="X11" s="447" t="n"/>
-      <c r="Y11" s="447" t="n"/>
-      <c r="Z11" s="447" t="n"/>
-      <c r="AA11" s="447" t="n"/>
-      <c r="AB11" s="447" t="n"/>
-      <c r="AC11" s="447" t="n"/>
-      <c r="AD11" s="447" t="n"/>
-      <c r="AE11" s="447" t="n"/>
-      <c r="AF11" s="447" t="n"/>
-      <c r="AG11" s="447" t="n"/>
-      <c r="AH11" s="447" t="n"/>
-      <c r="AI11" s="447" t="n"/>
-      <c r="AJ11" s="447" t="n"/>
-      <c r="AK11" s="447" t="n"/>
-      <c r="AL11" s="447" t="n"/>
-      <c r="AM11" s="447" t="n"/>
-      <c r="AN11" s="447" t="n"/>
+      <c r="A11" s="621" t="n"/>
+      <c r="B11" s="622" t="n"/>
+      <c r="C11" s="622" t="n"/>
+      <c r="D11" s="622" t="n"/>
+      <c r="E11" s="622" t="n"/>
+      <c r="F11" s="622" t="n"/>
+      <c r="G11" s="622" t="n"/>
+      <c r="H11" s="572" t="n"/>
+      <c r="I11" s="572" t="n"/>
+      <c r="J11" s="572" t="n"/>
+      <c r="K11" s="572" t="n"/>
+      <c r="L11" s="572" t="n"/>
+      <c r="M11" s="572" t="n"/>
+      <c r="N11" s="572" t="n"/>
+      <c r="O11" s="572" t="n"/>
+      <c r="P11" s="572" t="n"/>
+      <c r="Q11" s="572" t="n"/>
+      <c r="R11" s="572" t="n"/>
+      <c r="S11" s="572" t="n"/>
+      <c r="T11" s="572" t="n"/>
+      <c r="U11" s="572" t="n"/>
+      <c r="V11" s="572" t="n"/>
+      <c r="W11" s="572" t="n"/>
+      <c r="X11" s="572" t="n"/>
+      <c r="Y11" s="572" t="n"/>
+      <c r="Z11" s="572" t="n"/>
+      <c r="AA11" s="572" t="n"/>
+      <c r="AB11" s="572" t="n"/>
+      <c r="AC11" s="572" t="n"/>
+      <c r="AD11" s="572" t="n"/>
+      <c r="AE11" s="572" t="n"/>
+      <c r="AF11" s="572" t="n"/>
+      <c r="AG11" s="572" t="n"/>
+      <c r="AH11" s="572" t="n"/>
+      <c r="AI11" s="572" t="n"/>
+      <c r="AJ11" s="572" t="n"/>
+      <c r="AK11" s="572" t="n"/>
+      <c r="AL11" s="572" t="n"/>
+      <c r="AM11" s="572" t="n"/>
+      <c r="AN11" s="573" t="n"/>
     </row>
     <row r="12" hidden="1"/>
     <row r="13" hidden="1"/>
@@ -11767,8 +12498,9 @@
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
   </numFmts>
-  <fonts count="86">
+  <fonts count="87">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -520,6 +520,12 @@
       <color rgb="007A8FA6"/>
       <sz val="7"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001B3A6B"/>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="56">
     <fill>
@@ -799,7 +805,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="335">
+  <borders count="350">
     <border>
       <left/>
       <right/>
@@ -4393,13 +4399,166 @@
       </top>
       <bottom style="thin">
         <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="623">
+  <cellXfs count="691">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5917,6 +6076,196 @@
     <xf numFmtId="0" fontId="77" fillId="4" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="335" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -5997,11 +6346,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
+      <colOff>63378</colOff>
+      <row>0</row>
+      <rowOff>442597</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="235404" cy="67905"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -6027,11 +6376,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
+      <colOff>63378</colOff>
+      <row>0</row>
+      <rowOff>442597</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="235404" cy="67905"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -6075,6 +6424,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6358,2242 +6710,2242 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="505" t="n"/>
-      <c r="B1" s="506" t="n"/>
-      <c r="C1" s="507" t="inlineStr">
+      <c r="A1" s="339" t="n"/>
+      <c r="B1" s="53" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>RMA TRACKING LOG</t>
         </is>
       </c>
-      <c r="D1" s="506" t="n"/>
-      <c r="E1" s="506" t="n"/>
-      <c r="F1" s="506" t="n"/>
-      <c r="G1" s="506" t="n"/>
-      <c r="H1" s="508" t="n"/>
-      <c r="I1" s="509" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="623" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="J1" s="510" t="inlineStr">
+      <c r="J1" s="624" t="inlineStr">
         <is>
           <t>FRM-213</t>
         </is>
       </c>
-      <c r="K1" s="510" t="n"/>
-      <c r="L1" s="510" t="n"/>
-      <c r="M1" s="510" t="n"/>
-      <c r="N1" s="510" t="n"/>
-      <c r="O1" s="510" t="n"/>
-      <c r="P1" s="510" t="n"/>
-      <c r="Q1" s="510" t="n"/>
-      <c r="R1" s="510" t="n"/>
-      <c r="S1" s="510" t="n"/>
-      <c r="T1" s="510" t="n"/>
-      <c r="U1" s="510" t="n"/>
-      <c r="V1" s="510" t="n"/>
-      <c r="W1" s="510" t="n"/>
-      <c r="X1" s="510" t="n"/>
-      <c r="Y1" s="510" t="n"/>
-      <c r="Z1" s="510" t="n"/>
-      <c r="AA1" s="510" t="n"/>
-      <c r="AB1" s="510" t="n"/>
-      <c r="AC1" s="510" t="n"/>
-      <c r="AD1" s="511" t="n"/>
-      <c r="AE1" s="512" t="n"/>
-      <c r="AF1" s="513" t="n"/>
-      <c r="AG1" s="513" t="n"/>
-      <c r="AH1" s="514" t="n"/>
-      <c r="AI1" s="515" t="n"/>
-      <c r="AJ1" s="516" t="n"/>
-      <c r="AK1" s="516" t="n"/>
-      <c r="AL1" s="516" t="n"/>
-      <c r="AM1" s="516" t="n"/>
-      <c r="AN1" s="517" t="n"/>
+      <c r="K1" s="624" t="n"/>
+      <c r="L1" s="624" t="n"/>
+      <c r="M1" s="624" t="n"/>
+      <c r="N1" s="624" t="n"/>
+      <c r="O1" s="624" t="n"/>
+      <c r="P1" s="624" t="n"/>
+      <c r="Q1" s="624" t="n"/>
+      <c r="R1" s="624" t="n"/>
+      <c r="S1" s="624" t="n"/>
+      <c r="T1" s="624" t="n"/>
+      <c r="U1" s="624" t="n"/>
+      <c r="V1" s="624" t="n"/>
+      <c r="W1" s="624" t="n"/>
+      <c r="X1" s="624" t="n"/>
+      <c r="Y1" s="624" t="n"/>
+      <c r="Z1" s="624" t="n"/>
+      <c r="AA1" s="624" t="n"/>
+      <c r="AB1" s="624" t="n"/>
+      <c r="AC1" s="624" t="n"/>
+      <c r="AD1" s="624" t="n"/>
+      <c r="AE1" s="625" t="n"/>
+      <c r="AF1" s="625" t="n"/>
+      <c r="AG1" s="625" t="n"/>
+      <c r="AH1" s="625" t="n"/>
+      <c r="AI1" s="626" t="n"/>
+      <c r="AJ1" s="626" t="n"/>
+      <c r="AK1" s="626" t="n"/>
+      <c r="AL1" s="626" t="n"/>
+      <c r="AM1" s="626" t="n"/>
+      <c r="AN1" s="627" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="518" t="n"/>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
-      <c r="H2" s="519" t="n"/>
-      <c r="I2" s="520" t="inlineStr">
+      <c r="A2" s="9" t="n"/>
+      <c r="B2" s="54" t="n"/>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="628" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="J2" s="521" t="inlineStr">
+      <c r="J2" s="629" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="K2" s="521" t="n"/>
-      <c r="L2" s="521" t="n"/>
-      <c r="M2" s="521" t="n"/>
-      <c r="N2" s="521" t="n"/>
-      <c r="O2" s="521" t="n"/>
-      <c r="P2" s="521" t="n"/>
-      <c r="Q2" s="521" t="n"/>
-      <c r="R2" s="521" t="n"/>
-      <c r="S2" s="521" t="n"/>
-      <c r="T2" s="521" t="n"/>
-      <c r="U2" s="521" t="n"/>
-      <c r="V2" s="521" t="n"/>
-      <c r="W2" s="521" t="n"/>
-      <c r="X2" s="521" t="n"/>
-      <c r="Y2" s="521" t="n"/>
-      <c r="Z2" s="521" t="n"/>
-      <c r="AA2" s="521" t="n"/>
-      <c r="AB2" s="521" t="n"/>
-      <c r="AC2" s="521" t="n"/>
-      <c r="AD2" s="522" t="n"/>
-      <c r="AE2" s="523" t="n"/>
-      <c r="AF2" s="524" t="n"/>
-      <c r="AG2" s="524" t="n"/>
-      <c r="AH2" s="525" t="n"/>
-      <c r="AI2" s="526" t="n"/>
-      <c r="AJ2" s="527" t="n"/>
-      <c r="AK2" s="527" t="n"/>
-      <c r="AL2" s="527" t="n"/>
-      <c r="AM2" s="527" t="n"/>
-      <c r="AN2" s="528" t="n"/>
+      <c r="K2" s="629" t="n"/>
+      <c r="L2" s="629" t="n"/>
+      <c r="M2" s="629" t="n"/>
+      <c r="N2" s="629" t="n"/>
+      <c r="O2" s="629" t="n"/>
+      <c r="P2" s="629" t="n"/>
+      <c r="Q2" s="629" t="n"/>
+      <c r="R2" s="629" t="n"/>
+      <c r="S2" s="629" t="n"/>
+      <c r="T2" s="629" t="n"/>
+      <c r="U2" s="629" t="n"/>
+      <c r="V2" s="629" t="n"/>
+      <c r="W2" s="629" t="n"/>
+      <c r="X2" s="629" t="n"/>
+      <c r="Y2" s="629" t="n"/>
+      <c r="Z2" s="629" t="n"/>
+      <c r="AA2" s="629" t="n"/>
+      <c r="AB2" s="629" t="n"/>
+      <c r="AC2" s="629" t="n"/>
+      <c r="AD2" s="629" t="n"/>
+      <c r="AE2" s="630" t="n"/>
+      <c r="AF2" s="630" t="n"/>
+      <c r="AG2" s="630" t="n"/>
+      <c r="AH2" s="630" t="n"/>
+      <c r="AI2" s="631" t="n"/>
+      <c r="AJ2" s="631" t="n"/>
+      <c r="AK2" s="631" t="n"/>
+      <c r="AL2" s="631" t="n"/>
+      <c r="AM2" s="631" t="n"/>
+      <c r="AN2" s="632" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="518" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="519" t="n"/>
-      <c r="I3" s="520" t="inlineStr">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="54" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="628" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="J3" s="521" t="inlineStr">
+      <c r="J3" s="629" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="K3" s="521" t="n"/>
-      <c r="L3" s="521" t="n"/>
-      <c r="M3" s="521" t="n"/>
-      <c r="N3" s="521" t="n"/>
-      <c r="O3" s="521" t="n"/>
-      <c r="P3" s="521" t="n"/>
-      <c r="Q3" s="521" t="n"/>
-      <c r="R3" s="521" t="n"/>
-      <c r="S3" s="521" t="n"/>
-      <c r="T3" s="521" t="n"/>
-      <c r="U3" s="521" t="n"/>
-      <c r="V3" s="521" t="n"/>
-      <c r="W3" s="521" t="n"/>
-      <c r="X3" s="521" t="n"/>
-      <c r="Y3" s="521" t="n"/>
-      <c r="Z3" s="521" t="n"/>
-      <c r="AA3" s="521" t="n"/>
-      <c r="AB3" s="521" t="n"/>
-      <c r="AC3" s="521" t="n"/>
-      <c r="AD3" s="522" t="n"/>
-      <c r="AE3" s="523" t="n"/>
-      <c r="AF3" s="524" t="n"/>
-      <c r="AG3" s="524" t="n"/>
-      <c r="AH3" s="525" t="n"/>
-      <c r="AI3" s="526" t="n"/>
-      <c r="AJ3" s="527" t="n"/>
-      <c r="AK3" s="527" t="n"/>
-      <c r="AL3" s="527" t="n"/>
-      <c r="AM3" s="527" t="n"/>
-      <c r="AN3" s="528" t="n"/>
+      <c r="K3" s="629" t="n"/>
+      <c r="L3" s="629" t="n"/>
+      <c r="M3" s="629" t="n"/>
+      <c r="N3" s="629" t="n"/>
+      <c r="O3" s="629" t="n"/>
+      <c r="P3" s="629" t="n"/>
+      <c r="Q3" s="629" t="n"/>
+      <c r="R3" s="629" t="n"/>
+      <c r="S3" s="629" t="n"/>
+      <c r="T3" s="629" t="n"/>
+      <c r="U3" s="629" t="n"/>
+      <c r="V3" s="629" t="n"/>
+      <c r="W3" s="629" t="n"/>
+      <c r="X3" s="629" t="n"/>
+      <c r="Y3" s="629" t="n"/>
+      <c r="Z3" s="629" t="n"/>
+      <c r="AA3" s="629" t="n"/>
+      <c r="AB3" s="629" t="n"/>
+      <c r="AC3" s="629" t="n"/>
+      <c r="AD3" s="629" t="n"/>
+      <c r="AE3" s="630" t="n"/>
+      <c r="AF3" s="630" t="n"/>
+      <c r="AG3" s="630" t="n"/>
+      <c r="AH3" s="630" t="n"/>
+      <c r="AI3" s="631" t="n"/>
+      <c r="AJ3" s="631" t="n"/>
+      <c r="AK3" s="631" t="n"/>
+      <c r="AL3" s="631" t="n"/>
+      <c r="AM3" s="631" t="n"/>
+      <c r="AN3" s="632" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="518" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="529" t="inlineStr">
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="633" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="519" t="n"/>
-      <c r="I4" s="530" t="inlineStr">
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="634" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="J4" s="531" t="inlineStr">
+      <c r="J4" s="635" t="inlineStr">
         <is>
           <t>QA / Customer Service</t>
         </is>
       </c>
-      <c r="K4" s="531" t="n"/>
-      <c r="L4" s="531" t="n"/>
-      <c r="M4" s="531" t="n"/>
-      <c r="N4" s="531" t="n"/>
-      <c r="O4" s="531" t="n"/>
-      <c r="P4" s="531" t="n"/>
-      <c r="Q4" s="531" t="n"/>
-      <c r="R4" s="531" t="n"/>
-      <c r="S4" s="531" t="n"/>
-      <c r="T4" s="531" t="n"/>
-      <c r="U4" s="531" t="n"/>
-      <c r="V4" s="531" t="n"/>
-      <c r="W4" s="531" t="n"/>
-      <c r="X4" s="531" t="n"/>
-      <c r="Y4" s="531" t="n"/>
-      <c r="Z4" s="531" t="n"/>
-      <c r="AA4" s="531" t="n"/>
-      <c r="AB4" s="531" t="n"/>
-      <c r="AC4" s="531" t="n"/>
-      <c r="AD4" s="532" t="n"/>
-      <c r="AE4" s="523" t="n"/>
-      <c r="AF4" s="524" t="n"/>
-      <c r="AG4" s="524" t="n"/>
-      <c r="AH4" s="525" t="n"/>
-      <c r="AI4" s="526" t="n"/>
-      <c r="AJ4" s="527" t="n"/>
-      <c r="AK4" s="527" t="n"/>
-      <c r="AL4" s="527" t="n"/>
-      <c r="AM4" s="527" t="n"/>
-      <c r="AN4" s="528" t="n"/>
+      <c r="K4" s="635" t="n"/>
+      <c r="L4" s="635" t="n"/>
+      <c r="M4" s="635" t="n"/>
+      <c r="N4" s="635" t="n"/>
+      <c r="O4" s="635" t="n"/>
+      <c r="P4" s="635" t="n"/>
+      <c r="Q4" s="635" t="n"/>
+      <c r="R4" s="635" t="n"/>
+      <c r="S4" s="635" t="n"/>
+      <c r="T4" s="635" t="n"/>
+      <c r="U4" s="635" t="n"/>
+      <c r="V4" s="635" t="n"/>
+      <c r="W4" s="635" t="n"/>
+      <c r="X4" s="635" t="n"/>
+      <c r="Y4" s="635" t="n"/>
+      <c r="Z4" s="635" t="n"/>
+      <c r="AA4" s="635" t="n"/>
+      <c r="AB4" s="635" t="n"/>
+      <c r="AC4" s="635" t="n"/>
+      <c r="AD4" s="635" t="n"/>
+      <c r="AE4" s="630" t="n"/>
+      <c r="AF4" s="630" t="n"/>
+      <c r="AG4" s="630" t="n"/>
+      <c r="AH4" s="630" t="n"/>
+      <c r="AI4" s="631" t="n"/>
+      <c r="AJ4" s="631" t="n"/>
+      <c r="AK4" s="631" t="n"/>
+      <c r="AL4" s="631" t="n"/>
+      <c r="AM4" s="631" t="n"/>
+      <c r="AN4" s="632" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="533" t="n"/>
-      <c r="B5" s="534" t="n"/>
-      <c r="C5" s="535" t="inlineStr">
+      <c r="A5" s="18" t="n"/>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="636" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="534" t="n"/>
-      <c r="E5" s="534" t="n"/>
-      <c r="F5" s="534" t="n"/>
-      <c r="G5" s="534" t="n"/>
-      <c r="H5" s="536" t="n"/>
-      <c r="I5" s="537" t="inlineStr">
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="19" t="n"/>
+      <c r="H5" s="19" t="n"/>
+      <c r="I5" s="637" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="J5" s="538" t="inlineStr">
+      <c r="J5" s="638" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
       </c>
-      <c r="K5" s="538" t="n"/>
-      <c r="L5" s="538" t="n"/>
-      <c r="M5" s="538" t="n"/>
-      <c r="N5" s="538" t="n"/>
-      <c r="O5" s="538" t="n"/>
-      <c r="P5" s="538" t="n"/>
-      <c r="Q5" s="538" t="n"/>
-      <c r="R5" s="538" t="n"/>
-      <c r="S5" s="538" t="n"/>
-      <c r="T5" s="538" t="n"/>
-      <c r="U5" s="538" t="n"/>
-      <c r="V5" s="538" t="n"/>
-      <c r="W5" s="538" t="n"/>
-      <c r="X5" s="538" t="n"/>
-      <c r="Y5" s="538" t="n"/>
-      <c r="Z5" s="538" t="n"/>
-      <c r="AA5" s="538" t="n"/>
-      <c r="AB5" s="538" t="n"/>
-      <c r="AC5" s="538" t="n"/>
-      <c r="AD5" s="539" t="n"/>
-      <c r="AE5" s="540" t="n"/>
-      <c r="AF5" s="541" t="n"/>
-      <c r="AG5" s="541" t="n"/>
-      <c r="AH5" s="542" t="n"/>
-      <c r="AI5" s="543" t="n"/>
-      <c r="AJ5" s="544" t="n"/>
-      <c r="AK5" s="544" t="n"/>
-      <c r="AL5" s="544" t="n"/>
-      <c r="AM5" s="544" t="n"/>
-      <c r="AN5" s="545" t="n"/>
+      <c r="K5" s="638" t="n"/>
+      <c r="L5" s="638" t="n"/>
+      <c r="M5" s="638" t="n"/>
+      <c r="N5" s="638" t="n"/>
+      <c r="O5" s="638" t="n"/>
+      <c r="P5" s="638" t="n"/>
+      <c r="Q5" s="638" t="n"/>
+      <c r="R5" s="638" t="n"/>
+      <c r="S5" s="638" t="n"/>
+      <c r="T5" s="638" t="n"/>
+      <c r="U5" s="638" t="n"/>
+      <c r="V5" s="638" t="n"/>
+      <c r="W5" s="638" t="n"/>
+      <c r="X5" s="638" t="n"/>
+      <c r="Y5" s="638" t="n"/>
+      <c r="Z5" s="638" t="n"/>
+      <c r="AA5" s="638" t="n"/>
+      <c r="AB5" s="638" t="n"/>
+      <c r="AC5" s="638" t="n"/>
+      <c r="AD5" s="638" t="n"/>
+      <c r="AE5" s="639" t="n"/>
+      <c r="AF5" s="639" t="n"/>
+      <c r="AG5" s="639" t="n"/>
+      <c r="AH5" s="639" t="n"/>
+      <c r="AI5" s="640" t="n"/>
+      <c r="AJ5" s="640" t="n"/>
+      <c r="AK5" s="640" t="n"/>
+      <c r="AL5" s="640" t="n"/>
+      <c r="AM5" s="640" t="n"/>
+      <c r="AN5" s="641" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="546" t="n"/>
-      <c r="B6" s="547" t="n"/>
-      <c r="C6" s="547" t="n"/>
-      <c r="D6" s="547" t="n"/>
-      <c r="E6" s="547" t="n"/>
-      <c r="F6" s="547" t="n"/>
-      <c r="G6" s="547" t="n"/>
-      <c r="H6" s="547" t="n"/>
-      <c r="I6" s="547" t="n"/>
-      <c r="J6" s="547" t="n"/>
-      <c r="K6" s="547" t="n"/>
-      <c r="L6" s="547" t="n"/>
-      <c r="M6" s="547" t="n"/>
-      <c r="N6" s="547" t="n"/>
-      <c r="O6" s="547" t="n"/>
-      <c r="P6" s="547" t="n"/>
-      <c r="Q6" s="547" t="n"/>
-      <c r="R6" s="547" t="n"/>
-      <c r="S6" s="547" t="n"/>
-      <c r="T6" s="547" t="n"/>
-      <c r="U6" s="547" t="n"/>
-      <c r="V6" s="547" t="n"/>
-      <c r="W6" s="547" t="n"/>
-      <c r="X6" s="547" t="n"/>
-      <c r="Y6" s="547" t="n"/>
-      <c r="Z6" s="547" t="n"/>
-      <c r="AA6" s="547" t="n"/>
-      <c r="AB6" s="547" t="n"/>
-      <c r="AC6" s="547" t="n"/>
-      <c r="AD6" s="547" t="n"/>
-      <c r="AE6" s="547" t="n"/>
-      <c r="AF6" s="547" t="n"/>
-      <c r="AG6" s="547" t="n"/>
-      <c r="AH6" s="547" t="n"/>
-      <c r="AI6" s="547" t="n"/>
-      <c r="AJ6" s="547" t="n"/>
-      <c r="AK6" s="547" t="n"/>
-      <c r="AL6" s="547" t="n"/>
-      <c r="AM6" s="547" t="n"/>
-      <c r="AN6" s="547" t="n"/>
+      <c r="A6" s="642" t="n"/>
+      <c r="B6" s="643" t="n"/>
+      <c r="C6" s="643" t="n"/>
+      <c r="D6" s="643" t="n"/>
+      <c r="E6" s="643" t="n"/>
+      <c r="F6" s="643" t="n"/>
+      <c r="G6" s="643" t="n"/>
+      <c r="H6" s="643" t="n"/>
+      <c r="I6" s="643" t="n"/>
+      <c r="J6" s="643" t="n"/>
+      <c r="K6" s="643" t="n"/>
+      <c r="L6" s="643" t="n"/>
+      <c r="M6" s="643" t="n"/>
+      <c r="N6" s="643" t="n"/>
+      <c r="O6" s="643" t="n"/>
+      <c r="P6" s="643" t="n"/>
+      <c r="Q6" s="643" t="n"/>
+      <c r="R6" s="643" t="n"/>
+      <c r="S6" s="643" t="n"/>
+      <c r="T6" s="643" t="n"/>
+      <c r="U6" s="643" t="n"/>
+      <c r="V6" s="643" t="n"/>
+      <c r="W6" s="643" t="n"/>
+      <c r="X6" s="643" t="n"/>
+      <c r="Y6" s="643" t="n"/>
+      <c r="Z6" s="643" t="n"/>
+      <c r="AA6" s="643" t="n"/>
+      <c r="AB6" s="643" t="n"/>
+      <c r="AC6" s="643" t="n"/>
+      <c r="AD6" s="643" t="n"/>
+      <c r="AE6" s="643" t="n"/>
+      <c r="AF6" s="643" t="n"/>
+      <c r="AG6" s="643" t="n"/>
+      <c r="AH6" s="643" t="n"/>
+      <c r="AI6" s="643" t="n"/>
+      <c r="AJ6" s="643" t="n"/>
+      <c r="AK6" s="643" t="n"/>
+      <c r="AL6" s="643" t="n"/>
+      <c r="AM6" s="643" t="n"/>
+      <c r="AN6" s="643" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="548" t="inlineStr">
+      <c r="A7" s="644" t="inlineStr">
         <is>
           <t>1.  RMA HEADER</t>
         </is>
       </c>
-      <c r="B7" s="549" t="n"/>
-      <c r="C7" s="549" t="n"/>
-      <c r="D7" s="549" t="n"/>
-      <c r="E7" s="549" t="n"/>
-      <c r="F7" s="549" t="n"/>
-      <c r="G7" s="549" t="n"/>
-      <c r="H7" s="549" t="n"/>
-      <c r="I7" s="549" t="n"/>
-      <c r="J7" s="549" t="n"/>
-      <c r="K7" s="549" t="n"/>
-      <c r="L7" s="549" t="n"/>
-      <c r="M7" s="549" t="n"/>
-      <c r="N7" s="549" t="n"/>
-      <c r="O7" s="549" t="n"/>
-      <c r="P7" s="549" t="n"/>
-      <c r="Q7" s="549" t="n"/>
-      <c r="R7" s="549" t="n"/>
-      <c r="S7" s="549" t="n"/>
-      <c r="T7" s="549" t="n"/>
-      <c r="U7" s="549" t="n"/>
-      <c r="V7" s="549" t="n"/>
-      <c r="W7" s="549" t="n"/>
-      <c r="X7" s="549" t="n"/>
-      <c r="Y7" s="549" t="n"/>
-      <c r="Z7" s="549" t="n"/>
-      <c r="AA7" s="549" t="n"/>
-      <c r="AB7" s="549" t="n"/>
-      <c r="AC7" s="549" t="n"/>
-      <c r="AD7" s="549" t="n"/>
-      <c r="AE7" s="549" t="n"/>
-      <c r="AF7" s="549" t="n"/>
-      <c r="AG7" s="549" t="n"/>
-      <c r="AH7" s="549" t="n"/>
-      <c r="AI7" s="549" t="n"/>
-      <c r="AJ7" s="549" t="n"/>
-      <c r="AK7" s="549" t="n"/>
-      <c r="AL7" s="549" t="n"/>
-      <c r="AM7" s="549" t="n"/>
-      <c r="AN7" s="550" t="n"/>
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="27" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
+      <c r="H7" s="27" t="n"/>
+      <c r="I7" s="27" t="n"/>
+      <c r="J7" s="27" t="n"/>
+      <c r="K7" s="645" t="n"/>
+      <c r="L7" s="645" t="n"/>
+      <c r="M7" s="645" t="n"/>
+      <c r="N7" s="645" t="n"/>
+      <c r="O7" s="645" t="n"/>
+      <c r="P7" s="645" t="n"/>
+      <c r="Q7" s="645" t="n"/>
+      <c r="R7" s="645" t="n"/>
+      <c r="S7" s="645" t="n"/>
+      <c r="T7" s="645" t="n"/>
+      <c r="U7" s="645" t="n"/>
+      <c r="V7" s="645" t="n"/>
+      <c r="W7" s="645" t="n"/>
+      <c r="X7" s="645" t="n"/>
+      <c r="Y7" s="645" t="n"/>
+      <c r="Z7" s="645" t="n"/>
+      <c r="AA7" s="645" t="n"/>
+      <c r="AB7" s="645" t="n"/>
+      <c r="AC7" s="645" t="n"/>
+      <c r="AD7" s="645" t="n"/>
+      <c r="AE7" s="645" t="n"/>
+      <c r="AF7" s="645" t="n"/>
+      <c r="AG7" s="645" t="n"/>
+      <c r="AH7" s="645" t="n"/>
+      <c r="AI7" s="645" t="n"/>
+      <c r="AJ7" s="645" t="n"/>
+      <c r="AK7" s="645" t="n"/>
+      <c r="AL7" s="645" t="n"/>
+      <c r="AM7" s="645" t="n"/>
+      <c r="AN7" s="646" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="551" t="inlineStr">
+      <c r="A8" s="647" t="inlineStr">
         <is>
           <t>Open Period</t>
         </is>
       </c>
-      <c r="B8" s="552" t="n"/>
-      <c r="C8" s="553" t="inlineStr"/>
-      <c r="D8" s="552" t="n"/>
-      <c r="E8" s="552" t="n"/>
-      <c r="F8" s="554" t="inlineStr">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="648" t="inlineStr"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="649" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="G8" s="552" t="n"/>
-      <c r="H8" s="553" t="inlineStr"/>
-      <c r="I8" s="552" t="n"/>
-      <c r="J8" s="552" t="n"/>
-      <c r="K8" s="555" t="n"/>
-      <c r="L8" s="556" t="n"/>
-      <c r="M8" s="556" t="n"/>
-      <c r="N8" s="556" t="n"/>
-      <c r="O8" s="556" t="n"/>
-      <c r="P8" s="556" t="n"/>
-      <c r="Q8" s="556" t="n"/>
-      <c r="R8" s="556" t="n"/>
-      <c r="S8" s="556" t="n"/>
-      <c r="T8" s="556" t="n"/>
-      <c r="U8" s="556" t="n"/>
-      <c r="V8" s="556" t="n"/>
-      <c r="W8" s="556" t="n"/>
-      <c r="X8" s="556" t="n"/>
-      <c r="Y8" s="556" t="n"/>
-      <c r="Z8" s="556" t="n"/>
-      <c r="AA8" s="556" t="n"/>
-      <c r="AB8" s="556" t="n"/>
-      <c r="AC8" s="556" t="n"/>
-      <c r="AD8" s="556" t="n"/>
-      <c r="AE8" s="556" t="n"/>
-      <c r="AF8" s="556" t="n"/>
-      <c r="AG8" s="556" t="n"/>
-      <c r="AH8" s="556" t="n"/>
-      <c r="AI8" s="556" t="n"/>
-      <c r="AJ8" s="556" t="n"/>
-      <c r="AK8" s="556" t="n"/>
-      <c r="AL8" s="556" t="n"/>
-      <c r="AM8" s="556" t="n"/>
-      <c r="AN8" s="557" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="648" t="inlineStr"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="650" t="n"/>
+      <c r="L8" s="650" t="n"/>
+      <c r="M8" s="650" t="n"/>
+      <c r="N8" s="650" t="n"/>
+      <c r="O8" s="650" t="n"/>
+      <c r="P8" s="650" t="n"/>
+      <c r="Q8" s="650" t="n"/>
+      <c r="R8" s="650" t="n"/>
+      <c r="S8" s="650" t="n"/>
+      <c r="T8" s="650" t="n"/>
+      <c r="U8" s="650" t="n"/>
+      <c r="V8" s="650" t="n"/>
+      <c r="W8" s="650" t="n"/>
+      <c r="X8" s="650" t="n"/>
+      <c r="Y8" s="650" t="n"/>
+      <c r="Z8" s="650" t="n"/>
+      <c r="AA8" s="650" t="n"/>
+      <c r="AB8" s="650" t="n"/>
+      <c r="AC8" s="650" t="n"/>
+      <c r="AD8" s="650" t="n"/>
+      <c r="AE8" s="650" t="n"/>
+      <c r="AF8" s="650" t="n"/>
+      <c r="AG8" s="650" t="n"/>
+      <c r="AH8" s="650" t="n"/>
+      <c r="AI8" s="650" t="n"/>
+      <c r="AJ8" s="650" t="n"/>
+      <c r="AK8" s="650" t="n"/>
+      <c r="AL8" s="650" t="n"/>
+      <c r="AM8" s="650" t="n"/>
+      <c r="AN8" s="651" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="558" t="inlineStr">
+      <c r="A9" s="652" t="inlineStr">
         <is>
           <t>RMA Owner</t>
         </is>
       </c>
-      <c r="B9" s="437" t="n"/>
-      <c r="C9" s="559" t="inlineStr"/>
-      <c r="D9" s="437" t="n"/>
-      <c r="E9" s="437" t="n"/>
-      <c r="F9" s="560" t="inlineStr">
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="653" t="inlineStr"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="654" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="G9" s="437" t="n"/>
-      <c r="H9" s="559" t="inlineStr"/>
-      <c r="I9" s="437" t="n"/>
-      <c r="J9" s="437" t="n"/>
-      <c r="K9" s="561" t="n"/>
-      <c r="L9" s="446" t="n"/>
-      <c r="M9" s="446" t="n"/>
-      <c r="N9" s="446" t="n"/>
-      <c r="O9" s="446" t="n"/>
-      <c r="P9" s="446" t="n"/>
-      <c r="Q9" s="446" t="n"/>
-      <c r="R9" s="446" t="n"/>
-      <c r="S9" s="446" t="n"/>
-      <c r="T9" s="446" t="n"/>
-      <c r="U9" s="446" t="n"/>
-      <c r="V9" s="446" t="n"/>
-      <c r="W9" s="446" t="n"/>
-      <c r="X9" s="446" t="n"/>
-      <c r="Y9" s="446" t="n"/>
-      <c r="Z9" s="446" t="n"/>
-      <c r="AA9" s="446" t="n"/>
-      <c r="AB9" s="446" t="n"/>
-      <c r="AC9" s="446" t="n"/>
-      <c r="AD9" s="446" t="n"/>
-      <c r="AE9" s="446" t="n"/>
-      <c r="AF9" s="446" t="n"/>
-      <c r="AG9" s="446" t="n"/>
-      <c r="AH9" s="446" t="n"/>
-      <c r="AI9" s="446" t="n"/>
-      <c r="AJ9" s="446" t="n"/>
-      <c r="AK9" s="446" t="n"/>
-      <c r="AL9" s="446" t="n"/>
-      <c r="AM9" s="446" t="n"/>
-      <c r="AN9" s="562" t="n"/>
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="653" t="inlineStr"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="655" t="n"/>
+      <c r="L9" s="655" t="n"/>
+      <c r="M9" s="655" t="n"/>
+      <c r="N9" s="655" t="n"/>
+      <c r="O9" s="655" t="n"/>
+      <c r="P9" s="655" t="n"/>
+      <c r="Q9" s="655" t="n"/>
+      <c r="R9" s="655" t="n"/>
+      <c r="S9" s="655" t="n"/>
+      <c r="T9" s="655" t="n"/>
+      <c r="U9" s="655" t="n"/>
+      <c r="V9" s="655" t="n"/>
+      <c r="W9" s="655" t="n"/>
+      <c r="X9" s="655" t="n"/>
+      <c r="Y9" s="655" t="n"/>
+      <c r="Z9" s="655" t="n"/>
+      <c r="AA9" s="655" t="n"/>
+      <c r="AB9" s="655" t="n"/>
+      <c r="AC9" s="655" t="n"/>
+      <c r="AD9" s="655" t="n"/>
+      <c r="AE9" s="655" t="n"/>
+      <c r="AF9" s="655" t="n"/>
+      <c r="AG9" s="655" t="n"/>
+      <c r="AH9" s="655" t="n"/>
+      <c r="AI9" s="655" t="n"/>
+      <c r="AJ9" s="655" t="n"/>
+      <c r="AK9" s="655" t="n"/>
+      <c r="AL9" s="655" t="n"/>
+      <c r="AM9" s="655" t="n"/>
+      <c r="AN9" s="656" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="558" t="inlineStr">
+      <c r="A10" s="652" t="inlineStr">
         <is>
           <t>Evidence Folder</t>
         </is>
       </c>
-      <c r="B10" s="437" t="n"/>
-      <c r="C10" s="559" t="inlineStr"/>
-      <c r="D10" s="437" t="n"/>
-      <c r="E10" s="437" t="n"/>
-      <c r="F10" s="560" t="inlineStr">
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="653" t="inlineStr"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="654" t="inlineStr">
         <is>
           <t>Returned Qty / Condition</t>
         </is>
       </c>
-      <c r="G10" s="437" t="n"/>
-      <c r="H10" s="559" t="inlineStr"/>
-      <c r="I10" s="437" t="n"/>
-      <c r="J10" s="437" t="n"/>
-      <c r="K10" s="561" t="n"/>
-      <c r="L10" s="446" t="n"/>
-      <c r="M10" s="446" t="n"/>
-      <c r="N10" s="446" t="n"/>
-      <c r="O10" s="446" t="n"/>
-      <c r="P10" s="446" t="n"/>
-      <c r="Q10" s="446" t="n"/>
-      <c r="R10" s="446" t="n"/>
-      <c r="S10" s="446" t="n"/>
-      <c r="T10" s="446" t="n"/>
-      <c r="U10" s="446" t="n"/>
-      <c r="V10" s="446" t="n"/>
-      <c r="W10" s="446" t="n"/>
-      <c r="X10" s="446" t="n"/>
-      <c r="Y10" s="446" t="n"/>
-      <c r="Z10" s="446" t="n"/>
-      <c r="AA10" s="446" t="n"/>
-      <c r="AB10" s="446" t="n"/>
-      <c r="AC10" s="446" t="n"/>
-      <c r="AD10" s="446" t="n"/>
-      <c r="AE10" s="446" t="n"/>
-      <c r="AF10" s="446" t="n"/>
-      <c r="AG10" s="446" t="n"/>
-      <c r="AH10" s="446" t="n"/>
-      <c r="AI10" s="446" t="n"/>
-      <c r="AJ10" s="446" t="n"/>
-      <c r="AK10" s="446" t="n"/>
-      <c r="AL10" s="446" t="n"/>
-      <c r="AM10" s="446" t="n"/>
-      <c r="AN10" s="562" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="653" t="inlineStr"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="13" t="n"/>
+      <c r="K10" s="655" t="n"/>
+      <c r="L10" s="655" t="n"/>
+      <c r="M10" s="655" t="n"/>
+      <c r="N10" s="655" t="n"/>
+      <c r="O10" s="655" t="n"/>
+      <c r="P10" s="655" t="n"/>
+      <c r="Q10" s="655" t="n"/>
+      <c r="R10" s="655" t="n"/>
+      <c r="S10" s="655" t="n"/>
+      <c r="T10" s="655" t="n"/>
+      <c r="U10" s="655" t="n"/>
+      <c r="V10" s="655" t="n"/>
+      <c r="W10" s="655" t="n"/>
+      <c r="X10" s="655" t="n"/>
+      <c r="Y10" s="655" t="n"/>
+      <c r="Z10" s="655" t="n"/>
+      <c r="AA10" s="655" t="n"/>
+      <c r="AB10" s="655" t="n"/>
+      <c r="AC10" s="655" t="n"/>
+      <c r="AD10" s="655" t="n"/>
+      <c r="AE10" s="655" t="n"/>
+      <c r="AF10" s="655" t="n"/>
+      <c r="AG10" s="655" t="n"/>
+      <c r="AH10" s="655" t="n"/>
+      <c r="AI10" s="655" t="n"/>
+      <c r="AJ10" s="655" t="n"/>
+      <c r="AK10" s="655" t="n"/>
+      <c r="AL10" s="655" t="n"/>
+      <c r="AM10" s="655" t="n"/>
+      <c r="AN10" s="656" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="558" t="inlineStr">
+      <c r="A11" s="652" t="inlineStr">
         <is>
           <t>Receipt Ref. / Date</t>
         </is>
       </c>
-      <c r="B11" s="437" t="n"/>
-      <c r="C11" s="559" t="inlineStr"/>
-      <c r="D11" s="437" t="n"/>
-      <c r="E11" s="437" t="n"/>
-      <c r="F11" s="560" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="653" t="inlineStr"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="654" t="inlineStr">
         <is>
           <t>Evaluation Owner</t>
         </is>
       </c>
-      <c r="G11" s="437" t="n"/>
-      <c r="H11" s="559" t="inlineStr"/>
-      <c r="I11" s="437" t="n"/>
-      <c r="J11" s="437" t="n"/>
-      <c r="K11" s="563" t="n"/>
-      <c r="L11" s="437" t="n"/>
-      <c r="M11" s="437" t="n"/>
-      <c r="N11" s="437" t="n"/>
-      <c r="O11" s="437" t="n"/>
-      <c r="P11" s="437" t="n"/>
-      <c r="Q11" s="437" t="n"/>
-      <c r="R11" s="437" t="n"/>
-      <c r="S11" s="437" t="n"/>
-      <c r="T11" s="437" t="n"/>
-      <c r="U11" s="437" t="n"/>
-      <c r="V11" s="437" t="n"/>
-      <c r="W11" s="437" t="n"/>
-      <c r="X11" s="437" t="n"/>
-      <c r="Y11" s="437" t="n"/>
-      <c r="Z11" s="437" t="n"/>
-      <c r="AA11" s="437" t="n"/>
-      <c r="AB11" s="437" t="n"/>
-      <c r="AC11" s="437" t="n"/>
-      <c r="AD11" s="437" t="n"/>
-      <c r="AE11" s="437" t="n"/>
-      <c r="AF11" s="437" t="n"/>
-      <c r="AG11" s="437" t="n"/>
-      <c r="AH11" s="437" t="n"/>
-      <c r="AI11" s="437" t="n"/>
-      <c r="AJ11" s="437" t="n"/>
-      <c r="AK11" s="437" t="n"/>
-      <c r="AL11" s="437" t="n"/>
-      <c r="AM11" s="437" t="n"/>
-      <c r="AN11" s="564" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="653" t="inlineStr"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="13" t="n"/>
+      <c r="K11" s="657" t="n"/>
+      <c r="L11" s="657" t="n"/>
+      <c r="M11" s="657" t="n"/>
+      <c r="N11" s="657" t="n"/>
+      <c r="O11" s="657" t="n"/>
+      <c r="P11" s="657" t="n"/>
+      <c r="Q11" s="657" t="n"/>
+      <c r="R11" s="657" t="n"/>
+      <c r="S11" s="657" t="n"/>
+      <c r="T11" s="657" t="n"/>
+      <c r="U11" s="657" t="n"/>
+      <c r="V11" s="657" t="n"/>
+      <c r="W11" s="657" t="n"/>
+      <c r="X11" s="657" t="n"/>
+      <c r="Y11" s="657" t="n"/>
+      <c r="Z11" s="657" t="n"/>
+      <c r="AA11" s="657" t="n"/>
+      <c r="AB11" s="657" t="n"/>
+      <c r="AC11" s="657" t="n"/>
+      <c r="AD11" s="657" t="n"/>
+      <c r="AE11" s="657" t="n"/>
+      <c r="AF11" s="657" t="n"/>
+      <c r="AG11" s="657" t="n"/>
+      <c r="AH11" s="657" t="n"/>
+      <c r="AI11" s="657" t="n"/>
+      <c r="AJ11" s="657" t="n"/>
+      <c r="AK11" s="657" t="n"/>
+      <c r="AL11" s="657" t="n"/>
+      <c r="AM11" s="657" t="n"/>
+      <c r="AN11" s="658" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="565" t="inlineStr">
+      <c r="A12" s="659" t="inlineStr">
         <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="B12" s="566" t="n"/>
-      <c r="C12" s="567" t="inlineStr"/>
-      <c r="D12" s="566" t="n"/>
-      <c r="E12" s="566" t="n"/>
-      <c r="F12" s="568" t="inlineStr">
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="660" t="inlineStr"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="661" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="G12" s="566" t="n"/>
-      <c r="H12" s="567" t="inlineStr"/>
-      <c r="I12" s="566" t="n"/>
-      <c r="J12" s="566" t="n"/>
-      <c r="K12" s="569" t="n"/>
-      <c r="L12" s="566" t="n"/>
-      <c r="M12" s="566" t="n"/>
-      <c r="N12" s="566" t="n"/>
-      <c r="O12" s="566" t="n"/>
-      <c r="P12" s="566" t="n"/>
-      <c r="Q12" s="566" t="n"/>
-      <c r="R12" s="566" t="n"/>
-      <c r="S12" s="566" t="n"/>
-      <c r="T12" s="566" t="n"/>
-      <c r="U12" s="566" t="n"/>
-      <c r="V12" s="566" t="n"/>
-      <c r="W12" s="566" t="n"/>
-      <c r="X12" s="566" t="n"/>
-      <c r="Y12" s="566" t="n"/>
-      <c r="Z12" s="566" t="n"/>
-      <c r="AA12" s="566" t="n"/>
-      <c r="AB12" s="566" t="n"/>
-      <c r="AC12" s="566" t="n"/>
-      <c r="AD12" s="566" t="n"/>
-      <c r="AE12" s="566" t="n"/>
-      <c r="AF12" s="566" t="n"/>
-      <c r="AG12" s="566" t="n"/>
-      <c r="AH12" s="566" t="n"/>
-      <c r="AI12" s="566" t="n"/>
-      <c r="AJ12" s="566" t="n"/>
-      <c r="AK12" s="566" t="n"/>
-      <c r="AL12" s="566" t="n"/>
-      <c r="AM12" s="566" t="n"/>
-      <c r="AN12" s="570" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="660" t="inlineStr"/>
+      <c r="I12" s="19" t="n"/>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="662" t="n"/>
+      <c r="L12" s="662" t="n"/>
+      <c r="M12" s="662" t="n"/>
+      <c r="N12" s="662" t="n"/>
+      <c r="O12" s="662" t="n"/>
+      <c r="P12" s="662" t="n"/>
+      <c r="Q12" s="662" t="n"/>
+      <c r="R12" s="662" t="n"/>
+      <c r="S12" s="662" t="n"/>
+      <c r="T12" s="662" t="n"/>
+      <c r="U12" s="662" t="n"/>
+      <c r="V12" s="662" t="n"/>
+      <c r="W12" s="662" t="n"/>
+      <c r="X12" s="662" t="n"/>
+      <c r="Y12" s="662" t="n"/>
+      <c r="Z12" s="662" t="n"/>
+      <c r="AA12" s="662" t="n"/>
+      <c r="AB12" s="662" t="n"/>
+      <c r="AC12" s="662" t="n"/>
+      <c r="AD12" s="662" t="n"/>
+      <c r="AE12" s="662" t="n"/>
+      <c r="AF12" s="662" t="n"/>
+      <c r="AG12" s="662" t="n"/>
+      <c r="AH12" s="662" t="n"/>
+      <c r="AI12" s="662" t="n"/>
+      <c r="AJ12" s="662" t="n"/>
+      <c r="AK12" s="662" t="n"/>
+      <c r="AL12" s="662" t="n"/>
+      <c r="AM12" s="662" t="n"/>
+      <c r="AN12" s="663" t="n"/>
     </row>
     <row r="13" ht="3" customHeight="1">
-      <c r="A13" s="442" t="n"/>
-      <c r="B13" s="495" t="n"/>
-      <c r="C13" s="495" t="n"/>
-      <c r="D13" s="495" t="n"/>
-      <c r="E13" s="495" t="n"/>
-      <c r="F13" s="495" t="n"/>
-      <c r="G13" s="495" t="n"/>
-      <c r="H13" s="495" t="n"/>
-      <c r="I13" s="495" t="n"/>
-      <c r="J13" s="495" t="n"/>
-      <c r="K13" s="443" t="n"/>
-      <c r="L13" s="443" t="n"/>
-      <c r="M13" s="443" t="n"/>
-      <c r="N13" s="443" t="n"/>
-      <c r="O13" s="443" t="n"/>
-      <c r="P13" s="443" t="n"/>
-      <c r="Q13" s="443" t="n"/>
-      <c r="R13" s="443" t="n"/>
-      <c r="S13" s="443" t="n"/>
-      <c r="T13" s="443" t="n"/>
-      <c r="U13" s="443" t="n"/>
-      <c r="V13" s="443" t="n"/>
-      <c r="W13" s="443" t="n"/>
-      <c r="X13" s="443" t="n"/>
-      <c r="Y13" s="443" t="n"/>
-      <c r="Z13" s="443" t="n"/>
-      <c r="AA13" s="443" t="n"/>
-      <c r="AB13" s="443" t="n"/>
-      <c r="AC13" s="443" t="n"/>
-      <c r="AD13" s="443" t="n"/>
-      <c r="AE13" s="443" t="n"/>
-      <c r="AF13" s="443" t="n"/>
-      <c r="AG13" s="443" t="n"/>
-      <c r="AH13" s="443" t="n"/>
-      <c r="AI13" s="443" t="n"/>
-      <c r="AJ13" s="443" t="n"/>
-      <c r="AK13" s="443" t="n"/>
-      <c r="AL13" s="443" t="n"/>
-      <c r="AM13" s="443" t="n"/>
-      <c r="AN13" s="443" t="n"/>
+      <c r="A13" s="664" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="10" t="n"/>
+      <c r="K13" s="665" t="n"/>
+      <c r="L13" s="665" t="n"/>
+      <c r="M13" s="665" t="n"/>
+      <c r="N13" s="665" t="n"/>
+      <c r="O13" s="665" t="n"/>
+      <c r="P13" s="665" t="n"/>
+      <c r="Q13" s="665" t="n"/>
+      <c r="R13" s="665" t="n"/>
+      <c r="S13" s="665" t="n"/>
+      <c r="T13" s="665" t="n"/>
+      <c r="U13" s="665" t="n"/>
+      <c r="V13" s="665" t="n"/>
+      <c r="W13" s="665" t="n"/>
+      <c r="X13" s="665" t="n"/>
+      <c r="Y13" s="665" t="n"/>
+      <c r="Z13" s="665" t="n"/>
+      <c r="AA13" s="665" t="n"/>
+      <c r="AB13" s="665" t="n"/>
+      <c r="AC13" s="665" t="n"/>
+      <c r="AD13" s="665" t="n"/>
+      <c r="AE13" s="665" t="n"/>
+      <c r="AF13" s="665" t="n"/>
+      <c r="AG13" s="665" t="n"/>
+      <c r="AH13" s="665" t="n"/>
+      <c r="AI13" s="665" t="n"/>
+      <c r="AJ13" s="665" t="n"/>
+      <c r="AK13" s="665" t="n"/>
+      <c r="AL13" s="665" t="n"/>
+      <c r="AM13" s="665" t="n"/>
+      <c r="AN13" s="665" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="548" t="inlineStr">
+      <c r="A14" s="644" t="inlineStr">
         <is>
           <t>2.  RECEIPT AND EVALUATION SECTION</t>
         </is>
       </c>
-      <c r="B14" s="549" t="n"/>
-      <c r="C14" s="549" t="n"/>
-      <c r="D14" s="549" t="n"/>
-      <c r="E14" s="549" t="n"/>
-      <c r="F14" s="549" t="n"/>
-      <c r="G14" s="549" t="n"/>
-      <c r="H14" s="549" t="n"/>
-      <c r="I14" s="549" t="n"/>
-      <c r="J14" s="549" t="n"/>
-      <c r="K14" s="549" t="n"/>
-      <c r="L14" s="549" t="n"/>
-      <c r="M14" s="549" t="n"/>
-      <c r="N14" s="549" t="n"/>
-      <c r="O14" s="549" t="n"/>
-      <c r="P14" s="549" t="n"/>
-      <c r="Q14" s="549" t="n"/>
-      <c r="R14" s="549" t="n"/>
-      <c r="S14" s="549" t="n"/>
-      <c r="T14" s="549" t="n"/>
-      <c r="U14" s="549" t="n"/>
-      <c r="V14" s="549" t="n"/>
-      <c r="W14" s="549" t="n"/>
-      <c r="X14" s="549" t="n"/>
-      <c r="Y14" s="549" t="n"/>
-      <c r="Z14" s="549" t="n"/>
-      <c r="AA14" s="549" t="n"/>
-      <c r="AB14" s="549" t="n"/>
-      <c r="AC14" s="549" t="n"/>
-      <c r="AD14" s="549" t="n"/>
-      <c r="AE14" s="549" t="n"/>
-      <c r="AF14" s="549" t="n"/>
-      <c r="AG14" s="549" t="n"/>
-      <c r="AH14" s="549" t="n"/>
-      <c r="AI14" s="549" t="n"/>
-      <c r="AJ14" s="549" t="n"/>
-      <c r="AK14" s="549" t="n"/>
-      <c r="AL14" s="549" t="n"/>
-      <c r="AM14" s="549" t="n"/>
-      <c r="AN14" s="550" t="n"/>
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="27" t="n"/>
+      <c r="H14" s="27" t="n"/>
+      <c r="I14" s="27" t="n"/>
+      <c r="J14" s="27" t="n"/>
+      <c r="K14" s="645" t="n"/>
+      <c r="L14" s="645" t="n"/>
+      <c r="M14" s="645" t="n"/>
+      <c r="N14" s="645" t="n"/>
+      <c r="O14" s="645" t="n"/>
+      <c r="P14" s="645" t="n"/>
+      <c r="Q14" s="645" t="n"/>
+      <c r="R14" s="645" t="n"/>
+      <c r="S14" s="645" t="n"/>
+      <c r="T14" s="645" t="n"/>
+      <c r="U14" s="645" t="n"/>
+      <c r="V14" s="645" t="n"/>
+      <c r="W14" s="645" t="n"/>
+      <c r="X14" s="645" t="n"/>
+      <c r="Y14" s="645" t="n"/>
+      <c r="Z14" s="645" t="n"/>
+      <c r="AA14" s="645" t="n"/>
+      <c r="AB14" s="645" t="n"/>
+      <c r="AC14" s="645" t="n"/>
+      <c r="AD14" s="645" t="n"/>
+      <c r="AE14" s="645" t="n"/>
+      <c r="AF14" s="645" t="n"/>
+      <c r="AG14" s="645" t="n"/>
+      <c r="AH14" s="645" t="n"/>
+      <c r="AI14" s="645" t="n"/>
+      <c r="AJ14" s="645" t="n"/>
+      <c r="AK14" s="645" t="n"/>
+      <c r="AL14" s="645" t="n"/>
+      <c r="AM14" s="645" t="n"/>
+      <c r="AN14" s="646" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="551" t="inlineStr">
+      <c r="A15" s="647" t="inlineStr">
         <is>
           <t>Current Scope</t>
         </is>
       </c>
-      <c r="B15" s="552" t="n"/>
-      <c r="C15" s="553" t="inlineStr"/>
-      <c r="D15" s="552" t="n"/>
-      <c r="E15" s="552" t="n"/>
-      <c r="F15" s="554" t="inlineStr">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="648" t="inlineStr"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="649" t="inlineStr">
         <is>
           <t>Disposition Summary</t>
         </is>
       </c>
-      <c r="G15" s="552" t="n"/>
-      <c r="H15" s="553" t="inlineStr"/>
-      <c r="I15" s="552" t="n"/>
-      <c r="J15" s="552" t="n"/>
-      <c r="K15" s="555" t="n"/>
-      <c r="L15" s="556" t="n"/>
-      <c r="M15" s="556" t="n"/>
-      <c r="N15" s="556" t="n"/>
-      <c r="O15" s="556" t="n"/>
-      <c r="P15" s="556" t="n"/>
-      <c r="Q15" s="556" t="n"/>
-      <c r="R15" s="556" t="n"/>
-      <c r="S15" s="556" t="n"/>
-      <c r="T15" s="556" t="n"/>
-      <c r="U15" s="556" t="n"/>
-      <c r="V15" s="556" t="n"/>
-      <c r="W15" s="556" t="n"/>
-      <c r="X15" s="556" t="n"/>
-      <c r="Y15" s="556" t="n"/>
-      <c r="Z15" s="556" t="n"/>
-      <c r="AA15" s="556" t="n"/>
-      <c r="AB15" s="556" t="n"/>
-      <c r="AC15" s="556" t="n"/>
-      <c r="AD15" s="556" t="n"/>
-      <c r="AE15" s="556" t="n"/>
-      <c r="AF15" s="556" t="n"/>
-      <c r="AG15" s="556" t="n"/>
-      <c r="AH15" s="556" t="n"/>
-      <c r="AI15" s="556" t="n"/>
-      <c r="AJ15" s="556" t="n"/>
-      <c r="AK15" s="556" t="n"/>
-      <c r="AL15" s="556" t="n"/>
-      <c r="AM15" s="556" t="n"/>
-      <c r="AN15" s="557" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="648" t="inlineStr"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="650" t="n"/>
+      <c r="L15" s="650" t="n"/>
+      <c r="M15" s="650" t="n"/>
+      <c r="N15" s="650" t="n"/>
+      <c r="O15" s="650" t="n"/>
+      <c r="P15" s="650" t="n"/>
+      <c r="Q15" s="650" t="n"/>
+      <c r="R15" s="650" t="n"/>
+      <c r="S15" s="650" t="n"/>
+      <c r="T15" s="650" t="n"/>
+      <c r="U15" s="650" t="n"/>
+      <c r="V15" s="650" t="n"/>
+      <c r="W15" s="650" t="n"/>
+      <c r="X15" s="650" t="n"/>
+      <c r="Y15" s="650" t="n"/>
+      <c r="Z15" s="650" t="n"/>
+      <c r="AA15" s="650" t="n"/>
+      <c r="AB15" s="650" t="n"/>
+      <c r="AC15" s="650" t="n"/>
+      <c r="AD15" s="650" t="n"/>
+      <c r="AE15" s="650" t="n"/>
+      <c r="AF15" s="650" t="n"/>
+      <c r="AG15" s="650" t="n"/>
+      <c r="AH15" s="650" t="n"/>
+      <c r="AI15" s="650" t="n"/>
+      <c r="AJ15" s="650" t="n"/>
+      <c r="AK15" s="650" t="n"/>
+      <c r="AL15" s="650" t="n"/>
+      <c r="AM15" s="650" t="n"/>
+      <c r="AN15" s="651" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="558" t="inlineStr">
+      <c r="A16" s="652" t="inlineStr">
         <is>
           <t>Primary Return / Defect Note</t>
         </is>
       </c>
-      <c r="B16" s="437" t="n"/>
-      <c r="C16" s="559" t="inlineStr"/>
-      <c r="D16" s="437" t="n"/>
-      <c r="E16" s="437" t="n"/>
-      <c r="F16" s="560" t="inlineStr">
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="653" t="inlineStr"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="654" t="inlineStr">
         <is>
           <t>Next Review</t>
         </is>
       </c>
-      <c r="G16" s="437" t="n"/>
-      <c r="H16" s="559" t="inlineStr"/>
-      <c r="I16" s="437" t="n"/>
-      <c r="J16" s="437" t="n"/>
-      <c r="K16" s="561" t="n"/>
-      <c r="L16" s="446" t="n"/>
-      <c r="M16" s="446" t="n"/>
-      <c r="N16" s="446" t="n"/>
-      <c r="O16" s="446" t="n"/>
-      <c r="P16" s="446" t="n"/>
-      <c r="Q16" s="446" t="n"/>
-      <c r="R16" s="446" t="n"/>
-      <c r="S16" s="446" t="n"/>
-      <c r="T16" s="446" t="n"/>
-      <c r="U16" s="446" t="n"/>
-      <c r="V16" s="446" t="n"/>
-      <c r="W16" s="446" t="n"/>
-      <c r="X16" s="446" t="n"/>
-      <c r="Y16" s="446" t="n"/>
-      <c r="Z16" s="446" t="n"/>
-      <c r="AA16" s="446" t="n"/>
-      <c r="AB16" s="446" t="n"/>
-      <c r="AC16" s="446" t="n"/>
-      <c r="AD16" s="446" t="n"/>
-      <c r="AE16" s="446" t="n"/>
-      <c r="AF16" s="446" t="n"/>
-      <c r="AG16" s="446" t="n"/>
-      <c r="AH16" s="446" t="n"/>
-      <c r="AI16" s="446" t="n"/>
-      <c r="AJ16" s="446" t="n"/>
-      <c r="AK16" s="446" t="n"/>
-      <c r="AL16" s="446" t="n"/>
-      <c r="AM16" s="446" t="n"/>
-      <c r="AN16" s="562" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="653" t="inlineStr"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="13" t="n"/>
+      <c r="K16" s="655" t="n"/>
+      <c r="L16" s="655" t="n"/>
+      <c r="M16" s="655" t="n"/>
+      <c r="N16" s="655" t="n"/>
+      <c r="O16" s="655" t="n"/>
+      <c r="P16" s="655" t="n"/>
+      <c r="Q16" s="655" t="n"/>
+      <c r="R16" s="655" t="n"/>
+      <c r="S16" s="655" t="n"/>
+      <c r="T16" s="655" t="n"/>
+      <c r="U16" s="655" t="n"/>
+      <c r="V16" s="655" t="n"/>
+      <c r="W16" s="655" t="n"/>
+      <c r="X16" s="655" t="n"/>
+      <c r="Y16" s="655" t="n"/>
+      <c r="Z16" s="655" t="n"/>
+      <c r="AA16" s="655" t="n"/>
+      <c r="AB16" s="655" t="n"/>
+      <c r="AC16" s="655" t="n"/>
+      <c r="AD16" s="655" t="n"/>
+      <c r="AE16" s="655" t="n"/>
+      <c r="AF16" s="655" t="n"/>
+      <c r="AG16" s="655" t="n"/>
+      <c r="AH16" s="655" t="n"/>
+      <c r="AI16" s="655" t="n"/>
+      <c r="AJ16" s="655" t="n"/>
+      <c r="AK16" s="655" t="n"/>
+      <c r="AL16" s="655" t="n"/>
+      <c r="AM16" s="655" t="n"/>
+      <c r="AN16" s="656" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="558" t="inlineStr">
+      <c r="A17" s="652" t="inlineStr">
         <is>
           <t>Action Owner</t>
         </is>
       </c>
-      <c r="B17" s="437" t="n"/>
-      <c r="C17" s="559" t="inlineStr"/>
-      <c r="D17" s="437" t="n"/>
-      <c r="E17" s="437" t="n"/>
-      <c r="F17" s="560" t="inlineStr">
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="653" t="inlineStr"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="654" t="inlineStr">
         <is>
           <t>Next Review Date</t>
         </is>
       </c>
-      <c r="G17" s="437" t="n"/>
-      <c r="H17" s="559" t="inlineStr"/>
-      <c r="I17" s="437" t="n"/>
-      <c r="J17" s="437" t="n"/>
-      <c r="K17" s="561" t="n"/>
-      <c r="L17" s="446" t="n"/>
-      <c r="M17" s="446" t="n"/>
-      <c r="N17" s="446" t="n"/>
-      <c r="O17" s="446" t="n"/>
-      <c r="P17" s="446" t="n"/>
-      <c r="Q17" s="446" t="n"/>
-      <c r="R17" s="446" t="n"/>
-      <c r="S17" s="446" t="n"/>
-      <c r="T17" s="446" t="n"/>
-      <c r="U17" s="446" t="n"/>
-      <c r="V17" s="446" t="n"/>
-      <c r="W17" s="446" t="n"/>
-      <c r="X17" s="446" t="n"/>
-      <c r="Y17" s="446" t="n"/>
-      <c r="Z17" s="446" t="n"/>
-      <c r="AA17" s="446" t="n"/>
-      <c r="AB17" s="446" t="n"/>
-      <c r="AC17" s="446" t="n"/>
-      <c r="AD17" s="446" t="n"/>
-      <c r="AE17" s="446" t="n"/>
-      <c r="AF17" s="446" t="n"/>
-      <c r="AG17" s="446" t="n"/>
-      <c r="AH17" s="446" t="n"/>
-      <c r="AI17" s="446" t="n"/>
-      <c r="AJ17" s="446" t="n"/>
-      <c r="AK17" s="446" t="n"/>
-      <c r="AL17" s="446" t="n"/>
-      <c r="AM17" s="446" t="n"/>
-      <c r="AN17" s="562" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="653" t="inlineStr"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="13" t="n"/>
+      <c r="K17" s="655" t="n"/>
+      <c r="L17" s="655" t="n"/>
+      <c r="M17" s="655" t="n"/>
+      <c r="N17" s="655" t="n"/>
+      <c r="O17" s="655" t="n"/>
+      <c r="P17" s="655" t="n"/>
+      <c r="Q17" s="655" t="n"/>
+      <c r="R17" s="655" t="n"/>
+      <c r="S17" s="655" t="n"/>
+      <c r="T17" s="655" t="n"/>
+      <c r="U17" s="655" t="n"/>
+      <c r="V17" s="655" t="n"/>
+      <c r="W17" s="655" t="n"/>
+      <c r="X17" s="655" t="n"/>
+      <c r="Y17" s="655" t="n"/>
+      <c r="Z17" s="655" t="n"/>
+      <c r="AA17" s="655" t="n"/>
+      <c r="AB17" s="655" t="n"/>
+      <c r="AC17" s="655" t="n"/>
+      <c r="AD17" s="655" t="n"/>
+      <c r="AE17" s="655" t="n"/>
+      <c r="AF17" s="655" t="n"/>
+      <c r="AG17" s="655" t="n"/>
+      <c r="AH17" s="655" t="n"/>
+      <c r="AI17" s="655" t="n"/>
+      <c r="AJ17" s="655" t="n"/>
+      <c r="AK17" s="655" t="n"/>
+      <c r="AL17" s="655" t="n"/>
+      <c r="AM17" s="655" t="n"/>
+      <c r="AN17" s="656" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="565" t="inlineStr">
+      <c r="A18" s="659" t="inlineStr">
         <is>
           <t>Escalation if Not Disposed</t>
         </is>
       </c>
-      <c r="B18" s="566" t="n"/>
-      <c r="C18" s="567" t="inlineStr"/>
-      <c r="D18" s="566" t="n"/>
-      <c r="E18" s="566" t="n"/>
-      <c r="F18" s="568" t="inlineStr">
+      <c r="B18" s="22" t="n"/>
+      <c r="C18" s="660" t="inlineStr"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="661" t="inlineStr">
         <is>
           <t>Overall Status</t>
         </is>
       </c>
-      <c r="G18" s="566" t="n"/>
-      <c r="H18" s="567" t="inlineStr"/>
-      <c r="I18" s="566" t="n"/>
-      <c r="J18" s="566" t="n"/>
-      <c r="K18" s="571" t="n"/>
-      <c r="L18" s="572" t="n"/>
-      <c r="M18" s="572" t="n"/>
-      <c r="N18" s="572" t="n"/>
-      <c r="O18" s="572" t="n"/>
-      <c r="P18" s="572" t="n"/>
-      <c r="Q18" s="572" t="n"/>
-      <c r="R18" s="572" t="n"/>
-      <c r="S18" s="572" t="n"/>
-      <c r="T18" s="572" t="n"/>
-      <c r="U18" s="572" t="n"/>
-      <c r="V18" s="572" t="n"/>
-      <c r="W18" s="572" t="n"/>
-      <c r="X18" s="572" t="n"/>
-      <c r="Y18" s="572" t="n"/>
-      <c r="Z18" s="572" t="n"/>
-      <c r="AA18" s="572" t="n"/>
-      <c r="AB18" s="572" t="n"/>
-      <c r="AC18" s="572" t="n"/>
-      <c r="AD18" s="572" t="n"/>
-      <c r="AE18" s="572" t="n"/>
-      <c r="AF18" s="572" t="n"/>
-      <c r="AG18" s="572" t="n"/>
-      <c r="AH18" s="572" t="n"/>
-      <c r="AI18" s="572" t="n"/>
-      <c r="AJ18" s="572" t="n"/>
-      <c r="AK18" s="572" t="n"/>
-      <c r="AL18" s="572" t="n"/>
-      <c r="AM18" s="572" t="n"/>
-      <c r="AN18" s="573" t="n"/>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="660" t="inlineStr"/>
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="22" t="n"/>
+      <c r="K18" s="666" t="n"/>
+      <c r="L18" s="666" t="n"/>
+      <c r="M18" s="666" t="n"/>
+      <c r="N18" s="666" t="n"/>
+      <c r="O18" s="666" t="n"/>
+      <c r="P18" s="666" t="n"/>
+      <c r="Q18" s="666" t="n"/>
+      <c r="R18" s="666" t="n"/>
+      <c r="S18" s="666" t="n"/>
+      <c r="T18" s="666" t="n"/>
+      <c r="U18" s="666" t="n"/>
+      <c r="V18" s="666" t="n"/>
+      <c r="W18" s="666" t="n"/>
+      <c r="X18" s="666" t="n"/>
+      <c r="Y18" s="666" t="n"/>
+      <c r="Z18" s="666" t="n"/>
+      <c r="AA18" s="666" t="n"/>
+      <c r="AB18" s="666" t="n"/>
+      <c r="AC18" s="666" t="n"/>
+      <c r="AD18" s="666" t="n"/>
+      <c r="AE18" s="666" t="n"/>
+      <c r="AF18" s="666" t="n"/>
+      <c r="AG18" s="666" t="n"/>
+      <c r="AH18" s="666" t="n"/>
+      <c r="AI18" s="666" t="n"/>
+      <c r="AJ18" s="666" t="n"/>
+      <c r="AK18" s="666" t="n"/>
+      <c r="AL18" s="666" t="n"/>
+      <c r="AM18" s="666" t="n"/>
+      <c r="AN18" s="667" t="n"/>
     </row>
     <row r="19" ht="3" customHeight="1">
-      <c r="A19" s="442" t="n"/>
-      <c r="B19" s="495" t="n"/>
-      <c r="C19" s="495" t="n"/>
-      <c r="D19" s="495" t="n"/>
-      <c r="E19" s="495" t="n"/>
-      <c r="F19" s="495" t="n"/>
-      <c r="G19" s="495" t="n"/>
-      <c r="H19" s="495" t="n"/>
-      <c r="I19" s="495" t="n"/>
-      <c r="J19" s="495" t="n"/>
-      <c r="K19" s="443" t="n"/>
-      <c r="L19" s="443" t="n"/>
-      <c r="M19" s="443" t="n"/>
-      <c r="N19" s="443" t="n"/>
-      <c r="O19" s="443" t="n"/>
-      <c r="P19" s="443" t="n"/>
-      <c r="Q19" s="443" t="n"/>
-      <c r="R19" s="443" t="n"/>
-      <c r="S19" s="443" t="n"/>
-      <c r="T19" s="443" t="n"/>
-      <c r="U19" s="443" t="n"/>
-      <c r="V19" s="443" t="n"/>
-      <c r="W19" s="443" t="n"/>
-      <c r="X19" s="443" t="n"/>
-      <c r="Y19" s="443" t="n"/>
-      <c r="Z19" s="443" t="n"/>
-      <c r="AA19" s="443" t="n"/>
-      <c r="AB19" s="443" t="n"/>
-      <c r="AC19" s="443" t="n"/>
-      <c r="AD19" s="443" t="n"/>
-      <c r="AE19" s="443" t="n"/>
-      <c r="AF19" s="443" t="n"/>
-      <c r="AG19" s="443" t="n"/>
-      <c r="AH19" s="443" t="n"/>
-      <c r="AI19" s="443" t="n"/>
-      <c r="AJ19" s="443" t="n"/>
-      <c r="AK19" s="443" t="n"/>
-      <c r="AL19" s="443" t="n"/>
-      <c r="AM19" s="443" t="n"/>
-      <c r="AN19" s="443" t="n"/>
+      <c r="A19" s="664" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="665" t="n"/>
+      <c r="L19" s="665" t="n"/>
+      <c r="M19" s="665" t="n"/>
+      <c r="N19" s="665" t="n"/>
+      <c r="O19" s="665" t="n"/>
+      <c r="P19" s="665" t="n"/>
+      <c r="Q19" s="665" t="n"/>
+      <c r="R19" s="665" t="n"/>
+      <c r="S19" s="665" t="n"/>
+      <c r="T19" s="665" t="n"/>
+      <c r="U19" s="665" t="n"/>
+      <c r="V19" s="665" t="n"/>
+      <c r="W19" s="665" t="n"/>
+      <c r="X19" s="665" t="n"/>
+      <c r="Y19" s="665" t="n"/>
+      <c r="Z19" s="665" t="n"/>
+      <c r="AA19" s="665" t="n"/>
+      <c r="AB19" s="665" t="n"/>
+      <c r="AC19" s="665" t="n"/>
+      <c r="AD19" s="665" t="n"/>
+      <c r="AE19" s="665" t="n"/>
+      <c r="AF19" s="665" t="n"/>
+      <c r="AG19" s="665" t="n"/>
+      <c r="AH19" s="665" t="n"/>
+      <c r="AI19" s="665" t="n"/>
+      <c r="AJ19" s="665" t="n"/>
+      <c r="AK19" s="665" t="n"/>
+      <c r="AL19" s="665" t="n"/>
+      <c r="AM19" s="665" t="n"/>
+      <c r="AN19" s="665" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="548" t="inlineStr">
+      <c r="A20" s="644" t="inlineStr">
         <is>
           <t>3.  DISPOSITION SECTION</t>
         </is>
       </c>
-      <c r="B20" s="549" t="n"/>
-      <c r="C20" s="549" t="n"/>
-      <c r="D20" s="549" t="n"/>
-      <c r="E20" s="549" t="n"/>
-      <c r="F20" s="549" t="n"/>
-      <c r="G20" s="549" t="n"/>
-      <c r="H20" s="549" t="n"/>
-      <c r="I20" s="549" t="n"/>
-      <c r="J20" s="549" t="n"/>
-      <c r="K20" s="549" t="n"/>
-      <c r="L20" s="549" t="n"/>
-      <c r="M20" s="549" t="n"/>
-      <c r="N20" s="549" t="n"/>
-      <c r="O20" s="549" t="n"/>
-      <c r="P20" s="549" t="n"/>
-      <c r="Q20" s="549" t="n"/>
-      <c r="R20" s="549" t="n"/>
-      <c r="S20" s="549" t="n"/>
-      <c r="T20" s="549" t="n"/>
-      <c r="U20" s="549" t="n"/>
-      <c r="V20" s="549" t="n"/>
-      <c r="W20" s="549" t="n"/>
-      <c r="X20" s="549" t="n"/>
-      <c r="Y20" s="549" t="n"/>
-      <c r="Z20" s="549" t="n"/>
-      <c r="AA20" s="549" t="n"/>
-      <c r="AB20" s="549" t="n"/>
-      <c r="AC20" s="549" t="n"/>
-      <c r="AD20" s="549" t="n"/>
-      <c r="AE20" s="549" t="n"/>
-      <c r="AF20" s="549" t="n"/>
-      <c r="AG20" s="549" t="n"/>
-      <c r="AH20" s="549" t="n"/>
-      <c r="AI20" s="549" t="n"/>
-      <c r="AJ20" s="549" t="n"/>
-      <c r="AK20" s="549" t="n"/>
-      <c r="AL20" s="549" t="n"/>
-      <c r="AM20" s="549" t="n"/>
-      <c r="AN20" s="550" t="n"/>
+      <c r="B20" s="27" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="27" t="n"/>
+      <c r="H20" s="27" t="n"/>
+      <c r="I20" s="27" t="n"/>
+      <c r="J20" s="27" t="n"/>
+      <c r="K20" s="645" t="n"/>
+      <c r="L20" s="645" t="n"/>
+      <c r="M20" s="645" t="n"/>
+      <c r="N20" s="645" t="n"/>
+      <c r="O20" s="645" t="n"/>
+      <c r="P20" s="645" t="n"/>
+      <c r="Q20" s="645" t="n"/>
+      <c r="R20" s="645" t="n"/>
+      <c r="S20" s="645" t="n"/>
+      <c r="T20" s="645" t="n"/>
+      <c r="U20" s="645" t="n"/>
+      <c r="V20" s="645" t="n"/>
+      <c r="W20" s="645" t="n"/>
+      <c r="X20" s="645" t="n"/>
+      <c r="Y20" s="645" t="n"/>
+      <c r="Z20" s="645" t="n"/>
+      <c r="AA20" s="645" t="n"/>
+      <c r="AB20" s="645" t="n"/>
+      <c r="AC20" s="645" t="n"/>
+      <c r="AD20" s="645" t="n"/>
+      <c r="AE20" s="645" t="n"/>
+      <c r="AF20" s="645" t="n"/>
+      <c r="AG20" s="645" t="n"/>
+      <c r="AH20" s="645" t="n"/>
+      <c r="AI20" s="645" t="n"/>
+      <c r="AJ20" s="645" t="n"/>
+      <c r="AK20" s="645" t="n"/>
+      <c r="AL20" s="645" t="n"/>
+      <c r="AM20" s="645" t="n"/>
+      <c r="AN20" s="646" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="574" t="inlineStr">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B21" s="575" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="C21" s="575" t="inlineStr">
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>RMA ID</t>
         </is>
       </c>
-      <c r="D21" s="575" t="inlineStr">
+      <c r="D21" s="37" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="E21" s="575" t="inlineStr">
+      <c r="E21" s="37" t="inlineStr">
         <is>
           <t>Part / Revision</t>
         </is>
       </c>
-      <c r="F21" s="575" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>Qty / Condition</t>
         </is>
       </c>
-      <c r="G21" s="575" t="inlineStr">
+      <c r="G21" s="37" t="inlineStr">
         <is>
           <t>Disposition</t>
         </is>
       </c>
-      <c r="H21" s="575" t="inlineStr">
+      <c r="H21" s="37" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="I21" s="575" t="inlineStr">
+      <c r="I21" s="37" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J21" s="575" t="inlineStr">
+      <c r="J21" s="37" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="K21" s="575" t="n"/>
-      <c r="L21" s="575" t="n"/>
-      <c r="M21" s="575" t="n"/>
-      <c r="N21" s="575" t="n"/>
-      <c r="O21" s="575" t="n"/>
-      <c r="P21" s="575" t="n"/>
-      <c r="Q21" s="575" t="n"/>
-      <c r="R21" s="575" t="n"/>
-      <c r="S21" s="575" t="n"/>
-      <c r="T21" s="575" t="n"/>
-      <c r="U21" s="575" t="n"/>
-      <c r="V21" s="575" t="n"/>
-      <c r="W21" s="575" t="n"/>
-      <c r="X21" s="575" t="n"/>
-      <c r="Y21" s="575" t="n"/>
-      <c r="Z21" s="575" t="n"/>
-      <c r="AA21" s="575" t="n"/>
-      <c r="AB21" s="575" t="n"/>
-      <c r="AC21" s="575" t="n"/>
-      <c r="AD21" s="575" t="n"/>
-      <c r="AE21" s="575" t="n"/>
-      <c r="AF21" s="575" t="n"/>
-      <c r="AG21" s="575" t="n"/>
-      <c r="AH21" s="575" t="n"/>
-      <c r="AI21" s="575" t="n"/>
-      <c r="AJ21" s="575" t="n"/>
-      <c r="AK21" s="575" t="n"/>
-      <c r="AL21" s="575" t="n"/>
-      <c r="AM21" s="575" t="n"/>
-      <c r="AN21" s="576" t="n"/>
+      <c r="K21" s="37" t="n"/>
+      <c r="L21" s="37" t="n"/>
+      <c r="M21" s="37" t="n"/>
+      <c r="N21" s="37" t="n"/>
+      <c r="O21" s="37" t="n"/>
+      <c r="P21" s="37" t="n"/>
+      <c r="Q21" s="37" t="n"/>
+      <c r="R21" s="37" t="n"/>
+      <c r="S21" s="37" t="n"/>
+      <c r="T21" s="37" t="n"/>
+      <c r="U21" s="37" t="n"/>
+      <c r="V21" s="37" t="n"/>
+      <c r="W21" s="37" t="n"/>
+      <c r="X21" s="37" t="n"/>
+      <c r="Y21" s="37" t="n"/>
+      <c r="Z21" s="37" t="n"/>
+      <c r="AA21" s="37" t="n"/>
+      <c r="AB21" s="37" t="n"/>
+      <c r="AC21" s="37" t="n"/>
+      <c r="AD21" s="37" t="n"/>
+      <c r="AE21" s="37" t="n"/>
+      <c r="AF21" s="37" t="n"/>
+      <c r="AG21" s="37" t="n"/>
+      <c r="AH21" s="37" t="n"/>
+      <c r="AI21" s="37" t="n"/>
+      <c r="AJ21" s="37" t="n"/>
+      <c r="AK21" s="37" t="n"/>
+      <c r="AL21" s="37" t="n"/>
+      <c r="AM21" s="37" t="n"/>
+      <c r="AN21" s="668" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="577">
+      <c r="A22" s="669">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B22" s="578" t="n"/>
-      <c r="C22" s="579" t="n"/>
-      <c r="D22" s="579" t="n"/>
-      <c r="E22" s="579" t="n"/>
-      <c r="F22" s="579" t="n"/>
-      <c r="G22" s="579" t="n"/>
-      <c r="H22" s="579" t="n"/>
-      <c r="I22" s="579" t="n"/>
-      <c r="J22" s="579" t="n"/>
-      <c r="K22" s="556" t="n"/>
-      <c r="L22" s="556" t="n"/>
-      <c r="M22" s="556" t="n"/>
-      <c r="N22" s="556" t="n"/>
-      <c r="O22" s="556" t="n"/>
-      <c r="P22" s="556" t="n"/>
-      <c r="Q22" s="556" t="n"/>
-      <c r="R22" s="556" t="n"/>
-      <c r="S22" s="556" t="n"/>
-      <c r="T22" s="556" t="n"/>
-      <c r="U22" s="556" t="n"/>
-      <c r="V22" s="556" t="n"/>
-      <c r="W22" s="556" t="n"/>
-      <c r="X22" s="556" t="n"/>
-      <c r="Y22" s="556" t="n"/>
-      <c r="Z22" s="556" t="n"/>
-      <c r="AA22" s="556" t="n"/>
-      <c r="AB22" s="556" t="n"/>
-      <c r="AC22" s="556" t="n"/>
-      <c r="AD22" s="556" t="n"/>
-      <c r="AE22" s="556" t="n"/>
-      <c r="AF22" s="556" t="n"/>
-      <c r="AG22" s="556" t="n"/>
-      <c r="AH22" s="556" t="n"/>
-      <c r="AI22" s="556" t="n"/>
-      <c r="AJ22" s="556" t="n"/>
-      <c r="AK22" s="556" t="n"/>
-      <c r="AL22" s="556" t="n"/>
-      <c r="AM22" s="556" t="n"/>
-      <c r="AN22" s="557" t="n"/>
+      <c r="B22" s="670" t="n"/>
+      <c r="C22" s="648" t="n"/>
+      <c r="D22" s="648" t="n"/>
+      <c r="E22" s="648" t="n"/>
+      <c r="F22" s="648" t="n"/>
+      <c r="G22" s="648" t="n"/>
+      <c r="H22" s="648" t="n"/>
+      <c r="I22" s="648" t="n"/>
+      <c r="J22" s="648" t="n"/>
+      <c r="K22" s="650" t="n"/>
+      <c r="L22" s="650" t="n"/>
+      <c r="M22" s="650" t="n"/>
+      <c r="N22" s="650" t="n"/>
+      <c r="O22" s="650" t="n"/>
+      <c r="P22" s="650" t="n"/>
+      <c r="Q22" s="650" t="n"/>
+      <c r="R22" s="650" t="n"/>
+      <c r="S22" s="650" t="n"/>
+      <c r="T22" s="650" t="n"/>
+      <c r="U22" s="650" t="n"/>
+      <c r="V22" s="650" t="n"/>
+      <c r="W22" s="650" t="n"/>
+      <c r="X22" s="650" t="n"/>
+      <c r="Y22" s="650" t="n"/>
+      <c r="Z22" s="650" t="n"/>
+      <c r="AA22" s="650" t="n"/>
+      <c r="AB22" s="650" t="n"/>
+      <c r="AC22" s="650" t="n"/>
+      <c r="AD22" s="650" t="n"/>
+      <c r="AE22" s="650" t="n"/>
+      <c r="AF22" s="650" t="n"/>
+      <c r="AG22" s="650" t="n"/>
+      <c r="AH22" s="650" t="n"/>
+      <c r="AI22" s="650" t="n"/>
+      <c r="AJ22" s="650" t="n"/>
+      <c r="AK22" s="650" t="n"/>
+      <c r="AL22" s="650" t="n"/>
+      <c r="AM22" s="650" t="n"/>
+      <c r="AN22" s="651" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="580">
+      <c r="A23" s="671">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B23" s="457" t="n"/>
-      <c r="C23" s="581" t="n"/>
-      <c r="D23" s="581" t="n"/>
-      <c r="E23" s="581" t="n"/>
-      <c r="F23" s="581" t="n"/>
-      <c r="G23" s="581" t="n"/>
-      <c r="H23" s="581" t="n"/>
-      <c r="I23" s="581" t="n"/>
-      <c r="J23" s="581" t="n"/>
-      <c r="K23" s="446" t="n"/>
-      <c r="L23" s="446" t="n"/>
-      <c r="M23" s="446" t="n"/>
-      <c r="N23" s="446" t="n"/>
-      <c r="O23" s="446" t="n"/>
-      <c r="P23" s="446" t="n"/>
-      <c r="Q23" s="446" t="n"/>
-      <c r="R23" s="446" t="n"/>
-      <c r="S23" s="446" t="n"/>
-      <c r="T23" s="446" t="n"/>
-      <c r="U23" s="446" t="n"/>
-      <c r="V23" s="446" t="n"/>
-      <c r="W23" s="446" t="n"/>
-      <c r="X23" s="446" t="n"/>
-      <c r="Y23" s="446" t="n"/>
-      <c r="Z23" s="446" t="n"/>
-      <c r="AA23" s="446" t="n"/>
-      <c r="AB23" s="446" t="n"/>
-      <c r="AC23" s="446" t="n"/>
-      <c r="AD23" s="446" t="n"/>
-      <c r="AE23" s="446" t="n"/>
-      <c r="AF23" s="446" t="n"/>
-      <c r="AG23" s="446" t="n"/>
-      <c r="AH23" s="446" t="n"/>
-      <c r="AI23" s="446" t="n"/>
-      <c r="AJ23" s="446" t="n"/>
-      <c r="AK23" s="446" t="n"/>
-      <c r="AL23" s="446" t="n"/>
-      <c r="AM23" s="446" t="n"/>
-      <c r="AN23" s="562" t="n"/>
+      <c r="B23" s="672" t="n"/>
+      <c r="C23" s="673" t="n"/>
+      <c r="D23" s="673" t="n"/>
+      <c r="E23" s="673" t="n"/>
+      <c r="F23" s="673" t="n"/>
+      <c r="G23" s="673" t="n"/>
+      <c r="H23" s="673" t="n"/>
+      <c r="I23" s="673" t="n"/>
+      <c r="J23" s="673" t="n"/>
+      <c r="K23" s="655" t="n"/>
+      <c r="L23" s="655" t="n"/>
+      <c r="M23" s="655" t="n"/>
+      <c r="N23" s="655" t="n"/>
+      <c r="O23" s="655" t="n"/>
+      <c r="P23" s="655" t="n"/>
+      <c r="Q23" s="655" t="n"/>
+      <c r="R23" s="655" t="n"/>
+      <c r="S23" s="655" t="n"/>
+      <c r="T23" s="655" t="n"/>
+      <c r="U23" s="655" t="n"/>
+      <c r="V23" s="655" t="n"/>
+      <c r="W23" s="655" t="n"/>
+      <c r="X23" s="655" t="n"/>
+      <c r="Y23" s="655" t="n"/>
+      <c r="Z23" s="655" t="n"/>
+      <c r="AA23" s="655" t="n"/>
+      <c r="AB23" s="655" t="n"/>
+      <c r="AC23" s="655" t="n"/>
+      <c r="AD23" s="655" t="n"/>
+      <c r="AE23" s="655" t="n"/>
+      <c r="AF23" s="655" t="n"/>
+      <c r="AG23" s="655" t="n"/>
+      <c r="AH23" s="655" t="n"/>
+      <c r="AI23" s="655" t="n"/>
+      <c r="AJ23" s="655" t="n"/>
+      <c r="AK23" s="655" t="n"/>
+      <c r="AL23" s="655" t="n"/>
+      <c r="AM23" s="655" t="n"/>
+      <c r="AN23" s="656" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="580">
+      <c r="A24" s="671">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B24" s="582" t="n"/>
-      <c r="C24" s="583" t="n"/>
-      <c r="D24" s="583" t="n"/>
-      <c r="E24" s="583" t="n"/>
-      <c r="F24" s="583" t="n"/>
-      <c r="G24" s="583" t="n"/>
-      <c r="H24" s="583" t="n"/>
-      <c r="I24" s="583" t="n"/>
-      <c r="J24" s="583" t="n"/>
-      <c r="K24" s="446" t="n"/>
-      <c r="L24" s="446" t="n"/>
-      <c r="M24" s="446" t="n"/>
-      <c r="N24" s="446" t="n"/>
-      <c r="O24" s="446" t="n"/>
-      <c r="P24" s="446" t="n"/>
-      <c r="Q24" s="446" t="n"/>
-      <c r="R24" s="446" t="n"/>
-      <c r="S24" s="446" t="n"/>
-      <c r="T24" s="446" t="n"/>
-      <c r="U24" s="446" t="n"/>
-      <c r="V24" s="446" t="n"/>
-      <c r="W24" s="446" t="n"/>
-      <c r="X24" s="446" t="n"/>
-      <c r="Y24" s="446" t="n"/>
-      <c r="Z24" s="446" t="n"/>
-      <c r="AA24" s="446" t="n"/>
-      <c r="AB24" s="446" t="n"/>
-      <c r="AC24" s="446" t="n"/>
-      <c r="AD24" s="446" t="n"/>
-      <c r="AE24" s="446" t="n"/>
-      <c r="AF24" s="446" t="n"/>
-      <c r="AG24" s="446" t="n"/>
-      <c r="AH24" s="446" t="n"/>
-      <c r="AI24" s="446" t="n"/>
-      <c r="AJ24" s="446" t="n"/>
-      <c r="AK24" s="446" t="n"/>
-      <c r="AL24" s="446" t="n"/>
-      <c r="AM24" s="446" t="n"/>
-      <c r="AN24" s="562" t="n"/>
+      <c r="B24" s="674" t="n"/>
+      <c r="C24" s="653" t="n"/>
+      <c r="D24" s="653" t="n"/>
+      <c r="E24" s="653" t="n"/>
+      <c r="F24" s="653" t="n"/>
+      <c r="G24" s="653" t="n"/>
+      <c r="H24" s="653" t="n"/>
+      <c r="I24" s="653" t="n"/>
+      <c r="J24" s="653" t="n"/>
+      <c r="K24" s="655" t="n"/>
+      <c r="L24" s="655" t="n"/>
+      <c r="M24" s="655" t="n"/>
+      <c r="N24" s="655" t="n"/>
+      <c r="O24" s="655" t="n"/>
+      <c r="P24" s="655" t="n"/>
+      <c r="Q24" s="655" t="n"/>
+      <c r="R24" s="655" t="n"/>
+      <c r="S24" s="655" t="n"/>
+      <c r="T24" s="655" t="n"/>
+      <c r="U24" s="655" t="n"/>
+      <c r="V24" s="655" t="n"/>
+      <c r="W24" s="655" t="n"/>
+      <c r="X24" s="655" t="n"/>
+      <c r="Y24" s="655" t="n"/>
+      <c r="Z24" s="655" t="n"/>
+      <c r="AA24" s="655" t="n"/>
+      <c r="AB24" s="655" t="n"/>
+      <c r="AC24" s="655" t="n"/>
+      <c r="AD24" s="655" t="n"/>
+      <c r="AE24" s="655" t="n"/>
+      <c r="AF24" s="655" t="n"/>
+      <c r="AG24" s="655" t="n"/>
+      <c r="AH24" s="655" t="n"/>
+      <c r="AI24" s="655" t="n"/>
+      <c r="AJ24" s="655" t="n"/>
+      <c r="AK24" s="655" t="n"/>
+      <c r="AL24" s="655" t="n"/>
+      <c r="AM24" s="655" t="n"/>
+      <c r="AN24" s="656" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="580">
+      <c r="A25" s="671">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B25" s="457" t="n"/>
-      <c r="C25" s="581" t="n"/>
-      <c r="D25" s="581" t="n"/>
-      <c r="E25" s="581" t="n"/>
-      <c r="F25" s="581" t="n"/>
-      <c r="G25" s="581" t="n"/>
-      <c r="H25" s="581" t="n"/>
-      <c r="I25" s="581" t="n"/>
-      <c r="J25" s="581" t="n"/>
-      <c r="K25" s="446" t="n"/>
-      <c r="L25" s="446" t="n"/>
-      <c r="M25" s="446" t="n"/>
-      <c r="N25" s="446" t="n"/>
-      <c r="O25" s="446" t="n"/>
-      <c r="P25" s="446" t="n"/>
-      <c r="Q25" s="446" t="n"/>
-      <c r="R25" s="446" t="n"/>
-      <c r="S25" s="446" t="n"/>
-      <c r="T25" s="446" t="n"/>
-      <c r="U25" s="446" t="n"/>
-      <c r="V25" s="446" t="n"/>
-      <c r="W25" s="446" t="n"/>
-      <c r="X25" s="446" t="n"/>
-      <c r="Y25" s="446" t="n"/>
-      <c r="Z25" s="446" t="n"/>
-      <c r="AA25" s="446" t="n"/>
-      <c r="AB25" s="446" t="n"/>
-      <c r="AC25" s="446" t="n"/>
-      <c r="AD25" s="446" t="n"/>
-      <c r="AE25" s="446" t="n"/>
-      <c r="AF25" s="446" t="n"/>
-      <c r="AG25" s="446" t="n"/>
-      <c r="AH25" s="446" t="n"/>
-      <c r="AI25" s="446" t="n"/>
-      <c r="AJ25" s="446" t="n"/>
-      <c r="AK25" s="446" t="n"/>
-      <c r="AL25" s="446" t="n"/>
-      <c r="AM25" s="446" t="n"/>
-      <c r="AN25" s="562" t="n"/>
+      <c r="B25" s="672" t="n"/>
+      <c r="C25" s="673" t="n"/>
+      <c r="D25" s="673" t="n"/>
+      <c r="E25" s="673" t="n"/>
+      <c r="F25" s="673" t="n"/>
+      <c r="G25" s="673" t="n"/>
+      <c r="H25" s="673" t="n"/>
+      <c r="I25" s="673" t="n"/>
+      <c r="J25" s="673" t="n"/>
+      <c r="K25" s="655" t="n"/>
+      <c r="L25" s="655" t="n"/>
+      <c r="M25" s="655" t="n"/>
+      <c r="N25" s="655" t="n"/>
+      <c r="O25" s="655" t="n"/>
+      <c r="P25" s="655" t="n"/>
+      <c r="Q25" s="655" t="n"/>
+      <c r="R25" s="655" t="n"/>
+      <c r="S25" s="655" t="n"/>
+      <c r="T25" s="655" t="n"/>
+      <c r="U25" s="655" t="n"/>
+      <c r="V25" s="655" t="n"/>
+      <c r="W25" s="655" t="n"/>
+      <c r="X25" s="655" t="n"/>
+      <c r="Y25" s="655" t="n"/>
+      <c r="Z25" s="655" t="n"/>
+      <c r="AA25" s="655" t="n"/>
+      <c r="AB25" s="655" t="n"/>
+      <c r="AC25" s="655" t="n"/>
+      <c r="AD25" s="655" t="n"/>
+      <c r="AE25" s="655" t="n"/>
+      <c r="AF25" s="655" t="n"/>
+      <c r="AG25" s="655" t="n"/>
+      <c r="AH25" s="655" t="n"/>
+      <c r="AI25" s="655" t="n"/>
+      <c r="AJ25" s="655" t="n"/>
+      <c r="AK25" s="655" t="n"/>
+      <c r="AL25" s="655" t="n"/>
+      <c r="AM25" s="655" t="n"/>
+      <c r="AN25" s="656" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="580">
+      <c r="A26" s="671">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B26" s="582" t="n"/>
-      <c r="C26" s="583" t="n"/>
-      <c r="D26" s="583" t="n"/>
-      <c r="E26" s="583" t="n"/>
-      <c r="F26" s="583" t="n"/>
-      <c r="G26" s="583" t="n"/>
-      <c r="H26" s="583" t="n"/>
-      <c r="I26" s="583" t="n"/>
-      <c r="J26" s="583" t="n"/>
-      <c r="K26" s="446" t="n"/>
-      <c r="L26" s="446" t="n"/>
-      <c r="M26" s="446" t="n"/>
-      <c r="N26" s="446" t="n"/>
-      <c r="O26" s="446" t="n"/>
-      <c r="P26" s="446" t="n"/>
-      <c r="Q26" s="446" t="n"/>
-      <c r="R26" s="446" t="n"/>
-      <c r="S26" s="446" t="n"/>
-      <c r="T26" s="446" t="n"/>
-      <c r="U26" s="446" t="n"/>
-      <c r="V26" s="446" t="n"/>
-      <c r="W26" s="446" t="n"/>
-      <c r="X26" s="446" t="n"/>
-      <c r="Y26" s="446" t="n"/>
-      <c r="Z26" s="446" t="n"/>
-      <c r="AA26" s="446" t="n"/>
-      <c r="AB26" s="446" t="n"/>
-      <c r="AC26" s="446" t="n"/>
-      <c r="AD26" s="446" t="n"/>
-      <c r="AE26" s="446" t="n"/>
-      <c r="AF26" s="446" t="n"/>
-      <c r="AG26" s="446" t="n"/>
-      <c r="AH26" s="446" t="n"/>
-      <c r="AI26" s="446" t="n"/>
-      <c r="AJ26" s="446" t="n"/>
-      <c r="AK26" s="446" t="n"/>
-      <c r="AL26" s="446" t="n"/>
-      <c r="AM26" s="446" t="n"/>
-      <c r="AN26" s="562" t="n"/>
+      <c r="B26" s="674" t="n"/>
+      <c r="C26" s="653" t="n"/>
+      <c r="D26" s="653" t="n"/>
+      <c r="E26" s="653" t="n"/>
+      <c r="F26" s="653" t="n"/>
+      <c r="G26" s="653" t="n"/>
+      <c r="H26" s="653" t="n"/>
+      <c r="I26" s="653" t="n"/>
+      <c r="J26" s="653" t="n"/>
+      <c r="K26" s="655" t="n"/>
+      <c r="L26" s="655" t="n"/>
+      <c r="M26" s="655" t="n"/>
+      <c r="N26" s="655" t="n"/>
+      <c r="O26" s="655" t="n"/>
+      <c r="P26" s="655" t="n"/>
+      <c r="Q26" s="655" t="n"/>
+      <c r="R26" s="655" t="n"/>
+      <c r="S26" s="655" t="n"/>
+      <c r="T26" s="655" t="n"/>
+      <c r="U26" s="655" t="n"/>
+      <c r="V26" s="655" t="n"/>
+      <c r="W26" s="655" t="n"/>
+      <c r="X26" s="655" t="n"/>
+      <c r="Y26" s="655" t="n"/>
+      <c r="Z26" s="655" t="n"/>
+      <c r="AA26" s="655" t="n"/>
+      <c r="AB26" s="655" t="n"/>
+      <c r="AC26" s="655" t="n"/>
+      <c r="AD26" s="655" t="n"/>
+      <c r="AE26" s="655" t="n"/>
+      <c r="AF26" s="655" t="n"/>
+      <c r="AG26" s="655" t="n"/>
+      <c r="AH26" s="655" t="n"/>
+      <c r="AI26" s="655" t="n"/>
+      <c r="AJ26" s="655" t="n"/>
+      <c r="AK26" s="655" t="n"/>
+      <c r="AL26" s="655" t="n"/>
+      <c r="AM26" s="655" t="n"/>
+      <c r="AN26" s="656" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="580">
+      <c r="A27" s="671">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B27" s="457" t="n"/>
-      <c r="C27" s="581" t="n"/>
-      <c r="D27" s="581" t="n"/>
-      <c r="E27" s="581" t="n"/>
-      <c r="F27" s="581" t="n"/>
-      <c r="G27" s="581" t="n"/>
-      <c r="H27" s="581" t="n"/>
-      <c r="I27" s="581" t="n"/>
-      <c r="J27" s="581" t="n"/>
-      <c r="K27" s="446" t="n"/>
-      <c r="L27" s="446" t="n"/>
-      <c r="M27" s="446" t="n"/>
-      <c r="N27" s="446" t="n"/>
-      <c r="O27" s="446" t="n"/>
-      <c r="P27" s="446" t="n"/>
-      <c r="Q27" s="446" t="n"/>
-      <c r="R27" s="446" t="n"/>
-      <c r="S27" s="446" t="n"/>
-      <c r="T27" s="446" t="n"/>
-      <c r="U27" s="446" t="n"/>
-      <c r="V27" s="446" t="n"/>
-      <c r="W27" s="446" t="n"/>
-      <c r="X27" s="446" t="n"/>
-      <c r="Y27" s="446" t="n"/>
-      <c r="Z27" s="446" t="n"/>
-      <c r="AA27" s="446" t="n"/>
-      <c r="AB27" s="446" t="n"/>
-      <c r="AC27" s="446" t="n"/>
-      <c r="AD27" s="446" t="n"/>
-      <c r="AE27" s="446" t="n"/>
-      <c r="AF27" s="446" t="n"/>
-      <c r="AG27" s="446" t="n"/>
-      <c r="AH27" s="446" t="n"/>
-      <c r="AI27" s="446" t="n"/>
-      <c r="AJ27" s="446" t="n"/>
-      <c r="AK27" s="446" t="n"/>
-      <c r="AL27" s="446" t="n"/>
-      <c r="AM27" s="446" t="n"/>
-      <c r="AN27" s="562" t="n"/>
+      <c r="B27" s="672" t="n"/>
+      <c r="C27" s="673" t="n"/>
+      <c r="D27" s="673" t="n"/>
+      <c r="E27" s="673" t="n"/>
+      <c r="F27" s="673" t="n"/>
+      <c r="G27" s="673" t="n"/>
+      <c r="H27" s="673" t="n"/>
+      <c r="I27" s="673" t="n"/>
+      <c r="J27" s="673" t="n"/>
+      <c r="K27" s="655" t="n"/>
+      <c r="L27" s="655" t="n"/>
+      <c r="M27" s="655" t="n"/>
+      <c r="N27" s="655" t="n"/>
+      <c r="O27" s="655" t="n"/>
+      <c r="P27" s="655" t="n"/>
+      <c r="Q27" s="655" t="n"/>
+      <c r="R27" s="655" t="n"/>
+      <c r="S27" s="655" t="n"/>
+      <c r="T27" s="655" t="n"/>
+      <c r="U27" s="655" t="n"/>
+      <c r="V27" s="655" t="n"/>
+      <c r="W27" s="655" t="n"/>
+      <c r="X27" s="655" t="n"/>
+      <c r="Y27" s="655" t="n"/>
+      <c r="Z27" s="655" t="n"/>
+      <c r="AA27" s="655" t="n"/>
+      <c r="AB27" s="655" t="n"/>
+      <c r="AC27" s="655" t="n"/>
+      <c r="AD27" s="655" t="n"/>
+      <c r="AE27" s="655" t="n"/>
+      <c r="AF27" s="655" t="n"/>
+      <c r="AG27" s="655" t="n"/>
+      <c r="AH27" s="655" t="n"/>
+      <c r="AI27" s="655" t="n"/>
+      <c r="AJ27" s="655" t="n"/>
+      <c r="AK27" s="655" t="n"/>
+      <c r="AL27" s="655" t="n"/>
+      <c r="AM27" s="655" t="n"/>
+      <c r="AN27" s="656" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="580">
+      <c r="A28" s="671">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B28" s="582" t="n"/>
-      <c r="C28" s="583" t="n"/>
-      <c r="D28" s="583" t="n"/>
-      <c r="E28" s="583" t="n"/>
-      <c r="F28" s="583" t="n"/>
-      <c r="G28" s="583" t="n"/>
-      <c r="H28" s="583" t="n"/>
-      <c r="I28" s="583" t="n"/>
-      <c r="J28" s="583" t="n"/>
-      <c r="K28" s="446" t="n"/>
-      <c r="L28" s="446" t="n"/>
-      <c r="M28" s="446" t="n"/>
-      <c r="N28" s="446" t="n"/>
-      <c r="O28" s="446" t="n"/>
-      <c r="P28" s="446" t="n"/>
-      <c r="Q28" s="446" t="n"/>
-      <c r="R28" s="446" t="n"/>
-      <c r="S28" s="446" t="n"/>
-      <c r="T28" s="446" t="n"/>
-      <c r="U28" s="446" t="n"/>
-      <c r="V28" s="446" t="n"/>
-      <c r="W28" s="446" t="n"/>
-      <c r="X28" s="446" t="n"/>
-      <c r="Y28" s="446" t="n"/>
-      <c r="Z28" s="446" t="n"/>
-      <c r="AA28" s="446" t="n"/>
-      <c r="AB28" s="446" t="n"/>
-      <c r="AC28" s="446" t="n"/>
-      <c r="AD28" s="446" t="n"/>
-      <c r="AE28" s="446" t="n"/>
-      <c r="AF28" s="446" t="n"/>
-      <c r="AG28" s="446" t="n"/>
-      <c r="AH28" s="446" t="n"/>
-      <c r="AI28" s="446" t="n"/>
-      <c r="AJ28" s="446" t="n"/>
-      <c r="AK28" s="446" t="n"/>
-      <c r="AL28" s="446" t="n"/>
-      <c r="AM28" s="446" t="n"/>
-      <c r="AN28" s="562" t="n"/>
+      <c r="B28" s="674" t="n"/>
+      <c r="C28" s="653" t="n"/>
+      <c r="D28" s="653" t="n"/>
+      <c r="E28" s="653" t="n"/>
+      <c r="F28" s="653" t="n"/>
+      <c r="G28" s="653" t="n"/>
+      <c r="H28" s="653" t="n"/>
+      <c r="I28" s="653" t="n"/>
+      <c r="J28" s="653" t="n"/>
+      <c r="K28" s="655" t="n"/>
+      <c r="L28" s="655" t="n"/>
+      <c r="M28" s="655" t="n"/>
+      <c r="N28" s="655" t="n"/>
+      <c r="O28" s="655" t="n"/>
+      <c r="P28" s="655" t="n"/>
+      <c r="Q28" s="655" t="n"/>
+      <c r="R28" s="655" t="n"/>
+      <c r="S28" s="655" t="n"/>
+      <c r="T28" s="655" t="n"/>
+      <c r="U28" s="655" t="n"/>
+      <c r="V28" s="655" t="n"/>
+      <c r="W28" s="655" t="n"/>
+      <c r="X28" s="655" t="n"/>
+      <c r="Y28" s="655" t="n"/>
+      <c r="Z28" s="655" t="n"/>
+      <c r="AA28" s="655" t="n"/>
+      <c r="AB28" s="655" t="n"/>
+      <c r="AC28" s="655" t="n"/>
+      <c r="AD28" s="655" t="n"/>
+      <c r="AE28" s="655" t="n"/>
+      <c r="AF28" s="655" t="n"/>
+      <c r="AG28" s="655" t="n"/>
+      <c r="AH28" s="655" t="n"/>
+      <c r="AI28" s="655" t="n"/>
+      <c r="AJ28" s="655" t="n"/>
+      <c r="AK28" s="655" t="n"/>
+      <c r="AL28" s="655" t="n"/>
+      <c r="AM28" s="655" t="n"/>
+      <c r="AN28" s="656" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="580">
+      <c r="A29" s="671">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B29" s="457" t="n"/>
-      <c r="C29" s="581" t="n"/>
-      <c r="D29" s="581" t="n"/>
-      <c r="E29" s="581" t="n"/>
-      <c r="F29" s="581" t="n"/>
-      <c r="G29" s="581" t="n"/>
-      <c r="H29" s="581" t="n"/>
-      <c r="I29" s="581" t="n"/>
-      <c r="J29" s="581" t="n"/>
-      <c r="K29" s="446" t="n"/>
-      <c r="L29" s="446" t="n"/>
-      <c r="M29" s="446" t="n"/>
-      <c r="N29" s="446" t="n"/>
-      <c r="O29" s="446" t="n"/>
-      <c r="P29" s="446" t="n"/>
-      <c r="Q29" s="446" t="n"/>
-      <c r="R29" s="446" t="n"/>
-      <c r="S29" s="446" t="n"/>
-      <c r="T29" s="446" t="n"/>
-      <c r="U29" s="446" t="n"/>
-      <c r="V29" s="446" t="n"/>
-      <c r="W29" s="446" t="n"/>
-      <c r="X29" s="446" t="n"/>
-      <c r="Y29" s="446" t="n"/>
-      <c r="Z29" s="446" t="n"/>
-      <c r="AA29" s="446" t="n"/>
-      <c r="AB29" s="446" t="n"/>
-      <c r="AC29" s="446" t="n"/>
-      <c r="AD29" s="446" t="n"/>
-      <c r="AE29" s="446" t="n"/>
-      <c r="AF29" s="446" t="n"/>
-      <c r="AG29" s="446" t="n"/>
-      <c r="AH29" s="446" t="n"/>
-      <c r="AI29" s="446" t="n"/>
-      <c r="AJ29" s="446" t="n"/>
-      <c r="AK29" s="446" t="n"/>
-      <c r="AL29" s="446" t="n"/>
-      <c r="AM29" s="446" t="n"/>
-      <c r="AN29" s="562" t="n"/>
+      <c r="B29" s="672" t="n"/>
+      <c r="C29" s="673" t="n"/>
+      <c r="D29" s="673" t="n"/>
+      <c r="E29" s="673" t="n"/>
+      <c r="F29" s="673" t="n"/>
+      <c r="G29" s="673" t="n"/>
+      <c r="H29" s="673" t="n"/>
+      <c r="I29" s="673" t="n"/>
+      <c r="J29" s="673" t="n"/>
+      <c r="K29" s="655" t="n"/>
+      <c r="L29" s="655" t="n"/>
+      <c r="M29" s="655" t="n"/>
+      <c r="N29" s="655" t="n"/>
+      <c r="O29" s="655" t="n"/>
+      <c r="P29" s="655" t="n"/>
+      <c r="Q29" s="655" t="n"/>
+      <c r="R29" s="655" t="n"/>
+      <c r="S29" s="655" t="n"/>
+      <c r="T29" s="655" t="n"/>
+      <c r="U29" s="655" t="n"/>
+      <c r="V29" s="655" t="n"/>
+      <c r="W29" s="655" t="n"/>
+      <c r="X29" s="655" t="n"/>
+      <c r="Y29" s="655" t="n"/>
+      <c r="Z29" s="655" t="n"/>
+      <c r="AA29" s="655" t="n"/>
+      <c r="AB29" s="655" t="n"/>
+      <c r="AC29" s="655" t="n"/>
+      <c r="AD29" s="655" t="n"/>
+      <c r="AE29" s="655" t="n"/>
+      <c r="AF29" s="655" t="n"/>
+      <c r="AG29" s="655" t="n"/>
+      <c r="AH29" s="655" t="n"/>
+      <c r="AI29" s="655" t="n"/>
+      <c r="AJ29" s="655" t="n"/>
+      <c r="AK29" s="655" t="n"/>
+      <c r="AL29" s="655" t="n"/>
+      <c r="AM29" s="655" t="n"/>
+      <c r="AN29" s="656" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="580">
+      <c r="A30" s="671">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B30" s="582" t="n"/>
-      <c r="C30" s="583" t="n"/>
-      <c r="D30" s="583" t="n"/>
-      <c r="E30" s="583" t="n"/>
-      <c r="F30" s="583" t="n"/>
-      <c r="G30" s="583" t="n"/>
-      <c r="H30" s="583" t="n"/>
-      <c r="I30" s="583" t="n"/>
-      <c r="J30" s="583" t="n"/>
-      <c r="K30" s="446" t="n"/>
-      <c r="L30" s="446" t="n"/>
-      <c r="M30" s="446" t="n"/>
-      <c r="N30" s="446" t="n"/>
-      <c r="O30" s="446" t="n"/>
-      <c r="P30" s="446" t="n"/>
-      <c r="Q30" s="446" t="n"/>
-      <c r="R30" s="446" t="n"/>
-      <c r="S30" s="446" t="n"/>
-      <c r="T30" s="446" t="n"/>
-      <c r="U30" s="446" t="n"/>
-      <c r="V30" s="446" t="n"/>
-      <c r="W30" s="446" t="n"/>
-      <c r="X30" s="446" t="n"/>
-      <c r="Y30" s="446" t="n"/>
-      <c r="Z30" s="446" t="n"/>
-      <c r="AA30" s="446" t="n"/>
-      <c r="AB30" s="446" t="n"/>
-      <c r="AC30" s="446" t="n"/>
-      <c r="AD30" s="446" t="n"/>
-      <c r="AE30" s="446" t="n"/>
-      <c r="AF30" s="446" t="n"/>
-      <c r="AG30" s="446" t="n"/>
-      <c r="AH30" s="446" t="n"/>
-      <c r="AI30" s="446" t="n"/>
-      <c r="AJ30" s="446" t="n"/>
-      <c r="AK30" s="446" t="n"/>
-      <c r="AL30" s="446" t="n"/>
-      <c r="AM30" s="446" t="n"/>
-      <c r="AN30" s="562" t="n"/>
+      <c r="B30" s="674" t="n"/>
+      <c r="C30" s="653" t="n"/>
+      <c r="D30" s="653" t="n"/>
+      <c r="E30" s="653" t="n"/>
+      <c r="F30" s="653" t="n"/>
+      <c r="G30" s="653" t="n"/>
+      <c r="H30" s="653" t="n"/>
+      <c r="I30" s="653" t="n"/>
+      <c r="J30" s="653" t="n"/>
+      <c r="K30" s="655" t="n"/>
+      <c r="L30" s="655" t="n"/>
+      <c r="M30" s="655" t="n"/>
+      <c r="N30" s="655" t="n"/>
+      <c r="O30" s="655" t="n"/>
+      <c r="P30" s="655" t="n"/>
+      <c r="Q30" s="655" t="n"/>
+      <c r="R30" s="655" t="n"/>
+      <c r="S30" s="655" t="n"/>
+      <c r="T30" s="655" t="n"/>
+      <c r="U30" s="655" t="n"/>
+      <c r="V30" s="655" t="n"/>
+      <c r="W30" s="655" t="n"/>
+      <c r="X30" s="655" t="n"/>
+      <c r="Y30" s="655" t="n"/>
+      <c r="Z30" s="655" t="n"/>
+      <c r="AA30" s="655" t="n"/>
+      <c r="AB30" s="655" t="n"/>
+      <c r="AC30" s="655" t="n"/>
+      <c r="AD30" s="655" t="n"/>
+      <c r="AE30" s="655" t="n"/>
+      <c r="AF30" s="655" t="n"/>
+      <c r="AG30" s="655" t="n"/>
+      <c r="AH30" s="655" t="n"/>
+      <c r="AI30" s="655" t="n"/>
+      <c r="AJ30" s="655" t="n"/>
+      <c r="AK30" s="655" t="n"/>
+      <c r="AL30" s="655" t="n"/>
+      <c r="AM30" s="655" t="n"/>
+      <c r="AN30" s="656" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="580">
+      <c r="A31" s="671">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B31" s="457" t="n"/>
-      <c r="C31" s="581" t="n"/>
-      <c r="D31" s="581" t="n"/>
-      <c r="E31" s="581" t="n"/>
-      <c r="F31" s="581" t="n"/>
-      <c r="G31" s="581" t="n"/>
-      <c r="H31" s="581" t="n"/>
-      <c r="I31" s="581" t="n"/>
-      <c r="J31" s="581" t="n"/>
-      <c r="K31" s="446" t="n"/>
-      <c r="L31" s="446" t="n"/>
-      <c r="M31" s="446" t="n"/>
-      <c r="N31" s="446" t="n"/>
-      <c r="O31" s="446" t="n"/>
-      <c r="P31" s="446" t="n"/>
-      <c r="Q31" s="446" t="n"/>
-      <c r="R31" s="446" t="n"/>
-      <c r="S31" s="446" t="n"/>
-      <c r="T31" s="446" t="n"/>
-      <c r="U31" s="446" t="n"/>
-      <c r="V31" s="446" t="n"/>
-      <c r="W31" s="446" t="n"/>
-      <c r="X31" s="446" t="n"/>
-      <c r="Y31" s="446" t="n"/>
-      <c r="Z31" s="446" t="n"/>
-      <c r="AA31" s="446" t="n"/>
-      <c r="AB31" s="446" t="n"/>
-      <c r="AC31" s="446" t="n"/>
-      <c r="AD31" s="446" t="n"/>
-      <c r="AE31" s="446" t="n"/>
-      <c r="AF31" s="446" t="n"/>
-      <c r="AG31" s="446" t="n"/>
-      <c r="AH31" s="446" t="n"/>
-      <c r="AI31" s="446" t="n"/>
-      <c r="AJ31" s="446" t="n"/>
-      <c r="AK31" s="446" t="n"/>
-      <c r="AL31" s="446" t="n"/>
-      <c r="AM31" s="446" t="n"/>
-      <c r="AN31" s="562" t="n"/>
+      <c r="B31" s="672" t="n"/>
+      <c r="C31" s="673" t="n"/>
+      <c r="D31" s="673" t="n"/>
+      <c r="E31" s="673" t="n"/>
+      <c r="F31" s="673" t="n"/>
+      <c r="G31" s="673" t="n"/>
+      <c r="H31" s="673" t="n"/>
+      <c r="I31" s="673" t="n"/>
+      <c r="J31" s="673" t="n"/>
+      <c r="K31" s="655" t="n"/>
+      <c r="L31" s="655" t="n"/>
+      <c r="M31" s="655" t="n"/>
+      <c r="N31" s="655" t="n"/>
+      <c r="O31" s="655" t="n"/>
+      <c r="P31" s="655" t="n"/>
+      <c r="Q31" s="655" t="n"/>
+      <c r="R31" s="655" t="n"/>
+      <c r="S31" s="655" t="n"/>
+      <c r="T31" s="655" t="n"/>
+      <c r="U31" s="655" t="n"/>
+      <c r="V31" s="655" t="n"/>
+      <c r="W31" s="655" t="n"/>
+      <c r="X31" s="655" t="n"/>
+      <c r="Y31" s="655" t="n"/>
+      <c r="Z31" s="655" t="n"/>
+      <c r="AA31" s="655" t="n"/>
+      <c r="AB31" s="655" t="n"/>
+      <c r="AC31" s="655" t="n"/>
+      <c r="AD31" s="655" t="n"/>
+      <c r="AE31" s="655" t="n"/>
+      <c r="AF31" s="655" t="n"/>
+      <c r="AG31" s="655" t="n"/>
+      <c r="AH31" s="655" t="n"/>
+      <c r="AI31" s="655" t="n"/>
+      <c r="AJ31" s="655" t="n"/>
+      <c r="AK31" s="655" t="n"/>
+      <c r="AL31" s="655" t="n"/>
+      <c r="AM31" s="655" t="n"/>
+      <c r="AN31" s="656" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="580">
+      <c r="A32" s="671">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B32" s="582" t="n"/>
-      <c r="C32" s="583" t="n"/>
-      <c r="D32" s="583" t="n"/>
-      <c r="E32" s="583" t="n"/>
-      <c r="F32" s="583" t="n"/>
-      <c r="G32" s="583" t="n"/>
-      <c r="H32" s="583" t="n"/>
-      <c r="I32" s="583" t="n"/>
-      <c r="J32" s="583" t="n"/>
-      <c r="K32" s="446" t="n"/>
-      <c r="L32" s="446" t="n"/>
-      <c r="M32" s="446" t="n"/>
-      <c r="N32" s="446" t="n"/>
-      <c r="O32" s="446" t="n"/>
-      <c r="P32" s="446" t="n"/>
-      <c r="Q32" s="446" t="n"/>
-      <c r="R32" s="446" t="n"/>
-      <c r="S32" s="446" t="n"/>
-      <c r="T32" s="446" t="n"/>
-      <c r="U32" s="446" t="n"/>
-      <c r="V32" s="446" t="n"/>
-      <c r="W32" s="446" t="n"/>
-      <c r="X32" s="446" t="n"/>
-      <c r="Y32" s="446" t="n"/>
-      <c r="Z32" s="446" t="n"/>
-      <c r="AA32" s="446" t="n"/>
-      <c r="AB32" s="446" t="n"/>
-      <c r="AC32" s="446" t="n"/>
-      <c r="AD32" s="446" t="n"/>
-      <c r="AE32" s="446" t="n"/>
-      <c r="AF32" s="446" t="n"/>
-      <c r="AG32" s="446" t="n"/>
-      <c r="AH32" s="446" t="n"/>
-      <c r="AI32" s="446" t="n"/>
-      <c r="AJ32" s="446" t="n"/>
-      <c r="AK32" s="446" t="n"/>
-      <c r="AL32" s="446" t="n"/>
-      <c r="AM32" s="446" t="n"/>
-      <c r="AN32" s="562" t="n"/>
+      <c r="B32" s="674" t="n"/>
+      <c r="C32" s="653" t="n"/>
+      <c r="D32" s="653" t="n"/>
+      <c r="E32" s="653" t="n"/>
+      <c r="F32" s="653" t="n"/>
+      <c r="G32" s="653" t="n"/>
+      <c r="H32" s="653" t="n"/>
+      <c r="I32" s="653" t="n"/>
+      <c r="J32" s="653" t="n"/>
+      <c r="K32" s="655" t="n"/>
+      <c r="L32" s="655" t="n"/>
+      <c r="M32" s="655" t="n"/>
+      <c r="N32" s="655" t="n"/>
+      <c r="O32" s="655" t="n"/>
+      <c r="P32" s="655" t="n"/>
+      <c r="Q32" s="655" t="n"/>
+      <c r="R32" s="655" t="n"/>
+      <c r="S32" s="655" t="n"/>
+      <c r="T32" s="655" t="n"/>
+      <c r="U32" s="655" t="n"/>
+      <c r="V32" s="655" t="n"/>
+      <c r="W32" s="655" t="n"/>
+      <c r="X32" s="655" t="n"/>
+      <c r="Y32" s="655" t="n"/>
+      <c r="Z32" s="655" t="n"/>
+      <c r="AA32" s="655" t="n"/>
+      <c r="AB32" s="655" t="n"/>
+      <c r="AC32" s="655" t="n"/>
+      <c r="AD32" s="655" t="n"/>
+      <c r="AE32" s="655" t="n"/>
+      <c r="AF32" s="655" t="n"/>
+      <c r="AG32" s="655" t="n"/>
+      <c r="AH32" s="655" t="n"/>
+      <c r="AI32" s="655" t="n"/>
+      <c r="AJ32" s="655" t="n"/>
+      <c r="AK32" s="655" t="n"/>
+      <c r="AL32" s="655" t="n"/>
+      <c r="AM32" s="655" t="n"/>
+      <c r="AN32" s="656" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="580">
+      <c r="A33" s="671">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B33" s="457" t="n"/>
-      <c r="C33" s="581" t="n"/>
-      <c r="D33" s="581" t="n"/>
-      <c r="E33" s="581" t="n"/>
-      <c r="F33" s="581" t="n"/>
-      <c r="G33" s="581" t="n"/>
-      <c r="H33" s="581" t="n"/>
-      <c r="I33" s="581" t="n"/>
-      <c r="J33" s="581" t="n"/>
-      <c r="K33" s="446" t="n"/>
-      <c r="L33" s="446" t="n"/>
-      <c r="M33" s="446" t="n"/>
-      <c r="N33" s="446" t="n"/>
-      <c r="O33" s="446" t="n"/>
-      <c r="P33" s="446" t="n"/>
-      <c r="Q33" s="446" t="n"/>
-      <c r="R33" s="446" t="n"/>
-      <c r="S33" s="446" t="n"/>
-      <c r="T33" s="446" t="n"/>
-      <c r="U33" s="446" t="n"/>
-      <c r="V33" s="446" t="n"/>
-      <c r="W33" s="446" t="n"/>
-      <c r="X33" s="446" t="n"/>
-      <c r="Y33" s="446" t="n"/>
-      <c r="Z33" s="446" t="n"/>
-      <c r="AA33" s="446" t="n"/>
-      <c r="AB33" s="446" t="n"/>
-      <c r="AC33" s="446" t="n"/>
-      <c r="AD33" s="446" t="n"/>
-      <c r="AE33" s="446" t="n"/>
-      <c r="AF33" s="446" t="n"/>
-      <c r="AG33" s="446" t="n"/>
-      <c r="AH33" s="446" t="n"/>
-      <c r="AI33" s="446" t="n"/>
-      <c r="AJ33" s="446" t="n"/>
-      <c r="AK33" s="446" t="n"/>
-      <c r="AL33" s="446" t="n"/>
-      <c r="AM33" s="446" t="n"/>
-      <c r="AN33" s="562" t="n"/>
+      <c r="B33" s="672" t="n"/>
+      <c r="C33" s="673" t="n"/>
+      <c r="D33" s="673" t="n"/>
+      <c r="E33" s="673" t="n"/>
+      <c r="F33" s="673" t="n"/>
+      <c r="G33" s="673" t="n"/>
+      <c r="H33" s="673" t="n"/>
+      <c r="I33" s="673" t="n"/>
+      <c r="J33" s="673" t="n"/>
+      <c r="K33" s="655" t="n"/>
+      <c r="L33" s="655" t="n"/>
+      <c r="M33" s="655" t="n"/>
+      <c r="N33" s="655" t="n"/>
+      <c r="O33" s="655" t="n"/>
+      <c r="P33" s="655" t="n"/>
+      <c r="Q33" s="655" t="n"/>
+      <c r="R33" s="655" t="n"/>
+      <c r="S33" s="655" t="n"/>
+      <c r="T33" s="655" t="n"/>
+      <c r="U33" s="655" t="n"/>
+      <c r="V33" s="655" t="n"/>
+      <c r="W33" s="655" t="n"/>
+      <c r="X33" s="655" t="n"/>
+      <c r="Y33" s="655" t="n"/>
+      <c r="Z33" s="655" t="n"/>
+      <c r="AA33" s="655" t="n"/>
+      <c r="AB33" s="655" t="n"/>
+      <c r="AC33" s="655" t="n"/>
+      <c r="AD33" s="655" t="n"/>
+      <c r="AE33" s="655" t="n"/>
+      <c r="AF33" s="655" t="n"/>
+      <c r="AG33" s="655" t="n"/>
+      <c r="AH33" s="655" t="n"/>
+      <c r="AI33" s="655" t="n"/>
+      <c r="AJ33" s="655" t="n"/>
+      <c r="AK33" s="655" t="n"/>
+      <c r="AL33" s="655" t="n"/>
+      <c r="AM33" s="655" t="n"/>
+      <c r="AN33" s="656" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="580">
+      <c r="A34" s="671">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B34" s="582" t="n"/>
-      <c r="C34" s="583" t="n"/>
-      <c r="D34" s="583" t="n"/>
-      <c r="E34" s="583" t="n"/>
-      <c r="F34" s="583" t="n"/>
-      <c r="G34" s="583" t="n"/>
-      <c r="H34" s="583" t="n"/>
-      <c r="I34" s="583" t="n"/>
-      <c r="J34" s="583" t="n"/>
-      <c r="K34" s="446" t="n"/>
-      <c r="L34" s="446" t="n"/>
-      <c r="M34" s="446" t="n"/>
-      <c r="N34" s="446" t="n"/>
-      <c r="O34" s="446" t="n"/>
-      <c r="P34" s="446" t="n"/>
-      <c r="Q34" s="446" t="n"/>
-      <c r="R34" s="446" t="n"/>
-      <c r="S34" s="446" t="n"/>
-      <c r="T34" s="446" t="n"/>
-      <c r="U34" s="446" t="n"/>
-      <c r="V34" s="446" t="n"/>
-      <c r="W34" s="446" t="n"/>
-      <c r="X34" s="446" t="n"/>
-      <c r="Y34" s="446" t="n"/>
-      <c r="Z34" s="446" t="n"/>
-      <c r="AA34" s="446" t="n"/>
-      <c r="AB34" s="446" t="n"/>
-      <c r="AC34" s="446" t="n"/>
-      <c r="AD34" s="446" t="n"/>
-      <c r="AE34" s="446" t="n"/>
-      <c r="AF34" s="446" t="n"/>
-      <c r="AG34" s="446" t="n"/>
-      <c r="AH34" s="446" t="n"/>
-      <c r="AI34" s="446" t="n"/>
-      <c r="AJ34" s="446" t="n"/>
-      <c r="AK34" s="446" t="n"/>
-      <c r="AL34" s="446" t="n"/>
-      <c r="AM34" s="446" t="n"/>
-      <c r="AN34" s="562" t="n"/>
+      <c r="B34" s="674" t="n"/>
+      <c r="C34" s="653" t="n"/>
+      <c r="D34" s="653" t="n"/>
+      <c r="E34" s="653" t="n"/>
+      <c r="F34" s="653" t="n"/>
+      <c r="G34" s="653" t="n"/>
+      <c r="H34" s="653" t="n"/>
+      <c r="I34" s="653" t="n"/>
+      <c r="J34" s="653" t="n"/>
+      <c r="K34" s="655" t="n"/>
+      <c r="L34" s="655" t="n"/>
+      <c r="M34" s="655" t="n"/>
+      <c r="N34" s="655" t="n"/>
+      <c r="O34" s="655" t="n"/>
+      <c r="P34" s="655" t="n"/>
+      <c r="Q34" s="655" t="n"/>
+      <c r="R34" s="655" t="n"/>
+      <c r="S34" s="655" t="n"/>
+      <c r="T34" s="655" t="n"/>
+      <c r="U34" s="655" t="n"/>
+      <c r="V34" s="655" t="n"/>
+      <c r="W34" s="655" t="n"/>
+      <c r="X34" s="655" t="n"/>
+      <c r="Y34" s="655" t="n"/>
+      <c r="Z34" s="655" t="n"/>
+      <c r="AA34" s="655" t="n"/>
+      <c r="AB34" s="655" t="n"/>
+      <c r="AC34" s="655" t="n"/>
+      <c r="AD34" s="655" t="n"/>
+      <c r="AE34" s="655" t="n"/>
+      <c r="AF34" s="655" t="n"/>
+      <c r="AG34" s="655" t="n"/>
+      <c r="AH34" s="655" t="n"/>
+      <c r="AI34" s="655" t="n"/>
+      <c r="AJ34" s="655" t="n"/>
+      <c r="AK34" s="655" t="n"/>
+      <c r="AL34" s="655" t="n"/>
+      <c r="AM34" s="655" t="n"/>
+      <c r="AN34" s="656" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="580">
+      <c r="A35" s="671">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B35" s="457" t="n"/>
-      <c r="C35" s="581" t="n"/>
-      <c r="D35" s="581" t="n"/>
-      <c r="E35" s="581" t="n"/>
-      <c r="F35" s="581" t="n"/>
-      <c r="G35" s="581" t="n"/>
-      <c r="H35" s="581" t="n"/>
-      <c r="I35" s="581" t="n"/>
-      <c r="J35" s="581" t="n"/>
-      <c r="K35" s="446" t="n"/>
-      <c r="L35" s="446" t="n"/>
-      <c r="M35" s="446" t="n"/>
-      <c r="N35" s="446" t="n"/>
-      <c r="O35" s="446" t="n"/>
-      <c r="P35" s="446" t="n"/>
-      <c r="Q35" s="446" t="n"/>
-      <c r="R35" s="446" t="n"/>
-      <c r="S35" s="446" t="n"/>
-      <c r="T35" s="446" t="n"/>
-      <c r="U35" s="446" t="n"/>
-      <c r="V35" s="446" t="n"/>
-      <c r="W35" s="446" t="n"/>
-      <c r="X35" s="446" t="n"/>
-      <c r="Y35" s="446" t="n"/>
-      <c r="Z35" s="446" t="n"/>
-      <c r="AA35" s="446" t="n"/>
-      <c r="AB35" s="446" t="n"/>
-      <c r="AC35" s="446" t="n"/>
-      <c r="AD35" s="446" t="n"/>
-      <c r="AE35" s="446" t="n"/>
-      <c r="AF35" s="446" t="n"/>
-      <c r="AG35" s="446" t="n"/>
-      <c r="AH35" s="446" t="n"/>
-      <c r="AI35" s="446" t="n"/>
-      <c r="AJ35" s="446" t="n"/>
-      <c r="AK35" s="446" t="n"/>
-      <c r="AL35" s="446" t="n"/>
-      <c r="AM35" s="446" t="n"/>
-      <c r="AN35" s="562" t="n"/>
+      <c r="B35" s="672" t="n"/>
+      <c r="C35" s="673" t="n"/>
+      <c r="D35" s="673" t="n"/>
+      <c r="E35" s="673" t="n"/>
+      <c r="F35" s="673" t="n"/>
+      <c r="G35" s="673" t="n"/>
+      <c r="H35" s="673" t="n"/>
+      <c r="I35" s="673" t="n"/>
+      <c r="J35" s="673" t="n"/>
+      <c r="K35" s="655" t="n"/>
+      <c r="L35" s="655" t="n"/>
+      <c r="M35" s="655" t="n"/>
+      <c r="N35" s="655" t="n"/>
+      <c r="O35" s="655" t="n"/>
+      <c r="P35" s="655" t="n"/>
+      <c r="Q35" s="655" t="n"/>
+      <c r="R35" s="655" t="n"/>
+      <c r="S35" s="655" t="n"/>
+      <c r="T35" s="655" t="n"/>
+      <c r="U35" s="655" t="n"/>
+      <c r="V35" s="655" t="n"/>
+      <c r="W35" s="655" t="n"/>
+      <c r="X35" s="655" t="n"/>
+      <c r="Y35" s="655" t="n"/>
+      <c r="Z35" s="655" t="n"/>
+      <c r="AA35" s="655" t="n"/>
+      <c r="AB35" s="655" t="n"/>
+      <c r="AC35" s="655" t="n"/>
+      <c r="AD35" s="655" t="n"/>
+      <c r="AE35" s="655" t="n"/>
+      <c r="AF35" s="655" t="n"/>
+      <c r="AG35" s="655" t="n"/>
+      <c r="AH35" s="655" t="n"/>
+      <c r="AI35" s="655" t="n"/>
+      <c r="AJ35" s="655" t="n"/>
+      <c r="AK35" s="655" t="n"/>
+      <c r="AL35" s="655" t="n"/>
+      <c r="AM35" s="655" t="n"/>
+      <c r="AN35" s="656" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="580">
+      <c r="A36" s="671">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B36" s="582" t="n"/>
-      <c r="C36" s="583" t="n"/>
-      <c r="D36" s="583" t="n"/>
-      <c r="E36" s="583" t="n"/>
-      <c r="F36" s="583" t="n"/>
-      <c r="G36" s="583" t="n"/>
-      <c r="H36" s="583" t="n"/>
-      <c r="I36" s="583" t="n"/>
-      <c r="J36" s="583" t="n"/>
-      <c r="K36" s="446" t="n"/>
-      <c r="L36" s="446" t="n"/>
-      <c r="M36" s="446" t="n"/>
-      <c r="N36" s="446" t="n"/>
-      <c r="O36" s="446" t="n"/>
-      <c r="P36" s="446" t="n"/>
-      <c r="Q36" s="446" t="n"/>
-      <c r="R36" s="446" t="n"/>
-      <c r="S36" s="446" t="n"/>
-      <c r="T36" s="446" t="n"/>
-      <c r="U36" s="446" t="n"/>
-      <c r="V36" s="446" t="n"/>
-      <c r="W36" s="446" t="n"/>
-      <c r="X36" s="446" t="n"/>
-      <c r="Y36" s="446" t="n"/>
-      <c r="Z36" s="446" t="n"/>
-      <c r="AA36" s="446" t="n"/>
-      <c r="AB36" s="446" t="n"/>
-      <c r="AC36" s="446" t="n"/>
-      <c r="AD36" s="446" t="n"/>
-      <c r="AE36" s="446" t="n"/>
-      <c r="AF36" s="446" t="n"/>
-      <c r="AG36" s="446" t="n"/>
-      <c r="AH36" s="446" t="n"/>
-      <c r="AI36" s="446" t="n"/>
-      <c r="AJ36" s="446" t="n"/>
-      <c r="AK36" s="446" t="n"/>
-      <c r="AL36" s="446" t="n"/>
-      <c r="AM36" s="446" t="n"/>
-      <c r="AN36" s="562" t="n"/>
+      <c r="B36" s="674" t="n"/>
+      <c r="C36" s="653" t="n"/>
+      <c r="D36" s="653" t="n"/>
+      <c r="E36" s="653" t="n"/>
+      <c r="F36" s="653" t="n"/>
+      <c r="G36" s="653" t="n"/>
+      <c r="H36" s="653" t="n"/>
+      <c r="I36" s="653" t="n"/>
+      <c r="J36" s="653" t="n"/>
+      <c r="K36" s="655" t="n"/>
+      <c r="L36" s="655" t="n"/>
+      <c r="M36" s="655" t="n"/>
+      <c r="N36" s="655" t="n"/>
+      <c r="O36" s="655" t="n"/>
+      <c r="P36" s="655" t="n"/>
+      <c r="Q36" s="655" t="n"/>
+      <c r="R36" s="655" t="n"/>
+      <c r="S36" s="655" t="n"/>
+      <c r="T36" s="655" t="n"/>
+      <c r="U36" s="655" t="n"/>
+      <c r="V36" s="655" t="n"/>
+      <c r="W36" s="655" t="n"/>
+      <c r="X36" s="655" t="n"/>
+      <c r="Y36" s="655" t="n"/>
+      <c r="Z36" s="655" t="n"/>
+      <c r="AA36" s="655" t="n"/>
+      <c r="AB36" s="655" t="n"/>
+      <c r="AC36" s="655" t="n"/>
+      <c r="AD36" s="655" t="n"/>
+      <c r="AE36" s="655" t="n"/>
+      <c r="AF36" s="655" t="n"/>
+      <c r="AG36" s="655" t="n"/>
+      <c r="AH36" s="655" t="n"/>
+      <c r="AI36" s="655" t="n"/>
+      <c r="AJ36" s="655" t="n"/>
+      <c r="AK36" s="655" t="n"/>
+      <c r="AL36" s="655" t="n"/>
+      <c r="AM36" s="655" t="n"/>
+      <c r="AN36" s="656" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="580">
+      <c r="A37" s="671">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B37" s="457" t="n"/>
-      <c r="C37" s="581" t="n"/>
-      <c r="D37" s="581" t="n"/>
-      <c r="E37" s="581" t="n"/>
-      <c r="F37" s="581" t="n"/>
-      <c r="G37" s="581" t="n"/>
-      <c r="H37" s="581" t="n"/>
-      <c r="I37" s="581" t="n"/>
-      <c r="J37" s="581" t="n"/>
-      <c r="K37" s="446" t="n"/>
-      <c r="L37" s="446" t="n"/>
-      <c r="M37" s="446" t="n"/>
-      <c r="N37" s="446" t="n"/>
-      <c r="O37" s="446" t="n"/>
-      <c r="P37" s="446" t="n"/>
-      <c r="Q37" s="446" t="n"/>
-      <c r="R37" s="446" t="n"/>
-      <c r="S37" s="446" t="n"/>
-      <c r="T37" s="446" t="n"/>
-      <c r="U37" s="446" t="n"/>
-      <c r="V37" s="446" t="n"/>
-      <c r="W37" s="446" t="n"/>
-      <c r="X37" s="446" t="n"/>
-      <c r="Y37" s="446" t="n"/>
-      <c r="Z37" s="446" t="n"/>
-      <c r="AA37" s="446" t="n"/>
-      <c r="AB37" s="446" t="n"/>
-      <c r="AC37" s="446" t="n"/>
-      <c r="AD37" s="446" t="n"/>
-      <c r="AE37" s="446" t="n"/>
-      <c r="AF37" s="446" t="n"/>
-      <c r="AG37" s="446" t="n"/>
-      <c r="AH37" s="446" t="n"/>
-      <c r="AI37" s="446" t="n"/>
-      <c r="AJ37" s="446" t="n"/>
-      <c r="AK37" s="446" t="n"/>
-      <c r="AL37" s="446" t="n"/>
-      <c r="AM37" s="446" t="n"/>
-      <c r="AN37" s="562" t="n"/>
+      <c r="B37" s="672" t="n"/>
+      <c r="C37" s="673" t="n"/>
+      <c r="D37" s="673" t="n"/>
+      <c r="E37" s="673" t="n"/>
+      <c r="F37" s="673" t="n"/>
+      <c r="G37" s="673" t="n"/>
+      <c r="H37" s="673" t="n"/>
+      <c r="I37" s="673" t="n"/>
+      <c r="J37" s="673" t="n"/>
+      <c r="K37" s="655" t="n"/>
+      <c r="L37" s="655" t="n"/>
+      <c r="M37" s="655" t="n"/>
+      <c r="N37" s="655" t="n"/>
+      <c r="O37" s="655" t="n"/>
+      <c r="P37" s="655" t="n"/>
+      <c r="Q37" s="655" t="n"/>
+      <c r="R37" s="655" t="n"/>
+      <c r="S37" s="655" t="n"/>
+      <c r="T37" s="655" t="n"/>
+      <c r="U37" s="655" t="n"/>
+      <c r="V37" s="655" t="n"/>
+      <c r="W37" s="655" t="n"/>
+      <c r="X37" s="655" t="n"/>
+      <c r="Y37" s="655" t="n"/>
+      <c r="Z37" s="655" t="n"/>
+      <c r="AA37" s="655" t="n"/>
+      <c r="AB37" s="655" t="n"/>
+      <c r="AC37" s="655" t="n"/>
+      <c r="AD37" s="655" t="n"/>
+      <c r="AE37" s="655" t="n"/>
+      <c r="AF37" s="655" t="n"/>
+      <c r="AG37" s="655" t="n"/>
+      <c r="AH37" s="655" t="n"/>
+      <c r="AI37" s="655" t="n"/>
+      <c r="AJ37" s="655" t="n"/>
+      <c r="AK37" s="655" t="n"/>
+      <c r="AL37" s="655" t="n"/>
+      <c r="AM37" s="655" t="n"/>
+      <c r="AN37" s="656" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="580">
+      <c r="A38" s="671">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B38" s="582" t="n"/>
-      <c r="C38" s="583" t="n"/>
-      <c r="D38" s="583" t="n"/>
-      <c r="E38" s="583" t="n"/>
-      <c r="F38" s="583" t="n"/>
-      <c r="G38" s="583" t="n"/>
-      <c r="H38" s="583" t="n"/>
-      <c r="I38" s="583" t="n"/>
-      <c r="J38" s="583" t="n"/>
-      <c r="K38" s="446" t="n"/>
-      <c r="L38" s="446" t="n"/>
-      <c r="M38" s="446" t="n"/>
-      <c r="N38" s="446" t="n"/>
-      <c r="O38" s="446" t="n"/>
-      <c r="P38" s="446" t="n"/>
-      <c r="Q38" s="446" t="n"/>
-      <c r="R38" s="446" t="n"/>
-      <c r="S38" s="446" t="n"/>
-      <c r="T38" s="446" t="n"/>
-      <c r="U38" s="446" t="n"/>
-      <c r="V38" s="446" t="n"/>
-      <c r="W38" s="446" t="n"/>
-      <c r="X38" s="446" t="n"/>
-      <c r="Y38" s="446" t="n"/>
-      <c r="Z38" s="446" t="n"/>
-      <c r="AA38" s="446" t="n"/>
-      <c r="AB38" s="446" t="n"/>
-      <c r="AC38" s="446" t="n"/>
-      <c r="AD38" s="446" t="n"/>
-      <c r="AE38" s="446" t="n"/>
-      <c r="AF38" s="446" t="n"/>
-      <c r="AG38" s="446" t="n"/>
-      <c r="AH38" s="446" t="n"/>
-      <c r="AI38" s="446" t="n"/>
-      <c r="AJ38" s="446" t="n"/>
-      <c r="AK38" s="446" t="n"/>
-      <c r="AL38" s="446" t="n"/>
-      <c r="AM38" s="446" t="n"/>
-      <c r="AN38" s="562" t="n"/>
+      <c r="B38" s="674" t="n"/>
+      <c r="C38" s="653" t="n"/>
+      <c r="D38" s="653" t="n"/>
+      <c r="E38" s="653" t="n"/>
+      <c r="F38" s="653" t="n"/>
+      <c r="G38" s="653" t="n"/>
+      <c r="H38" s="653" t="n"/>
+      <c r="I38" s="653" t="n"/>
+      <c r="J38" s="653" t="n"/>
+      <c r="K38" s="655" t="n"/>
+      <c r="L38" s="655" t="n"/>
+      <c r="M38" s="655" t="n"/>
+      <c r="N38" s="655" t="n"/>
+      <c r="O38" s="655" t="n"/>
+      <c r="P38" s="655" t="n"/>
+      <c r="Q38" s="655" t="n"/>
+      <c r="R38" s="655" t="n"/>
+      <c r="S38" s="655" t="n"/>
+      <c r="T38" s="655" t="n"/>
+      <c r="U38" s="655" t="n"/>
+      <c r="V38" s="655" t="n"/>
+      <c r="W38" s="655" t="n"/>
+      <c r="X38" s="655" t="n"/>
+      <c r="Y38" s="655" t="n"/>
+      <c r="Z38" s="655" t="n"/>
+      <c r="AA38" s="655" t="n"/>
+      <c r="AB38" s="655" t="n"/>
+      <c r="AC38" s="655" t="n"/>
+      <c r="AD38" s="655" t="n"/>
+      <c r="AE38" s="655" t="n"/>
+      <c r="AF38" s="655" t="n"/>
+      <c r="AG38" s="655" t="n"/>
+      <c r="AH38" s="655" t="n"/>
+      <c r="AI38" s="655" t="n"/>
+      <c r="AJ38" s="655" t="n"/>
+      <c r="AK38" s="655" t="n"/>
+      <c r="AL38" s="655" t="n"/>
+      <c r="AM38" s="655" t="n"/>
+      <c r="AN38" s="656" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="584">
+      <c r="A39" s="675">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B39" s="585" t="n"/>
-      <c r="C39" s="586" t="n"/>
-      <c r="D39" s="586" t="n"/>
-      <c r="E39" s="586" t="n"/>
-      <c r="F39" s="586" t="n"/>
-      <c r="G39" s="586" t="n"/>
-      <c r="H39" s="586" t="n"/>
-      <c r="I39" s="586" t="n"/>
-      <c r="J39" s="586" t="n"/>
-      <c r="K39" s="572" t="n"/>
-      <c r="L39" s="572" t="n"/>
-      <c r="M39" s="572" t="n"/>
-      <c r="N39" s="572" t="n"/>
-      <c r="O39" s="572" t="n"/>
-      <c r="P39" s="572" t="n"/>
-      <c r="Q39" s="572" t="n"/>
-      <c r="R39" s="572" t="n"/>
-      <c r="S39" s="572" t="n"/>
-      <c r="T39" s="572" t="n"/>
-      <c r="U39" s="572" t="n"/>
-      <c r="V39" s="572" t="n"/>
-      <c r="W39" s="572" t="n"/>
-      <c r="X39" s="572" t="n"/>
-      <c r="Y39" s="572" t="n"/>
-      <c r="Z39" s="572" t="n"/>
-      <c r="AA39" s="572" t="n"/>
-      <c r="AB39" s="572" t="n"/>
-      <c r="AC39" s="572" t="n"/>
-      <c r="AD39" s="572" t="n"/>
-      <c r="AE39" s="572" t="n"/>
-      <c r="AF39" s="572" t="n"/>
-      <c r="AG39" s="572" t="n"/>
-      <c r="AH39" s="572" t="n"/>
-      <c r="AI39" s="572" t="n"/>
-      <c r="AJ39" s="572" t="n"/>
-      <c r="AK39" s="572" t="n"/>
-      <c r="AL39" s="572" t="n"/>
-      <c r="AM39" s="572" t="n"/>
-      <c r="AN39" s="573" t="n"/>
+      <c r="B39" s="676" t="n"/>
+      <c r="C39" s="677" t="n"/>
+      <c r="D39" s="677" t="n"/>
+      <c r="E39" s="677" t="n"/>
+      <c r="F39" s="677" t="n"/>
+      <c r="G39" s="677" t="n"/>
+      <c r="H39" s="677" t="n"/>
+      <c r="I39" s="677" t="n"/>
+      <c r="J39" s="677" t="n"/>
+      <c r="K39" s="666" t="n"/>
+      <c r="L39" s="666" t="n"/>
+      <c r="M39" s="666" t="n"/>
+      <c r="N39" s="666" t="n"/>
+      <c r="O39" s="666" t="n"/>
+      <c r="P39" s="666" t="n"/>
+      <c r="Q39" s="666" t="n"/>
+      <c r="R39" s="666" t="n"/>
+      <c r="S39" s="666" t="n"/>
+      <c r="T39" s="666" t="n"/>
+      <c r="U39" s="666" t="n"/>
+      <c r="V39" s="666" t="n"/>
+      <c r="W39" s="666" t="n"/>
+      <c r="X39" s="666" t="n"/>
+      <c r="Y39" s="666" t="n"/>
+      <c r="Z39" s="666" t="n"/>
+      <c r="AA39" s="666" t="n"/>
+      <c r="AB39" s="666" t="n"/>
+      <c r="AC39" s="666" t="n"/>
+      <c r="AD39" s="666" t="n"/>
+      <c r="AE39" s="666" t="n"/>
+      <c r="AF39" s="666" t="n"/>
+      <c r="AG39" s="666" t="n"/>
+      <c r="AH39" s="666" t="n"/>
+      <c r="AI39" s="666" t="n"/>
+      <c r="AJ39" s="666" t="n"/>
+      <c r="AK39" s="666" t="n"/>
+      <c r="AL39" s="666" t="n"/>
+      <c r="AM39" s="666" t="n"/>
+      <c r="AN39" s="667" t="n"/>
     </row>
     <row r="40" ht="3" customHeight="1">
-      <c r="A40" s="442" t="n"/>
-      <c r="B40" s="495" t="n"/>
-      <c r="C40" s="495" t="n"/>
-      <c r="D40" s="495" t="n"/>
-      <c r="E40" s="495" t="n"/>
-      <c r="F40" s="495" t="n"/>
-      <c r="G40" s="495" t="n"/>
-      <c r="H40" s="495" t="n"/>
-      <c r="I40" s="495" t="n"/>
-      <c r="J40" s="495" t="n"/>
-      <c r="K40" s="443" t="n"/>
-      <c r="L40" s="443" t="n"/>
-      <c r="M40" s="443" t="n"/>
-      <c r="N40" s="443" t="n"/>
-      <c r="O40" s="443" t="n"/>
-      <c r="P40" s="443" t="n"/>
-      <c r="Q40" s="443" t="n"/>
-      <c r="R40" s="443" t="n"/>
-      <c r="S40" s="443" t="n"/>
-      <c r="T40" s="443" t="n"/>
-      <c r="U40" s="443" t="n"/>
-      <c r="V40" s="443" t="n"/>
-      <c r="W40" s="443" t="n"/>
-      <c r="X40" s="443" t="n"/>
-      <c r="Y40" s="443" t="n"/>
-      <c r="Z40" s="443" t="n"/>
-      <c r="AA40" s="443" t="n"/>
-      <c r="AB40" s="443" t="n"/>
-      <c r="AC40" s="443" t="n"/>
-      <c r="AD40" s="443" t="n"/>
-      <c r="AE40" s="443" t="n"/>
-      <c r="AF40" s="443" t="n"/>
-      <c r="AG40" s="443" t="n"/>
-      <c r="AH40" s="443" t="n"/>
-      <c r="AI40" s="443" t="n"/>
-      <c r="AJ40" s="443" t="n"/>
-      <c r="AK40" s="443" t="n"/>
-      <c r="AL40" s="443" t="n"/>
-      <c r="AM40" s="443" t="n"/>
-      <c r="AN40" s="443" t="n"/>
+      <c r="A40" s="664" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="n"/>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="665" t="n"/>
+      <c r="L40" s="665" t="n"/>
+      <c r="M40" s="665" t="n"/>
+      <c r="N40" s="665" t="n"/>
+      <c r="O40" s="665" t="n"/>
+      <c r="P40" s="665" t="n"/>
+      <c r="Q40" s="665" t="n"/>
+      <c r="R40" s="665" t="n"/>
+      <c r="S40" s="665" t="n"/>
+      <c r="T40" s="665" t="n"/>
+      <c r="U40" s="665" t="n"/>
+      <c r="V40" s="665" t="n"/>
+      <c r="W40" s="665" t="n"/>
+      <c r="X40" s="665" t="n"/>
+      <c r="Y40" s="665" t="n"/>
+      <c r="Z40" s="665" t="n"/>
+      <c r="AA40" s="665" t="n"/>
+      <c r="AB40" s="665" t="n"/>
+      <c r="AC40" s="665" t="n"/>
+      <c r="AD40" s="665" t="n"/>
+      <c r="AE40" s="665" t="n"/>
+      <c r="AF40" s="665" t="n"/>
+      <c r="AG40" s="665" t="n"/>
+      <c r="AH40" s="665" t="n"/>
+      <c r="AI40" s="665" t="n"/>
+      <c r="AJ40" s="665" t="n"/>
+      <c r="AK40" s="665" t="n"/>
+      <c r="AL40" s="665" t="n"/>
+      <c r="AM40" s="665" t="n"/>
+      <c r="AN40" s="665" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="548" t="inlineStr">
+      <c r="A41" s="644" t="inlineStr">
         <is>
           <t>4.  CLOSURE AND EVIDENCE SECTION</t>
         </is>
       </c>
-      <c r="B41" s="549" t="n"/>
-      <c r="C41" s="549" t="n"/>
-      <c r="D41" s="549" t="n"/>
-      <c r="E41" s="549" t="n"/>
-      <c r="F41" s="549" t="n"/>
-      <c r="G41" s="549" t="n"/>
-      <c r="H41" s="549" t="n"/>
-      <c r="I41" s="549" t="n"/>
-      <c r="J41" s="549" t="n"/>
-      <c r="K41" s="549" t="n"/>
-      <c r="L41" s="549" t="n"/>
-      <c r="M41" s="549" t="n"/>
-      <c r="N41" s="549" t="n"/>
-      <c r="O41" s="549" t="n"/>
-      <c r="P41" s="549" t="n"/>
-      <c r="Q41" s="549" t="n"/>
-      <c r="R41" s="549" t="n"/>
-      <c r="S41" s="549" t="n"/>
-      <c r="T41" s="549" t="n"/>
-      <c r="U41" s="549" t="n"/>
-      <c r="V41" s="549" t="n"/>
-      <c r="W41" s="549" t="n"/>
-      <c r="X41" s="549" t="n"/>
-      <c r="Y41" s="549" t="n"/>
-      <c r="Z41" s="549" t="n"/>
-      <c r="AA41" s="549" t="n"/>
-      <c r="AB41" s="549" t="n"/>
-      <c r="AC41" s="549" t="n"/>
-      <c r="AD41" s="549" t="n"/>
-      <c r="AE41" s="549" t="n"/>
-      <c r="AF41" s="549" t="n"/>
-      <c r="AG41" s="549" t="n"/>
-      <c r="AH41" s="549" t="n"/>
-      <c r="AI41" s="549" t="n"/>
-      <c r="AJ41" s="549" t="n"/>
-      <c r="AK41" s="549" t="n"/>
-      <c r="AL41" s="549" t="n"/>
-      <c r="AM41" s="549" t="n"/>
-      <c r="AN41" s="550" t="n"/>
+      <c r="B41" s="27" t="n"/>
+      <c r="C41" s="27" t="n"/>
+      <c r="D41" s="27" t="n"/>
+      <c r="E41" s="27" t="n"/>
+      <c r="F41" s="27" t="n"/>
+      <c r="G41" s="27" t="n"/>
+      <c r="H41" s="27" t="n"/>
+      <c r="I41" s="27" t="n"/>
+      <c r="J41" s="27" t="n"/>
+      <c r="K41" s="645" t="n"/>
+      <c r="L41" s="645" t="n"/>
+      <c r="M41" s="645" t="n"/>
+      <c r="N41" s="645" t="n"/>
+      <c r="O41" s="645" t="n"/>
+      <c r="P41" s="645" t="n"/>
+      <c r="Q41" s="645" t="n"/>
+      <c r="R41" s="645" t="n"/>
+      <c r="S41" s="645" t="n"/>
+      <c r="T41" s="645" t="n"/>
+      <c r="U41" s="645" t="n"/>
+      <c r="V41" s="645" t="n"/>
+      <c r="W41" s="645" t="n"/>
+      <c r="X41" s="645" t="n"/>
+      <c r="Y41" s="645" t="n"/>
+      <c r="Z41" s="645" t="n"/>
+      <c r="AA41" s="645" t="n"/>
+      <c r="AB41" s="645" t="n"/>
+      <c r="AC41" s="645" t="n"/>
+      <c r="AD41" s="645" t="n"/>
+      <c r="AE41" s="645" t="n"/>
+      <c r="AF41" s="645" t="n"/>
+      <c r="AG41" s="645" t="n"/>
+      <c r="AH41" s="645" t="n"/>
+      <c r="AI41" s="645" t="n"/>
+      <c r="AJ41" s="645" t="n"/>
+      <c r="AK41" s="645" t="n"/>
+      <c r="AL41" s="645" t="n"/>
+      <c r="AM41" s="645" t="n"/>
+      <c r="AN41" s="646" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="587" t="inlineStr">
+      <c r="A42" s="678" t="inlineStr">
         <is>
           <t>Periodic review</t>
         </is>
       </c>
-      <c r="B42" s="552" t="n"/>
-      <c r="C42" s="552" t="n"/>
-      <c r="D42" s="588" t="inlineStr">
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="679" t="inlineStr">
         <is>
           <t>Open items / escalation</t>
         </is>
       </c>
-      <c r="E42" s="552" t="n"/>
-      <c r="F42" s="552" t="n"/>
-      <c r="G42" s="588" t="inlineStr">
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="679" t="inlineStr">
         <is>
           <t>Approval / archive</t>
         </is>
       </c>
-      <c r="H42" s="552" t="n"/>
-      <c r="I42" s="552" t="n"/>
-      <c r="J42" s="552" t="n"/>
-      <c r="K42" s="555" t="n"/>
-      <c r="L42" s="556" t="n"/>
-      <c r="M42" s="556" t="n"/>
-      <c r="N42" s="556" t="n"/>
-      <c r="O42" s="556" t="n"/>
-      <c r="P42" s="556" t="n"/>
-      <c r="Q42" s="556" t="n"/>
-      <c r="R42" s="556" t="n"/>
-      <c r="S42" s="556" t="n"/>
-      <c r="T42" s="556" t="n"/>
-      <c r="U42" s="556" t="n"/>
-      <c r="V42" s="556" t="n"/>
-      <c r="W42" s="556" t="n"/>
-      <c r="X42" s="556" t="n"/>
-      <c r="Y42" s="556" t="n"/>
-      <c r="Z42" s="556" t="n"/>
-      <c r="AA42" s="556" t="n"/>
-      <c r="AB42" s="556" t="n"/>
-      <c r="AC42" s="556" t="n"/>
-      <c r="AD42" s="556" t="n"/>
-      <c r="AE42" s="556" t="n"/>
-      <c r="AF42" s="556" t="n"/>
-      <c r="AG42" s="556" t="n"/>
-      <c r="AH42" s="556" t="n"/>
-      <c r="AI42" s="556" t="n"/>
-      <c r="AJ42" s="556" t="n"/>
-      <c r="AK42" s="556" t="n"/>
-      <c r="AL42" s="556" t="n"/>
-      <c r="AM42" s="556" t="n"/>
-      <c r="AN42" s="557" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="6" t="n"/>
+      <c r="K42" s="650" t="n"/>
+      <c r="L42" s="650" t="n"/>
+      <c r="M42" s="650" t="n"/>
+      <c r="N42" s="650" t="n"/>
+      <c r="O42" s="650" t="n"/>
+      <c r="P42" s="650" t="n"/>
+      <c r="Q42" s="650" t="n"/>
+      <c r="R42" s="650" t="n"/>
+      <c r="S42" s="650" t="n"/>
+      <c r="T42" s="650" t="n"/>
+      <c r="U42" s="650" t="n"/>
+      <c r="V42" s="650" t="n"/>
+      <c r="W42" s="650" t="n"/>
+      <c r="X42" s="650" t="n"/>
+      <c r="Y42" s="650" t="n"/>
+      <c r="Z42" s="650" t="n"/>
+      <c r="AA42" s="650" t="n"/>
+      <c r="AB42" s="650" t="n"/>
+      <c r="AC42" s="650" t="n"/>
+      <c r="AD42" s="650" t="n"/>
+      <c r="AE42" s="650" t="n"/>
+      <c r="AF42" s="650" t="n"/>
+      <c r="AG42" s="650" t="n"/>
+      <c r="AH42" s="650" t="n"/>
+      <c r="AI42" s="650" t="n"/>
+      <c r="AJ42" s="650" t="n"/>
+      <c r="AK42" s="650" t="n"/>
+      <c r="AL42" s="650" t="n"/>
+      <c r="AM42" s="650" t="n"/>
+      <c r="AN42" s="651" t="n"/>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="589" t="inlineStr">
+      <c r="A43" s="213" t="inlineStr">
         <is>
           <t>Return-material tracking memory only; formal quality investigation remains in linked quality records.
 Review owner: _____________________________________________</t>
         </is>
       </c>
-      <c r="B43" s="437" t="n"/>
-      <c r="C43" s="437" t="n"/>
-      <c r="D43" s="590" t="inlineStr">
+      <c r="B43" s="12" t="n"/>
+      <c r="C43" s="13" t="n"/>
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>Final evidence ref: ________________________________________
 Outstanding items / actions: ________________________________</t>
         </is>
       </c>
-      <c r="E43" s="437" t="n"/>
-      <c r="F43" s="437" t="n"/>
-      <c r="G43" s="591" t="inlineStr">
+      <c r="E43" s="12" t="n"/>
+      <c r="F43" s="13" t="n"/>
+      <c r="G43" s="196" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="H43" s="437" t="n"/>
-      <c r="I43" s="437" t="n"/>
-      <c r="J43" s="437" t="n"/>
-      <c r="K43" s="561" t="n"/>
-      <c r="L43" s="446" t="n"/>
-      <c r="M43" s="446" t="n"/>
-      <c r="N43" s="446" t="n"/>
-      <c r="O43" s="446" t="n"/>
-      <c r="P43" s="446" t="n"/>
-      <c r="Q43" s="446" t="n"/>
-      <c r="R43" s="446" t="n"/>
-      <c r="S43" s="446" t="n"/>
-      <c r="T43" s="446" t="n"/>
-      <c r="U43" s="446" t="n"/>
-      <c r="V43" s="446" t="n"/>
-      <c r="W43" s="446" t="n"/>
-      <c r="X43" s="446" t="n"/>
-      <c r="Y43" s="446" t="n"/>
-      <c r="Z43" s="446" t="n"/>
-      <c r="AA43" s="446" t="n"/>
-      <c r="AB43" s="446" t="n"/>
-      <c r="AC43" s="446" t="n"/>
-      <c r="AD43" s="446" t="n"/>
-      <c r="AE43" s="446" t="n"/>
-      <c r="AF43" s="446" t="n"/>
-      <c r="AG43" s="446" t="n"/>
-      <c r="AH43" s="446" t="n"/>
-      <c r="AI43" s="446" t="n"/>
-      <c r="AJ43" s="446" t="n"/>
-      <c r="AK43" s="446" t="n"/>
-      <c r="AL43" s="446" t="n"/>
-      <c r="AM43" s="446" t="n"/>
-      <c r="AN43" s="562" t="n"/>
+      <c r="H43" s="12" t="n"/>
+      <c r="I43" s="12" t="n"/>
+      <c r="J43" s="13" t="n"/>
+      <c r="K43" s="655" t="n"/>
+      <c r="L43" s="655" t="n"/>
+      <c r="M43" s="655" t="n"/>
+      <c r="N43" s="655" t="n"/>
+      <c r="O43" s="655" t="n"/>
+      <c r="P43" s="655" t="n"/>
+      <c r="Q43" s="655" t="n"/>
+      <c r="R43" s="655" t="n"/>
+      <c r="S43" s="655" t="n"/>
+      <c r="T43" s="655" t="n"/>
+      <c r="U43" s="655" t="n"/>
+      <c r="V43" s="655" t="n"/>
+      <c r="W43" s="655" t="n"/>
+      <c r="X43" s="655" t="n"/>
+      <c r="Y43" s="655" t="n"/>
+      <c r="Z43" s="655" t="n"/>
+      <c r="AA43" s="655" t="n"/>
+      <c r="AB43" s="655" t="n"/>
+      <c r="AC43" s="655" t="n"/>
+      <c r="AD43" s="655" t="n"/>
+      <c r="AE43" s="655" t="n"/>
+      <c r="AF43" s="655" t="n"/>
+      <c r="AG43" s="655" t="n"/>
+      <c r="AH43" s="655" t="n"/>
+      <c r="AI43" s="655" t="n"/>
+      <c r="AJ43" s="655" t="n"/>
+      <c r="AK43" s="655" t="n"/>
+      <c r="AL43" s="655" t="n"/>
+      <c r="AM43" s="655" t="n"/>
+      <c r="AN43" s="656" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="592" t="n"/>
-      <c r="B44" s="437" t="n"/>
-      <c r="C44" s="437" t="n"/>
-      <c r="D44" s="563" t="n"/>
-      <c r="E44" s="437" t="n"/>
-      <c r="F44" s="437" t="n"/>
-      <c r="G44" s="563" t="n"/>
-      <c r="H44" s="437" t="n"/>
-      <c r="I44" s="437" t="n"/>
-      <c r="J44" s="437" t="n"/>
-      <c r="K44" s="561" t="n"/>
-      <c r="L44" s="446" t="n"/>
-      <c r="M44" s="446" t="n"/>
-      <c r="N44" s="446" t="n"/>
-      <c r="O44" s="446" t="n"/>
-      <c r="P44" s="446" t="n"/>
-      <c r="Q44" s="446" t="n"/>
-      <c r="R44" s="446" t="n"/>
-      <c r="S44" s="446" t="n"/>
-      <c r="T44" s="446" t="n"/>
-      <c r="U44" s="446" t="n"/>
-      <c r="V44" s="446" t="n"/>
-      <c r="W44" s="446" t="n"/>
-      <c r="X44" s="446" t="n"/>
-      <c r="Y44" s="446" t="n"/>
-      <c r="Z44" s="446" t="n"/>
-      <c r="AA44" s="446" t="n"/>
-      <c r="AB44" s="446" t="n"/>
-      <c r="AC44" s="446" t="n"/>
-      <c r="AD44" s="446" t="n"/>
-      <c r="AE44" s="446" t="n"/>
-      <c r="AF44" s="446" t="n"/>
-      <c r="AG44" s="446" t="n"/>
-      <c r="AH44" s="446" t="n"/>
-      <c r="AI44" s="446" t="n"/>
-      <c r="AJ44" s="446" t="n"/>
-      <c r="AK44" s="446" t="n"/>
-      <c r="AL44" s="446" t="n"/>
-      <c r="AM44" s="446" t="n"/>
-      <c r="AN44" s="562" t="n"/>
+      <c r="A44" s="16" t="n"/>
+      <c r="B44" s="12" t="n"/>
+      <c r="C44" s="13" t="n"/>
+      <c r="D44" s="12" t="n"/>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="13" t="n"/>
+      <c r="G44" s="12" t="n"/>
+      <c r="H44" s="12" t="n"/>
+      <c r="I44" s="12" t="n"/>
+      <c r="J44" s="13" t="n"/>
+      <c r="K44" s="655" t="n"/>
+      <c r="L44" s="655" t="n"/>
+      <c r="M44" s="655" t="n"/>
+      <c r="N44" s="655" t="n"/>
+      <c r="O44" s="655" t="n"/>
+      <c r="P44" s="655" t="n"/>
+      <c r="Q44" s="655" t="n"/>
+      <c r="R44" s="655" t="n"/>
+      <c r="S44" s="655" t="n"/>
+      <c r="T44" s="655" t="n"/>
+      <c r="U44" s="655" t="n"/>
+      <c r="V44" s="655" t="n"/>
+      <c r="W44" s="655" t="n"/>
+      <c r="X44" s="655" t="n"/>
+      <c r="Y44" s="655" t="n"/>
+      <c r="Z44" s="655" t="n"/>
+      <c r="AA44" s="655" t="n"/>
+      <c r="AB44" s="655" t="n"/>
+      <c r="AC44" s="655" t="n"/>
+      <c r="AD44" s="655" t="n"/>
+      <c r="AE44" s="655" t="n"/>
+      <c r="AF44" s="655" t="n"/>
+      <c r="AG44" s="655" t="n"/>
+      <c r="AH44" s="655" t="n"/>
+      <c r="AI44" s="655" t="n"/>
+      <c r="AJ44" s="655" t="n"/>
+      <c r="AK44" s="655" t="n"/>
+      <c r="AL44" s="655" t="n"/>
+      <c r="AM44" s="655" t="n"/>
+      <c r="AN44" s="656" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="592" t="n"/>
-      <c r="B45" s="437" t="n"/>
-      <c r="C45" s="437" t="n"/>
-      <c r="D45" s="563" t="n"/>
-      <c r="E45" s="437" t="n"/>
-      <c r="F45" s="437" t="n"/>
-      <c r="G45" s="563" t="n"/>
-      <c r="H45" s="437" t="n"/>
-      <c r="I45" s="437" t="n"/>
-      <c r="J45" s="437" t="n"/>
-      <c r="K45" s="561" t="n"/>
-      <c r="L45" s="446" t="n"/>
-      <c r="M45" s="446" t="n"/>
-      <c r="N45" s="446" t="n"/>
-      <c r="O45" s="446" t="n"/>
-      <c r="P45" s="446" t="n"/>
-      <c r="Q45" s="446" t="n"/>
-      <c r="R45" s="446" t="n"/>
-      <c r="S45" s="446" t="n"/>
-      <c r="T45" s="446" t="n"/>
-      <c r="U45" s="446" t="n"/>
-      <c r="V45" s="446" t="n"/>
-      <c r="W45" s="446" t="n"/>
-      <c r="X45" s="446" t="n"/>
-      <c r="Y45" s="446" t="n"/>
-      <c r="Z45" s="446" t="n"/>
-      <c r="AA45" s="446" t="n"/>
-      <c r="AB45" s="446" t="n"/>
-      <c r="AC45" s="446" t="n"/>
-      <c r="AD45" s="446" t="n"/>
-      <c r="AE45" s="446" t="n"/>
-      <c r="AF45" s="446" t="n"/>
-      <c r="AG45" s="446" t="n"/>
-      <c r="AH45" s="446" t="n"/>
-      <c r="AI45" s="446" t="n"/>
-      <c r="AJ45" s="446" t="n"/>
-      <c r="AK45" s="446" t="n"/>
-      <c r="AL45" s="446" t="n"/>
-      <c r="AM45" s="446" t="n"/>
-      <c r="AN45" s="562" t="n"/>
+      <c r="A45" s="16" t="n"/>
+      <c r="B45" s="12" t="n"/>
+      <c r="C45" s="13" t="n"/>
+      <c r="D45" s="12" t="n"/>
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="13" t="n"/>
+      <c r="G45" s="12" t="n"/>
+      <c r="H45" s="12" t="n"/>
+      <c r="I45" s="12" t="n"/>
+      <c r="J45" s="13" t="n"/>
+      <c r="K45" s="655" t="n"/>
+      <c r="L45" s="655" t="n"/>
+      <c r="M45" s="655" t="n"/>
+      <c r="N45" s="655" t="n"/>
+      <c r="O45" s="655" t="n"/>
+      <c r="P45" s="655" t="n"/>
+      <c r="Q45" s="655" t="n"/>
+      <c r="R45" s="655" t="n"/>
+      <c r="S45" s="655" t="n"/>
+      <c r="T45" s="655" t="n"/>
+      <c r="U45" s="655" t="n"/>
+      <c r="V45" s="655" t="n"/>
+      <c r="W45" s="655" t="n"/>
+      <c r="X45" s="655" t="n"/>
+      <c r="Y45" s="655" t="n"/>
+      <c r="Z45" s="655" t="n"/>
+      <c r="AA45" s="655" t="n"/>
+      <c r="AB45" s="655" t="n"/>
+      <c r="AC45" s="655" t="n"/>
+      <c r="AD45" s="655" t="n"/>
+      <c r="AE45" s="655" t="n"/>
+      <c r="AF45" s="655" t="n"/>
+      <c r="AG45" s="655" t="n"/>
+      <c r="AH45" s="655" t="n"/>
+      <c r="AI45" s="655" t="n"/>
+      <c r="AJ45" s="655" t="n"/>
+      <c r="AK45" s="655" t="n"/>
+      <c r="AL45" s="655" t="n"/>
+      <c r="AM45" s="655" t="n"/>
+      <c r="AN45" s="656" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="593" t="n"/>
-      <c r="B46" s="566" t="n"/>
-      <c r="C46" s="566" t="n"/>
-      <c r="D46" s="569" t="n"/>
-      <c r="E46" s="566" t="n"/>
-      <c r="F46" s="566" t="n"/>
-      <c r="G46" s="569" t="n"/>
-      <c r="H46" s="566" t="n"/>
-      <c r="I46" s="566" t="n"/>
-      <c r="J46" s="566" t="n"/>
-      <c r="K46" s="571" t="n"/>
-      <c r="L46" s="572" t="n"/>
-      <c r="M46" s="572" t="n"/>
-      <c r="N46" s="572" t="n"/>
-      <c r="O46" s="572" t="n"/>
-      <c r="P46" s="572" t="n"/>
-      <c r="Q46" s="572" t="n"/>
-      <c r="R46" s="572" t="n"/>
-      <c r="S46" s="572" t="n"/>
-      <c r="T46" s="572" t="n"/>
-      <c r="U46" s="572" t="n"/>
-      <c r="V46" s="572" t="n"/>
-      <c r="W46" s="572" t="n"/>
-      <c r="X46" s="572" t="n"/>
-      <c r="Y46" s="572" t="n"/>
-      <c r="Z46" s="572" t="n"/>
-      <c r="AA46" s="572" t="n"/>
-      <c r="AB46" s="572" t="n"/>
-      <c r="AC46" s="572" t="n"/>
-      <c r="AD46" s="572" t="n"/>
-      <c r="AE46" s="572" t="n"/>
-      <c r="AF46" s="572" t="n"/>
-      <c r="AG46" s="572" t="n"/>
-      <c r="AH46" s="572" t="n"/>
-      <c r="AI46" s="572" t="n"/>
-      <c r="AJ46" s="572" t="n"/>
-      <c r="AK46" s="572" t="n"/>
-      <c r="AL46" s="572" t="n"/>
-      <c r="AM46" s="572" t="n"/>
-      <c r="AN46" s="573" t="n"/>
+      <c r="A46" s="18" t="n"/>
+      <c r="B46" s="19" t="n"/>
+      <c r="C46" s="22" t="n"/>
+      <c r="D46" s="19" t="n"/>
+      <c r="E46" s="19" t="n"/>
+      <c r="F46" s="22" t="n"/>
+      <c r="G46" s="19" t="n"/>
+      <c r="H46" s="19" t="n"/>
+      <c r="I46" s="19" t="n"/>
+      <c r="J46" s="22" t="n"/>
+      <c r="K46" s="666" t="n"/>
+      <c r="L46" s="666" t="n"/>
+      <c r="M46" s="666" t="n"/>
+      <c r="N46" s="666" t="n"/>
+      <c r="O46" s="666" t="n"/>
+      <c r="P46" s="666" t="n"/>
+      <c r="Q46" s="666" t="n"/>
+      <c r="R46" s="666" t="n"/>
+      <c r="S46" s="666" t="n"/>
+      <c r="T46" s="666" t="n"/>
+      <c r="U46" s="666" t="n"/>
+      <c r="V46" s="666" t="n"/>
+      <c r="W46" s="666" t="n"/>
+      <c r="X46" s="666" t="n"/>
+      <c r="Y46" s="666" t="n"/>
+      <c r="Z46" s="666" t="n"/>
+      <c r="AA46" s="666" t="n"/>
+      <c r="AB46" s="666" t="n"/>
+      <c r="AC46" s="666" t="n"/>
+      <c r="AD46" s="666" t="n"/>
+      <c r="AE46" s="666" t="n"/>
+      <c r="AF46" s="666" t="n"/>
+      <c r="AG46" s="666" t="n"/>
+      <c r="AH46" s="666" t="n"/>
+      <c r="AI46" s="666" t="n"/>
+      <c r="AJ46" s="666" t="n"/>
+      <c r="AK46" s="666" t="n"/>
+      <c r="AL46" s="666" t="n"/>
+      <c r="AM46" s="666" t="n"/>
+      <c r="AN46" s="667" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="548" t="inlineStr">
+      <c r="A47" s="644" t="inlineStr">
         <is>
           <t>NOTICE  —  Enter data only in designated white input cells. One form per event or job unless this workbook is designated as rolling. Do not add, delete or resize columns/rows. File naming: FRM-213_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="549" t="n"/>
-      <c r="C47" s="549" t="n"/>
-      <c r="D47" s="549" t="n"/>
-      <c r="E47" s="549" t="n"/>
-      <c r="F47" s="549" t="n"/>
-      <c r="G47" s="549" t="n"/>
-      <c r="H47" s="549" t="n"/>
-      <c r="I47" s="549" t="n"/>
-      <c r="J47" s="549" t="n"/>
-      <c r="K47" s="549" t="n"/>
-      <c r="L47" s="549" t="n"/>
-      <c r="M47" s="549" t="n"/>
-      <c r="N47" s="549" t="n"/>
-      <c r="O47" s="549" t="n"/>
-      <c r="P47" s="549" t="n"/>
-      <c r="Q47" s="549" t="n"/>
-      <c r="R47" s="549" t="n"/>
-      <c r="S47" s="549" t="n"/>
-      <c r="T47" s="549" t="n"/>
-      <c r="U47" s="549" t="n"/>
-      <c r="V47" s="549" t="n"/>
-      <c r="W47" s="549" t="n"/>
-      <c r="X47" s="549" t="n"/>
-      <c r="Y47" s="549" t="n"/>
-      <c r="Z47" s="549" t="n"/>
-      <c r="AA47" s="549" t="n"/>
-      <c r="AB47" s="549" t="n"/>
-      <c r="AC47" s="549" t="n"/>
-      <c r="AD47" s="549" t="n"/>
-      <c r="AE47" s="549" t="n"/>
-      <c r="AF47" s="549" t="n"/>
-      <c r="AG47" s="549" t="n"/>
-      <c r="AH47" s="549" t="n"/>
-      <c r="AI47" s="549" t="n"/>
-      <c r="AJ47" s="549" t="n"/>
-      <c r="AK47" s="549" t="n"/>
-      <c r="AL47" s="549" t="n"/>
-      <c r="AM47" s="549" t="n"/>
-      <c r="AN47" s="550" t="n"/>
+      <c r="B47" s="27" t="n"/>
+      <c r="C47" s="27" t="n"/>
+      <c r="D47" s="27" t="n"/>
+      <c r="E47" s="27" t="n"/>
+      <c r="F47" s="27" t="n"/>
+      <c r="G47" s="27" t="n"/>
+      <c r="H47" s="27" t="n"/>
+      <c r="I47" s="27" t="n"/>
+      <c r="J47" s="27" t="n"/>
+      <c r="K47" s="645" t="n"/>
+      <c r="L47" s="645" t="n"/>
+      <c r="M47" s="645" t="n"/>
+      <c r="N47" s="645" t="n"/>
+      <c r="O47" s="645" t="n"/>
+      <c r="P47" s="645" t="n"/>
+      <c r="Q47" s="645" t="n"/>
+      <c r="R47" s="645" t="n"/>
+      <c r="S47" s="645" t="n"/>
+      <c r="T47" s="645" t="n"/>
+      <c r="U47" s="645" t="n"/>
+      <c r="V47" s="645" t="n"/>
+      <c r="W47" s="645" t="n"/>
+      <c r="X47" s="645" t="n"/>
+      <c r="Y47" s="645" t="n"/>
+      <c r="Z47" s="645" t="n"/>
+      <c r="AA47" s="645" t="n"/>
+      <c r="AB47" s="645" t="n"/>
+      <c r="AC47" s="645" t="n"/>
+      <c r="AD47" s="645" t="n"/>
+      <c r="AE47" s="645" t="n"/>
+      <c r="AF47" s="645" t="n"/>
+      <c r="AG47" s="645" t="n"/>
+      <c r="AH47" s="645" t="n"/>
+      <c r="AI47" s="645" t="n"/>
+      <c r="AJ47" s="645" t="n"/>
+      <c r="AK47" s="645" t="n"/>
+      <c r="AL47" s="645" t="n"/>
+      <c r="AM47" s="645" t="n"/>
+      <c r="AN47" s="646" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="1"/>
     <row r="49" hidden="1" outlineLevel="1"/>
@@ -8851,7 +9203,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CFRM-213  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
+    <oddFooter>&amp;C&amp;"Segoe UI"&amp;7 FRM-213  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -8870,7 +9222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:CU7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -9486,7 +9838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN8"/>
+  <dimension ref="A1:CU8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -10209,1300 +10561,1300 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="505" t="n"/>
-      <c r="B1" s="506" t="n"/>
-      <c r="C1" s="507" t="inlineStr">
+      <c r="A1" s="339" t="n"/>
+      <c r="B1" s="53" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>PERIODIC REVIEW RECORD</t>
         </is>
       </c>
-      <c r="D1" s="506" t="n"/>
-      <c r="E1" s="506" t="n"/>
-      <c r="F1" s="506" t="n"/>
-      <c r="G1" s="597" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="680" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="H1" s="598" t="inlineStr">
+      <c r="H1" s="681" t="inlineStr">
         <is>
           <t>FRM-213</t>
         </is>
       </c>
-      <c r="I1" s="509" t="n"/>
-      <c r="J1" s="510" t="n"/>
-      <c r="K1" s="510" t="n"/>
-      <c r="L1" s="510" t="n"/>
-      <c r="M1" s="510" t="n"/>
-      <c r="N1" s="510" t="n"/>
-      <c r="O1" s="510" t="n"/>
-      <c r="P1" s="510" t="n"/>
-      <c r="Q1" s="510" t="n"/>
-      <c r="R1" s="510" t="n"/>
-      <c r="S1" s="510" t="n"/>
-      <c r="T1" s="510" t="n"/>
-      <c r="U1" s="510" t="n"/>
-      <c r="V1" s="510" t="n"/>
-      <c r="W1" s="510" t="n"/>
-      <c r="X1" s="510" t="n"/>
-      <c r="Y1" s="510" t="n"/>
-      <c r="Z1" s="510" t="n"/>
-      <c r="AA1" s="510" t="n"/>
-      <c r="AB1" s="510" t="n"/>
-      <c r="AC1" s="510" t="n"/>
-      <c r="AD1" s="511" t="n"/>
-      <c r="AE1" s="512" t="n"/>
-      <c r="AF1" s="513" t="n"/>
-      <c r="AG1" s="513" t="n"/>
-      <c r="AH1" s="514" t="n"/>
-      <c r="AI1" s="515" t="n"/>
-      <c r="AJ1" s="516" t="n"/>
-      <c r="AK1" s="516" t="n"/>
-      <c r="AL1" s="516" t="n"/>
-      <c r="AM1" s="516" t="n"/>
-      <c r="AN1" s="517" t="n"/>
+      <c r="I1" s="624" t="n"/>
+      <c r="J1" s="624" t="n"/>
+      <c r="K1" s="624" t="n"/>
+      <c r="L1" s="624" t="n"/>
+      <c r="M1" s="624" t="n"/>
+      <c r="N1" s="624" t="n"/>
+      <c r="O1" s="624" t="n"/>
+      <c r="P1" s="624" t="n"/>
+      <c r="Q1" s="624" t="n"/>
+      <c r="R1" s="624" t="n"/>
+      <c r="S1" s="624" t="n"/>
+      <c r="T1" s="624" t="n"/>
+      <c r="U1" s="624" t="n"/>
+      <c r="V1" s="624" t="n"/>
+      <c r="W1" s="624" t="n"/>
+      <c r="X1" s="624" t="n"/>
+      <c r="Y1" s="624" t="n"/>
+      <c r="Z1" s="624" t="n"/>
+      <c r="AA1" s="624" t="n"/>
+      <c r="AB1" s="624" t="n"/>
+      <c r="AC1" s="624" t="n"/>
+      <c r="AD1" s="624" t="n"/>
+      <c r="AE1" s="625" t="n"/>
+      <c r="AF1" s="625" t="n"/>
+      <c r="AG1" s="625" t="n"/>
+      <c r="AH1" s="625" t="n"/>
+      <c r="AI1" s="626" t="n"/>
+      <c r="AJ1" s="626" t="n"/>
+      <c r="AK1" s="626" t="n"/>
+      <c r="AL1" s="626" t="n"/>
+      <c r="AM1" s="626" t="n"/>
+      <c r="AN1" s="627" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="518" t="n"/>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="599" t="inlineStr">
+      <c r="A2" s="9" t="n"/>
+      <c r="B2" s="54" t="n"/>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="682" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="H2" s="600" t="inlineStr">
+      <c r="H2" s="683" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="I2" s="520" t="n"/>
-      <c r="J2" s="521" t="n"/>
-      <c r="K2" s="521" t="n"/>
-      <c r="L2" s="521" t="n"/>
-      <c r="M2" s="521" t="n"/>
-      <c r="N2" s="521" t="n"/>
-      <c r="O2" s="521" t="n"/>
-      <c r="P2" s="521" t="n"/>
-      <c r="Q2" s="521" t="n"/>
-      <c r="R2" s="521" t="n"/>
-      <c r="S2" s="521" t="n"/>
-      <c r="T2" s="521" t="n"/>
-      <c r="U2" s="521" t="n"/>
-      <c r="V2" s="521" t="n"/>
-      <c r="W2" s="521" t="n"/>
-      <c r="X2" s="521" t="n"/>
-      <c r="Y2" s="521" t="n"/>
-      <c r="Z2" s="521" t="n"/>
-      <c r="AA2" s="521" t="n"/>
-      <c r="AB2" s="521" t="n"/>
-      <c r="AC2" s="521" t="n"/>
-      <c r="AD2" s="522" t="n"/>
-      <c r="AE2" s="523" t="n"/>
-      <c r="AF2" s="524" t="n"/>
-      <c r="AG2" s="524" t="n"/>
-      <c r="AH2" s="525" t="n"/>
-      <c r="AI2" s="526" t="n"/>
-      <c r="AJ2" s="527" t="n"/>
-      <c r="AK2" s="527" t="n"/>
-      <c r="AL2" s="527" t="n"/>
-      <c r="AM2" s="527" t="n"/>
-      <c r="AN2" s="528" t="n"/>
+      <c r="I2" s="629" t="n"/>
+      <c r="J2" s="629" t="n"/>
+      <c r="K2" s="629" t="n"/>
+      <c r="L2" s="629" t="n"/>
+      <c r="M2" s="629" t="n"/>
+      <c r="N2" s="629" t="n"/>
+      <c r="O2" s="629" t="n"/>
+      <c r="P2" s="629" t="n"/>
+      <c r="Q2" s="629" t="n"/>
+      <c r="R2" s="629" t="n"/>
+      <c r="S2" s="629" t="n"/>
+      <c r="T2" s="629" t="n"/>
+      <c r="U2" s="629" t="n"/>
+      <c r="V2" s="629" t="n"/>
+      <c r="W2" s="629" t="n"/>
+      <c r="X2" s="629" t="n"/>
+      <c r="Y2" s="629" t="n"/>
+      <c r="Z2" s="629" t="n"/>
+      <c r="AA2" s="629" t="n"/>
+      <c r="AB2" s="629" t="n"/>
+      <c r="AC2" s="629" t="n"/>
+      <c r="AD2" s="629" t="n"/>
+      <c r="AE2" s="630" t="n"/>
+      <c r="AF2" s="630" t="n"/>
+      <c r="AG2" s="630" t="n"/>
+      <c r="AH2" s="630" t="n"/>
+      <c r="AI2" s="631" t="n"/>
+      <c r="AJ2" s="631" t="n"/>
+      <c r="AK2" s="631" t="n"/>
+      <c r="AL2" s="631" t="n"/>
+      <c r="AM2" s="631" t="n"/>
+      <c r="AN2" s="632" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="518" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="599" t="inlineStr">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="54" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="682" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="H3" s="600" t="inlineStr">
+      <c r="H3" s="683" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I3" s="520" t="n"/>
-      <c r="J3" s="521" t="n"/>
-      <c r="K3" s="521" t="n"/>
-      <c r="L3" s="521" t="n"/>
-      <c r="M3" s="521" t="n"/>
-      <c r="N3" s="521" t="n"/>
-      <c r="O3" s="521" t="n"/>
-      <c r="P3" s="521" t="n"/>
-      <c r="Q3" s="521" t="n"/>
-      <c r="R3" s="521" t="n"/>
-      <c r="S3" s="521" t="n"/>
-      <c r="T3" s="521" t="n"/>
-      <c r="U3" s="521" t="n"/>
-      <c r="V3" s="521" t="n"/>
-      <c r="W3" s="521" t="n"/>
-      <c r="X3" s="521" t="n"/>
-      <c r="Y3" s="521" t="n"/>
-      <c r="Z3" s="521" t="n"/>
-      <c r="AA3" s="521" t="n"/>
-      <c r="AB3" s="521" t="n"/>
-      <c r="AC3" s="521" t="n"/>
-      <c r="AD3" s="522" t="n"/>
-      <c r="AE3" s="523" t="n"/>
-      <c r="AF3" s="524" t="n"/>
-      <c r="AG3" s="524" t="n"/>
-      <c r="AH3" s="525" t="n"/>
-      <c r="AI3" s="526" t="n"/>
-      <c r="AJ3" s="527" t="n"/>
-      <c r="AK3" s="527" t="n"/>
-      <c r="AL3" s="527" t="n"/>
-      <c r="AM3" s="527" t="n"/>
-      <c r="AN3" s="528" t="n"/>
+      <c r="I3" s="629" t="n"/>
+      <c r="J3" s="629" t="n"/>
+      <c r="K3" s="629" t="n"/>
+      <c r="L3" s="629" t="n"/>
+      <c r="M3" s="629" t="n"/>
+      <c r="N3" s="629" t="n"/>
+      <c r="O3" s="629" t="n"/>
+      <c r="P3" s="629" t="n"/>
+      <c r="Q3" s="629" t="n"/>
+      <c r="R3" s="629" t="n"/>
+      <c r="S3" s="629" t="n"/>
+      <c r="T3" s="629" t="n"/>
+      <c r="U3" s="629" t="n"/>
+      <c r="V3" s="629" t="n"/>
+      <c r="W3" s="629" t="n"/>
+      <c r="X3" s="629" t="n"/>
+      <c r="Y3" s="629" t="n"/>
+      <c r="Z3" s="629" t="n"/>
+      <c r="AA3" s="629" t="n"/>
+      <c r="AB3" s="629" t="n"/>
+      <c r="AC3" s="629" t="n"/>
+      <c r="AD3" s="629" t="n"/>
+      <c r="AE3" s="630" t="n"/>
+      <c r="AF3" s="630" t="n"/>
+      <c r="AG3" s="630" t="n"/>
+      <c r="AH3" s="630" t="n"/>
+      <c r="AI3" s="631" t="n"/>
+      <c r="AJ3" s="631" t="n"/>
+      <c r="AK3" s="631" t="n"/>
+      <c r="AL3" s="631" t="n"/>
+      <c r="AM3" s="631" t="n"/>
+      <c r="AN3" s="632" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="518" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="529" t="inlineStr">
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="633" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="599" t="inlineStr">
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="682" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H4" s="600" t="inlineStr">
+      <c r="H4" s="683" t="inlineStr">
         <is>
           <t>QA / Customer Service</t>
         </is>
       </c>
-      <c r="I4" s="530" t="n"/>
-      <c r="J4" s="531" t="n"/>
-      <c r="K4" s="531" t="n"/>
-      <c r="L4" s="531" t="n"/>
-      <c r="M4" s="531" t="n"/>
-      <c r="N4" s="531" t="n"/>
-      <c r="O4" s="531" t="n"/>
-      <c r="P4" s="531" t="n"/>
-      <c r="Q4" s="531" t="n"/>
-      <c r="R4" s="531" t="n"/>
-      <c r="S4" s="531" t="n"/>
-      <c r="T4" s="531" t="n"/>
-      <c r="U4" s="531" t="n"/>
-      <c r="V4" s="531" t="n"/>
-      <c r="W4" s="531" t="n"/>
-      <c r="X4" s="531" t="n"/>
-      <c r="Y4" s="531" t="n"/>
-      <c r="Z4" s="531" t="n"/>
-      <c r="AA4" s="531" t="n"/>
-      <c r="AB4" s="531" t="n"/>
-      <c r="AC4" s="531" t="n"/>
-      <c r="AD4" s="532" t="n"/>
-      <c r="AE4" s="523" t="n"/>
-      <c r="AF4" s="524" t="n"/>
-      <c r="AG4" s="524" t="n"/>
-      <c r="AH4" s="525" t="n"/>
-      <c r="AI4" s="526" t="n"/>
-      <c r="AJ4" s="527" t="n"/>
-      <c r="AK4" s="527" t="n"/>
-      <c r="AL4" s="527" t="n"/>
-      <c r="AM4" s="527" t="n"/>
-      <c r="AN4" s="528" t="n"/>
+      <c r="I4" s="635" t="n"/>
+      <c r="J4" s="635" t="n"/>
+      <c r="K4" s="635" t="n"/>
+      <c r="L4" s="635" t="n"/>
+      <c r="M4" s="635" t="n"/>
+      <c r="N4" s="635" t="n"/>
+      <c r="O4" s="635" t="n"/>
+      <c r="P4" s="635" t="n"/>
+      <c r="Q4" s="635" t="n"/>
+      <c r="R4" s="635" t="n"/>
+      <c r="S4" s="635" t="n"/>
+      <c r="T4" s="635" t="n"/>
+      <c r="U4" s="635" t="n"/>
+      <c r="V4" s="635" t="n"/>
+      <c r="W4" s="635" t="n"/>
+      <c r="X4" s="635" t="n"/>
+      <c r="Y4" s="635" t="n"/>
+      <c r="Z4" s="635" t="n"/>
+      <c r="AA4" s="635" t="n"/>
+      <c r="AB4" s="635" t="n"/>
+      <c r="AC4" s="635" t="n"/>
+      <c r="AD4" s="635" t="n"/>
+      <c r="AE4" s="630" t="n"/>
+      <c r="AF4" s="630" t="n"/>
+      <c r="AG4" s="630" t="n"/>
+      <c r="AH4" s="630" t="n"/>
+      <c r="AI4" s="631" t="n"/>
+      <c r="AJ4" s="631" t="n"/>
+      <c r="AK4" s="631" t="n"/>
+      <c r="AL4" s="631" t="n"/>
+      <c r="AM4" s="631" t="n"/>
+      <c r="AN4" s="632" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="533" t="n"/>
-      <c r="B5" s="534" t="n"/>
-      <c r="C5" s="535" t="inlineStr">
+      <c r="A5" s="18" t="n"/>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="636" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="534" t="n"/>
-      <c r="E5" s="534" t="n"/>
-      <c r="F5" s="534" t="n"/>
-      <c r="G5" s="601" t="inlineStr">
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="684" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="H5" s="602" t="inlineStr">
+      <c r="H5" s="685" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
       </c>
-      <c r="I5" s="537" t="n"/>
-      <c r="J5" s="538" t="n"/>
-      <c r="K5" s="538" t="n"/>
-      <c r="L5" s="538" t="n"/>
-      <c r="M5" s="538" t="n"/>
-      <c r="N5" s="538" t="n"/>
-      <c r="O5" s="538" t="n"/>
-      <c r="P5" s="538" t="n"/>
-      <c r="Q5" s="538" t="n"/>
-      <c r="R5" s="538" t="n"/>
-      <c r="S5" s="538" t="n"/>
-      <c r="T5" s="538" t="n"/>
-      <c r="U5" s="538" t="n"/>
-      <c r="V5" s="538" t="n"/>
-      <c r="W5" s="538" t="n"/>
-      <c r="X5" s="538" t="n"/>
-      <c r="Y5" s="538" t="n"/>
-      <c r="Z5" s="538" t="n"/>
-      <c r="AA5" s="538" t="n"/>
-      <c r="AB5" s="538" t="n"/>
-      <c r="AC5" s="538" t="n"/>
-      <c r="AD5" s="539" t="n"/>
-      <c r="AE5" s="540" t="n"/>
-      <c r="AF5" s="541" t="n"/>
-      <c r="AG5" s="541" t="n"/>
-      <c r="AH5" s="542" t="n"/>
-      <c r="AI5" s="543" t="n"/>
-      <c r="AJ5" s="544" t="n"/>
-      <c r="AK5" s="544" t="n"/>
-      <c r="AL5" s="544" t="n"/>
-      <c r="AM5" s="544" t="n"/>
-      <c r="AN5" s="545" t="n"/>
+      <c r="I5" s="638" t="n"/>
+      <c r="J5" s="638" t="n"/>
+      <c r="K5" s="638" t="n"/>
+      <c r="L5" s="638" t="n"/>
+      <c r="M5" s="638" t="n"/>
+      <c r="N5" s="638" t="n"/>
+      <c r="O5" s="638" t="n"/>
+      <c r="P5" s="638" t="n"/>
+      <c r="Q5" s="638" t="n"/>
+      <c r="R5" s="638" t="n"/>
+      <c r="S5" s="638" t="n"/>
+      <c r="T5" s="638" t="n"/>
+      <c r="U5" s="638" t="n"/>
+      <c r="V5" s="638" t="n"/>
+      <c r="W5" s="638" t="n"/>
+      <c r="X5" s="638" t="n"/>
+      <c r="Y5" s="638" t="n"/>
+      <c r="Z5" s="638" t="n"/>
+      <c r="AA5" s="638" t="n"/>
+      <c r="AB5" s="638" t="n"/>
+      <c r="AC5" s="638" t="n"/>
+      <c r="AD5" s="638" t="n"/>
+      <c r="AE5" s="639" t="n"/>
+      <c r="AF5" s="639" t="n"/>
+      <c r="AG5" s="639" t="n"/>
+      <c r="AH5" s="639" t="n"/>
+      <c r="AI5" s="640" t="n"/>
+      <c r="AJ5" s="640" t="n"/>
+      <c r="AK5" s="640" t="n"/>
+      <c r="AL5" s="640" t="n"/>
+      <c r="AM5" s="640" t="n"/>
+      <c r="AN5" s="641" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="546" t="n"/>
-      <c r="B6" s="547" t="n"/>
-      <c r="C6" s="547" t="n"/>
-      <c r="D6" s="547" t="n"/>
-      <c r="E6" s="547" t="n"/>
-      <c r="F6" s="547" t="n"/>
-      <c r="G6" s="547" t="n"/>
-      <c r="H6" s="547" t="n"/>
-      <c r="I6" s="547" t="n"/>
-      <c r="J6" s="547" t="n"/>
-      <c r="K6" s="547" t="n"/>
-      <c r="L6" s="547" t="n"/>
-      <c r="M6" s="547" t="n"/>
-      <c r="N6" s="547" t="n"/>
-      <c r="O6" s="547" t="n"/>
-      <c r="P6" s="547" t="n"/>
-      <c r="Q6" s="547" t="n"/>
-      <c r="R6" s="547" t="n"/>
-      <c r="S6" s="547" t="n"/>
-      <c r="T6" s="547" t="n"/>
-      <c r="U6" s="547" t="n"/>
-      <c r="V6" s="547" t="n"/>
-      <c r="W6" s="547" t="n"/>
-      <c r="X6" s="547" t="n"/>
-      <c r="Y6" s="547" t="n"/>
-      <c r="Z6" s="547" t="n"/>
-      <c r="AA6" s="547" t="n"/>
-      <c r="AB6" s="547" t="n"/>
-      <c r="AC6" s="547" t="n"/>
-      <c r="AD6" s="547" t="n"/>
-      <c r="AE6" s="547" t="n"/>
-      <c r="AF6" s="547" t="n"/>
-      <c r="AG6" s="547" t="n"/>
-      <c r="AH6" s="547" t="n"/>
-      <c r="AI6" s="547" t="n"/>
-      <c r="AJ6" s="547" t="n"/>
-      <c r="AK6" s="547" t="n"/>
-      <c r="AL6" s="547" t="n"/>
-      <c r="AM6" s="547" t="n"/>
-      <c r="AN6" s="547" t="n"/>
+      <c r="A6" s="642" t="n"/>
+      <c r="B6" s="643" t="n"/>
+      <c r="C6" s="643" t="n"/>
+      <c r="D6" s="643" t="n"/>
+      <c r="E6" s="643" t="n"/>
+      <c r="F6" s="643" t="n"/>
+      <c r="G6" s="643" t="n"/>
+      <c r="H6" s="643" t="n"/>
+      <c r="I6" s="643" t="n"/>
+      <c r="J6" s="643" t="n"/>
+      <c r="K6" s="643" t="n"/>
+      <c r="L6" s="643" t="n"/>
+      <c r="M6" s="643" t="n"/>
+      <c r="N6" s="643" t="n"/>
+      <c r="O6" s="643" t="n"/>
+      <c r="P6" s="643" t="n"/>
+      <c r="Q6" s="643" t="n"/>
+      <c r="R6" s="643" t="n"/>
+      <c r="S6" s="643" t="n"/>
+      <c r="T6" s="643" t="n"/>
+      <c r="U6" s="643" t="n"/>
+      <c r="V6" s="643" t="n"/>
+      <c r="W6" s="643" t="n"/>
+      <c r="X6" s="643" t="n"/>
+      <c r="Y6" s="643" t="n"/>
+      <c r="Z6" s="643" t="n"/>
+      <c r="AA6" s="643" t="n"/>
+      <c r="AB6" s="643" t="n"/>
+      <c r="AC6" s="643" t="n"/>
+      <c r="AD6" s="643" t="n"/>
+      <c r="AE6" s="643" t="n"/>
+      <c r="AF6" s="643" t="n"/>
+      <c r="AG6" s="643" t="n"/>
+      <c r="AH6" s="643" t="n"/>
+      <c r="AI6" s="643" t="n"/>
+      <c r="AJ6" s="643" t="n"/>
+      <c r="AK6" s="643" t="n"/>
+      <c r="AL6" s="643" t="n"/>
+      <c r="AM6" s="643" t="n"/>
+      <c r="AN6" s="643" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="548" t="inlineStr">
+      <c r="A7" s="644" t="inlineStr">
         <is>
           <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
         </is>
       </c>
-      <c r="B7" s="549" t="n"/>
-      <c r="C7" s="549" t="n"/>
-      <c r="D7" s="549" t="n"/>
-      <c r="E7" s="549" t="n"/>
-      <c r="F7" s="549" t="n"/>
-      <c r="G7" s="549" t="n"/>
-      <c r="H7" s="549" t="n"/>
-      <c r="I7" s="549" t="n"/>
-      <c r="J7" s="549" t="n"/>
-      <c r="K7" s="549" t="n"/>
-      <c r="L7" s="549" t="n"/>
-      <c r="M7" s="549" t="n"/>
-      <c r="N7" s="549" t="n"/>
-      <c r="O7" s="549" t="n"/>
-      <c r="P7" s="549" t="n"/>
-      <c r="Q7" s="549" t="n"/>
-      <c r="R7" s="549" t="n"/>
-      <c r="S7" s="549" t="n"/>
-      <c r="T7" s="549" t="n"/>
-      <c r="U7" s="549" t="n"/>
-      <c r="V7" s="549" t="n"/>
-      <c r="W7" s="549" t="n"/>
-      <c r="X7" s="549" t="n"/>
-      <c r="Y7" s="549" t="n"/>
-      <c r="Z7" s="549" t="n"/>
-      <c r="AA7" s="549" t="n"/>
-      <c r="AB7" s="549" t="n"/>
-      <c r="AC7" s="549" t="n"/>
-      <c r="AD7" s="549" t="n"/>
-      <c r="AE7" s="549" t="n"/>
-      <c r="AF7" s="549" t="n"/>
-      <c r="AG7" s="549" t="n"/>
-      <c r="AH7" s="549" t="n"/>
-      <c r="AI7" s="549" t="n"/>
-      <c r="AJ7" s="549" t="n"/>
-      <c r="AK7" s="549" t="n"/>
-      <c r="AL7" s="549" t="n"/>
-      <c r="AM7" s="549" t="n"/>
-      <c r="AN7" s="550" t="n"/>
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="27" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
+      <c r="H7" s="27" t="n"/>
+      <c r="I7" s="645" t="n"/>
+      <c r="J7" s="645" t="n"/>
+      <c r="K7" s="645" t="n"/>
+      <c r="L7" s="645" t="n"/>
+      <c r="M7" s="645" t="n"/>
+      <c r="N7" s="645" t="n"/>
+      <c r="O7" s="645" t="n"/>
+      <c r="P7" s="645" t="n"/>
+      <c r="Q7" s="645" t="n"/>
+      <c r="R7" s="645" t="n"/>
+      <c r="S7" s="645" t="n"/>
+      <c r="T7" s="645" t="n"/>
+      <c r="U7" s="645" t="n"/>
+      <c r="V7" s="645" t="n"/>
+      <c r="W7" s="645" t="n"/>
+      <c r="X7" s="645" t="n"/>
+      <c r="Y7" s="645" t="n"/>
+      <c r="Z7" s="645" t="n"/>
+      <c r="AA7" s="645" t="n"/>
+      <c r="AB7" s="645" t="n"/>
+      <c r="AC7" s="645" t="n"/>
+      <c r="AD7" s="645" t="n"/>
+      <c r="AE7" s="645" t="n"/>
+      <c r="AF7" s="645" t="n"/>
+      <c r="AG7" s="645" t="n"/>
+      <c r="AH7" s="645" t="n"/>
+      <c r="AI7" s="645" t="n"/>
+      <c r="AJ7" s="645" t="n"/>
+      <c r="AK7" s="645" t="n"/>
+      <c r="AL7" s="645" t="n"/>
+      <c r="AM7" s="645" t="n"/>
+      <c r="AN7" s="646" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="551" t="inlineStr">
+      <c r="A8" s="647" t="inlineStr">
         <is>
           <t>Parent Form</t>
         </is>
       </c>
-      <c r="B8" s="552" t="n"/>
-      <c r="C8" s="553" t="inlineStr">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="648" t="inlineStr">
         <is>
           <t>FRM-213 · RMA TRACKING LOG</t>
         </is>
       </c>
-      <c r="D8" s="552" t="n"/>
-      <c r="E8" s="554" t="inlineStr">
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="649" t="inlineStr">
         <is>
           <t>Support Tab</t>
         </is>
       </c>
-      <c r="F8" s="552" t="n"/>
-      <c r="G8" s="553" t="inlineStr">
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="648" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="H8" s="552" t="n"/>
-      <c r="I8" s="555" t="n"/>
-      <c r="J8" s="556" t="n"/>
-      <c r="K8" s="556" t="n"/>
-      <c r="L8" s="556" t="n"/>
-      <c r="M8" s="556" t="n"/>
-      <c r="N8" s="556" t="n"/>
-      <c r="O8" s="556" t="n"/>
-      <c r="P8" s="556" t="n"/>
-      <c r="Q8" s="556" t="n"/>
-      <c r="R8" s="556" t="n"/>
-      <c r="S8" s="556" t="n"/>
-      <c r="T8" s="556" t="n"/>
-      <c r="U8" s="556" t="n"/>
-      <c r="V8" s="556" t="n"/>
-      <c r="W8" s="556" t="n"/>
-      <c r="X8" s="556" t="n"/>
-      <c r="Y8" s="556" t="n"/>
-      <c r="Z8" s="556" t="n"/>
-      <c r="AA8" s="556" t="n"/>
-      <c r="AB8" s="556" t="n"/>
-      <c r="AC8" s="556" t="n"/>
-      <c r="AD8" s="556" t="n"/>
-      <c r="AE8" s="556" t="n"/>
-      <c r="AF8" s="556" t="n"/>
-      <c r="AG8" s="556" t="n"/>
-      <c r="AH8" s="556" t="n"/>
-      <c r="AI8" s="556" t="n"/>
-      <c r="AJ8" s="556" t="n"/>
-      <c r="AK8" s="556" t="n"/>
-      <c r="AL8" s="556" t="n"/>
-      <c r="AM8" s="556" t="n"/>
-      <c r="AN8" s="557" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="650" t="n"/>
+      <c r="J8" s="650" t="n"/>
+      <c r="K8" s="650" t="n"/>
+      <c r="L8" s="650" t="n"/>
+      <c r="M8" s="650" t="n"/>
+      <c r="N8" s="650" t="n"/>
+      <c r="O8" s="650" t="n"/>
+      <c r="P8" s="650" t="n"/>
+      <c r="Q8" s="650" t="n"/>
+      <c r="R8" s="650" t="n"/>
+      <c r="S8" s="650" t="n"/>
+      <c r="T8" s="650" t="n"/>
+      <c r="U8" s="650" t="n"/>
+      <c r="V8" s="650" t="n"/>
+      <c r="W8" s="650" t="n"/>
+      <c r="X8" s="650" t="n"/>
+      <c r="Y8" s="650" t="n"/>
+      <c r="Z8" s="650" t="n"/>
+      <c r="AA8" s="650" t="n"/>
+      <c r="AB8" s="650" t="n"/>
+      <c r="AC8" s="650" t="n"/>
+      <c r="AD8" s="650" t="n"/>
+      <c r="AE8" s="650" t="n"/>
+      <c r="AF8" s="650" t="n"/>
+      <c r="AG8" s="650" t="n"/>
+      <c r="AH8" s="650" t="n"/>
+      <c r="AI8" s="650" t="n"/>
+      <c r="AJ8" s="650" t="n"/>
+      <c r="AK8" s="650" t="n"/>
+      <c r="AL8" s="650" t="n"/>
+      <c r="AM8" s="650" t="n"/>
+      <c r="AN8" s="651" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="558" t="inlineStr">
+      <c r="A9" s="652" t="inlineStr">
         <is>
           <t>Tab Purpose</t>
         </is>
       </c>
-      <c r="B9" s="437" t="n"/>
-      <c r="C9" s="559" t="inlineStr">
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="653" t="inlineStr">
         <is>
           <t>Periodic review and closeout support sheet for the rolling workbook.</t>
         </is>
       </c>
-      <c r="D9" s="437" t="n"/>
-      <c r="E9" s="560" t="inlineStr">
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="654" t="inlineStr">
         <is>
           <t>Working Owner</t>
         </is>
       </c>
-      <c r="F9" s="437" t="n"/>
-      <c r="G9" s="559" t="inlineStr">
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="653" t="inlineStr">
         <is>
           <t>QA / Customer Service</t>
         </is>
       </c>
-      <c r="H9" s="437" t="n"/>
-      <c r="I9" s="561" t="n"/>
-      <c r="J9" s="446" t="n"/>
-      <c r="K9" s="446" t="n"/>
-      <c r="L9" s="446" t="n"/>
-      <c r="M9" s="446" t="n"/>
-      <c r="N9" s="446" t="n"/>
-      <c r="O9" s="446" t="n"/>
-      <c r="P9" s="446" t="n"/>
-      <c r="Q9" s="446" t="n"/>
-      <c r="R9" s="446" t="n"/>
-      <c r="S9" s="446" t="n"/>
-      <c r="T9" s="446" t="n"/>
-      <c r="U9" s="446" t="n"/>
-      <c r="V9" s="446" t="n"/>
-      <c r="W9" s="446" t="n"/>
-      <c r="X9" s="446" t="n"/>
-      <c r="Y9" s="446" t="n"/>
-      <c r="Z9" s="446" t="n"/>
-      <c r="AA9" s="446" t="n"/>
-      <c r="AB9" s="446" t="n"/>
-      <c r="AC9" s="446" t="n"/>
-      <c r="AD9" s="446" t="n"/>
-      <c r="AE9" s="446" t="n"/>
-      <c r="AF9" s="446" t="n"/>
-      <c r="AG9" s="446" t="n"/>
-      <c r="AH9" s="446" t="n"/>
-      <c r="AI9" s="446" t="n"/>
-      <c r="AJ9" s="446" t="n"/>
-      <c r="AK9" s="446" t="n"/>
-      <c r="AL9" s="446" t="n"/>
-      <c r="AM9" s="446" t="n"/>
-      <c r="AN9" s="562" t="n"/>
+      <c r="H9" s="13" t="n"/>
+      <c r="I9" s="655" t="n"/>
+      <c r="J9" s="655" t="n"/>
+      <c r="K9" s="655" t="n"/>
+      <c r="L9" s="655" t="n"/>
+      <c r="M9" s="655" t="n"/>
+      <c r="N9" s="655" t="n"/>
+      <c r="O9" s="655" t="n"/>
+      <c r="P9" s="655" t="n"/>
+      <c r="Q9" s="655" t="n"/>
+      <c r="R9" s="655" t="n"/>
+      <c r="S9" s="655" t="n"/>
+      <c r="T9" s="655" t="n"/>
+      <c r="U9" s="655" t="n"/>
+      <c r="V9" s="655" t="n"/>
+      <c r="W9" s="655" t="n"/>
+      <c r="X9" s="655" t="n"/>
+      <c r="Y9" s="655" t="n"/>
+      <c r="Z9" s="655" t="n"/>
+      <c r="AA9" s="655" t="n"/>
+      <c r="AB9" s="655" t="n"/>
+      <c r="AC9" s="655" t="n"/>
+      <c r="AD9" s="655" t="n"/>
+      <c r="AE9" s="655" t="n"/>
+      <c r="AF9" s="655" t="n"/>
+      <c r="AG9" s="655" t="n"/>
+      <c r="AH9" s="655" t="n"/>
+      <c r="AI9" s="655" t="n"/>
+      <c r="AJ9" s="655" t="n"/>
+      <c r="AK9" s="655" t="n"/>
+      <c r="AL9" s="655" t="n"/>
+      <c r="AM9" s="655" t="n"/>
+      <c r="AN9" s="656" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="558" t="inlineStr">
+      <c r="A10" s="652" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B10" s="437" t="n"/>
-      <c r="C10" s="559" t="inlineStr">
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="653" t="inlineStr">
         <is>
           <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
         </is>
       </c>
-      <c r="D10" s="437" t="n"/>
-      <c r="E10" s="560" t="inlineStr">
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="654" t="inlineStr">
         <is>
           <t>Reviewed By</t>
         </is>
       </c>
-      <c r="F10" s="437" t="n"/>
-      <c r="G10" s="559" t="inlineStr">
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="653" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
       </c>
-      <c r="H10" s="437" t="n"/>
-      <c r="I10" s="561" t="n"/>
-      <c r="J10" s="446" t="n"/>
-      <c r="K10" s="446" t="n"/>
-      <c r="L10" s="446" t="n"/>
-      <c r="M10" s="446" t="n"/>
-      <c r="N10" s="446" t="n"/>
-      <c r="O10" s="446" t="n"/>
-      <c r="P10" s="446" t="n"/>
-      <c r="Q10" s="446" t="n"/>
-      <c r="R10" s="446" t="n"/>
-      <c r="S10" s="446" t="n"/>
-      <c r="T10" s="446" t="n"/>
-      <c r="U10" s="446" t="n"/>
-      <c r="V10" s="446" t="n"/>
-      <c r="W10" s="446" t="n"/>
-      <c r="X10" s="446" t="n"/>
-      <c r="Y10" s="446" t="n"/>
-      <c r="Z10" s="446" t="n"/>
-      <c r="AA10" s="446" t="n"/>
-      <c r="AB10" s="446" t="n"/>
-      <c r="AC10" s="446" t="n"/>
-      <c r="AD10" s="446" t="n"/>
-      <c r="AE10" s="446" t="n"/>
-      <c r="AF10" s="446" t="n"/>
-      <c r="AG10" s="446" t="n"/>
-      <c r="AH10" s="446" t="n"/>
-      <c r="AI10" s="446" t="n"/>
-      <c r="AJ10" s="446" t="n"/>
-      <c r="AK10" s="446" t="n"/>
-      <c r="AL10" s="446" t="n"/>
-      <c r="AM10" s="446" t="n"/>
-      <c r="AN10" s="562" t="n"/>
+      <c r="H10" s="13" t="n"/>
+      <c r="I10" s="655" t="n"/>
+      <c r="J10" s="655" t="n"/>
+      <c r="K10" s="655" t="n"/>
+      <c r="L10" s="655" t="n"/>
+      <c r="M10" s="655" t="n"/>
+      <c r="N10" s="655" t="n"/>
+      <c r="O10" s="655" t="n"/>
+      <c r="P10" s="655" t="n"/>
+      <c r="Q10" s="655" t="n"/>
+      <c r="R10" s="655" t="n"/>
+      <c r="S10" s="655" t="n"/>
+      <c r="T10" s="655" t="n"/>
+      <c r="U10" s="655" t="n"/>
+      <c r="V10" s="655" t="n"/>
+      <c r="W10" s="655" t="n"/>
+      <c r="X10" s="655" t="n"/>
+      <c r="Y10" s="655" t="n"/>
+      <c r="Z10" s="655" t="n"/>
+      <c r="AA10" s="655" t="n"/>
+      <c r="AB10" s="655" t="n"/>
+      <c r="AC10" s="655" t="n"/>
+      <c r="AD10" s="655" t="n"/>
+      <c r="AE10" s="655" t="n"/>
+      <c r="AF10" s="655" t="n"/>
+      <c r="AG10" s="655" t="n"/>
+      <c r="AH10" s="655" t="n"/>
+      <c r="AI10" s="655" t="n"/>
+      <c r="AJ10" s="655" t="n"/>
+      <c r="AK10" s="655" t="n"/>
+      <c r="AL10" s="655" t="n"/>
+      <c r="AM10" s="655" t="n"/>
+      <c r="AN10" s="656" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="558" t="inlineStr">
+      <c r="A11" s="652" t="inlineStr">
         <is>
           <t>Update Trigger</t>
         </is>
       </c>
-      <c r="B11" s="437" t="n"/>
-      <c r="C11" s="559" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="653" t="inlineStr">
         <is>
           <t>Update when the linked review, evidence or follow-up status changes.</t>
         </is>
       </c>
-      <c r="D11" s="437" t="n"/>
-      <c r="E11" s="560" t="inlineStr">
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="654" t="inlineStr">
         <is>
           <t>Data Structure</t>
         </is>
       </c>
-      <c r="F11" s="437" t="n"/>
-      <c r="G11" s="559" t="inlineStr">
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="653" t="inlineStr">
         <is>
           <t>Structured Excel Table with filters and print-title rows.</t>
         </is>
       </c>
-      <c r="H11" s="437" t="n"/>
-      <c r="I11" s="563" t="n"/>
-      <c r="J11" s="437" t="n"/>
-      <c r="K11" s="437" t="n"/>
-      <c r="L11" s="437" t="n"/>
-      <c r="M11" s="437" t="n"/>
-      <c r="N11" s="437" t="n"/>
-      <c r="O11" s="437" t="n"/>
-      <c r="P11" s="437" t="n"/>
-      <c r="Q11" s="437" t="n"/>
-      <c r="R11" s="437" t="n"/>
-      <c r="S11" s="437" t="n"/>
-      <c r="T11" s="437" t="n"/>
-      <c r="U11" s="437" t="n"/>
-      <c r="V11" s="437" t="n"/>
-      <c r="W11" s="437" t="n"/>
-      <c r="X11" s="437" t="n"/>
-      <c r="Y11" s="437" t="n"/>
-      <c r="Z11" s="437" t="n"/>
-      <c r="AA11" s="437" t="n"/>
-      <c r="AB11" s="437" t="n"/>
-      <c r="AC11" s="437" t="n"/>
-      <c r="AD11" s="437" t="n"/>
-      <c r="AE11" s="437" t="n"/>
-      <c r="AF11" s="437" t="n"/>
-      <c r="AG11" s="437" t="n"/>
-      <c r="AH11" s="437" t="n"/>
-      <c r="AI11" s="437" t="n"/>
-      <c r="AJ11" s="437" t="n"/>
-      <c r="AK11" s="437" t="n"/>
-      <c r="AL11" s="437" t="n"/>
-      <c r="AM11" s="437" t="n"/>
-      <c r="AN11" s="564" t="n"/>
+      <c r="H11" s="13" t="n"/>
+      <c r="I11" s="657" t="n"/>
+      <c r="J11" s="657" t="n"/>
+      <c r="K11" s="657" t="n"/>
+      <c r="L11" s="657" t="n"/>
+      <c r="M11" s="657" t="n"/>
+      <c r="N11" s="657" t="n"/>
+      <c r="O11" s="657" t="n"/>
+      <c r="P11" s="657" t="n"/>
+      <c r="Q11" s="657" t="n"/>
+      <c r="R11" s="657" t="n"/>
+      <c r="S11" s="657" t="n"/>
+      <c r="T11" s="657" t="n"/>
+      <c r="U11" s="657" t="n"/>
+      <c r="V11" s="657" t="n"/>
+      <c r="W11" s="657" t="n"/>
+      <c r="X11" s="657" t="n"/>
+      <c r="Y11" s="657" t="n"/>
+      <c r="Z11" s="657" t="n"/>
+      <c r="AA11" s="657" t="n"/>
+      <c r="AB11" s="657" t="n"/>
+      <c r="AC11" s="657" t="n"/>
+      <c r="AD11" s="657" t="n"/>
+      <c r="AE11" s="657" t="n"/>
+      <c r="AF11" s="657" t="n"/>
+      <c r="AG11" s="657" t="n"/>
+      <c r="AH11" s="657" t="n"/>
+      <c r="AI11" s="657" t="n"/>
+      <c r="AJ11" s="657" t="n"/>
+      <c r="AK11" s="657" t="n"/>
+      <c r="AL11" s="657" t="n"/>
+      <c r="AM11" s="657" t="n"/>
+      <c r="AN11" s="658" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="565" t="inlineStr">
+      <c r="A12" s="659" t="inlineStr">
         <is>
           <t>Retention Rule</t>
         </is>
       </c>
-      <c r="B12" s="566" t="n"/>
-      <c r="C12" s="567" t="inlineStr">
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="660" t="inlineStr">
         <is>
           <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
         </is>
       </c>
-      <c r="D12" s="566" t="n"/>
-      <c r="E12" s="568" t="inlineStr">
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="661" t="inlineStr">
         <is>
           <t>Controlled Status</t>
         </is>
       </c>
-      <c r="F12" s="566" t="n"/>
-      <c r="G12" s="567" t="inlineStr">
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="660" t="inlineStr">
         <is>
           <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
         </is>
       </c>
-      <c r="H12" s="566" t="n"/>
-      <c r="I12" s="571" t="n"/>
-      <c r="J12" s="572" t="n"/>
-      <c r="K12" s="572" t="n"/>
-      <c r="L12" s="572" t="n"/>
-      <c r="M12" s="572" t="n"/>
-      <c r="N12" s="572" t="n"/>
-      <c r="O12" s="572" t="n"/>
-      <c r="P12" s="572" t="n"/>
-      <c r="Q12" s="572" t="n"/>
-      <c r="R12" s="572" t="n"/>
-      <c r="S12" s="572" t="n"/>
-      <c r="T12" s="572" t="n"/>
-      <c r="U12" s="572" t="n"/>
-      <c r="V12" s="572" t="n"/>
-      <c r="W12" s="572" t="n"/>
-      <c r="X12" s="572" t="n"/>
-      <c r="Y12" s="572" t="n"/>
-      <c r="Z12" s="572" t="n"/>
-      <c r="AA12" s="572" t="n"/>
-      <c r="AB12" s="572" t="n"/>
-      <c r="AC12" s="572" t="n"/>
-      <c r="AD12" s="572" t="n"/>
-      <c r="AE12" s="572" t="n"/>
-      <c r="AF12" s="572" t="n"/>
-      <c r="AG12" s="572" t="n"/>
-      <c r="AH12" s="572" t="n"/>
-      <c r="AI12" s="572" t="n"/>
-      <c r="AJ12" s="572" t="n"/>
-      <c r="AK12" s="572" t="n"/>
-      <c r="AL12" s="572" t="n"/>
-      <c r="AM12" s="572" t="n"/>
-      <c r="AN12" s="573" t="n"/>
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="666" t="n"/>
+      <c r="J12" s="666" t="n"/>
+      <c r="K12" s="666" t="n"/>
+      <c r="L12" s="666" t="n"/>
+      <c r="M12" s="666" t="n"/>
+      <c r="N12" s="666" t="n"/>
+      <c r="O12" s="666" t="n"/>
+      <c r="P12" s="666" t="n"/>
+      <c r="Q12" s="666" t="n"/>
+      <c r="R12" s="666" t="n"/>
+      <c r="S12" s="666" t="n"/>
+      <c r="T12" s="666" t="n"/>
+      <c r="U12" s="666" t="n"/>
+      <c r="V12" s="666" t="n"/>
+      <c r="W12" s="666" t="n"/>
+      <c r="X12" s="666" t="n"/>
+      <c r="Y12" s="666" t="n"/>
+      <c r="Z12" s="666" t="n"/>
+      <c r="AA12" s="666" t="n"/>
+      <c r="AB12" s="666" t="n"/>
+      <c r="AC12" s="666" t="n"/>
+      <c r="AD12" s="666" t="n"/>
+      <c r="AE12" s="666" t="n"/>
+      <c r="AF12" s="666" t="n"/>
+      <c r="AG12" s="666" t="n"/>
+      <c r="AH12" s="666" t="n"/>
+      <c r="AI12" s="666" t="n"/>
+      <c r="AJ12" s="666" t="n"/>
+      <c r="AK12" s="666" t="n"/>
+      <c r="AL12" s="666" t="n"/>
+      <c r="AM12" s="666" t="n"/>
+      <c r="AN12" s="667" t="n"/>
     </row>
     <row r="13" ht="3" customHeight="1">
-      <c r="A13" s="442" t="n"/>
-      <c r="B13" s="495" t="n"/>
-      <c r="C13" s="495" t="n"/>
-      <c r="D13" s="495" t="n"/>
-      <c r="E13" s="495" t="n"/>
-      <c r="F13" s="495" t="n"/>
-      <c r="G13" s="495" t="n"/>
-      <c r="H13" s="495" t="n"/>
-      <c r="I13" s="443" t="n"/>
-      <c r="J13" s="443" t="n"/>
-      <c r="K13" s="443" t="n"/>
-      <c r="L13" s="443" t="n"/>
-      <c r="M13" s="443" t="n"/>
-      <c r="N13" s="443" t="n"/>
-      <c r="O13" s="443" t="n"/>
-      <c r="P13" s="443" t="n"/>
-      <c r="Q13" s="443" t="n"/>
-      <c r="R13" s="443" t="n"/>
-      <c r="S13" s="443" t="n"/>
-      <c r="T13" s="443" t="n"/>
-      <c r="U13" s="443" t="n"/>
-      <c r="V13" s="443" t="n"/>
-      <c r="W13" s="443" t="n"/>
-      <c r="X13" s="443" t="n"/>
-      <c r="Y13" s="443" t="n"/>
-      <c r="Z13" s="443" t="n"/>
-      <c r="AA13" s="443" t="n"/>
-      <c r="AB13" s="443" t="n"/>
-      <c r="AC13" s="443" t="n"/>
-      <c r="AD13" s="443" t="n"/>
-      <c r="AE13" s="443" t="n"/>
-      <c r="AF13" s="443" t="n"/>
-      <c r="AG13" s="443" t="n"/>
-      <c r="AH13" s="443" t="n"/>
-      <c r="AI13" s="443" t="n"/>
-      <c r="AJ13" s="443" t="n"/>
-      <c r="AK13" s="443" t="n"/>
-      <c r="AL13" s="443" t="n"/>
-      <c r="AM13" s="443" t="n"/>
-      <c r="AN13" s="443" t="n"/>
+      <c r="A13" s="664" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="665" t="n"/>
+      <c r="J13" s="665" t="n"/>
+      <c r="K13" s="665" t="n"/>
+      <c r="L13" s="665" t="n"/>
+      <c r="M13" s="665" t="n"/>
+      <c r="N13" s="665" t="n"/>
+      <c r="O13" s="665" t="n"/>
+      <c r="P13" s="665" t="n"/>
+      <c r="Q13" s="665" t="n"/>
+      <c r="R13" s="665" t="n"/>
+      <c r="S13" s="665" t="n"/>
+      <c r="T13" s="665" t="n"/>
+      <c r="U13" s="665" t="n"/>
+      <c r="V13" s="665" t="n"/>
+      <c r="W13" s="665" t="n"/>
+      <c r="X13" s="665" t="n"/>
+      <c r="Y13" s="665" t="n"/>
+      <c r="Z13" s="665" t="n"/>
+      <c r="AA13" s="665" t="n"/>
+      <c r="AB13" s="665" t="n"/>
+      <c r="AC13" s="665" t="n"/>
+      <c r="AD13" s="665" t="n"/>
+      <c r="AE13" s="665" t="n"/>
+      <c r="AF13" s="665" t="n"/>
+      <c r="AG13" s="665" t="n"/>
+      <c r="AH13" s="665" t="n"/>
+      <c r="AI13" s="665" t="n"/>
+      <c r="AJ13" s="665" t="n"/>
+      <c r="AK13" s="665" t="n"/>
+      <c r="AL13" s="665" t="n"/>
+      <c r="AM13" s="665" t="n"/>
+      <c r="AN13" s="665" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="548" t="inlineStr">
+      <c r="A14" s="644" t="inlineStr">
         <is>
           <t>2.  WORKING TABLE / DETAIL LINES</t>
         </is>
       </c>
-      <c r="B14" s="549" t="n"/>
-      <c r="C14" s="549" t="n"/>
-      <c r="D14" s="549" t="n"/>
-      <c r="E14" s="549" t="n"/>
-      <c r="F14" s="549" t="n"/>
-      <c r="G14" s="549" t="n"/>
-      <c r="H14" s="549" t="n"/>
-      <c r="I14" s="549" t="n"/>
-      <c r="J14" s="549" t="n"/>
-      <c r="K14" s="549" t="n"/>
-      <c r="L14" s="549" t="n"/>
-      <c r="M14" s="549" t="n"/>
-      <c r="N14" s="549" t="n"/>
-      <c r="O14" s="549" t="n"/>
-      <c r="P14" s="549" t="n"/>
-      <c r="Q14" s="549" t="n"/>
-      <c r="R14" s="549" t="n"/>
-      <c r="S14" s="549" t="n"/>
-      <c r="T14" s="549" t="n"/>
-      <c r="U14" s="549" t="n"/>
-      <c r="V14" s="549" t="n"/>
-      <c r="W14" s="549" t="n"/>
-      <c r="X14" s="549" t="n"/>
-      <c r="Y14" s="549" t="n"/>
-      <c r="Z14" s="549" t="n"/>
-      <c r="AA14" s="549" t="n"/>
-      <c r="AB14" s="549" t="n"/>
-      <c r="AC14" s="549" t="n"/>
-      <c r="AD14" s="549" t="n"/>
-      <c r="AE14" s="549" t="n"/>
-      <c r="AF14" s="549" t="n"/>
-      <c r="AG14" s="549" t="n"/>
-      <c r="AH14" s="549" t="n"/>
-      <c r="AI14" s="549" t="n"/>
-      <c r="AJ14" s="549" t="n"/>
-      <c r="AK14" s="549" t="n"/>
-      <c r="AL14" s="549" t="n"/>
-      <c r="AM14" s="549" t="n"/>
-      <c r="AN14" s="550" t="n"/>
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="27" t="n"/>
+      <c r="H14" s="27" t="n"/>
+      <c r="I14" s="645" t="n"/>
+      <c r="J14" s="645" t="n"/>
+      <c r="K14" s="645" t="n"/>
+      <c r="L14" s="645" t="n"/>
+      <c r="M14" s="645" t="n"/>
+      <c r="N14" s="645" t="n"/>
+      <c r="O14" s="645" t="n"/>
+      <c r="P14" s="645" t="n"/>
+      <c r="Q14" s="645" t="n"/>
+      <c r="R14" s="645" t="n"/>
+      <c r="S14" s="645" t="n"/>
+      <c r="T14" s="645" t="n"/>
+      <c r="U14" s="645" t="n"/>
+      <c r="V14" s="645" t="n"/>
+      <c r="W14" s="645" t="n"/>
+      <c r="X14" s="645" t="n"/>
+      <c r="Y14" s="645" t="n"/>
+      <c r="Z14" s="645" t="n"/>
+      <c r="AA14" s="645" t="n"/>
+      <c r="AB14" s="645" t="n"/>
+      <c r="AC14" s="645" t="n"/>
+      <c r="AD14" s="645" t="n"/>
+      <c r="AE14" s="645" t="n"/>
+      <c r="AF14" s="645" t="n"/>
+      <c r="AG14" s="645" t="n"/>
+      <c r="AH14" s="645" t="n"/>
+      <c r="AI14" s="645" t="n"/>
+      <c r="AJ14" s="645" t="n"/>
+      <c r="AK14" s="645" t="n"/>
+      <c r="AL14" s="645" t="n"/>
+      <c r="AM14" s="645" t="n"/>
+      <c r="AN14" s="646" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="548" t="inlineStr">
+      <c r="A15" s="644" t="inlineStr">
         <is>
           <t>Periodic review and closeout support sheet for the rolling workbook.</t>
         </is>
       </c>
-      <c r="B15" s="549" t="n"/>
-      <c r="C15" s="549" t="n"/>
-      <c r="D15" s="549" t="n"/>
-      <c r="E15" s="549" t="n"/>
-      <c r="F15" s="549" t="n"/>
-      <c r="G15" s="549" t="n"/>
-      <c r="H15" s="549" t="n"/>
-      <c r="I15" s="549" t="n"/>
-      <c r="J15" s="549" t="n"/>
-      <c r="K15" s="549" t="n"/>
-      <c r="L15" s="549" t="n"/>
-      <c r="M15" s="549" t="n"/>
-      <c r="N15" s="549" t="n"/>
-      <c r="O15" s="549" t="n"/>
-      <c r="P15" s="549" t="n"/>
-      <c r="Q15" s="549" t="n"/>
-      <c r="R15" s="549" t="n"/>
-      <c r="S15" s="549" t="n"/>
-      <c r="T15" s="549" t="n"/>
-      <c r="U15" s="549" t="n"/>
-      <c r="V15" s="549" t="n"/>
-      <c r="W15" s="549" t="n"/>
-      <c r="X15" s="549" t="n"/>
-      <c r="Y15" s="549" t="n"/>
-      <c r="Z15" s="549" t="n"/>
-      <c r="AA15" s="549" t="n"/>
-      <c r="AB15" s="549" t="n"/>
-      <c r="AC15" s="549" t="n"/>
-      <c r="AD15" s="549" t="n"/>
-      <c r="AE15" s="549" t="n"/>
-      <c r="AF15" s="549" t="n"/>
-      <c r="AG15" s="549" t="n"/>
-      <c r="AH15" s="549" t="n"/>
-      <c r="AI15" s="549" t="n"/>
-      <c r="AJ15" s="549" t="n"/>
-      <c r="AK15" s="549" t="n"/>
-      <c r="AL15" s="549" t="n"/>
-      <c r="AM15" s="549" t="n"/>
-      <c r="AN15" s="550" t="n"/>
+      <c r="B15" s="27" t="n"/>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="27" t="n"/>
+      <c r="H15" s="27" t="n"/>
+      <c r="I15" s="645" t="n"/>
+      <c r="J15" s="645" t="n"/>
+      <c r="K15" s="645" t="n"/>
+      <c r="L15" s="645" t="n"/>
+      <c r="M15" s="645" t="n"/>
+      <c r="N15" s="645" t="n"/>
+      <c r="O15" s="645" t="n"/>
+      <c r="P15" s="645" t="n"/>
+      <c r="Q15" s="645" t="n"/>
+      <c r="R15" s="645" t="n"/>
+      <c r="S15" s="645" t="n"/>
+      <c r="T15" s="645" t="n"/>
+      <c r="U15" s="645" t="n"/>
+      <c r="V15" s="645" t="n"/>
+      <c r="W15" s="645" t="n"/>
+      <c r="X15" s="645" t="n"/>
+      <c r="Y15" s="645" t="n"/>
+      <c r="Z15" s="645" t="n"/>
+      <c r="AA15" s="645" t="n"/>
+      <c r="AB15" s="645" t="n"/>
+      <c r="AC15" s="645" t="n"/>
+      <c r="AD15" s="645" t="n"/>
+      <c r="AE15" s="645" t="n"/>
+      <c r="AF15" s="645" t="n"/>
+      <c r="AG15" s="645" t="n"/>
+      <c r="AH15" s="645" t="n"/>
+      <c r="AI15" s="645" t="n"/>
+      <c r="AJ15" s="645" t="n"/>
+      <c r="AK15" s="645" t="n"/>
+      <c r="AL15" s="645" t="n"/>
+      <c r="AM15" s="645" t="n"/>
+      <c r="AN15" s="646" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="574" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B16" s="575" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>Review Item</t>
         </is>
       </c>
-      <c r="C16" s="575" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>Expectation / Rule</t>
         </is>
       </c>
-      <c r="D16" s="575" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="E16" s="575" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="F16" s="575" t="inlineStr">
+      <c r="F16" s="37" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G16" s="575" t="inlineStr">
+      <c r="G16" s="37" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="H16" s="575" t="inlineStr">
+      <c r="H16" s="37" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="I16" s="575" t="n"/>
-      <c r="J16" s="575" t="n"/>
-      <c r="K16" s="575" t="n"/>
-      <c r="L16" s="575" t="n"/>
-      <c r="M16" s="575" t="n"/>
-      <c r="N16" s="575" t="n"/>
-      <c r="O16" s="575" t="n"/>
-      <c r="P16" s="575" t="n"/>
-      <c r="Q16" s="575" t="n"/>
-      <c r="R16" s="575" t="n"/>
-      <c r="S16" s="575" t="n"/>
-      <c r="T16" s="575" t="n"/>
-      <c r="U16" s="575" t="n"/>
-      <c r="V16" s="575" t="n"/>
-      <c r="W16" s="575" t="n"/>
-      <c r="X16" s="575" t="n"/>
-      <c r="Y16" s="575" t="n"/>
-      <c r="Z16" s="575" t="n"/>
-      <c r="AA16" s="575" t="n"/>
-      <c r="AB16" s="575" t="n"/>
-      <c r="AC16" s="575" t="n"/>
-      <c r="AD16" s="575" t="n"/>
-      <c r="AE16" s="575" t="n"/>
-      <c r="AF16" s="575" t="n"/>
-      <c r="AG16" s="575" t="n"/>
-      <c r="AH16" s="575" t="n"/>
-      <c r="AI16" s="575" t="n"/>
-      <c r="AJ16" s="575" t="n"/>
-      <c r="AK16" s="575" t="n"/>
-      <c r="AL16" s="575" t="n"/>
-      <c r="AM16" s="575" t="n"/>
-      <c r="AN16" s="576" t="n"/>
+      <c r="I16" s="37" t="n"/>
+      <c r="J16" s="37" t="n"/>
+      <c r="K16" s="37" t="n"/>
+      <c r="L16" s="37" t="n"/>
+      <c r="M16" s="37" t="n"/>
+      <c r="N16" s="37" t="n"/>
+      <c r="O16" s="37" t="n"/>
+      <c r="P16" s="37" t="n"/>
+      <c r="Q16" s="37" t="n"/>
+      <c r="R16" s="37" t="n"/>
+      <c r="S16" s="37" t="n"/>
+      <c r="T16" s="37" t="n"/>
+      <c r="U16" s="37" t="n"/>
+      <c r="V16" s="37" t="n"/>
+      <c r="W16" s="37" t="n"/>
+      <c r="X16" s="37" t="n"/>
+      <c r="Y16" s="37" t="n"/>
+      <c r="Z16" s="37" t="n"/>
+      <c r="AA16" s="37" t="n"/>
+      <c r="AB16" s="37" t="n"/>
+      <c r="AC16" s="37" t="n"/>
+      <c r="AD16" s="37" t="n"/>
+      <c r="AE16" s="37" t="n"/>
+      <c r="AF16" s="37" t="n"/>
+      <c r="AG16" s="37" t="n"/>
+      <c r="AH16" s="37" t="n"/>
+      <c r="AI16" s="37" t="n"/>
+      <c r="AJ16" s="37" t="n"/>
+      <c r="AK16" s="37" t="n"/>
+      <c r="AL16" s="37" t="n"/>
+      <c r="AM16" s="37" t="n"/>
+      <c r="AN16" s="668" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="577">
+      <c r="A17" s="669">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B17" s="553" t="n"/>
-      <c r="C17" s="579" t="n"/>
-      <c r="D17" s="579" t="n"/>
-      <c r="E17" s="603" t="n"/>
-      <c r="F17" s="579" t="n"/>
-      <c r="G17" s="579" t="n"/>
-      <c r="H17" s="579" t="n"/>
-      <c r="I17" s="556" t="n"/>
-      <c r="J17" s="556" t="n"/>
-      <c r="K17" s="556" t="n"/>
-      <c r="L17" s="556" t="n"/>
-      <c r="M17" s="556" t="n"/>
-      <c r="N17" s="556" t="n"/>
-      <c r="O17" s="556" t="n"/>
-      <c r="P17" s="556" t="n"/>
-      <c r="Q17" s="556" t="n"/>
-      <c r="R17" s="556" t="n"/>
-      <c r="S17" s="556" t="n"/>
-      <c r="T17" s="556" t="n"/>
-      <c r="U17" s="556" t="n"/>
-      <c r="V17" s="556" t="n"/>
-      <c r="W17" s="556" t="n"/>
-      <c r="X17" s="556" t="n"/>
-      <c r="Y17" s="556" t="n"/>
-      <c r="Z17" s="556" t="n"/>
-      <c r="AA17" s="556" t="n"/>
-      <c r="AB17" s="556" t="n"/>
-      <c r="AC17" s="556" t="n"/>
-      <c r="AD17" s="556" t="n"/>
-      <c r="AE17" s="556" t="n"/>
-      <c r="AF17" s="556" t="n"/>
-      <c r="AG17" s="556" t="n"/>
-      <c r="AH17" s="556" t="n"/>
-      <c r="AI17" s="556" t="n"/>
-      <c r="AJ17" s="556" t="n"/>
-      <c r="AK17" s="556" t="n"/>
-      <c r="AL17" s="556" t="n"/>
-      <c r="AM17" s="556" t="n"/>
-      <c r="AN17" s="557" t="n"/>
+      <c r="B17" s="648" t="n"/>
+      <c r="C17" s="648" t="n"/>
+      <c r="D17" s="648" t="n"/>
+      <c r="E17" s="686" t="n"/>
+      <c r="F17" s="648" t="n"/>
+      <c r="G17" s="648" t="n"/>
+      <c r="H17" s="648" t="n"/>
+      <c r="I17" s="650" t="n"/>
+      <c r="J17" s="650" t="n"/>
+      <c r="K17" s="650" t="n"/>
+      <c r="L17" s="650" t="n"/>
+      <c r="M17" s="650" t="n"/>
+      <c r="N17" s="650" t="n"/>
+      <c r="O17" s="650" t="n"/>
+      <c r="P17" s="650" t="n"/>
+      <c r="Q17" s="650" t="n"/>
+      <c r="R17" s="650" t="n"/>
+      <c r="S17" s="650" t="n"/>
+      <c r="T17" s="650" t="n"/>
+      <c r="U17" s="650" t="n"/>
+      <c r="V17" s="650" t="n"/>
+      <c r="W17" s="650" t="n"/>
+      <c r="X17" s="650" t="n"/>
+      <c r="Y17" s="650" t="n"/>
+      <c r="Z17" s="650" t="n"/>
+      <c r="AA17" s="650" t="n"/>
+      <c r="AB17" s="650" t="n"/>
+      <c r="AC17" s="650" t="n"/>
+      <c r="AD17" s="650" t="n"/>
+      <c r="AE17" s="650" t="n"/>
+      <c r="AF17" s="650" t="n"/>
+      <c r="AG17" s="650" t="n"/>
+      <c r="AH17" s="650" t="n"/>
+      <c r="AI17" s="650" t="n"/>
+      <c r="AJ17" s="650" t="n"/>
+      <c r="AK17" s="650" t="n"/>
+      <c r="AL17" s="650" t="n"/>
+      <c r="AM17" s="650" t="n"/>
+      <c r="AN17" s="651" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="580">
+      <c r="A18" s="671">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B18" s="458" t="n"/>
-      <c r="C18" s="581" t="n"/>
-      <c r="D18" s="581" t="n"/>
-      <c r="E18" s="604" t="n"/>
-      <c r="F18" s="581" t="n"/>
-      <c r="G18" s="581" t="n"/>
-      <c r="H18" s="581" t="n"/>
-      <c r="I18" s="446" t="n"/>
-      <c r="J18" s="446" t="n"/>
-      <c r="K18" s="446" t="n"/>
-      <c r="L18" s="446" t="n"/>
-      <c r="M18" s="446" t="n"/>
-      <c r="N18" s="446" t="n"/>
-      <c r="O18" s="446" t="n"/>
-      <c r="P18" s="446" t="n"/>
-      <c r="Q18" s="446" t="n"/>
-      <c r="R18" s="446" t="n"/>
-      <c r="S18" s="446" t="n"/>
-      <c r="T18" s="446" t="n"/>
-      <c r="U18" s="446" t="n"/>
-      <c r="V18" s="446" t="n"/>
-      <c r="W18" s="446" t="n"/>
-      <c r="X18" s="446" t="n"/>
-      <c r="Y18" s="446" t="n"/>
-      <c r="Z18" s="446" t="n"/>
-      <c r="AA18" s="446" t="n"/>
-      <c r="AB18" s="446" t="n"/>
-      <c r="AC18" s="446" t="n"/>
-      <c r="AD18" s="446" t="n"/>
-      <c r="AE18" s="446" t="n"/>
-      <c r="AF18" s="446" t="n"/>
-      <c r="AG18" s="446" t="n"/>
-      <c r="AH18" s="446" t="n"/>
-      <c r="AI18" s="446" t="n"/>
-      <c r="AJ18" s="446" t="n"/>
-      <c r="AK18" s="446" t="n"/>
-      <c r="AL18" s="446" t="n"/>
-      <c r="AM18" s="446" t="n"/>
-      <c r="AN18" s="562" t="n"/>
+      <c r="B18" s="673" t="n"/>
+      <c r="C18" s="673" t="n"/>
+      <c r="D18" s="673" t="n"/>
+      <c r="E18" s="687" t="n"/>
+      <c r="F18" s="673" t="n"/>
+      <c r="G18" s="673" t="n"/>
+      <c r="H18" s="673" t="n"/>
+      <c r="I18" s="655" t="n"/>
+      <c r="J18" s="655" t="n"/>
+      <c r="K18" s="655" t="n"/>
+      <c r="L18" s="655" t="n"/>
+      <c r="M18" s="655" t="n"/>
+      <c r="N18" s="655" t="n"/>
+      <c r="O18" s="655" t="n"/>
+      <c r="P18" s="655" t="n"/>
+      <c r="Q18" s="655" t="n"/>
+      <c r="R18" s="655" t="n"/>
+      <c r="S18" s="655" t="n"/>
+      <c r="T18" s="655" t="n"/>
+      <c r="U18" s="655" t="n"/>
+      <c r="V18" s="655" t="n"/>
+      <c r="W18" s="655" t="n"/>
+      <c r="X18" s="655" t="n"/>
+      <c r="Y18" s="655" t="n"/>
+      <c r="Z18" s="655" t="n"/>
+      <c r="AA18" s="655" t="n"/>
+      <c r="AB18" s="655" t="n"/>
+      <c r="AC18" s="655" t="n"/>
+      <c r="AD18" s="655" t="n"/>
+      <c r="AE18" s="655" t="n"/>
+      <c r="AF18" s="655" t="n"/>
+      <c r="AG18" s="655" t="n"/>
+      <c r="AH18" s="655" t="n"/>
+      <c r="AI18" s="655" t="n"/>
+      <c r="AJ18" s="655" t="n"/>
+      <c r="AK18" s="655" t="n"/>
+      <c r="AL18" s="655" t="n"/>
+      <c r="AM18" s="655" t="n"/>
+      <c r="AN18" s="656" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="580">
+      <c r="A19" s="671">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B19" s="559" t="n"/>
-      <c r="C19" s="583" t="n"/>
-      <c r="D19" s="583" t="n"/>
-      <c r="E19" s="605" t="n"/>
-      <c r="F19" s="583" t="n"/>
-      <c r="G19" s="583" t="n"/>
-      <c r="H19" s="583" t="n"/>
-      <c r="I19" s="446" t="n"/>
-      <c r="J19" s="446" t="n"/>
-      <c r="K19" s="446" t="n"/>
-      <c r="L19" s="446" t="n"/>
-      <c r="M19" s="446" t="n"/>
-      <c r="N19" s="446" t="n"/>
-      <c r="O19" s="446" t="n"/>
-      <c r="P19" s="446" t="n"/>
-      <c r="Q19" s="446" t="n"/>
-      <c r="R19" s="446" t="n"/>
-      <c r="S19" s="446" t="n"/>
-      <c r="T19" s="446" t="n"/>
-      <c r="U19" s="446" t="n"/>
-      <c r="V19" s="446" t="n"/>
-      <c r="W19" s="446" t="n"/>
-      <c r="X19" s="446" t="n"/>
-      <c r="Y19" s="446" t="n"/>
-      <c r="Z19" s="446" t="n"/>
-      <c r="AA19" s="446" t="n"/>
-      <c r="AB19" s="446" t="n"/>
-      <c r="AC19" s="446" t="n"/>
-      <c r="AD19" s="446" t="n"/>
-      <c r="AE19" s="446" t="n"/>
-      <c r="AF19" s="446" t="n"/>
-      <c r="AG19" s="446" t="n"/>
-      <c r="AH19" s="446" t="n"/>
-      <c r="AI19" s="446" t="n"/>
-      <c r="AJ19" s="446" t="n"/>
-      <c r="AK19" s="446" t="n"/>
-      <c r="AL19" s="446" t="n"/>
-      <c r="AM19" s="446" t="n"/>
-      <c r="AN19" s="562" t="n"/>
+      <c r="B19" s="653" t="n"/>
+      <c r="C19" s="653" t="n"/>
+      <c r="D19" s="653" t="n"/>
+      <c r="E19" s="688" t="n"/>
+      <c r="F19" s="653" t="n"/>
+      <c r="G19" s="653" t="n"/>
+      <c r="H19" s="653" t="n"/>
+      <c r="I19" s="655" t="n"/>
+      <c r="J19" s="655" t="n"/>
+      <c r="K19" s="655" t="n"/>
+      <c r="L19" s="655" t="n"/>
+      <c r="M19" s="655" t="n"/>
+      <c r="N19" s="655" t="n"/>
+      <c r="O19" s="655" t="n"/>
+      <c r="P19" s="655" t="n"/>
+      <c r="Q19" s="655" t="n"/>
+      <c r="R19" s="655" t="n"/>
+      <c r="S19" s="655" t="n"/>
+      <c r="T19" s="655" t="n"/>
+      <c r="U19" s="655" t="n"/>
+      <c r="V19" s="655" t="n"/>
+      <c r="W19" s="655" t="n"/>
+      <c r="X19" s="655" t="n"/>
+      <c r="Y19" s="655" t="n"/>
+      <c r="Z19" s="655" t="n"/>
+      <c r="AA19" s="655" t="n"/>
+      <c r="AB19" s="655" t="n"/>
+      <c r="AC19" s="655" t="n"/>
+      <c r="AD19" s="655" t="n"/>
+      <c r="AE19" s="655" t="n"/>
+      <c r="AF19" s="655" t="n"/>
+      <c r="AG19" s="655" t="n"/>
+      <c r="AH19" s="655" t="n"/>
+      <c r="AI19" s="655" t="n"/>
+      <c r="AJ19" s="655" t="n"/>
+      <c r="AK19" s="655" t="n"/>
+      <c r="AL19" s="655" t="n"/>
+      <c r="AM19" s="655" t="n"/>
+      <c r="AN19" s="656" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="580">
+      <c r="A20" s="671">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B20" s="458" t="n"/>
-      <c r="C20" s="581" t="n"/>
-      <c r="D20" s="581" t="n"/>
-      <c r="E20" s="604" t="n"/>
-      <c r="F20" s="581" t="n"/>
-      <c r="G20" s="581" t="n"/>
-      <c r="H20" s="581" t="n"/>
-      <c r="I20" s="446" t="n"/>
-      <c r="J20" s="446" t="n"/>
-      <c r="K20" s="446" t="n"/>
-      <c r="L20" s="446" t="n"/>
-      <c r="M20" s="446" t="n"/>
-      <c r="N20" s="446" t="n"/>
-      <c r="O20" s="446" t="n"/>
-      <c r="P20" s="446" t="n"/>
-      <c r="Q20" s="446" t="n"/>
-      <c r="R20" s="446" t="n"/>
-      <c r="S20" s="446" t="n"/>
-      <c r="T20" s="446" t="n"/>
-      <c r="U20" s="446" t="n"/>
-      <c r="V20" s="446" t="n"/>
-      <c r="W20" s="446" t="n"/>
-      <c r="X20" s="446" t="n"/>
-      <c r="Y20" s="446" t="n"/>
-      <c r="Z20" s="446" t="n"/>
-      <c r="AA20" s="446" t="n"/>
-      <c r="AB20" s="446" t="n"/>
-      <c r="AC20" s="446" t="n"/>
-      <c r="AD20" s="446" t="n"/>
-      <c r="AE20" s="446" t="n"/>
-      <c r="AF20" s="446" t="n"/>
-      <c r="AG20" s="446" t="n"/>
-      <c r="AH20" s="446" t="n"/>
-      <c r="AI20" s="446" t="n"/>
-      <c r="AJ20" s="446" t="n"/>
-      <c r="AK20" s="446" t="n"/>
-      <c r="AL20" s="446" t="n"/>
-      <c r="AM20" s="446" t="n"/>
-      <c r="AN20" s="562" t="n"/>
+      <c r="B20" s="673" t="n"/>
+      <c r="C20" s="673" t="n"/>
+      <c r="D20" s="673" t="n"/>
+      <c r="E20" s="687" t="n"/>
+      <c r="F20" s="673" t="n"/>
+      <c r="G20" s="673" t="n"/>
+      <c r="H20" s="673" t="n"/>
+      <c r="I20" s="655" t="n"/>
+      <c r="J20" s="655" t="n"/>
+      <c r="K20" s="655" t="n"/>
+      <c r="L20" s="655" t="n"/>
+      <c r="M20" s="655" t="n"/>
+      <c r="N20" s="655" t="n"/>
+      <c r="O20" s="655" t="n"/>
+      <c r="P20" s="655" t="n"/>
+      <c r="Q20" s="655" t="n"/>
+      <c r="R20" s="655" t="n"/>
+      <c r="S20" s="655" t="n"/>
+      <c r="T20" s="655" t="n"/>
+      <c r="U20" s="655" t="n"/>
+      <c r="V20" s="655" t="n"/>
+      <c r="W20" s="655" t="n"/>
+      <c r="X20" s="655" t="n"/>
+      <c r="Y20" s="655" t="n"/>
+      <c r="Z20" s="655" t="n"/>
+      <c r="AA20" s="655" t="n"/>
+      <c r="AB20" s="655" t="n"/>
+      <c r="AC20" s="655" t="n"/>
+      <c r="AD20" s="655" t="n"/>
+      <c r="AE20" s="655" t="n"/>
+      <c r="AF20" s="655" t="n"/>
+      <c r="AG20" s="655" t="n"/>
+      <c r="AH20" s="655" t="n"/>
+      <c r="AI20" s="655" t="n"/>
+      <c r="AJ20" s="655" t="n"/>
+      <c r="AK20" s="655" t="n"/>
+      <c r="AL20" s="655" t="n"/>
+      <c r="AM20" s="655" t="n"/>
+      <c r="AN20" s="656" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="580">
+      <c r="A21" s="671">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B21" s="559" t="n"/>
-      <c r="C21" s="583" t="n"/>
-      <c r="D21" s="583" t="n"/>
-      <c r="E21" s="605" t="n"/>
-      <c r="F21" s="583" t="n"/>
-      <c r="G21" s="583" t="n"/>
-      <c r="H21" s="583" t="n"/>
-      <c r="I21" s="446" t="n"/>
-      <c r="J21" s="446" t="n"/>
-      <c r="K21" s="446" t="n"/>
-      <c r="L21" s="446" t="n"/>
-      <c r="M21" s="446" t="n"/>
-      <c r="N21" s="446" t="n"/>
-      <c r="O21" s="446" t="n"/>
-      <c r="P21" s="446" t="n"/>
-      <c r="Q21" s="446" t="n"/>
-      <c r="R21" s="446" t="n"/>
-      <c r="S21" s="446" t="n"/>
-      <c r="T21" s="446" t="n"/>
-      <c r="U21" s="446" t="n"/>
-      <c r="V21" s="446" t="n"/>
-      <c r="W21" s="446" t="n"/>
-      <c r="X21" s="446" t="n"/>
-      <c r="Y21" s="446" t="n"/>
-      <c r="Z21" s="446" t="n"/>
-      <c r="AA21" s="446" t="n"/>
-      <c r="AB21" s="446" t="n"/>
-      <c r="AC21" s="446" t="n"/>
-      <c r="AD21" s="446" t="n"/>
-      <c r="AE21" s="446" t="n"/>
-      <c r="AF21" s="446" t="n"/>
-      <c r="AG21" s="446" t="n"/>
-      <c r="AH21" s="446" t="n"/>
-      <c r="AI21" s="446" t="n"/>
-      <c r="AJ21" s="446" t="n"/>
-      <c r="AK21" s="446" t="n"/>
-      <c r="AL21" s="446" t="n"/>
-      <c r="AM21" s="446" t="n"/>
-      <c r="AN21" s="562" t="n"/>
+      <c r="B21" s="653" t="n"/>
+      <c r="C21" s="653" t="n"/>
+      <c r="D21" s="653" t="n"/>
+      <c r="E21" s="688" t="n"/>
+      <c r="F21" s="653" t="n"/>
+      <c r="G21" s="653" t="n"/>
+      <c r="H21" s="653" t="n"/>
+      <c r="I21" s="655" t="n"/>
+      <c r="J21" s="655" t="n"/>
+      <c r="K21" s="655" t="n"/>
+      <c r="L21" s="655" t="n"/>
+      <c r="M21" s="655" t="n"/>
+      <c r="N21" s="655" t="n"/>
+      <c r="O21" s="655" t="n"/>
+      <c r="P21" s="655" t="n"/>
+      <c r="Q21" s="655" t="n"/>
+      <c r="R21" s="655" t="n"/>
+      <c r="S21" s="655" t="n"/>
+      <c r="T21" s="655" t="n"/>
+      <c r="U21" s="655" t="n"/>
+      <c r="V21" s="655" t="n"/>
+      <c r="W21" s="655" t="n"/>
+      <c r="X21" s="655" t="n"/>
+      <c r="Y21" s="655" t="n"/>
+      <c r="Z21" s="655" t="n"/>
+      <c r="AA21" s="655" t="n"/>
+      <c r="AB21" s="655" t="n"/>
+      <c r="AC21" s="655" t="n"/>
+      <c r="AD21" s="655" t="n"/>
+      <c r="AE21" s="655" t="n"/>
+      <c r="AF21" s="655" t="n"/>
+      <c r="AG21" s="655" t="n"/>
+      <c r="AH21" s="655" t="n"/>
+      <c r="AI21" s="655" t="n"/>
+      <c r="AJ21" s="655" t="n"/>
+      <c r="AK21" s="655" t="n"/>
+      <c r="AL21" s="655" t="n"/>
+      <c r="AM21" s="655" t="n"/>
+      <c r="AN21" s="656" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="580">
+      <c r="A22" s="671">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B22" s="458" t="n"/>
-      <c r="C22" s="581" t="n"/>
-      <c r="D22" s="581" t="n"/>
-      <c r="E22" s="604" t="n"/>
-      <c r="F22" s="581" t="n"/>
-      <c r="G22" s="581" t="n"/>
-      <c r="H22" s="581" t="n"/>
-      <c r="I22" s="446" t="n"/>
-      <c r="J22" s="446" t="n"/>
-      <c r="K22" s="446" t="n"/>
-      <c r="L22" s="446" t="n"/>
-      <c r="M22" s="446" t="n"/>
-      <c r="N22" s="446" t="n"/>
-      <c r="O22" s="446" t="n"/>
-      <c r="P22" s="446" t="n"/>
-      <c r="Q22" s="446" t="n"/>
-      <c r="R22" s="446" t="n"/>
-      <c r="S22" s="446" t="n"/>
-      <c r="T22" s="446" t="n"/>
-      <c r="U22" s="446" t="n"/>
-      <c r="V22" s="446" t="n"/>
-      <c r="W22" s="446" t="n"/>
-      <c r="X22" s="446" t="n"/>
-      <c r="Y22" s="446" t="n"/>
-      <c r="Z22" s="446" t="n"/>
-      <c r="AA22" s="446" t="n"/>
-      <c r="AB22" s="446" t="n"/>
-      <c r="AC22" s="446" t="n"/>
-      <c r="AD22" s="446" t="n"/>
-      <c r="AE22" s="446" t="n"/>
-      <c r="AF22" s="446" t="n"/>
-      <c r="AG22" s="446" t="n"/>
-      <c r="AH22" s="446" t="n"/>
-      <c r="AI22" s="446" t="n"/>
-      <c r="AJ22" s="446" t="n"/>
-      <c r="AK22" s="446" t="n"/>
-      <c r="AL22" s="446" t="n"/>
-      <c r="AM22" s="446" t="n"/>
-      <c r="AN22" s="562" t="n"/>
+      <c r="B22" s="673" t="n"/>
+      <c r="C22" s="673" t="n"/>
+      <c r="D22" s="673" t="n"/>
+      <c r="E22" s="687" t="n"/>
+      <c r="F22" s="673" t="n"/>
+      <c r="G22" s="673" t="n"/>
+      <c r="H22" s="673" t="n"/>
+      <c r="I22" s="655" t="n"/>
+      <c r="J22" s="655" t="n"/>
+      <c r="K22" s="655" t="n"/>
+      <c r="L22" s="655" t="n"/>
+      <c r="M22" s="655" t="n"/>
+      <c r="N22" s="655" t="n"/>
+      <c r="O22" s="655" t="n"/>
+      <c r="P22" s="655" t="n"/>
+      <c r="Q22" s="655" t="n"/>
+      <c r="R22" s="655" t="n"/>
+      <c r="S22" s="655" t="n"/>
+      <c r="T22" s="655" t="n"/>
+      <c r="U22" s="655" t="n"/>
+      <c r="V22" s="655" t="n"/>
+      <c r="W22" s="655" t="n"/>
+      <c r="X22" s="655" t="n"/>
+      <c r="Y22" s="655" t="n"/>
+      <c r="Z22" s="655" t="n"/>
+      <c r="AA22" s="655" t="n"/>
+      <c r="AB22" s="655" t="n"/>
+      <c r="AC22" s="655" t="n"/>
+      <c r="AD22" s="655" t="n"/>
+      <c r="AE22" s="655" t="n"/>
+      <c r="AF22" s="655" t="n"/>
+      <c r="AG22" s="655" t="n"/>
+      <c r="AH22" s="655" t="n"/>
+      <c r="AI22" s="655" t="n"/>
+      <c r="AJ22" s="655" t="n"/>
+      <c r="AK22" s="655" t="n"/>
+      <c r="AL22" s="655" t="n"/>
+      <c r="AM22" s="655" t="n"/>
+      <c r="AN22" s="656" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="580">
+      <c r="A23" s="671">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B23" s="559" t="n"/>
-      <c r="C23" s="583" t="n"/>
-      <c r="D23" s="583" t="n"/>
-      <c r="E23" s="605" t="n"/>
-      <c r="F23" s="583" t="n"/>
-      <c r="G23" s="583" t="n"/>
-      <c r="H23" s="583" t="n"/>
-      <c r="I23" s="446" t="n"/>
-      <c r="J23" s="446" t="n"/>
-      <c r="K23" s="446" t="n"/>
-      <c r="L23" s="446" t="n"/>
-      <c r="M23" s="446" t="n"/>
-      <c r="N23" s="446" t="n"/>
-      <c r="O23" s="446" t="n"/>
-      <c r="P23" s="446" t="n"/>
-      <c r="Q23" s="446" t="n"/>
-      <c r="R23" s="446" t="n"/>
-      <c r="S23" s="446" t="n"/>
-      <c r="T23" s="446" t="n"/>
-      <c r="U23" s="446" t="n"/>
-      <c r="V23" s="446" t="n"/>
-      <c r="W23" s="446" t="n"/>
-      <c r="X23" s="446" t="n"/>
-      <c r="Y23" s="446" t="n"/>
-      <c r="Z23" s="446" t="n"/>
-      <c r="AA23" s="446" t="n"/>
-      <c r="AB23" s="446" t="n"/>
-      <c r="AC23" s="446" t="n"/>
-      <c r="AD23" s="446" t="n"/>
-      <c r="AE23" s="446" t="n"/>
-      <c r="AF23" s="446" t="n"/>
-      <c r="AG23" s="446" t="n"/>
-      <c r="AH23" s="446" t="n"/>
-      <c r="AI23" s="446" t="n"/>
-      <c r="AJ23" s="446" t="n"/>
-      <c r="AK23" s="446" t="n"/>
-      <c r="AL23" s="446" t="n"/>
-      <c r="AM23" s="446" t="n"/>
-      <c r="AN23" s="562" t="n"/>
+      <c r="B23" s="653" t="n"/>
+      <c r="C23" s="653" t="n"/>
+      <c r="D23" s="653" t="n"/>
+      <c r="E23" s="688" t="n"/>
+      <c r="F23" s="653" t="n"/>
+      <c r="G23" s="653" t="n"/>
+      <c r="H23" s="653" t="n"/>
+      <c r="I23" s="655" t="n"/>
+      <c r="J23" s="655" t="n"/>
+      <c r="K23" s="655" t="n"/>
+      <c r="L23" s="655" t="n"/>
+      <c r="M23" s="655" t="n"/>
+      <c r="N23" s="655" t="n"/>
+      <c r="O23" s="655" t="n"/>
+      <c r="P23" s="655" t="n"/>
+      <c r="Q23" s="655" t="n"/>
+      <c r="R23" s="655" t="n"/>
+      <c r="S23" s="655" t="n"/>
+      <c r="T23" s="655" t="n"/>
+      <c r="U23" s="655" t="n"/>
+      <c r="V23" s="655" t="n"/>
+      <c r="W23" s="655" t="n"/>
+      <c r="X23" s="655" t="n"/>
+      <c r="Y23" s="655" t="n"/>
+      <c r="Z23" s="655" t="n"/>
+      <c r="AA23" s="655" t="n"/>
+      <c r="AB23" s="655" t="n"/>
+      <c r="AC23" s="655" t="n"/>
+      <c r="AD23" s="655" t="n"/>
+      <c r="AE23" s="655" t="n"/>
+      <c r="AF23" s="655" t="n"/>
+      <c r="AG23" s="655" t="n"/>
+      <c r="AH23" s="655" t="n"/>
+      <c r="AI23" s="655" t="n"/>
+      <c r="AJ23" s="655" t="n"/>
+      <c r="AK23" s="655" t="n"/>
+      <c r="AL23" s="655" t="n"/>
+      <c r="AM23" s="655" t="n"/>
+      <c r="AN23" s="656" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="580">
+      <c r="A24" s="671">
         <f>ROW()-ROW($A$17)+1</f>
         <v/>
       </c>
-      <c r="B24" s="458" t="n"/>
-      <c r="C24" s="581" t="n"/>
-      <c r="D24" s="581" t="n"/>
-      <c r="E24" s="604" t="n"/>
-      <c r="F24" s="581" t="n"/>
-      <c r="G24" s="581" t="n"/>
-      <c r="H24" s="581" t="n"/>
-      <c r="I24" s="446" t="n"/>
-      <c r="J24" s="446" t="n"/>
-      <c r="K24" s="446" t="n"/>
-      <c r="L24" s="446" t="n"/>
-      <c r="M24" s="446" t="n"/>
-      <c r="N24" s="446" t="n"/>
-      <c r="O24" s="446" t="n"/>
-      <c r="P24" s="446" t="n"/>
-      <c r="Q24" s="446" t="n"/>
-      <c r="R24" s="446" t="n"/>
-      <c r="S24" s="446" t="n"/>
-      <c r="T24" s="446" t="n"/>
-      <c r="U24" s="446" t="n"/>
-      <c r="V24" s="446" t="n"/>
-      <c r="W24" s="446" t="n"/>
-      <c r="X24" s="446" t="n"/>
-      <c r="Y24" s="446" t="n"/>
-      <c r="Z24" s="446" t="n"/>
-      <c r="AA24" s="446" t="n"/>
-      <c r="AB24" s="446" t="n"/>
-      <c r="AC24" s="446" t="n"/>
-      <c r="AD24" s="446" t="n"/>
-      <c r="AE24" s="446" t="n"/>
-      <c r="AF24" s="446" t="n"/>
-      <c r="AG24" s="446" t="n"/>
-      <c r="AH24" s="446" t="n"/>
-      <c r="AI24" s="446" t="n"/>
-      <c r="AJ24" s="446" t="n"/>
-      <c r="AK24" s="446" t="n"/>
-      <c r="AL24" s="446" t="n"/>
-      <c r="AM24" s="446" t="n"/>
-      <c r="AN24" s="562" t="n"/>
+      <c r="B24" s="673" t="n"/>
+      <c r="C24" s="673" t="n"/>
+      <c r="D24" s="673" t="n"/>
+      <c r="E24" s="687" t="n"/>
+      <c r="F24" s="673" t="n"/>
+      <c r="G24" s="673" t="n"/>
+      <c r="H24" s="673" t="n"/>
+      <c r="I24" s="655" t="n"/>
+      <c r="J24" s="655" t="n"/>
+      <c r="K24" s="655" t="n"/>
+      <c r="L24" s="655" t="n"/>
+      <c r="M24" s="655" t="n"/>
+      <c r="N24" s="655" t="n"/>
+      <c r="O24" s="655" t="n"/>
+      <c r="P24" s="655" t="n"/>
+      <c r="Q24" s="655" t="n"/>
+      <c r="R24" s="655" t="n"/>
+      <c r="S24" s="655" t="n"/>
+      <c r="T24" s="655" t="n"/>
+      <c r="U24" s="655" t="n"/>
+      <c r="V24" s="655" t="n"/>
+      <c r="W24" s="655" t="n"/>
+      <c r="X24" s="655" t="n"/>
+      <c r="Y24" s="655" t="n"/>
+      <c r="Z24" s="655" t="n"/>
+      <c r="AA24" s="655" t="n"/>
+      <c r="AB24" s="655" t="n"/>
+      <c r="AC24" s="655" t="n"/>
+      <c r="AD24" s="655" t="n"/>
+      <c r="AE24" s="655" t="n"/>
+      <c r="AF24" s="655" t="n"/>
+      <c r="AG24" s="655" t="n"/>
+      <c r="AH24" s="655" t="n"/>
+      <c r="AI24" s="655" t="n"/>
+      <c r="AJ24" s="655" t="n"/>
+      <c r="AK24" s="655" t="n"/>
+      <c r="AL24" s="655" t="n"/>
+      <c r="AM24" s="655" t="n"/>
+      <c r="AN24" s="656" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="596" t="n"/>
-      <c r="B25" s="571" t="n"/>
-      <c r="C25" s="572" t="n"/>
-      <c r="D25" s="572" t="n"/>
-      <c r="E25" s="572" t="n"/>
-      <c r="F25" s="572" t="n"/>
-      <c r="G25" s="572" t="n"/>
-      <c r="H25" s="572" t="n"/>
-      <c r="I25" s="572" t="n"/>
-      <c r="J25" s="572" t="n"/>
-      <c r="K25" s="572" t="n"/>
-      <c r="L25" s="572" t="n"/>
-      <c r="M25" s="572" t="n"/>
-      <c r="N25" s="572" t="n"/>
-      <c r="O25" s="572" t="n"/>
-      <c r="P25" s="572" t="n"/>
-      <c r="Q25" s="572" t="n"/>
-      <c r="R25" s="572" t="n"/>
-      <c r="S25" s="572" t="n"/>
-      <c r="T25" s="572" t="n"/>
-      <c r="U25" s="572" t="n"/>
-      <c r="V25" s="572" t="n"/>
-      <c r="W25" s="572" t="n"/>
-      <c r="X25" s="572" t="n"/>
-      <c r="Y25" s="572" t="n"/>
-      <c r="Z25" s="572" t="n"/>
-      <c r="AA25" s="572" t="n"/>
-      <c r="AB25" s="572" t="n"/>
-      <c r="AC25" s="572" t="n"/>
-      <c r="AD25" s="572" t="n"/>
-      <c r="AE25" s="572" t="n"/>
-      <c r="AF25" s="572" t="n"/>
-      <c r="AG25" s="572" t="n"/>
-      <c r="AH25" s="572" t="n"/>
-      <c r="AI25" s="572" t="n"/>
-      <c r="AJ25" s="572" t="n"/>
-      <c r="AK25" s="572" t="n"/>
-      <c r="AL25" s="572" t="n"/>
-      <c r="AM25" s="572" t="n"/>
-      <c r="AN25" s="573" t="n"/>
+      <c r="A25" s="689" t="n"/>
+      <c r="B25" s="666" t="n"/>
+      <c r="C25" s="666" t="n"/>
+      <c r="D25" s="666" t="n"/>
+      <c r="E25" s="666" t="n"/>
+      <c r="F25" s="666" t="n"/>
+      <c r="G25" s="666" t="n"/>
+      <c r="H25" s="666" t="n"/>
+      <c r="I25" s="666" t="n"/>
+      <c r="J25" s="666" t="n"/>
+      <c r="K25" s="666" t="n"/>
+      <c r="L25" s="666" t="n"/>
+      <c r="M25" s="666" t="n"/>
+      <c r="N25" s="666" t="n"/>
+      <c r="O25" s="666" t="n"/>
+      <c r="P25" s="666" t="n"/>
+      <c r="Q25" s="666" t="n"/>
+      <c r="R25" s="666" t="n"/>
+      <c r="S25" s="666" t="n"/>
+      <c r="T25" s="666" t="n"/>
+      <c r="U25" s="666" t="n"/>
+      <c r="V25" s="666" t="n"/>
+      <c r="W25" s="666" t="n"/>
+      <c r="X25" s="666" t="n"/>
+      <c r="Y25" s="666" t="n"/>
+      <c r="Z25" s="666" t="n"/>
+      <c r="AA25" s="666" t="n"/>
+      <c r="AB25" s="666" t="n"/>
+      <c r="AC25" s="666" t="n"/>
+      <c r="AD25" s="666" t="n"/>
+      <c r="AE25" s="666" t="n"/>
+      <c r="AF25" s="666" t="n"/>
+      <c r="AG25" s="666" t="n"/>
+      <c r="AH25" s="666" t="n"/>
+      <c r="AI25" s="666" t="n"/>
+      <c r="AJ25" s="666" t="n"/>
+      <c r="AK25" s="666" t="n"/>
+      <c r="AL25" s="666" t="n"/>
+      <c r="AM25" s="666" t="n"/>
+      <c r="AN25" s="667" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="548" t="inlineStr">
+      <c r="A26" s="644" t="inlineStr">
         <is>
           <t>NOTICE  —  Periodic review and closeout support sheet for the rolling workbook.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B26" s="549" t="n"/>
-      <c r="C26" s="549" t="n"/>
-      <c r="D26" s="549" t="n"/>
-      <c r="E26" s="549" t="n"/>
-      <c r="F26" s="549" t="n"/>
-      <c r="G26" s="549" t="n"/>
-      <c r="H26" s="549" t="n"/>
-      <c r="I26" s="549" t="n"/>
-      <c r="J26" s="549" t="n"/>
-      <c r="K26" s="549" t="n"/>
-      <c r="L26" s="549" t="n"/>
-      <c r="M26" s="549" t="n"/>
-      <c r="N26" s="549" t="n"/>
-      <c r="O26" s="549" t="n"/>
-      <c r="P26" s="549" t="n"/>
-      <c r="Q26" s="549" t="n"/>
-      <c r="R26" s="549" t="n"/>
-      <c r="S26" s="549" t="n"/>
-      <c r="T26" s="549" t="n"/>
-      <c r="U26" s="549" t="n"/>
-      <c r="V26" s="549" t="n"/>
-      <c r="W26" s="549" t="n"/>
-      <c r="X26" s="549" t="n"/>
-      <c r="Y26" s="549" t="n"/>
-      <c r="Z26" s="549" t="n"/>
-      <c r="AA26" s="549" t="n"/>
-      <c r="AB26" s="549" t="n"/>
-      <c r="AC26" s="549" t="n"/>
-      <c r="AD26" s="549" t="n"/>
-      <c r="AE26" s="549" t="n"/>
-      <c r="AF26" s="549" t="n"/>
-      <c r="AG26" s="549" t="n"/>
-      <c r="AH26" s="549" t="n"/>
-      <c r="AI26" s="549" t="n"/>
-      <c r="AJ26" s="549" t="n"/>
-      <c r="AK26" s="549" t="n"/>
-      <c r="AL26" s="549" t="n"/>
-      <c r="AM26" s="549" t="n"/>
-      <c r="AN26" s="550" t="n"/>
+      <c r="B26" s="27" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="27" t="n"/>
+      <c r="G26" s="27" t="n"/>
+      <c r="H26" s="27" t="n"/>
+      <c r="I26" s="645" t="n"/>
+      <c r="J26" s="645" t="n"/>
+      <c r="K26" s="645" t="n"/>
+      <c r="L26" s="645" t="n"/>
+      <c r="M26" s="645" t="n"/>
+      <c r="N26" s="645" t="n"/>
+      <c r="O26" s="645" t="n"/>
+      <c r="P26" s="645" t="n"/>
+      <c r="Q26" s="645" t="n"/>
+      <c r="R26" s="645" t="n"/>
+      <c r="S26" s="645" t="n"/>
+      <c r="T26" s="645" t="n"/>
+      <c r="U26" s="645" t="n"/>
+      <c r="V26" s="645" t="n"/>
+      <c r="W26" s="645" t="n"/>
+      <c r="X26" s="645" t="n"/>
+      <c r="Y26" s="645" t="n"/>
+      <c r="Z26" s="645" t="n"/>
+      <c r="AA26" s="645" t="n"/>
+      <c r="AB26" s="645" t="n"/>
+      <c r="AC26" s="645" t="n"/>
+      <c r="AD26" s="645" t="n"/>
+      <c r="AE26" s="645" t="n"/>
+      <c r="AF26" s="645" t="n"/>
+      <c r="AG26" s="645" t="n"/>
+      <c r="AH26" s="645" t="n"/>
+      <c r="AI26" s="645" t="n"/>
+      <c r="AJ26" s="645" t="n"/>
+      <c r="AK26" s="645" t="n"/>
+      <c r="AL26" s="645" t="n"/>
+      <c r="AM26" s="645" t="n"/>
+      <c r="AN26" s="646" t="n"/>
     </row>
     <row r="27" hidden="1" outlineLevel="1"/>
     <row r="28" hidden="1" outlineLevel="1"/>
@@ -11725,7 +12077,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CFRM-213  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
+    <oddFooter>&amp;C&amp;"Segoe UI"&amp;7 FRM-213  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -11744,7 +12096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:CU11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -11795,12 +12147,12 @@
           <t>REF_LINKS</t>
         </is>
       </c>
-      <c r="B1" s="506" t="n"/>
-      <c r="C1" s="506" t="n"/>
-      <c r="D1" s="506" t="n"/>
-      <c r="E1" s="506" t="n"/>
-      <c r="F1" s="506" t="n"/>
-      <c r="G1" s="506" t="n"/>
+      <c r="B1" s="690" t="n"/>
+      <c r="C1" s="690" t="n"/>
+      <c r="D1" s="690" t="n"/>
+      <c r="E1" s="690" t="n"/>
+      <c r="F1" s="690" t="n"/>
+      <c r="G1" s="690" t="n"/>
       <c r="H1" s="607" t="n"/>
       <c r="I1" s="509" t="n"/>
       <c r="J1" s="510" t="n"/>
@@ -11841,12 +12193,6 @@
           <t>Reference Epicor / M365 / controlled documents only.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="609" t="n"/>
       <c r="I2" s="520" t="n"/>
       <c r="J2" s="521" t="n"/>

--- a/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
@@ -4,10 +4,10 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM-213_LOG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="veryHidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVIEW" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_STATUS_CORE">'_LISTS'!$A$2:$A$7</definedName>
@@ -4558,7 +4558,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="691">
+  <cellXfs count="704">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6266,6 +6266,43 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="335" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -6364,6 +6401,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6394,6 +6434,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6710,18 +6753,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="339" t="n"/>
-      <c r="B1" s="53" t="n"/>
+      <c r="A1" s="413" t="n"/>
+      <c r="B1" s="310" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
           <t>RMA TRACKING LOG</t>
         </is>
       </c>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
+      <c r="D1" s="268" t="n"/>
+      <c r="E1" s="268" t="n"/>
+      <c r="F1" s="268" t="n"/>
+      <c r="G1" s="268" t="n"/>
+      <c r="H1" s="268" t="n"/>
       <c r="I1" s="623" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -6764,14 +6807,9 @@
       <c r="AN1" s="627" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="B2" s="54" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
+      <c r="A2" s="275" t="n"/>
+      <c r="B2" s="312" t="n"/>
+      <c r="C2" s="275" t="n"/>
       <c r="I2" s="628" t="inlineStr">
         <is>
           <t>Revision</t>
@@ -6814,14 +6852,9 @@
       <c r="AN2" s="632" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="B3" s="54" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
+      <c r="A3" s="275" t="n"/>
+      <c r="B3" s="312" t="n"/>
+      <c r="C3" s="275" t="n"/>
       <c r="I3" s="628" t="inlineStr">
         <is>
           <t>Eff. Date</t>
@@ -6864,18 +6897,13 @@
       <c r="AN3" s="632" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="B4" s="54" t="n"/>
+      <c r="A4" s="275" t="n"/>
+      <c r="B4" s="312" t="n"/>
       <c r="C4" s="633" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="10" t="n"/>
       <c r="I4" s="634" t="inlineStr">
         <is>
           <t>Owner</t>
@@ -6918,18 +6946,18 @@
       <c r="AN4" s="632" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="24" t="n"/>
+      <c r="A5" s="282" t="n"/>
+      <c r="B5" s="287" t="n"/>
       <c r="C5" s="636" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="19" t="n"/>
-      <c r="H5" s="19" t="n"/>
+      <c r="D5" s="283" t="n"/>
+      <c r="E5" s="283" t="n"/>
+      <c r="F5" s="283" t="n"/>
+      <c r="G5" s="283" t="n"/>
+      <c r="H5" s="283" t="n"/>
       <c r="I5" s="637" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7019,15 +7047,15 @@
           <t>1.  RMA HEADER</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
+      <c r="B7" s="289" t="n"/>
+      <c r="C7" s="289" t="n"/>
+      <c r="D7" s="289" t="n"/>
+      <c r="E7" s="289" t="n"/>
+      <c r="F7" s="289" t="n"/>
+      <c r="G7" s="289" t="n"/>
+      <c r="H7" s="289" t="n"/>
+      <c r="I7" s="289" t="n"/>
+      <c r="J7" s="289" t="n"/>
       <c r="K7" s="645" t="n"/>
       <c r="L7" s="645" t="n"/>
       <c r="M7" s="645" t="n"/>
@@ -7060,24 +7088,24 @@
       <c r="AN7" s="646" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="647" t="inlineStr">
+      <c r="A8" s="691" t="inlineStr">
         <is>
           <t>Open Period</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="648" t="inlineStr"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="649" t="inlineStr">
+      <c r="B8" s="272" t="n"/>
+      <c r="C8" s="330" t="inlineStr"/>
+      <c r="D8" s="271" t="n"/>
+      <c r="E8" s="272" t="n"/>
+      <c r="F8" s="692" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="648" t="inlineStr"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="6" t="n"/>
+      <c r="G8" s="272" t="n"/>
+      <c r="H8" s="330" t="inlineStr"/>
+      <c r="I8" s="271" t="n"/>
+      <c r="J8" s="272" t="n"/>
       <c r="K8" s="650" t="n"/>
       <c r="L8" s="650" t="n"/>
       <c r="M8" s="650" t="n"/>
@@ -7110,24 +7138,24 @@
       <c r="AN8" s="651" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="652" t="inlineStr">
+      <c r="A9" s="693" t="inlineStr">
         <is>
           <t>RMA Owner</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="653" t="inlineStr"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="654" t="inlineStr">
+      <c r="B9" s="278" t="n"/>
+      <c r="C9" s="694" t="inlineStr"/>
+      <c r="D9" s="277" t="n"/>
+      <c r="E9" s="278" t="n"/>
+      <c r="F9" s="695" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="653" t="inlineStr"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="13" t="n"/>
+      <c r="G9" s="278" t="n"/>
+      <c r="H9" s="694" t="inlineStr"/>
+      <c r="I9" s="277" t="n"/>
+      <c r="J9" s="278" t="n"/>
       <c r="K9" s="655" t="n"/>
       <c r="L9" s="655" t="n"/>
       <c r="M9" s="655" t="n"/>
@@ -7160,24 +7188,24 @@
       <c r="AN9" s="656" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="652" t="inlineStr">
+      <c r="A10" s="693" t="inlineStr">
         <is>
           <t>Evidence Folder</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="653" t="inlineStr"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="654" t="inlineStr">
+      <c r="B10" s="278" t="n"/>
+      <c r="C10" s="694" t="inlineStr"/>
+      <c r="D10" s="277" t="n"/>
+      <c r="E10" s="278" t="n"/>
+      <c r="F10" s="695" t="inlineStr">
         <is>
           <t>Returned Qty / Condition</t>
         </is>
       </c>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="653" t="inlineStr"/>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="13" t="n"/>
+      <c r="G10" s="278" t="n"/>
+      <c r="H10" s="694" t="inlineStr"/>
+      <c r="I10" s="277" t="n"/>
+      <c r="J10" s="278" t="n"/>
       <c r="K10" s="655" t="n"/>
       <c r="L10" s="655" t="n"/>
       <c r="M10" s="655" t="n"/>
@@ -7210,24 +7238,24 @@
       <c r="AN10" s="656" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="652" t="inlineStr">
+      <c r="A11" s="693" t="inlineStr">
         <is>
           <t>Receipt Ref. / Date</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="653" t="inlineStr"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="654" t="inlineStr">
+      <c r="B11" s="278" t="n"/>
+      <c r="C11" s="694" t="inlineStr"/>
+      <c r="D11" s="277" t="n"/>
+      <c r="E11" s="278" t="n"/>
+      <c r="F11" s="695" t="inlineStr">
         <is>
           <t>Evaluation Owner</t>
         </is>
       </c>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="653" t="inlineStr"/>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="13" t="n"/>
+      <c r="G11" s="278" t="n"/>
+      <c r="H11" s="694" t="inlineStr"/>
+      <c r="I11" s="277" t="n"/>
+      <c r="J11" s="278" t="n"/>
       <c r="K11" s="657" t="n"/>
       <c r="L11" s="657" t="n"/>
       <c r="M11" s="657" t="n"/>
@@ -7260,24 +7288,24 @@
       <c r="AN11" s="658" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="659" t="inlineStr">
+      <c r="A12" s="696" t="inlineStr">
         <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="660" t="inlineStr"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="22" t="n"/>
-      <c r="F12" s="661" t="inlineStr">
+      <c r="B12" s="285" t="n"/>
+      <c r="C12" s="697" t="inlineStr"/>
+      <c r="D12" s="283" t="n"/>
+      <c r="E12" s="285" t="n"/>
+      <c r="F12" s="698" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="G12" s="22" t="n"/>
-      <c r="H12" s="660" t="inlineStr"/>
-      <c r="I12" s="19" t="n"/>
-      <c r="J12" s="22" t="n"/>
+      <c r="G12" s="285" t="n"/>
+      <c r="H12" s="697" t="inlineStr"/>
+      <c r="I12" s="283" t="n"/>
+      <c r="J12" s="285" t="n"/>
       <c r="K12" s="662" t="n"/>
       <c r="L12" s="662" t="n"/>
       <c r="M12" s="662" t="n"/>
@@ -7357,15 +7385,15 @@
           <t>2.  RECEIPT AND EVALUATION SECTION</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="27" t="n"/>
-      <c r="I14" s="27" t="n"/>
-      <c r="J14" s="27" t="n"/>
+      <c r="B14" s="289" t="n"/>
+      <c r="C14" s="289" t="n"/>
+      <c r="D14" s="289" t="n"/>
+      <c r="E14" s="289" t="n"/>
+      <c r="F14" s="289" t="n"/>
+      <c r="G14" s="289" t="n"/>
+      <c r="H14" s="289" t="n"/>
+      <c r="I14" s="289" t="n"/>
+      <c r="J14" s="289" t="n"/>
       <c r="K14" s="645" t="n"/>
       <c r="L14" s="645" t="n"/>
       <c r="M14" s="645" t="n"/>
@@ -7398,24 +7426,24 @@
       <c r="AN14" s="646" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="647" t="inlineStr">
+      <c r="A15" s="691" t="inlineStr">
         <is>
           <t>Current Scope</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="648" t="inlineStr"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="649" t="inlineStr">
+      <c r="B15" s="272" t="n"/>
+      <c r="C15" s="330" t="inlineStr"/>
+      <c r="D15" s="271" t="n"/>
+      <c r="E15" s="272" t="n"/>
+      <c r="F15" s="692" t="inlineStr">
         <is>
           <t>Disposition Summary</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="648" t="inlineStr"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="6" t="n"/>
+      <c r="G15" s="272" t="n"/>
+      <c r="H15" s="330" t="inlineStr"/>
+      <c r="I15" s="271" t="n"/>
+      <c r="J15" s="272" t="n"/>
       <c r="K15" s="650" t="n"/>
       <c r="L15" s="650" t="n"/>
       <c r="M15" s="650" t="n"/>
@@ -7448,24 +7476,24 @@
       <c r="AN15" s="651" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="652" t="inlineStr">
+      <c r="A16" s="693" t="inlineStr">
         <is>
           <t>Primary Return / Defect Note</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="653" t="inlineStr"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="654" t="inlineStr">
+      <c r="B16" s="278" t="n"/>
+      <c r="C16" s="694" t="inlineStr"/>
+      <c r="D16" s="277" t="n"/>
+      <c r="E16" s="278" t="n"/>
+      <c r="F16" s="695" t="inlineStr">
         <is>
           <t>Next Review</t>
         </is>
       </c>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="653" t="inlineStr"/>
-      <c r="I16" s="12" t="n"/>
-      <c r="J16" s="13" t="n"/>
+      <c r="G16" s="278" t="n"/>
+      <c r="H16" s="694" t="inlineStr"/>
+      <c r="I16" s="277" t="n"/>
+      <c r="J16" s="278" t="n"/>
       <c r="K16" s="655" t="n"/>
       <c r="L16" s="655" t="n"/>
       <c r="M16" s="655" t="n"/>
@@ -7498,24 +7526,24 @@
       <c r="AN16" s="656" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="652" t="inlineStr">
+      <c r="A17" s="693" t="inlineStr">
         <is>
           <t>Action Owner</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="653" t="inlineStr"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="654" t="inlineStr">
+      <c r="B17" s="278" t="n"/>
+      <c r="C17" s="694" t="inlineStr"/>
+      <c r="D17" s="277" t="n"/>
+      <c r="E17" s="278" t="n"/>
+      <c r="F17" s="695" t="inlineStr">
         <is>
           <t>Next Review Date</t>
         </is>
       </c>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="653" t="inlineStr"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="13" t="n"/>
+      <c r="G17" s="278" t="n"/>
+      <c r="H17" s="694" t="inlineStr"/>
+      <c r="I17" s="277" t="n"/>
+      <c r="J17" s="278" t="n"/>
       <c r="K17" s="655" t="n"/>
       <c r="L17" s="655" t="n"/>
       <c r="M17" s="655" t="n"/>
@@ -7548,24 +7576,24 @@
       <c r="AN17" s="656" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="659" t="inlineStr">
+      <c r="A18" s="696" t="inlineStr">
         <is>
           <t>Escalation if Not Disposed</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="660" t="inlineStr"/>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="22" t="n"/>
-      <c r="F18" s="661" t="inlineStr">
+      <c r="B18" s="285" t="n"/>
+      <c r="C18" s="697" t="inlineStr"/>
+      <c r="D18" s="283" t="n"/>
+      <c r="E18" s="285" t="n"/>
+      <c r="F18" s="698" t="inlineStr">
         <is>
           <t>Overall Status</t>
         </is>
       </c>
-      <c r="G18" s="22" t="n"/>
-      <c r="H18" s="660" t="inlineStr"/>
-      <c r="I18" s="19" t="n"/>
-      <c r="J18" s="22" t="n"/>
+      <c r="G18" s="285" t="n"/>
+      <c r="H18" s="697" t="inlineStr"/>
+      <c r="I18" s="283" t="n"/>
+      <c r="J18" s="285" t="n"/>
       <c r="K18" s="666" t="n"/>
       <c r="L18" s="666" t="n"/>
       <c r="M18" s="666" t="n"/>
@@ -7645,15 +7673,15 @@
           <t>3.  DISPOSITION SECTION</t>
         </is>
       </c>
-      <c r="B20" s="27" t="n"/>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="27" t="n"/>
-      <c r="H20" s="27" t="n"/>
-      <c r="I20" s="27" t="n"/>
-      <c r="J20" s="27" t="n"/>
+      <c r="B20" s="289" t="n"/>
+      <c r="C20" s="289" t="n"/>
+      <c r="D20" s="289" t="n"/>
+      <c r="E20" s="289" t="n"/>
+      <c r="F20" s="289" t="n"/>
+      <c r="G20" s="289" t="n"/>
+      <c r="H20" s="289" t="n"/>
+      <c r="I20" s="289" t="n"/>
+      <c r="J20" s="289" t="n"/>
       <c r="K20" s="645" t="n"/>
       <c r="L20" s="645" t="n"/>
       <c r="M20" s="645" t="n"/>
@@ -8625,15 +8653,15 @@
           <t>4.  CLOSURE AND EVIDENCE SECTION</t>
         </is>
       </c>
-      <c r="B41" s="27" t="n"/>
-      <c r="C41" s="27" t="n"/>
-      <c r="D41" s="27" t="n"/>
-      <c r="E41" s="27" t="n"/>
-      <c r="F41" s="27" t="n"/>
-      <c r="G41" s="27" t="n"/>
-      <c r="H41" s="27" t="n"/>
-      <c r="I41" s="27" t="n"/>
-      <c r="J41" s="27" t="n"/>
+      <c r="B41" s="289" t="n"/>
+      <c r="C41" s="289" t="n"/>
+      <c r="D41" s="289" t="n"/>
+      <c r="E41" s="289" t="n"/>
+      <c r="F41" s="289" t="n"/>
+      <c r="G41" s="289" t="n"/>
+      <c r="H41" s="289" t="n"/>
+      <c r="I41" s="289" t="n"/>
+      <c r="J41" s="289" t="n"/>
       <c r="K41" s="645" t="n"/>
       <c r="L41" s="645" t="n"/>
       <c r="M41" s="645" t="n"/>
@@ -8666,28 +8694,28 @@
       <c r="AN41" s="646" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="678" t="inlineStr">
+      <c r="A42" s="699" t="inlineStr">
         <is>
           <t>Periodic review</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="679" t="inlineStr">
+      <c r="B42" s="271" t="n"/>
+      <c r="C42" s="272" t="n"/>
+      <c r="D42" s="700" t="inlineStr">
         <is>
           <t>Open items / escalation</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="6" t="n"/>
-      <c r="G42" s="679" t="inlineStr">
+      <c r="E42" s="271" t="n"/>
+      <c r="F42" s="272" t="n"/>
+      <c r="G42" s="700" t="inlineStr">
         <is>
           <t>Approval / archive</t>
         </is>
       </c>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="6" t="n"/>
+      <c r="H42" s="271" t="n"/>
+      <c r="I42" s="271" t="n"/>
+      <c r="J42" s="272" t="n"/>
       <c r="K42" s="650" t="n"/>
       <c r="L42" s="650" t="n"/>
       <c r="M42" s="650" t="n"/>
@@ -8720,30 +8748,26 @@
       <c r="AN42" s="651" t="n"/>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="213" t="inlineStr">
+      <c r="A43" s="701" t="inlineStr">
         <is>
           <t>Return-material tracking memory only; formal quality investigation remains in linked quality records.
 Review owner: _____________________________________________</t>
         </is>
       </c>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="13" t="n"/>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="C43" s="702" t="n"/>
+      <c r="D43" s="296" t="inlineStr">
         <is>
           <t>Final evidence ref: ________________________________________
 Outstanding items / actions: ________________________________</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="13" t="n"/>
-      <c r="G43" s="196" t="inlineStr">
+      <c r="F43" s="702" t="n"/>
+      <c r="G43" s="703" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="H43" s="12" t="n"/>
-      <c r="I43" s="12" t="n"/>
-      <c r="J43" s="13" t="n"/>
+      <c r="J43" s="702" t="n"/>
       <c r="K43" s="655" t="n"/>
       <c r="L43" s="655" t="n"/>
       <c r="M43" s="655" t="n"/>
@@ -8776,16 +8800,10 @@
       <c r="AN43" s="656" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="16" t="n"/>
-      <c r="B44" s="12" t="n"/>
-      <c r="C44" s="13" t="n"/>
-      <c r="D44" s="12" t="n"/>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="12" t="n"/>
-      <c r="H44" s="12" t="n"/>
-      <c r="I44" s="12" t="n"/>
-      <c r="J44" s="13" t="n"/>
+      <c r="A44" s="275" t="n"/>
+      <c r="C44" s="702" t="n"/>
+      <c r="F44" s="702" t="n"/>
+      <c r="J44" s="702" t="n"/>
       <c r="K44" s="655" t="n"/>
       <c r="L44" s="655" t="n"/>
       <c r="M44" s="655" t="n"/>
@@ -8818,16 +8836,10 @@
       <c r="AN44" s="656" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="16" t="n"/>
-      <c r="B45" s="12" t="n"/>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="12" t="n"/>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="13" t="n"/>
-      <c r="G45" s="12" t="n"/>
-      <c r="H45" s="12" t="n"/>
-      <c r="I45" s="12" t="n"/>
-      <c r="J45" s="13" t="n"/>
+      <c r="A45" s="275" t="n"/>
+      <c r="C45" s="702" t="n"/>
+      <c r="F45" s="702" t="n"/>
+      <c r="J45" s="702" t="n"/>
       <c r="K45" s="655" t="n"/>
       <c r="L45" s="655" t="n"/>
       <c r="M45" s="655" t="n"/>
@@ -8860,16 +8872,16 @@
       <c r="AN45" s="656" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="18" t="n"/>
-      <c r="B46" s="19" t="n"/>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="19" t="n"/>
-      <c r="E46" s="19" t="n"/>
-      <c r="F46" s="22" t="n"/>
-      <c r="G46" s="19" t="n"/>
-      <c r="H46" s="19" t="n"/>
-      <c r="I46" s="19" t="n"/>
-      <c r="J46" s="22" t="n"/>
+      <c r="A46" s="281" t="n"/>
+      <c r="B46" s="277" t="n"/>
+      <c r="C46" s="278" t="n"/>
+      <c r="D46" s="277" t="n"/>
+      <c r="E46" s="277" t="n"/>
+      <c r="F46" s="278" t="n"/>
+      <c r="G46" s="277" t="n"/>
+      <c r="H46" s="277" t="n"/>
+      <c r="I46" s="277" t="n"/>
+      <c r="J46" s="278" t="n"/>
       <c r="K46" s="666" t="n"/>
       <c r="L46" s="666" t="n"/>
       <c r="M46" s="666" t="n"/>
@@ -8907,15 +8919,15 @@
           <t>NOTICE  —  Enter data only in designated white input cells. One form per event or job unless this workbook is designated as rolling. Do not add, delete or resize columns/rows. File naming: FRM-213_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="27" t="n"/>
-      <c r="C47" s="27" t="n"/>
-      <c r="D47" s="27" t="n"/>
-      <c r="E47" s="27" t="n"/>
-      <c r="F47" s="27" t="n"/>
-      <c r="G47" s="27" t="n"/>
-      <c r="H47" s="27" t="n"/>
-      <c r="I47" s="27" t="n"/>
-      <c r="J47" s="27" t="n"/>
+      <c r="B47" s="289" t="n"/>
+      <c r="C47" s="289" t="n"/>
+      <c r="D47" s="289" t="n"/>
+      <c r="E47" s="289" t="n"/>
+      <c r="F47" s="289" t="n"/>
+      <c r="G47" s="289" t="n"/>
+      <c r="H47" s="289" t="n"/>
+      <c r="I47" s="289" t="n"/>
+      <c r="J47" s="289" t="n"/>
       <c r="K47" s="645" t="n"/>
       <c r="L47" s="645" t="n"/>
       <c r="M47" s="645" t="n"/>
@@ -9222,7 +9234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU7"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -9838,7 +9850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU8"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -10561,16 +10573,16 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="339" t="n"/>
-      <c r="B1" s="53" t="n"/>
+      <c r="A1" s="413" t="n"/>
+      <c r="B1" s="310" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
           <t>PERIODIC REVIEW RECORD</t>
         </is>
       </c>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
+      <c r="D1" s="268" t="n"/>
+      <c r="E1" s="268" t="n"/>
+      <c r="F1" s="268" t="n"/>
       <c r="G1" s="680" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -10615,12 +10627,9 @@
       <c r="AN1" s="627" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="B2" s="54" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
+      <c r="A2" s="275" t="n"/>
+      <c r="B2" s="312" t="n"/>
+      <c r="C2" s="275" t="n"/>
       <c r="G2" s="682" t="inlineStr">
         <is>
           <t>Revision</t>
@@ -10665,12 +10674,9 @@
       <c r="AN2" s="632" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="B3" s="54" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
+      <c r="A3" s="275" t="n"/>
+      <c r="B3" s="312" t="n"/>
+      <c r="C3" s="275" t="n"/>
       <c r="G3" s="682" t="inlineStr">
         <is>
           <t>Eff. Date</t>
@@ -10715,16 +10721,13 @@
       <c r="AN3" s="632" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="B4" s="54" t="n"/>
+      <c r="A4" s="275" t="n"/>
+      <c r="B4" s="312" t="n"/>
       <c r="C4" s="633" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
       <c r="G4" s="682" t="inlineStr">
         <is>
           <t>Owner</t>
@@ -10769,16 +10772,16 @@
       <c r="AN4" s="632" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="24" t="n"/>
+      <c r="A5" s="282" t="n"/>
+      <c r="B5" s="287" t="n"/>
       <c r="C5" s="636" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
+      <c r="D5" s="283" t="n"/>
+      <c r="E5" s="283" t="n"/>
+      <c r="F5" s="283" t="n"/>
       <c r="G5" s="684" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -10870,13 +10873,13 @@
           <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
+      <c r="B7" s="289" t="n"/>
+      <c r="C7" s="289" t="n"/>
+      <c r="D7" s="289" t="n"/>
+      <c r="E7" s="289" t="n"/>
+      <c r="F7" s="289" t="n"/>
+      <c r="G7" s="289" t="n"/>
+      <c r="H7" s="289" t="n"/>
       <c r="I7" s="645" t="n"/>
       <c r="J7" s="645" t="n"/>
       <c r="K7" s="645" t="n"/>
@@ -10911,30 +10914,30 @@
       <c r="AN7" s="646" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="647" t="inlineStr">
+      <c r="A8" s="691" t="inlineStr">
         <is>
           <t>Parent Form</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="648" t="inlineStr">
+      <c r="B8" s="272" t="n"/>
+      <c r="C8" s="330" t="inlineStr">
         <is>
           <t>FRM-213 · RMA TRACKING LOG</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="649" t="inlineStr">
+      <c r="D8" s="272" t="n"/>
+      <c r="E8" s="692" t="inlineStr">
         <is>
           <t>Support Tab</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="648" t="inlineStr">
+      <c r="F8" s="272" t="n"/>
+      <c r="G8" s="330" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="H8" s="6" t="n"/>
+      <c r="H8" s="272" t="n"/>
       <c r="I8" s="650" t="n"/>
       <c r="J8" s="650" t="n"/>
       <c r="K8" s="650" t="n"/>
@@ -10969,30 +10972,30 @@
       <c r="AN8" s="651" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="652" t="inlineStr">
+      <c r="A9" s="693" t="inlineStr">
         <is>
           <t>Tab Purpose</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="653" t="inlineStr">
+      <c r="B9" s="278" t="n"/>
+      <c r="C9" s="694" t="inlineStr">
         <is>
           <t>Periodic review and closeout support sheet for the rolling workbook.</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="654" t="inlineStr">
+      <c r="D9" s="278" t="n"/>
+      <c r="E9" s="695" t="inlineStr">
         <is>
           <t>Working Owner</t>
         </is>
       </c>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="653" t="inlineStr">
+      <c r="F9" s="278" t="n"/>
+      <c r="G9" s="694" t="inlineStr">
         <is>
           <t>QA / Customer Service</t>
         </is>
       </c>
-      <c r="H9" s="13" t="n"/>
+      <c r="H9" s="278" t="n"/>
       <c r="I9" s="655" t="n"/>
       <c r="J9" s="655" t="n"/>
       <c r="K9" s="655" t="n"/>
@@ -11027,30 +11030,30 @@
       <c r="AN9" s="656" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="652" t="inlineStr">
+      <c r="A10" s="693" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="653" t="inlineStr">
+      <c r="B10" s="278" t="n"/>
+      <c r="C10" s="694" t="inlineStr">
         <is>
           <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="654" t="inlineStr">
+      <c r="D10" s="278" t="n"/>
+      <c r="E10" s="695" t="inlineStr">
         <is>
           <t>Reviewed By</t>
         </is>
       </c>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="653" t="inlineStr">
+      <c r="F10" s="278" t="n"/>
+      <c r="G10" s="694" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
       </c>
-      <c r="H10" s="13" t="n"/>
+      <c r="H10" s="278" t="n"/>
       <c r="I10" s="655" t="n"/>
       <c r="J10" s="655" t="n"/>
       <c r="K10" s="655" t="n"/>
@@ -11085,30 +11088,30 @@
       <c r="AN10" s="656" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="652" t="inlineStr">
+      <c r="A11" s="693" t="inlineStr">
         <is>
           <t>Update Trigger</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="653" t="inlineStr">
+      <c r="B11" s="278" t="n"/>
+      <c r="C11" s="694" t="inlineStr">
         <is>
           <t>Update when the linked review, evidence or follow-up status changes.</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="654" t="inlineStr">
+      <c r="D11" s="278" t="n"/>
+      <c r="E11" s="695" t="inlineStr">
         <is>
           <t>Data Structure</t>
         </is>
       </c>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="653" t="inlineStr">
+      <c r="F11" s="278" t="n"/>
+      <c r="G11" s="694" t="inlineStr">
         <is>
           <t>Structured Excel Table with filters and print-title rows.</t>
         </is>
       </c>
-      <c r="H11" s="13" t="n"/>
+      <c r="H11" s="278" t="n"/>
       <c r="I11" s="657" t="n"/>
       <c r="J11" s="657" t="n"/>
       <c r="K11" s="657" t="n"/>
@@ -11143,30 +11146,30 @@
       <c r="AN11" s="658" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="659" t="inlineStr">
+      <c r="A12" s="696" t="inlineStr">
         <is>
           <t>Retention Rule</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="660" t="inlineStr">
+      <c r="B12" s="285" t="n"/>
+      <c r="C12" s="697" t="inlineStr">
         <is>
           <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
         </is>
       </c>
-      <c r="D12" s="22" t="n"/>
-      <c r="E12" s="661" t="inlineStr">
+      <c r="D12" s="285" t="n"/>
+      <c r="E12" s="698" t="inlineStr">
         <is>
           <t>Controlled Status</t>
         </is>
       </c>
-      <c r="F12" s="22" t="n"/>
-      <c r="G12" s="660" t="inlineStr">
+      <c r="F12" s="285" t="n"/>
+      <c r="G12" s="697" t="inlineStr">
         <is>
           <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
         </is>
       </c>
-      <c r="H12" s="22" t="n"/>
+      <c r="H12" s="285" t="n"/>
       <c r="I12" s="666" t="n"/>
       <c r="J12" s="666" t="n"/>
       <c r="K12" s="666" t="n"/>
@@ -11248,13 +11251,13 @@
           <t>2.  WORKING TABLE / DETAIL LINES</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="27" t="n"/>
+      <c r="B14" s="289" t="n"/>
+      <c r="C14" s="289" t="n"/>
+      <c r="D14" s="289" t="n"/>
+      <c r="E14" s="289" t="n"/>
+      <c r="F14" s="289" t="n"/>
+      <c r="G14" s="289" t="n"/>
+      <c r="H14" s="289" t="n"/>
       <c r="I14" s="645" t="n"/>
       <c r="J14" s="645" t="n"/>
       <c r="K14" s="645" t="n"/>
@@ -11294,13 +11297,13 @@
           <t>Periodic review and closeout support sheet for the rolling workbook.</t>
         </is>
       </c>
-      <c r="B15" s="27" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="27" t="n"/>
-      <c r="E15" s="27" t="n"/>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="27" t="n"/>
-      <c r="H15" s="27" t="n"/>
+      <c r="B15" s="289" t="n"/>
+      <c r="C15" s="289" t="n"/>
+      <c r="D15" s="289" t="n"/>
+      <c r="E15" s="289" t="n"/>
+      <c r="F15" s="289" t="n"/>
+      <c r="G15" s="289" t="n"/>
+      <c r="H15" s="289" t="n"/>
       <c r="I15" s="645" t="n"/>
       <c r="J15" s="645" t="n"/>
       <c r="K15" s="645" t="n"/>
@@ -11816,13 +11819,13 @@
           <t>NOTICE  —  Periodic review and closeout support sheet for the rolling workbook.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B26" s="27" t="n"/>
-      <c r="C26" s="27" t="n"/>
-      <c r="D26" s="27" t="n"/>
-      <c r="E26" s="27" t="n"/>
-      <c r="F26" s="27" t="n"/>
-      <c r="G26" s="27" t="n"/>
-      <c r="H26" s="27" t="n"/>
+      <c r="B26" s="289" t="n"/>
+      <c r="C26" s="289" t="n"/>
+      <c r="D26" s="289" t="n"/>
+      <c r="E26" s="289" t="n"/>
+      <c r="F26" s="289" t="n"/>
+      <c r="G26" s="289" t="n"/>
+      <c r="H26" s="289" t="n"/>
       <c r="I26" s="645" t="n"/>
       <c r="J26" s="645" t="n"/>
       <c r="K26" s="645" t="n"/>
@@ -12096,7 +12099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CU11"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>

--- a/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
@@ -6,7 +6,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM-213_LOG" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="veryHidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVIEW" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVIEW" sheetId="4" state="veryHidden" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>

--- a/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
@@ -27,13 +27,395 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
+  </si>
+  <si>
+    <t>1.  RMA HEADER</t>
+  </si>
+  <si>
+    <t>2.  RECEIPT AND EVALUATION SECTION</t>
+  </si>
+  <si>
+    <t>2.  WORKING TABLE / DETAIL LINES</t>
+  </si>
+  <si>
+    <t>3.  DISPOSITION SECTION</t>
+  </si>
+  <si>
+    <t>4.  CLOSURE AND EVIDENCE SECTION</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$17)+1</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$22)+1</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>Action Owner</t>
+  </si>
+  <si>
+    <t>Approval / archive</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>CONDITIONAL</t>
+  </si>
+  <si>
+    <t>CUST-001 Alpha Semi</t>
+  </si>
+  <si>
+    <t>CUST-002 NovaFab</t>
+  </si>
+  <si>
+    <t>CUST-003 Orion Tech</t>
+  </si>
+  <si>
+    <t>CUST-004 Quantum Devices</t>
+  </si>
+  <si>
+    <t>CUSTOMER</t>
+  </si>
+  <si>
+    <t>Commercial Owner</t>
+  </si>
+  <si>
+    <t>Controlled Status</t>
+  </si>
+  <si>
+    <t>Current Scope</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Data Structure</t>
+  </si>
+  <si>
+    <t>DateTime</t>
+  </si>
+  <si>
+    <t>Disposition</t>
+  </si>
+  <si>
+    <t>Disposition Summary</t>
+  </si>
+  <si>
+    <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
+  </si>
+  <si>
+    <t>Document / Record</t>
+  </si>
+  <si>
+    <t>Eff. Date</t>
+  </si>
+  <si>
+    <t>Engineering Lead</t>
+  </si>
+  <si>
+    <t>Epicor://Job/JOB-240001</t>
+  </si>
+  <si>
+    <t>Escalation if Not Disposed</t>
+  </si>
+  <si>
+    <t>Evaluation Owner</t>
+  </si>
+  <si>
+    <t>Evidence Folder</t>
+  </si>
+  <si>
+    <t>Evidence Ref</t>
+  </si>
+  <si>
+    <t>Expectation / Rule</t>
+  </si>
+  <si>
+    <t>FRM-213</t>
+  </si>
+  <si>
+    <t>FRM-213 · RMA TRACKING LOG</t>
+  </si>
+  <si>
+    <t>Final evidence ref: ________________________________________
+Outstanding items / actions: ________________________________</t>
+  </si>
+  <si>
+    <t>Form Code</t>
+  </si>
+  <si>
+    <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>M365://dossier/JOB-240001</t>
+  </si>
+  <si>
+    <t>MONITORING</t>
+  </si>
+  <si>
+    <t>Maintenance Lead</t>
+  </si>
+  <si>
+    <t>NOTICE  —  Enter data only in designated white input cells. One form per event or job unless this workbook is designated as rolling. Do not add, delete or resize columns/rows. File naming: FRM-213_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
+  </si>
+  <si>
+    <t>NOTICE  —  Periodic review and closeout support sheet for the rolling workbook.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
+  </si>
+  <si>
+    <t>Name / Signature / Date</t>
+  </si>
+  <si>
+    <t>Next Review</t>
+  </si>
+  <si>
+    <t>Next Review Date</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>Open Period</t>
+  </si>
+  <si>
+    <t>Open items / escalation</t>
+  </si>
+  <si>
+    <t>Overall Status</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>PERIODIC REVIEW RECORD</t>
+  </si>
+  <si>
+    <t>PN-1001 / Rev.A</t>
+  </si>
+  <si>
+    <t>PN-1002 / Rev.B</t>
+  </si>
+  <si>
+    <t>PN-1003 / Rev.C</t>
+  </si>
+  <si>
+    <t>PN-1004 / Rev.D</t>
+  </si>
+  <si>
+    <t>Parent Form</t>
+  </si>
+  <si>
+    <t>Part / Revision</t>
+  </si>
+  <si>
+    <t>Part No. / Revision</t>
+  </si>
+  <si>
+    <t>Periodic review</t>
+  </si>
+  <si>
+    <t>Periodic review and closeout support sheet for the rolling workbook.</t>
+  </si>
+  <si>
+    <t>Planning Lead</t>
+  </si>
+  <si>
+    <t>Primary Return / Defect Note</t>
+  </si>
+  <si>
+    <t>Production Supervisor</t>
+  </si>
+  <si>
+    <t>QA / Customer Service</t>
+  </si>
+  <si>
+    <t>QA Engineer</t>
+  </si>
+  <si>
+    <t>QA Manager</t>
+  </si>
+  <si>
+    <t>Qty / Condition</t>
+  </si>
+  <si>
+    <t>Quality Management System  ·  Controlled Document</t>
+  </si>
+  <si>
+    <t>REF_CUSTOMER_MASTER</t>
+  </si>
+  <si>
+    <t>REF_EVIDENCE_LINK</t>
+  </si>
+  <si>
+    <t>REF_LINKS</t>
+  </si>
+  <si>
+    <t>REF_OWNER_PERSON_MASTER</t>
+  </si>
+  <si>
+    <t>REF_PART_REV_MASTER</t>
+  </si>
+  <si>
+    <t>REJECT</t>
+  </si>
+  <si>
+    <t>REVIEW</t>
+  </si>
+  <si>
+    <t>RMA ID</t>
+  </si>
+  <si>
+    <t>RMA Owner</t>
+  </si>
+  <si>
+    <t>RMA TRACKING LOG</t>
+  </si>
+  <si>
+    <t>Receipt Ref. / Date</t>
+  </si>
+  <si>
+    <t>Record Status</t>
+  </si>
+  <si>
+    <t>Ref Type</t>
+  </si>
+  <si>
+    <t>Reference Epicor / M365 / controlled documents only.</t>
+  </si>
+  <si>
+    <t>Retention Rule</t>
+  </si>
+  <si>
+    <t>Return-material tracking memory only; formal quality investigation remains in linked quality records.
+Review owner: _____________________________________________</t>
+  </si>
+  <si>
+    <t>Returned Qty / Condition</t>
+  </si>
+  <si>
+    <t>Review Date</t>
+  </si>
+  <si>
+    <t>Review Item</t>
+  </si>
+  <si>
+    <t>Reviewed By</t>
+  </si>
+  <si>
+    <t>Reviewer</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>SP://evidence/FRM-202/001</t>
+  </si>
+  <si>
+    <t>SP://evidence/FRM-306/002</t>
+  </si>
+  <si>
+    <t>SUPERSEDED</t>
+  </si>
+  <si>
+    <t>Setup Technician</t>
+  </si>
+  <si>
+    <t>Source of Truth</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Structured Excel Table with filters and print-title rows.</t>
+  </si>
+  <si>
+    <t>Support Tab</t>
+  </si>
+  <si>
+    <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
+  </si>
+  <si>
+    <t>System of Record</t>
+  </si>
+  <si>
+    <t>TIER 1</t>
+  </si>
+  <si>
+    <t>TIER 2</t>
+  </si>
+  <si>
+    <t>TIER 3</t>
+  </si>
+  <si>
+    <t>Tab Purpose</t>
+  </si>
+  <si>
+    <t>Unique Ref</t>
+  </si>
+  <si>
+    <t>Update Trigger</t>
+  </si>
+  <si>
+    <t>Update when the linked review, evidence or follow-up status changes.</t>
+  </si>
+  <si>
+    <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>VAL_DECISION_GATE_CORE</t>
+  </si>
+  <si>
+    <t>VAL_ESCALATION_LEVEL</t>
+  </si>
+  <si>
+    <t>VAL_STATUS_CORE</t>
+  </si>
+  <si>
+    <t>VOID</t>
+  </si>
+  <si>
+    <t>WAR ROOM</t>
+  </si>
+  <si>
+    <t>Working Owner</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
   </numFmts>
-  <fonts count="87">
+  <fonts count="88">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -526,8 +908,13 @@
       <color rgb="001B3A6B"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007B4F00"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="56">
+  <fills count="57">
     <fill>
       <patternFill/>
     </fill>
@@ -804,8 +1191,13 @@
         <fgColor rgb="000C2D48"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="350">
+  <borders count="353">
     <border>
       <left/>
       <right/>
@@ -4552,13 +4944,47 @@
       </top>
       <bottom style="thin">
         <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="704">
+  <cellXfs count="707">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6301,6 +6727,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="57" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="56" borderId="350" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="56" borderId="351" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="56" borderId="352" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8913,51 +9348,51 @@
       <c r="AM46" s="666" t="n"/>
       <c r="AN46" s="667" t="n"/>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="644" t="inlineStr">
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="704" t="inlineStr">
         <is>
           <t>NOTICE  —  Enter data only in designated white input cells. One form per event or job unless this workbook is designated as rolling. Do not add, delete or resize columns/rows. File naming: FRM-213_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="289" t="n"/>
-      <c r="C47" s="289" t="n"/>
-      <c r="D47" s="289" t="n"/>
-      <c r="E47" s="289" t="n"/>
-      <c r="F47" s="289" t="n"/>
-      <c r="G47" s="289" t="n"/>
-      <c r="H47" s="289" t="n"/>
-      <c r="I47" s="289" t="n"/>
-      <c r="J47" s="289" t="n"/>
-      <c r="K47" s="645" t="n"/>
-      <c r="L47" s="645" t="n"/>
-      <c r="M47" s="645" t="n"/>
-      <c r="N47" s="645" t="n"/>
-      <c r="O47" s="645" t="n"/>
-      <c r="P47" s="645" t="n"/>
-      <c r="Q47" s="645" t="n"/>
-      <c r="R47" s="645" t="n"/>
-      <c r="S47" s="645" t="n"/>
-      <c r="T47" s="645" t="n"/>
-      <c r="U47" s="645" t="n"/>
-      <c r="V47" s="645" t="n"/>
-      <c r="W47" s="645" t="n"/>
-      <c r="X47" s="645" t="n"/>
-      <c r="Y47" s="645" t="n"/>
-      <c r="Z47" s="645" t="n"/>
-      <c r="AA47" s="645" t="n"/>
-      <c r="AB47" s="645" t="n"/>
-      <c r="AC47" s="645" t="n"/>
-      <c r="AD47" s="645" t="n"/>
-      <c r="AE47" s="645" t="n"/>
-      <c r="AF47" s="645" t="n"/>
-      <c r="AG47" s="645" t="n"/>
-      <c r="AH47" s="645" t="n"/>
-      <c r="AI47" s="645" t="n"/>
-      <c r="AJ47" s="645" t="n"/>
-      <c r="AK47" s="645" t="n"/>
-      <c r="AL47" s="645" t="n"/>
-      <c r="AM47" s="645" t="n"/>
-      <c r="AN47" s="646" t="n"/>
+      <c r="B47" s="705" t="n"/>
+      <c r="C47" s="705" t="n"/>
+      <c r="D47" s="705" t="n"/>
+      <c r="E47" s="705" t="n"/>
+      <c r="F47" s="705" t="n"/>
+      <c r="G47" s="705" t="n"/>
+      <c r="H47" s="705" t="n"/>
+      <c r="I47" s="705" t="n"/>
+      <c r="J47" s="705" t="n"/>
+      <c r="K47" s="705" t="n"/>
+      <c r="L47" s="705" t="n"/>
+      <c r="M47" s="705" t="n"/>
+      <c r="N47" s="705" t="n"/>
+      <c r="O47" s="705" t="n"/>
+      <c r="P47" s="705" t="n"/>
+      <c r="Q47" s="705" t="n"/>
+      <c r="R47" s="705" t="n"/>
+      <c r="S47" s="705" t="n"/>
+      <c r="T47" s="705" t="n"/>
+      <c r="U47" s="705" t="n"/>
+      <c r="V47" s="705" t="n"/>
+      <c r="W47" s="705" t="n"/>
+      <c r="X47" s="705" t="n"/>
+      <c r="Y47" s="705" t="n"/>
+      <c r="Z47" s="705" t="n"/>
+      <c r="AA47" s="705" t="n"/>
+      <c r="AB47" s="705" t="n"/>
+      <c r="AC47" s="705" t="n"/>
+      <c r="AD47" s="705" t="n"/>
+      <c r="AE47" s="705" t="n"/>
+      <c r="AF47" s="705" t="n"/>
+      <c r="AG47" s="705" t="n"/>
+      <c r="AH47" s="705" t="n"/>
+      <c r="AI47" s="705" t="n"/>
+      <c r="AJ47" s="705" t="n"/>
+      <c r="AK47" s="705" t="n"/>
+      <c r="AL47" s="705" t="n"/>
+      <c r="AM47" s="705" t="n"/>
+      <c r="AN47" s="706" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="1"/>
     <row r="49" hidden="1" outlineLevel="1"/>

--- a/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
@@ -1197,7 +1197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="353">
+  <borders count="355">
     <border>
       <left/>
       <right/>
@@ -4979,6 +4979,26 @@
       <bottom style="thin">
         <color rgb="00F9A825"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">

--- a/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
@@ -27,395 +27,13 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
-  </si>
-  <si>
-    <t>1.  RMA HEADER</t>
-  </si>
-  <si>
-    <t>2.  RECEIPT AND EVALUATION SECTION</t>
-  </si>
-  <si>
-    <t>2.  WORKING TABLE / DETAIL LINES</t>
-  </si>
-  <si>
-    <t>3.  DISPOSITION SECTION</t>
-  </si>
-  <si>
-    <t>4.  CLOSURE AND EVIDENCE SECTION</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$17)+1</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$22)+1</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>Action Owner</t>
-  </si>
-  <si>
-    <t>Approval / archive</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>CONDITIONAL</t>
-  </si>
-  <si>
-    <t>CUST-001 Alpha Semi</t>
-  </si>
-  <si>
-    <t>CUST-002 NovaFab</t>
-  </si>
-  <si>
-    <t>CUST-003 Orion Tech</t>
-  </si>
-  <si>
-    <t>CUST-004 Quantum Devices</t>
-  </si>
-  <si>
-    <t>CUSTOMER</t>
-  </si>
-  <si>
-    <t>Commercial Owner</t>
-  </si>
-  <si>
-    <t>Controlled Status</t>
-  </si>
-  <si>
-    <t>Current Scope</t>
-  </si>
-  <si>
-    <t>Customer</t>
-  </si>
-  <si>
-    <t>Data Structure</t>
-  </si>
-  <si>
-    <t>DateTime</t>
-  </si>
-  <si>
-    <t>Disposition</t>
-  </si>
-  <si>
-    <t>Disposition Summary</t>
-  </si>
-  <si>
-    <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
-  </si>
-  <si>
-    <t>Document / Record</t>
-  </si>
-  <si>
-    <t>Eff. Date</t>
-  </si>
-  <si>
-    <t>Engineering Lead</t>
-  </si>
-  <si>
-    <t>Epicor://Job/JOB-240001</t>
-  </si>
-  <si>
-    <t>Escalation if Not Disposed</t>
-  </si>
-  <si>
-    <t>Evaluation Owner</t>
-  </si>
-  <si>
-    <t>Evidence Folder</t>
-  </si>
-  <si>
-    <t>Evidence Ref</t>
-  </si>
-  <si>
-    <t>Expectation / Rule</t>
-  </si>
-  <si>
-    <t>FRM-213</t>
-  </si>
-  <si>
-    <t>FRM-213 · RMA TRACKING LOG</t>
-  </si>
-  <si>
-    <t>Final evidence ref: ________________________________________
-Outstanding items / actions: ________________________________</t>
-  </si>
-  <si>
-    <t>Form Code</t>
-  </si>
-  <si>
-    <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
-    <t>M365://dossier/JOB-240001</t>
-  </si>
-  <si>
-    <t>MONITORING</t>
-  </si>
-  <si>
-    <t>Maintenance Lead</t>
-  </si>
-  <si>
-    <t>NOTICE  —  Enter data only in designated white input cells. One form per event or job unless this workbook is designated as rolling. Do not add, delete or resize columns/rows. File naming: FRM-213_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
-  </si>
-  <si>
-    <t>NOTICE  —  Periodic review and closeout support sheet for the rolling workbook.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
-  </si>
-  <si>
-    <t>Name / Signature / Date</t>
-  </si>
-  <si>
-    <t>Next Review</t>
-  </si>
-  <si>
-    <t>Next Review Date</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>Open Period</t>
-  </si>
-  <si>
-    <t>Open items / escalation</t>
-  </si>
-  <si>
-    <t>Overall Status</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>PERIODIC REVIEW RECORD</t>
-  </si>
-  <si>
-    <t>PN-1001 / Rev.A</t>
-  </si>
-  <si>
-    <t>PN-1002 / Rev.B</t>
-  </si>
-  <si>
-    <t>PN-1003 / Rev.C</t>
-  </si>
-  <si>
-    <t>PN-1004 / Rev.D</t>
-  </si>
-  <si>
-    <t>Parent Form</t>
-  </si>
-  <si>
-    <t>Part / Revision</t>
-  </si>
-  <si>
-    <t>Part No. / Revision</t>
-  </si>
-  <si>
-    <t>Periodic review</t>
-  </si>
-  <si>
-    <t>Periodic review and closeout support sheet for the rolling workbook.</t>
-  </si>
-  <si>
-    <t>Planning Lead</t>
-  </si>
-  <si>
-    <t>Primary Return / Defect Note</t>
-  </si>
-  <si>
-    <t>Production Supervisor</t>
-  </si>
-  <si>
-    <t>QA / Customer Service</t>
-  </si>
-  <si>
-    <t>QA Engineer</t>
-  </si>
-  <si>
-    <t>QA Manager</t>
-  </si>
-  <si>
-    <t>Qty / Condition</t>
-  </si>
-  <si>
-    <t>Quality Management System  ·  Controlled Document</t>
-  </si>
-  <si>
-    <t>REF_CUSTOMER_MASTER</t>
-  </si>
-  <si>
-    <t>REF_EVIDENCE_LINK</t>
-  </si>
-  <si>
-    <t>REF_LINKS</t>
-  </si>
-  <si>
-    <t>REF_OWNER_PERSON_MASTER</t>
-  </si>
-  <si>
-    <t>REF_PART_REV_MASTER</t>
-  </si>
-  <si>
-    <t>REJECT</t>
-  </si>
-  <si>
-    <t>REVIEW</t>
-  </si>
-  <si>
-    <t>RMA ID</t>
-  </si>
-  <si>
-    <t>RMA Owner</t>
-  </si>
-  <si>
-    <t>RMA TRACKING LOG</t>
-  </si>
-  <si>
-    <t>Receipt Ref. / Date</t>
-  </si>
-  <si>
-    <t>Record Status</t>
-  </si>
-  <si>
-    <t>Ref Type</t>
-  </si>
-  <si>
-    <t>Reference Epicor / M365 / controlled documents only.</t>
-  </si>
-  <si>
-    <t>Retention Rule</t>
-  </si>
-  <si>
-    <t>Return-material tracking memory only; formal quality investigation remains in linked quality records.
-Review owner: _____________________________________________</t>
-  </si>
-  <si>
-    <t>Returned Qty / Condition</t>
-  </si>
-  <si>
-    <t>Review Date</t>
-  </si>
-  <si>
-    <t>Review Item</t>
-  </si>
-  <si>
-    <t>Reviewed By</t>
-  </si>
-  <si>
-    <t>Reviewer</t>
-  </si>
-  <si>
-    <t>Revision</t>
-  </si>
-  <si>
-    <t>SP://evidence/FRM-202/001</t>
-  </si>
-  <si>
-    <t>SP://evidence/FRM-306/002</t>
-  </si>
-  <si>
-    <t>SUPERSEDED</t>
-  </si>
-  <si>
-    <t>Setup Technician</t>
-  </si>
-  <si>
-    <t>Source of Truth</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Structured Excel Table with filters and print-title rows.</t>
-  </si>
-  <si>
-    <t>Support Tab</t>
-  </si>
-  <si>
-    <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
-  </si>
-  <si>
-    <t>System of Record</t>
-  </si>
-  <si>
-    <t>TIER 1</t>
-  </si>
-  <si>
-    <t>TIER 2</t>
-  </si>
-  <si>
-    <t>TIER 3</t>
-  </si>
-  <si>
-    <t>Tab Purpose</t>
-  </si>
-  <si>
-    <t>Unique Ref</t>
-  </si>
-  <si>
-    <t>Update Trigger</t>
-  </si>
-  <si>
-    <t>Update when the linked review, evidence or follow-up status changes.</t>
-  </si>
-  <si>
-    <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
-  </si>
-  <si>
-    <t>V0</t>
-  </si>
-  <si>
-    <t>VAL_DECISION_GATE_CORE</t>
-  </si>
-  <si>
-    <t>VAL_ESCALATION_LEVEL</t>
-  </si>
-  <si>
-    <t>VAL_STATUS_CORE</t>
-  </si>
-  <si>
-    <t>VOID</t>
-  </si>
-  <si>
-    <t>WAR ROOM</t>
-  </si>
-  <si>
-    <t>Working Owner</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
   </numFmts>
-  <fonts count="88">
+  <fonts count="89">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -913,6 +531,9 @@
       <color rgb="007B4F00"/>
       <sz val="7"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
   <fills count="57">
     <fill>
@@ -1197,7 +818,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="355">
+  <borders count="356">
     <border>
       <left/>
       <right/>
@@ -4999,12 +4620,22 @@
         <color rgb="00F9A825"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="707">
+  <cellXfs count="727">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6758,6 +6389,40 @@
     <xf numFmtId="0" fontId="87" fillId="56" borderId="352" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="309" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="310" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="311" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="312" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="314" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="315" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="83" fillId="52" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="318" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="320" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="52" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="355" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="51" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -9689,7 +9354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -9734,381 +9399,770 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="430" t="inlineStr">
-        <is>
-          <t>VAL_DECISION_GATE_CORE</t>
-        </is>
-      </c>
-      <c r="B1" s="430" t="inlineStr">
-        <is>
-          <t>VAL_ESCALATION_LEVEL</t>
-        </is>
-      </c>
-      <c r="C1" s="430" t="inlineStr">
-        <is>
-          <t>VAL_STATUS_CORE</t>
-        </is>
-      </c>
-      <c r="D1" s="430" t="n"/>
-      <c r="E1" s="430" t="n"/>
-      <c r="F1" s="430" t="n"/>
-      <c r="G1" s="430" t="n"/>
-      <c r="H1" s="430" t="n"/>
-      <c r="I1" s="430" t="n"/>
-      <c r="J1" s="430" t="n"/>
-      <c r="K1" s="430" t="n"/>
-      <c r="L1" s="430" t="n"/>
-      <c r="M1" s="430" t="n"/>
-      <c r="N1" s="430" t="n"/>
-      <c r="O1" s="430" t="n"/>
-      <c r="P1" s="430" t="n"/>
-      <c r="Q1" s="430" t="n"/>
-      <c r="R1" s="430" t="n"/>
-      <c r="S1" s="430" t="n"/>
-      <c r="T1" s="430" t="n"/>
-      <c r="U1" s="430" t="n"/>
-      <c r="V1" s="430" t="n"/>
-      <c r="W1" s="430" t="n"/>
-      <c r="X1" s="430" t="n"/>
-      <c r="Y1" s="430" t="n"/>
-      <c r="Z1" s="430" t="n"/>
-      <c r="AA1" s="430" t="n"/>
-      <c r="AB1" s="430" t="n"/>
-      <c r="AC1" s="430" t="n"/>
-      <c r="AD1" s="430" t="n"/>
-      <c r="AE1" s="430" t="n"/>
-      <c r="AF1" s="430" t="n"/>
-      <c r="AG1" s="430" t="n"/>
-      <c r="AH1" s="430" t="n"/>
-      <c r="AI1" s="430" t="n"/>
-      <c r="AJ1" s="430" t="n"/>
-      <c r="AK1" s="430" t="n"/>
-      <c r="AL1" s="430" t="n"/>
-      <c r="AM1" s="430" t="n"/>
-      <c r="AN1" s="430" t="n"/>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="707" t="n"/>
+      <c r="B1" s="708" t="n"/>
+      <c r="C1" s="708" t="n"/>
+      <c r="D1" s="708" t="n"/>
+      <c r="E1" s="708" t="n"/>
+      <c r="F1" s="708" t="n"/>
+      <c r="G1" s="708" t="n"/>
+      <c r="H1" s="709" t="n"/>
+      <c r="I1" s="710" t="inlineStr"/>
+      <c r="J1" s="708" t="n"/>
+      <c r="K1" s="708" t="n"/>
+      <c r="L1" s="708" t="n"/>
+      <c r="M1" s="708" t="n"/>
+      <c r="N1" s="708" t="n"/>
+      <c r="O1" s="708" t="n"/>
+      <c r="P1" s="708" t="n"/>
+      <c r="Q1" s="708" t="n"/>
+      <c r="R1" s="708" t="n"/>
+      <c r="S1" s="708" t="n"/>
+      <c r="T1" s="708" t="n"/>
+      <c r="U1" s="708" t="n"/>
+      <c r="V1" s="708" t="n"/>
+      <c r="W1" s="708" t="n"/>
+      <c r="X1" s="708" t="n"/>
+      <c r="Y1" s="708" t="n"/>
+      <c r="Z1" s="708" t="n"/>
+      <c r="AA1" s="708" t="n"/>
+      <c r="AB1" s="708" t="n"/>
+      <c r="AC1" s="708" t="n"/>
+      <c r="AD1" s="709" t="n"/>
+      <c r="AE1" s="513" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="708" t="n"/>
+      <c r="AG1" s="708" t="n"/>
+      <c r="AH1" s="711" t="n"/>
+      <c r="AI1" s="516" t="n"/>
+      <c r="AJ1" s="708" t="n"/>
+      <c r="AK1" s="708" t="n"/>
+      <c r="AL1" s="708" t="n"/>
+      <c r="AM1" s="708" t="n"/>
+      <c r="AN1" s="709" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" s="430" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="B2" s="430" t="inlineStr">
-        <is>
-          <t>TIER 1</t>
-        </is>
-      </c>
-      <c r="C2" s="430" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="D2" s="430" t="n"/>
-      <c r="E2" s="430" t="n"/>
-      <c r="F2" s="430" t="n"/>
-      <c r="G2" s="430" t="n"/>
-      <c r="H2" s="430" t="n"/>
-      <c r="I2" s="430" t="n"/>
-      <c r="J2" s="430" t="n"/>
-      <c r="K2" s="430" t="n"/>
-      <c r="L2" s="430" t="n"/>
-      <c r="M2" s="430" t="n"/>
-      <c r="N2" s="430" t="n"/>
-      <c r="O2" s="430" t="n"/>
-      <c r="P2" s="430" t="n"/>
-      <c r="Q2" s="430" t="n"/>
-      <c r="R2" s="430" t="n"/>
-      <c r="S2" s="430" t="n"/>
-      <c r="T2" s="430" t="n"/>
-      <c r="U2" s="430" t="n"/>
-      <c r="V2" s="430" t="n"/>
-      <c r="W2" s="430" t="n"/>
-      <c r="X2" s="430" t="n"/>
-      <c r="Y2" s="430" t="n"/>
-      <c r="Z2" s="430" t="n"/>
-      <c r="AA2" s="430" t="n"/>
-      <c r="AB2" s="430" t="n"/>
-      <c r="AC2" s="430" t="n"/>
-      <c r="AD2" s="430" t="n"/>
-      <c r="AE2" s="430" t="n"/>
-      <c r="AF2" s="430" t="n"/>
-      <c r="AG2" s="430" t="n"/>
-      <c r="AH2" s="430" t="n"/>
-      <c r="AI2" s="430" t="n"/>
-      <c r="AJ2" s="430" t="n"/>
-      <c r="AK2" s="430" t="n"/>
-      <c r="AL2" s="430" t="n"/>
-      <c r="AM2" s="430" t="n"/>
-      <c r="AN2" s="430" t="n"/>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="712" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="713" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="713" t="n"/>
+      <c r="AE2" s="714" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="10" t="n"/>
+      <c r="AG2" s="10" t="n"/>
+      <c r="AH2" s="715" t="n"/>
+      <c r="AI2" s="716" t="n"/>
+      <c r="AJ2" s="10" t="n"/>
+      <c r="AK2" s="10" t="n"/>
+      <c r="AL2" s="10" t="n"/>
+      <c r="AM2" s="10" t="n"/>
+      <c r="AN2" s="713" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="430" t="inlineStr">
-        <is>
-          <t>CONDITIONAL</t>
-        </is>
-      </c>
-      <c r="B3" s="430" t="inlineStr">
-        <is>
-          <t>TIER 2</t>
-        </is>
-      </c>
-      <c r="C3" s="430" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
-        </is>
-      </c>
-      <c r="D3" s="430" t="n"/>
-      <c r="E3" s="430" t="n"/>
-      <c r="F3" s="430" t="n"/>
-      <c r="G3" s="430" t="n"/>
-      <c r="H3" s="430" t="n"/>
-      <c r="I3" s="430" t="n"/>
-      <c r="J3" s="430" t="n"/>
-      <c r="K3" s="430" t="n"/>
-      <c r="L3" s="430" t="n"/>
-      <c r="M3" s="430" t="n"/>
-      <c r="N3" s="430" t="n"/>
-      <c r="O3" s="430" t="n"/>
-      <c r="P3" s="430" t="n"/>
-      <c r="Q3" s="430" t="n"/>
-      <c r="R3" s="430" t="n"/>
-      <c r="S3" s="430" t="n"/>
-      <c r="T3" s="430" t="n"/>
-      <c r="U3" s="430" t="n"/>
-      <c r="V3" s="430" t="n"/>
-      <c r="W3" s="430" t="n"/>
-      <c r="X3" s="430" t="n"/>
-      <c r="Y3" s="430" t="n"/>
-      <c r="Z3" s="430" t="n"/>
-      <c r="AA3" s="430" t="n"/>
-      <c r="AB3" s="430" t="n"/>
-      <c r="AC3" s="430" t="n"/>
-      <c r="AD3" s="430" t="n"/>
-      <c r="AE3" s="430" t="n"/>
-      <c r="AF3" s="430" t="n"/>
-      <c r="AG3" s="430" t="n"/>
-      <c r="AH3" s="430" t="n"/>
-      <c r="AI3" s="430" t="n"/>
-      <c r="AJ3" s="430" t="n"/>
-      <c r="AK3" s="430" t="n"/>
-      <c r="AL3" s="430" t="n"/>
-      <c r="AM3" s="430" t="n"/>
-      <c r="AN3" s="430" t="n"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="712" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="713" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="713" t="n"/>
+      <c r="AE3" s="714" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="715" t="n"/>
+      <c r="AI3" s="716" t="n"/>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="713" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="430" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="B4" s="430" t="inlineStr">
-        <is>
-          <t>TIER 3</t>
-        </is>
-      </c>
-      <c r="C4" s="430" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="D4" s="430" t="n"/>
-      <c r="E4" s="430" t="n"/>
-      <c r="F4" s="430" t="n"/>
-      <c r="G4" s="430" t="n"/>
-      <c r="H4" s="430" t="n"/>
-      <c r="I4" s="430" t="n"/>
-      <c r="J4" s="430" t="n"/>
-      <c r="K4" s="430" t="n"/>
-      <c r="L4" s="430" t="n"/>
-      <c r="M4" s="430" t="n"/>
-      <c r="N4" s="430" t="n"/>
-      <c r="O4" s="430" t="n"/>
-      <c r="P4" s="430" t="n"/>
-      <c r="Q4" s="430" t="n"/>
-      <c r="R4" s="430" t="n"/>
-      <c r="S4" s="430" t="n"/>
-      <c r="T4" s="430" t="n"/>
-      <c r="U4" s="430" t="n"/>
-      <c r="V4" s="430" t="n"/>
-      <c r="W4" s="430" t="n"/>
-      <c r="X4" s="430" t="n"/>
-      <c r="Y4" s="430" t="n"/>
-      <c r="Z4" s="430" t="n"/>
-      <c r="AA4" s="430" t="n"/>
-      <c r="AB4" s="430" t="n"/>
-      <c r="AC4" s="430" t="n"/>
-      <c r="AD4" s="430" t="n"/>
-      <c r="AE4" s="430" t="n"/>
-      <c r="AF4" s="430" t="n"/>
-      <c r="AG4" s="430" t="n"/>
-      <c r="AH4" s="430" t="n"/>
-      <c r="AI4" s="430" t="n"/>
-      <c r="AJ4" s="430" t="n"/>
-      <c r="AK4" s="430" t="n"/>
-      <c r="AL4" s="430" t="n"/>
-      <c r="AM4" s="430" t="n"/>
-      <c r="AN4" s="430" t="n"/>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="712" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="713" t="n"/>
+      <c r="I4" s="717" t="inlineStr"/>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="713" t="n"/>
+      <c r="AE4" s="714" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="715" t="n"/>
+      <c r="AI4" s="716" t="n"/>
+      <c r="AJ4" s="10" t="n"/>
+      <c r="AK4" s="10" t="n"/>
+      <c r="AL4" s="10" t="n"/>
+      <c r="AM4" s="10" t="n"/>
+      <c r="AN4" s="713" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="430" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="B5" s="430" t="inlineStr">
-        <is>
-          <t>WAR ROOM</t>
-        </is>
-      </c>
-      <c r="C5" s="430" t="inlineStr">
-        <is>
-          <t>MONITORING</t>
-        </is>
-      </c>
-      <c r="D5" s="430" t="n"/>
-      <c r="E5" s="430" t="n"/>
-      <c r="F5" s="430" t="n"/>
-      <c r="G5" s="430" t="n"/>
-      <c r="H5" s="430" t="n"/>
-      <c r="I5" s="430" t="n"/>
-      <c r="J5" s="430" t="n"/>
-      <c r="K5" s="430" t="n"/>
-      <c r="L5" s="430" t="n"/>
-      <c r="M5" s="430" t="n"/>
-      <c r="N5" s="430" t="n"/>
-      <c r="O5" s="430" t="n"/>
-      <c r="P5" s="430" t="n"/>
-      <c r="Q5" s="430" t="n"/>
-      <c r="R5" s="430" t="n"/>
-      <c r="S5" s="430" t="n"/>
-      <c r="T5" s="430" t="n"/>
-      <c r="U5" s="430" t="n"/>
-      <c r="V5" s="430" t="n"/>
-      <c r="W5" s="430" t="n"/>
-      <c r="X5" s="430" t="n"/>
-      <c r="Y5" s="430" t="n"/>
-      <c r="Z5" s="430" t="n"/>
-      <c r="AA5" s="430" t="n"/>
-      <c r="AB5" s="430" t="n"/>
-      <c r="AC5" s="430" t="n"/>
-      <c r="AD5" s="430" t="n"/>
-      <c r="AE5" s="430" t="n"/>
-      <c r="AF5" s="430" t="n"/>
-      <c r="AG5" s="430" t="n"/>
-      <c r="AH5" s="430" t="n"/>
-      <c r="AI5" s="430" t="n"/>
-      <c r="AJ5" s="430" t="n"/>
-      <c r="AK5" s="430" t="n"/>
-      <c r="AL5" s="430" t="n"/>
-      <c r="AM5" s="430" t="n"/>
-      <c r="AN5" s="430" t="n"/>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="718" t="n"/>
+      <c r="B5" s="719" t="n"/>
+      <c r="C5" s="719" t="n"/>
+      <c r="D5" s="719" t="n"/>
+      <c r="E5" s="719" t="n"/>
+      <c r="F5" s="719" t="n"/>
+      <c r="G5" s="719" t="n"/>
+      <c r="H5" s="720" t="n"/>
+      <c r="I5" s="721" t="inlineStr"/>
+      <c r="J5" s="719" t="n"/>
+      <c r="K5" s="719" t="n"/>
+      <c r="L5" s="719" t="n"/>
+      <c r="M5" s="719" t="n"/>
+      <c r="N5" s="719" t="n"/>
+      <c r="O5" s="719" t="n"/>
+      <c r="P5" s="719" t="n"/>
+      <c r="Q5" s="719" t="n"/>
+      <c r="R5" s="719" t="n"/>
+      <c r="S5" s="719" t="n"/>
+      <c r="T5" s="719" t="n"/>
+      <c r="U5" s="719" t="n"/>
+      <c r="V5" s="719" t="n"/>
+      <c r="W5" s="719" t="n"/>
+      <c r="X5" s="719" t="n"/>
+      <c r="Y5" s="719" t="n"/>
+      <c r="Z5" s="719" t="n"/>
+      <c r="AA5" s="719" t="n"/>
+      <c r="AB5" s="719" t="n"/>
+      <c r="AC5" s="719" t="n"/>
+      <c r="AD5" s="720" t="n"/>
+      <c r="AE5" s="722" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="719" t="n"/>
+      <c r="AG5" s="719" t="n"/>
+      <c r="AH5" s="723" t="n"/>
+      <c r="AI5" s="724" t="n"/>
+      <c r="AJ5" s="719" t="n"/>
+      <c r="AK5" s="719" t="n"/>
+      <c r="AL5" s="719" t="n"/>
+      <c r="AM5" s="719" t="n"/>
+      <c r="AN5" s="720" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="430" t="n"/>
-      <c r="B6" s="430" t="inlineStr">
-        <is>
-          <t>CUSTOMER</t>
-        </is>
-      </c>
-      <c r="C6" s="430" t="inlineStr">
-        <is>
-          <t>SUPERSEDED</t>
-        </is>
-      </c>
-      <c r="D6" s="430" t="n"/>
-      <c r="E6" s="430" t="n"/>
-      <c r="F6" s="430" t="n"/>
-      <c r="G6" s="430" t="n"/>
-      <c r="H6" s="430" t="n"/>
-      <c r="I6" s="430" t="n"/>
-      <c r="J6" s="430" t="n"/>
-      <c r="K6" s="430" t="n"/>
-      <c r="L6" s="430" t="n"/>
-      <c r="M6" s="430" t="n"/>
-      <c r="N6" s="430" t="n"/>
-      <c r="O6" s="430" t="n"/>
-      <c r="P6" s="430" t="n"/>
-      <c r="Q6" s="430" t="n"/>
-      <c r="R6" s="430" t="n"/>
-      <c r="S6" s="430" t="n"/>
-      <c r="T6" s="430" t="n"/>
-      <c r="U6" s="430" t="n"/>
-      <c r="V6" s="430" t="n"/>
-      <c r="W6" s="430" t="n"/>
-      <c r="X6" s="430" t="n"/>
-      <c r="Y6" s="430" t="n"/>
-      <c r="Z6" s="430" t="n"/>
-      <c r="AA6" s="430" t="n"/>
-      <c r="AB6" s="430" t="n"/>
-      <c r="AC6" s="430" t="n"/>
-      <c r="AD6" s="430" t="n"/>
-      <c r="AE6" s="430" t="n"/>
-      <c r="AF6" s="430" t="n"/>
-      <c r="AG6" s="430" t="n"/>
-      <c r="AH6" s="430" t="n"/>
-      <c r="AI6" s="430" t="n"/>
-      <c r="AJ6" s="430" t="n"/>
-      <c r="AK6" s="430" t="n"/>
-      <c r="AL6" s="430" t="n"/>
-      <c r="AM6" s="430" t="n"/>
-      <c r="AN6" s="430" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="725" t="n"/>
+      <c r="B6" s="725" t="n"/>
+      <c r="C6" s="725" t="n"/>
+      <c r="D6" s="725" t="n"/>
+      <c r="E6" s="725" t="n"/>
+      <c r="F6" s="725" t="n"/>
+      <c r="G6" s="725" t="n"/>
+      <c r="H6" s="725" t="n"/>
+      <c r="I6" s="725" t="n"/>
+      <c r="J6" s="725" t="n"/>
+      <c r="K6" s="725" t="n"/>
+      <c r="L6" s="725" t="n"/>
+      <c r="M6" s="725" t="n"/>
+      <c r="N6" s="725" t="n"/>
+      <c r="O6" s="725" t="n"/>
+      <c r="P6" s="725" t="n"/>
+      <c r="Q6" s="725" t="n"/>
+      <c r="R6" s="725" t="n"/>
+      <c r="S6" s="725" t="n"/>
+      <c r="T6" s="725" t="n"/>
+      <c r="U6" s="725" t="n"/>
+      <c r="V6" s="725" t="n"/>
+      <c r="W6" s="725" t="n"/>
+      <c r="X6" s="725" t="n"/>
+      <c r="Y6" s="725" t="n"/>
+      <c r="Z6" s="725" t="n"/>
+      <c r="AA6" s="725" t="n"/>
+      <c r="AB6" s="725" t="n"/>
+      <c r="AC6" s="725" t="n"/>
+      <c r="AD6" s="725" t="n"/>
+      <c r="AE6" s="725" t="n"/>
+      <c r="AF6" s="725" t="n"/>
+      <c r="AG6" s="725" t="n"/>
+      <c r="AH6" s="725" t="n"/>
+      <c r="AI6" s="725" t="n"/>
+      <c r="AJ6" s="725" t="n"/>
+      <c r="AK6" s="725" t="n"/>
+      <c r="AL6" s="725" t="n"/>
+      <c r="AM6" s="725" t="n"/>
+      <c r="AN6" s="725" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="430" t="n"/>
-      <c r="B7" s="430" t="n"/>
+      <c r="A7" s="430" t="inlineStr">
+        <is>
+          <t>VAL_DECISION_GATE_CORE</t>
+        </is>
+      </c>
+      <c r="B7" s="430" t="inlineStr">
+        <is>
+          <t>VAL_ESCALATION_LEVEL</t>
+        </is>
+      </c>
       <c r="C7" s="430" t="inlineStr">
         <is>
+          <t>VAL_STATUS_CORE</t>
+        </is>
+      </c>
+      <c r="D7" s="726" t="n"/>
+      <c r="E7" s="726" t="n"/>
+      <c r="F7" s="726" t="n"/>
+      <c r="G7" s="726" t="n"/>
+      <c r="H7" s="726" t="n"/>
+      <c r="I7" s="726" t="n"/>
+      <c r="J7" s="726" t="n"/>
+      <c r="K7" s="726" t="n"/>
+      <c r="L7" s="726" t="n"/>
+      <c r="M7" s="726" t="n"/>
+      <c r="N7" s="726" t="n"/>
+      <c r="O7" s="726" t="n"/>
+      <c r="P7" s="726" t="n"/>
+      <c r="Q7" s="726" t="n"/>
+      <c r="R7" s="726" t="n"/>
+      <c r="S7" s="726" t="n"/>
+      <c r="T7" s="726" t="n"/>
+      <c r="U7" s="726" t="n"/>
+      <c r="V7" s="726" t="n"/>
+      <c r="W7" s="726" t="n"/>
+      <c r="X7" s="726" t="n"/>
+      <c r="Y7" s="726" t="n"/>
+      <c r="Z7" s="726" t="n"/>
+      <c r="AA7" s="726" t="n"/>
+      <c r="AB7" s="726" t="n"/>
+      <c r="AC7" s="726" t="n"/>
+      <c r="AD7" s="726" t="n"/>
+      <c r="AE7" s="726" t="n"/>
+      <c r="AF7" s="726" t="n"/>
+      <c r="AG7" s="726" t="n"/>
+      <c r="AH7" s="726" t="n"/>
+      <c r="AI7" s="726" t="n"/>
+      <c r="AJ7" s="726" t="n"/>
+      <c r="AK7" s="726" t="n"/>
+      <c r="AL7" s="726" t="n"/>
+      <c r="AM7" s="726" t="n"/>
+      <c r="AN7" s="726" t="n"/>
+    </row>
+    <row r="8" hidden="1">
+      <c r="A8" s="430" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="B8" s="430" t="inlineStr">
+        <is>
+          <t>TIER 1</t>
+        </is>
+      </c>
+      <c r="C8" s="430" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D8" s="726" t="n"/>
+      <c r="E8" s="726" t="n"/>
+      <c r="F8" s="726" t="n"/>
+      <c r="G8" s="726" t="n"/>
+      <c r="H8" s="726" t="n"/>
+      <c r="I8" s="726" t="n"/>
+      <c r="J8" s="726" t="n"/>
+      <c r="K8" s="726" t="n"/>
+      <c r="L8" s="726" t="n"/>
+      <c r="M8" s="726" t="n"/>
+      <c r="N8" s="726" t="n"/>
+      <c r="O8" s="726" t="n"/>
+      <c r="P8" s="726" t="n"/>
+      <c r="Q8" s="726" t="n"/>
+      <c r="R8" s="726" t="n"/>
+      <c r="S8" s="726" t="n"/>
+      <c r="T8" s="726" t="n"/>
+      <c r="U8" s="726" t="n"/>
+      <c r="V8" s="726" t="n"/>
+      <c r="W8" s="726" t="n"/>
+      <c r="X8" s="726" t="n"/>
+      <c r="Y8" s="726" t="n"/>
+      <c r="Z8" s="726" t="n"/>
+      <c r="AA8" s="726" t="n"/>
+      <c r="AB8" s="726" t="n"/>
+      <c r="AC8" s="726" t="n"/>
+      <c r="AD8" s="726" t="n"/>
+      <c r="AE8" s="726" t="n"/>
+      <c r="AF8" s="726" t="n"/>
+      <c r="AG8" s="726" t="n"/>
+      <c r="AH8" s="726" t="n"/>
+      <c r="AI8" s="726" t="n"/>
+      <c r="AJ8" s="726" t="n"/>
+      <c r="AK8" s="726" t="n"/>
+      <c r="AL8" s="726" t="n"/>
+      <c r="AM8" s="726" t="n"/>
+      <c r="AN8" s="726" t="n"/>
+    </row>
+    <row r="9" hidden="1">
+      <c r="A9" s="430" t="inlineStr">
+        <is>
+          <t>CONDITIONAL</t>
+        </is>
+      </c>
+      <c r="B9" s="430" t="inlineStr">
+        <is>
+          <t>TIER 2</t>
+        </is>
+      </c>
+      <c r="C9" s="430" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="D9" s="726" t="n"/>
+      <c r="E9" s="726" t="n"/>
+      <c r="F9" s="726" t="n"/>
+      <c r="G9" s="726" t="n"/>
+      <c r="H9" s="726" t="n"/>
+      <c r="I9" s="726" t="n"/>
+      <c r="J9" s="726" t="n"/>
+      <c r="K9" s="726" t="n"/>
+      <c r="L9" s="726" t="n"/>
+      <c r="M9" s="726" t="n"/>
+      <c r="N9" s="726" t="n"/>
+      <c r="O9" s="726" t="n"/>
+      <c r="P9" s="726" t="n"/>
+      <c r="Q9" s="726" t="n"/>
+      <c r="R9" s="726" t="n"/>
+      <c r="S9" s="726" t="n"/>
+      <c r="T9" s="726" t="n"/>
+      <c r="U9" s="726" t="n"/>
+      <c r="V9" s="726" t="n"/>
+      <c r="W9" s="726" t="n"/>
+      <c r="X9" s="726" t="n"/>
+      <c r="Y9" s="726" t="n"/>
+      <c r="Z9" s="726" t="n"/>
+      <c r="AA9" s="726" t="n"/>
+      <c r="AB9" s="726" t="n"/>
+      <c r="AC9" s="726" t="n"/>
+      <c r="AD9" s="726" t="n"/>
+      <c r="AE9" s="726" t="n"/>
+      <c r="AF9" s="726" t="n"/>
+      <c r="AG9" s="726" t="n"/>
+      <c r="AH9" s="726" t="n"/>
+      <c r="AI9" s="726" t="n"/>
+      <c r="AJ9" s="726" t="n"/>
+      <c r="AK9" s="726" t="n"/>
+      <c r="AL9" s="726" t="n"/>
+      <c r="AM9" s="726" t="n"/>
+      <c r="AN9" s="726" t="n"/>
+    </row>
+    <row r="10" hidden="1">
+      <c r="A10" s="430" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="B10" s="430" t="inlineStr">
+        <is>
+          <t>TIER 3</t>
+        </is>
+      </c>
+      <c r="C10" s="430" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D10" s="726" t="n"/>
+      <c r="E10" s="726" t="n"/>
+      <c r="F10" s="726" t="n"/>
+      <c r="G10" s="726" t="n"/>
+      <c r="H10" s="726" t="n"/>
+      <c r="I10" s="726" t="n"/>
+      <c r="J10" s="726" t="n"/>
+      <c r="K10" s="726" t="n"/>
+      <c r="L10" s="726" t="n"/>
+      <c r="M10" s="726" t="n"/>
+      <c r="N10" s="726" t="n"/>
+      <c r="O10" s="726" t="n"/>
+      <c r="P10" s="726" t="n"/>
+      <c r="Q10" s="726" t="n"/>
+      <c r="R10" s="726" t="n"/>
+      <c r="S10" s="726" t="n"/>
+      <c r="T10" s="726" t="n"/>
+      <c r="U10" s="726" t="n"/>
+      <c r="V10" s="726" t="n"/>
+      <c r="W10" s="726" t="n"/>
+      <c r="X10" s="726" t="n"/>
+      <c r="Y10" s="726" t="n"/>
+      <c r="Z10" s="726" t="n"/>
+      <c r="AA10" s="726" t="n"/>
+      <c r="AB10" s="726" t="n"/>
+      <c r="AC10" s="726" t="n"/>
+      <c r="AD10" s="726" t="n"/>
+      <c r="AE10" s="726" t="n"/>
+      <c r="AF10" s="726" t="n"/>
+      <c r="AG10" s="726" t="n"/>
+      <c r="AH10" s="726" t="n"/>
+      <c r="AI10" s="726" t="n"/>
+      <c r="AJ10" s="726" t="n"/>
+      <c r="AK10" s="726" t="n"/>
+      <c r="AL10" s="726" t="n"/>
+      <c r="AM10" s="726" t="n"/>
+      <c r="AN10" s="726" t="n"/>
+    </row>
+    <row r="11" hidden="1">
+      <c r="A11" s="430" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="B11" s="430" t="inlineStr">
+        <is>
+          <t>WAR ROOM</t>
+        </is>
+      </c>
+      <c r="C11" s="430" t="inlineStr">
+        <is>
+          <t>MONITORING</t>
+        </is>
+      </c>
+      <c r="D11" s="726" t="n"/>
+      <c r="E11" s="726" t="n"/>
+      <c r="F11" s="726" t="n"/>
+      <c r="G11" s="726" t="n"/>
+      <c r="H11" s="726" t="n"/>
+      <c r="I11" s="726" t="n"/>
+      <c r="J11" s="726" t="n"/>
+      <c r="K11" s="726" t="n"/>
+      <c r="L11" s="726" t="n"/>
+      <c r="M11" s="726" t="n"/>
+      <c r="N11" s="726" t="n"/>
+      <c r="O11" s="726" t="n"/>
+      <c r="P11" s="726" t="n"/>
+      <c r="Q11" s="726" t="n"/>
+      <c r="R11" s="726" t="n"/>
+      <c r="S11" s="726" t="n"/>
+      <c r="T11" s="726" t="n"/>
+      <c r="U11" s="726" t="n"/>
+      <c r="V11" s="726" t="n"/>
+      <c r="W11" s="726" t="n"/>
+      <c r="X11" s="726" t="n"/>
+      <c r="Y11" s="726" t="n"/>
+      <c r="Z11" s="726" t="n"/>
+      <c r="AA11" s="726" t="n"/>
+      <c r="AB11" s="726" t="n"/>
+      <c r="AC11" s="726" t="n"/>
+      <c r="AD11" s="726" t="n"/>
+      <c r="AE11" s="726" t="n"/>
+      <c r="AF11" s="726" t="n"/>
+      <c r="AG11" s="726" t="n"/>
+      <c r="AH11" s="726" t="n"/>
+      <c r="AI11" s="726" t="n"/>
+      <c r="AJ11" s="726" t="n"/>
+      <c r="AK11" s="726" t="n"/>
+      <c r="AL11" s="726" t="n"/>
+      <c r="AM11" s="726" t="n"/>
+      <c r="AN11" s="726" t="n"/>
+    </row>
+    <row r="12" hidden="1">
+      <c r="A12" s="726" t="n"/>
+      <c r="B12" s="430" t="inlineStr">
+        <is>
+          <t>CUSTOMER</t>
+        </is>
+      </c>
+      <c r="C12" s="430" t="inlineStr">
+        <is>
+          <t>SUPERSEDED</t>
+        </is>
+      </c>
+      <c r="D12" s="726" t="n"/>
+      <c r="E12" s="726" t="n"/>
+      <c r="F12" s="726" t="n"/>
+      <c r="G12" s="726" t="n"/>
+      <c r="H12" s="726" t="n"/>
+      <c r="I12" s="726" t="n"/>
+      <c r="J12" s="726" t="n"/>
+      <c r="K12" s="726" t="n"/>
+      <c r="L12" s="726" t="n"/>
+      <c r="M12" s="726" t="n"/>
+      <c r="N12" s="726" t="n"/>
+      <c r="O12" s="726" t="n"/>
+      <c r="P12" s="726" t="n"/>
+      <c r="Q12" s="726" t="n"/>
+      <c r="R12" s="726" t="n"/>
+      <c r="S12" s="726" t="n"/>
+      <c r="T12" s="726" t="n"/>
+      <c r="U12" s="726" t="n"/>
+      <c r="V12" s="726" t="n"/>
+      <c r="W12" s="726" t="n"/>
+      <c r="X12" s="726" t="n"/>
+      <c r="Y12" s="726" t="n"/>
+      <c r="Z12" s="726" t="n"/>
+      <c r="AA12" s="726" t="n"/>
+      <c r="AB12" s="726" t="n"/>
+      <c r="AC12" s="726" t="n"/>
+      <c r="AD12" s="726" t="n"/>
+      <c r="AE12" s="726" t="n"/>
+      <c r="AF12" s="726" t="n"/>
+      <c r="AG12" s="726" t="n"/>
+      <c r="AH12" s="726" t="n"/>
+      <c r="AI12" s="726" t="n"/>
+      <c r="AJ12" s="726" t="n"/>
+      <c r="AK12" s="726" t="n"/>
+      <c r="AL12" s="726" t="n"/>
+      <c r="AM12" s="726" t="n"/>
+      <c r="AN12" s="726" t="n"/>
+    </row>
+    <row r="13" hidden="1">
+      <c r="A13" s="726" t="n"/>
+      <c r="B13" s="726" t="n"/>
+      <c r="C13" s="430" t="inlineStr">
+        <is>
           <t>VOID</t>
         </is>
       </c>
-      <c r="D7" s="430" t="n"/>
-      <c r="E7" s="430" t="n"/>
-      <c r="F7" s="430" t="n"/>
-      <c r="G7" s="430" t="n"/>
-      <c r="H7" s="430" t="n"/>
-      <c r="I7" s="430" t="n"/>
-      <c r="J7" s="430" t="n"/>
-      <c r="K7" s="430" t="n"/>
-      <c r="L7" s="430" t="n"/>
-      <c r="M7" s="430" t="n"/>
-      <c r="N7" s="430" t="n"/>
-      <c r="O7" s="430" t="n"/>
-      <c r="P7" s="430" t="n"/>
-      <c r="Q7" s="430" t="n"/>
-      <c r="R7" s="430" t="n"/>
-      <c r="S7" s="430" t="n"/>
-      <c r="T7" s="430" t="n"/>
-      <c r="U7" s="430" t="n"/>
-      <c r="V7" s="430" t="n"/>
-      <c r="W7" s="430" t="n"/>
-      <c r="X7" s="430" t="n"/>
-      <c r="Y7" s="430" t="n"/>
-      <c r="Z7" s="430" t="n"/>
-      <c r="AA7" s="430" t="n"/>
-      <c r="AB7" s="430" t="n"/>
-      <c r="AC7" s="430" t="n"/>
-      <c r="AD7" s="430" t="n"/>
-      <c r="AE7" s="430" t="n"/>
-      <c r="AF7" s="430" t="n"/>
-      <c r="AG7" s="430" t="n"/>
-      <c r="AH7" s="430" t="n"/>
-      <c r="AI7" s="430" t="n"/>
-      <c r="AJ7" s="430" t="n"/>
-      <c r="AK7" s="430" t="n"/>
-      <c r="AL7" s="430" t="n"/>
-      <c r="AM7" s="430" t="n"/>
-      <c r="AN7" s="430" t="n"/>
+      <c r="D13" s="726" t="n"/>
+      <c r="E13" s="726" t="n"/>
+      <c r="F13" s="726" t="n"/>
+      <c r="G13" s="726" t="n"/>
+      <c r="H13" s="726" t="n"/>
+      <c r="I13" s="726" t="n"/>
+      <c r="J13" s="726" t="n"/>
+      <c r="K13" s="726" t="n"/>
+      <c r="L13" s="726" t="n"/>
+      <c r="M13" s="726" t="n"/>
+      <c r="N13" s="726" t="n"/>
+      <c r="O13" s="726" t="n"/>
+      <c r="P13" s="726" t="n"/>
+      <c r="Q13" s="726" t="n"/>
+      <c r="R13" s="726" t="n"/>
+      <c r="S13" s="726" t="n"/>
+      <c r="T13" s="726" t="n"/>
+      <c r="U13" s="726" t="n"/>
+      <c r="V13" s="726" t="n"/>
+      <c r="W13" s="726" t="n"/>
+      <c r="X13" s="726" t="n"/>
+      <c r="Y13" s="726" t="n"/>
+      <c r="Z13" s="726" t="n"/>
+      <c r="AA13" s="726" t="n"/>
+      <c r="AB13" s="726" t="n"/>
+      <c r="AC13" s="726" t="n"/>
+      <c r="AD13" s="726" t="n"/>
+      <c r="AE13" s="726" t="n"/>
+      <c r="AF13" s="726" t="n"/>
+      <c r="AG13" s="726" t="n"/>
+      <c r="AH13" s="726" t="n"/>
+      <c r="AI13" s="726" t="n"/>
+      <c r="AJ13" s="726" t="n"/>
+      <c r="AK13" s="726" t="n"/>
+      <c r="AL13" s="726" t="n"/>
+      <c r="AM13" s="726" t="n"/>
+      <c r="AN13" s="726" t="n"/>
     </row>
-    <row r="8" hidden="1"/>
-    <row r="9" hidden="1"/>
-    <row r="10" hidden="1"/>
-    <row r="11" hidden="1"/>
-    <row r="12" hidden="1"/>
-    <row r="13" hidden="1"/>
-    <row r="14" hidden="1"/>
-    <row r="15" hidden="1"/>
-    <row r="16" hidden="1"/>
+    <row r="14" hidden="1">
+      <c r="A14" s="726" t="n"/>
+      <c r="B14" s="726" t="n"/>
+      <c r="C14" s="726" t="n"/>
+      <c r="D14" s="726" t="n"/>
+      <c r="E14" s="726" t="n"/>
+      <c r="F14" s="726" t="n"/>
+      <c r="G14" s="726" t="n"/>
+      <c r="H14" s="726" t="n"/>
+      <c r="I14" s="726" t="n"/>
+      <c r="J14" s="726" t="n"/>
+      <c r="K14" s="726" t="n"/>
+      <c r="L14" s="726" t="n"/>
+      <c r="M14" s="726" t="n"/>
+      <c r="N14" s="726" t="n"/>
+      <c r="O14" s="726" t="n"/>
+      <c r="P14" s="726" t="n"/>
+      <c r="Q14" s="726" t="n"/>
+      <c r="R14" s="726" t="n"/>
+      <c r="S14" s="726" t="n"/>
+      <c r="T14" s="726" t="n"/>
+      <c r="U14" s="726" t="n"/>
+      <c r="V14" s="726" t="n"/>
+      <c r="W14" s="726" t="n"/>
+      <c r="X14" s="726" t="n"/>
+      <c r="Y14" s="726" t="n"/>
+      <c r="Z14" s="726" t="n"/>
+      <c r="AA14" s="726" t="n"/>
+      <c r="AB14" s="726" t="n"/>
+      <c r="AC14" s="726" t="n"/>
+      <c r="AD14" s="726" t="n"/>
+      <c r="AE14" s="726" t="n"/>
+      <c r="AF14" s="726" t="n"/>
+      <c r="AG14" s="726" t="n"/>
+      <c r="AH14" s="726" t="n"/>
+      <c r="AI14" s="726" t="n"/>
+      <c r="AJ14" s="726" t="n"/>
+      <c r="AK14" s="726" t="n"/>
+      <c r="AL14" s="726" t="n"/>
+      <c r="AM14" s="726" t="n"/>
+      <c r="AN14" s="726" t="n"/>
+    </row>
+    <row r="15" hidden="1">
+      <c r="A15" s="726" t="n"/>
+      <c r="B15" s="726" t="n"/>
+      <c r="C15" s="726" t="n"/>
+      <c r="D15" s="726" t="n"/>
+      <c r="E15" s="726" t="n"/>
+      <c r="F15" s="726" t="n"/>
+      <c r="G15" s="726" t="n"/>
+      <c r="H15" s="726" t="n"/>
+      <c r="I15" s="726" t="n"/>
+      <c r="J15" s="726" t="n"/>
+      <c r="K15" s="726" t="n"/>
+      <c r="L15" s="726" t="n"/>
+      <c r="M15" s="726" t="n"/>
+      <c r="N15" s="726" t="n"/>
+      <c r="O15" s="726" t="n"/>
+      <c r="P15" s="726" t="n"/>
+      <c r="Q15" s="726" t="n"/>
+      <c r="R15" s="726" t="n"/>
+      <c r="S15" s="726" t="n"/>
+      <c r="T15" s="726" t="n"/>
+      <c r="U15" s="726" t="n"/>
+      <c r="V15" s="726" t="n"/>
+      <c r="W15" s="726" t="n"/>
+      <c r="X15" s="726" t="n"/>
+      <c r="Y15" s="726" t="n"/>
+      <c r="Z15" s="726" t="n"/>
+      <c r="AA15" s="726" t="n"/>
+      <c r="AB15" s="726" t="n"/>
+      <c r="AC15" s="726" t="n"/>
+      <c r="AD15" s="726" t="n"/>
+      <c r="AE15" s="726" t="n"/>
+      <c r="AF15" s="726" t="n"/>
+      <c r="AG15" s="726" t="n"/>
+      <c r="AH15" s="726" t="n"/>
+      <c r="AI15" s="726" t="n"/>
+      <c r="AJ15" s="726" t="n"/>
+      <c r="AK15" s="726" t="n"/>
+      <c r="AL15" s="726" t="n"/>
+      <c r="AM15" s="726" t="n"/>
+      <c r="AN15" s="726" t="n"/>
+    </row>
+    <row r="16" hidden="1">
+      <c r="A16" s="726" t="n"/>
+      <c r="B16" s="726" t="n"/>
+      <c r="C16" s="726" t="n"/>
+      <c r="D16" s="726" t="n"/>
+      <c r="E16" s="726" t="n"/>
+      <c r="F16" s="726" t="n"/>
+      <c r="G16" s="726" t="n"/>
+      <c r="H16" s="726" t="n"/>
+      <c r="I16" s="726" t="n"/>
+      <c r="J16" s="726" t="n"/>
+      <c r="K16" s="726" t="n"/>
+      <c r="L16" s="726" t="n"/>
+      <c r="M16" s="726" t="n"/>
+      <c r="N16" s="726" t="n"/>
+      <c r="O16" s="726" t="n"/>
+      <c r="P16" s="726" t="n"/>
+      <c r="Q16" s="726" t="n"/>
+      <c r="R16" s="726" t="n"/>
+      <c r="S16" s="726" t="n"/>
+      <c r="T16" s="726" t="n"/>
+      <c r="U16" s="726" t="n"/>
+      <c r="V16" s="726" t="n"/>
+      <c r="W16" s="726" t="n"/>
+      <c r="X16" s="726" t="n"/>
+      <c r="Y16" s="726" t="n"/>
+      <c r="Z16" s="726" t="n"/>
+      <c r="AA16" s="726" t="n"/>
+      <c r="AB16" s="726" t="n"/>
+      <c r="AC16" s="726" t="n"/>
+      <c r="AD16" s="726" t="n"/>
+      <c r="AE16" s="726" t="n"/>
+      <c r="AF16" s="726" t="n"/>
+      <c r="AG16" s="726" t="n"/>
+      <c r="AH16" s="726" t="n"/>
+      <c r="AI16" s="726" t="n"/>
+      <c r="AJ16" s="726" t="n"/>
+      <c r="AK16" s="726" t="n"/>
+      <c r="AL16" s="726" t="n"/>
+      <c r="AM16" s="726" t="n"/>
+      <c r="AN16" s="726" t="n"/>
+    </row>
     <row r="17" hidden="1"/>
     <row r="18" hidden="1"/>
     <row r="19" hidden="1"/>
@@ -10294,6 +10348,22 @@
     <row r="199" hidden="1"/>
     <row r="200" hidden="1"/>
   </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
+  </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -10305,7 +10375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN8"/>
+  <dimension ref="A1:AN17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -10350,443 +10420,832 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="594" t="inlineStr">
-        <is>
-          <t>REF_CUSTOMER_MASTER</t>
-        </is>
-      </c>
-      <c r="B1" s="552" t="inlineStr">
-        <is>
-          <t>REF_EVIDENCE_LINK</t>
-        </is>
-      </c>
-      <c r="C1" s="552" t="inlineStr">
-        <is>
-          <t>REF_OWNER_PERSON_MASTER</t>
-        </is>
-      </c>
-      <c r="D1" s="552" t="inlineStr">
-        <is>
-          <t>REF_PART_REV_MASTER</t>
-        </is>
-      </c>
-      <c r="E1" s="552" t="n"/>
-      <c r="F1" s="552" t="n"/>
-      <c r="G1" s="552" t="n"/>
-      <c r="H1" s="552" t="n"/>
-      <c r="I1" s="552" t="n"/>
-      <c r="J1" s="552" t="n"/>
-      <c r="K1" s="552" t="n"/>
-      <c r="L1" s="552" t="n"/>
-      <c r="M1" s="552" t="n"/>
-      <c r="N1" s="552" t="n"/>
-      <c r="O1" s="552" t="n"/>
-      <c r="P1" s="552" t="n"/>
-      <c r="Q1" s="552" t="n"/>
-      <c r="R1" s="552" t="n"/>
-      <c r="S1" s="552" t="n"/>
-      <c r="T1" s="552" t="n"/>
-      <c r="U1" s="552" t="n"/>
-      <c r="V1" s="552" t="n"/>
-      <c r="W1" s="552" t="n"/>
-      <c r="X1" s="552" t="n"/>
-      <c r="Y1" s="552" t="n"/>
-      <c r="Z1" s="552" t="n"/>
-      <c r="AA1" s="552" t="n"/>
-      <c r="AB1" s="552" t="n"/>
-      <c r="AC1" s="552" t="n"/>
-      <c r="AD1" s="552" t="n"/>
-      <c r="AE1" s="552" t="n"/>
-      <c r="AF1" s="552" t="n"/>
-      <c r="AG1" s="552" t="n"/>
-      <c r="AH1" s="552" t="n"/>
-      <c r="AI1" s="552" t="n"/>
-      <c r="AJ1" s="552" t="n"/>
-      <c r="AK1" s="552" t="n"/>
-      <c r="AL1" s="552" t="n"/>
-      <c r="AM1" s="552" t="n"/>
-      <c r="AN1" s="595" t="n"/>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="707" t="n"/>
+      <c r="B1" s="708" t="n"/>
+      <c r="C1" s="708" t="n"/>
+      <c r="D1" s="708" t="n"/>
+      <c r="E1" s="708" t="n"/>
+      <c r="F1" s="708" t="n"/>
+      <c r="G1" s="708" t="n"/>
+      <c r="H1" s="709" t="n"/>
+      <c r="I1" s="710" t="inlineStr"/>
+      <c r="J1" s="708" t="n"/>
+      <c r="K1" s="708" t="n"/>
+      <c r="L1" s="708" t="n"/>
+      <c r="M1" s="708" t="n"/>
+      <c r="N1" s="708" t="n"/>
+      <c r="O1" s="708" t="n"/>
+      <c r="P1" s="708" t="n"/>
+      <c r="Q1" s="708" t="n"/>
+      <c r="R1" s="708" t="n"/>
+      <c r="S1" s="708" t="n"/>
+      <c r="T1" s="708" t="n"/>
+      <c r="U1" s="708" t="n"/>
+      <c r="V1" s="708" t="n"/>
+      <c r="W1" s="708" t="n"/>
+      <c r="X1" s="708" t="n"/>
+      <c r="Y1" s="708" t="n"/>
+      <c r="Z1" s="708" t="n"/>
+      <c r="AA1" s="708" t="n"/>
+      <c r="AB1" s="708" t="n"/>
+      <c r="AC1" s="708" t="n"/>
+      <c r="AD1" s="709" t="n"/>
+      <c r="AE1" s="513" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="708" t="n"/>
+      <c r="AG1" s="708" t="n"/>
+      <c r="AH1" s="711" t="n"/>
+      <c r="AI1" s="516" t="n"/>
+      <c r="AJ1" s="708" t="n"/>
+      <c r="AK1" s="708" t="n"/>
+      <c r="AL1" s="708" t="n"/>
+      <c r="AM1" s="708" t="n"/>
+      <c r="AN1" s="709" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" s="592" t="inlineStr">
-        <is>
-          <t>CUST-001 Alpha Semi</t>
-        </is>
-      </c>
-      <c r="B2" s="437" t="inlineStr">
-        <is>
-          <t>M365://dossier/JOB-240001</t>
-        </is>
-      </c>
-      <c r="C2" s="437" t="inlineStr">
-        <is>
-          <t>Planning Lead</t>
-        </is>
-      </c>
-      <c r="D2" s="437" t="inlineStr">
-        <is>
-          <t>PN-1001 / Rev.A</t>
-        </is>
-      </c>
-      <c r="E2" s="437" t="n"/>
-      <c r="F2" s="437" t="n"/>
-      <c r="G2" s="437" t="n"/>
-      <c r="H2" s="437" t="n"/>
-      <c r="I2" s="437" t="n"/>
-      <c r="J2" s="437" t="n"/>
-      <c r="K2" s="437" t="n"/>
-      <c r="L2" s="437" t="n"/>
-      <c r="M2" s="437" t="n"/>
-      <c r="N2" s="437" t="n"/>
-      <c r="O2" s="437" t="n"/>
-      <c r="P2" s="437" t="n"/>
-      <c r="Q2" s="437" t="n"/>
-      <c r="R2" s="437" t="n"/>
-      <c r="S2" s="437" t="n"/>
-      <c r="T2" s="437" t="n"/>
-      <c r="U2" s="437" t="n"/>
-      <c r="V2" s="437" t="n"/>
-      <c r="W2" s="437" t="n"/>
-      <c r="X2" s="437" t="n"/>
-      <c r="Y2" s="437" t="n"/>
-      <c r="Z2" s="437" t="n"/>
-      <c r="AA2" s="437" t="n"/>
-      <c r="AB2" s="437" t="n"/>
-      <c r="AC2" s="437" t="n"/>
-      <c r="AD2" s="437" t="n"/>
-      <c r="AE2" s="437" t="n"/>
-      <c r="AF2" s="437" t="n"/>
-      <c r="AG2" s="437" t="n"/>
-      <c r="AH2" s="437" t="n"/>
-      <c r="AI2" s="437" t="n"/>
-      <c r="AJ2" s="437" t="n"/>
-      <c r="AK2" s="437" t="n"/>
-      <c r="AL2" s="437" t="n"/>
-      <c r="AM2" s="437" t="n"/>
-      <c r="AN2" s="564" t="n"/>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="712" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="713" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="713" t="n"/>
+      <c r="AE2" s="714" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="10" t="n"/>
+      <c r="AG2" s="10" t="n"/>
+      <c r="AH2" s="715" t="n"/>
+      <c r="AI2" s="716" t="n"/>
+      <c r="AJ2" s="10" t="n"/>
+      <c r="AK2" s="10" t="n"/>
+      <c r="AL2" s="10" t="n"/>
+      <c r="AM2" s="10" t="n"/>
+      <c r="AN2" s="713" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="592" t="inlineStr">
-        <is>
-          <t>CUST-002 NovaFab</t>
-        </is>
-      </c>
-      <c r="B3" s="437" t="inlineStr">
-        <is>
-          <t>SP://evidence/FRM-202/001</t>
-        </is>
-      </c>
-      <c r="C3" s="437" t="inlineStr">
-        <is>
-          <t>Production Supervisor</t>
-        </is>
-      </c>
-      <c r="D3" s="437" t="inlineStr">
-        <is>
-          <t>PN-1002 / Rev.B</t>
-        </is>
-      </c>
-      <c r="E3" s="437" t="n"/>
-      <c r="F3" s="437" t="n"/>
-      <c r="G3" s="437" t="n"/>
-      <c r="H3" s="437" t="n"/>
-      <c r="I3" s="437" t="n"/>
-      <c r="J3" s="437" t="n"/>
-      <c r="K3" s="437" t="n"/>
-      <c r="L3" s="437" t="n"/>
-      <c r="M3" s="437" t="n"/>
-      <c r="N3" s="437" t="n"/>
-      <c r="O3" s="437" t="n"/>
-      <c r="P3" s="437" t="n"/>
-      <c r="Q3" s="437" t="n"/>
-      <c r="R3" s="437" t="n"/>
-      <c r="S3" s="437" t="n"/>
-      <c r="T3" s="437" t="n"/>
-      <c r="U3" s="437" t="n"/>
-      <c r="V3" s="437" t="n"/>
-      <c r="W3" s="437" t="n"/>
-      <c r="X3" s="437" t="n"/>
-      <c r="Y3" s="437" t="n"/>
-      <c r="Z3" s="437" t="n"/>
-      <c r="AA3" s="437" t="n"/>
-      <c r="AB3" s="437" t="n"/>
-      <c r="AC3" s="437" t="n"/>
-      <c r="AD3" s="437" t="n"/>
-      <c r="AE3" s="437" t="n"/>
-      <c r="AF3" s="437" t="n"/>
-      <c r="AG3" s="437" t="n"/>
-      <c r="AH3" s="437" t="n"/>
-      <c r="AI3" s="437" t="n"/>
-      <c r="AJ3" s="437" t="n"/>
-      <c r="AK3" s="437" t="n"/>
-      <c r="AL3" s="437" t="n"/>
-      <c r="AM3" s="437" t="n"/>
-      <c r="AN3" s="564" t="n"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="712" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="713" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="713" t="n"/>
+      <c r="AE3" s="714" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="715" t="n"/>
+      <c r="AI3" s="716" t="n"/>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="713" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="592" t="inlineStr">
-        <is>
-          <t>CUST-003 Orion Tech</t>
-        </is>
-      </c>
-      <c r="B4" s="437" t="inlineStr">
-        <is>
-          <t>SP://evidence/FRM-306/002</t>
-        </is>
-      </c>
-      <c r="C4" s="437" t="inlineStr">
-        <is>
-          <t>QA Engineer</t>
-        </is>
-      </c>
-      <c r="D4" s="437" t="inlineStr">
-        <is>
-          <t>PN-1003 / Rev.C</t>
-        </is>
-      </c>
-      <c r="E4" s="437" t="n"/>
-      <c r="F4" s="437" t="n"/>
-      <c r="G4" s="437" t="n"/>
-      <c r="H4" s="437" t="n"/>
-      <c r="I4" s="437" t="n"/>
-      <c r="J4" s="437" t="n"/>
-      <c r="K4" s="437" t="n"/>
-      <c r="L4" s="437" t="n"/>
-      <c r="M4" s="437" t="n"/>
-      <c r="N4" s="437" t="n"/>
-      <c r="O4" s="437" t="n"/>
-      <c r="P4" s="437" t="n"/>
-      <c r="Q4" s="437" t="n"/>
-      <c r="R4" s="437" t="n"/>
-      <c r="S4" s="437" t="n"/>
-      <c r="T4" s="437" t="n"/>
-      <c r="U4" s="437" t="n"/>
-      <c r="V4" s="437" t="n"/>
-      <c r="W4" s="437" t="n"/>
-      <c r="X4" s="437" t="n"/>
-      <c r="Y4" s="437" t="n"/>
-      <c r="Z4" s="437" t="n"/>
-      <c r="AA4" s="437" t="n"/>
-      <c r="AB4" s="437" t="n"/>
-      <c r="AC4" s="437" t="n"/>
-      <c r="AD4" s="437" t="n"/>
-      <c r="AE4" s="437" t="n"/>
-      <c r="AF4" s="437" t="n"/>
-      <c r="AG4" s="437" t="n"/>
-      <c r="AH4" s="437" t="n"/>
-      <c r="AI4" s="437" t="n"/>
-      <c r="AJ4" s="437" t="n"/>
-      <c r="AK4" s="437" t="n"/>
-      <c r="AL4" s="437" t="n"/>
-      <c r="AM4" s="437" t="n"/>
-      <c r="AN4" s="564" t="n"/>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="712" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="713" t="n"/>
+      <c r="I4" s="717" t="inlineStr"/>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="713" t="n"/>
+      <c r="AE4" s="714" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="715" t="n"/>
+      <c r="AI4" s="716" t="n"/>
+      <c r="AJ4" s="10" t="n"/>
+      <c r="AK4" s="10" t="n"/>
+      <c r="AL4" s="10" t="n"/>
+      <c r="AM4" s="10" t="n"/>
+      <c r="AN4" s="713" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="592" t="inlineStr">
-        <is>
-          <t>CUST-004 Quantum Devices</t>
-        </is>
-      </c>
-      <c r="B5" s="437" t="inlineStr">
-        <is>
-          <t>Epicor://Job/JOB-240001</t>
-        </is>
-      </c>
-      <c r="C5" s="437" t="inlineStr">
-        <is>
-          <t>Engineering Lead</t>
-        </is>
-      </c>
-      <c r="D5" s="437" t="inlineStr">
-        <is>
-          <t>PN-1004 / Rev.D</t>
-        </is>
-      </c>
-      <c r="E5" s="437" t="n"/>
-      <c r="F5" s="437" t="n"/>
-      <c r="G5" s="437" t="n"/>
-      <c r="H5" s="437" t="n"/>
-      <c r="I5" s="437" t="n"/>
-      <c r="J5" s="437" t="n"/>
-      <c r="K5" s="437" t="n"/>
-      <c r="L5" s="437" t="n"/>
-      <c r="M5" s="437" t="n"/>
-      <c r="N5" s="437" t="n"/>
-      <c r="O5" s="437" t="n"/>
-      <c r="P5" s="437" t="n"/>
-      <c r="Q5" s="437" t="n"/>
-      <c r="R5" s="437" t="n"/>
-      <c r="S5" s="437" t="n"/>
-      <c r="T5" s="437" t="n"/>
-      <c r="U5" s="437" t="n"/>
-      <c r="V5" s="437" t="n"/>
-      <c r="W5" s="437" t="n"/>
-      <c r="X5" s="437" t="n"/>
-      <c r="Y5" s="437" t="n"/>
-      <c r="Z5" s="437" t="n"/>
-      <c r="AA5" s="437" t="n"/>
-      <c r="AB5" s="437" t="n"/>
-      <c r="AC5" s="437" t="n"/>
-      <c r="AD5" s="437" t="n"/>
-      <c r="AE5" s="437" t="n"/>
-      <c r="AF5" s="437" t="n"/>
-      <c r="AG5" s="437" t="n"/>
-      <c r="AH5" s="437" t="n"/>
-      <c r="AI5" s="437" t="n"/>
-      <c r="AJ5" s="437" t="n"/>
-      <c r="AK5" s="437" t="n"/>
-      <c r="AL5" s="437" t="n"/>
-      <c r="AM5" s="437" t="n"/>
-      <c r="AN5" s="564" t="n"/>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="718" t="n"/>
+      <c r="B5" s="719" t="n"/>
+      <c r="C5" s="719" t="n"/>
+      <c r="D5" s="719" t="n"/>
+      <c r="E5" s="719" t="n"/>
+      <c r="F5" s="719" t="n"/>
+      <c r="G5" s="719" t="n"/>
+      <c r="H5" s="720" t="n"/>
+      <c r="I5" s="721" t="inlineStr"/>
+      <c r="J5" s="719" t="n"/>
+      <c r="K5" s="719" t="n"/>
+      <c r="L5" s="719" t="n"/>
+      <c r="M5" s="719" t="n"/>
+      <c r="N5" s="719" t="n"/>
+      <c r="O5" s="719" t="n"/>
+      <c r="P5" s="719" t="n"/>
+      <c r="Q5" s="719" t="n"/>
+      <c r="R5" s="719" t="n"/>
+      <c r="S5" s="719" t="n"/>
+      <c r="T5" s="719" t="n"/>
+      <c r="U5" s="719" t="n"/>
+      <c r="V5" s="719" t="n"/>
+      <c r="W5" s="719" t="n"/>
+      <c r="X5" s="719" t="n"/>
+      <c r="Y5" s="719" t="n"/>
+      <c r="Z5" s="719" t="n"/>
+      <c r="AA5" s="719" t="n"/>
+      <c r="AB5" s="719" t="n"/>
+      <c r="AC5" s="719" t="n"/>
+      <c r="AD5" s="720" t="n"/>
+      <c r="AE5" s="722" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="719" t="n"/>
+      <c r="AG5" s="719" t="n"/>
+      <c r="AH5" s="723" t="n"/>
+      <c r="AI5" s="724" t="n"/>
+      <c r="AJ5" s="719" t="n"/>
+      <c r="AK5" s="719" t="n"/>
+      <c r="AL5" s="719" t="n"/>
+      <c r="AM5" s="719" t="n"/>
+      <c r="AN5" s="720" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="592" t="n"/>
-      <c r="B6" s="437" t="n"/>
-      <c r="C6" s="437" t="inlineStr">
-        <is>
-          <t>Setup Technician</t>
-        </is>
-      </c>
-      <c r="D6" s="437" t="n"/>
-      <c r="E6" s="437" t="n"/>
-      <c r="F6" s="437" t="n"/>
-      <c r="G6" s="437" t="n"/>
-      <c r="H6" s="437" t="n"/>
-      <c r="I6" s="437" t="n"/>
-      <c r="J6" s="437" t="n"/>
-      <c r="K6" s="437" t="n"/>
-      <c r="L6" s="437" t="n"/>
-      <c r="M6" s="437" t="n"/>
-      <c r="N6" s="437" t="n"/>
-      <c r="O6" s="437" t="n"/>
-      <c r="P6" s="437" t="n"/>
-      <c r="Q6" s="437" t="n"/>
-      <c r="R6" s="437" t="n"/>
-      <c r="S6" s="437" t="n"/>
-      <c r="T6" s="437" t="n"/>
-      <c r="U6" s="437" t="n"/>
-      <c r="V6" s="437" t="n"/>
-      <c r="W6" s="437" t="n"/>
-      <c r="X6" s="437" t="n"/>
-      <c r="Y6" s="437" t="n"/>
-      <c r="Z6" s="437" t="n"/>
-      <c r="AA6" s="437" t="n"/>
-      <c r="AB6" s="437" t="n"/>
-      <c r="AC6" s="437" t="n"/>
-      <c r="AD6" s="437" t="n"/>
-      <c r="AE6" s="437" t="n"/>
-      <c r="AF6" s="437" t="n"/>
-      <c r="AG6" s="437" t="n"/>
-      <c r="AH6" s="437" t="n"/>
-      <c r="AI6" s="437" t="n"/>
-      <c r="AJ6" s="437" t="n"/>
-      <c r="AK6" s="437" t="n"/>
-      <c r="AL6" s="437" t="n"/>
-      <c r="AM6" s="437" t="n"/>
-      <c r="AN6" s="564" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="725" t="n"/>
+      <c r="B6" s="725" t="n"/>
+      <c r="C6" s="725" t="n"/>
+      <c r="D6" s="725" t="n"/>
+      <c r="E6" s="725" t="n"/>
+      <c r="F6" s="725" t="n"/>
+      <c r="G6" s="725" t="n"/>
+      <c r="H6" s="725" t="n"/>
+      <c r="I6" s="725" t="n"/>
+      <c r="J6" s="725" t="n"/>
+      <c r="K6" s="725" t="n"/>
+      <c r="L6" s="725" t="n"/>
+      <c r="M6" s="725" t="n"/>
+      <c r="N6" s="725" t="n"/>
+      <c r="O6" s="725" t="n"/>
+      <c r="P6" s="725" t="n"/>
+      <c r="Q6" s="725" t="n"/>
+      <c r="R6" s="725" t="n"/>
+      <c r="S6" s="725" t="n"/>
+      <c r="T6" s="725" t="n"/>
+      <c r="U6" s="725" t="n"/>
+      <c r="V6" s="725" t="n"/>
+      <c r="W6" s="725" t="n"/>
+      <c r="X6" s="725" t="n"/>
+      <c r="Y6" s="725" t="n"/>
+      <c r="Z6" s="725" t="n"/>
+      <c r="AA6" s="725" t="n"/>
+      <c r="AB6" s="725" t="n"/>
+      <c r="AC6" s="725" t="n"/>
+      <c r="AD6" s="725" t="n"/>
+      <c r="AE6" s="725" t="n"/>
+      <c r="AF6" s="725" t="n"/>
+      <c r="AG6" s="725" t="n"/>
+      <c r="AH6" s="725" t="n"/>
+      <c r="AI6" s="725" t="n"/>
+      <c r="AJ6" s="725" t="n"/>
+      <c r="AK6" s="725" t="n"/>
+      <c r="AL6" s="725" t="n"/>
+      <c r="AM6" s="725" t="n"/>
+      <c r="AN6" s="725" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="592" t="n"/>
-      <c r="B7" s="437" t="n"/>
-      <c r="C7" s="437" t="inlineStr">
-        <is>
-          <t>Maintenance Lead</t>
-        </is>
-      </c>
-      <c r="D7" s="437" t="n"/>
-      <c r="E7" s="437" t="n"/>
-      <c r="F7" s="437" t="n"/>
-      <c r="G7" s="437" t="n"/>
-      <c r="H7" s="437" t="n"/>
-      <c r="I7" s="437" t="n"/>
-      <c r="J7" s="437" t="n"/>
-      <c r="K7" s="437" t="n"/>
-      <c r="L7" s="437" t="n"/>
-      <c r="M7" s="437" t="n"/>
-      <c r="N7" s="437" t="n"/>
-      <c r="O7" s="437" t="n"/>
-      <c r="P7" s="437" t="n"/>
-      <c r="Q7" s="437" t="n"/>
-      <c r="R7" s="437" t="n"/>
-      <c r="S7" s="437" t="n"/>
-      <c r="T7" s="437" t="n"/>
-      <c r="U7" s="437" t="n"/>
-      <c r="V7" s="437" t="n"/>
-      <c r="W7" s="437" t="n"/>
-      <c r="X7" s="437" t="n"/>
-      <c r="Y7" s="437" t="n"/>
-      <c r="Z7" s="437" t="n"/>
-      <c r="AA7" s="437" t="n"/>
-      <c r="AB7" s="437" t="n"/>
-      <c r="AC7" s="437" t="n"/>
-      <c r="AD7" s="437" t="n"/>
-      <c r="AE7" s="437" t="n"/>
-      <c r="AF7" s="437" t="n"/>
-      <c r="AG7" s="437" t="n"/>
-      <c r="AH7" s="437" t="n"/>
-      <c r="AI7" s="437" t="n"/>
-      <c r="AJ7" s="437" t="n"/>
-      <c r="AK7" s="437" t="n"/>
-      <c r="AL7" s="437" t="n"/>
-      <c r="AM7" s="437" t="n"/>
-      <c r="AN7" s="564" t="n"/>
+      <c r="A7" s="594" t="inlineStr">
+        <is>
+          <t>REF_CUSTOMER_MASTER</t>
+        </is>
+      </c>
+      <c r="B7" s="552" t="inlineStr">
+        <is>
+          <t>REF_EVIDENCE_LINK</t>
+        </is>
+      </c>
+      <c r="C7" s="552" t="inlineStr">
+        <is>
+          <t>REF_OWNER_PERSON_MASTER</t>
+        </is>
+      </c>
+      <c r="D7" s="552" t="inlineStr">
+        <is>
+          <t>REF_PART_REV_MASTER</t>
+        </is>
+      </c>
+      <c r="E7" s="726" t="n"/>
+      <c r="F7" s="726" t="n"/>
+      <c r="G7" s="726" t="n"/>
+      <c r="H7" s="726" t="n"/>
+      <c r="I7" s="726" t="n"/>
+      <c r="J7" s="726" t="n"/>
+      <c r="K7" s="726" t="n"/>
+      <c r="L7" s="726" t="n"/>
+      <c r="M7" s="726" t="n"/>
+      <c r="N7" s="726" t="n"/>
+      <c r="O7" s="726" t="n"/>
+      <c r="P7" s="726" t="n"/>
+      <c r="Q7" s="726" t="n"/>
+      <c r="R7" s="726" t="n"/>
+      <c r="S7" s="726" t="n"/>
+      <c r="T7" s="726" t="n"/>
+      <c r="U7" s="726" t="n"/>
+      <c r="V7" s="726" t="n"/>
+      <c r="W7" s="726" t="n"/>
+      <c r="X7" s="726" t="n"/>
+      <c r="Y7" s="726" t="n"/>
+      <c r="Z7" s="726" t="n"/>
+      <c r="AA7" s="726" t="n"/>
+      <c r="AB7" s="726" t="n"/>
+      <c r="AC7" s="726" t="n"/>
+      <c r="AD7" s="726" t="n"/>
+      <c r="AE7" s="726" t="n"/>
+      <c r="AF7" s="726" t="n"/>
+      <c r="AG7" s="726" t="n"/>
+      <c r="AH7" s="726" t="n"/>
+      <c r="AI7" s="726" t="n"/>
+      <c r="AJ7" s="726" t="n"/>
+      <c r="AK7" s="726" t="n"/>
+      <c r="AL7" s="726" t="n"/>
+      <c r="AM7" s="726" t="n"/>
+      <c r="AN7" s="726" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="596" t="n"/>
-      <c r="B8" s="572" t="n"/>
-      <c r="C8" s="572" t="inlineStr">
+      <c r="A8" s="592" t="inlineStr">
+        <is>
+          <t>CUST-001 Alpha Semi</t>
+        </is>
+      </c>
+      <c r="B8" s="437" t="inlineStr">
+        <is>
+          <t>M365://dossier/JOB-240001</t>
+        </is>
+      </c>
+      <c r="C8" s="437" t="inlineStr">
+        <is>
+          <t>Planning Lead</t>
+        </is>
+      </c>
+      <c r="D8" s="437" t="inlineStr">
+        <is>
+          <t>PN-1001 / Rev.A</t>
+        </is>
+      </c>
+      <c r="E8" s="726" t="n"/>
+      <c r="F8" s="726" t="n"/>
+      <c r="G8" s="726" t="n"/>
+      <c r="H8" s="726" t="n"/>
+      <c r="I8" s="726" t="n"/>
+      <c r="J8" s="726" t="n"/>
+      <c r="K8" s="726" t="n"/>
+      <c r="L8" s="726" t="n"/>
+      <c r="M8" s="726" t="n"/>
+      <c r="N8" s="726" t="n"/>
+      <c r="O8" s="726" t="n"/>
+      <c r="P8" s="726" t="n"/>
+      <c r="Q8" s="726" t="n"/>
+      <c r="R8" s="726" t="n"/>
+      <c r="S8" s="726" t="n"/>
+      <c r="T8" s="726" t="n"/>
+      <c r="U8" s="726" t="n"/>
+      <c r="V8" s="726" t="n"/>
+      <c r="W8" s="726" t="n"/>
+      <c r="X8" s="726" t="n"/>
+      <c r="Y8" s="726" t="n"/>
+      <c r="Z8" s="726" t="n"/>
+      <c r="AA8" s="726" t="n"/>
+      <c r="AB8" s="726" t="n"/>
+      <c r="AC8" s="726" t="n"/>
+      <c r="AD8" s="726" t="n"/>
+      <c r="AE8" s="726" t="n"/>
+      <c r="AF8" s="726" t="n"/>
+      <c r="AG8" s="726" t="n"/>
+      <c r="AH8" s="726" t="n"/>
+      <c r="AI8" s="726" t="n"/>
+      <c r="AJ8" s="726" t="n"/>
+      <c r="AK8" s="726" t="n"/>
+      <c r="AL8" s="726" t="n"/>
+      <c r="AM8" s="726" t="n"/>
+      <c r="AN8" s="726" t="n"/>
+    </row>
+    <row r="9" hidden="1">
+      <c r="A9" s="592" t="inlineStr">
+        <is>
+          <t>CUST-002 NovaFab</t>
+        </is>
+      </c>
+      <c r="B9" s="437" t="inlineStr">
+        <is>
+          <t>SP://evidence/FRM-202/001</t>
+        </is>
+      </c>
+      <c r="C9" s="437" t="inlineStr">
+        <is>
+          <t>Production Supervisor</t>
+        </is>
+      </c>
+      <c r="D9" s="437" t="inlineStr">
+        <is>
+          <t>PN-1002 / Rev.B</t>
+        </is>
+      </c>
+      <c r="E9" s="726" t="n"/>
+      <c r="F9" s="726" t="n"/>
+      <c r="G9" s="726" t="n"/>
+      <c r="H9" s="726" t="n"/>
+      <c r="I9" s="726" t="n"/>
+      <c r="J9" s="726" t="n"/>
+      <c r="K9" s="726" t="n"/>
+      <c r="L9" s="726" t="n"/>
+      <c r="M9" s="726" t="n"/>
+      <c r="N9" s="726" t="n"/>
+      <c r="O9" s="726" t="n"/>
+      <c r="P9" s="726" t="n"/>
+      <c r="Q9" s="726" t="n"/>
+      <c r="R9" s="726" t="n"/>
+      <c r="S9" s="726" t="n"/>
+      <c r="T9" s="726" t="n"/>
+      <c r="U9" s="726" t="n"/>
+      <c r="V9" s="726" t="n"/>
+      <c r="W9" s="726" t="n"/>
+      <c r="X9" s="726" t="n"/>
+      <c r="Y9" s="726" t="n"/>
+      <c r="Z9" s="726" t="n"/>
+      <c r="AA9" s="726" t="n"/>
+      <c r="AB9" s="726" t="n"/>
+      <c r="AC9" s="726" t="n"/>
+      <c r="AD9" s="726" t="n"/>
+      <c r="AE9" s="726" t="n"/>
+      <c r="AF9" s="726" t="n"/>
+      <c r="AG9" s="726" t="n"/>
+      <c r="AH9" s="726" t="n"/>
+      <c r="AI9" s="726" t="n"/>
+      <c r="AJ9" s="726" t="n"/>
+      <c r="AK9" s="726" t="n"/>
+      <c r="AL9" s="726" t="n"/>
+      <c r="AM9" s="726" t="n"/>
+      <c r="AN9" s="726" t="n"/>
+    </row>
+    <row r="10" hidden="1">
+      <c r="A10" s="592" t="inlineStr">
+        <is>
+          <t>CUST-003 Orion Tech</t>
+        </is>
+      </c>
+      <c r="B10" s="437" t="inlineStr">
+        <is>
+          <t>SP://evidence/FRM-306/002</t>
+        </is>
+      </c>
+      <c r="C10" s="437" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="D10" s="437" t="inlineStr">
+        <is>
+          <t>PN-1003 / Rev.C</t>
+        </is>
+      </c>
+      <c r="E10" s="726" t="n"/>
+      <c r="F10" s="726" t="n"/>
+      <c r="G10" s="726" t="n"/>
+      <c r="H10" s="726" t="n"/>
+      <c r="I10" s="726" t="n"/>
+      <c r="J10" s="726" t="n"/>
+      <c r="K10" s="726" t="n"/>
+      <c r="L10" s="726" t="n"/>
+      <c r="M10" s="726" t="n"/>
+      <c r="N10" s="726" t="n"/>
+      <c r="O10" s="726" t="n"/>
+      <c r="P10" s="726" t="n"/>
+      <c r="Q10" s="726" t="n"/>
+      <c r="R10" s="726" t="n"/>
+      <c r="S10" s="726" t="n"/>
+      <c r="T10" s="726" t="n"/>
+      <c r="U10" s="726" t="n"/>
+      <c r="V10" s="726" t="n"/>
+      <c r="W10" s="726" t="n"/>
+      <c r="X10" s="726" t="n"/>
+      <c r="Y10" s="726" t="n"/>
+      <c r="Z10" s="726" t="n"/>
+      <c r="AA10" s="726" t="n"/>
+      <c r="AB10" s="726" t="n"/>
+      <c r="AC10" s="726" t="n"/>
+      <c r="AD10" s="726" t="n"/>
+      <c r="AE10" s="726" t="n"/>
+      <c r="AF10" s="726" t="n"/>
+      <c r="AG10" s="726" t="n"/>
+      <c r="AH10" s="726" t="n"/>
+      <c r="AI10" s="726" t="n"/>
+      <c r="AJ10" s="726" t="n"/>
+      <c r="AK10" s="726" t="n"/>
+      <c r="AL10" s="726" t="n"/>
+      <c r="AM10" s="726" t="n"/>
+      <c r="AN10" s="726" t="n"/>
+    </row>
+    <row r="11" hidden="1">
+      <c r="A11" s="592" t="inlineStr">
+        <is>
+          <t>CUST-004 Quantum Devices</t>
+        </is>
+      </c>
+      <c r="B11" s="437" t="inlineStr">
+        <is>
+          <t>Epicor://Job/JOB-240001</t>
+        </is>
+      </c>
+      <c r="C11" s="437" t="inlineStr">
+        <is>
+          <t>Engineering Lead</t>
+        </is>
+      </c>
+      <c r="D11" s="437" t="inlineStr">
+        <is>
+          <t>PN-1004 / Rev.D</t>
+        </is>
+      </c>
+      <c r="E11" s="726" t="n"/>
+      <c r="F11" s="726" t="n"/>
+      <c r="G11" s="726" t="n"/>
+      <c r="H11" s="726" t="n"/>
+      <c r="I11" s="726" t="n"/>
+      <c r="J11" s="726" t="n"/>
+      <c r="K11" s="726" t="n"/>
+      <c r="L11" s="726" t="n"/>
+      <c r="M11" s="726" t="n"/>
+      <c r="N11" s="726" t="n"/>
+      <c r="O11" s="726" t="n"/>
+      <c r="P11" s="726" t="n"/>
+      <c r="Q11" s="726" t="n"/>
+      <c r="R11" s="726" t="n"/>
+      <c r="S11" s="726" t="n"/>
+      <c r="T11" s="726" t="n"/>
+      <c r="U11" s="726" t="n"/>
+      <c r="V11" s="726" t="n"/>
+      <c r="W11" s="726" t="n"/>
+      <c r="X11" s="726" t="n"/>
+      <c r="Y11" s="726" t="n"/>
+      <c r="Z11" s="726" t="n"/>
+      <c r="AA11" s="726" t="n"/>
+      <c r="AB11" s="726" t="n"/>
+      <c r="AC11" s="726" t="n"/>
+      <c r="AD11" s="726" t="n"/>
+      <c r="AE11" s="726" t="n"/>
+      <c r="AF11" s="726" t="n"/>
+      <c r="AG11" s="726" t="n"/>
+      <c r="AH11" s="726" t="n"/>
+      <c r="AI11" s="726" t="n"/>
+      <c r="AJ11" s="726" t="n"/>
+      <c r="AK11" s="726" t="n"/>
+      <c r="AL11" s="726" t="n"/>
+      <c r="AM11" s="726" t="n"/>
+      <c r="AN11" s="726" t="n"/>
+    </row>
+    <row r="12" hidden="1">
+      <c r="A12" s="726" t="n"/>
+      <c r="B12" s="726" t="n"/>
+      <c r="C12" s="437" t="inlineStr">
+        <is>
+          <t>Setup Technician</t>
+        </is>
+      </c>
+      <c r="D12" s="726" t="n"/>
+      <c r="E12" s="726" t="n"/>
+      <c r="F12" s="726" t="n"/>
+      <c r="G12" s="726" t="n"/>
+      <c r="H12" s="726" t="n"/>
+      <c r="I12" s="726" t="n"/>
+      <c r="J12" s="726" t="n"/>
+      <c r="K12" s="726" t="n"/>
+      <c r="L12" s="726" t="n"/>
+      <c r="M12" s="726" t="n"/>
+      <c r="N12" s="726" t="n"/>
+      <c r="O12" s="726" t="n"/>
+      <c r="P12" s="726" t="n"/>
+      <c r="Q12" s="726" t="n"/>
+      <c r="R12" s="726" t="n"/>
+      <c r="S12" s="726" t="n"/>
+      <c r="T12" s="726" t="n"/>
+      <c r="U12" s="726" t="n"/>
+      <c r="V12" s="726" t="n"/>
+      <c r="W12" s="726" t="n"/>
+      <c r="X12" s="726" t="n"/>
+      <c r="Y12" s="726" t="n"/>
+      <c r="Z12" s="726" t="n"/>
+      <c r="AA12" s="726" t="n"/>
+      <c r="AB12" s="726" t="n"/>
+      <c r="AC12" s="726" t="n"/>
+      <c r="AD12" s="726" t="n"/>
+      <c r="AE12" s="726" t="n"/>
+      <c r="AF12" s="726" t="n"/>
+      <c r="AG12" s="726" t="n"/>
+      <c r="AH12" s="726" t="n"/>
+      <c r="AI12" s="726" t="n"/>
+      <c r="AJ12" s="726" t="n"/>
+      <c r="AK12" s="726" t="n"/>
+      <c r="AL12" s="726" t="n"/>
+      <c r="AM12" s="726" t="n"/>
+      <c r="AN12" s="726" t="n"/>
+    </row>
+    <row r="13" hidden="1">
+      <c r="A13" s="726" t="n"/>
+      <c r="B13" s="726" t="n"/>
+      <c r="C13" s="437" t="inlineStr">
+        <is>
+          <t>Maintenance Lead</t>
+        </is>
+      </c>
+      <c r="D13" s="726" t="n"/>
+      <c r="E13" s="726" t="n"/>
+      <c r="F13" s="726" t="n"/>
+      <c r="G13" s="726" t="n"/>
+      <c r="H13" s="726" t="n"/>
+      <c r="I13" s="726" t="n"/>
+      <c r="J13" s="726" t="n"/>
+      <c r="K13" s="726" t="n"/>
+      <c r="L13" s="726" t="n"/>
+      <c r="M13" s="726" t="n"/>
+      <c r="N13" s="726" t="n"/>
+      <c r="O13" s="726" t="n"/>
+      <c r="P13" s="726" t="n"/>
+      <c r="Q13" s="726" t="n"/>
+      <c r="R13" s="726" t="n"/>
+      <c r="S13" s="726" t="n"/>
+      <c r="T13" s="726" t="n"/>
+      <c r="U13" s="726" t="n"/>
+      <c r="V13" s="726" t="n"/>
+      <c r="W13" s="726" t="n"/>
+      <c r="X13" s="726" t="n"/>
+      <c r="Y13" s="726" t="n"/>
+      <c r="Z13" s="726" t="n"/>
+      <c r="AA13" s="726" t="n"/>
+      <c r="AB13" s="726" t="n"/>
+      <c r="AC13" s="726" t="n"/>
+      <c r="AD13" s="726" t="n"/>
+      <c r="AE13" s="726" t="n"/>
+      <c r="AF13" s="726" t="n"/>
+      <c r="AG13" s="726" t="n"/>
+      <c r="AH13" s="726" t="n"/>
+      <c r="AI13" s="726" t="n"/>
+      <c r="AJ13" s="726" t="n"/>
+      <c r="AK13" s="726" t="n"/>
+      <c r="AL13" s="726" t="n"/>
+      <c r="AM13" s="726" t="n"/>
+      <c r="AN13" s="726" t="n"/>
+    </row>
+    <row r="14" hidden="1">
+      <c r="A14" s="726" t="n"/>
+      <c r="B14" s="726" t="n"/>
+      <c r="C14" s="572" t="inlineStr">
         <is>
           <t>Commercial Owner</t>
         </is>
       </c>
-      <c r="D8" s="572" t="n"/>
-      <c r="E8" s="572" t="n"/>
-      <c r="F8" s="572" t="n"/>
-      <c r="G8" s="572" t="n"/>
-      <c r="H8" s="572" t="n"/>
-      <c r="I8" s="572" t="n"/>
-      <c r="J8" s="572" t="n"/>
-      <c r="K8" s="572" t="n"/>
-      <c r="L8" s="572" t="n"/>
-      <c r="M8" s="572" t="n"/>
-      <c r="N8" s="572" t="n"/>
-      <c r="O8" s="572" t="n"/>
-      <c r="P8" s="572" t="n"/>
-      <c r="Q8" s="572" t="n"/>
-      <c r="R8" s="572" t="n"/>
-      <c r="S8" s="572" t="n"/>
-      <c r="T8" s="572" t="n"/>
-      <c r="U8" s="572" t="n"/>
-      <c r="V8" s="572" t="n"/>
-      <c r="W8" s="572" t="n"/>
-      <c r="X8" s="572" t="n"/>
-      <c r="Y8" s="572" t="n"/>
-      <c r="Z8" s="572" t="n"/>
-      <c r="AA8" s="572" t="n"/>
-      <c r="AB8" s="572" t="n"/>
-      <c r="AC8" s="572" t="n"/>
-      <c r="AD8" s="572" t="n"/>
-      <c r="AE8" s="572" t="n"/>
-      <c r="AF8" s="572" t="n"/>
-      <c r="AG8" s="572" t="n"/>
-      <c r="AH8" s="572" t="n"/>
-      <c r="AI8" s="572" t="n"/>
-      <c r="AJ8" s="572" t="n"/>
-      <c r="AK8" s="572" t="n"/>
-      <c r="AL8" s="572" t="n"/>
-      <c r="AM8" s="572" t="n"/>
-      <c r="AN8" s="573" t="n"/>
+      <c r="D14" s="726" t="n"/>
+      <c r="E14" s="726" t="n"/>
+      <c r="F14" s="726" t="n"/>
+      <c r="G14" s="726" t="n"/>
+      <c r="H14" s="726" t="n"/>
+      <c r="I14" s="726" t="n"/>
+      <c r="J14" s="726" t="n"/>
+      <c r="K14" s="726" t="n"/>
+      <c r="L14" s="726" t="n"/>
+      <c r="M14" s="726" t="n"/>
+      <c r="N14" s="726" t="n"/>
+      <c r="O14" s="726" t="n"/>
+      <c r="P14" s="726" t="n"/>
+      <c r="Q14" s="726" t="n"/>
+      <c r="R14" s="726" t="n"/>
+      <c r="S14" s="726" t="n"/>
+      <c r="T14" s="726" t="n"/>
+      <c r="U14" s="726" t="n"/>
+      <c r="V14" s="726" t="n"/>
+      <c r="W14" s="726" t="n"/>
+      <c r="X14" s="726" t="n"/>
+      <c r="Y14" s="726" t="n"/>
+      <c r="Z14" s="726" t="n"/>
+      <c r="AA14" s="726" t="n"/>
+      <c r="AB14" s="726" t="n"/>
+      <c r="AC14" s="726" t="n"/>
+      <c r="AD14" s="726" t="n"/>
+      <c r="AE14" s="726" t="n"/>
+      <c r="AF14" s="726" t="n"/>
+      <c r="AG14" s="726" t="n"/>
+      <c r="AH14" s="726" t="n"/>
+      <c r="AI14" s="726" t="n"/>
+      <c r="AJ14" s="726" t="n"/>
+      <c r="AK14" s="726" t="n"/>
+      <c r="AL14" s="726" t="n"/>
+      <c r="AM14" s="726" t="n"/>
+      <c r="AN14" s="726" t="n"/>
     </row>
-    <row r="9" hidden="1"/>
-    <row r="10" hidden="1"/>
-    <row r="11" hidden="1"/>
-    <row r="12" hidden="1"/>
-    <row r="13" hidden="1"/>
-    <row r="14" hidden="1"/>
-    <row r="15" hidden="1"/>
-    <row r="16" hidden="1"/>
-    <row r="17" hidden="1"/>
+    <row r="15" hidden="1">
+      <c r="A15" s="726" t="n"/>
+      <c r="B15" s="726" t="n"/>
+      <c r="C15" s="726" t="n"/>
+      <c r="D15" s="726" t="n"/>
+      <c r="E15" s="726" t="n"/>
+      <c r="F15" s="726" t="n"/>
+      <c r="G15" s="726" t="n"/>
+      <c r="H15" s="726" t="n"/>
+      <c r="I15" s="726" t="n"/>
+      <c r="J15" s="726" t="n"/>
+      <c r="K15" s="726" t="n"/>
+      <c r="L15" s="726" t="n"/>
+      <c r="M15" s="726" t="n"/>
+      <c r="N15" s="726" t="n"/>
+      <c r="O15" s="726" t="n"/>
+      <c r="P15" s="726" t="n"/>
+      <c r="Q15" s="726" t="n"/>
+      <c r="R15" s="726" t="n"/>
+      <c r="S15" s="726" t="n"/>
+      <c r="T15" s="726" t="n"/>
+      <c r="U15" s="726" t="n"/>
+      <c r="V15" s="726" t="n"/>
+      <c r="W15" s="726" t="n"/>
+      <c r="X15" s="726" t="n"/>
+      <c r="Y15" s="726" t="n"/>
+      <c r="Z15" s="726" t="n"/>
+      <c r="AA15" s="726" t="n"/>
+      <c r="AB15" s="726" t="n"/>
+      <c r="AC15" s="726" t="n"/>
+      <c r="AD15" s="726" t="n"/>
+      <c r="AE15" s="726" t="n"/>
+      <c r="AF15" s="726" t="n"/>
+      <c r="AG15" s="726" t="n"/>
+      <c r="AH15" s="726" t="n"/>
+      <c r="AI15" s="726" t="n"/>
+      <c r="AJ15" s="726" t="n"/>
+      <c r="AK15" s="726" t="n"/>
+      <c r="AL15" s="726" t="n"/>
+      <c r="AM15" s="726" t="n"/>
+      <c r="AN15" s="726" t="n"/>
+    </row>
+    <row r="16" hidden="1">
+      <c r="A16" s="726" t="n"/>
+      <c r="B16" s="726" t="n"/>
+      <c r="C16" s="726" t="n"/>
+      <c r="D16" s="726" t="n"/>
+      <c r="E16" s="726" t="n"/>
+      <c r="F16" s="726" t="n"/>
+      <c r="G16" s="726" t="n"/>
+      <c r="H16" s="726" t="n"/>
+      <c r="I16" s="726" t="n"/>
+      <c r="J16" s="726" t="n"/>
+      <c r="K16" s="726" t="n"/>
+      <c r="L16" s="726" t="n"/>
+      <c r="M16" s="726" t="n"/>
+      <c r="N16" s="726" t="n"/>
+      <c r="O16" s="726" t="n"/>
+      <c r="P16" s="726" t="n"/>
+      <c r="Q16" s="726" t="n"/>
+      <c r="R16" s="726" t="n"/>
+      <c r="S16" s="726" t="n"/>
+      <c r="T16" s="726" t="n"/>
+      <c r="U16" s="726" t="n"/>
+      <c r="V16" s="726" t="n"/>
+      <c r="W16" s="726" t="n"/>
+      <c r="X16" s="726" t="n"/>
+      <c r="Y16" s="726" t="n"/>
+      <c r="Z16" s="726" t="n"/>
+      <c r="AA16" s="726" t="n"/>
+      <c r="AB16" s="726" t="n"/>
+      <c r="AC16" s="726" t="n"/>
+      <c r="AD16" s="726" t="n"/>
+      <c r="AE16" s="726" t="n"/>
+      <c r="AF16" s="726" t="n"/>
+      <c r="AG16" s="726" t="n"/>
+      <c r="AH16" s="726" t="n"/>
+      <c r="AI16" s="726" t="n"/>
+      <c r="AJ16" s="726" t="n"/>
+      <c r="AK16" s="726" t="n"/>
+      <c r="AL16" s="726" t="n"/>
+      <c r="AM16" s="726" t="n"/>
+      <c r="AN16" s="726" t="n"/>
+    </row>
+    <row r="17" hidden="1">
+      <c r="A17" s="726" t="n"/>
+      <c r="B17" s="726" t="n"/>
+      <c r="C17" s="726" t="n"/>
+      <c r="D17" s="726" t="n"/>
+      <c r="E17" s="726" t="n"/>
+      <c r="F17" s="726" t="n"/>
+      <c r="G17" s="726" t="n"/>
+      <c r="H17" s="726" t="n"/>
+      <c r="I17" s="726" t="n"/>
+      <c r="J17" s="726" t="n"/>
+      <c r="K17" s="726" t="n"/>
+      <c r="L17" s="726" t="n"/>
+      <c r="M17" s="726" t="n"/>
+      <c r="N17" s="726" t="n"/>
+      <c r="O17" s="726" t="n"/>
+      <c r="P17" s="726" t="n"/>
+      <c r="Q17" s="726" t="n"/>
+      <c r="R17" s="726" t="n"/>
+      <c r="S17" s="726" t="n"/>
+      <c r="T17" s="726" t="n"/>
+      <c r="U17" s="726" t="n"/>
+      <c r="V17" s="726" t="n"/>
+      <c r="W17" s="726" t="n"/>
+      <c r="X17" s="726" t="n"/>
+      <c r="Y17" s="726" t="n"/>
+      <c r="Z17" s="726" t="n"/>
+      <c r="AA17" s="726" t="n"/>
+      <c r="AB17" s="726" t="n"/>
+      <c r="AC17" s="726" t="n"/>
+      <c r="AD17" s="726" t="n"/>
+      <c r="AE17" s="726" t="n"/>
+      <c r="AF17" s="726" t="n"/>
+      <c r="AG17" s="726" t="n"/>
+      <c r="AH17" s="726" t="n"/>
+      <c r="AI17" s="726" t="n"/>
+      <c r="AJ17" s="726" t="n"/>
+      <c r="AK17" s="726" t="n"/>
+      <c r="AL17" s="726" t="n"/>
+      <c r="AM17" s="726" t="n"/>
+      <c r="AN17" s="726" t="n"/>
+    </row>
     <row r="18" hidden="1"/>
     <row r="19" hidden="1"/>
     <row r="20" hidden="1"/>
@@ -10971,6 +11430,22 @@
     <row r="199" hidden="1"/>
     <row r="200" hidden="1"/>
   </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
+  </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -12268,51 +12743,51 @@
       <c r="AM25" s="666" t="n"/>
       <c r="AN25" s="667" t="n"/>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="644" t="inlineStr">
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="704" t="inlineStr">
         <is>
           <t>NOTICE  —  Periodic review and closeout support sheet for the rolling workbook.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B26" s="289" t="n"/>
-      <c r="C26" s="289" t="n"/>
-      <c r="D26" s="289" t="n"/>
-      <c r="E26" s="289" t="n"/>
-      <c r="F26" s="289" t="n"/>
-      <c r="G26" s="289" t="n"/>
-      <c r="H26" s="289" t="n"/>
-      <c r="I26" s="645" t="n"/>
-      <c r="J26" s="645" t="n"/>
-      <c r="K26" s="645" t="n"/>
-      <c r="L26" s="645" t="n"/>
-      <c r="M26" s="645" t="n"/>
-      <c r="N26" s="645" t="n"/>
-      <c r="O26" s="645" t="n"/>
-      <c r="P26" s="645" t="n"/>
-      <c r="Q26" s="645" t="n"/>
-      <c r="R26" s="645" t="n"/>
-      <c r="S26" s="645" t="n"/>
-      <c r="T26" s="645" t="n"/>
-      <c r="U26" s="645" t="n"/>
-      <c r="V26" s="645" t="n"/>
-      <c r="W26" s="645" t="n"/>
-      <c r="X26" s="645" t="n"/>
-      <c r="Y26" s="645" t="n"/>
-      <c r="Z26" s="645" t="n"/>
-      <c r="AA26" s="645" t="n"/>
-      <c r="AB26" s="645" t="n"/>
-      <c r="AC26" s="645" t="n"/>
-      <c r="AD26" s="645" t="n"/>
-      <c r="AE26" s="645" t="n"/>
-      <c r="AF26" s="645" t="n"/>
-      <c r="AG26" s="645" t="n"/>
-      <c r="AH26" s="645" t="n"/>
-      <c r="AI26" s="645" t="n"/>
-      <c r="AJ26" s="645" t="n"/>
-      <c r="AK26" s="645" t="n"/>
-      <c r="AL26" s="645" t="n"/>
-      <c r="AM26" s="645" t="n"/>
-      <c r="AN26" s="646" t="n"/>
+      <c r="B26" s="705" t="n"/>
+      <c r="C26" s="705" t="n"/>
+      <c r="D26" s="705" t="n"/>
+      <c r="E26" s="705" t="n"/>
+      <c r="F26" s="705" t="n"/>
+      <c r="G26" s="705" t="n"/>
+      <c r="H26" s="705" t="n"/>
+      <c r="I26" s="705" t="n"/>
+      <c r="J26" s="705" t="n"/>
+      <c r="K26" s="705" t="n"/>
+      <c r="L26" s="705" t="n"/>
+      <c r="M26" s="705" t="n"/>
+      <c r="N26" s="705" t="n"/>
+      <c r="O26" s="705" t="n"/>
+      <c r="P26" s="705" t="n"/>
+      <c r="Q26" s="705" t="n"/>
+      <c r="R26" s="705" t="n"/>
+      <c r="S26" s="705" t="n"/>
+      <c r="T26" s="705" t="n"/>
+      <c r="U26" s="705" t="n"/>
+      <c r="V26" s="705" t="n"/>
+      <c r="W26" s="705" t="n"/>
+      <c r="X26" s="705" t="n"/>
+      <c r="Y26" s="705" t="n"/>
+      <c r="Z26" s="705" t="n"/>
+      <c r="AA26" s="705" t="n"/>
+      <c r="AB26" s="705" t="n"/>
+      <c r="AC26" s="705" t="n"/>
+      <c r="AD26" s="705" t="n"/>
+      <c r="AE26" s="705" t="n"/>
+      <c r="AF26" s="705" t="n"/>
+      <c r="AG26" s="705" t="n"/>
+      <c r="AH26" s="705" t="n"/>
+      <c r="AI26" s="705" t="n"/>
+      <c r="AJ26" s="705" t="n"/>
+      <c r="AK26" s="705" t="n"/>
+      <c r="AL26" s="705" t="n"/>
+      <c r="AM26" s="705" t="n"/>
+      <c r="AN26" s="706" t="n"/>
     </row>
     <row r="27" hidden="1" outlineLevel="1"/>
     <row r="28" hidden="1" outlineLevel="1"/>
@@ -12554,7 +13029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -12600,506 +13075,895 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="606" t="inlineStr">
-        <is>
-          <t>REF_LINKS</t>
-        </is>
-      </c>
-      <c r="B1" s="690" t="n"/>
-      <c r="C1" s="690" t="n"/>
-      <c r="D1" s="690" t="n"/>
-      <c r="E1" s="690" t="n"/>
-      <c r="F1" s="690" t="n"/>
-      <c r="G1" s="690" t="n"/>
-      <c r="H1" s="607" t="n"/>
-      <c r="I1" s="509" t="n"/>
-      <c r="J1" s="510" t="n"/>
-      <c r="K1" s="510" t="n"/>
-      <c r="L1" s="510" t="n"/>
-      <c r="M1" s="510" t="n"/>
-      <c r="N1" s="510" t="n"/>
-      <c r="O1" s="510" t="n"/>
-      <c r="P1" s="510" t="n"/>
-      <c r="Q1" s="510" t="n"/>
-      <c r="R1" s="510" t="n"/>
-      <c r="S1" s="510" t="n"/>
-      <c r="T1" s="510" t="n"/>
-      <c r="U1" s="510" t="n"/>
-      <c r="V1" s="510" t="n"/>
-      <c r="W1" s="510" t="n"/>
-      <c r="X1" s="510" t="n"/>
-      <c r="Y1" s="510" t="n"/>
-      <c r="Z1" s="510" t="n"/>
-      <c r="AA1" s="510" t="n"/>
-      <c r="AB1" s="510" t="n"/>
-      <c r="AC1" s="510" t="n"/>
-      <c r="AD1" s="511" t="n"/>
-      <c r="AE1" s="512" t="n"/>
-      <c r="AF1" s="513" t="n"/>
-      <c r="AG1" s="513" t="n"/>
-      <c r="AH1" s="514" t="n"/>
-      <c r="AI1" s="515" t="n"/>
-      <c r="AJ1" s="516" t="n"/>
-      <c r="AK1" s="516" t="n"/>
-      <c r="AL1" s="516" t="n"/>
-      <c r="AM1" s="516" t="n"/>
-      <c r="AN1" s="517" t="n"/>
+      <c r="A1" s="707" t="n"/>
+      <c r="B1" s="708" t="n"/>
+      <c r="C1" s="708" t="n"/>
+      <c r="D1" s="708" t="n"/>
+      <c r="E1" s="708" t="n"/>
+      <c r="F1" s="708" t="n"/>
+      <c r="G1" s="708" t="n"/>
+      <c r="H1" s="709" t="n"/>
+      <c r="I1" s="710" t="inlineStr"/>
+      <c r="J1" s="708" t="n"/>
+      <c r="K1" s="708" t="n"/>
+      <c r="L1" s="708" t="n"/>
+      <c r="M1" s="708" t="n"/>
+      <c r="N1" s="708" t="n"/>
+      <c r="O1" s="708" t="n"/>
+      <c r="P1" s="708" t="n"/>
+      <c r="Q1" s="708" t="n"/>
+      <c r="R1" s="708" t="n"/>
+      <c r="S1" s="708" t="n"/>
+      <c r="T1" s="708" t="n"/>
+      <c r="U1" s="708" t="n"/>
+      <c r="V1" s="708" t="n"/>
+      <c r="W1" s="708" t="n"/>
+      <c r="X1" s="708" t="n"/>
+      <c r="Y1" s="708" t="n"/>
+      <c r="Z1" s="708" t="n"/>
+      <c r="AA1" s="708" t="n"/>
+      <c r="AB1" s="708" t="n"/>
+      <c r="AC1" s="708" t="n"/>
+      <c r="AD1" s="709" t="n"/>
+      <c r="AE1" s="513" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="708" t="n"/>
+      <c r="AG1" s="708" t="n"/>
+      <c r="AH1" s="711" t="n"/>
+      <c r="AI1" s="516" t="n"/>
+      <c r="AJ1" s="708" t="n"/>
+      <c r="AK1" s="708" t="n"/>
+      <c r="AL1" s="708" t="n"/>
+      <c r="AM1" s="708" t="n"/>
+      <c r="AN1" s="709" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="608" t="inlineStr">
-        <is>
-          <t>Reference Epicor / M365 / controlled documents only.</t>
-        </is>
-      </c>
-      <c r="H2" s="609" t="n"/>
-      <c r="I2" s="520" t="n"/>
-      <c r="J2" s="521" t="n"/>
-      <c r="K2" s="521" t="n"/>
-      <c r="L2" s="521" t="n"/>
-      <c r="M2" s="521" t="n"/>
-      <c r="N2" s="521" t="n"/>
-      <c r="O2" s="521" t="n"/>
-      <c r="P2" s="521" t="n"/>
-      <c r="Q2" s="521" t="n"/>
-      <c r="R2" s="521" t="n"/>
-      <c r="S2" s="521" t="n"/>
-      <c r="T2" s="521" t="n"/>
-      <c r="U2" s="521" t="n"/>
-      <c r="V2" s="521" t="n"/>
-      <c r="W2" s="521" t="n"/>
-      <c r="X2" s="521" t="n"/>
-      <c r="Y2" s="521" t="n"/>
-      <c r="Z2" s="521" t="n"/>
-      <c r="AA2" s="521" t="n"/>
-      <c r="AB2" s="521" t="n"/>
-      <c r="AC2" s="521" t="n"/>
-      <c r="AD2" s="522" t="n"/>
-      <c r="AE2" s="523" t="n"/>
-      <c r="AF2" s="524" t="n"/>
-      <c r="AG2" s="524" t="n"/>
-      <c r="AH2" s="525" t="n"/>
-      <c r="AI2" s="526" t="n"/>
-      <c r="AJ2" s="527" t="n"/>
-      <c r="AK2" s="527" t="n"/>
-      <c r="AL2" s="527" t="n"/>
-      <c r="AM2" s="527" t="n"/>
-      <c r="AN2" s="528" t="n"/>
+      <c r="A2" s="712" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="713" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="713" t="n"/>
+      <c r="AE2" s="714" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="10" t="n"/>
+      <c r="AG2" s="10" t="n"/>
+      <c r="AH2" s="715" t="n"/>
+      <c r="AI2" s="716" t="n"/>
+      <c r="AJ2" s="10" t="n"/>
+      <c r="AK2" s="10" t="n"/>
+      <c r="AL2" s="10" t="n"/>
+      <c r="AM2" s="10" t="n"/>
+      <c r="AN2" s="713" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="610" t="inlineStr">
-        <is>
-          <t>Ref Type</t>
-        </is>
-      </c>
-      <c r="B3" s="611" t="inlineStr">
-        <is>
-          <t>Document / Record</t>
-        </is>
-      </c>
-      <c r="C3" s="611" t="inlineStr">
-        <is>
-          <t>System of Record</t>
-        </is>
-      </c>
-      <c r="D3" s="611" t="inlineStr">
-        <is>
-          <t>Unique Ref</t>
-        </is>
-      </c>
-      <c r="E3" s="611" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F3" s="611" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G3" s="611" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="H3" s="609" t="n"/>
-      <c r="I3" s="520" t="n"/>
-      <c r="J3" s="521" t="n"/>
-      <c r="K3" s="521" t="n"/>
-      <c r="L3" s="521" t="n"/>
-      <c r="M3" s="521" t="n"/>
-      <c r="N3" s="521" t="n"/>
-      <c r="O3" s="521" t="n"/>
-      <c r="P3" s="521" t="n"/>
-      <c r="Q3" s="521" t="n"/>
-      <c r="R3" s="521" t="n"/>
-      <c r="S3" s="521" t="n"/>
-      <c r="T3" s="521" t="n"/>
-      <c r="U3" s="521" t="n"/>
-      <c r="V3" s="521" t="n"/>
-      <c r="W3" s="521" t="n"/>
-      <c r="X3" s="521" t="n"/>
-      <c r="Y3" s="521" t="n"/>
-      <c r="Z3" s="521" t="n"/>
-      <c r="AA3" s="521" t="n"/>
-      <c r="AB3" s="521" t="n"/>
-      <c r="AC3" s="521" t="n"/>
-      <c r="AD3" s="522" t="n"/>
-      <c r="AE3" s="523" t="n"/>
-      <c r="AF3" s="524" t="n"/>
-      <c r="AG3" s="524" t="n"/>
-      <c r="AH3" s="525" t="n"/>
-      <c r="AI3" s="526" t="n"/>
-      <c r="AJ3" s="527" t="n"/>
-      <c r="AK3" s="527" t="n"/>
-      <c r="AL3" s="527" t="n"/>
-      <c r="AM3" s="527" t="n"/>
-      <c r="AN3" s="528" t="n"/>
+      <c r="A3" s="712" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="713" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="713" t="n"/>
+      <c r="AE3" s="714" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="715" t="n"/>
+      <c r="AI3" s="716" t="n"/>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="713" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="612" t="n"/>
-      <c r="B4" s="613" t="n"/>
-      <c r="C4" s="613" t="n"/>
-      <c r="D4" s="613" t="n"/>
-      <c r="E4" s="613" t="n"/>
-      <c r="F4" s="613" t="n"/>
-      <c r="G4" s="613" t="n"/>
-      <c r="H4" s="609" t="n"/>
-      <c r="I4" s="530" t="n"/>
-      <c r="J4" s="531" t="n"/>
-      <c r="K4" s="531" t="n"/>
-      <c r="L4" s="531" t="n"/>
-      <c r="M4" s="531" t="n"/>
-      <c r="N4" s="531" t="n"/>
-      <c r="O4" s="531" t="n"/>
-      <c r="P4" s="531" t="n"/>
-      <c r="Q4" s="531" t="n"/>
-      <c r="R4" s="531" t="n"/>
-      <c r="S4" s="531" t="n"/>
-      <c r="T4" s="531" t="n"/>
-      <c r="U4" s="531" t="n"/>
-      <c r="V4" s="531" t="n"/>
-      <c r="W4" s="531" t="n"/>
-      <c r="X4" s="531" t="n"/>
-      <c r="Y4" s="531" t="n"/>
-      <c r="Z4" s="531" t="n"/>
-      <c r="AA4" s="531" t="n"/>
-      <c r="AB4" s="531" t="n"/>
-      <c r="AC4" s="531" t="n"/>
-      <c r="AD4" s="532" t="n"/>
-      <c r="AE4" s="523" t="n"/>
-      <c r="AF4" s="524" t="n"/>
-      <c r="AG4" s="524" t="n"/>
-      <c r="AH4" s="525" t="n"/>
-      <c r="AI4" s="526" t="n"/>
-      <c r="AJ4" s="527" t="n"/>
-      <c r="AK4" s="527" t="n"/>
-      <c r="AL4" s="527" t="n"/>
-      <c r="AM4" s="527" t="n"/>
-      <c r="AN4" s="528" t="n"/>
+      <c r="A4" s="712" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="713" t="n"/>
+      <c r="I4" s="717" t="inlineStr"/>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="713" t="n"/>
+      <c r="AE4" s="714" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="715" t="n"/>
+      <c r="AI4" s="716" t="n"/>
+      <c r="AJ4" s="10" t="n"/>
+      <c r="AK4" s="10" t="n"/>
+      <c r="AL4" s="10" t="n"/>
+      <c r="AM4" s="10" t="n"/>
+      <c r="AN4" s="713" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="614" t="n"/>
-      <c r="B5" s="615" t="n"/>
-      <c r="C5" s="615" t="n"/>
-      <c r="D5" s="615" t="n"/>
-      <c r="E5" s="615" t="n"/>
-      <c r="F5" s="615" t="n"/>
-      <c r="G5" s="615" t="n"/>
-      <c r="H5" s="616" t="n"/>
-      <c r="I5" s="537" t="n"/>
-      <c r="J5" s="538" t="n"/>
-      <c r="K5" s="538" t="n"/>
-      <c r="L5" s="538" t="n"/>
-      <c r="M5" s="538" t="n"/>
-      <c r="N5" s="538" t="n"/>
-      <c r="O5" s="538" t="n"/>
-      <c r="P5" s="538" t="n"/>
-      <c r="Q5" s="538" t="n"/>
-      <c r="R5" s="538" t="n"/>
-      <c r="S5" s="538" t="n"/>
-      <c r="T5" s="538" t="n"/>
-      <c r="U5" s="538" t="n"/>
-      <c r="V5" s="538" t="n"/>
-      <c r="W5" s="538" t="n"/>
-      <c r="X5" s="538" t="n"/>
-      <c r="Y5" s="538" t="n"/>
-      <c r="Z5" s="538" t="n"/>
-      <c r="AA5" s="538" t="n"/>
-      <c r="AB5" s="538" t="n"/>
-      <c r="AC5" s="538" t="n"/>
-      <c r="AD5" s="539" t="n"/>
-      <c r="AE5" s="540" t="n"/>
-      <c r="AF5" s="541" t="n"/>
-      <c r="AG5" s="541" t="n"/>
-      <c r="AH5" s="542" t="n"/>
-      <c r="AI5" s="543" t="n"/>
-      <c r="AJ5" s="544" t="n"/>
-      <c r="AK5" s="544" t="n"/>
-      <c r="AL5" s="544" t="n"/>
-      <c r="AM5" s="544" t="n"/>
-      <c r="AN5" s="545" t="n"/>
+      <c r="A5" s="718" t="n"/>
+      <c r="B5" s="719" t="n"/>
+      <c r="C5" s="719" t="n"/>
+      <c r="D5" s="719" t="n"/>
+      <c r="E5" s="719" t="n"/>
+      <c r="F5" s="719" t="n"/>
+      <c r="G5" s="719" t="n"/>
+      <c r="H5" s="720" t="n"/>
+      <c r="I5" s="721" t="inlineStr"/>
+      <c r="J5" s="719" t="n"/>
+      <c r="K5" s="719" t="n"/>
+      <c r="L5" s="719" t="n"/>
+      <c r="M5" s="719" t="n"/>
+      <c r="N5" s="719" t="n"/>
+      <c r="O5" s="719" t="n"/>
+      <c r="P5" s="719" t="n"/>
+      <c r="Q5" s="719" t="n"/>
+      <c r="R5" s="719" t="n"/>
+      <c r="S5" s="719" t="n"/>
+      <c r="T5" s="719" t="n"/>
+      <c r="U5" s="719" t="n"/>
+      <c r="V5" s="719" t="n"/>
+      <c r="W5" s="719" t="n"/>
+      <c r="X5" s="719" t="n"/>
+      <c r="Y5" s="719" t="n"/>
+      <c r="Z5" s="719" t="n"/>
+      <c r="AA5" s="719" t="n"/>
+      <c r="AB5" s="719" t="n"/>
+      <c r="AC5" s="719" t="n"/>
+      <c r="AD5" s="720" t="n"/>
+      <c r="AE5" s="722" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="719" t="n"/>
+      <c r="AG5" s="719" t="n"/>
+      <c r="AH5" s="723" t="n"/>
+      <c r="AI5" s="724" t="n"/>
+      <c r="AJ5" s="719" t="n"/>
+      <c r="AK5" s="719" t="n"/>
+      <c r="AL5" s="719" t="n"/>
+      <c r="AM5" s="719" t="n"/>
+      <c r="AN5" s="720" t="n"/>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="617" t="n"/>
-      <c r="B6" s="618" t="n"/>
-      <c r="C6" s="618" t="n"/>
-      <c r="D6" s="618" t="n"/>
-      <c r="E6" s="618" t="n"/>
-      <c r="F6" s="618" t="n"/>
-      <c r="G6" s="618" t="n"/>
-      <c r="H6" s="552" t="n"/>
-      <c r="I6" s="552" t="n"/>
-      <c r="J6" s="552" t="n"/>
-      <c r="K6" s="552" t="n"/>
-      <c r="L6" s="552" t="n"/>
-      <c r="M6" s="552" t="n"/>
-      <c r="N6" s="552" t="n"/>
-      <c r="O6" s="552" t="n"/>
-      <c r="P6" s="552" t="n"/>
-      <c r="Q6" s="552" t="n"/>
-      <c r="R6" s="552" t="n"/>
-      <c r="S6" s="552" t="n"/>
-      <c r="T6" s="552" t="n"/>
-      <c r="U6" s="552" t="n"/>
-      <c r="V6" s="552" t="n"/>
-      <c r="W6" s="552" t="n"/>
-      <c r="X6" s="552" t="n"/>
-      <c r="Y6" s="552" t="n"/>
-      <c r="Z6" s="552" t="n"/>
-      <c r="AA6" s="552" t="n"/>
-      <c r="AB6" s="552" t="n"/>
-      <c r="AC6" s="552" t="n"/>
-      <c r="AD6" s="552" t="n"/>
-      <c r="AE6" s="552" t="n"/>
-      <c r="AF6" s="552" t="n"/>
-      <c r="AG6" s="552" t="n"/>
-      <c r="AH6" s="552" t="n"/>
-      <c r="AI6" s="552" t="n"/>
-      <c r="AJ6" s="552" t="n"/>
-      <c r="AK6" s="552" t="n"/>
-      <c r="AL6" s="552" t="n"/>
-      <c r="AM6" s="552" t="n"/>
-      <c r="AN6" s="595" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="725" t="n"/>
+      <c r="B6" s="725" t="n"/>
+      <c r="C6" s="725" t="n"/>
+      <c r="D6" s="725" t="n"/>
+      <c r="E6" s="725" t="n"/>
+      <c r="F6" s="725" t="n"/>
+      <c r="G6" s="725" t="n"/>
+      <c r="H6" s="725" t="n"/>
+      <c r="I6" s="725" t="n"/>
+      <c r="J6" s="725" t="n"/>
+      <c r="K6" s="725" t="n"/>
+      <c r="L6" s="725" t="n"/>
+      <c r="M6" s="725" t="n"/>
+      <c r="N6" s="725" t="n"/>
+      <c r="O6" s="725" t="n"/>
+      <c r="P6" s="725" t="n"/>
+      <c r="Q6" s="725" t="n"/>
+      <c r="R6" s="725" t="n"/>
+      <c r="S6" s="725" t="n"/>
+      <c r="T6" s="725" t="n"/>
+      <c r="U6" s="725" t="n"/>
+      <c r="V6" s="725" t="n"/>
+      <c r="W6" s="725" t="n"/>
+      <c r="X6" s="725" t="n"/>
+      <c r="Y6" s="725" t="n"/>
+      <c r="Z6" s="725" t="n"/>
+      <c r="AA6" s="725" t="n"/>
+      <c r="AB6" s="725" t="n"/>
+      <c r="AC6" s="725" t="n"/>
+      <c r="AD6" s="725" t="n"/>
+      <c r="AE6" s="725" t="n"/>
+      <c r="AF6" s="725" t="n"/>
+      <c r="AG6" s="725" t="n"/>
+      <c r="AH6" s="725" t="n"/>
+      <c r="AI6" s="725" t="n"/>
+      <c r="AJ6" s="725" t="n"/>
+      <c r="AK6" s="725" t="n"/>
+      <c r="AL6" s="725" t="n"/>
+      <c r="AM6" s="725" t="n"/>
+      <c r="AN6" s="725" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="619" t="n"/>
-      <c r="B7" s="620" t="n"/>
-      <c r="C7" s="620" t="n"/>
-      <c r="D7" s="620" t="n"/>
-      <c r="E7" s="620" t="n"/>
-      <c r="F7" s="620" t="n"/>
-      <c r="G7" s="620" t="n"/>
-      <c r="H7" s="437" t="n"/>
-      <c r="I7" s="437" t="n"/>
-      <c r="J7" s="437" t="n"/>
-      <c r="K7" s="437" t="n"/>
-      <c r="L7" s="437" t="n"/>
-      <c r="M7" s="437" t="n"/>
-      <c r="N7" s="437" t="n"/>
-      <c r="O7" s="437" t="n"/>
-      <c r="P7" s="437" t="n"/>
-      <c r="Q7" s="437" t="n"/>
-      <c r="R7" s="437" t="n"/>
-      <c r="S7" s="437" t="n"/>
-      <c r="T7" s="437" t="n"/>
-      <c r="U7" s="437" t="n"/>
-      <c r="V7" s="437" t="n"/>
-      <c r="W7" s="437" t="n"/>
-      <c r="X7" s="437" t="n"/>
-      <c r="Y7" s="437" t="n"/>
-      <c r="Z7" s="437" t="n"/>
-      <c r="AA7" s="437" t="n"/>
-      <c r="AB7" s="437" t="n"/>
-      <c r="AC7" s="437" t="n"/>
-      <c r="AD7" s="437" t="n"/>
-      <c r="AE7" s="437" t="n"/>
-      <c r="AF7" s="437" t="n"/>
-      <c r="AG7" s="437" t="n"/>
-      <c r="AH7" s="437" t="n"/>
-      <c r="AI7" s="437" t="n"/>
-      <c r="AJ7" s="437" t="n"/>
-      <c r="AK7" s="437" t="n"/>
-      <c r="AL7" s="437" t="n"/>
-      <c r="AM7" s="437" t="n"/>
-      <c r="AN7" s="564" t="n"/>
+      <c r="A7" s="606" t="inlineStr">
+        <is>
+          <t>REF_LINKS</t>
+        </is>
+      </c>
+      <c r="B7" s="690" t="n"/>
+      <c r="C7" s="690" t="n"/>
+      <c r="D7" s="690" t="n"/>
+      <c r="E7" s="690" t="n"/>
+      <c r="F7" s="690" t="n"/>
+      <c r="G7" s="690" t="n"/>
+      <c r="H7" s="726" t="n"/>
+      <c r="I7" s="726" t="n"/>
+      <c r="J7" s="726" t="n"/>
+      <c r="K7" s="726" t="n"/>
+      <c r="L7" s="726" t="n"/>
+      <c r="M7" s="726" t="n"/>
+      <c r="N7" s="726" t="n"/>
+      <c r="O7" s="726" t="n"/>
+      <c r="P7" s="726" t="n"/>
+      <c r="Q7" s="726" t="n"/>
+      <c r="R7" s="726" t="n"/>
+      <c r="S7" s="726" t="n"/>
+      <c r="T7" s="726" t="n"/>
+      <c r="U7" s="726" t="n"/>
+      <c r="V7" s="726" t="n"/>
+      <c r="W7" s="726" t="n"/>
+      <c r="X7" s="726" t="n"/>
+      <c r="Y7" s="726" t="n"/>
+      <c r="Z7" s="726" t="n"/>
+      <c r="AA7" s="726" t="n"/>
+      <c r="AB7" s="726" t="n"/>
+      <c r="AC7" s="726" t="n"/>
+      <c r="AD7" s="726" t="n"/>
+      <c r="AE7" s="726" t="n"/>
+      <c r="AF7" s="726" t="n"/>
+      <c r="AG7" s="726" t="n"/>
+      <c r="AH7" s="726" t="n"/>
+      <c r="AI7" s="726" t="n"/>
+      <c r="AJ7" s="726" t="n"/>
+      <c r="AK7" s="726" t="n"/>
+      <c r="AL7" s="726" t="n"/>
+      <c r="AM7" s="726" t="n"/>
+      <c r="AN7" s="726" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="619" t="n"/>
-      <c r="B8" s="620" t="n"/>
-      <c r="C8" s="620" t="n"/>
-      <c r="D8" s="620" t="n"/>
-      <c r="E8" s="620" t="n"/>
-      <c r="F8" s="620" t="n"/>
-      <c r="G8" s="620" t="n"/>
-      <c r="H8" s="446" t="n"/>
-      <c r="I8" s="446" t="n"/>
-      <c r="J8" s="446" t="n"/>
-      <c r="K8" s="446" t="n"/>
-      <c r="L8" s="446" t="n"/>
-      <c r="M8" s="446" t="n"/>
-      <c r="N8" s="446" t="n"/>
-      <c r="O8" s="446" t="n"/>
-      <c r="P8" s="446" t="n"/>
-      <c r="Q8" s="446" t="n"/>
-      <c r="R8" s="446" t="n"/>
-      <c r="S8" s="446" t="n"/>
-      <c r="T8" s="446" t="n"/>
-      <c r="U8" s="446" t="n"/>
-      <c r="V8" s="446" t="n"/>
-      <c r="W8" s="446" t="n"/>
-      <c r="X8" s="446" t="n"/>
-      <c r="Y8" s="446" t="n"/>
-      <c r="Z8" s="446" t="n"/>
-      <c r="AA8" s="446" t="n"/>
-      <c r="AB8" s="446" t="n"/>
-      <c r="AC8" s="446" t="n"/>
-      <c r="AD8" s="446" t="n"/>
-      <c r="AE8" s="446" t="n"/>
-      <c r="AF8" s="446" t="n"/>
-      <c r="AG8" s="446" t="n"/>
-      <c r="AH8" s="446" t="n"/>
-      <c r="AI8" s="446" t="n"/>
-      <c r="AJ8" s="446" t="n"/>
-      <c r="AK8" s="446" t="n"/>
-      <c r="AL8" s="446" t="n"/>
-      <c r="AM8" s="446" t="n"/>
-      <c r="AN8" s="562" t="n"/>
+      <c r="A8" s="608" t="inlineStr">
+        <is>
+          <t>Reference Epicor / M365 / controlled documents only.</t>
+        </is>
+      </c>
+      <c r="H8" s="726" t="n"/>
+      <c r="I8" s="726" t="n"/>
+      <c r="J8" s="726" t="n"/>
+      <c r="K8" s="726" t="n"/>
+      <c r="L8" s="726" t="n"/>
+      <c r="M8" s="726" t="n"/>
+      <c r="N8" s="726" t="n"/>
+      <c r="O8" s="726" t="n"/>
+      <c r="P8" s="726" t="n"/>
+      <c r="Q8" s="726" t="n"/>
+      <c r="R8" s="726" t="n"/>
+      <c r="S8" s="726" t="n"/>
+      <c r="T8" s="726" t="n"/>
+      <c r="U8" s="726" t="n"/>
+      <c r="V8" s="726" t="n"/>
+      <c r="W8" s="726" t="n"/>
+      <c r="X8" s="726" t="n"/>
+      <c r="Y8" s="726" t="n"/>
+      <c r="Z8" s="726" t="n"/>
+      <c r="AA8" s="726" t="n"/>
+      <c r="AB8" s="726" t="n"/>
+      <c r="AC8" s="726" t="n"/>
+      <c r="AD8" s="726" t="n"/>
+      <c r="AE8" s="726" t="n"/>
+      <c r="AF8" s="726" t="n"/>
+      <c r="AG8" s="726" t="n"/>
+      <c r="AH8" s="726" t="n"/>
+      <c r="AI8" s="726" t="n"/>
+      <c r="AJ8" s="726" t="n"/>
+      <c r="AK8" s="726" t="n"/>
+      <c r="AL8" s="726" t="n"/>
+      <c r="AM8" s="726" t="n"/>
+      <c r="AN8" s="726" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="619" t="n"/>
-      <c r="B9" s="620" t="n"/>
-      <c r="C9" s="620" t="n"/>
-      <c r="D9" s="620" t="n"/>
-      <c r="E9" s="620" t="n"/>
-      <c r="F9" s="620" t="n"/>
-      <c r="G9" s="620" t="n"/>
-      <c r="H9" s="446" t="n"/>
-      <c r="I9" s="446" t="n"/>
-      <c r="J9" s="446" t="n"/>
-      <c r="K9" s="446" t="n"/>
-      <c r="L9" s="446" t="n"/>
-      <c r="M9" s="446" t="n"/>
-      <c r="N9" s="446" t="n"/>
-      <c r="O9" s="446" t="n"/>
-      <c r="P9" s="446" t="n"/>
-      <c r="Q9" s="446" t="n"/>
-      <c r="R9" s="446" t="n"/>
-      <c r="S9" s="446" t="n"/>
-      <c r="T9" s="446" t="n"/>
-      <c r="U9" s="446" t="n"/>
-      <c r="V9" s="446" t="n"/>
-      <c r="W9" s="446" t="n"/>
-      <c r="X9" s="446" t="n"/>
-      <c r="Y9" s="446" t="n"/>
-      <c r="Z9" s="446" t="n"/>
-      <c r="AA9" s="446" t="n"/>
-      <c r="AB9" s="446" t="n"/>
-      <c r="AC9" s="446" t="n"/>
-      <c r="AD9" s="446" t="n"/>
-      <c r="AE9" s="446" t="n"/>
-      <c r="AF9" s="446" t="n"/>
-      <c r="AG9" s="446" t="n"/>
-      <c r="AH9" s="446" t="n"/>
-      <c r="AI9" s="446" t="n"/>
-      <c r="AJ9" s="446" t="n"/>
-      <c r="AK9" s="446" t="n"/>
-      <c r="AL9" s="446" t="n"/>
-      <c r="AM9" s="446" t="n"/>
-      <c r="AN9" s="562" t="n"/>
+      <c r="A9" s="610" t="inlineStr">
+        <is>
+          <t>Ref Type</t>
+        </is>
+      </c>
+      <c r="B9" s="611" t="inlineStr">
+        <is>
+          <t>Document / Record</t>
+        </is>
+      </c>
+      <c r="C9" s="611" t="inlineStr">
+        <is>
+          <t>System of Record</t>
+        </is>
+      </c>
+      <c r="D9" s="611" t="inlineStr">
+        <is>
+          <t>Unique Ref</t>
+        </is>
+      </c>
+      <c r="E9" s="611" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F9" s="611" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G9" s="611" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="H9" s="726" t="n"/>
+      <c r="I9" s="726" t="n"/>
+      <c r="J9" s="726" t="n"/>
+      <c r="K9" s="726" t="n"/>
+      <c r="L9" s="726" t="n"/>
+      <c r="M9" s="726" t="n"/>
+      <c r="N9" s="726" t="n"/>
+      <c r="O9" s="726" t="n"/>
+      <c r="P9" s="726" t="n"/>
+      <c r="Q9" s="726" t="n"/>
+      <c r="R9" s="726" t="n"/>
+      <c r="S9" s="726" t="n"/>
+      <c r="T9" s="726" t="n"/>
+      <c r="U9" s="726" t="n"/>
+      <c r="V9" s="726" t="n"/>
+      <c r="W9" s="726" t="n"/>
+      <c r="X9" s="726" t="n"/>
+      <c r="Y9" s="726" t="n"/>
+      <c r="Z9" s="726" t="n"/>
+      <c r="AA9" s="726" t="n"/>
+      <c r="AB9" s="726" t="n"/>
+      <c r="AC9" s="726" t="n"/>
+      <c r="AD9" s="726" t="n"/>
+      <c r="AE9" s="726" t="n"/>
+      <c r="AF9" s="726" t="n"/>
+      <c r="AG9" s="726" t="n"/>
+      <c r="AH9" s="726" t="n"/>
+      <c r="AI9" s="726" t="n"/>
+      <c r="AJ9" s="726" t="n"/>
+      <c r="AK9" s="726" t="n"/>
+      <c r="AL9" s="726" t="n"/>
+      <c r="AM9" s="726" t="n"/>
+      <c r="AN9" s="726" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="619" t="n"/>
-      <c r="B10" s="620" t="n"/>
-      <c r="C10" s="620" t="n"/>
-      <c r="D10" s="620" t="n"/>
-      <c r="E10" s="620" t="n"/>
-      <c r="F10" s="620" t="n"/>
-      <c r="G10" s="620" t="n"/>
-      <c r="H10" s="446" t="n"/>
-      <c r="I10" s="446" t="n"/>
-      <c r="J10" s="446" t="n"/>
-      <c r="K10" s="446" t="n"/>
-      <c r="L10" s="446" t="n"/>
-      <c r="M10" s="446" t="n"/>
-      <c r="N10" s="446" t="n"/>
-      <c r="O10" s="446" t="n"/>
-      <c r="P10" s="446" t="n"/>
-      <c r="Q10" s="446" t="n"/>
-      <c r="R10" s="446" t="n"/>
-      <c r="S10" s="446" t="n"/>
-      <c r="T10" s="446" t="n"/>
-      <c r="U10" s="446" t="n"/>
-      <c r="V10" s="446" t="n"/>
-      <c r="W10" s="446" t="n"/>
-      <c r="X10" s="446" t="n"/>
-      <c r="Y10" s="446" t="n"/>
-      <c r="Z10" s="446" t="n"/>
-      <c r="AA10" s="446" t="n"/>
-      <c r="AB10" s="446" t="n"/>
-      <c r="AC10" s="446" t="n"/>
-      <c r="AD10" s="446" t="n"/>
-      <c r="AE10" s="446" t="n"/>
-      <c r="AF10" s="446" t="n"/>
-      <c r="AG10" s="446" t="n"/>
-      <c r="AH10" s="446" t="n"/>
-      <c r="AI10" s="446" t="n"/>
-      <c r="AJ10" s="446" t="n"/>
-      <c r="AK10" s="446" t="n"/>
-      <c r="AL10" s="446" t="n"/>
-      <c r="AM10" s="446" t="n"/>
-      <c r="AN10" s="562" t="n"/>
+      <c r="A10" s="726" t="n"/>
+      <c r="B10" s="726" t="n"/>
+      <c r="C10" s="726" t="n"/>
+      <c r="D10" s="726" t="n"/>
+      <c r="E10" s="726" t="n"/>
+      <c r="F10" s="726" t="n"/>
+      <c r="G10" s="726" t="n"/>
+      <c r="H10" s="726" t="n"/>
+      <c r="I10" s="726" t="n"/>
+      <c r="J10" s="726" t="n"/>
+      <c r="K10" s="726" t="n"/>
+      <c r="L10" s="726" t="n"/>
+      <c r="M10" s="726" t="n"/>
+      <c r="N10" s="726" t="n"/>
+      <c r="O10" s="726" t="n"/>
+      <c r="P10" s="726" t="n"/>
+      <c r="Q10" s="726" t="n"/>
+      <c r="R10" s="726" t="n"/>
+      <c r="S10" s="726" t="n"/>
+      <c r="T10" s="726" t="n"/>
+      <c r="U10" s="726" t="n"/>
+      <c r="V10" s="726" t="n"/>
+      <c r="W10" s="726" t="n"/>
+      <c r="X10" s="726" t="n"/>
+      <c r="Y10" s="726" t="n"/>
+      <c r="Z10" s="726" t="n"/>
+      <c r="AA10" s="726" t="n"/>
+      <c r="AB10" s="726" t="n"/>
+      <c r="AC10" s="726" t="n"/>
+      <c r="AD10" s="726" t="n"/>
+      <c r="AE10" s="726" t="n"/>
+      <c r="AF10" s="726" t="n"/>
+      <c r="AG10" s="726" t="n"/>
+      <c r="AH10" s="726" t="n"/>
+      <c r="AI10" s="726" t="n"/>
+      <c r="AJ10" s="726" t="n"/>
+      <c r="AK10" s="726" t="n"/>
+      <c r="AL10" s="726" t="n"/>
+      <c r="AM10" s="726" t="n"/>
+      <c r="AN10" s="726" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="621" t="n"/>
-      <c r="B11" s="622" t="n"/>
-      <c r="C11" s="622" t="n"/>
-      <c r="D11" s="622" t="n"/>
-      <c r="E11" s="622" t="n"/>
-      <c r="F11" s="622" t="n"/>
-      <c r="G11" s="622" t="n"/>
-      <c r="H11" s="572" t="n"/>
-      <c r="I11" s="572" t="n"/>
-      <c r="J11" s="572" t="n"/>
-      <c r="K11" s="572" t="n"/>
-      <c r="L11" s="572" t="n"/>
-      <c r="M11" s="572" t="n"/>
-      <c r="N11" s="572" t="n"/>
-      <c r="O11" s="572" t="n"/>
-      <c r="P11" s="572" t="n"/>
-      <c r="Q11" s="572" t="n"/>
-      <c r="R11" s="572" t="n"/>
-      <c r="S11" s="572" t="n"/>
-      <c r="T11" s="572" t="n"/>
-      <c r="U11" s="572" t="n"/>
-      <c r="V11" s="572" t="n"/>
-      <c r="W11" s="572" t="n"/>
-      <c r="X11" s="572" t="n"/>
-      <c r="Y11" s="572" t="n"/>
-      <c r="Z11" s="572" t="n"/>
-      <c r="AA11" s="572" t="n"/>
-      <c r="AB11" s="572" t="n"/>
-      <c r="AC11" s="572" t="n"/>
-      <c r="AD11" s="572" t="n"/>
-      <c r="AE11" s="572" t="n"/>
-      <c r="AF11" s="572" t="n"/>
-      <c r="AG11" s="572" t="n"/>
-      <c r="AH11" s="572" t="n"/>
-      <c r="AI11" s="572" t="n"/>
-      <c r="AJ11" s="572" t="n"/>
-      <c r="AK11" s="572" t="n"/>
-      <c r="AL11" s="572" t="n"/>
-      <c r="AM11" s="572" t="n"/>
-      <c r="AN11" s="573" t="n"/>
+      <c r="A11" s="726" t="n"/>
+      <c r="B11" s="726" t="n"/>
+      <c r="C11" s="726" t="n"/>
+      <c r="D11" s="726" t="n"/>
+      <c r="E11" s="726" t="n"/>
+      <c r="F11" s="726" t="n"/>
+      <c r="G11" s="726" t="n"/>
+      <c r="H11" s="726" t="n"/>
+      <c r="I11" s="726" t="n"/>
+      <c r="J11" s="726" t="n"/>
+      <c r="K11" s="726" t="n"/>
+      <c r="L11" s="726" t="n"/>
+      <c r="M11" s="726" t="n"/>
+      <c r="N11" s="726" t="n"/>
+      <c r="O11" s="726" t="n"/>
+      <c r="P11" s="726" t="n"/>
+      <c r="Q11" s="726" t="n"/>
+      <c r="R11" s="726" t="n"/>
+      <c r="S11" s="726" t="n"/>
+      <c r="T11" s="726" t="n"/>
+      <c r="U11" s="726" t="n"/>
+      <c r="V11" s="726" t="n"/>
+      <c r="W11" s="726" t="n"/>
+      <c r="X11" s="726" t="n"/>
+      <c r="Y11" s="726" t="n"/>
+      <c r="Z11" s="726" t="n"/>
+      <c r="AA11" s="726" t="n"/>
+      <c r="AB11" s="726" t="n"/>
+      <c r="AC11" s="726" t="n"/>
+      <c r="AD11" s="726" t="n"/>
+      <c r="AE11" s="726" t="n"/>
+      <c r="AF11" s="726" t="n"/>
+      <c r="AG11" s="726" t="n"/>
+      <c r="AH11" s="726" t="n"/>
+      <c r="AI11" s="726" t="n"/>
+      <c r="AJ11" s="726" t="n"/>
+      <c r="AK11" s="726" t="n"/>
+      <c r="AL11" s="726" t="n"/>
+      <c r="AM11" s="726" t="n"/>
+      <c r="AN11" s="726" t="n"/>
     </row>
-    <row r="12" hidden="1"/>
-    <row r="13" hidden="1"/>
-    <row r="14" hidden="1"/>
-    <row r="15" hidden="1"/>
-    <row r="16" hidden="1"/>
-    <row r="17" hidden="1"/>
-    <row r="18" hidden="1"/>
-    <row r="19" hidden="1"/>
-    <row r="20" hidden="1"/>
+    <row r="12" hidden="1">
+      <c r="A12" s="726" t="n"/>
+      <c r="B12" s="726" t="n"/>
+      <c r="C12" s="726" t="n"/>
+      <c r="D12" s="726" t="n"/>
+      <c r="E12" s="726" t="n"/>
+      <c r="F12" s="726" t="n"/>
+      <c r="G12" s="726" t="n"/>
+      <c r="H12" s="726" t="n"/>
+      <c r="I12" s="726" t="n"/>
+      <c r="J12" s="726" t="n"/>
+      <c r="K12" s="726" t="n"/>
+      <c r="L12" s="726" t="n"/>
+      <c r="M12" s="726" t="n"/>
+      <c r="N12" s="726" t="n"/>
+      <c r="O12" s="726" t="n"/>
+      <c r="P12" s="726" t="n"/>
+      <c r="Q12" s="726" t="n"/>
+      <c r="R12" s="726" t="n"/>
+      <c r="S12" s="726" t="n"/>
+      <c r="T12" s="726" t="n"/>
+      <c r="U12" s="726" t="n"/>
+      <c r="V12" s="726" t="n"/>
+      <c r="W12" s="726" t="n"/>
+      <c r="X12" s="726" t="n"/>
+      <c r="Y12" s="726" t="n"/>
+      <c r="Z12" s="726" t="n"/>
+      <c r="AA12" s="726" t="n"/>
+      <c r="AB12" s="726" t="n"/>
+      <c r="AC12" s="726" t="n"/>
+      <c r="AD12" s="726" t="n"/>
+      <c r="AE12" s="726" t="n"/>
+      <c r="AF12" s="726" t="n"/>
+      <c r="AG12" s="726" t="n"/>
+      <c r="AH12" s="726" t="n"/>
+      <c r="AI12" s="726" t="n"/>
+      <c r="AJ12" s="726" t="n"/>
+      <c r="AK12" s="726" t="n"/>
+      <c r="AL12" s="726" t="n"/>
+      <c r="AM12" s="726" t="n"/>
+      <c r="AN12" s="726" t="n"/>
+    </row>
+    <row r="13" hidden="1">
+      <c r="A13" s="726" t="n"/>
+      <c r="B13" s="726" t="n"/>
+      <c r="C13" s="726" t="n"/>
+      <c r="D13" s="726" t="n"/>
+      <c r="E13" s="726" t="n"/>
+      <c r="F13" s="726" t="n"/>
+      <c r="G13" s="726" t="n"/>
+      <c r="H13" s="726" t="n"/>
+      <c r="I13" s="726" t="n"/>
+      <c r="J13" s="726" t="n"/>
+      <c r="K13" s="726" t="n"/>
+      <c r="L13" s="726" t="n"/>
+      <c r="M13" s="726" t="n"/>
+      <c r="N13" s="726" t="n"/>
+      <c r="O13" s="726" t="n"/>
+      <c r="P13" s="726" t="n"/>
+      <c r="Q13" s="726" t="n"/>
+      <c r="R13" s="726" t="n"/>
+      <c r="S13" s="726" t="n"/>
+      <c r="T13" s="726" t="n"/>
+      <c r="U13" s="726" t="n"/>
+      <c r="V13" s="726" t="n"/>
+      <c r="W13" s="726" t="n"/>
+      <c r="X13" s="726" t="n"/>
+      <c r="Y13" s="726" t="n"/>
+      <c r="Z13" s="726" t="n"/>
+      <c r="AA13" s="726" t="n"/>
+      <c r="AB13" s="726" t="n"/>
+      <c r="AC13" s="726" t="n"/>
+      <c r="AD13" s="726" t="n"/>
+      <c r="AE13" s="726" t="n"/>
+      <c r="AF13" s="726" t="n"/>
+      <c r="AG13" s="726" t="n"/>
+      <c r="AH13" s="726" t="n"/>
+      <c r="AI13" s="726" t="n"/>
+      <c r="AJ13" s="726" t="n"/>
+      <c r="AK13" s="726" t="n"/>
+      <c r="AL13" s="726" t="n"/>
+      <c r="AM13" s="726" t="n"/>
+      <c r="AN13" s="726" t="n"/>
+    </row>
+    <row r="14" hidden="1">
+      <c r="A14" s="726" t="n"/>
+      <c r="B14" s="726" t="n"/>
+      <c r="C14" s="726" t="n"/>
+      <c r="D14" s="726" t="n"/>
+      <c r="E14" s="726" t="n"/>
+      <c r="F14" s="726" t="n"/>
+      <c r="G14" s="726" t="n"/>
+      <c r="H14" s="726" t="n"/>
+      <c r="I14" s="726" t="n"/>
+      <c r="J14" s="726" t="n"/>
+      <c r="K14" s="726" t="n"/>
+      <c r="L14" s="726" t="n"/>
+      <c r="M14" s="726" t="n"/>
+      <c r="N14" s="726" t="n"/>
+      <c r="O14" s="726" t="n"/>
+      <c r="P14" s="726" t="n"/>
+      <c r="Q14" s="726" t="n"/>
+      <c r="R14" s="726" t="n"/>
+      <c r="S14" s="726" t="n"/>
+      <c r="T14" s="726" t="n"/>
+      <c r="U14" s="726" t="n"/>
+      <c r="V14" s="726" t="n"/>
+      <c r="W14" s="726" t="n"/>
+      <c r="X14" s="726" t="n"/>
+      <c r="Y14" s="726" t="n"/>
+      <c r="Z14" s="726" t="n"/>
+      <c r="AA14" s="726" t="n"/>
+      <c r="AB14" s="726" t="n"/>
+      <c r="AC14" s="726" t="n"/>
+      <c r="AD14" s="726" t="n"/>
+      <c r="AE14" s="726" t="n"/>
+      <c r="AF14" s="726" t="n"/>
+      <c r="AG14" s="726" t="n"/>
+      <c r="AH14" s="726" t="n"/>
+      <c r="AI14" s="726" t="n"/>
+      <c r="AJ14" s="726" t="n"/>
+      <c r="AK14" s="726" t="n"/>
+      <c r="AL14" s="726" t="n"/>
+      <c r="AM14" s="726" t="n"/>
+      <c r="AN14" s="726" t="n"/>
+    </row>
+    <row r="15" hidden="1">
+      <c r="A15" s="726" t="n"/>
+      <c r="B15" s="726" t="n"/>
+      <c r="C15" s="726" t="n"/>
+      <c r="D15" s="726" t="n"/>
+      <c r="E15" s="726" t="n"/>
+      <c r="F15" s="726" t="n"/>
+      <c r="G15" s="726" t="n"/>
+      <c r="H15" s="726" t="n"/>
+      <c r="I15" s="726" t="n"/>
+      <c r="J15" s="726" t="n"/>
+      <c r="K15" s="726" t="n"/>
+      <c r="L15" s="726" t="n"/>
+      <c r="M15" s="726" t="n"/>
+      <c r="N15" s="726" t="n"/>
+      <c r="O15" s="726" t="n"/>
+      <c r="P15" s="726" t="n"/>
+      <c r="Q15" s="726" t="n"/>
+      <c r="R15" s="726" t="n"/>
+      <c r="S15" s="726" t="n"/>
+      <c r="T15" s="726" t="n"/>
+      <c r="U15" s="726" t="n"/>
+      <c r="V15" s="726" t="n"/>
+      <c r="W15" s="726" t="n"/>
+      <c r="X15" s="726" t="n"/>
+      <c r="Y15" s="726" t="n"/>
+      <c r="Z15" s="726" t="n"/>
+      <c r="AA15" s="726" t="n"/>
+      <c r="AB15" s="726" t="n"/>
+      <c r="AC15" s="726" t="n"/>
+      <c r="AD15" s="726" t="n"/>
+      <c r="AE15" s="726" t="n"/>
+      <c r="AF15" s="726" t="n"/>
+      <c r="AG15" s="726" t="n"/>
+      <c r="AH15" s="726" t="n"/>
+      <c r="AI15" s="726" t="n"/>
+      <c r="AJ15" s="726" t="n"/>
+      <c r="AK15" s="726" t="n"/>
+      <c r="AL15" s="726" t="n"/>
+      <c r="AM15" s="726" t="n"/>
+      <c r="AN15" s="726" t="n"/>
+    </row>
+    <row r="16" hidden="1">
+      <c r="A16" s="726" t="n"/>
+      <c r="B16" s="726" t="n"/>
+      <c r="C16" s="726" t="n"/>
+      <c r="D16" s="726" t="n"/>
+      <c r="E16" s="726" t="n"/>
+      <c r="F16" s="726" t="n"/>
+      <c r="G16" s="726" t="n"/>
+      <c r="H16" s="726" t="n"/>
+      <c r="I16" s="726" t="n"/>
+      <c r="J16" s="726" t="n"/>
+      <c r="K16" s="726" t="n"/>
+      <c r="L16" s="726" t="n"/>
+      <c r="M16" s="726" t="n"/>
+      <c r="N16" s="726" t="n"/>
+      <c r="O16" s="726" t="n"/>
+      <c r="P16" s="726" t="n"/>
+      <c r="Q16" s="726" t="n"/>
+      <c r="R16" s="726" t="n"/>
+      <c r="S16" s="726" t="n"/>
+      <c r="T16" s="726" t="n"/>
+      <c r="U16" s="726" t="n"/>
+      <c r="V16" s="726" t="n"/>
+      <c r="W16" s="726" t="n"/>
+      <c r="X16" s="726" t="n"/>
+      <c r="Y16" s="726" t="n"/>
+      <c r="Z16" s="726" t="n"/>
+      <c r="AA16" s="726" t="n"/>
+      <c r="AB16" s="726" t="n"/>
+      <c r="AC16" s="726" t="n"/>
+      <c r="AD16" s="726" t="n"/>
+      <c r="AE16" s="726" t="n"/>
+      <c r="AF16" s="726" t="n"/>
+      <c r="AG16" s="726" t="n"/>
+      <c r="AH16" s="726" t="n"/>
+      <c r="AI16" s="726" t="n"/>
+      <c r="AJ16" s="726" t="n"/>
+      <c r="AK16" s="726" t="n"/>
+      <c r="AL16" s="726" t="n"/>
+      <c r="AM16" s="726" t="n"/>
+      <c r="AN16" s="726" t="n"/>
+    </row>
+    <row r="17" hidden="1">
+      <c r="A17" s="726" t="n"/>
+      <c r="B17" s="726" t="n"/>
+      <c r="C17" s="726" t="n"/>
+      <c r="D17" s="726" t="n"/>
+      <c r="E17" s="726" t="n"/>
+      <c r="F17" s="726" t="n"/>
+      <c r="G17" s="726" t="n"/>
+      <c r="H17" s="726" t="n"/>
+      <c r="I17" s="726" t="n"/>
+      <c r="J17" s="726" t="n"/>
+      <c r="K17" s="726" t="n"/>
+      <c r="L17" s="726" t="n"/>
+      <c r="M17" s="726" t="n"/>
+      <c r="N17" s="726" t="n"/>
+      <c r="O17" s="726" t="n"/>
+      <c r="P17" s="726" t="n"/>
+      <c r="Q17" s="726" t="n"/>
+      <c r="R17" s="726" t="n"/>
+      <c r="S17" s="726" t="n"/>
+      <c r="T17" s="726" t="n"/>
+      <c r="U17" s="726" t="n"/>
+      <c r="V17" s="726" t="n"/>
+      <c r="W17" s="726" t="n"/>
+      <c r="X17" s="726" t="n"/>
+      <c r="Y17" s="726" t="n"/>
+      <c r="Z17" s="726" t="n"/>
+      <c r="AA17" s="726" t="n"/>
+      <c r="AB17" s="726" t="n"/>
+      <c r="AC17" s="726" t="n"/>
+      <c r="AD17" s="726" t="n"/>
+      <c r="AE17" s="726" t="n"/>
+      <c r="AF17" s="726" t="n"/>
+      <c r="AG17" s="726" t="n"/>
+      <c r="AH17" s="726" t="n"/>
+      <c r="AI17" s="726" t="n"/>
+      <c r="AJ17" s="726" t="n"/>
+      <c r="AK17" s="726" t="n"/>
+      <c r="AL17" s="726" t="n"/>
+      <c r="AM17" s="726" t="n"/>
+      <c r="AN17" s="726" t="n"/>
+    </row>
+    <row r="18" hidden="1">
+      <c r="A18" s="726" t="n"/>
+      <c r="B18" s="726" t="n"/>
+      <c r="C18" s="726" t="n"/>
+      <c r="D18" s="726" t="n"/>
+      <c r="E18" s="726" t="n"/>
+      <c r="F18" s="726" t="n"/>
+      <c r="G18" s="726" t="n"/>
+      <c r="H18" s="726" t="n"/>
+      <c r="I18" s="726" t="n"/>
+      <c r="J18" s="726" t="n"/>
+      <c r="K18" s="726" t="n"/>
+      <c r="L18" s="726" t="n"/>
+      <c r="M18" s="726" t="n"/>
+      <c r="N18" s="726" t="n"/>
+      <c r="O18" s="726" t="n"/>
+      <c r="P18" s="726" t="n"/>
+      <c r="Q18" s="726" t="n"/>
+      <c r="R18" s="726" t="n"/>
+      <c r="S18" s="726" t="n"/>
+      <c r="T18" s="726" t="n"/>
+      <c r="U18" s="726" t="n"/>
+      <c r="V18" s="726" t="n"/>
+      <c r="W18" s="726" t="n"/>
+      <c r="X18" s="726" t="n"/>
+      <c r="Y18" s="726" t="n"/>
+      <c r="Z18" s="726" t="n"/>
+      <c r="AA18" s="726" t="n"/>
+      <c r="AB18" s="726" t="n"/>
+      <c r="AC18" s="726" t="n"/>
+      <c r="AD18" s="726" t="n"/>
+      <c r="AE18" s="726" t="n"/>
+      <c r="AF18" s="726" t="n"/>
+      <c r="AG18" s="726" t="n"/>
+      <c r="AH18" s="726" t="n"/>
+      <c r="AI18" s="726" t="n"/>
+      <c r="AJ18" s="726" t="n"/>
+      <c r="AK18" s="726" t="n"/>
+      <c r="AL18" s="726" t="n"/>
+      <c r="AM18" s="726" t="n"/>
+      <c r="AN18" s="726" t="n"/>
+    </row>
+    <row r="19" hidden="1">
+      <c r="A19" s="726" t="n"/>
+      <c r="B19" s="726" t="n"/>
+      <c r="C19" s="726" t="n"/>
+      <c r="D19" s="726" t="n"/>
+      <c r="E19" s="726" t="n"/>
+      <c r="F19" s="726" t="n"/>
+      <c r="G19" s="726" t="n"/>
+      <c r="H19" s="726" t="n"/>
+      <c r="I19" s="726" t="n"/>
+      <c r="J19" s="726" t="n"/>
+      <c r="K19" s="726" t="n"/>
+      <c r="L19" s="726" t="n"/>
+      <c r="M19" s="726" t="n"/>
+      <c r="N19" s="726" t="n"/>
+      <c r="O19" s="726" t="n"/>
+      <c r="P19" s="726" t="n"/>
+      <c r="Q19" s="726" t="n"/>
+      <c r="R19" s="726" t="n"/>
+      <c r="S19" s="726" t="n"/>
+      <c r="T19" s="726" t="n"/>
+      <c r="U19" s="726" t="n"/>
+      <c r="V19" s="726" t="n"/>
+      <c r="W19" s="726" t="n"/>
+      <c r="X19" s="726" t="n"/>
+      <c r="Y19" s="726" t="n"/>
+      <c r="Z19" s="726" t="n"/>
+      <c r="AA19" s="726" t="n"/>
+      <c r="AB19" s="726" t="n"/>
+      <c r="AC19" s="726" t="n"/>
+      <c r="AD19" s="726" t="n"/>
+      <c r="AE19" s="726" t="n"/>
+      <c r="AF19" s="726" t="n"/>
+      <c r="AG19" s="726" t="n"/>
+      <c r="AH19" s="726" t="n"/>
+      <c r="AI19" s="726" t="n"/>
+      <c r="AJ19" s="726" t="n"/>
+      <c r="AK19" s="726" t="n"/>
+      <c r="AL19" s="726" t="n"/>
+      <c r="AM19" s="726" t="n"/>
+      <c r="AN19" s="726" t="n"/>
+    </row>
+    <row r="20" hidden="1">
+      <c r="A20" s="726" t="n"/>
+      <c r="B20" s="726" t="n"/>
+      <c r="C20" s="726" t="n"/>
+      <c r="D20" s="726" t="n"/>
+      <c r="E20" s="726" t="n"/>
+      <c r="F20" s="726" t="n"/>
+      <c r="G20" s="726" t="n"/>
+      <c r="H20" s="726" t="n"/>
+      <c r="I20" s="726" t="n"/>
+      <c r="J20" s="726" t="n"/>
+      <c r="K20" s="726" t="n"/>
+      <c r="L20" s="726" t="n"/>
+      <c r="M20" s="726" t="n"/>
+      <c r="N20" s="726" t="n"/>
+      <c r="O20" s="726" t="n"/>
+      <c r="P20" s="726" t="n"/>
+      <c r="Q20" s="726" t="n"/>
+      <c r="R20" s="726" t="n"/>
+      <c r="S20" s="726" t="n"/>
+      <c r="T20" s="726" t="n"/>
+      <c r="U20" s="726" t="n"/>
+      <c r="V20" s="726" t="n"/>
+      <c r="W20" s="726" t="n"/>
+      <c r="X20" s="726" t="n"/>
+      <c r="Y20" s="726" t="n"/>
+      <c r="Z20" s="726" t="n"/>
+      <c r="AA20" s="726" t="n"/>
+      <c r="AB20" s="726" t="n"/>
+      <c r="AC20" s="726" t="n"/>
+      <c r="AD20" s="726" t="n"/>
+      <c r="AE20" s="726" t="n"/>
+      <c r="AF20" s="726" t="n"/>
+      <c r="AG20" s="726" t="n"/>
+      <c r="AH20" s="726" t="n"/>
+      <c r="AI20" s="726" t="n"/>
+      <c r="AJ20" s="726" t="n"/>
+      <c r="AK20" s="726" t="n"/>
+      <c r="AL20" s="726" t="n"/>
+      <c r="AM20" s="726" t="n"/>
+      <c r="AN20" s="726" t="n"/>
+    </row>
     <row r="21" hidden="1"/>
     <row r="22" hidden="1"/>
     <row r="23" hidden="1"/>
@@ -13281,9 +14145,23 @@
     <row r="199" hidden="1"/>
     <row r="200" hidden="1"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="16">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation sqref="A4:A11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use controlled drop-down values only." prompt="Select REF_EVIDENCE_LINK" type="list">

--- a/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
@@ -818,7 +818,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="356">
+  <borders count="362">
     <border>
       <left/>
       <right/>
@@ -4630,12 +4630,82 @@
       <bottom style="medium">
         <color rgb="002C9CD7"/>
       </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="727">
+  <cellXfs count="789">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6423,6 +6493,158 @@
     </xf>
     <xf numFmtId="0" fontId="88" fillId="51" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="356" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="338" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="357" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="359" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="360" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="361" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -6503,11 +6725,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>63378</colOff>
-      <row>0</row>
-      <rowOff>442597</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="235404" cy="67905"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -6521,9 +6743,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6536,11 +6755,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>63378</colOff>
-      <row>0</row>
-      <rowOff>442597</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="235404" cy="67905"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -6554,9 +6773,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6573,7 +6789,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -6587,9 +6803,66 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1123950" cy="323850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1123950" cy="323850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -6872,10 +7145,10 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="413" t="n"/>
       <c r="B1" s="310" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="788" t="inlineStr">
         <is>
           <t>RMA TRACKING LOG</t>
         </is>
@@ -6884,7 +7157,7 @@
       <c r="E1" s="268" t="n"/>
       <c r="F1" s="268" t="n"/>
       <c r="G1" s="268" t="n"/>
-      <c r="H1" s="268" t="n"/>
+      <c r="H1" s="310" t="n"/>
       <c r="I1" s="623" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -6927,285 +7200,296 @@
       <c r="AN1" s="627" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="B2" s="312" t="n"/>
-      <c r="C2" s="275" t="n"/>
-      <c r="I2" s="628" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="727" t="n"/>
+      <c r="C2" s="727" t="n"/>
+      <c r="D2" s="727" t="n"/>
+      <c r="E2" s="727" t="n"/>
+      <c r="F2" s="727" t="n"/>
+      <c r="G2" s="727" t="n"/>
+      <c r="H2" s="728" t="n"/>
+      <c r="I2" s="341" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="J2" s="629" t="inlineStr">
+      <c r="J2" s="341" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="K2" s="629" t="n"/>
-      <c r="L2" s="629" t="n"/>
-      <c r="M2" s="629" t="n"/>
-      <c r="N2" s="629" t="n"/>
-      <c r="O2" s="629" t="n"/>
-      <c r="P2" s="629" t="n"/>
-      <c r="Q2" s="629" t="n"/>
-      <c r="R2" s="629" t="n"/>
-      <c r="S2" s="629" t="n"/>
-      <c r="T2" s="629" t="n"/>
-      <c r="U2" s="629" t="n"/>
-      <c r="V2" s="629" t="n"/>
-      <c r="W2" s="629" t="n"/>
-      <c r="X2" s="629" t="n"/>
-      <c r="Y2" s="629" t="n"/>
-      <c r="Z2" s="629" t="n"/>
-      <c r="AA2" s="629" t="n"/>
-      <c r="AB2" s="629" t="n"/>
-      <c r="AC2" s="629" t="n"/>
-      <c r="AD2" s="629" t="n"/>
-      <c r="AE2" s="630" t="n"/>
-      <c r="AF2" s="630" t="n"/>
-      <c r="AG2" s="630" t="n"/>
-      <c r="AH2" s="630" t="n"/>
-      <c r="AI2" s="631" t="n"/>
-      <c r="AJ2" s="631" t="n"/>
-      <c r="AK2" s="631" t="n"/>
-      <c r="AL2" s="631" t="n"/>
-      <c r="AM2" s="631" t="n"/>
-      <c r="AN2" s="632" t="n"/>
+      <c r="K2" s="624" t="n"/>
+      <c r="L2" s="624" t="n"/>
+      <c r="M2" s="624" t="n"/>
+      <c r="N2" s="624" t="n"/>
+      <c r="O2" s="624" t="n"/>
+      <c r="P2" s="624" t="n"/>
+      <c r="Q2" s="624" t="n"/>
+      <c r="R2" s="624" t="n"/>
+      <c r="S2" s="624" t="n"/>
+      <c r="T2" s="624" t="n"/>
+      <c r="U2" s="624" t="n"/>
+      <c r="V2" s="624" t="n"/>
+      <c r="W2" s="624" t="n"/>
+      <c r="X2" s="624" t="n"/>
+      <c r="Y2" s="624" t="n"/>
+      <c r="Z2" s="624" t="n"/>
+      <c r="AA2" s="624" t="n"/>
+      <c r="AB2" s="624" t="n"/>
+      <c r="AC2" s="624" t="n"/>
+      <c r="AD2" s="729" t="n"/>
+      <c r="AE2" s="730" t="n"/>
+      <c r="AF2" s="730" t="n"/>
+      <c r="AG2" s="730" t="n"/>
+      <c r="AH2" s="731" t="n"/>
+      <c r="AI2" s="732" t="n"/>
+      <c r="AJ2" s="732" t="n"/>
+      <c r="AK2" s="732" t="n"/>
+      <c r="AL2" s="732" t="n"/>
+      <c r="AM2" s="732" t="n"/>
+      <c r="AN2" s="733" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="B3" s="312" t="n"/>
-      <c r="C3" s="275" t="n"/>
-      <c r="I3" s="628" t="inlineStr">
+      <c r="A3" s="734" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="735" t="n"/>
+      <c r="I3" s="348" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="J3" s="629" t="inlineStr">
+      <c r="J3" s="348" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="K3" s="629" t="n"/>
-      <c r="L3" s="629" t="n"/>
-      <c r="M3" s="629" t="n"/>
-      <c r="N3" s="629" t="n"/>
-      <c r="O3" s="629" t="n"/>
-      <c r="P3" s="629" t="n"/>
-      <c r="Q3" s="629" t="n"/>
-      <c r="R3" s="629" t="n"/>
-      <c r="S3" s="629" t="n"/>
-      <c r="T3" s="629" t="n"/>
-      <c r="U3" s="629" t="n"/>
-      <c r="V3" s="629" t="n"/>
-      <c r="W3" s="629" t="n"/>
-      <c r="X3" s="629" t="n"/>
-      <c r="Y3" s="629" t="n"/>
-      <c r="Z3" s="629" t="n"/>
-      <c r="AA3" s="629" t="n"/>
-      <c r="AB3" s="629" t="n"/>
-      <c r="AC3" s="629" t="n"/>
-      <c r="AD3" s="629" t="n"/>
-      <c r="AE3" s="630" t="n"/>
-      <c r="AF3" s="630" t="n"/>
-      <c r="AG3" s="630" t="n"/>
-      <c r="AH3" s="630" t="n"/>
-      <c r="AI3" s="631" t="n"/>
-      <c r="AJ3" s="631" t="n"/>
-      <c r="AK3" s="631" t="n"/>
-      <c r="AL3" s="631" t="n"/>
-      <c r="AM3" s="631" t="n"/>
-      <c r="AN3" s="632" t="n"/>
+      <c r="K3" s="736" t="n"/>
+      <c r="L3" s="736" t="n"/>
+      <c r="M3" s="736" t="n"/>
+      <c r="N3" s="736" t="n"/>
+      <c r="O3" s="736" t="n"/>
+      <c r="P3" s="736" t="n"/>
+      <c r="Q3" s="736" t="n"/>
+      <c r="R3" s="736" t="n"/>
+      <c r="S3" s="736" t="n"/>
+      <c r="T3" s="736" t="n"/>
+      <c r="U3" s="736" t="n"/>
+      <c r="V3" s="736" t="n"/>
+      <c r="W3" s="736" t="n"/>
+      <c r="X3" s="736" t="n"/>
+      <c r="Y3" s="736" t="n"/>
+      <c r="Z3" s="736" t="n"/>
+      <c r="AA3" s="736" t="n"/>
+      <c r="AB3" s="736" t="n"/>
+      <c r="AC3" s="736" t="n"/>
+      <c r="AD3" s="737" t="n"/>
+      <c r="AE3" s="738" t="n"/>
+      <c r="AF3" s="738" t="n"/>
+      <c r="AG3" s="738" t="n"/>
+      <c r="AH3" s="739" t="n"/>
+      <c r="AI3" s="740" t="n"/>
+      <c r="AJ3" s="740" t="n"/>
+      <c r="AK3" s="740" t="n"/>
+      <c r="AL3" s="740" t="n"/>
+      <c r="AM3" s="740" t="n"/>
+      <c r="AN3" s="741" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="B4" s="312" t="n"/>
-      <c r="C4" s="633" t="inlineStr">
+      <c r="A4" s="734" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="529" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="I4" s="634" t="inlineStr">
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="735" t="n"/>
+      <c r="I4" s="348" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="J4" s="635" t="inlineStr">
+      <c r="J4" s="348" t="inlineStr">
         <is>
           <t>QA / Customer Service</t>
         </is>
       </c>
-      <c r="K4" s="635" t="n"/>
-      <c r="L4" s="635" t="n"/>
-      <c r="M4" s="635" t="n"/>
-      <c r="N4" s="635" t="n"/>
-      <c r="O4" s="635" t="n"/>
-      <c r="P4" s="635" t="n"/>
-      <c r="Q4" s="635" t="n"/>
-      <c r="R4" s="635" t="n"/>
-      <c r="S4" s="635" t="n"/>
-      <c r="T4" s="635" t="n"/>
-      <c r="U4" s="635" t="n"/>
-      <c r="V4" s="635" t="n"/>
-      <c r="W4" s="635" t="n"/>
-      <c r="X4" s="635" t="n"/>
-      <c r="Y4" s="635" t="n"/>
-      <c r="Z4" s="635" t="n"/>
-      <c r="AA4" s="635" t="n"/>
-      <c r="AB4" s="635" t="n"/>
-      <c r="AC4" s="635" t="n"/>
-      <c r="AD4" s="635" t="n"/>
-      <c r="AE4" s="630" t="n"/>
-      <c r="AF4" s="630" t="n"/>
-      <c r="AG4" s="630" t="n"/>
-      <c r="AH4" s="630" t="n"/>
-      <c r="AI4" s="631" t="n"/>
-      <c r="AJ4" s="631" t="n"/>
-      <c r="AK4" s="631" t="n"/>
-      <c r="AL4" s="631" t="n"/>
-      <c r="AM4" s="631" t="n"/>
-      <c r="AN4" s="632" t="n"/>
+      <c r="K4" s="531" t="n"/>
+      <c r="L4" s="531" t="n"/>
+      <c r="M4" s="531" t="n"/>
+      <c r="N4" s="531" t="n"/>
+      <c r="O4" s="531" t="n"/>
+      <c r="P4" s="531" t="n"/>
+      <c r="Q4" s="531" t="n"/>
+      <c r="R4" s="531" t="n"/>
+      <c r="S4" s="531" t="n"/>
+      <c r="T4" s="531" t="n"/>
+      <c r="U4" s="531" t="n"/>
+      <c r="V4" s="531" t="n"/>
+      <c r="W4" s="531" t="n"/>
+      <c r="X4" s="531" t="n"/>
+      <c r="Y4" s="531" t="n"/>
+      <c r="Z4" s="531" t="n"/>
+      <c r="AA4" s="531" t="n"/>
+      <c r="AB4" s="531" t="n"/>
+      <c r="AC4" s="531" t="n"/>
+      <c r="AD4" s="742" t="n"/>
+      <c r="AE4" s="738" t="n"/>
+      <c r="AF4" s="738" t="n"/>
+      <c r="AG4" s="738" t="n"/>
+      <c r="AH4" s="739" t="n"/>
+      <c r="AI4" s="740" t="n"/>
+      <c r="AJ4" s="740" t="n"/>
+      <c r="AK4" s="740" t="n"/>
+      <c r="AL4" s="740" t="n"/>
+      <c r="AM4" s="740" t="n"/>
+      <c r="AN4" s="741" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="282" t="n"/>
-      <c r="B5" s="287" t="n"/>
-      <c r="C5" s="636" t="inlineStr">
+      <c r="A5" s="734" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="743" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="283" t="n"/>
-      <c r="E5" s="283" t="n"/>
-      <c r="F5" s="283" t="n"/>
-      <c r="G5" s="283" t="n"/>
-      <c r="H5" s="283" t="n"/>
-      <c r="I5" s="637" t="inlineStr">
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="735" t="n"/>
+      <c r="I5" s="529" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="J5" s="638" t="inlineStr">
+      <c r="J5" s="529" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
       </c>
-      <c r="K5" s="638" t="n"/>
-      <c r="L5" s="638" t="n"/>
-      <c r="M5" s="638" t="n"/>
-      <c r="N5" s="638" t="n"/>
-      <c r="O5" s="638" t="n"/>
-      <c r="P5" s="638" t="n"/>
-      <c r="Q5" s="638" t="n"/>
-      <c r="R5" s="638" t="n"/>
-      <c r="S5" s="638" t="n"/>
-      <c r="T5" s="638" t="n"/>
-      <c r="U5" s="638" t="n"/>
-      <c r="V5" s="638" t="n"/>
-      <c r="W5" s="638" t="n"/>
-      <c r="X5" s="638" t="n"/>
-      <c r="Y5" s="638" t="n"/>
-      <c r="Z5" s="638" t="n"/>
-      <c r="AA5" s="638" t="n"/>
-      <c r="AB5" s="638" t="n"/>
-      <c r="AC5" s="638" t="n"/>
-      <c r="AD5" s="638" t="n"/>
-      <c r="AE5" s="639" t="n"/>
-      <c r="AF5" s="639" t="n"/>
-      <c r="AG5" s="639" t="n"/>
-      <c r="AH5" s="639" t="n"/>
-      <c r="AI5" s="640" t="n"/>
-      <c r="AJ5" s="640" t="n"/>
-      <c r="AK5" s="640" t="n"/>
-      <c r="AL5" s="640" t="n"/>
-      <c r="AM5" s="640" t="n"/>
-      <c r="AN5" s="641" t="n"/>
+      <c r="K5" s="744" t="n"/>
+      <c r="L5" s="744" t="n"/>
+      <c r="M5" s="744" t="n"/>
+      <c r="N5" s="744" t="n"/>
+      <c r="O5" s="744" t="n"/>
+      <c r="P5" s="744" t="n"/>
+      <c r="Q5" s="744" t="n"/>
+      <c r="R5" s="744" t="n"/>
+      <c r="S5" s="744" t="n"/>
+      <c r="T5" s="744" t="n"/>
+      <c r="U5" s="744" t="n"/>
+      <c r="V5" s="744" t="n"/>
+      <c r="W5" s="744" t="n"/>
+      <c r="X5" s="744" t="n"/>
+      <c r="Y5" s="744" t="n"/>
+      <c r="Z5" s="744" t="n"/>
+      <c r="AA5" s="744" t="n"/>
+      <c r="AB5" s="744" t="n"/>
+      <c r="AC5" s="744" t="n"/>
+      <c r="AD5" s="745" t="n"/>
+      <c r="AE5" s="738" t="n"/>
+      <c r="AF5" s="738" t="n"/>
+      <c r="AG5" s="738" t="n"/>
+      <c r="AH5" s="739" t="n"/>
+      <c r="AI5" s="740" t="n"/>
+      <c r="AJ5" s="740" t="n"/>
+      <c r="AK5" s="740" t="n"/>
+      <c r="AL5" s="740" t="n"/>
+      <c r="AM5" s="740" t="n"/>
+      <c r="AN5" s="741" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="642" t="n"/>
-      <c r="B6" s="643" t="n"/>
-      <c r="C6" s="643" t="n"/>
-      <c r="D6" s="643" t="n"/>
-      <c r="E6" s="643" t="n"/>
-      <c r="F6" s="643" t="n"/>
-      <c r="G6" s="643" t="n"/>
-      <c r="H6" s="643" t="n"/>
-      <c r="I6" s="643" t="n"/>
-      <c r="J6" s="643" t="n"/>
-      <c r="K6" s="643" t="n"/>
-      <c r="L6" s="643" t="n"/>
-      <c r="M6" s="643" t="n"/>
-      <c r="N6" s="643" t="n"/>
-      <c r="O6" s="643" t="n"/>
-      <c r="P6" s="643" t="n"/>
-      <c r="Q6" s="643" t="n"/>
-      <c r="R6" s="643" t="n"/>
-      <c r="S6" s="643" t="n"/>
-      <c r="T6" s="643" t="n"/>
-      <c r="U6" s="643" t="n"/>
-      <c r="V6" s="643" t="n"/>
-      <c r="W6" s="643" t="n"/>
-      <c r="X6" s="643" t="n"/>
-      <c r="Y6" s="643" t="n"/>
-      <c r="Z6" s="643" t="n"/>
-      <c r="AA6" s="643" t="n"/>
-      <c r="AB6" s="643" t="n"/>
-      <c r="AC6" s="643" t="n"/>
-      <c r="AD6" s="643" t="n"/>
-      <c r="AE6" s="643" t="n"/>
-      <c r="AF6" s="643" t="n"/>
-      <c r="AG6" s="643" t="n"/>
-      <c r="AH6" s="643" t="n"/>
-      <c r="AI6" s="643" t="n"/>
-      <c r="AJ6" s="643" t="n"/>
-      <c r="AK6" s="643" t="n"/>
-      <c r="AL6" s="643" t="n"/>
-      <c r="AM6" s="643" t="n"/>
-      <c r="AN6" s="643" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="358" t="n"/>
+      <c r="B6" s="746" t="n"/>
+      <c r="C6" s="746" t="n"/>
+      <c r="D6" s="746" t="n"/>
+      <c r="E6" s="746" t="n"/>
+      <c r="F6" s="746" t="n"/>
+      <c r="G6" s="746" t="n"/>
+      <c r="H6" s="747" t="n"/>
+      <c r="I6" s="746" t="n"/>
+      <c r="J6" s="746" t="n"/>
+      <c r="K6" s="746" t="n"/>
+      <c r="L6" s="746" t="n"/>
+      <c r="M6" s="746" t="n"/>
+      <c r="N6" s="746" t="n"/>
+      <c r="O6" s="746" t="n"/>
+      <c r="P6" s="746" t="n"/>
+      <c r="Q6" s="746" t="n"/>
+      <c r="R6" s="746" t="n"/>
+      <c r="S6" s="746" t="n"/>
+      <c r="T6" s="746" t="n"/>
+      <c r="U6" s="746" t="n"/>
+      <c r="V6" s="746" t="n"/>
+      <c r="W6" s="746" t="n"/>
+      <c r="X6" s="746" t="n"/>
+      <c r="Y6" s="746" t="n"/>
+      <c r="Z6" s="746" t="n"/>
+      <c r="AA6" s="746" t="n"/>
+      <c r="AB6" s="746" t="n"/>
+      <c r="AC6" s="746" t="n"/>
+      <c r="AD6" s="747" t="n"/>
+      <c r="AE6" s="748" t="n"/>
+      <c r="AF6" s="748" t="n"/>
+      <c r="AG6" s="748" t="n"/>
+      <c r="AH6" s="749" t="n"/>
+      <c r="AI6" s="750" t="n"/>
+      <c r="AJ6" s="750" t="n"/>
+      <c r="AK6" s="750" t="n"/>
+      <c r="AL6" s="750" t="n"/>
+      <c r="AM6" s="750" t="n"/>
+      <c r="AN6" s="751" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="644" t="inlineStr">
-        <is>
-          <t>1.  RMA HEADER</t>
-        </is>
-      </c>
-      <c r="B7" s="289" t="n"/>
-      <c r="C7" s="289" t="n"/>
-      <c r="D7" s="289" t="n"/>
-      <c r="E7" s="289" t="n"/>
-      <c r="F7" s="289" t="n"/>
-      <c r="G7" s="289" t="n"/>
-      <c r="H7" s="289" t="n"/>
-      <c r="I7" s="289" t="n"/>
-      <c r="J7" s="289" t="n"/>
-      <c r="K7" s="645" t="n"/>
-      <c r="L7" s="645" t="n"/>
-      <c r="M7" s="645" t="n"/>
-      <c r="N7" s="645" t="n"/>
-      <c r="O7" s="645" t="n"/>
-      <c r="P7" s="645" t="n"/>
-      <c r="Q7" s="645" t="n"/>
-      <c r="R7" s="645" t="n"/>
-      <c r="S7" s="645" t="n"/>
-      <c r="T7" s="645" t="n"/>
-      <c r="U7" s="645" t="n"/>
-      <c r="V7" s="645" t="n"/>
-      <c r="W7" s="645" t="n"/>
-      <c r="X7" s="645" t="n"/>
-      <c r="Y7" s="645" t="n"/>
-      <c r="Z7" s="645" t="n"/>
-      <c r="AA7" s="645" t="n"/>
-      <c r="AB7" s="645" t="n"/>
-      <c r="AC7" s="645" t="n"/>
-      <c r="AD7" s="645" t="n"/>
-      <c r="AE7" s="645" t="n"/>
-      <c r="AF7" s="645" t="n"/>
-      <c r="AG7" s="645" t="n"/>
-      <c r="AH7" s="645" t="n"/>
-      <c r="AI7" s="645" t="n"/>
-      <c r="AJ7" s="645" t="n"/>
-      <c r="AK7" s="645" t="n"/>
-      <c r="AL7" s="645" t="n"/>
-      <c r="AM7" s="645" t="n"/>
-      <c r="AN7" s="646" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="752" t="n"/>
+      <c r="B7" s="753" t="n"/>
+      <c r="C7" s="753" t="n"/>
+      <c r="D7" s="753" t="n"/>
+      <c r="E7" s="753" t="n"/>
+      <c r="F7" s="753" t="n"/>
+      <c r="G7" s="753" t="n"/>
+      <c r="H7" s="753" t="n"/>
+      <c r="I7" s="753" t="n"/>
+      <c r="J7" s="753" t="n"/>
+      <c r="K7" s="752" t="n"/>
+      <c r="L7" s="752" t="n"/>
+      <c r="M7" s="752" t="n"/>
+      <c r="N7" s="752" t="n"/>
+      <c r="O7" s="752" t="n"/>
+      <c r="P7" s="752" t="n"/>
+      <c r="Q7" s="752" t="n"/>
+      <c r="R7" s="752" t="n"/>
+      <c r="S7" s="752" t="n"/>
+      <c r="T7" s="752" t="n"/>
+      <c r="U7" s="752" t="n"/>
+      <c r="V7" s="752" t="n"/>
+      <c r="W7" s="752" t="n"/>
+      <c r="X7" s="752" t="n"/>
+      <c r="Y7" s="752" t="n"/>
+      <c r="Z7" s="752" t="n"/>
+      <c r="AA7" s="752" t="n"/>
+      <c r="AB7" s="752" t="n"/>
+      <c r="AC7" s="752" t="n"/>
+      <c r="AD7" s="752" t="n"/>
+      <c r="AE7" s="752" t="n"/>
+      <c r="AF7" s="752" t="n"/>
+      <c r="AG7" s="752" t="n"/>
+      <c r="AH7" s="752" t="n"/>
+      <c r="AI7" s="752" t="n"/>
+      <c r="AJ7" s="752" t="n"/>
+      <c r="AK7" s="752" t="n"/>
+      <c r="AL7" s="752" t="n"/>
+      <c r="AM7" s="752" t="n"/>
+      <c r="AN7" s="752" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="691" t="inlineStr">
@@ -7459,15 +7743,15 @@
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="664" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
-      <c r="I13" s="10" t="n"/>
-      <c r="J13" s="10" t="n"/>
+      <c r="B13" s="665" t="n"/>
+      <c r="C13" s="665" t="n"/>
+      <c r="D13" s="665" t="n"/>
+      <c r="E13" s="665" t="n"/>
+      <c r="F13" s="665" t="n"/>
+      <c r="G13" s="665" t="n"/>
+      <c r="H13" s="665" t="n"/>
+      <c r="I13" s="665" t="n"/>
+      <c r="J13" s="665" t="n"/>
       <c r="K13" s="665" t="n"/>
       <c r="L13" s="665" t="n"/>
       <c r="M13" s="665" t="n"/>
@@ -7747,15 +8031,15 @@
     </row>
     <row r="19" ht="3" customHeight="1">
       <c r="A19" s="664" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="10" t="n"/>
-      <c r="J19" s="10" t="n"/>
+      <c r="B19" s="665" t="n"/>
+      <c r="C19" s="665" t="n"/>
+      <c r="D19" s="665" t="n"/>
+      <c r="E19" s="665" t="n"/>
+      <c r="F19" s="665" t="n"/>
+      <c r="G19" s="665" t="n"/>
+      <c r="H19" s="665" t="n"/>
+      <c r="I19" s="665" t="n"/>
+      <c r="J19" s="665" t="n"/>
       <c r="K19" s="665" t="n"/>
       <c r="L19" s="665" t="n"/>
       <c r="M19" s="665" t="n"/>
@@ -8727,15 +9011,15 @@
     </row>
     <row r="40" ht="3" customHeight="1">
       <c r="A40" s="664" t="n"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="10" t="n"/>
-      <c r="H40" s="10" t="n"/>
-      <c r="I40" s="10" t="n"/>
-      <c r="J40" s="10" t="n"/>
+      <c r="B40" s="665" t="n"/>
+      <c r="C40" s="665" t="n"/>
+      <c r="D40" s="665" t="n"/>
+      <c r="E40" s="665" t="n"/>
+      <c r="F40" s="665" t="n"/>
+      <c r="G40" s="665" t="n"/>
+      <c r="H40" s="665" t="n"/>
+      <c r="I40" s="665" t="n"/>
+      <c r="J40" s="665" t="n"/>
       <c r="K40" s="665" t="n"/>
       <c r="L40" s="665" t="n"/>
       <c r="M40" s="665" t="n"/>
@@ -9034,50 +9318,50 @@
       <c r="AN46" s="667" t="n"/>
     </row>
     <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="704" t="inlineStr">
+      <c r="A47" s="407" t="inlineStr">
         <is>
           <t>NOTICE  —  Enter data only in designated white input cells. One form per event or job unless this workbook is designated as rolling. Do not add, delete or resize columns/rows. File naming: FRM-213_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="705" t="n"/>
-      <c r="C47" s="705" t="n"/>
-      <c r="D47" s="705" t="n"/>
-      <c r="E47" s="705" t="n"/>
-      <c r="F47" s="705" t="n"/>
-      <c r="G47" s="705" t="n"/>
-      <c r="H47" s="705" t="n"/>
-      <c r="I47" s="705" t="n"/>
-      <c r="J47" s="705" t="n"/>
-      <c r="K47" s="705" t="n"/>
-      <c r="L47" s="705" t="n"/>
-      <c r="M47" s="705" t="n"/>
-      <c r="N47" s="705" t="n"/>
-      <c r="O47" s="705" t="n"/>
-      <c r="P47" s="705" t="n"/>
-      <c r="Q47" s="705" t="n"/>
-      <c r="R47" s="705" t="n"/>
-      <c r="S47" s="705" t="n"/>
-      <c r="T47" s="705" t="n"/>
-      <c r="U47" s="705" t="n"/>
-      <c r="V47" s="705" t="n"/>
-      <c r="W47" s="705" t="n"/>
-      <c r="X47" s="705" t="n"/>
-      <c r="Y47" s="705" t="n"/>
-      <c r="Z47" s="705" t="n"/>
-      <c r="AA47" s="705" t="n"/>
-      <c r="AB47" s="705" t="n"/>
-      <c r="AC47" s="705" t="n"/>
-      <c r="AD47" s="705" t="n"/>
-      <c r="AE47" s="705" t="n"/>
-      <c r="AF47" s="705" t="n"/>
-      <c r="AG47" s="705" t="n"/>
-      <c r="AH47" s="705" t="n"/>
-      <c r="AI47" s="705" t="n"/>
-      <c r="AJ47" s="705" t="n"/>
-      <c r="AK47" s="705" t="n"/>
-      <c r="AL47" s="705" t="n"/>
-      <c r="AM47" s="705" t="n"/>
-      <c r="AN47" s="706" t="n"/>
+      <c r="B47" s="408" t="n"/>
+      <c r="C47" s="408" t="n"/>
+      <c r="D47" s="408" t="n"/>
+      <c r="E47" s="408" t="n"/>
+      <c r="F47" s="408" t="n"/>
+      <c r="G47" s="408" t="n"/>
+      <c r="H47" s="408" t="n"/>
+      <c r="I47" s="408" t="n"/>
+      <c r="J47" s="408" t="n"/>
+      <c r="K47" s="408" t="n"/>
+      <c r="L47" s="408" t="n"/>
+      <c r="M47" s="408" t="n"/>
+      <c r="N47" s="408" t="n"/>
+      <c r="O47" s="408" t="n"/>
+      <c r="P47" s="408" t="n"/>
+      <c r="Q47" s="408" t="n"/>
+      <c r="R47" s="408" t="n"/>
+      <c r="S47" s="408" t="n"/>
+      <c r="T47" s="408" t="n"/>
+      <c r="U47" s="408" t="n"/>
+      <c r="V47" s="408" t="n"/>
+      <c r="W47" s="408" t="n"/>
+      <c r="X47" s="408" t="n"/>
+      <c r="Y47" s="408" t="n"/>
+      <c r="Z47" s="408" t="n"/>
+      <c r="AA47" s="408" t="n"/>
+      <c r="AB47" s="408" t="n"/>
+      <c r="AC47" s="408" t="n"/>
+      <c r="AD47" s="408" t="n"/>
+      <c r="AE47" s="408" t="n"/>
+      <c r="AF47" s="408" t="n"/>
+      <c r="AG47" s="408" t="n"/>
+      <c r="AH47" s="408" t="n"/>
+      <c r="AI47" s="408" t="n"/>
+      <c r="AJ47" s="408" t="n"/>
+      <c r="AK47" s="408" t="n"/>
+      <c r="AL47" s="408" t="n"/>
+      <c r="AM47" s="408" t="n"/>
+      <c r="AN47" s="409" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="1"/>
     <row r="49" hidden="1" outlineLevel="1"/>
@@ -9399,331 +9683,319 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="707" t="n"/>
-      <c r="B1" s="708" t="n"/>
-      <c r="C1" s="708" t="n"/>
-      <c r="D1" s="708" t="n"/>
-      <c r="E1" s="708" t="n"/>
-      <c r="F1" s="708" t="n"/>
-      <c r="G1" s="708" t="n"/>
-      <c r="H1" s="709" t="n"/>
-      <c r="I1" s="710" t="inlineStr"/>
-      <c r="J1" s="708" t="n"/>
-      <c r="K1" s="708" t="n"/>
-      <c r="L1" s="708" t="n"/>
-      <c r="M1" s="708" t="n"/>
-      <c r="N1" s="708" t="n"/>
-      <c r="O1" s="708" t="n"/>
-      <c r="P1" s="708" t="n"/>
-      <c r="Q1" s="708" t="n"/>
-      <c r="R1" s="708" t="n"/>
-      <c r="S1" s="708" t="n"/>
-      <c r="T1" s="708" t="n"/>
-      <c r="U1" s="708" t="n"/>
-      <c r="V1" s="708" t="n"/>
-      <c r="W1" s="708" t="n"/>
-      <c r="X1" s="708" t="n"/>
-      <c r="Y1" s="708" t="n"/>
-      <c r="Z1" s="708" t="n"/>
-      <c r="AA1" s="708" t="n"/>
-      <c r="AB1" s="708" t="n"/>
-      <c r="AC1" s="708" t="n"/>
-      <c r="AD1" s="709" t="n"/>
-      <c r="AE1" s="513" t="inlineStr">
+    <row r="1" hidden="1">
+      <c r="A1" s="754" t="n"/>
+      <c r="B1" s="690" t="n"/>
+      <c r="C1" s="690" t="n"/>
+      <c r="D1" s="690" t="n"/>
+      <c r="E1" s="690" t="n"/>
+      <c r="F1" s="690" t="n"/>
+      <c r="G1" s="690" t="n"/>
+      <c r="H1" s="755" t="n"/>
+      <c r="I1" s="756" t="inlineStr"/>
+      <c r="J1" s="690" t="n"/>
+      <c r="K1" s="690" t="n"/>
+      <c r="L1" s="690" t="n"/>
+      <c r="M1" s="690" t="n"/>
+      <c r="N1" s="690" t="n"/>
+      <c r="O1" s="690" t="n"/>
+      <c r="P1" s="690" t="n"/>
+      <c r="Q1" s="690" t="n"/>
+      <c r="R1" s="690" t="n"/>
+      <c r="S1" s="690" t="n"/>
+      <c r="T1" s="690" t="n"/>
+      <c r="U1" s="690" t="n"/>
+      <c r="V1" s="690" t="n"/>
+      <c r="W1" s="690" t="n"/>
+      <c r="X1" s="690" t="n"/>
+      <c r="Y1" s="690" t="n"/>
+      <c r="Z1" s="690" t="n"/>
+      <c r="AA1" s="690" t="n"/>
+      <c r="AB1" s="690" t="n"/>
+      <c r="AC1" s="690" t="n"/>
+      <c r="AD1" s="755" t="n"/>
+      <c r="AE1" s="514" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="708" t="n"/>
-      <c r="AG1" s="708" t="n"/>
-      <c r="AH1" s="711" t="n"/>
-      <c r="AI1" s="516" t="n"/>
-      <c r="AJ1" s="708" t="n"/>
-      <c r="AK1" s="708" t="n"/>
-      <c r="AL1" s="708" t="n"/>
-      <c r="AM1" s="708" t="n"/>
-      <c r="AN1" s="709" t="n"/>
+      <c r="AF1" s="690" t="n"/>
+      <c r="AG1" s="690" t="n"/>
+      <c r="AH1" s="757" t="n"/>
+      <c r="AI1" s="517" t="n"/>
+      <c r="AJ1" s="690" t="n"/>
+      <c r="AK1" s="690" t="n"/>
+      <c r="AL1" s="690" t="n"/>
+      <c r="AM1" s="690" t="n"/>
+      <c r="AN1" s="755" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="712" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="713" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="713" t="n"/>
-      <c r="AE2" s="714" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="727" t="n"/>
+      <c r="C2" s="727" t="n"/>
+      <c r="D2" s="727" t="n"/>
+      <c r="E2" s="727" t="n"/>
+      <c r="F2" s="727" t="n"/>
+      <c r="G2" s="727" t="n"/>
+      <c r="H2" s="728" t="n"/>
+      <c r="I2" s="727" t="n"/>
+      <c r="J2" s="727" t="n"/>
+      <c r="K2" s="727" t="n"/>
+      <c r="L2" s="727" t="n"/>
+      <c r="M2" s="727" t="n"/>
+      <c r="N2" s="727" t="n"/>
+      <c r="O2" s="727" t="n"/>
+      <c r="P2" s="727" t="n"/>
+      <c r="Q2" s="727" t="n"/>
+      <c r="R2" s="727" t="n"/>
+      <c r="S2" s="727" t="n"/>
+      <c r="T2" s="727" t="n"/>
+      <c r="U2" s="727" t="n"/>
+      <c r="V2" s="727" t="n"/>
+      <c r="W2" s="727" t="n"/>
+      <c r="X2" s="727" t="n"/>
+      <c r="Y2" s="727" t="n"/>
+      <c r="Z2" s="727" t="n"/>
+      <c r="AA2" s="727" t="n"/>
+      <c r="AB2" s="727" t="n"/>
+      <c r="AC2" s="727" t="n"/>
+      <c r="AD2" s="728" t="n"/>
+      <c r="AE2" s="758" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="10" t="n"/>
-      <c r="AG2" s="10" t="n"/>
-      <c r="AH2" s="715" t="n"/>
-      <c r="AI2" s="716" t="n"/>
-      <c r="AJ2" s="10" t="n"/>
-      <c r="AK2" s="10" t="n"/>
-      <c r="AL2" s="10" t="n"/>
-      <c r="AM2" s="10" t="n"/>
-      <c r="AN2" s="713" t="n"/>
+      <c r="AF2" s="759" t="n"/>
+      <c r="AG2" s="759" t="n"/>
+      <c r="AH2" s="760" t="n"/>
+      <c r="AI2" s="732" t="n"/>
+      <c r="AJ2" s="761" t="n"/>
+      <c r="AK2" s="761" t="n"/>
+      <c r="AL2" s="761" t="n"/>
+      <c r="AM2" s="761" t="n"/>
+      <c r="AN2" s="762" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="712" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="713" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="713" t="n"/>
-      <c r="AE3" s="714" t="inlineStr">
+      <c r="A3" s="734" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="735" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="735" t="n"/>
+      <c r="AE3" s="763" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="10" t="n"/>
-      <c r="AH3" s="715" t="n"/>
-      <c r="AI3" s="716" t="n"/>
-      <c r="AJ3" s="10" t="n"/>
-      <c r="AK3" s="10" t="n"/>
-      <c r="AL3" s="10" t="n"/>
-      <c r="AM3" s="10" t="n"/>
-      <c r="AN3" s="713" t="n"/>
+      <c r="AF3" s="764" t="n"/>
+      <c r="AG3" s="764" t="n"/>
+      <c r="AH3" s="765" t="n"/>
+      <c r="AI3" s="740" t="n"/>
+      <c r="AJ3" s="766" t="n"/>
+      <c r="AK3" s="766" t="n"/>
+      <c r="AL3" s="766" t="n"/>
+      <c r="AM3" s="766" t="n"/>
+      <c r="AN3" s="767" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="712" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="713" t="n"/>
-      <c r="I4" s="717" t="inlineStr"/>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="713" t="n"/>
-      <c r="AE4" s="714" t="inlineStr">
+      <c r="A4" s="734" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="735" t="n"/>
+      <c r="I4" s="768" t="inlineStr"/>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="735" t="n"/>
+      <c r="AE4" s="763" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="10" t="n"/>
-      <c r="AG4" s="10" t="n"/>
-      <c r="AH4" s="715" t="n"/>
-      <c r="AI4" s="716" t="n"/>
-      <c r="AJ4" s="10" t="n"/>
-      <c r="AK4" s="10" t="n"/>
-      <c r="AL4" s="10" t="n"/>
-      <c r="AM4" s="10" t="n"/>
-      <c r="AN4" s="713" t="n"/>
+      <c r="AF4" s="764" t="n"/>
+      <c r="AG4" s="764" t="n"/>
+      <c r="AH4" s="765" t="n"/>
+      <c r="AI4" s="740" t="n"/>
+      <c r="AJ4" s="766" t="n"/>
+      <c r="AK4" s="766" t="n"/>
+      <c r="AL4" s="766" t="n"/>
+      <c r="AM4" s="766" t="n"/>
+      <c r="AN4" s="767" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="718" t="n"/>
-      <c r="B5" s="719" t="n"/>
-      <c r="C5" s="719" t="n"/>
-      <c r="D5" s="719" t="n"/>
-      <c r="E5" s="719" t="n"/>
-      <c r="F5" s="719" t="n"/>
-      <c r="G5" s="719" t="n"/>
-      <c r="H5" s="720" t="n"/>
-      <c r="I5" s="721" t="inlineStr"/>
-      <c r="J5" s="719" t="n"/>
-      <c r="K5" s="719" t="n"/>
-      <c r="L5" s="719" t="n"/>
-      <c r="M5" s="719" t="n"/>
-      <c r="N5" s="719" t="n"/>
-      <c r="O5" s="719" t="n"/>
-      <c r="P5" s="719" t="n"/>
-      <c r="Q5" s="719" t="n"/>
-      <c r="R5" s="719" t="n"/>
-      <c r="S5" s="719" t="n"/>
-      <c r="T5" s="719" t="n"/>
-      <c r="U5" s="719" t="n"/>
-      <c r="V5" s="719" t="n"/>
-      <c r="W5" s="719" t="n"/>
-      <c r="X5" s="719" t="n"/>
-      <c r="Y5" s="719" t="n"/>
-      <c r="Z5" s="719" t="n"/>
-      <c r="AA5" s="719" t="n"/>
-      <c r="AB5" s="719" t="n"/>
-      <c r="AC5" s="719" t="n"/>
-      <c r="AD5" s="720" t="n"/>
-      <c r="AE5" s="722" t="inlineStr">
+      <c r="A5" s="734" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="735" t="n"/>
+      <c r="I5" s="769" t="inlineStr"/>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="735" t="n"/>
+      <c r="AE5" s="763" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="719" t="n"/>
-      <c r="AG5" s="719" t="n"/>
-      <c r="AH5" s="723" t="n"/>
-      <c r="AI5" s="724" t="n"/>
-      <c r="AJ5" s="719" t="n"/>
-      <c r="AK5" s="719" t="n"/>
-      <c r="AL5" s="719" t="n"/>
-      <c r="AM5" s="719" t="n"/>
-      <c r="AN5" s="720" t="n"/>
+      <c r="AF5" s="764" t="n"/>
+      <c r="AG5" s="764" t="n"/>
+      <c r="AH5" s="765" t="n"/>
+      <c r="AI5" s="740" t="n"/>
+      <c r="AJ5" s="766" t="n"/>
+      <c r="AK5" s="766" t="n"/>
+      <c r="AL5" s="766" t="n"/>
+      <c r="AM5" s="766" t="n"/>
+      <c r="AN5" s="767" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="725" t="n"/>
-      <c r="B6" s="725" t="n"/>
-      <c r="C6" s="725" t="n"/>
-      <c r="D6" s="725" t="n"/>
-      <c r="E6" s="725" t="n"/>
-      <c r="F6" s="725" t="n"/>
-      <c r="G6" s="725" t="n"/>
-      <c r="H6" s="725" t="n"/>
-      <c r="I6" s="725" t="n"/>
-      <c r="J6" s="725" t="n"/>
-      <c r="K6" s="725" t="n"/>
-      <c r="L6" s="725" t="n"/>
-      <c r="M6" s="725" t="n"/>
-      <c r="N6" s="725" t="n"/>
-      <c r="O6" s="725" t="n"/>
-      <c r="P6" s="725" t="n"/>
-      <c r="Q6" s="725" t="n"/>
-      <c r="R6" s="725" t="n"/>
-      <c r="S6" s="725" t="n"/>
-      <c r="T6" s="725" t="n"/>
-      <c r="U6" s="725" t="n"/>
-      <c r="V6" s="725" t="n"/>
-      <c r="W6" s="725" t="n"/>
-      <c r="X6" s="725" t="n"/>
-      <c r="Y6" s="725" t="n"/>
-      <c r="Z6" s="725" t="n"/>
-      <c r="AA6" s="725" t="n"/>
-      <c r="AB6" s="725" t="n"/>
-      <c r="AC6" s="725" t="n"/>
-      <c r="AD6" s="725" t="n"/>
-      <c r="AE6" s="725" t="n"/>
-      <c r="AF6" s="725" t="n"/>
-      <c r="AG6" s="725" t="n"/>
-      <c r="AH6" s="725" t="n"/>
-      <c r="AI6" s="725" t="n"/>
-      <c r="AJ6" s="725" t="n"/>
-      <c r="AK6" s="725" t="n"/>
-      <c r="AL6" s="725" t="n"/>
-      <c r="AM6" s="725" t="n"/>
-      <c r="AN6" s="725" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="770" t="n"/>
+      <c r="B6" s="771" t="n"/>
+      <c r="C6" s="771" t="n"/>
+      <c r="D6" s="771" t="n"/>
+      <c r="E6" s="771" t="n"/>
+      <c r="F6" s="771" t="n"/>
+      <c r="G6" s="771" t="n"/>
+      <c r="H6" s="772" t="n"/>
+      <c r="I6" s="771" t="n"/>
+      <c r="J6" s="771" t="n"/>
+      <c r="K6" s="771" t="n"/>
+      <c r="L6" s="771" t="n"/>
+      <c r="M6" s="771" t="n"/>
+      <c r="N6" s="771" t="n"/>
+      <c r="O6" s="771" t="n"/>
+      <c r="P6" s="771" t="n"/>
+      <c r="Q6" s="771" t="n"/>
+      <c r="R6" s="771" t="n"/>
+      <c r="S6" s="771" t="n"/>
+      <c r="T6" s="771" t="n"/>
+      <c r="U6" s="771" t="n"/>
+      <c r="V6" s="771" t="n"/>
+      <c r="W6" s="771" t="n"/>
+      <c r="X6" s="771" t="n"/>
+      <c r="Y6" s="771" t="n"/>
+      <c r="Z6" s="771" t="n"/>
+      <c r="AA6" s="771" t="n"/>
+      <c r="AB6" s="771" t="n"/>
+      <c r="AC6" s="771" t="n"/>
+      <c r="AD6" s="772" t="n"/>
+      <c r="AE6" s="773" t="n"/>
+      <c r="AF6" s="773" t="n"/>
+      <c r="AG6" s="773" t="n"/>
+      <c r="AH6" s="774" t="n"/>
+      <c r="AI6" s="775" t="n"/>
+      <c r="AJ6" s="775" t="n"/>
+      <c r="AK6" s="775" t="n"/>
+      <c r="AL6" s="775" t="n"/>
+      <c r="AM6" s="775" t="n"/>
+      <c r="AN6" s="776" t="n"/>
     </row>
-    <row r="7">
-      <c r="A7" s="430" t="inlineStr">
-        <is>
-          <t>VAL_DECISION_GATE_CORE</t>
-        </is>
-      </c>
-      <c r="B7" s="430" t="inlineStr">
-        <is>
-          <t>VAL_ESCALATION_LEVEL</t>
-        </is>
-      </c>
-      <c r="C7" s="430" t="inlineStr">
-        <is>
-          <t>VAL_STATUS_CORE</t>
-        </is>
-      </c>
-      <c r="D7" s="726" t="n"/>
-      <c r="E7" s="726" t="n"/>
-      <c r="F7" s="726" t="n"/>
-      <c r="G7" s="726" t="n"/>
-      <c r="H7" s="726" t="n"/>
-      <c r="I7" s="726" t="n"/>
-      <c r="J7" s="726" t="n"/>
-      <c r="K7" s="726" t="n"/>
-      <c r="L7" s="726" t="n"/>
-      <c r="M7" s="726" t="n"/>
-      <c r="N7" s="726" t="n"/>
-      <c r="O7" s="726" t="n"/>
-      <c r="P7" s="726" t="n"/>
-      <c r="Q7" s="726" t="n"/>
-      <c r="R7" s="726" t="n"/>
-      <c r="S7" s="726" t="n"/>
-      <c r="T7" s="726" t="n"/>
-      <c r="U7" s="726" t="n"/>
-      <c r="V7" s="726" t="n"/>
-      <c r="W7" s="726" t="n"/>
-      <c r="X7" s="726" t="n"/>
-      <c r="Y7" s="726" t="n"/>
-      <c r="Z7" s="726" t="n"/>
-      <c r="AA7" s="726" t="n"/>
-      <c r="AB7" s="726" t="n"/>
-      <c r="AC7" s="726" t="n"/>
-      <c r="AD7" s="726" t="n"/>
-      <c r="AE7" s="726" t="n"/>
-      <c r="AF7" s="726" t="n"/>
-      <c r="AG7" s="726" t="n"/>
-      <c r="AH7" s="726" t="n"/>
-      <c r="AI7" s="726" t="n"/>
-      <c r="AJ7" s="726" t="n"/>
-      <c r="AK7" s="726" t="n"/>
-      <c r="AL7" s="726" t="n"/>
-      <c r="AM7" s="726" t="n"/>
-      <c r="AN7" s="726" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="777" t="n"/>
+      <c r="B7" s="777" t="n"/>
+      <c r="C7" s="777" t="n"/>
+      <c r="D7" s="778" t="n"/>
+      <c r="E7" s="778" t="n"/>
+      <c r="F7" s="778" t="n"/>
+      <c r="G7" s="778" t="n"/>
+      <c r="H7" s="778" t="n"/>
+      <c r="I7" s="778" t="n"/>
+      <c r="J7" s="778" t="n"/>
+      <c r="K7" s="778" t="n"/>
+      <c r="L7" s="778" t="n"/>
+      <c r="M7" s="778" t="n"/>
+      <c r="N7" s="778" t="n"/>
+      <c r="O7" s="778" t="n"/>
+      <c r="P7" s="778" t="n"/>
+      <c r="Q7" s="778" t="n"/>
+      <c r="R7" s="778" t="n"/>
+      <c r="S7" s="778" t="n"/>
+      <c r="T7" s="778" t="n"/>
+      <c r="U7" s="778" t="n"/>
+      <c r="V7" s="778" t="n"/>
+      <c r="W7" s="778" t="n"/>
+      <c r="X7" s="778" t="n"/>
+      <c r="Y7" s="778" t="n"/>
+      <c r="Z7" s="778" t="n"/>
+      <c r="AA7" s="778" t="n"/>
+      <c r="AB7" s="778" t="n"/>
+      <c r="AC7" s="778" t="n"/>
+      <c r="AD7" s="778" t="n"/>
+      <c r="AE7" s="778" t="n"/>
+      <c r="AF7" s="778" t="n"/>
+      <c r="AG7" s="778" t="n"/>
+      <c r="AH7" s="778" t="n"/>
+      <c r="AI7" s="778" t="n"/>
+      <c r="AJ7" s="778" t="n"/>
+      <c r="AK7" s="778" t="n"/>
+      <c r="AL7" s="778" t="n"/>
+      <c r="AM7" s="778" t="n"/>
+      <c r="AN7" s="778" t="n"/>
     </row>
     <row r="8" hidden="1">
       <c r="A8" s="430" t="inlineStr">
@@ -10366,6 +10638,7 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10420,353 +10693,337 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="707" t="n"/>
-      <c r="B1" s="708" t="n"/>
-      <c r="C1" s="708" t="n"/>
-      <c r="D1" s="708" t="n"/>
-      <c r="E1" s="708" t="n"/>
-      <c r="F1" s="708" t="n"/>
-      <c r="G1" s="708" t="n"/>
-      <c r="H1" s="709" t="n"/>
-      <c r="I1" s="710" t="inlineStr"/>
-      <c r="J1" s="708" t="n"/>
-      <c r="K1" s="708" t="n"/>
-      <c r="L1" s="708" t="n"/>
-      <c r="M1" s="708" t="n"/>
-      <c r="N1" s="708" t="n"/>
-      <c r="O1" s="708" t="n"/>
-      <c r="P1" s="708" t="n"/>
-      <c r="Q1" s="708" t="n"/>
-      <c r="R1" s="708" t="n"/>
-      <c r="S1" s="708" t="n"/>
-      <c r="T1" s="708" t="n"/>
-      <c r="U1" s="708" t="n"/>
-      <c r="V1" s="708" t="n"/>
-      <c r="W1" s="708" t="n"/>
-      <c r="X1" s="708" t="n"/>
-      <c r="Y1" s="708" t="n"/>
-      <c r="Z1" s="708" t="n"/>
-      <c r="AA1" s="708" t="n"/>
-      <c r="AB1" s="708" t="n"/>
-      <c r="AC1" s="708" t="n"/>
-      <c r="AD1" s="709" t="n"/>
-      <c r="AE1" s="513" t="inlineStr">
+    <row r="1" hidden="1">
+      <c r="A1" s="754" t="n"/>
+      <c r="B1" s="690" t="n"/>
+      <c r="C1" s="690" t="n"/>
+      <c r="D1" s="690" t="n"/>
+      <c r="E1" s="690" t="n"/>
+      <c r="F1" s="690" t="n"/>
+      <c r="G1" s="690" t="n"/>
+      <c r="H1" s="755" t="n"/>
+      <c r="I1" s="756" t="inlineStr"/>
+      <c r="J1" s="690" t="n"/>
+      <c r="K1" s="690" t="n"/>
+      <c r="L1" s="690" t="n"/>
+      <c r="M1" s="690" t="n"/>
+      <c r="N1" s="690" t="n"/>
+      <c r="O1" s="690" t="n"/>
+      <c r="P1" s="690" t="n"/>
+      <c r="Q1" s="690" t="n"/>
+      <c r="R1" s="690" t="n"/>
+      <c r="S1" s="690" t="n"/>
+      <c r="T1" s="690" t="n"/>
+      <c r="U1" s="690" t="n"/>
+      <c r="V1" s="690" t="n"/>
+      <c r="W1" s="690" t="n"/>
+      <c r="X1" s="690" t="n"/>
+      <c r="Y1" s="690" t="n"/>
+      <c r="Z1" s="690" t="n"/>
+      <c r="AA1" s="690" t="n"/>
+      <c r="AB1" s="690" t="n"/>
+      <c r="AC1" s="690" t="n"/>
+      <c r="AD1" s="755" t="n"/>
+      <c r="AE1" s="514" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="708" t="n"/>
-      <c r="AG1" s="708" t="n"/>
-      <c r="AH1" s="711" t="n"/>
-      <c r="AI1" s="516" t="n"/>
-      <c r="AJ1" s="708" t="n"/>
-      <c r="AK1" s="708" t="n"/>
-      <c r="AL1" s="708" t="n"/>
-      <c r="AM1" s="708" t="n"/>
-      <c r="AN1" s="709" t="n"/>
+      <c r="AF1" s="690" t="n"/>
+      <c r="AG1" s="690" t="n"/>
+      <c r="AH1" s="757" t="n"/>
+      <c r="AI1" s="517" t="n"/>
+      <c r="AJ1" s="690" t="n"/>
+      <c r="AK1" s="690" t="n"/>
+      <c r="AL1" s="690" t="n"/>
+      <c r="AM1" s="690" t="n"/>
+      <c r="AN1" s="755" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="712" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="713" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="713" t="n"/>
-      <c r="AE2" s="714" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="727" t="n"/>
+      <c r="C2" s="727" t="n"/>
+      <c r="D2" s="727" t="n"/>
+      <c r="E2" s="727" t="n"/>
+      <c r="F2" s="727" t="n"/>
+      <c r="G2" s="727" t="n"/>
+      <c r="H2" s="728" t="n"/>
+      <c r="I2" s="727" t="n"/>
+      <c r="J2" s="727" t="n"/>
+      <c r="K2" s="727" t="n"/>
+      <c r="L2" s="727" t="n"/>
+      <c r="M2" s="727" t="n"/>
+      <c r="N2" s="727" t="n"/>
+      <c r="O2" s="727" t="n"/>
+      <c r="P2" s="727" t="n"/>
+      <c r="Q2" s="727" t="n"/>
+      <c r="R2" s="727" t="n"/>
+      <c r="S2" s="727" t="n"/>
+      <c r="T2" s="727" t="n"/>
+      <c r="U2" s="727" t="n"/>
+      <c r="V2" s="727" t="n"/>
+      <c r="W2" s="727" t="n"/>
+      <c r="X2" s="727" t="n"/>
+      <c r="Y2" s="727" t="n"/>
+      <c r="Z2" s="727" t="n"/>
+      <c r="AA2" s="727" t="n"/>
+      <c r="AB2" s="727" t="n"/>
+      <c r="AC2" s="727" t="n"/>
+      <c r="AD2" s="728" t="n"/>
+      <c r="AE2" s="758" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="10" t="n"/>
-      <c r="AG2" s="10" t="n"/>
-      <c r="AH2" s="715" t="n"/>
-      <c r="AI2" s="716" t="n"/>
-      <c r="AJ2" s="10" t="n"/>
-      <c r="AK2" s="10" t="n"/>
-      <c r="AL2" s="10" t="n"/>
-      <c r="AM2" s="10" t="n"/>
-      <c r="AN2" s="713" t="n"/>
+      <c r="AF2" s="759" t="n"/>
+      <c r="AG2" s="759" t="n"/>
+      <c r="AH2" s="760" t="n"/>
+      <c r="AI2" s="732" t="n"/>
+      <c r="AJ2" s="761" t="n"/>
+      <c r="AK2" s="761" t="n"/>
+      <c r="AL2" s="761" t="n"/>
+      <c r="AM2" s="761" t="n"/>
+      <c r="AN2" s="762" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="712" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="713" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="713" t="n"/>
-      <c r="AE3" s="714" t="inlineStr">
+      <c r="A3" s="734" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="735" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="735" t="n"/>
+      <c r="AE3" s="763" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="10" t="n"/>
-      <c r="AH3" s="715" t="n"/>
-      <c r="AI3" s="716" t="n"/>
-      <c r="AJ3" s="10" t="n"/>
-      <c r="AK3" s="10" t="n"/>
-      <c r="AL3" s="10" t="n"/>
-      <c r="AM3" s="10" t="n"/>
-      <c r="AN3" s="713" t="n"/>
+      <c r="AF3" s="764" t="n"/>
+      <c r="AG3" s="764" t="n"/>
+      <c r="AH3" s="765" t="n"/>
+      <c r="AI3" s="740" t="n"/>
+      <c r="AJ3" s="766" t="n"/>
+      <c r="AK3" s="766" t="n"/>
+      <c r="AL3" s="766" t="n"/>
+      <c r="AM3" s="766" t="n"/>
+      <c r="AN3" s="767" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="712" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="713" t="n"/>
-      <c r="I4" s="717" t="inlineStr"/>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="713" t="n"/>
-      <c r="AE4" s="714" t="inlineStr">
+      <c r="A4" s="734" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="735" t="n"/>
+      <c r="I4" s="768" t="inlineStr"/>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="735" t="n"/>
+      <c r="AE4" s="763" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="10" t="n"/>
-      <c r="AG4" s="10" t="n"/>
-      <c r="AH4" s="715" t="n"/>
-      <c r="AI4" s="716" t="n"/>
-      <c r="AJ4" s="10" t="n"/>
-      <c r="AK4" s="10" t="n"/>
-      <c r="AL4" s="10" t="n"/>
-      <c r="AM4" s="10" t="n"/>
-      <c r="AN4" s="713" t="n"/>
+      <c r="AF4" s="764" t="n"/>
+      <c r="AG4" s="764" t="n"/>
+      <c r="AH4" s="765" t="n"/>
+      <c r="AI4" s="740" t="n"/>
+      <c r="AJ4" s="766" t="n"/>
+      <c r="AK4" s="766" t="n"/>
+      <c r="AL4" s="766" t="n"/>
+      <c r="AM4" s="766" t="n"/>
+      <c r="AN4" s="767" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="718" t="n"/>
-      <c r="B5" s="719" t="n"/>
-      <c r="C5" s="719" t="n"/>
-      <c r="D5" s="719" t="n"/>
-      <c r="E5" s="719" t="n"/>
-      <c r="F5" s="719" t="n"/>
-      <c r="G5" s="719" t="n"/>
-      <c r="H5" s="720" t="n"/>
-      <c r="I5" s="721" t="inlineStr"/>
-      <c r="J5" s="719" t="n"/>
-      <c r="K5" s="719" t="n"/>
-      <c r="L5" s="719" t="n"/>
-      <c r="M5" s="719" t="n"/>
-      <c r="N5" s="719" t="n"/>
-      <c r="O5" s="719" t="n"/>
-      <c r="P5" s="719" t="n"/>
-      <c r="Q5" s="719" t="n"/>
-      <c r="R5" s="719" t="n"/>
-      <c r="S5" s="719" t="n"/>
-      <c r="T5" s="719" t="n"/>
-      <c r="U5" s="719" t="n"/>
-      <c r="V5" s="719" t="n"/>
-      <c r="W5" s="719" t="n"/>
-      <c r="X5" s="719" t="n"/>
-      <c r="Y5" s="719" t="n"/>
-      <c r="Z5" s="719" t="n"/>
-      <c r="AA5" s="719" t="n"/>
-      <c r="AB5" s="719" t="n"/>
-      <c r="AC5" s="719" t="n"/>
-      <c r="AD5" s="720" t="n"/>
-      <c r="AE5" s="722" t="inlineStr">
+      <c r="A5" s="734" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="735" t="n"/>
+      <c r="I5" s="769" t="inlineStr"/>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="735" t="n"/>
+      <c r="AE5" s="763" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="719" t="n"/>
-      <c r="AG5" s="719" t="n"/>
-      <c r="AH5" s="723" t="n"/>
-      <c r="AI5" s="724" t="n"/>
-      <c r="AJ5" s="719" t="n"/>
-      <c r="AK5" s="719" t="n"/>
-      <c r="AL5" s="719" t="n"/>
-      <c r="AM5" s="719" t="n"/>
-      <c r="AN5" s="720" t="n"/>
+      <c r="AF5" s="764" t="n"/>
+      <c r="AG5" s="764" t="n"/>
+      <c r="AH5" s="765" t="n"/>
+      <c r="AI5" s="740" t="n"/>
+      <c r="AJ5" s="766" t="n"/>
+      <c r="AK5" s="766" t="n"/>
+      <c r="AL5" s="766" t="n"/>
+      <c r="AM5" s="766" t="n"/>
+      <c r="AN5" s="767" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="725" t="n"/>
-      <c r="B6" s="725" t="n"/>
-      <c r="C6" s="725" t="n"/>
-      <c r="D6" s="725" t="n"/>
-      <c r="E6" s="725" t="n"/>
-      <c r="F6" s="725" t="n"/>
-      <c r="G6" s="725" t="n"/>
-      <c r="H6" s="725" t="n"/>
-      <c r="I6" s="725" t="n"/>
-      <c r="J6" s="725" t="n"/>
-      <c r="K6" s="725" t="n"/>
-      <c r="L6" s="725" t="n"/>
-      <c r="M6" s="725" t="n"/>
-      <c r="N6" s="725" t="n"/>
-      <c r="O6" s="725" t="n"/>
-      <c r="P6" s="725" t="n"/>
-      <c r="Q6" s="725" t="n"/>
-      <c r="R6" s="725" t="n"/>
-      <c r="S6" s="725" t="n"/>
-      <c r="T6" s="725" t="n"/>
-      <c r="U6" s="725" t="n"/>
-      <c r="V6" s="725" t="n"/>
-      <c r="W6" s="725" t="n"/>
-      <c r="X6" s="725" t="n"/>
-      <c r="Y6" s="725" t="n"/>
-      <c r="Z6" s="725" t="n"/>
-      <c r="AA6" s="725" t="n"/>
-      <c r="AB6" s="725" t="n"/>
-      <c r="AC6" s="725" t="n"/>
-      <c r="AD6" s="725" t="n"/>
-      <c r="AE6" s="725" t="n"/>
-      <c r="AF6" s="725" t="n"/>
-      <c r="AG6" s="725" t="n"/>
-      <c r="AH6" s="725" t="n"/>
-      <c r="AI6" s="725" t="n"/>
-      <c r="AJ6" s="725" t="n"/>
-      <c r="AK6" s="725" t="n"/>
-      <c r="AL6" s="725" t="n"/>
-      <c r="AM6" s="725" t="n"/>
-      <c r="AN6" s="725" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="770" t="n"/>
+      <c r="B6" s="771" t="n"/>
+      <c r="C6" s="771" t="n"/>
+      <c r="D6" s="771" t="n"/>
+      <c r="E6" s="771" t="n"/>
+      <c r="F6" s="771" t="n"/>
+      <c r="G6" s="771" t="n"/>
+      <c r="H6" s="772" t="n"/>
+      <c r="I6" s="771" t="n"/>
+      <c r="J6" s="771" t="n"/>
+      <c r="K6" s="771" t="n"/>
+      <c r="L6" s="771" t="n"/>
+      <c r="M6" s="771" t="n"/>
+      <c r="N6" s="771" t="n"/>
+      <c r="O6" s="771" t="n"/>
+      <c r="P6" s="771" t="n"/>
+      <c r="Q6" s="771" t="n"/>
+      <c r="R6" s="771" t="n"/>
+      <c r="S6" s="771" t="n"/>
+      <c r="T6" s="771" t="n"/>
+      <c r="U6" s="771" t="n"/>
+      <c r="V6" s="771" t="n"/>
+      <c r="W6" s="771" t="n"/>
+      <c r="X6" s="771" t="n"/>
+      <c r="Y6" s="771" t="n"/>
+      <c r="Z6" s="771" t="n"/>
+      <c r="AA6" s="771" t="n"/>
+      <c r="AB6" s="771" t="n"/>
+      <c r="AC6" s="771" t="n"/>
+      <c r="AD6" s="772" t="n"/>
+      <c r="AE6" s="773" t="n"/>
+      <c r="AF6" s="773" t="n"/>
+      <c r="AG6" s="773" t="n"/>
+      <c r="AH6" s="774" t="n"/>
+      <c r="AI6" s="775" t="n"/>
+      <c r="AJ6" s="775" t="n"/>
+      <c r="AK6" s="775" t="n"/>
+      <c r="AL6" s="775" t="n"/>
+      <c r="AM6" s="775" t="n"/>
+      <c r="AN6" s="776" t="n"/>
     </row>
-    <row r="7">
-      <c r="A7" s="594" t="inlineStr">
-        <is>
-          <t>REF_CUSTOMER_MASTER</t>
-        </is>
-      </c>
-      <c r="B7" s="552" t="inlineStr">
-        <is>
-          <t>REF_EVIDENCE_LINK</t>
-        </is>
-      </c>
-      <c r="C7" s="552" t="inlineStr">
-        <is>
-          <t>REF_OWNER_PERSON_MASTER</t>
-        </is>
-      </c>
-      <c r="D7" s="552" t="inlineStr">
-        <is>
-          <t>REF_PART_REV_MASTER</t>
-        </is>
-      </c>
-      <c r="E7" s="726" t="n"/>
-      <c r="F7" s="726" t="n"/>
-      <c r="G7" s="726" t="n"/>
-      <c r="H7" s="726" t="n"/>
-      <c r="I7" s="726" t="n"/>
-      <c r="J7" s="726" t="n"/>
-      <c r="K7" s="726" t="n"/>
-      <c r="L7" s="726" t="n"/>
-      <c r="M7" s="726" t="n"/>
-      <c r="N7" s="726" t="n"/>
-      <c r="O7" s="726" t="n"/>
-      <c r="P7" s="726" t="n"/>
-      <c r="Q7" s="726" t="n"/>
-      <c r="R7" s="726" t="n"/>
-      <c r="S7" s="726" t="n"/>
-      <c r="T7" s="726" t="n"/>
-      <c r="U7" s="726" t="n"/>
-      <c r="V7" s="726" t="n"/>
-      <c r="W7" s="726" t="n"/>
-      <c r="X7" s="726" t="n"/>
-      <c r="Y7" s="726" t="n"/>
-      <c r="Z7" s="726" t="n"/>
-      <c r="AA7" s="726" t="n"/>
-      <c r="AB7" s="726" t="n"/>
-      <c r="AC7" s="726" t="n"/>
-      <c r="AD7" s="726" t="n"/>
-      <c r="AE7" s="726" t="n"/>
-      <c r="AF7" s="726" t="n"/>
-      <c r="AG7" s="726" t="n"/>
-      <c r="AH7" s="726" t="n"/>
-      <c r="AI7" s="726" t="n"/>
-      <c r="AJ7" s="726" t="n"/>
-      <c r="AK7" s="726" t="n"/>
-      <c r="AL7" s="726" t="n"/>
-      <c r="AM7" s="726" t="n"/>
-      <c r="AN7" s="726" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="777" t="n"/>
+      <c r="B7" s="777" t="n"/>
+      <c r="C7" s="777" t="n"/>
+      <c r="D7" s="777" t="n"/>
+      <c r="E7" s="778" t="n"/>
+      <c r="F7" s="778" t="n"/>
+      <c r="G7" s="778" t="n"/>
+      <c r="H7" s="778" t="n"/>
+      <c r="I7" s="778" t="n"/>
+      <c r="J7" s="778" t="n"/>
+      <c r="K7" s="778" t="n"/>
+      <c r="L7" s="778" t="n"/>
+      <c r="M7" s="778" t="n"/>
+      <c r="N7" s="778" t="n"/>
+      <c r="O7" s="778" t="n"/>
+      <c r="P7" s="778" t="n"/>
+      <c r="Q7" s="778" t="n"/>
+      <c r="R7" s="778" t="n"/>
+      <c r="S7" s="778" t="n"/>
+      <c r="T7" s="778" t="n"/>
+      <c r="U7" s="778" t="n"/>
+      <c r="V7" s="778" t="n"/>
+      <c r="W7" s="778" t="n"/>
+      <c r="X7" s="778" t="n"/>
+      <c r="Y7" s="778" t="n"/>
+      <c r="Z7" s="778" t="n"/>
+      <c r="AA7" s="778" t="n"/>
+      <c r="AB7" s="778" t="n"/>
+      <c r="AC7" s="778" t="n"/>
+      <c r="AD7" s="778" t="n"/>
+      <c r="AE7" s="778" t="n"/>
+      <c r="AF7" s="778" t="n"/>
+      <c r="AG7" s="778" t="n"/>
+      <c r="AH7" s="778" t="n"/>
+      <c r="AI7" s="778" t="n"/>
+      <c r="AJ7" s="778" t="n"/>
+      <c r="AK7" s="778" t="n"/>
+      <c r="AL7" s="778" t="n"/>
+      <c r="AM7" s="778" t="n"/>
+      <c r="AN7" s="778" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="592" t="inlineStr">
+      <c r="A8" s="779" t="inlineStr">
         <is>
           <t>CUST-001 Alpha Semi</t>
         </is>
       </c>
-      <c r="B8" s="437" t="inlineStr">
+      <c r="B8" s="780" t="inlineStr">
         <is>
           <t>M365://dossier/JOB-240001</t>
         </is>
       </c>
-      <c r="C8" s="437" t="inlineStr">
+      <c r="C8" s="780" t="inlineStr">
         <is>
           <t>Planning Lead</t>
         </is>
       </c>
-      <c r="D8" s="437" t="inlineStr">
+      <c r="D8" s="780" t="inlineStr">
         <is>
           <t>PN-1001 / Rev.A</t>
         </is>
@@ -10809,22 +11066,22 @@
       <c r="AN8" s="726" t="n"/>
     </row>
     <row r="9" hidden="1">
-      <c r="A9" s="592" t="inlineStr">
+      <c r="A9" s="779" t="inlineStr">
         <is>
           <t>CUST-002 NovaFab</t>
         </is>
       </c>
-      <c r="B9" s="437" t="inlineStr">
+      <c r="B9" s="780" t="inlineStr">
         <is>
           <t>SP://evidence/FRM-202/001</t>
         </is>
       </c>
-      <c r="C9" s="437" t="inlineStr">
+      <c r="C9" s="780" t="inlineStr">
         <is>
           <t>Production Supervisor</t>
         </is>
       </c>
-      <c r="D9" s="437" t="inlineStr">
+      <c r="D9" s="780" t="inlineStr">
         <is>
           <t>PN-1002 / Rev.B</t>
         </is>
@@ -10867,22 +11124,22 @@
       <c r="AN9" s="726" t="n"/>
     </row>
     <row r="10" hidden="1">
-      <c r="A10" s="592" t="inlineStr">
+      <c r="A10" s="779" t="inlineStr">
         <is>
           <t>CUST-003 Orion Tech</t>
         </is>
       </c>
-      <c r="B10" s="437" t="inlineStr">
+      <c r="B10" s="780" t="inlineStr">
         <is>
           <t>SP://evidence/FRM-306/002</t>
         </is>
       </c>
-      <c r="C10" s="437" t="inlineStr">
+      <c r="C10" s="780" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="D10" s="437" t="inlineStr">
+      <c r="D10" s="780" t="inlineStr">
         <is>
           <t>PN-1003 / Rev.C</t>
         </is>
@@ -10925,22 +11182,22 @@
       <c r="AN10" s="726" t="n"/>
     </row>
     <row r="11" hidden="1">
-      <c r="A11" s="592" t="inlineStr">
+      <c r="A11" s="779" t="inlineStr">
         <is>
           <t>CUST-004 Quantum Devices</t>
         </is>
       </c>
-      <c r="B11" s="437" t="inlineStr">
+      <c r="B11" s="780" t="inlineStr">
         <is>
           <t>Epicor://Job/JOB-240001</t>
         </is>
       </c>
-      <c r="C11" s="437" t="inlineStr">
+      <c r="C11" s="780" t="inlineStr">
         <is>
           <t>Engineering Lead</t>
         </is>
       </c>
-      <c r="D11" s="437" t="inlineStr">
+      <c r="D11" s="780" t="inlineStr">
         <is>
           <t>PN-1004 / Rev.D</t>
         </is>
@@ -10985,7 +11242,7 @@
     <row r="12" hidden="1">
       <c r="A12" s="726" t="n"/>
       <c r="B12" s="726" t="n"/>
-      <c r="C12" s="437" t="inlineStr">
+      <c r="C12" s="780" t="inlineStr">
         <is>
           <t>Setup Technician</t>
         </is>
@@ -11031,7 +11288,7 @@
     <row r="13" hidden="1">
       <c r="A13" s="726" t="n"/>
       <c r="B13" s="726" t="n"/>
-      <c r="C13" s="437" t="inlineStr">
+      <c r="C13" s="780" t="inlineStr">
         <is>
           <t>Maintenance Lead</t>
         </is>
@@ -11077,7 +11334,7 @@
     <row r="14" hidden="1">
       <c r="A14" s="726" t="n"/>
       <c r="B14" s="726" t="n"/>
-      <c r="C14" s="572" t="inlineStr">
+      <c r="C14" s="781" t="inlineStr">
         <is>
           <t>Commercial Owner</t>
         </is>
@@ -11448,6 +11705,7 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11502,7 +11760,7 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="413" t="n"/>
       <c r="B1" s="310" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -11557,291 +11815,296 @@
       <c r="AN1" s="627" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="B2" s="312" t="n"/>
-      <c r="C2" s="275" t="n"/>
-      <c r="G2" s="682" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="727" t="n"/>
+      <c r="C2" s="727" t="n"/>
+      <c r="D2" s="727" t="n"/>
+      <c r="E2" s="727" t="n"/>
+      <c r="F2" s="727" t="n"/>
+      <c r="G2" s="782" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="H2" s="683" t="inlineStr">
+      <c r="H2" s="783" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="I2" s="629" t="n"/>
-      <c r="J2" s="629" t="n"/>
-      <c r="K2" s="629" t="n"/>
-      <c r="L2" s="629" t="n"/>
-      <c r="M2" s="629" t="n"/>
-      <c r="N2" s="629" t="n"/>
-      <c r="O2" s="629" t="n"/>
-      <c r="P2" s="629" t="n"/>
-      <c r="Q2" s="629" t="n"/>
-      <c r="R2" s="629" t="n"/>
-      <c r="S2" s="629" t="n"/>
-      <c r="T2" s="629" t="n"/>
-      <c r="U2" s="629" t="n"/>
-      <c r="V2" s="629" t="n"/>
-      <c r="W2" s="629" t="n"/>
-      <c r="X2" s="629" t="n"/>
-      <c r="Y2" s="629" t="n"/>
-      <c r="Z2" s="629" t="n"/>
-      <c r="AA2" s="629" t="n"/>
-      <c r="AB2" s="629" t="n"/>
-      <c r="AC2" s="629" t="n"/>
-      <c r="AD2" s="629" t="n"/>
-      <c r="AE2" s="630" t="n"/>
-      <c r="AF2" s="630" t="n"/>
-      <c r="AG2" s="630" t="n"/>
-      <c r="AH2" s="630" t="n"/>
-      <c r="AI2" s="631" t="n"/>
-      <c r="AJ2" s="631" t="n"/>
-      <c r="AK2" s="631" t="n"/>
-      <c r="AL2" s="631" t="n"/>
-      <c r="AM2" s="631" t="n"/>
-      <c r="AN2" s="632" t="n"/>
+      <c r="I2" s="624" t="n"/>
+      <c r="J2" s="624" t="n"/>
+      <c r="K2" s="624" t="n"/>
+      <c r="L2" s="624" t="n"/>
+      <c r="M2" s="624" t="n"/>
+      <c r="N2" s="624" t="n"/>
+      <c r="O2" s="624" t="n"/>
+      <c r="P2" s="624" t="n"/>
+      <c r="Q2" s="624" t="n"/>
+      <c r="R2" s="624" t="n"/>
+      <c r="S2" s="624" t="n"/>
+      <c r="T2" s="624" t="n"/>
+      <c r="U2" s="624" t="n"/>
+      <c r="V2" s="624" t="n"/>
+      <c r="W2" s="624" t="n"/>
+      <c r="X2" s="624" t="n"/>
+      <c r="Y2" s="624" t="n"/>
+      <c r="Z2" s="624" t="n"/>
+      <c r="AA2" s="624" t="n"/>
+      <c r="AB2" s="624" t="n"/>
+      <c r="AC2" s="624" t="n"/>
+      <c r="AD2" s="729" t="n"/>
+      <c r="AE2" s="730" t="n"/>
+      <c r="AF2" s="730" t="n"/>
+      <c r="AG2" s="730" t="n"/>
+      <c r="AH2" s="731" t="n"/>
+      <c r="AI2" s="732" t="n"/>
+      <c r="AJ2" s="732" t="n"/>
+      <c r="AK2" s="732" t="n"/>
+      <c r="AL2" s="732" t="n"/>
+      <c r="AM2" s="732" t="n"/>
+      <c r="AN2" s="733" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="B3" s="312" t="n"/>
-      <c r="C3" s="275" t="n"/>
-      <c r="G3" s="682" t="inlineStr">
+      <c r="A3" s="734" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="599" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="H3" s="683" t="inlineStr">
+      <c r="H3" s="784" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I3" s="629" t="n"/>
-      <c r="J3" s="629" t="n"/>
-      <c r="K3" s="629" t="n"/>
-      <c r="L3" s="629" t="n"/>
-      <c r="M3" s="629" t="n"/>
-      <c r="N3" s="629" t="n"/>
-      <c r="O3" s="629" t="n"/>
-      <c r="P3" s="629" t="n"/>
-      <c r="Q3" s="629" t="n"/>
-      <c r="R3" s="629" t="n"/>
-      <c r="S3" s="629" t="n"/>
-      <c r="T3" s="629" t="n"/>
-      <c r="U3" s="629" t="n"/>
-      <c r="V3" s="629" t="n"/>
-      <c r="W3" s="629" t="n"/>
-      <c r="X3" s="629" t="n"/>
-      <c r="Y3" s="629" t="n"/>
-      <c r="Z3" s="629" t="n"/>
-      <c r="AA3" s="629" t="n"/>
-      <c r="AB3" s="629" t="n"/>
-      <c r="AC3" s="629" t="n"/>
-      <c r="AD3" s="629" t="n"/>
-      <c r="AE3" s="630" t="n"/>
-      <c r="AF3" s="630" t="n"/>
-      <c r="AG3" s="630" t="n"/>
-      <c r="AH3" s="630" t="n"/>
-      <c r="AI3" s="631" t="n"/>
-      <c r="AJ3" s="631" t="n"/>
-      <c r="AK3" s="631" t="n"/>
-      <c r="AL3" s="631" t="n"/>
-      <c r="AM3" s="631" t="n"/>
-      <c r="AN3" s="632" t="n"/>
+      <c r="I3" s="736" t="n"/>
+      <c r="J3" s="736" t="n"/>
+      <c r="K3" s="736" t="n"/>
+      <c r="L3" s="736" t="n"/>
+      <c r="M3" s="736" t="n"/>
+      <c r="N3" s="736" t="n"/>
+      <c r="O3" s="736" t="n"/>
+      <c r="P3" s="736" t="n"/>
+      <c r="Q3" s="736" t="n"/>
+      <c r="R3" s="736" t="n"/>
+      <c r="S3" s="736" t="n"/>
+      <c r="T3" s="736" t="n"/>
+      <c r="U3" s="736" t="n"/>
+      <c r="V3" s="736" t="n"/>
+      <c r="W3" s="736" t="n"/>
+      <c r="X3" s="736" t="n"/>
+      <c r="Y3" s="736" t="n"/>
+      <c r="Z3" s="736" t="n"/>
+      <c r="AA3" s="736" t="n"/>
+      <c r="AB3" s="736" t="n"/>
+      <c r="AC3" s="736" t="n"/>
+      <c r="AD3" s="737" t="n"/>
+      <c r="AE3" s="738" t="n"/>
+      <c r="AF3" s="738" t="n"/>
+      <c r="AG3" s="738" t="n"/>
+      <c r="AH3" s="739" t="n"/>
+      <c r="AI3" s="740" t="n"/>
+      <c r="AJ3" s="740" t="n"/>
+      <c r="AK3" s="740" t="n"/>
+      <c r="AL3" s="740" t="n"/>
+      <c r="AM3" s="740" t="n"/>
+      <c r="AN3" s="741" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="B4" s="312" t="n"/>
-      <c r="C4" s="633" t="inlineStr">
+      <c r="A4" s="734" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="529" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="G4" s="682" t="inlineStr">
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="599" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H4" s="683" t="inlineStr">
+      <c r="H4" s="784" t="inlineStr">
         <is>
           <t>QA / Customer Service</t>
         </is>
       </c>
-      <c r="I4" s="635" t="n"/>
-      <c r="J4" s="635" t="n"/>
-      <c r="K4" s="635" t="n"/>
-      <c r="L4" s="635" t="n"/>
-      <c r="M4" s="635" t="n"/>
-      <c r="N4" s="635" t="n"/>
-      <c r="O4" s="635" t="n"/>
-      <c r="P4" s="635" t="n"/>
-      <c r="Q4" s="635" t="n"/>
-      <c r="R4" s="635" t="n"/>
-      <c r="S4" s="635" t="n"/>
-      <c r="T4" s="635" t="n"/>
-      <c r="U4" s="635" t="n"/>
-      <c r="V4" s="635" t="n"/>
-      <c r="W4" s="635" t="n"/>
-      <c r="X4" s="635" t="n"/>
-      <c r="Y4" s="635" t="n"/>
-      <c r="Z4" s="635" t="n"/>
-      <c r="AA4" s="635" t="n"/>
-      <c r="AB4" s="635" t="n"/>
-      <c r="AC4" s="635" t="n"/>
-      <c r="AD4" s="635" t="n"/>
-      <c r="AE4" s="630" t="n"/>
-      <c r="AF4" s="630" t="n"/>
-      <c r="AG4" s="630" t="n"/>
-      <c r="AH4" s="630" t="n"/>
-      <c r="AI4" s="631" t="n"/>
-      <c r="AJ4" s="631" t="n"/>
-      <c r="AK4" s="631" t="n"/>
-      <c r="AL4" s="631" t="n"/>
-      <c r="AM4" s="631" t="n"/>
-      <c r="AN4" s="632" t="n"/>
+      <c r="I4" s="531" t="n"/>
+      <c r="J4" s="531" t="n"/>
+      <c r="K4" s="531" t="n"/>
+      <c r="L4" s="531" t="n"/>
+      <c r="M4" s="531" t="n"/>
+      <c r="N4" s="531" t="n"/>
+      <c r="O4" s="531" t="n"/>
+      <c r="P4" s="531" t="n"/>
+      <c r="Q4" s="531" t="n"/>
+      <c r="R4" s="531" t="n"/>
+      <c r="S4" s="531" t="n"/>
+      <c r="T4" s="531" t="n"/>
+      <c r="U4" s="531" t="n"/>
+      <c r="V4" s="531" t="n"/>
+      <c r="W4" s="531" t="n"/>
+      <c r="X4" s="531" t="n"/>
+      <c r="Y4" s="531" t="n"/>
+      <c r="Z4" s="531" t="n"/>
+      <c r="AA4" s="531" t="n"/>
+      <c r="AB4" s="531" t="n"/>
+      <c r="AC4" s="531" t="n"/>
+      <c r="AD4" s="742" t="n"/>
+      <c r="AE4" s="738" t="n"/>
+      <c r="AF4" s="738" t="n"/>
+      <c r="AG4" s="738" t="n"/>
+      <c r="AH4" s="739" t="n"/>
+      <c r="AI4" s="740" t="n"/>
+      <c r="AJ4" s="740" t="n"/>
+      <c r="AK4" s="740" t="n"/>
+      <c r="AL4" s="740" t="n"/>
+      <c r="AM4" s="740" t="n"/>
+      <c r="AN4" s="741" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="282" t="n"/>
-      <c r="B5" s="287" t="n"/>
-      <c r="C5" s="636" t="inlineStr">
+      <c r="A5" s="734" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="743" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="283" t="n"/>
-      <c r="E5" s="283" t="n"/>
-      <c r="F5" s="283" t="n"/>
-      <c r="G5" s="684" t="inlineStr">
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="599" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="H5" s="685" t="inlineStr">
+      <c r="H5" s="784" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
       </c>
-      <c r="I5" s="638" t="n"/>
-      <c r="J5" s="638" t="n"/>
-      <c r="K5" s="638" t="n"/>
-      <c r="L5" s="638" t="n"/>
-      <c r="M5" s="638" t="n"/>
-      <c r="N5" s="638" t="n"/>
-      <c r="O5" s="638" t="n"/>
-      <c r="P5" s="638" t="n"/>
-      <c r="Q5" s="638" t="n"/>
-      <c r="R5" s="638" t="n"/>
-      <c r="S5" s="638" t="n"/>
-      <c r="T5" s="638" t="n"/>
-      <c r="U5" s="638" t="n"/>
-      <c r="V5" s="638" t="n"/>
-      <c r="W5" s="638" t="n"/>
-      <c r="X5" s="638" t="n"/>
-      <c r="Y5" s="638" t="n"/>
-      <c r="Z5" s="638" t="n"/>
-      <c r="AA5" s="638" t="n"/>
-      <c r="AB5" s="638" t="n"/>
-      <c r="AC5" s="638" t="n"/>
-      <c r="AD5" s="638" t="n"/>
-      <c r="AE5" s="639" t="n"/>
-      <c r="AF5" s="639" t="n"/>
-      <c r="AG5" s="639" t="n"/>
-      <c r="AH5" s="639" t="n"/>
-      <c r="AI5" s="640" t="n"/>
-      <c r="AJ5" s="640" t="n"/>
-      <c r="AK5" s="640" t="n"/>
-      <c r="AL5" s="640" t="n"/>
-      <c r="AM5" s="640" t="n"/>
-      <c r="AN5" s="641" t="n"/>
+      <c r="I5" s="744" t="n"/>
+      <c r="J5" s="744" t="n"/>
+      <c r="K5" s="744" t="n"/>
+      <c r="L5" s="744" t="n"/>
+      <c r="M5" s="744" t="n"/>
+      <c r="N5" s="744" t="n"/>
+      <c r="O5" s="744" t="n"/>
+      <c r="P5" s="744" t="n"/>
+      <c r="Q5" s="744" t="n"/>
+      <c r="R5" s="744" t="n"/>
+      <c r="S5" s="744" t="n"/>
+      <c r="T5" s="744" t="n"/>
+      <c r="U5" s="744" t="n"/>
+      <c r="V5" s="744" t="n"/>
+      <c r="W5" s="744" t="n"/>
+      <c r="X5" s="744" t="n"/>
+      <c r="Y5" s="744" t="n"/>
+      <c r="Z5" s="744" t="n"/>
+      <c r="AA5" s="744" t="n"/>
+      <c r="AB5" s="744" t="n"/>
+      <c r="AC5" s="744" t="n"/>
+      <c r="AD5" s="745" t="n"/>
+      <c r="AE5" s="738" t="n"/>
+      <c r="AF5" s="738" t="n"/>
+      <c r="AG5" s="738" t="n"/>
+      <c r="AH5" s="739" t="n"/>
+      <c r="AI5" s="740" t="n"/>
+      <c r="AJ5" s="740" t="n"/>
+      <c r="AK5" s="740" t="n"/>
+      <c r="AL5" s="740" t="n"/>
+      <c r="AM5" s="740" t="n"/>
+      <c r="AN5" s="741" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="642" t="n"/>
-      <c r="B6" s="643" t="n"/>
-      <c r="C6" s="643" t="n"/>
-      <c r="D6" s="643" t="n"/>
-      <c r="E6" s="643" t="n"/>
-      <c r="F6" s="643" t="n"/>
-      <c r="G6" s="643" t="n"/>
-      <c r="H6" s="643" t="n"/>
-      <c r="I6" s="643" t="n"/>
-      <c r="J6" s="643" t="n"/>
-      <c r="K6" s="643" t="n"/>
-      <c r="L6" s="643" t="n"/>
-      <c r="M6" s="643" t="n"/>
-      <c r="N6" s="643" t="n"/>
-      <c r="O6" s="643" t="n"/>
-      <c r="P6" s="643" t="n"/>
-      <c r="Q6" s="643" t="n"/>
-      <c r="R6" s="643" t="n"/>
-      <c r="S6" s="643" t="n"/>
-      <c r="T6" s="643" t="n"/>
-      <c r="U6" s="643" t="n"/>
-      <c r="V6" s="643" t="n"/>
-      <c r="W6" s="643" t="n"/>
-      <c r="X6" s="643" t="n"/>
-      <c r="Y6" s="643" t="n"/>
-      <c r="Z6" s="643" t="n"/>
-      <c r="AA6" s="643" t="n"/>
-      <c r="AB6" s="643" t="n"/>
-      <c r="AC6" s="643" t="n"/>
-      <c r="AD6" s="643" t="n"/>
-      <c r="AE6" s="643" t="n"/>
-      <c r="AF6" s="643" t="n"/>
-      <c r="AG6" s="643" t="n"/>
-      <c r="AH6" s="643" t="n"/>
-      <c r="AI6" s="643" t="n"/>
-      <c r="AJ6" s="643" t="n"/>
-      <c r="AK6" s="643" t="n"/>
-      <c r="AL6" s="643" t="n"/>
-      <c r="AM6" s="643" t="n"/>
-      <c r="AN6" s="643" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="358" t="n"/>
+      <c r="B6" s="746" t="n"/>
+      <c r="C6" s="746" t="n"/>
+      <c r="D6" s="746" t="n"/>
+      <c r="E6" s="746" t="n"/>
+      <c r="F6" s="746" t="n"/>
+      <c r="G6" s="746" t="n"/>
+      <c r="H6" s="747" t="n"/>
+      <c r="I6" s="746" t="n"/>
+      <c r="J6" s="746" t="n"/>
+      <c r="K6" s="746" t="n"/>
+      <c r="L6" s="746" t="n"/>
+      <c r="M6" s="746" t="n"/>
+      <c r="N6" s="746" t="n"/>
+      <c r="O6" s="746" t="n"/>
+      <c r="P6" s="746" t="n"/>
+      <c r="Q6" s="746" t="n"/>
+      <c r="R6" s="746" t="n"/>
+      <c r="S6" s="746" t="n"/>
+      <c r="T6" s="746" t="n"/>
+      <c r="U6" s="746" t="n"/>
+      <c r="V6" s="746" t="n"/>
+      <c r="W6" s="746" t="n"/>
+      <c r="X6" s="746" t="n"/>
+      <c r="Y6" s="746" t="n"/>
+      <c r="Z6" s="746" t="n"/>
+      <c r="AA6" s="746" t="n"/>
+      <c r="AB6" s="746" t="n"/>
+      <c r="AC6" s="746" t="n"/>
+      <c r="AD6" s="747" t="n"/>
+      <c r="AE6" s="748" t="n"/>
+      <c r="AF6" s="748" t="n"/>
+      <c r="AG6" s="748" t="n"/>
+      <c r="AH6" s="749" t="n"/>
+      <c r="AI6" s="750" t="n"/>
+      <c r="AJ6" s="750" t="n"/>
+      <c r="AK6" s="750" t="n"/>
+      <c r="AL6" s="750" t="n"/>
+      <c r="AM6" s="750" t="n"/>
+      <c r="AN6" s="751" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="644" t="inlineStr">
-        <is>
-          <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
-        </is>
-      </c>
-      <c r="B7" s="289" t="n"/>
-      <c r="C7" s="289" t="n"/>
-      <c r="D7" s="289" t="n"/>
-      <c r="E7" s="289" t="n"/>
-      <c r="F7" s="289" t="n"/>
-      <c r="G7" s="289" t="n"/>
-      <c r="H7" s="289" t="n"/>
-      <c r="I7" s="645" t="n"/>
-      <c r="J7" s="645" t="n"/>
-      <c r="K7" s="645" t="n"/>
-      <c r="L7" s="645" t="n"/>
-      <c r="M7" s="645" t="n"/>
-      <c r="N7" s="645" t="n"/>
-      <c r="O7" s="645" t="n"/>
-      <c r="P7" s="645" t="n"/>
-      <c r="Q7" s="645" t="n"/>
-      <c r="R7" s="645" t="n"/>
-      <c r="S7" s="645" t="n"/>
-      <c r="T7" s="645" t="n"/>
-      <c r="U7" s="645" t="n"/>
-      <c r="V7" s="645" t="n"/>
-      <c r="W7" s="645" t="n"/>
-      <c r="X7" s="645" t="n"/>
-      <c r="Y7" s="645" t="n"/>
-      <c r="Z7" s="645" t="n"/>
-      <c r="AA7" s="645" t="n"/>
-      <c r="AB7" s="645" t="n"/>
-      <c r="AC7" s="645" t="n"/>
-      <c r="AD7" s="645" t="n"/>
-      <c r="AE7" s="645" t="n"/>
-      <c r="AF7" s="645" t="n"/>
-      <c r="AG7" s="645" t="n"/>
-      <c r="AH7" s="645" t="n"/>
-      <c r="AI7" s="645" t="n"/>
-      <c r="AJ7" s="645" t="n"/>
-      <c r="AK7" s="645" t="n"/>
-      <c r="AL7" s="645" t="n"/>
-      <c r="AM7" s="645" t="n"/>
-      <c r="AN7" s="646" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="752" t="n"/>
+      <c r="B7" s="753" t="n"/>
+      <c r="C7" s="753" t="n"/>
+      <c r="D7" s="753" t="n"/>
+      <c r="E7" s="753" t="n"/>
+      <c r="F7" s="753" t="n"/>
+      <c r="G7" s="753" t="n"/>
+      <c r="H7" s="753" t="n"/>
+      <c r="I7" s="752" t="n"/>
+      <c r="J7" s="752" t="n"/>
+      <c r="K7" s="752" t="n"/>
+      <c r="L7" s="752" t="n"/>
+      <c r="M7" s="752" t="n"/>
+      <c r="N7" s="752" t="n"/>
+      <c r="O7" s="752" t="n"/>
+      <c r="P7" s="752" t="n"/>
+      <c r="Q7" s="752" t="n"/>
+      <c r="R7" s="752" t="n"/>
+      <c r="S7" s="752" t="n"/>
+      <c r="T7" s="752" t="n"/>
+      <c r="U7" s="752" t="n"/>
+      <c r="V7" s="752" t="n"/>
+      <c r="W7" s="752" t="n"/>
+      <c r="X7" s="752" t="n"/>
+      <c r="Y7" s="752" t="n"/>
+      <c r="Z7" s="752" t="n"/>
+      <c r="AA7" s="752" t="n"/>
+      <c r="AB7" s="752" t="n"/>
+      <c r="AC7" s="752" t="n"/>
+      <c r="AD7" s="752" t="n"/>
+      <c r="AE7" s="752" t="n"/>
+      <c r="AF7" s="752" t="n"/>
+      <c r="AG7" s="752" t="n"/>
+      <c r="AH7" s="752" t="n"/>
+      <c r="AI7" s="752" t="n"/>
+      <c r="AJ7" s="752" t="n"/>
+      <c r="AK7" s="752" t="n"/>
+      <c r="AL7" s="752" t="n"/>
+      <c r="AM7" s="752" t="n"/>
+      <c r="AN7" s="752" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="691" t="inlineStr">
@@ -12135,13 +12398,13 @@
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="664" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
+      <c r="B13" s="665" t="n"/>
+      <c r="C13" s="665" t="n"/>
+      <c r="D13" s="665" t="n"/>
+      <c r="E13" s="665" t="n"/>
+      <c r="F13" s="665" t="n"/>
+      <c r="G13" s="665" t="n"/>
+      <c r="H13" s="665" t="n"/>
       <c r="I13" s="665" t="n"/>
       <c r="J13" s="665" t="n"/>
       <c r="K13" s="665" t="n"/>
@@ -12744,50 +13007,50 @@
       <c r="AN25" s="667" t="n"/>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="704" t="inlineStr">
+      <c r="A26" s="407" t="inlineStr">
         <is>
           <t>NOTICE  —  Periodic review and closeout support sheet for the rolling workbook.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B26" s="705" t="n"/>
-      <c r="C26" s="705" t="n"/>
-      <c r="D26" s="705" t="n"/>
-      <c r="E26" s="705" t="n"/>
-      <c r="F26" s="705" t="n"/>
-      <c r="G26" s="705" t="n"/>
-      <c r="H26" s="705" t="n"/>
-      <c r="I26" s="705" t="n"/>
-      <c r="J26" s="705" t="n"/>
-      <c r="K26" s="705" t="n"/>
-      <c r="L26" s="705" t="n"/>
-      <c r="M26" s="705" t="n"/>
-      <c r="N26" s="705" t="n"/>
-      <c r="O26" s="705" t="n"/>
-      <c r="P26" s="705" t="n"/>
-      <c r="Q26" s="705" t="n"/>
-      <c r="R26" s="705" t="n"/>
-      <c r="S26" s="705" t="n"/>
-      <c r="T26" s="705" t="n"/>
-      <c r="U26" s="705" t="n"/>
-      <c r="V26" s="705" t="n"/>
-      <c r="W26" s="705" t="n"/>
-      <c r="X26" s="705" t="n"/>
-      <c r="Y26" s="705" t="n"/>
-      <c r="Z26" s="705" t="n"/>
-      <c r="AA26" s="705" t="n"/>
-      <c r="AB26" s="705" t="n"/>
-      <c r="AC26" s="705" t="n"/>
-      <c r="AD26" s="705" t="n"/>
-      <c r="AE26" s="705" t="n"/>
-      <c r="AF26" s="705" t="n"/>
-      <c r="AG26" s="705" t="n"/>
-      <c r="AH26" s="705" t="n"/>
-      <c r="AI26" s="705" t="n"/>
-      <c r="AJ26" s="705" t="n"/>
-      <c r="AK26" s="705" t="n"/>
-      <c r="AL26" s="705" t="n"/>
-      <c r="AM26" s="705" t="n"/>
-      <c r="AN26" s="706" t="n"/>
+      <c r="B26" s="408" t="n"/>
+      <c r="C26" s="408" t="n"/>
+      <c r="D26" s="408" t="n"/>
+      <c r="E26" s="408" t="n"/>
+      <c r="F26" s="408" t="n"/>
+      <c r="G26" s="408" t="n"/>
+      <c r="H26" s="408" t="n"/>
+      <c r="I26" s="408" t="n"/>
+      <c r="J26" s="408" t="n"/>
+      <c r="K26" s="408" t="n"/>
+      <c r="L26" s="408" t="n"/>
+      <c r="M26" s="408" t="n"/>
+      <c r="N26" s="408" t="n"/>
+      <c r="O26" s="408" t="n"/>
+      <c r="P26" s="408" t="n"/>
+      <c r="Q26" s="408" t="n"/>
+      <c r="R26" s="408" t="n"/>
+      <c r="S26" s="408" t="n"/>
+      <c r="T26" s="408" t="n"/>
+      <c r="U26" s="408" t="n"/>
+      <c r="V26" s="408" t="n"/>
+      <c r="W26" s="408" t="n"/>
+      <c r="X26" s="408" t="n"/>
+      <c r="Y26" s="408" t="n"/>
+      <c r="Z26" s="408" t="n"/>
+      <c r="AA26" s="408" t="n"/>
+      <c r="AB26" s="408" t="n"/>
+      <c r="AC26" s="408" t="n"/>
+      <c r="AD26" s="408" t="n"/>
+      <c r="AE26" s="408" t="n"/>
+      <c r="AF26" s="408" t="n"/>
+      <c r="AG26" s="408" t="n"/>
+      <c r="AH26" s="408" t="n"/>
+      <c r="AI26" s="408" t="n"/>
+      <c r="AJ26" s="408" t="n"/>
+      <c r="AK26" s="408" t="n"/>
+      <c r="AL26" s="408" t="n"/>
+      <c r="AM26" s="408" t="n"/>
+      <c r="AN26" s="409" t="n"/>
     </row>
     <row r="27" hidden="1" outlineLevel="1"/>
     <row r="28" hidden="1" outlineLevel="1"/>
@@ -13074,326 +13337,322 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="707" t="n"/>
-      <c r="B1" s="708" t="n"/>
-      <c r="C1" s="708" t="n"/>
-      <c r="D1" s="708" t="n"/>
-      <c r="E1" s="708" t="n"/>
-      <c r="F1" s="708" t="n"/>
-      <c r="G1" s="708" t="n"/>
-      <c r="H1" s="709" t="n"/>
-      <c r="I1" s="710" t="inlineStr"/>
-      <c r="J1" s="708" t="n"/>
-      <c r="K1" s="708" t="n"/>
-      <c r="L1" s="708" t="n"/>
-      <c r="M1" s="708" t="n"/>
-      <c r="N1" s="708" t="n"/>
-      <c r="O1" s="708" t="n"/>
-      <c r="P1" s="708" t="n"/>
-      <c r="Q1" s="708" t="n"/>
-      <c r="R1" s="708" t="n"/>
-      <c r="S1" s="708" t="n"/>
-      <c r="T1" s="708" t="n"/>
-      <c r="U1" s="708" t="n"/>
-      <c r="V1" s="708" t="n"/>
-      <c r="W1" s="708" t="n"/>
-      <c r="X1" s="708" t="n"/>
-      <c r="Y1" s="708" t="n"/>
-      <c r="Z1" s="708" t="n"/>
-      <c r="AA1" s="708" t="n"/>
-      <c r="AB1" s="708" t="n"/>
-      <c r="AC1" s="708" t="n"/>
-      <c r="AD1" s="709" t="n"/>
-      <c r="AE1" s="513" t="inlineStr">
+    <row r="1" hidden="1">
+      <c r="A1" s="754" t="n"/>
+      <c r="B1" s="690" t="n"/>
+      <c r="C1" s="690" t="n"/>
+      <c r="D1" s="690" t="n"/>
+      <c r="E1" s="690" t="n"/>
+      <c r="F1" s="690" t="n"/>
+      <c r="G1" s="690" t="n"/>
+      <c r="H1" s="755" t="n"/>
+      <c r="I1" s="756" t="inlineStr"/>
+      <c r="J1" s="690" t="n"/>
+      <c r="K1" s="690" t="n"/>
+      <c r="L1" s="690" t="n"/>
+      <c r="M1" s="690" t="n"/>
+      <c r="N1" s="690" t="n"/>
+      <c r="O1" s="690" t="n"/>
+      <c r="P1" s="690" t="n"/>
+      <c r="Q1" s="690" t="n"/>
+      <c r="R1" s="690" t="n"/>
+      <c r="S1" s="690" t="n"/>
+      <c r="T1" s="690" t="n"/>
+      <c r="U1" s="690" t="n"/>
+      <c r="V1" s="690" t="n"/>
+      <c r="W1" s="690" t="n"/>
+      <c r="X1" s="690" t="n"/>
+      <c r="Y1" s="690" t="n"/>
+      <c r="Z1" s="690" t="n"/>
+      <c r="AA1" s="690" t="n"/>
+      <c r="AB1" s="690" t="n"/>
+      <c r="AC1" s="690" t="n"/>
+      <c r="AD1" s="755" t="n"/>
+      <c r="AE1" s="514" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="708" t="n"/>
-      <c r="AG1" s="708" t="n"/>
-      <c r="AH1" s="711" t="n"/>
-      <c r="AI1" s="516" t="n"/>
-      <c r="AJ1" s="708" t="n"/>
-      <c r="AK1" s="708" t="n"/>
-      <c r="AL1" s="708" t="n"/>
-      <c r="AM1" s="708" t="n"/>
-      <c r="AN1" s="709" t="n"/>
+      <c r="AF1" s="690" t="n"/>
+      <c r="AG1" s="690" t="n"/>
+      <c r="AH1" s="757" t="n"/>
+      <c r="AI1" s="517" t="n"/>
+      <c r="AJ1" s="690" t="n"/>
+      <c r="AK1" s="690" t="n"/>
+      <c r="AL1" s="690" t="n"/>
+      <c r="AM1" s="690" t="n"/>
+      <c r="AN1" s="755" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="712" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="713" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="713" t="n"/>
-      <c r="AE2" s="714" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="727" t="n"/>
+      <c r="C2" s="727" t="n"/>
+      <c r="D2" s="727" t="n"/>
+      <c r="E2" s="727" t="n"/>
+      <c r="F2" s="727" t="n"/>
+      <c r="G2" s="727" t="n"/>
+      <c r="H2" s="728" t="n"/>
+      <c r="I2" s="727" t="n"/>
+      <c r="J2" s="727" t="n"/>
+      <c r="K2" s="727" t="n"/>
+      <c r="L2" s="727" t="n"/>
+      <c r="M2" s="727" t="n"/>
+      <c r="N2" s="727" t="n"/>
+      <c r="O2" s="727" t="n"/>
+      <c r="P2" s="727" t="n"/>
+      <c r="Q2" s="727" t="n"/>
+      <c r="R2" s="727" t="n"/>
+      <c r="S2" s="727" t="n"/>
+      <c r="T2" s="727" t="n"/>
+      <c r="U2" s="727" t="n"/>
+      <c r="V2" s="727" t="n"/>
+      <c r="W2" s="727" t="n"/>
+      <c r="X2" s="727" t="n"/>
+      <c r="Y2" s="727" t="n"/>
+      <c r="Z2" s="727" t="n"/>
+      <c r="AA2" s="727" t="n"/>
+      <c r="AB2" s="727" t="n"/>
+      <c r="AC2" s="727" t="n"/>
+      <c r="AD2" s="728" t="n"/>
+      <c r="AE2" s="758" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="10" t="n"/>
-      <c r="AG2" s="10" t="n"/>
-      <c r="AH2" s="715" t="n"/>
-      <c r="AI2" s="716" t="n"/>
-      <c r="AJ2" s="10" t="n"/>
-      <c r="AK2" s="10" t="n"/>
-      <c r="AL2" s="10" t="n"/>
-      <c r="AM2" s="10" t="n"/>
-      <c r="AN2" s="713" t="n"/>
+      <c r="AF2" s="759" t="n"/>
+      <c r="AG2" s="759" t="n"/>
+      <c r="AH2" s="760" t="n"/>
+      <c r="AI2" s="732" t="n"/>
+      <c r="AJ2" s="761" t="n"/>
+      <c r="AK2" s="761" t="n"/>
+      <c r="AL2" s="761" t="n"/>
+      <c r="AM2" s="761" t="n"/>
+      <c r="AN2" s="762" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="712" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="713" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="713" t="n"/>
-      <c r="AE3" s="714" t="inlineStr">
+      <c r="A3" s="734" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="735" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="735" t="n"/>
+      <c r="AE3" s="763" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="10" t="n"/>
-      <c r="AH3" s="715" t="n"/>
-      <c r="AI3" s="716" t="n"/>
-      <c r="AJ3" s="10" t="n"/>
-      <c r="AK3" s="10" t="n"/>
-      <c r="AL3" s="10" t="n"/>
-      <c r="AM3" s="10" t="n"/>
-      <c r="AN3" s="713" t="n"/>
+      <c r="AF3" s="764" t="n"/>
+      <c r="AG3" s="764" t="n"/>
+      <c r="AH3" s="765" t="n"/>
+      <c r="AI3" s="740" t="n"/>
+      <c r="AJ3" s="766" t="n"/>
+      <c r="AK3" s="766" t="n"/>
+      <c r="AL3" s="766" t="n"/>
+      <c r="AM3" s="766" t="n"/>
+      <c r="AN3" s="767" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="712" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="713" t="n"/>
-      <c r="I4" s="717" t="inlineStr"/>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="713" t="n"/>
-      <c r="AE4" s="714" t="inlineStr">
+      <c r="A4" s="734" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="735" t="n"/>
+      <c r="I4" s="768" t="inlineStr"/>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="735" t="n"/>
+      <c r="AE4" s="763" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="10" t="n"/>
-      <c r="AG4" s="10" t="n"/>
-      <c r="AH4" s="715" t="n"/>
-      <c r="AI4" s="716" t="n"/>
-      <c r="AJ4" s="10" t="n"/>
-      <c r="AK4" s="10" t="n"/>
-      <c r="AL4" s="10" t="n"/>
-      <c r="AM4" s="10" t="n"/>
-      <c r="AN4" s="713" t="n"/>
+      <c r="AF4" s="764" t="n"/>
+      <c r="AG4" s="764" t="n"/>
+      <c r="AH4" s="765" t="n"/>
+      <c r="AI4" s="740" t="n"/>
+      <c r="AJ4" s="766" t="n"/>
+      <c r="AK4" s="766" t="n"/>
+      <c r="AL4" s="766" t="n"/>
+      <c r="AM4" s="766" t="n"/>
+      <c r="AN4" s="767" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="718" t="n"/>
-      <c r="B5" s="719" t="n"/>
-      <c r="C5" s="719" t="n"/>
-      <c r="D5" s="719" t="n"/>
-      <c r="E5" s="719" t="n"/>
-      <c r="F5" s="719" t="n"/>
-      <c r="G5" s="719" t="n"/>
-      <c r="H5" s="720" t="n"/>
-      <c r="I5" s="721" t="inlineStr"/>
-      <c r="J5" s="719" t="n"/>
-      <c r="K5" s="719" t="n"/>
-      <c r="L5" s="719" t="n"/>
-      <c r="M5" s="719" t="n"/>
-      <c r="N5" s="719" t="n"/>
-      <c r="O5" s="719" t="n"/>
-      <c r="P5" s="719" t="n"/>
-      <c r="Q5" s="719" t="n"/>
-      <c r="R5" s="719" t="n"/>
-      <c r="S5" s="719" t="n"/>
-      <c r="T5" s="719" t="n"/>
-      <c r="U5" s="719" t="n"/>
-      <c r="V5" s="719" t="n"/>
-      <c r="W5" s="719" t="n"/>
-      <c r="X5" s="719" t="n"/>
-      <c r="Y5" s="719" t="n"/>
-      <c r="Z5" s="719" t="n"/>
-      <c r="AA5" s="719" t="n"/>
-      <c r="AB5" s="719" t="n"/>
-      <c r="AC5" s="719" t="n"/>
-      <c r="AD5" s="720" t="n"/>
-      <c r="AE5" s="722" t="inlineStr">
+      <c r="A5" s="734" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="735" t="n"/>
+      <c r="I5" s="769" t="inlineStr"/>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="735" t="n"/>
+      <c r="AE5" s="763" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="719" t="n"/>
-      <c r="AG5" s="719" t="n"/>
-      <c r="AH5" s="723" t="n"/>
-      <c r="AI5" s="724" t="n"/>
-      <c r="AJ5" s="719" t="n"/>
-      <c r="AK5" s="719" t="n"/>
-      <c r="AL5" s="719" t="n"/>
-      <c r="AM5" s="719" t="n"/>
-      <c r="AN5" s="720" t="n"/>
+      <c r="AF5" s="764" t="n"/>
+      <c r="AG5" s="764" t="n"/>
+      <c r="AH5" s="765" t="n"/>
+      <c r="AI5" s="740" t="n"/>
+      <c r="AJ5" s="766" t="n"/>
+      <c r="AK5" s="766" t="n"/>
+      <c r="AL5" s="766" t="n"/>
+      <c r="AM5" s="766" t="n"/>
+      <c r="AN5" s="767" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="725" t="n"/>
-      <c r="B6" s="725" t="n"/>
-      <c r="C6" s="725" t="n"/>
-      <c r="D6" s="725" t="n"/>
-      <c r="E6" s="725" t="n"/>
-      <c r="F6" s="725" t="n"/>
-      <c r="G6" s="725" t="n"/>
-      <c r="H6" s="725" t="n"/>
-      <c r="I6" s="725" t="n"/>
-      <c r="J6" s="725" t="n"/>
-      <c r="K6" s="725" t="n"/>
-      <c r="L6" s="725" t="n"/>
-      <c r="M6" s="725" t="n"/>
-      <c r="N6" s="725" t="n"/>
-      <c r="O6" s="725" t="n"/>
-      <c r="P6" s="725" t="n"/>
-      <c r="Q6" s="725" t="n"/>
-      <c r="R6" s="725" t="n"/>
-      <c r="S6" s="725" t="n"/>
-      <c r="T6" s="725" t="n"/>
-      <c r="U6" s="725" t="n"/>
-      <c r="V6" s="725" t="n"/>
-      <c r="W6" s="725" t="n"/>
-      <c r="X6" s="725" t="n"/>
-      <c r="Y6" s="725" t="n"/>
-      <c r="Z6" s="725" t="n"/>
-      <c r="AA6" s="725" t="n"/>
-      <c r="AB6" s="725" t="n"/>
-      <c r="AC6" s="725" t="n"/>
-      <c r="AD6" s="725" t="n"/>
-      <c r="AE6" s="725" t="n"/>
-      <c r="AF6" s="725" t="n"/>
-      <c r="AG6" s="725" t="n"/>
-      <c r="AH6" s="725" t="n"/>
-      <c r="AI6" s="725" t="n"/>
-      <c r="AJ6" s="725" t="n"/>
-      <c r="AK6" s="725" t="n"/>
-      <c r="AL6" s="725" t="n"/>
-      <c r="AM6" s="725" t="n"/>
-      <c r="AN6" s="725" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="770" t="n"/>
+      <c r="B6" s="771" t="n"/>
+      <c r="C6" s="771" t="n"/>
+      <c r="D6" s="771" t="n"/>
+      <c r="E6" s="771" t="n"/>
+      <c r="F6" s="771" t="n"/>
+      <c r="G6" s="771" t="n"/>
+      <c r="H6" s="772" t="n"/>
+      <c r="I6" s="771" t="n"/>
+      <c r="J6" s="771" t="n"/>
+      <c r="K6" s="771" t="n"/>
+      <c r="L6" s="771" t="n"/>
+      <c r="M6" s="771" t="n"/>
+      <c r="N6" s="771" t="n"/>
+      <c r="O6" s="771" t="n"/>
+      <c r="P6" s="771" t="n"/>
+      <c r="Q6" s="771" t="n"/>
+      <c r="R6" s="771" t="n"/>
+      <c r="S6" s="771" t="n"/>
+      <c r="T6" s="771" t="n"/>
+      <c r="U6" s="771" t="n"/>
+      <c r="V6" s="771" t="n"/>
+      <c r="W6" s="771" t="n"/>
+      <c r="X6" s="771" t="n"/>
+      <c r="Y6" s="771" t="n"/>
+      <c r="Z6" s="771" t="n"/>
+      <c r="AA6" s="771" t="n"/>
+      <c r="AB6" s="771" t="n"/>
+      <c r="AC6" s="771" t="n"/>
+      <c r="AD6" s="772" t="n"/>
+      <c r="AE6" s="773" t="n"/>
+      <c r="AF6" s="773" t="n"/>
+      <c r="AG6" s="773" t="n"/>
+      <c r="AH6" s="774" t="n"/>
+      <c r="AI6" s="775" t="n"/>
+      <c r="AJ6" s="775" t="n"/>
+      <c r="AK6" s="775" t="n"/>
+      <c r="AL6" s="775" t="n"/>
+      <c r="AM6" s="775" t="n"/>
+      <c r="AN6" s="776" t="n"/>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="606" t="inlineStr">
-        <is>
-          <t>REF_LINKS</t>
-        </is>
-      </c>
-      <c r="B7" s="690" t="n"/>
-      <c r="C7" s="690" t="n"/>
-      <c r="D7" s="690" t="n"/>
-      <c r="E7" s="690" t="n"/>
-      <c r="F7" s="690" t="n"/>
-      <c r="G7" s="690" t="n"/>
-      <c r="H7" s="726" t="n"/>
-      <c r="I7" s="726" t="n"/>
-      <c r="J7" s="726" t="n"/>
-      <c r="K7" s="726" t="n"/>
-      <c r="L7" s="726" t="n"/>
-      <c r="M7" s="726" t="n"/>
-      <c r="N7" s="726" t="n"/>
-      <c r="O7" s="726" t="n"/>
-      <c r="P7" s="726" t="n"/>
-      <c r="Q7" s="726" t="n"/>
-      <c r="R7" s="726" t="n"/>
-      <c r="S7" s="726" t="n"/>
-      <c r="T7" s="726" t="n"/>
-      <c r="U7" s="726" t="n"/>
-      <c r="V7" s="726" t="n"/>
-      <c r="W7" s="726" t="n"/>
-      <c r="X7" s="726" t="n"/>
-      <c r="Y7" s="726" t="n"/>
-      <c r="Z7" s="726" t="n"/>
-      <c r="AA7" s="726" t="n"/>
-      <c r="AB7" s="726" t="n"/>
-      <c r="AC7" s="726" t="n"/>
-      <c r="AD7" s="726" t="n"/>
-      <c r="AE7" s="726" t="n"/>
-      <c r="AF7" s="726" t="n"/>
-      <c r="AG7" s="726" t="n"/>
-      <c r="AH7" s="726" t="n"/>
-      <c r="AI7" s="726" t="n"/>
-      <c r="AJ7" s="726" t="n"/>
-      <c r="AK7" s="726" t="n"/>
-      <c r="AL7" s="726" t="n"/>
-      <c r="AM7" s="726" t="n"/>
-      <c r="AN7" s="726" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="785" t="n"/>
+      <c r="B7" s="753" t="n"/>
+      <c r="C7" s="753" t="n"/>
+      <c r="D7" s="753" t="n"/>
+      <c r="E7" s="753" t="n"/>
+      <c r="F7" s="753" t="n"/>
+      <c r="G7" s="753" t="n"/>
+      <c r="H7" s="778" t="n"/>
+      <c r="I7" s="778" t="n"/>
+      <c r="J7" s="778" t="n"/>
+      <c r="K7" s="778" t="n"/>
+      <c r="L7" s="778" t="n"/>
+      <c r="M7" s="778" t="n"/>
+      <c r="N7" s="778" t="n"/>
+      <c r="O7" s="778" t="n"/>
+      <c r="P7" s="778" t="n"/>
+      <c r="Q7" s="778" t="n"/>
+      <c r="R7" s="778" t="n"/>
+      <c r="S7" s="778" t="n"/>
+      <c r="T7" s="778" t="n"/>
+      <c r="U7" s="778" t="n"/>
+      <c r="V7" s="778" t="n"/>
+      <c r="W7" s="778" t="n"/>
+      <c r="X7" s="778" t="n"/>
+      <c r="Y7" s="778" t="n"/>
+      <c r="Z7" s="778" t="n"/>
+      <c r="AA7" s="778" t="n"/>
+      <c r="AB7" s="778" t="n"/>
+      <c r="AC7" s="778" t="n"/>
+      <c r="AD7" s="778" t="n"/>
+      <c r="AE7" s="778" t="n"/>
+      <c r="AF7" s="778" t="n"/>
+      <c r="AG7" s="778" t="n"/>
+      <c r="AH7" s="778" t="n"/>
+      <c r="AI7" s="778" t="n"/>
+      <c r="AJ7" s="778" t="n"/>
+      <c r="AK7" s="778" t="n"/>
+      <c r="AL7" s="778" t="n"/>
+      <c r="AM7" s="778" t="n"/>
+      <c r="AN7" s="778" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="608" t="inlineStr">
+      <c r="A8" s="786" t="inlineStr">
         <is>
           <t>Reference Epicor / M365 / controlled documents only.</t>
         </is>
@@ -13433,7 +13692,7 @@
       <c r="AN8" s="726" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="610" t="inlineStr">
+      <c r="A9" s="787" t="inlineStr">
         <is>
           <t>Ref Type</t>
         </is>

--- a/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
@@ -4963,6 +4963,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4993,6 +4996,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5023,6 +5029,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7480,6 +7489,7 @@
       <c r="G24" s="387" t="n"/>
       <c r="H24" s="388" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="423" t="inlineStr">
         <is>

--- a/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
@@ -4,10 +4,10 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM-213_LOG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVIEW" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="veryHidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVIEW" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_STATUS_CORE">'_LISTS'!$A$2:$A$7</definedName>
@@ -7489,7 +7489,6 @@
       <c r="G24" s="387" t="n"/>
       <c r="H24" s="388" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="423" t="inlineStr">
         <is>

--- a/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
@@ -4,10 +4,11 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM-213_LOG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="veryHidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVIEW" sheetId="4" state="veryHidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="5" state="veryHidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVIEW" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REV_HISTORY" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_STATUS_CORE">'_LISTS'!$A$2:$A$7</definedName>
@@ -4945,11 +4946,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>161925</colOff>
+      <colOff>219075</colOff>
       <row>0</row>
-      <rowOff>314325</rowOff>
+      <rowOff>257175</rowOff>
     </from>
-    <ext cx="1123950" cy="323850"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -4978,44 +4979,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>161925</colOff>
+      <colOff>219075</colOff>
       <row>0</row>
-      <rowOff>314325</rowOff>
+      <rowOff>257175</rowOff>
     </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -5269,7 +5237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:AW47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.64" customWidth="1" min="1" max="1"/>
@@ -5504,7 +5472,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="418" t="inlineStr">
         <is>
-          <t>Review Date</t>
+          <t>Linked FRM-211 / FRM-651</t>
         </is>
       </c>
       <c r="B12" s="290" t="n"/>
@@ -5513,11 +5481,15 @@
       <c r="E12" s="290" t="n"/>
       <c r="F12" s="418" t="inlineStr">
         <is>
-          <t>Record Status</t>
+          <t>Ref: SOP-201</t>
         </is>
       </c>
       <c r="G12" s="290" t="n"/>
-      <c r="H12" s="419" t="inlineStr"/>
+      <c r="H12" s="419" t="inlineStr">
+        <is>
+          <t>Retain: 10 years per QMS schedule</t>
+        </is>
+      </c>
       <c r="I12" s="289" t="n"/>
       <c r="J12" s="290" t="n"/>
     </row>
@@ -8098,9 +8070,88 @@
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial release</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QMS Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cross-ref: FRM-211, FRM-651; Parent ref: SOP-201</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QMS Upgrade</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/02-FRM-200/FRM-213_RMA_Tracking_Log.xlsx
@@ -757,7 +757,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="245">
+  <borders count="246">
     <border>
       <left/>
       <right/>
@@ -3511,12 +3511,16 @@
         <color rgb="000078D4"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="494">
+  <cellXfs count="495">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -4707,6 +4711,7 @@
     <xf numFmtId="0" fontId="82" fillId="48" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="245" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4783,6 +4788,60 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="E9" authorId="0" shapeId="0">
+      <text>
+        <t>Ngày RMA
+Ngày nhận yêu cầu trả hàng. Format: YYYY-MM-DD.</t>
+      </text>
+    </comment>
+    <comment ref="M9" authorId="0" shapeId="0">
+      <text>
+        <t>Khách hàng
+Khách hàng trả hàng.</t>
+      </text>
+    </comment>
+    <comment ref="W9" authorId="0" shapeId="0">
+      <text>
+        <t>Chi tiết / Số lượng
+Mã part và số lượng trả về.
+Ví dụ: HES-1234 x 5 pcs</t>
+      </text>
+    </comment>
+    <comment ref="AG9" authorId="0" shapeId="0">
+      <text>
+        <t>Lý do
+Lý do trả hàng.
+Ví dụ: Out of tolerance, surface damage, wrong revision.</t>
+      </text>
+    </comment>
+    <comment ref="AQ9" authorId="0" shapeId="0">
+      <text>
+        <t>Trạng thái
+OPEN = đang xử lý.
+RECEIVED = đã nhận hàng trả.
+INVESTIGATING = đang điều tra.
+CLOSED = đã giải quyết.</t>
+      </text>
+    </comment>
+    <comment ref="AY9" authorId="0" shapeId="0">
+      <text>
+        <t>Quyết định
+REWORK = sửa lại.
+REPLACE = làm mới thay thế.
+CREDIT = hoàn tiền.
+REJECT RMA = từ chối trả hàng.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -4806,6 +4865,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5417,7 +5479,7 @@
       <c r="BD6" s="30" t="n"/>
     </row>
     <row r="7" ht="4" customHeight="1" s="264">
-      <c r="A7" s="469" t="n"/>
+      <c r="A7" s="494" t="n"/>
       <c r="B7" s="26" t="n"/>
       <c r="C7" s="26" t="n"/>
       <c r="D7" s="26" t="n"/>
@@ -6823,7 +6885,7 @@
       <c r="BD29" s="492" t="n"/>
     </row>
     <row r="30" ht="4" customHeight="1" s="264">
-      <c r="A30" s="469" t="n"/>
+      <c r="A30" s="494" t="n"/>
       <c r="B30" s="26" t="n"/>
       <c r="C30" s="26" t="n"/>
       <c r="D30" s="26" t="n"/>
@@ -6883,7 +6945,7 @@
     <row r="31" ht="24" customHeight="1" s="264">
       <c r="A31" s="493" t="inlineStr">
         <is>
-          <t>NOTICE — Ref: SOP-201. Retain: 10 years.</t>
+          <t>NOTICE — Track all customer returns. Link to NCR (FRM-651) for root cause investigation. Ref: SOP-201. Retain: 10 years.</t>
         </is>
       </c>
       <c r="B31" s="471" t="n"/>
@@ -6989,8 +7051,8 @@
     <mergeCell ref="AY23:BD23"/>
     <mergeCell ref="M15:V15"/>
     <mergeCell ref="AY13:BD13"/>
+    <mergeCell ref="M28:V28"/>
     <mergeCell ref="W12:AF12"/>
-    <mergeCell ref="M28:V28"/>
     <mergeCell ref="W21:AF21"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A22:D22"/>
@@ -7046,9 +7108,9 @@
     <mergeCell ref="W29:AF29"/>
     <mergeCell ref="W23:AF23"/>
     <mergeCell ref="AG14:AP14"/>
+    <mergeCell ref="A30:BD30"/>
+    <mergeCell ref="AW4:BD4"/>
     <mergeCell ref="M21:V21"/>
-    <mergeCell ref="AW4:BD4"/>
-    <mergeCell ref="A30:BD30"/>
     <mergeCell ref="AG23:AP23"/>
     <mergeCell ref="W13:AF13"/>
     <mergeCell ref="AQ21:AX21"/>
@@ -7113,6 +7175,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
